--- a/Другое/2026/Доходы-Расходы_copy.xlsx
+++ b/Другое/2026/Доходы-Расходы_copy.xlsx
@@ -3850,6 +3850,127 @@
           </rPr>
           <t xml:space="preserve">
 Долями - за журнальчик орнамент</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="T16" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Простава на работе</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="T17" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Снять квартиру в мск</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="U17" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Билеты на электричку
+туда-обратно</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="V17" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Подарок кулику</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="T18" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Покушать и погулять в МСК</t>
         </r>
       </text>
     </comment>
@@ -4288,7 +4409,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="20">
+  <fills count="21">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -4400,6 +4521,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF062D4E"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -4604,7 +4731,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="109">
+  <cellXfs count="110">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4794,6 +4921,25 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="29" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="29" fillId="19" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="29" fillId="19" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="23" fillId="19" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="31" fillId="19" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="31" fillId="19" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="19" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4839,25 +4985,6 @@
     <xf numFmtId="0" fontId="31" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="29" fillId="19" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="29" fillId="19" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="23" fillId="19" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="31" fillId="19" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="31" fillId="19" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="19" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="25" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4875,6 +5002,9 @@
     </xf>
     <xf numFmtId="164" fontId="25" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="25" fillId="20" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5213,7 +5343,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -5460,32 +5590,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:46" ht="60.75" customHeight="1">
-      <c r="A1" s="81" t="s">
+      <c r="A1" s="88" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="81"/>
-      <c r="C1" s="81"/>
-      <c r="D1" s="81"/>
-      <c r="E1" s="81"/>
-      <c r="F1" s="81"/>
-      <c r="G1" s="81"/>
-      <c r="H1" s="81"/>
-      <c r="I1" s="81"/>
-      <c r="J1" s="81"/>
-      <c r="K1" s="81"/>
-      <c r="L1" s="81"/>
-      <c r="M1" s="81"/>
-      <c r="N1" s="81"/>
-      <c r="O1" s="81"/>
-      <c r="P1" s="81"/>
-      <c r="Q1" s="81"/>
-      <c r="R1" s="81"/>
-      <c r="S1" s="81"/>
-      <c r="T1" s="81"/>
-      <c r="U1" s="81"/>
-      <c r="V1" s="81"/>
-      <c r="W1" s="81"/>
-      <c r="X1" s="81"/>
+      <c r="B1" s="88"/>
+      <c r="C1" s="88"/>
+      <c r="D1" s="88"/>
+      <c r="E1" s="88"/>
+      <c r="F1" s="88"/>
+      <c r="G1" s="88"/>
+      <c r="H1" s="88"/>
+      <c r="I1" s="88"/>
+      <c r="J1" s="88"/>
+      <c r="K1" s="88"/>
+      <c r="L1" s="88"/>
+      <c r="M1" s="88"/>
+      <c r="N1" s="88"/>
+      <c r="O1" s="88"/>
+      <c r="P1" s="88"/>
+      <c r="Q1" s="88"/>
+      <c r="R1" s="88"/>
+      <c r="S1" s="88"/>
+      <c r="T1" s="88"/>
+      <c r="U1" s="88"/>
+      <c r="V1" s="88"/>
+      <c r="W1" s="88"/>
+      <c r="X1" s="88"/>
     </row>
     <row r="2" spans="1:46" ht="45" customHeight="1">
       <c r="A2" s="3" t="s">
@@ -6684,10 +6814,10 @@
       </c>
     </row>
     <row r="31" spans="1:24">
-      <c r="A31" s="82" t="s">
+      <c r="A31" s="89" t="s">
         <v>20</v>
       </c>
-      <c r="B31" s="82"/>
+      <c r="B31" s="89"/>
       <c r="C31" s="13">
         <f>SUM(C3:C30)</f>
         <v>19992.27</v>
@@ -6810,32 +6940,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:46" ht="60.75" customHeight="1">
-      <c r="A1" s="84" t="s">
+      <c r="A1" s="91" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="84"/>
-      <c r="C1" s="84"/>
-      <c r="D1" s="84"/>
-      <c r="E1" s="84"/>
-      <c r="F1" s="84"/>
-      <c r="G1" s="84"/>
-      <c r="H1" s="84"/>
-      <c r="I1" s="84"/>
-      <c r="J1" s="84"/>
-      <c r="K1" s="84"/>
-      <c r="L1" s="84"/>
-      <c r="M1" s="84"/>
-      <c r="N1" s="84"/>
-      <c r="O1" s="84"/>
-      <c r="P1" s="84"/>
-      <c r="Q1" s="84"/>
-      <c r="R1" s="84"/>
-      <c r="S1" s="84"/>
-      <c r="T1" s="84"/>
-      <c r="U1" s="84"/>
-      <c r="V1" s="84"/>
-      <c r="W1" s="84"/>
-      <c r="X1" s="84"/>
+      <c r="B1" s="91"/>
+      <c r="C1" s="91"/>
+      <c r="D1" s="91"/>
+      <c r="E1" s="91"/>
+      <c r="F1" s="91"/>
+      <c r="G1" s="91"/>
+      <c r="H1" s="91"/>
+      <c r="I1" s="91"/>
+      <c r="J1" s="91"/>
+      <c r="K1" s="91"/>
+      <c r="L1" s="91"/>
+      <c r="M1" s="91"/>
+      <c r="N1" s="91"/>
+      <c r="O1" s="91"/>
+      <c r="P1" s="91"/>
+      <c r="Q1" s="91"/>
+      <c r="R1" s="91"/>
+      <c r="S1" s="91"/>
+      <c r="T1" s="91"/>
+      <c r="U1" s="91"/>
+      <c r="V1" s="91"/>
+      <c r="W1" s="91"/>
+      <c r="X1" s="91"/>
     </row>
     <row r="2" spans="1:46" ht="45" customHeight="1">
       <c r="A2" s="30" t="s">
@@ -8046,10 +8176,10 @@
       <c r="X31" s="31"/>
     </row>
     <row r="32" spans="1:24">
-      <c r="A32" s="83" t="s">
+      <c r="A32" s="90" t="s">
         <v>20</v>
       </c>
-      <c r="B32" s="83"/>
+      <c r="B32" s="90"/>
       <c r="C32" s="28">
         <f>SUM(C3:C31)</f>
         <v>16843.349999999999</v>
@@ -8172,33 +8302,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:47" ht="60.75" customHeight="1">
-      <c r="A1" s="84" t="s">
+      <c r="A1" s="91" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="84"/>
-      <c r="C1" s="84"/>
-      <c r="D1" s="84"/>
-      <c r="E1" s="84"/>
-      <c r="F1" s="84"/>
-      <c r="G1" s="84"/>
-      <c r="H1" s="84"/>
-      <c r="I1" s="84"/>
-      <c r="J1" s="84"/>
-      <c r="K1" s="84"/>
-      <c r="L1" s="84"/>
-      <c r="M1" s="84"/>
-      <c r="N1" s="84"/>
-      <c r="O1" s="84"/>
-      <c r="P1" s="84"/>
-      <c r="Q1" s="84"/>
-      <c r="R1" s="84"/>
-      <c r="S1" s="84"/>
-      <c r="T1" s="84"/>
-      <c r="U1" s="84"/>
-      <c r="V1" s="84"/>
-      <c r="W1" s="84"/>
-      <c r="X1" s="84"/>
-      <c r="Y1" s="84"/>
+      <c r="B1" s="91"/>
+      <c r="C1" s="91"/>
+      <c r="D1" s="91"/>
+      <c r="E1" s="91"/>
+      <c r="F1" s="91"/>
+      <c r="G1" s="91"/>
+      <c r="H1" s="91"/>
+      <c r="I1" s="91"/>
+      <c r="J1" s="91"/>
+      <c r="K1" s="91"/>
+      <c r="L1" s="91"/>
+      <c r="M1" s="91"/>
+      <c r="N1" s="91"/>
+      <c r="O1" s="91"/>
+      <c r="P1" s="91"/>
+      <c r="Q1" s="91"/>
+      <c r="R1" s="91"/>
+      <c r="S1" s="91"/>
+      <c r="T1" s="91"/>
+      <c r="U1" s="91"/>
+      <c r="V1" s="91"/>
+      <c r="W1" s="91"/>
+      <c r="X1" s="91"/>
+      <c r="Y1" s="91"/>
     </row>
     <row r="2" spans="1:47" ht="45" customHeight="1">
       <c r="A2" s="30" t="s">
@@ -9016,10 +9146,10 @@
       <c r="Y19" s="43"/>
     </row>
     <row r="20" spans="1:27">
-      <c r="A20" s="86" t="s">
+      <c r="A20" s="93" t="s">
         <v>35</v>
       </c>
-      <c r="B20" s="87"/>
+      <c r="B20" s="94"/>
       <c r="C20" s="45">
         <f>SUM(C3:C19)</f>
         <v>12278.83</v>
@@ -9739,10 +9869,10 @@
       <c r="Y35" s="43"/>
     </row>
     <row r="36" spans="1:25">
-      <c r="A36" s="86" t="s">
+      <c r="A36" s="93" t="s">
         <v>36</v>
       </c>
-      <c r="B36" s="87"/>
+      <c r="B36" s="94"/>
       <c r="C36" s="45">
         <f>SUM(C21:C35)</f>
         <v>11057.89</v>
@@ -9837,10 +9967,10 @@
       </c>
     </row>
     <row r="37" spans="1:25" ht="31.5" customHeight="1">
-      <c r="A37" s="85" t="s">
+      <c r="A37" s="92" t="s">
         <v>37</v>
       </c>
-      <c r="B37" s="85"/>
+      <c r="B37" s="92"/>
       <c r="C37" s="48">
         <f>SUM(C20,C36)</f>
         <v>23336.720000000001</v>
@@ -9970,33 +10100,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:47" ht="60.75" customHeight="1">
-      <c r="A1" s="88" t="s">
+      <c r="A1" s="95" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="88"/>
-      <c r="C1" s="88"/>
-      <c r="D1" s="88"/>
-      <c r="E1" s="88"/>
-      <c r="F1" s="88"/>
-      <c r="G1" s="88"/>
-      <c r="H1" s="88"/>
-      <c r="I1" s="88"/>
-      <c r="J1" s="88"/>
-      <c r="K1" s="88"/>
-      <c r="L1" s="88"/>
-      <c r="M1" s="88"/>
-      <c r="N1" s="88"/>
-      <c r="O1" s="88"/>
-      <c r="P1" s="88"/>
-      <c r="Q1" s="88"/>
-      <c r="R1" s="88"/>
-      <c r="S1" s="88"/>
-      <c r="T1" s="88"/>
-      <c r="U1" s="88"/>
-      <c r="V1" s="88"/>
-      <c r="W1" s="88"/>
-      <c r="X1" s="88"/>
-      <c r="Y1" s="88"/>
+      <c r="B1" s="95"/>
+      <c r="C1" s="95"/>
+      <c r="D1" s="95"/>
+      <c r="E1" s="95"/>
+      <c r="F1" s="95"/>
+      <c r="G1" s="95"/>
+      <c r="H1" s="95"/>
+      <c r="I1" s="95"/>
+      <c r="J1" s="95"/>
+      <c r="K1" s="95"/>
+      <c r="L1" s="95"/>
+      <c r="M1" s="95"/>
+      <c r="N1" s="95"/>
+      <c r="O1" s="95"/>
+      <c r="P1" s="95"/>
+      <c r="Q1" s="95"/>
+      <c r="R1" s="95"/>
+      <c r="S1" s="95"/>
+      <c r="T1" s="95"/>
+      <c r="U1" s="95"/>
+      <c r="V1" s="95"/>
+      <c r="W1" s="95"/>
+      <c r="X1" s="95"/>
+      <c r="Y1" s="95"/>
     </row>
     <row r="2" spans="1:47" ht="45" customHeight="1">
       <c r="A2" s="59" t="s">
@@ -10706,10 +10836,10 @@
       <c r="Y17" s="65"/>
     </row>
     <row r="18" spans="1:27">
-      <c r="A18" s="89" t="s">
+      <c r="A18" s="96" t="s">
         <v>35</v>
       </c>
-      <c r="B18" s="89"/>
+      <c r="B18" s="96"/>
       <c r="C18" s="73">
         <f t="shared" ref="C18:X18" si="1">SUM(C3:C17)</f>
         <v>8428.35</v>
@@ -11462,10 +11592,10 @@
       <c r="Y34" s="69"/>
     </row>
     <row r="35" spans="1:25">
-      <c r="A35" s="89" t="s">
+      <c r="A35" s="96" t="s">
         <v>36</v>
       </c>
-      <c r="B35" s="89"/>
+      <c r="B35" s="96"/>
       <c r="C35" s="73">
         <f>SUM(C19:C34)</f>
         <v>10739.46</v>
@@ -11560,10 +11690,10 @@
       </c>
     </row>
     <row r="36" spans="1:25" ht="31.5" customHeight="1">
-      <c r="A36" s="90" t="s">
+      <c r="A36" s="97" t="s">
         <v>37</v>
       </c>
-      <c r="B36" s="90"/>
+      <c r="B36" s="97"/>
       <c r="C36" s="70">
         <f>SUM(C18,C35)</f>
         <v>19167.809999999998</v>
@@ -11701,33 +11831,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:47" ht="60.75" customHeight="1">
-      <c r="A1" s="91" t="s">
+      <c r="A1" s="98" t="s">
         <v>58</v>
       </c>
-      <c r="B1" s="91"/>
-      <c r="C1" s="91"/>
-      <c r="D1" s="91"/>
-      <c r="E1" s="91"/>
-      <c r="F1" s="91"/>
-      <c r="G1" s="91"/>
-      <c r="H1" s="91"/>
-      <c r="I1" s="91"/>
-      <c r="J1" s="91"/>
-      <c r="K1" s="91"/>
-      <c r="L1" s="91"/>
-      <c r="M1" s="91"/>
-      <c r="N1" s="91"/>
-      <c r="O1" s="91"/>
-      <c r="P1" s="91"/>
-      <c r="Q1" s="91"/>
-      <c r="R1" s="91"/>
-      <c r="S1" s="91"/>
-      <c r="T1" s="91"/>
-      <c r="U1" s="91"/>
-      <c r="V1" s="91"/>
-      <c r="W1" s="91"/>
-      <c r="X1" s="91"/>
-      <c r="Y1" s="91"/>
+      <c r="B1" s="98"/>
+      <c r="C1" s="98"/>
+      <c r="D1" s="98"/>
+      <c r="E1" s="98"/>
+      <c r="F1" s="98"/>
+      <c r="G1" s="98"/>
+      <c r="H1" s="98"/>
+      <c r="I1" s="98"/>
+      <c r="J1" s="98"/>
+      <c r="K1" s="98"/>
+      <c r="L1" s="98"/>
+      <c r="M1" s="98"/>
+      <c r="N1" s="98"/>
+      <c r="O1" s="98"/>
+      <c r="P1" s="98"/>
+      <c r="Q1" s="98"/>
+      <c r="R1" s="98"/>
+      <c r="S1" s="98"/>
+      <c r="T1" s="98"/>
+      <c r="U1" s="98"/>
+      <c r="V1" s="98"/>
+      <c r="W1" s="98"/>
+      <c r="X1" s="98"/>
+      <c r="Y1" s="98"/>
     </row>
     <row r="2" spans="1:47" ht="45" customHeight="1">
       <c r="A2" s="76" t="s">
@@ -12466,10 +12596,10 @@
       <c r="Y17" s="65"/>
     </row>
     <row r="18" spans="1:27">
-      <c r="A18" s="92" t="s">
+      <c r="A18" s="99" t="s">
         <v>35</v>
       </c>
-      <c r="B18" s="92"/>
+      <c r="B18" s="99"/>
       <c r="C18" s="79">
         <f t="shared" ref="C18:X18" si="1">SUM(C3:C17)</f>
         <v>7904</v>
@@ -13117,10 +13247,10 @@
       <c r="Y34" s="69"/>
     </row>
     <row r="35" spans="1:25">
-      <c r="A35" s="92" t="s">
+      <c r="A35" s="99" t="s">
         <v>36</v>
       </c>
-      <c r="B35" s="92"/>
+      <c r="B35" s="99"/>
       <c r="C35" s="79">
         <f>SUM(C19:C34)</f>
         <v>0</v>
@@ -13215,10 +13345,10 @@
       </c>
     </row>
     <row r="36" spans="1:25" ht="31.5" customHeight="1">
-      <c r="A36" s="93" t="s">
+      <c r="A36" s="100" t="s">
         <v>37</v>
       </c>
-      <c r="B36" s="93"/>
+      <c r="B36" s="100"/>
       <c r="C36" s="74">
         <f>SUM(C18,C35)</f>
         <v>7904</v>
@@ -13356,33 +13486,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:47" ht="60.75" customHeight="1">
-      <c r="A1" s="94" t="s">
+      <c r="A1" s="101" t="s">
         <v>59</v>
       </c>
-      <c r="B1" s="94"/>
-      <c r="C1" s="94"/>
-      <c r="D1" s="94"/>
-      <c r="E1" s="94"/>
-      <c r="F1" s="94"/>
-      <c r="G1" s="94"/>
-      <c r="H1" s="94"/>
-      <c r="I1" s="94"/>
-      <c r="J1" s="94"/>
-      <c r="K1" s="94"/>
-      <c r="L1" s="94"/>
-      <c r="M1" s="94"/>
-      <c r="N1" s="94"/>
-      <c r="O1" s="94"/>
-      <c r="P1" s="94"/>
-      <c r="Q1" s="94"/>
-      <c r="R1" s="94"/>
-      <c r="S1" s="94"/>
-      <c r="T1" s="94"/>
-      <c r="U1" s="94"/>
-      <c r="V1" s="94"/>
-      <c r="W1" s="94"/>
-      <c r="X1" s="94"/>
-      <c r="Y1" s="94"/>
+      <c r="B1" s="101"/>
+      <c r="C1" s="101"/>
+      <c r="D1" s="101"/>
+      <c r="E1" s="101"/>
+      <c r="F1" s="101"/>
+      <c r="G1" s="101"/>
+      <c r="H1" s="101"/>
+      <c r="I1" s="101"/>
+      <c r="J1" s="101"/>
+      <c r="K1" s="101"/>
+      <c r="L1" s="101"/>
+      <c r="M1" s="101"/>
+      <c r="N1" s="101"/>
+      <c r="O1" s="101"/>
+      <c r="P1" s="101"/>
+      <c r="Q1" s="101"/>
+      <c r="R1" s="101"/>
+      <c r="S1" s="101"/>
+      <c r="T1" s="101"/>
+      <c r="U1" s="101"/>
+      <c r="V1" s="101"/>
+      <c r="W1" s="101"/>
+      <c r="X1" s="101"/>
+      <c r="Y1" s="101"/>
     </row>
     <row r="2" spans="1:47" ht="45" customHeight="1">
       <c r="A2" s="76" t="s">
@@ -13451,13 +13581,13 @@
       <c r="V2" s="76" t="s">
         <v>26</v>
       </c>
-      <c r="W2" s="96" t="s">
+      <c r="W2" s="81" t="s">
         <v>22</v>
       </c>
-      <c r="X2" s="96" t="s">
+      <c r="X2" s="81" t="s">
         <v>19</v>
       </c>
-      <c r="Y2" s="96" t="s">
+      <c r="Y2" s="81" t="s">
         <v>21</v>
       </c>
       <c r="Z2" s="1"/>
@@ -13946,7 +14076,10 @@
       <c r="B14" s="67" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="72"/>
+      <c r="C14" s="72">
+        <f>219+2054.78</f>
+        <v>2273.7800000000002</v>
+      </c>
       <c r="D14" s="72"/>
       <c r="E14" s="72"/>
       <c r="F14" s="72"/>
@@ -13968,9 +14101,12 @@
       <c r="V14" s="72"/>
       <c r="W14" s="72">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="X14" s="107"/>
+        <v>2273.7800000000002</v>
+      </c>
+      <c r="X14" s="64">
+        <f>37634-14878.51</f>
+        <v>22755.489999999998</v>
+      </c>
       <c r="Y14" s="104"/>
     </row>
     <row r="15" spans="1:47" ht="15.75">
@@ -13992,7 +14128,9 @@
       <c r="L15" s="71"/>
       <c r="M15" s="71"/>
       <c r="N15" s="71"/>
-      <c r="O15" s="71"/>
+      <c r="O15" s="71">
+        <v>328</v>
+      </c>
       <c r="P15" s="71"/>
       <c r="Q15" s="71"/>
       <c r="R15" s="71"/>
@@ -14002,7 +14140,7 @@
       <c r="V15" s="71"/>
       <c r="W15" s="71">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>328</v>
       </c>
       <c r="X15" s="107"/>
       <c r="Y15" s="104"/>
@@ -14031,12 +14169,14 @@
       <c r="Q16" s="72"/>
       <c r="R16" s="72"/>
       <c r="S16" s="72"/>
-      <c r="T16" s="72"/>
+      <c r="T16" s="109">
+        <v>4000</v>
+      </c>
       <c r="U16" s="72"/>
       <c r="V16" s="72"/>
       <c r="W16" s="72">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="X16" s="107"/>
       <c r="Y16" s="104"/>
@@ -14065,12 +14205,18 @@
       <c r="Q17" s="71"/>
       <c r="R17" s="71"/>
       <c r="S17" s="71"/>
-      <c r="T17" s="71"/>
-      <c r="U17" s="71"/>
-      <c r="V17" s="71"/>
+      <c r="T17" s="109">
+        <v>10000</v>
+      </c>
+      <c r="U17" s="109">
+        <v>4000</v>
+      </c>
+      <c r="V17" s="109">
+        <v>7500</v>
+      </c>
       <c r="W17" s="71">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>21500</v>
       </c>
       <c r="X17" s="107"/>
       <c r="Y17" s="104"/>
@@ -14099,12 +14245,15 @@
       <c r="Q18" s="72"/>
       <c r="R18" s="72"/>
       <c r="S18" s="72"/>
-      <c r="T18" s="72"/>
+      <c r="T18" s="109">
+        <f>17000</f>
+        <v>17000</v>
+      </c>
       <c r="U18" s="72"/>
       <c r="V18" s="72"/>
       <c r="W18" s="72">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>17000</v>
       </c>
       <c r="X18" s="107"/>
       <c r="Y18" s="104"/>
@@ -14144,13 +14293,13 @@
       <c r="Y19" s="105"/>
     </row>
     <row r="20" spans="1:27" ht="14.25" customHeight="1">
-      <c r="A20" s="92" t="s">
+      <c r="A20" s="99" t="s">
         <v>35</v>
       </c>
-      <c r="B20" s="92"/>
+      <c r="B20" s="99"/>
       <c r="C20" s="79">
         <f t="shared" ref="C20:X20" si="1">SUM(C3:C17)</f>
-        <v>7605.21</v>
+        <v>9878.99</v>
       </c>
       <c r="D20" s="79">
         <f t="shared" si="1"/>
@@ -14198,7 +14347,7 @@
       </c>
       <c r="O20" s="79">
         <f t="shared" si="1"/>
-        <v>2258</v>
+        <v>2586</v>
       </c>
       <c r="P20" s="79">
         <f t="shared" si="1"/>
@@ -14218,27 +14367,27 @@
       </c>
       <c r="T20" s="79">
         <f t="shared" si="1"/>
-        <v>1188</v>
+        <v>15188</v>
       </c>
       <c r="U20" s="79">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="V20" s="79">
         <f t="shared" si="1"/>
-        <v>950</v>
-      </c>
-      <c r="W20" s="97">
+        <v>8450</v>
+      </c>
+      <c r="W20" s="82">
         <f t="shared" si="1"/>
-        <v>52531.069999999992</v>
-      </c>
-      <c r="X20" s="98">
+        <v>80632.849999999991</v>
+      </c>
+      <c r="X20" s="83">
         <f t="shared" si="1"/>
-        <v>75904.334999999992</v>
-      </c>
-      <c r="Y20" s="99">
+        <v>98659.824999999983</v>
+      </c>
+      <c r="Y20" s="84">
         <f>X20-W20</f>
-        <v>23373.264999999999</v>
+        <v>18026.974999999991</v>
       </c>
     </row>
     <row r="21" spans="1:27" ht="15.75">
@@ -14739,10 +14888,10 @@
       <c r="Y36" s="105"/>
     </row>
     <row r="37" spans="1:25">
-      <c r="A37" s="92" t="s">
+      <c r="A37" s="99" t="s">
         <v>36</v>
       </c>
-      <c r="B37" s="92"/>
+      <c r="B37" s="99"/>
       <c r="C37" s="79">
         <f>SUM(C21:C36)</f>
         <v>0</v>
@@ -14823,27 +14972,27 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="W37" s="97">
+      <c r="W37" s="82">
         <f>SUM(W21:W36)</f>
         <v>0</v>
       </c>
-      <c r="X37" s="98">
+      <c r="X37" s="83">
         <f>SUM(X21:X36)</f>
         <v>0</v>
       </c>
-      <c r="Y37" s="100">
+      <c r="Y37" s="85">
         <f>X37-W37</f>
         <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:25" ht="31.5" customHeight="1">
-      <c r="A38" s="95" t="s">
+      <c r="A38" s="102" t="s">
         <v>37</v>
       </c>
-      <c r="B38" s="95"/>
+      <c r="B38" s="102"/>
       <c r="C38" s="78">
         <f>SUM(C20,C37)</f>
-        <v>7605.21</v>
+        <v>9878.99</v>
       </c>
       <c r="D38" s="78">
         <f t="shared" ref="D38:W38" si="3">SUM(D20,D37)</f>
@@ -14891,7 +15040,7 @@
       </c>
       <c r="O38" s="78">
         <f t="shared" si="3"/>
-        <v>2258</v>
+        <v>2586</v>
       </c>
       <c r="P38" s="78">
         <f t="shared" si="3"/>
@@ -14911,27 +15060,27 @@
       </c>
       <c r="T38" s="78">
         <f t="shared" si="3"/>
-        <v>1188</v>
+        <v>15188</v>
       </c>
       <c r="U38" s="78">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="V38" s="78">
         <f t="shared" si="3"/>
-        <v>950</v>
-      </c>
-      <c r="W38" s="101">
+        <v>8450</v>
+      </c>
+      <c r="W38" s="86">
         <f t="shared" si="3"/>
-        <v>52531.069999999992</v>
-      </c>
-      <c r="X38" s="101">
+        <v>80632.849999999991</v>
+      </c>
+      <c r="X38" s="86">
         <f>SUM(X20,X37)</f>
-        <v>75904.334999999992</v>
-      </c>
-      <c r="Y38" s="102">
+        <v>98659.824999999983</v>
+      </c>
+      <c r="Y38" s="87">
         <f>SUM(Y20,Y37)</f>
-        <v>23373.264999999999</v>
+        <v>18026.974999999991</v>
       </c>
     </row>
     <row r="42" spans="1:25">
@@ -14947,15 +15096,16 @@
       <c r="K42" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="A1:Y1"/>
     <mergeCell ref="A20:B20"/>
     <mergeCell ref="A37:B37"/>
     <mergeCell ref="A38:B38"/>
     <mergeCell ref="Y3:Y19"/>
     <mergeCell ref="Y21:Y36"/>
-    <mergeCell ref="X4:X19"/>
     <mergeCell ref="X22:X36"/>
+    <mergeCell ref="X4:X13"/>
+    <mergeCell ref="X15:X19"/>
   </mergeCells>
   <conditionalFormatting sqref="Y20:Y21 Y37:Y38">
     <cfRule type="expression" dxfId="1" priority="1">

--- a/Другое/2026/Доходы-Расходы_copy.xlsx
+++ b/Другое/2026/Доходы-Расходы_copy.xlsx
@@ -1529,7 +1529,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">
 КФЦ</t>
@@ -1554,7 +1555,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">
 Журналы Чтиво и Книга про вино</t>
@@ -1579,7 +1581,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">
 Поке
@@ -1605,7 +1608,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">
 Поке
@@ -1631,7 +1635,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">
 До-до пицца
@@ -1657,7 +1662,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">
 Лапшичка</t>
@@ -1682,7 +1688,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">
 Яндекс Плюс</t>
@@ -1707,7 +1714,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">
 КФЦ</t>
@@ -1722,7 +1730,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t>Автор:</t>
         </r>
@@ -1731,7 +1740,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">
 В долг у бати</t>
@@ -1746,7 +1756,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t>Автор:</t>
         </r>
@@ -1755,7 +1766,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">
 Брэкфаст бенд</t>
@@ -1832,7 +1844,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t>Автор:</t>
         </r>
@@ -1841,7 +1854,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">
 Вк музыка, белье, сотовая связь</t>
@@ -1856,7 +1870,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t>Автор:</t>
         </r>
@@ -1865,7 +1880,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">
 Долг маме
@@ -1881,7 +1897,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t>Автор:</t>
         </r>
@@ -1890,7 +1907,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">
 Поход в гиннес на обед</t>
@@ -2087,7 +2105,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t>Автор:</t>
         </r>
@@ -2096,7 +2115,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">
 Про мясо
@@ -2112,7 +2132,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t>Автор:</t>
         </r>
@@ -2121,7 +2142,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">
 Чикен хаус</t>
@@ -2136,7 +2158,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t>Автор:</t>
         </r>
@@ -2145,7 +2168,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">
 Макдоналдс
@@ -2161,7 +2185,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t>Автор:</t>
         </r>
@@ -2170,7 +2195,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">
 Сиги</t>
@@ -2185,7 +2211,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t>Автор:</t>
         </r>
@@ -2194,7 +2221,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">
 Интернет</t>
@@ -2209,7 +2237,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t>Автор:</t>
         </r>
@@ -2218,7 +2247,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">
 журнал Чтиво
@@ -2234,7 +2264,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t>Автор:</t>
         </r>
@@ -2243,7 +2274,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">
 Макдоналдс + Мяуча</t>
@@ -2258,7 +2290,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t>Автор:</t>
         </r>
@@ -2267,7 +2300,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">
 журнал ЧТИВО
@@ -2283,7 +2317,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t>Автор:</t>
         </r>
@@ -2292,7 +2327,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">
 На бенз</t>
@@ -2307,7 +2343,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t>Автор:</t>
         </r>
@@ -2316,7 +2353,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">
 Рыбалка</t>
@@ -2331,7 +2369,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t>Автор:</t>
         </r>
@@ -2340,7 +2379,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">
 Теле 2</t>
@@ -3356,7 +3396,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t>Автор:</t>
         </r>
@@ -3365,7 +3406,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">
 Мама перевела Ане (дала в долг)</t>
@@ -3469,7 +3511,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">
 Макдоналдс</t>
@@ -3520,7 +3563,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t>Автор:</t>
         </r>
@@ -3529,7 +3573,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">
 Компенсация за ВПЧ
@@ -3545,7 +3590,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t>Автор:</t>
         </r>
@@ -3554,7 +3600,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">
 Яндекс Плюс</t>
@@ -3569,7 +3616,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t>Автор:</t>
         </r>
@@ -3578,7 +3626,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">
 Завтрак в 1/2</t>
@@ -3593,7 +3642,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t>Автор:</t>
         </r>
@@ -3602,7 +3652,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">
 ВК музыка
@@ -3618,7 +3669,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t>Автор:</t>
         </r>
@@ -3627,7 +3679,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">
 Покупка ЧТИВО</t>
@@ -3642,7 +3695,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t>Автор:</t>
         </r>
@@ -3651,7 +3705,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">
 Промясо</t>
@@ -3666,7 +3721,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t>Автор:</t>
         </r>
@@ -3675,7 +3731,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">
 Поке + бабл ти
@@ -3691,7 +3748,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t>Автор:</t>
         </r>
@@ -3700,7 +3758,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">
 Долями за орнамент
@@ -3716,7 +3775,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t>Автор:</t>
         </r>
@@ -3725,7 +3785,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">
 T2</t>
@@ -3740,7 +3801,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t>Автор:</t>
         </r>
@@ -3749,7 +3811,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">
 Макдоналдс</t>
@@ -3764,7 +3827,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t>Автор:</t>
         </r>
@@ -3773,7 +3837,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">
 ВПН</t>
@@ -3788,7 +3853,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t>Автор:</t>
         </r>
@@ -3797,7 +3863,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">
 Ане на таблетки</t>
@@ -3812,7 +3879,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t>Автор:</t>
         </r>
@@ -3821,7 +3889,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">
 Извинительный букет
@@ -3837,7 +3906,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t>Автор:</t>
         </r>
@@ -3846,13 +3916,92 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">
 Долями - за журнальчик орнамент</t>
         </r>
       </text>
     </comment>
+    <comment ref="Q15" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+За такси + вино</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="S15" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+t2</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F16" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Обед</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="T16" authorId="0">
       <text>
         <r>
@@ -3861,7 +4010,23 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Парикмахерская</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="U16" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t>Автор:</t>
         </r>
@@ -3870,7 +4035,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">
 Простава на работе</t>
@@ -3885,7 +4051,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t>Автор:</t>
         </r>
@@ -3894,7 +4061,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">
 Снять квартиру в мск</t>
@@ -3909,7 +4077,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t>Автор:</t>
         </r>
@@ -3918,7 +4087,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">
 Билеты на электричку
@@ -3934,7 +4104,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t>Автор:</t>
         </r>
@@ -3943,7 +4114,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">
 Подарок кулику</t>
@@ -3958,7 +4130,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t>Автор:</t>
         </r>
@@ -3967,7 +4140,8 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
+            <charset val="204"/>
           </rPr>
           <t xml:space="preserve">
 Покушать и погулять в МСК</t>
@@ -4169,7 +4343,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;₽&quot;"/>
   </numFmts>
-  <fonts count="32">
+  <fonts count="30">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4281,12 +4455,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FFFFC000"/>
       <name val="Impact"/>
@@ -4305,13 +4473,6 @@
       <color theme="1"/>
       <name val="Antique Olive"/>
       <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
     </font>
     <font>
       <b/>
@@ -4854,90 +5015,93 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="17" fillId="15" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="17" fillId="15" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="16" fillId="15" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="16" fillId="15" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="23" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="21" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="21" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="25" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="25" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="23" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="23" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="25" fillId="17" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="25" fillId="17" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="23" fillId="17" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="23" fillId="17" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="20" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="25" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="23" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="25" fillId="17" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="23" fillId="17" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="21" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="25" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="18" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="26" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="18" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="29" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="27" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="25" fillId="18" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="27" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="18" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="31" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="27" fillId="19" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="29" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="164" fontId="27" fillId="19" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="21" fillId="19" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="29" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="28" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="29" fillId="19" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="29" fillId="19" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="29" fillId="19" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="23" fillId="19" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="31" fillId="19" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="31" fillId="19" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="20" fillId="19" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="19" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="23" fillId="20" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -4961,50 +5125,47 @@
     <xf numFmtId="0" fontId="13" fillId="14" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="23" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="25" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="23" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="25" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="23" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="25" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="25" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="23" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="25" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="23" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="25" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="23" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="25" fillId="20" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5343,7 +5504,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -5590,32 +5751,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:46" ht="60.75" customHeight="1">
-      <c r="A1" s="88" t="s">
+      <c r="A1" s="89" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="88"/>
-      <c r="C1" s="88"/>
-      <c r="D1" s="88"/>
-      <c r="E1" s="88"/>
-      <c r="F1" s="88"/>
-      <c r="G1" s="88"/>
-      <c r="H1" s="88"/>
-      <c r="I1" s="88"/>
-      <c r="J1" s="88"/>
-      <c r="K1" s="88"/>
-      <c r="L1" s="88"/>
-      <c r="M1" s="88"/>
-      <c r="N1" s="88"/>
-      <c r="O1" s="88"/>
-      <c r="P1" s="88"/>
-      <c r="Q1" s="88"/>
-      <c r="R1" s="88"/>
-      <c r="S1" s="88"/>
-      <c r="T1" s="88"/>
-      <c r="U1" s="88"/>
-      <c r="V1" s="88"/>
-      <c r="W1" s="88"/>
-      <c r="X1" s="88"/>
+      <c r="B1" s="89"/>
+      <c r="C1" s="89"/>
+      <c r="D1" s="89"/>
+      <c r="E1" s="89"/>
+      <c r="F1" s="89"/>
+      <c r="G1" s="89"/>
+      <c r="H1" s="89"/>
+      <c r="I1" s="89"/>
+      <c r="J1" s="89"/>
+      <c r="K1" s="89"/>
+      <c r="L1" s="89"/>
+      <c r="M1" s="89"/>
+      <c r="N1" s="89"/>
+      <c r="O1" s="89"/>
+      <c r="P1" s="89"/>
+      <c r="Q1" s="89"/>
+      <c r="R1" s="89"/>
+      <c r="S1" s="89"/>
+      <c r="T1" s="89"/>
+      <c r="U1" s="89"/>
+      <c r="V1" s="89"/>
+      <c r="W1" s="89"/>
+      <c r="X1" s="89"/>
     </row>
     <row r="2" spans="1:46" ht="45" customHeight="1">
       <c r="A2" s="3" t="s">
@@ -6814,10 +6975,10 @@
       </c>
     </row>
     <row r="31" spans="1:24">
-      <c r="A31" s="89" t="s">
+      <c r="A31" s="90" t="s">
         <v>20</v>
       </c>
-      <c r="B31" s="89"/>
+      <c r="B31" s="90"/>
       <c r="C31" s="13">
         <f>SUM(C3:C30)</f>
         <v>19992.27</v>
@@ -6940,32 +7101,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:46" ht="60.75" customHeight="1">
-      <c r="A1" s="91" t="s">
+      <c r="A1" s="92" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="91"/>
-      <c r="C1" s="91"/>
-      <c r="D1" s="91"/>
-      <c r="E1" s="91"/>
-      <c r="F1" s="91"/>
-      <c r="G1" s="91"/>
-      <c r="H1" s="91"/>
-      <c r="I1" s="91"/>
-      <c r="J1" s="91"/>
-      <c r="K1" s="91"/>
-      <c r="L1" s="91"/>
-      <c r="M1" s="91"/>
-      <c r="N1" s="91"/>
-      <c r="O1" s="91"/>
-      <c r="P1" s="91"/>
-      <c r="Q1" s="91"/>
-      <c r="R1" s="91"/>
-      <c r="S1" s="91"/>
-      <c r="T1" s="91"/>
-      <c r="U1" s="91"/>
-      <c r="V1" s="91"/>
-      <c r="W1" s="91"/>
-      <c r="X1" s="91"/>
+      <c r="B1" s="92"/>
+      <c r="C1" s="92"/>
+      <c r="D1" s="92"/>
+      <c r="E1" s="92"/>
+      <c r="F1" s="92"/>
+      <c r="G1" s="92"/>
+      <c r="H1" s="92"/>
+      <c r="I1" s="92"/>
+      <c r="J1" s="92"/>
+      <c r="K1" s="92"/>
+      <c r="L1" s="92"/>
+      <c r="M1" s="92"/>
+      <c r="N1" s="92"/>
+      <c r="O1" s="92"/>
+      <c r="P1" s="92"/>
+      <c r="Q1" s="92"/>
+      <c r="R1" s="92"/>
+      <c r="S1" s="92"/>
+      <c r="T1" s="92"/>
+      <c r="U1" s="92"/>
+      <c r="V1" s="92"/>
+      <c r="W1" s="92"/>
+      <c r="X1" s="92"/>
     </row>
     <row r="2" spans="1:46" ht="45" customHeight="1">
       <c r="A2" s="30" t="s">
@@ -8176,10 +8337,10 @@
       <c r="X31" s="31"/>
     </row>
     <row r="32" spans="1:24">
-      <c r="A32" s="90" t="s">
+      <c r="A32" s="91" t="s">
         <v>20</v>
       </c>
-      <c r="B32" s="90"/>
+      <c r="B32" s="91"/>
       <c r="C32" s="28">
         <f>SUM(C3:C31)</f>
         <v>16843.349999999999</v>
@@ -8302,33 +8463,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:47" ht="60.75" customHeight="1">
-      <c r="A1" s="91" t="s">
+      <c r="A1" s="92" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="91"/>
-      <c r="C1" s="91"/>
-      <c r="D1" s="91"/>
-      <c r="E1" s="91"/>
-      <c r="F1" s="91"/>
-      <c r="G1" s="91"/>
-      <c r="H1" s="91"/>
-      <c r="I1" s="91"/>
-      <c r="J1" s="91"/>
-      <c r="K1" s="91"/>
-      <c r="L1" s="91"/>
-      <c r="M1" s="91"/>
-      <c r="N1" s="91"/>
-      <c r="O1" s="91"/>
-      <c r="P1" s="91"/>
-      <c r="Q1" s="91"/>
-      <c r="R1" s="91"/>
-      <c r="S1" s="91"/>
-      <c r="T1" s="91"/>
-      <c r="U1" s="91"/>
-      <c r="V1" s="91"/>
-      <c r="W1" s="91"/>
-      <c r="X1" s="91"/>
-      <c r="Y1" s="91"/>
+      <c r="B1" s="92"/>
+      <c r="C1" s="92"/>
+      <c r="D1" s="92"/>
+      <c r="E1" s="92"/>
+      <c r="F1" s="92"/>
+      <c r="G1" s="92"/>
+      <c r="H1" s="92"/>
+      <c r="I1" s="92"/>
+      <c r="J1" s="92"/>
+      <c r="K1" s="92"/>
+      <c r="L1" s="92"/>
+      <c r="M1" s="92"/>
+      <c r="N1" s="92"/>
+      <c r="O1" s="92"/>
+      <c r="P1" s="92"/>
+      <c r="Q1" s="92"/>
+      <c r="R1" s="92"/>
+      <c r="S1" s="92"/>
+      <c r="T1" s="92"/>
+      <c r="U1" s="92"/>
+      <c r="V1" s="92"/>
+      <c r="W1" s="92"/>
+      <c r="X1" s="92"/>
+      <c r="Y1" s="92"/>
     </row>
     <row r="2" spans="1:47" ht="45" customHeight="1">
       <c r="A2" s="30" t="s">
@@ -9146,10 +9307,10 @@
       <c r="Y19" s="43"/>
     </row>
     <row r="20" spans="1:27">
-      <c r="A20" s="93" t="s">
+      <c r="A20" s="94" t="s">
         <v>35</v>
       </c>
-      <c r="B20" s="94"/>
+      <c r="B20" s="95"/>
       <c r="C20" s="45">
         <f>SUM(C3:C19)</f>
         <v>12278.83</v>
@@ -9869,10 +10030,10 @@
       <c r="Y35" s="43"/>
     </row>
     <row r="36" spans="1:25">
-      <c r="A36" s="93" t="s">
+      <c r="A36" s="94" t="s">
         <v>36</v>
       </c>
-      <c r="B36" s="94"/>
+      <c r="B36" s="95"/>
       <c r="C36" s="45">
         <f>SUM(C21:C35)</f>
         <v>11057.89</v>
@@ -9967,10 +10128,10 @@
       </c>
     </row>
     <row r="37" spans="1:25" ht="31.5" customHeight="1">
-      <c r="A37" s="92" t="s">
+      <c r="A37" s="93" t="s">
         <v>37</v>
       </c>
-      <c r="B37" s="92"/>
+      <c r="B37" s="93"/>
       <c r="C37" s="48">
         <f>SUM(C20,C36)</f>
         <v>23336.720000000001</v>
@@ -10100,33 +10261,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:47" ht="60.75" customHeight="1">
-      <c r="A1" s="95" t="s">
+      <c r="A1" s="96" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="95"/>
-      <c r="C1" s="95"/>
-      <c r="D1" s="95"/>
-      <c r="E1" s="95"/>
-      <c r="F1" s="95"/>
-      <c r="G1" s="95"/>
-      <c r="H1" s="95"/>
-      <c r="I1" s="95"/>
-      <c r="J1" s="95"/>
-      <c r="K1" s="95"/>
-      <c r="L1" s="95"/>
-      <c r="M1" s="95"/>
-      <c r="N1" s="95"/>
-      <c r="O1" s="95"/>
-      <c r="P1" s="95"/>
-      <c r="Q1" s="95"/>
-      <c r="R1" s="95"/>
-      <c r="S1" s="95"/>
-      <c r="T1" s="95"/>
-      <c r="U1" s="95"/>
-      <c r="V1" s="95"/>
-      <c r="W1" s="95"/>
-      <c r="X1" s="95"/>
-      <c r="Y1" s="95"/>
+      <c r="B1" s="96"/>
+      <c r="C1" s="96"/>
+      <c r="D1" s="96"/>
+      <c r="E1" s="96"/>
+      <c r="F1" s="96"/>
+      <c r="G1" s="96"/>
+      <c r="H1" s="96"/>
+      <c r="I1" s="96"/>
+      <c r="J1" s="96"/>
+      <c r="K1" s="96"/>
+      <c r="L1" s="96"/>
+      <c r="M1" s="96"/>
+      <c r="N1" s="96"/>
+      <c r="O1" s="96"/>
+      <c r="P1" s="96"/>
+      <c r="Q1" s="96"/>
+      <c r="R1" s="96"/>
+      <c r="S1" s="96"/>
+      <c r="T1" s="96"/>
+      <c r="U1" s="96"/>
+      <c r="V1" s="96"/>
+      <c r="W1" s="96"/>
+      <c r="X1" s="96"/>
+      <c r="Y1" s="96"/>
     </row>
     <row r="2" spans="1:47" ht="45" customHeight="1">
       <c r="A2" s="59" t="s">
@@ -10836,10 +10997,10 @@
       <c r="Y17" s="65"/>
     </row>
     <row r="18" spans="1:27">
-      <c r="A18" s="96" t="s">
+      <c r="A18" s="97" t="s">
         <v>35</v>
       </c>
-      <c r="B18" s="96"/>
+      <c r="B18" s="97"/>
       <c r="C18" s="73">
         <f t="shared" ref="C18:X18" si="1">SUM(C3:C17)</f>
         <v>8428.35</v>
@@ -11592,10 +11753,10 @@
       <c r="Y34" s="69"/>
     </row>
     <row r="35" spans="1:25">
-      <c r="A35" s="96" t="s">
+      <c r="A35" s="97" t="s">
         <v>36</v>
       </c>
-      <c r="B35" s="96"/>
+      <c r="B35" s="97"/>
       <c r="C35" s="73">
         <f>SUM(C19:C34)</f>
         <v>10739.46</v>
@@ -11690,10 +11851,10 @@
       </c>
     </row>
     <row r="36" spans="1:25" ht="31.5" customHeight="1">
-      <c r="A36" s="97" t="s">
+      <c r="A36" s="98" t="s">
         <v>37</v>
       </c>
-      <c r="B36" s="97"/>
+      <c r="B36" s="98"/>
       <c r="C36" s="70">
         <f>SUM(C18,C35)</f>
         <v>19167.809999999998</v>
@@ -11831,33 +11992,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:47" ht="60.75" customHeight="1">
-      <c r="A1" s="98" t="s">
+      <c r="A1" s="99" t="s">
         <v>58</v>
       </c>
-      <c r="B1" s="98"/>
-      <c r="C1" s="98"/>
-      <c r="D1" s="98"/>
-      <c r="E1" s="98"/>
-      <c r="F1" s="98"/>
-      <c r="G1" s="98"/>
-      <c r="H1" s="98"/>
-      <c r="I1" s="98"/>
-      <c r="J1" s="98"/>
-      <c r="K1" s="98"/>
-      <c r="L1" s="98"/>
-      <c r="M1" s="98"/>
-      <c r="N1" s="98"/>
-      <c r="O1" s="98"/>
-      <c r="P1" s="98"/>
-      <c r="Q1" s="98"/>
-      <c r="R1" s="98"/>
-      <c r="S1" s="98"/>
-      <c r="T1" s="98"/>
-      <c r="U1" s="98"/>
-      <c r="V1" s="98"/>
-      <c r="W1" s="98"/>
-      <c r="X1" s="98"/>
-      <c r="Y1" s="98"/>
+      <c r="B1" s="99"/>
+      <c r="C1" s="99"/>
+      <c r="D1" s="99"/>
+      <c r="E1" s="99"/>
+      <c r="F1" s="99"/>
+      <c r="G1" s="99"/>
+      <c r="H1" s="99"/>
+      <c r="I1" s="99"/>
+      <c r="J1" s="99"/>
+      <c r="K1" s="99"/>
+      <c r="L1" s="99"/>
+      <c r="M1" s="99"/>
+      <c r="N1" s="99"/>
+      <c r="O1" s="99"/>
+      <c r="P1" s="99"/>
+      <c r="Q1" s="99"/>
+      <c r="R1" s="99"/>
+      <c r="S1" s="99"/>
+      <c r="T1" s="99"/>
+      <c r="U1" s="99"/>
+      <c r="V1" s="99"/>
+      <c r="W1" s="99"/>
+      <c r="X1" s="99"/>
+      <c r="Y1" s="99"/>
     </row>
     <row r="2" spans="1:47" ht="45" customHeight="1">
       <c r="A2" s="76" t="s">
@@ -12596,10 +12757,10 @@
       <c r="Y17" s="65"/>
     </row>
     <row r="18" spans="1:27">
-      <c r="A18" s="99" t="s">
+      <c r="A18" s="100" t="s">
         <v>35</v>
       </c>
-      <c r="B18" s="99"/>
+      <c r="B18" s="100"/>
       <c r="C18" s="79">
         <f t="shared" ref="C18:X18" si="1">SUM(C3:C17)</f>
         <v>7904</v>
@@ -13247,10 +13408,10 @@
       <c r="Y34" s="69"/>
     </row>
     <row r="35" spans="1:25">
-      <c r="A35" s="99" t="s">
+      <c r="A35" s="100" t="s">
         <v>36</v>
       </c>
-      <c r="B35" s="99"/>
+      <c r="B35" s="100"/>
       <c r="C35" s="79">
         <f>SUM(C19:C34)</f>
         <v>0</v>
@@ -13345,10 +13506,10 @@
       </c>
     </row>
     <row r="36" spans="1:25" ht="31.5" customHeight="1">
-      <c r="A36" s="100" t="s">
+      <c r="A36" s="101" t="s">
         <v>37</v>
       </c>
-      <c r="B36" s="100"/>
+      <c r="B36" s="101"/>
       <c r="C36" s="74">
         <f>SUM(C18,C35)</f>
         <v>7904</v>
@@ -13486,33 +13647,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:47" ht="60.75" customHeight="1">
-      <c r="A1" s="101" t="s">
+      <c r="A1" s="102" t="s">
         <v>59</v>
       </c>
-      <c r="B1" s="101"/>
-      <c r="C1" s="101"/>
-      <c r="D1" s="101"/>
-      <c r="E1" s="101"/>
-      <c r="F1" s="101"/>
-      <c r="G1" s="101"/>
-      <c r="H1" s="101"/>
-      <c r="I1" s="101"/>
-      <c r="J1" s="101"/>
-      <c r="K1" s="101"/>
-      <c r="L1" s="101"/>
-      <c r="M1" s="101"/>
-      <c r="N1" s="101"/>
-      <c r="O1" s="101"/>
-      <c r="P1" s="101"/>
-      <c r="Q1" s="101"/>
-      <c r="R1" s="101"/>
-      <c r="S1" s="101"/>
-      <c r="T1" s="101"/>
-      <c r="U1" s="101"/>
-      <c r="V1" s="101"/>
-      <c r="W1" s="101"/>
-      <c r="X1" s="101"/>
-      <c r="Y1" s="101"/>
+      <c r="B1" s="102"/>
+      <c r="C1" s="102"/>
+      <c r="D1" s="102"/>
+      <c r="E1" s="102"/>
+      <c r="F1" s="102"/>
+      <c r="G1" s="102"/>
+      <c r="H1" s="102"/>
+      <c r="I1" s="102"/>
+      <c r="J1" s="102"/>
+      <c r="K1" s="102"/>
+      <c r="L1" s="102"/>
+      <c r="M1" s="102"/>
+      <c r="N1" s="102"/>
+      <c r="O1" s="102"/>
+      <c r="P1" s="102"/>
+      <c r="Q1" s="102"/>
+      <c r="R1" s="102"/>
+      <c r="S1" s="102"/>
+      <c r="T1" s="102"/>
+      <c r="U1" s="102"/>
+      <c r="V1" s="102"/>
+      <c r="W1" s="102"/>
+      <c r="X1" s="102"/>
+      <c r="Y1" s="102"/>
     </row>
     <row r="2" spans="1:47" ht="45" customHeight="1">
       <c r="A2" s="76" t="s">
@@ -13659,7 +13820,7 @@
         <f>(94085+57723.67)/2</f>
         <v>75904.334999999992</v>
       </c>
-      <c r="Y3" s="103"/>
+      <c r="Y3" s="104"/>
     </row>
     <row r="4" spans="1:47" ht="15.75">
       <c r="A4" s="66">
@@ -13707,8 +13868,8 @@
         <f>SUM(C4:V4)</f>
         <v>10533.31</v>
       </c>
-      <c r="X4" s="106"/>
-      <c r="Y4" s="104"/>
+      <c r="X4" s="107"/>
+      <c r="Y4" s="105"/>
     </row>
     <row r="5" spans="1:47" ht="15.75">
       <c r="A5" s="62">
@@ -13746,8 +13907,8 @@
         <f t="shared" ref="W5:W19" si="0">SUM(C5:V5)</f>
         <v>1455</v>
       </c>
-      <c r="X5" s="107"/>
-      <c r="Y5" s="104"/>
+      <c r="X5" s="108"/>
+      <c r="Y5" s="105"/>
     </row>
     <row r="6" spans="1:47" ht="15.75">
       <c r="A6" s="66">
@@ -13786,8 +13947,8 @@
         <f t="shared" si="0"/>
         <v>1803.8400000000001</v>
       </c>
-      <c r="X6" s="107"/>
-      <c r="Y6" s="104"/>
+      <c r="X6" s="108"/>
+      <c r="Y6" s="105"/>
     </row>
     <row r="7" spans="1:47" ht="15" customHeight="1">
       <c r="A7" s="62">
@@ -13829,8 +13990,8 @@
         <f t="shared" si="0"/>
         <v>3302.61</v>
       </c>
-      <c r="X7" s="107"/>
-      <c r="Y7" s="104"/>
+      <c r="X7" s="108"/>
+      <c r="Y7" s="105"/>
     </row>
     <row r="8" spans="1:47" ht="15.75">
       <c r="A8" s="66">
@@ -13870,8 +14031,8 @@
         <f t="shared" si="0"/>
         <v>2255</v>
       </c>
-      <c r="X8" s="107"/>
-      <c r="Y8" s="104"/>
+      <c r="X8" s="108"/>
+      <c r="Y8" s="105"/>
     </row>
     <row r="9" spans="1:47" ht="15.75">
       <c r="A9" s="62">
@@ -13908,8 +14069,8 @@
         <f t="shared" si="0"/>
         <v>1095</v>
       </c>
-      <c r="X9" s="107"/>
-      <c r="Y9" s="104"/>
+      <c r="X9" s="108"/>
+      <c r="Y9" s="105"/>
     </row>
     <row r="10" spans="1:47" ht="15.75">
       <c r="A10" s="66">
@@ -13951,8 +14112,8 @@
         <f t="shared" si="0"/>
         <v>4914</v>
       </c>
-      <c r="X10" s="107"/>
-      <c r="Y10" s="104"/>
+      <c r="X10" s="108"/>
+      <c r="Y10" s="105"/>
     </row>
     <row r="11" spans="1:47" ht="15.75">
       <c r="A11" s="62">
@@ -13990,8 +14151,8 @@
         <f t="shared" si="0"/>
         <v>4632.68</v>
       </c>
-      <c r="X11" s="107"/>
-      <c r="Y11" s="104"/>
+      <c r="X11" s="108"/>
+      <c r="Y11" s="105"/>
     </row>
     <row r="12" spans="1:47" ht="15.75">
       <c r="A12" s="66">
@@ -14026,8 +14187,8 @@
         <f t="shared" si="0"/>
         <v>4475</v>
       </c>
-      <c r="X12" s="107"/>
-      <c r="Y12" s="104"/>
+      <c r="X12" s="108"/>
+      <c r="Y12" s="105"/>
     </row>
     <row r="13" spans="1:47" ht="15.75">
       <c r="A13" s="62">
@@ -14066,8 +14227,8 @@
         <f t="shared" si="0"/>
         <v>4015.63</v>
       </c>
-      <c r="X13" s="107"/>
-      <c r="Y13" s="104"/>
+      <c r="X13" s="108"/>
+      <c r="Y13" s="105"/>
     </row>
     <row r="14" spans="1:47" ht="15.75">
       <c r="A14" s="66">
@@ -14107,7 +14268,7 @@
         <f>37634-14878.51</f>
         <v>22755.489999999998</v>
       </c>
-      <c r="Y14" s="104"/>
+      <c r="Y14" s="105"/>
     </row>
     <row r="15" spans="1:47" ht="15.75">
       <c r="A15" s="62">
@@ -14116,8 +14277,12 @@
       <c r="B15" s="63" t="s">
         <v>2</v>
       </c>
-      <c r="C15" s="71"/>
-      <c r="D15" s="71"/>
+      <c r="C15" s="71">
+        <v>364</v>
+      </c>
+      <c r="D15" s="71">
+        <v>584</v>
+      </c>
       <c r="E15" s="71"/>
       <c r="F15" s="71"/>
       <c r="G15" s="71"/>
@@ -14132,18 +14297,23 @@
         <v>328</v>
       </c>
       <c r="P15" s="71"/>
-      <c r="Q15" s="71"/>
+      <c r="Q15" s="71">
+        <f>1500+1120.98</f>
+        <v>2620.98</v>
+      </c>
       <c r="R15" s="71"/>
-      <c r="S15" s="71"/>
+      <c r="S15" s="71">
+        <v>200</v>
+      </c>
       <c r="T15" s="71"/>
       <c r="U15" s="71"/>
       <c r="V15" s="71"/>
       <c r="W15" s="71">
         <f t="shared" si="0"/>
-        <v>328</v>
-      </c>
-      <c r="X15" s="107"/>
-      <c r="Y15" s="104"/>
+        <v>4096.9799999999996</v>
+      </c>
+      <c r="X15" s="108"/>
+      <c r="Y15" s="105"/>
     </row>
     <row r="16" spans="1:47" ht="15.75">
       <c r="A16" s="66">
@@ -14155,7 +14325,9 @@
       <c r="C16" s="72"/>
       <c r="D16" s="72"/>
       <c r="E16" s="72"/>
-      <c r="F16" s="72"/>
+      <c r="F16" s="72">
+        <v>1080</v>
+      </c>
       <c r="G16" s="72"/>
       <c r="H16" s="72"/>
       <c r="I16" s="72"/>
@@ -14164,22 +14336,26 @@
       <c r="L16" s="72"/>
       <c r="M16" s="72"/>
       <c r="N16" s="72"/>
-      <c r="O16" s="72"/>
+      <c r="O16" s="72">
+        <v>413</v>
+      </c>
       <c r="P16" s="72"/>
       <c r="Q16" s="72"/>
       <c r="R16" s="72"/>
       <c r="S16" s="72"/>
-      <c r="T16" s="109">
+      <c r="T16" s="88">
+        <v>1100</v>
+      </c>
+      <c r="U16" s="88">
         <v>4000</v>
       </c>
-      <c r="U16" s="72"/>
       <c r="V16" s="72"/>
       <c r="W16" s="72">
         <f t="shared" si="0"/>
-        <v>4000</v>
-      </c>
-      <c r="X16" s="107"/>
-      <c r="Y16" s="104"/>
+        <v>6593</v>
+      </c>
+      <c r="X16" s="108"/>
+      <c r="Y16" s="105"/>
     </row>
     <row r="17" spans="1:27" ht="15.75">
       <c r="A17" s="62">
@@ -14205,21 +14381,21 @@
       <c r="Q17" s="71"/>
       <c r="R17" s="71"/>
       <c r="S17" s="71"/>
-      <c r="T17" s="109">
+      <c r="T17" s="88">
         <v>10000</v>
       </c>
-      <c r="U17" s="109">
+      <c r="U17" s="88">
         <v>4000</v>
       </c>
-      <c r="V17" s="109">
+      <c r="V17" s="88">
         <v>7500</v>
       </c>
       <c r="W17" s="71">
         <f t="shared" si="0"/>
         <v>21500</v>
       </c>
-      <c r="X17" s="107"/>
-      <c r="Y17" s="104"/>
+      <c r="X17" s="108"/>
+      <c r="Y17" s="105"/>
     </row>
     <row r="18" spans="1:27" ht="15.75">
       <c r="A18" s="66">
@@ -14245,7 +14421,7 @@
       <c r="Q18" s="72"/>
       <c r="R18" s="72"/>
       <c r="S18" s="72"/>
-      <c r="T18" s="109">
+      <c r="T18" s="88">
         <f>17000</f>
         <v>17000</v>
       </c>
@@ -14255,8 +14431,8 @@
         <f t="shared" si="0"/>
         <v>17000</v>
       </c>
-      <c r="X18" s="107"/>
-      <c r="Y18" s="104"/>
+      <c r="X18" s="108"/>
+      <c r="Y18" s="105"/>
     </row>
     <row r="19" spans="1:27" ht="15.75">
       <c r="A19" s="62">
@@ -14289,21 +14465,21 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="X19" s="108"/>
-      <c r="Y19" s="105"/>
+      <c r="X19" s="109"/>
+      <c r="Y19" s="106"/>
     </row>
     <row r="20" spans="1:27" ht="14.25" customHeight="1">
-      <c r="A20" s="99" t="s">
+      <c r="A20" s="100" t="s">
         <v>35</v>
       </c>
-      <c r="B20" s="99"/>
+      <c r="B20" s="100"/>
       <c r="C20" s="79">
         <f t="shared" ref="C20:X20" si="1">SUM(C3:C17)</f>
-        <v>9878.99</v>
+        <v>10242.99</v>
       </c>
       <c r="D20" s="79">
         <f t="shared" si="1"/>
-        <v>4941.25</v>
+        <v>5525.25</v>
       </c>
       <c r="E20" s="79">
         <f t="shared" si="1"/>
@@ -14311,7 +14487,7 @@
       </c>
       <c r="F20" s="79">
         <f t="shared" si="1"/>
-        <v>960</v>
+        <v>2040</v>
       </c>
       <c r="G20" s="79">
         <f t="shared" si="1"/>
@@ -14347,7 +14523,7 @@
       </c>
       <c r="O20" s="79">
         <f t="shared" si="1"/>
-        <v>2586</v>
+        <v>2999</v>
       </c>
       <c r="P20" s="79">
         <f t="shared" si="1"/>
@@ -14355,7 +14531,7 @@
       </c>
       <c r="Q20" s="79">
         <f t="shared" si="1"/>
-        <v>18525</v>
+        <v>21145.98</v>
       </c>
       <c r="R20" s="79">
         <f t="shared" si="1"/>
@@ -14363,15 +14539,15 @@
       </c>
       <c r="S20" s="79">
         <f t="shared" si="1"/>
-        <v>4372.63</v>
+        <v>4572.63</v>
       </c>
       <c r="T20" s="79">
         <f t="shared" si="1"/>
-        <v>15188</v>
+        <v>12288</v>
       </c>
       <c r="U20" s="79">
         <f t="shared" si="1"/>
-        <v>4000</v>
+        <v>8000</v>
       </c>
       <c r="V20" s="79">
         <f t="shared" si="1"/>
@@ -14379,7 +14555,7 @@
       </c>
       <c r="W20" s="82">
         <f t="shared" si="1"/>
-        <v>80632.849999999991</v>
+        <v>86994.829999999987</v>
       </c>
       <c r="X20" s="83">
         <f t="shared" si="1"/>
@@ -14387,7 +14563,7 @@
       </c>
       <c r="Y20" s="84">
         <f>X20-W20</f>
-        <v>18026.974999999991</v>
+        <v>11664.994999999995</v>
       </c>
     </row>
     <row r="21" spans="1:27" ht="15.75">
@@ -14419,7 +14595,7 @@
       <c r="V21" s="71"/>
       <c r="W21" s="71"/>
       <c r="X21" s="64"/>
-      <c r="Y21" s="103"/>
+      <c r="Y21" s="104"/>
     </row>
     <row r="22" spans="1:27" ht="15.75">
       <c r="A22" s="66">
@@ -14449,8 +14625,8 @@
       <c r="U22" s="72"/>
       <c r="V22" s="72"/>
       <c r="W22" s="72"/>
-      <c r="X22" s="106"/>
-      <c r="Y22" s="104"/>
+      <c r="X22" s="107"/>
+      <c r="Y22" s="105"/>
       <c r="AA22" s="44"/>
     </row>
     <row r="23" spans="1:27" ht="15.75">
@@ -14481,8 +14657,8 @@
       <c r="U23" s="71"/>
       <c r="V23" s="71"/>
       <c r="W23" s="71"/>
-      <c r="X23" s="107"/>
-      <c r="Y23" s="104"/>
+      <c r="X23" s="108"/>
+      <c r="Y23" s="105"/>
     </row>
     <row r="24" spans="1:27" ht="15.75">
       <c r="A24" s="66">
@@ -14512,8 +14688,8 @@
       <c r="U24" s="72"/>
       <c r="V24" s="72"/>
       <c r="W24" s="72"/>
-      <c r="X24" s="107"/>
-      <c r="Y24" s="104"/>
+      <c r="X24" s="108"/>
+      <c r="Y24" s="105"/>
     </row>
     <row r="25" spans="1:27" ht="15.75">
       <c r="A25" s="62">
@@ -14543,8 +14719,8 @@
       <c r="U25" s="71"/>
       <c r="V25" s="71"/>
       <c r="W25" s="71"/>
-      <c r="X25" s="107"/>
-      <c r="Y25" s="104"/>
+      <c r="X25" s="108"/>
+      <c r="Y25" s="105"/>
     </row>
     <row r="26" spans="1:27" ht="15.75">
       <c r="A26" s="66">
@@ -14574,8 +14750,8 @@
       <c r="U26" s="72"/>
       <c r="V26" s="72"/>
       <c r="W26" s="72"/>
-      <c r="X26" s="107"/>
-      <c r="Y26" s="104"/>
+      <c r="X26" s="108"/>
+      <c r="Y26" s="105"/>
     </row>
     <row r="27" spans="1:27" ht="15.75">
       <c r="A27" s="62">
@@ -14605,8 +14781,8 @@
       <c r="U27" s="71"/>
       <c r="V27" s="71"/>
       <c r="W27" s="71"/>
-      <c r="X27" s="107"/>
-      <c r="Y27" s="104"/>
+      <c r="X27" s="108"/>
+      <c r="Y27" s="105"/>
     </row>
     <row r="28" spans="1:27" ht="15.75">
       <c r="A28" s="66">
@@ -14636,8 +14812,8 @@
       <c r="U28" s="72"/>
       <c r="V28" s="72"/>
       <c r="W28" s="72"/>
-      <c r="X28" s="107"/>
-      <c r="Y28" s="104"/>
+      <c r="X28" s="108"/>
+      <c r="Y28" s="105"/>
     </row>
     <row r="29" spans="1:27" ht="15.75">
       <c r="A29" s="62">
@@ -14667,8 +14843,8 @@
       <c r="U29" s="71"/>
       <c r="V29" s="71"/>
       <c r="W29" s="71"/>
-      <c r="X29" s="107"/>
-      <c r="Y29" s="104"/>
+      <c r="X29" s="108"/>
+      <c r="Y29" s="105"/>
     </row>
     <row r="30" spans="1:27" ht="15.75">
       <c r="A30" s="66">
@@ -14698,8 +14874,8 @@
       <c r="U30" s="72"/>
       <c r="V30" s="72"/>
       <c r="W30" s="72"/>
-      <c r="X30" s="107"/>
-      <c r="Y30" s="104"/>
+      <c r="X30" s="108"/>
+      <c r="Y30" s="105"/>
     </row>
     <row r="31" spans="1:27" ht="15.75">
       <c r="A31" s="62">
@@ -14729,8 +14905,8 @@
       <c r="U31" s="71"/>
       <c r="V31" s="71"/>
       <c r="W31" s="71"/>
-      <c r="X31" s="107"/>
-      <c r="Y31" s="104"/>
+      <c r="X31" s="108"/>
+      <c r="Y31" s="105"/>
     </row>
     <row r="32" spans="1:27" ht="15.75">
       <c r="A32" s="66">
@@ -14760,8 +14936,8 @@
       <c r="U32" s="72"/>
       <c r="V32" s="72"/>
       <c r="W32" s="72"/>
-      <c r="X32" s="107"/>
-      <c r="Y32" s="104"/>
+      <c r="X32" s="108"/>
+      <c r="Y32" s="105"/>
     </row>
     <row r="33" spans="1:25" ht="15.75">
       <c r="A33" s="62">
@@ -14791,8 +14967,8 @@
       <c r="U33" s="71"/>
       <c r="V33" s="71"/>
       <c r="W33" s="71"/>
-      <c r="X33" s="107"/>
-      <c r="Y33" s="104"/>
+      <c r="X33" s="108"/>
+      <c r="Y33" s="105"/>
     </row>
     <row r="34" spans="1:25" ht="15.75">
       <c r="A34" s="66">
@@ -14822,8 +14998,8 @@
       <c r="U34" s="72"/>
       <c r="V34" s="72"/>
       <c r="W34" s="72"/>
-      <c r="X34" s="107"/>
-      <c r="Y34" s="104"/>
+      <c r="X34" s="108"/>
+      <c r="Y34" s="105"/>
     </row>
     <row r="35" spans="1:25" ht="15.75">
       <c r="A35" s="62">
@@ -14853,8 +15029,8 @@
       <c r="U35" s="71"/>
       <c r="V35" s="71"/>
       <c r="W35" s="71"/>
-      <c r="X35" s="107"/>
-      <c r="Y35" s="104"/>
+      <c r="X35" s="108"/>
+      <c r="Y35" s="105"/>
     </row>
     <row r="36" spans="1:25" ht="15.75">
       <c r="A36" s="66">
@@ -14884,14 +15060,14 @@
       <c r="U36" s="72"/>
       <c r="V36" s="72"/>
       <c r="W36" s="72"/>
-      <c r="X36" s="108"/>
-      <c r="Y36" s="105"/>
+      <c r="X36" s="109"/>
+      <c r="Y36" s="106"/>
     </row>
     <row r="37" spans="1:25">
-      <c r="A37" s="99" t="s">
+      <c r="A37" s="100" t="s">
         <v>36</v>
       </c>
-      <c r="B37" s="99"/>
+      <c r="B37" s="100"/>
       <c r="C37" s="79">
         <f>SUM(C21:C36)</f>
         <v>0</v>
@@ -14986,17 +15162,17 @@
       </c>
     </row>
     <row r="38" spans="1:25" ht="31.5" customHeight="1">
-      <c r="A38" s="102" t="s">
+      <c r="A38" s="103" t="s">
         <v>37</v>
       </c>
-      <c r="B38" s="102"/>
+      <c r="B38" s="103"/>
       <c r="C38" s="78">
         <f>SUM(C20,C37)</f>
-        <v>9878.99</v>
+        <v>10242.99</v>
       </c>
       <c r="D38" s="78">
         <f t="shared" ref="D38:W38" si="3">SUM(D20,D37)</f>
-        <v>4941.25</v>
+        <v>5525.25</v>
       </c>
       <c r="E38" s="78">
         <f t="shared" si="3"/>
@@ -15004,7 +15180,7 @@
       </c>
       <c r="F38" s="78">
         <f t="shared" si="3"/>
-        <v>960</v>
+        <v>2040</v>
       </c>
       <c r="G38" s="78">
         <f t="shared" si="3"/>
@@ -15040,7 +15216,7 @@
       </c>
       <c r="O38" s="78">
         <f t="shared" si="3"/>
-        <v>2586</v>
+        <v>2999</v>
       </c>
       <c r="P38" s="78">
         <f t="shared" si="3"/>
@@ -15048,7 +15224,7 @@
       </c>
       <c r="Q38" s="78">
         <f t="shared" si="3"/>
-        <v>18525</v>
+        <v>21145.98</v>
       </c>
       <c r="R38" s="78">
         <f t="shared" si="3"/>
@@ -15056,15 +15232,15 @@
       </c>
       <c r="S38" s="78">
         <f>SUM(S20,S37)</f>
-        <v>4372.63</v>
+        <v>4572.63</v>
       </c>
       <c r="T38" s="78">
         <f t="shared" si="3"/>
-        <v>15188</v>
+        <v>12288</v>
       </c>
       <c r="U38" s="78">
         <f t="shared" si="3"/>
-        <v>4000</v>
+        <v>8000</v>
       </c>
       <c r="V38" s="78">
         <f t="shared" si="3"/>
@@ -15072,7 +15248,7 @@
       </c>
       <c r="W38" s="86">
         <f t="shared" si="3"/>
-        <v>80632.849999999991</v>
+        <v>86994.829999999987</v>
       </c>
       <c r="X38" s="86">
         <f>SUM(X20,X37)</f>
@@ -15080,7 +15256,7 @@
       </c>
       <c r="Y38" s="87">
         <f>SUM(Y20,Y37)</f>
-        <v>18026.974999999991</v>
+        <v>11664.994999999995</v>
       </c>
     </row>
     <row r="42" spans="1:25">

--- a/Другое/2026/Доходы-Расходы_copy.xlsx
+++ b/Другое/2026/Доходы-Расходы_copy.xlsx
@@ -1,8 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="6" rupBuild="4507"/>
-  <workbookPr filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="6"/>
   </bookViews>
@@ -15,9 +15,9 @@
     <sheet name=" Июнь 2026" sheetId="7" r:id="rId6"/>
     <sheet name="Июль 2026" sheetId="8" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="125725"/>
-  <extLst xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main">
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+  <calcPr calcId="162913"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
@@ -30,7 +30,7 @@
     <author>Автор</author>
   </authors>
   <commentList>
-    <comment ref="S3" authorId="0">
+    <comment ref="S3" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -57,7 +57,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P11" authorId="0">
+    <comment ref="P11" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -84,7 +84,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R16" authorId="0">
+    <comment ref="R16" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -111,7 +111,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P20" authorId="0">
+    <comment ref="P20" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -137,7 +137,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P24" authorId="0">
+    <comment ref="P24" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -163,7 +163,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H25" authorId="0">
+    <comment ref="H25" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -190,7 +190,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J25" authorId="0">
+    <comment ref="J25" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -216,7 +216,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J26" authorId="0">
+    <comment ref="J26" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -242,7 +242,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L26" authorId="0">
+    <comment ref="L26" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -268,7 +268,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P26" authorId="0">
+    <comment ref="P26" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -294,7 +294,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J27" authorId="0">
+    <comment ref="J27" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -330,7 +330,7 @@
     <author>Автор</author>
   </authors>
   <commentList>
-    <comment ref="R3" authorId="0">
+    <comment ref="R3" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -356,7 +356,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F4" authorId="0">
+    <comment ref="F4" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -382,7 +382,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R4" authorId="0">
+    <comment ref="R4" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -409,7 +409,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S4" authorId="0">
+    <comment ref="S4" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -435,7 +435,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T4" authorId="0">
+    <comment ref="T4" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -461,7 +461,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G5" authorId="0">
+    <comment ref="G5" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -487,7 +487,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P5" authorId="0">
+    <comment ref="P5" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -513,7 +513,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P6" authorId="0">
+    <comment ref="P6" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -540,7 +540,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S10" authorId="0">
+    <comment ref="S10" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -566,7 +566,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A11" authorId="0">
+    <comment ref="A11" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -592,7 +592,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R18" authorId="0">
+    <comment ref="R18" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -619,7 +619,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S18" authorId="0">
+    <comment ref="S18" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -645,7 +645,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R19" authorId="0">
+    <comment ref="R19" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -672,7 +672,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S19" authorId="0">
+    <comment ref="S19" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -698,7 +698,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S20" authorId="0">
+    <comment ref="S20" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -724,7 +724,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T20" authorId="0">
+    <comment ref="T20" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -750,7 +750,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S22" authorId="0">
+    <comment ref="S22" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -776,7 +776,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S26" authorId="0">
+    <comment ref="S26" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -812,7 +812,7 @@
     <author>Автор</author>
   </authors>
   <commentList>
-    <comment ref="Q3" authorId="0">
+    <comment ref="Q3" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -828,7 +828,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S3" authorId="0">
+    <comment ref="S3" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -855,7 +855,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T3" authorId="0">
+    <comment ref="T3" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -882,7 +882,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="U3" authorId="0">
+    <comment ref="U3" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -908,7 +908,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H4" authorId="0">
+    <comment ref="H4" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -934,7 +934,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K4" authorId="0">
+    <comment ref="K4" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -960,7 +960,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N4" authorId="0">
+    <comment ref="N4" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -986,7 +986,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q4" authorId="0">
+    <comment ref="Q4" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1013,7 +1013,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S4" authorId="0">
+    <comment ref="S4" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1040,7 +1040,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="U4" authorId="0">
+    <comment ref="U4" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1067,7 +1067,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V4" authorId="0">
+    <comment ref="V4" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1093,7 +1093,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I5" authorId="0">
+    <comment ref="I5" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1120,7 +1120,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S5" authorId="0">
+    <comment ref="S5" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1146,7 +1146,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K6" authorId="0">
+    <comment ref="K6" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1173,7 +1173,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S6" authorId="0">
+    <comment ref="S6" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1200,7 +1200,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H8" authorId="0">
+    <comment ref="H8" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1216,7 +1216,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E10" authorId="0">
+    <comment ref="E10" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1243,7 +1243,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X11" authorId="0">
+    <comment ref="X11" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1270,7 +1270,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X12" authorId="0">
+    <comment ref="X12" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1296,7 +1296,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H14" authorId="0">
+    <comment ref="H14" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1323,7 +1323,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H15" authorId="0">
+    <comment ref="H15" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1339,7 +1339,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T15" authorId="0">
+    <comment ref="T15" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1354,7 +1354,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E17" authorId="0">
+    <comment ref="E17" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1380,7 +1380,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q17" authorId="0">
+    <comment ref="Q17" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1406,7 +1406,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S19" authorId="0">
+    <comment ref="S19" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1432,7 +1432,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S21" authorId="0">
+    <comment ref="S21" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1459,7 +1459,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T21" authorId="0">
+    <comment ref="T21" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1485,7 +1485,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F22" authorId="0">
+    <comment ref="F22" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1511,7 +1511,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H22" authorId="0">
+    <comment ref="H22" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1537,7 +1537,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T22" authorId="0">
+    <comment ref="T22" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1563,7 +1563,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E24" authorId="0">
+    <comment ref="E24" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1590,7 +1590,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F25" authorId="0">
+    <comment ref="F25" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1617,7 +1617,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E27" authorId="0">
+    <comment ref="E27" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1644,7 +1644,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H29" authorId="0">
+    <comment ref="H29" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1670,7 +1670,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S29" authorId="0">
+    <comment ref="S29" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1696,7 +1696,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F30" authorId="0">
+    <comment ref="F30" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1722,7 +1722,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X30" authorId="0">
+    <comment ref="X30" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1748,7 +1748,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H31" authorId="0">
+    <comment ref="H31" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1774,7 +1774,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S33" authorId="0">
+    <comment ref="S33" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1800,7 +1800,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X35" authorId="0">
+    <comment ref="X35" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1836,7 +1836,7 @@
     <author>Автор</author>
   </authors>
   <commentList>
-    <comment ref="S3" authorId="0">
+    <comment ref="S3" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1862,7 +1862,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T3" authorId="0">
+    <comment ref="T3" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1889,7 +1889,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H4" authorId="0">
+    <comment ref="H4" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1915,7 +1915,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F5" authorId="0">
+    <comment ref="F5" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1941,7 +1941,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S5" authorId="0">
+    <comment ref="S5" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1967,7 +1967,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H6" authorId="0">
+    <comment ref="H6" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1993,7 +1993,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K7" authorId="0">
+    <comment ref="K7" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -2019,7 +2019,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X7" authorId="0">
+    <comment ref="X7" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -2045,7 +2045,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K8" authorId="0">
+    <comment ref="K8" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -2071,7 +2071,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K9" authorId="0">
+    <comment ref="K9" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -2097,7 +2097,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F10" authorId="0">
+    <comment ref="F10" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -2124,7 +2124,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H11" authorId="0">
+    <comment ref="H11" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -2150,7 +2150,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H13" authorId="0">
+    <comment ref="H13" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -2177,7 +2177,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q19" authorId="0">
+    <comment ref="Q19" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -2203,7 +2203,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S19" authorId="0">
+    <comment ref="S19" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -2229,7 +2229,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T20" authorId="0">
+    <comment ref="T20" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -2256,7 +2256,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H21" authorId="0">
+    <comment ref="H21" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -2282,7 +2282,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T21" authorId="0">
+    <comment ref="T21" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -2309,7 +2309,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X21" authorId="0">
+    <comment ref="X21" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -2335,7 +2335,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J24" authorId="0">
+    <comment ref="J24" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -2361,7 +2361,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S24" authorId="0">
+    <comment ref="S24" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -2387,7 +2387,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V25" authorId="0">
+    <comment ref="V25" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -2413,7 +2413,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H27" authorId="0">
+    <comment ref="H27" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -2439,7 +2439,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S27" authorId="0">
+    <comment ref="S27" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -2465,7 +2465,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H28" authorId="0">
+    <comment ref="H28" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -2491,7 +2491,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V28" authorId="0">
+    <comment ref="V28" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -2518,7 +2518,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X28" authorId="0">
+    <comment ref="X28" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -2544,7 +2544,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E29" authorId="0">
+    <comment ref="E29" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -2570,7 +2570,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X29" authorId="0">
+    <comment ref="X29" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -2596,7 +2596,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S31" authorId="0">
+    <comment ref="S31" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -2622,7 +2622,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S33" authorId="0">
+    <comment ref="S33" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -2648,7 +2648,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X34" authorId="0">
+    <comment ref="X34" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -2685,7 +2685,7 @@
     <author>Автор</author>
   </authors>
   <commentList>
-    <comment ref="F3" authorId="0">
+    <comment ref="F3" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -2711,7 +2711,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H3" authorId="0">
+    <comment ref="H3" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -2737,7 +2737,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S3" authorId="0">
+    <comment ref="S3" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -2763,7 +2763,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T3" authorId="0">
+    <comment ref="T3" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -2789,7 +2789,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V3" authorId="0">
+    <comment ref="V3" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -2815,7 +2815,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H4" authorId="0">
+    <comment ref="H4" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -2841,7 +2841,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N4" authorId="0">
+    <comment ref="N4" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -2867,7 +2867,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q4" authorId="0">
+    <comment ref="Q4" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -2893,7 +2893,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S4" authorId="0">
+    <comment ref="S4" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -2919,7 +2919,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H5" authorId="0">
+    <comment ref="H5" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -2945,7 +2945,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T5" authorId="0">
+    <comment ref="T5" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -2971,7 +2971,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F6" authorId="0">
+    <comment ref="F6" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -2997,7 +2997,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H6" authorId="0">
+    <comment ref="H6" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -3023,7 +3023,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T6" authorId="0">
+    <comment ref="T6" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -3049,7 +3049,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q7" authorId="0">
+    <comment ref="Q7" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -3075,7 +3075,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F8" authorId="0">
+    <comment ref="F8" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -3101,7 +3101,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q8" authorId="0">
+    <comment ref="Q8" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -3127,7 +3127,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S8" authorId="0">
+    <comment ref="S8" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -3153,7 +3153,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q9" authorId="0">
+    <comment ref="Q9" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -3179,7 +3179,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X9" authorId="0">
+    <comment ref="X9" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -3205,7 +3205,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E10" authorId="0">
+    <comment ref="E10" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -3231,7 +3231,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E11" authorId="0">
+    <comment ref="E11" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -3257,7 +3257,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I11" authorId="0">
+    <comment ref="I11" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -3283,7 +3283,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q12" authorId="0">
+    <comment ref="Q12" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -3310,7 +3310,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q13" authorId="0">
+    <comment ref="Q13" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -3336,7 +3336,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S13" authorId="0">
+    <comment ref="S13" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -3362,7 +3362,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X14" authorId="0">
+    <comment ref="X14" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -3388,7 +3388,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X16" authorId="0">
+    <comment ref="X16" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -3414,7 +3414,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H17" authorId="0">
+    <comment ref="H17" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -3441,7 +3441,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S17" authorId="0">
+    <comment ref="S17" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -3467,7 +3467,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T17" authorId="0">
+    <comment ref="T17" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -3493,7 +3493,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H19" authorId="0">
+    <comment ref="H19" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -3519,7 +3519,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N19" authorId="0">
+    <comment ref="N19" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -3555,7 +3555,7 @@
     <author>Автор</author>
   </authors>
   <commentList>
-    <comment ref="Q3" authorId="0">
+    <comment ref="Q3" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -3582,7 +3582,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S3" authorId="0">
+    <comment ref="S3" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -3608,7 +3608,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H4" authorId="0">
+    <comment ref="H4" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -3634,7 +3634,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S5" authorId="0">
+    <comment ref="S5" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -3661,7 +3661,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V6" authorId="0">
+    <comment ref="V6" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -3687,7 +3687,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F7" authorId="0">
+    <comment ref="F7" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -3713,7 +3713,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q8" authorId="0">
+    <comment ref="Q8" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -3740,7 +3740,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S8" authorId="0">
+    <comment ref="S8" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -3767,7 +3767,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S9" authorId="0">
+    <comment ref="S9" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -3793,7 +3793,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E10" authorId="0">
+    <comment ref="E10" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -3819,7 +3819,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S10" authorId="0">
+    <comment ref="S10" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -3845,7 +3845,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q12" authorId="0">
+    <comment ref="Q12" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -3871,7 +3871,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q13" authorId="0">
+    <comment ref="Q13" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -3898,7 +3898,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S13" authorId="0">
+    <comment ref="S13" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -3924,7 +3924,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q15" authorId="0">
+    <comment ref="Q15" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -3950,7 +3950,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S15" authorId="0">
+    <comment ref="S15" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -3976,7 +3976,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F16" authorId="0">
+    <comment ref="F16" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -4002,7 +4002,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T16" authorId="0">
+    <comment ref="T16" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -4017,16 +4017,15 @@
         </r>
       </text>
     </comment>
-    <comment ref="U16" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="204"/>
+    <comment ref="S17" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
           </rPr>
           <t>Автор:</t>
         </r>
@@ -4035,24 +4034,22 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="204"/>
+            <charset val="1"/>
           </rPr>
           <t xml:space="preserve">
-Простава на работе</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="T17" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="204"/>
+Интернет</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="S18" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
           </rPr>
           <t>Автор:</t>
         </r>
@@ -4061,24 +4058,22 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="204"/>
+            <charset val="1"/>
           </rPr>
           <t xml:space="preserve">
-Снять квартиру в мск</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="U17" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="204"/>
+Яндекс Плюс</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="U18" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
           </rPr>
           <t>Автор:</t>
         </r>
@@ -4087,25 +4082,22 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="204"/>
+            <charset val="1"/>
           </rPr>
           <t xml:space="preserve">
-Билеты на электричку
-туда-обратно</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="V17" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="204"/>
+Подарок Кулику</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="V19" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
           </rPr>
           <t>Автор:</t>
         </r>
@@ -4114,37 +4106,10 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="204"/>
+            <charset val="1"/>
           </rPr>
           <t xml:space="preserve">
-Подарок кулику</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="T18" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="204"/>
-          </rPr>
-          <t>Автор:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="204"/>
-          </rPr>
-          <t xml:space="preserve">
-Покушать и погулять в МСК</t>
+Поездка в МСК к Кулику на ДР</t>
         </r>
       </text>
     </comment>
@@ -4339,11 +4304,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;₽&quot;"/>
   </numFmts>
-  <fonts count="30">
+  <fonts count="32">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4569,6 +4534,19 @@
       <charset val="204"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="21">
     <fill>
@@ -4687,7 +4665,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor theme="2" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5101,9 +5079,6 @@
     <xf numFmtId="164" fontId="20" fillId="19" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="20" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -5166,6 +5141,9 @@
     </xf>
     <xf numFmtId="164" fontId="23" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="20" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5504,14 +5482,14 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="C3:H17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -5545,7 +5523,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="3:8" ht="16.5">
+    <row r="5" spans="3:8" ht="15.75">
       <c r="C5" s="52" t="s">
         <v>43</v>
       </c>
@@ -5565,7 +5543,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="6" spans="3:8" ht="16.5">
+    <row r="6" spans="3:8" ht="15.75">
       <c r="C6" s="52" t="s">
         <v>44</v>
       </c>
@@ -5586,7 +5564,7 @@
         <v>1260.5599999999977</v>
       </c>
     </row>
-    <row r="7" spans="3:8" ht="16.5">
+    <row r="7" spans="3:8" ht="15.75">
       <c r="C7" s="52" t="s">
         <v>45</v>
       </c>
@@ -5607,7 +5585,7 @@
         <v>-11931.300000000003</v>
       </c>
     </row>
-    <row r="8" spans="3:8" ht="16.5">
+    <row r="8" spans="3:8" ht="15.75">
       <c r="C8" s="52" t="s">
         <v>46</v>
       </c>
@@ -5628,7 +5606,7 @@
         <v>59.059999999997672</v>
       </c>
     </row>
-    <row r="9" spans="3:8" ht="16.5">
+    <row r="9" spans="3:8" ht="15.75">
       <c r="C9" s="52" t="s">
         <v>47</v>
       </c>
@@ -5638,7 +5616,7 @@
       <c r="G9" s="51"/>
       <c r="H9" s="51"/>
     </row>
-    <row r="10" spans="3:8" ht="16.5">
+    <row r="10" spans="3:8" ht="15.75">
       <c r="C10" s="52" t="s">
         <v>48</v>
       </c>
@@ -5648,7 +5626,7 @@
       <c r="G10" s="51"/>
       <c r="H10" s="51"/>
     </row>
-    <row r="11" spans="3:8" ht="16.5">
+    <row r="11" spans="3:8" ht="15.75">
       <c r="C11" s="52" t="s">
         <v>49</v>
       </c>
@@ -5658,7 +5636,7 @@
       <c r="G11" s="51"/>
       <c r="H11" s="51"/>
     </row>
-    <row r="12" spans="3:8" ht="16.5">
+    <row r="12" spans="3:8" ht="15.75">
       <c r="C12" s="52" t="s">
         <v>50</v>
       </c>
@@ -5668,7 +5646,7 @@
       <c r="G12" s="51"/>
       <c r="H12" s="51"/>
     </row>
-    <row r="13" spans="3:8" ht="16.5">
+    <row r="13" spans="3:8" ht="15.75">
       <c r="C13" s="52" t="s">
         <v>51</v>
       </c>
@@ -5678,7 +5656,7 @@
       <c r="G13" s="51"/>
       <c r="H13" s="51"/>
     </row>
-    <row r="14" spans="3:8" ht="16.5">
+    <row r="14" spans="3:8" ht="15.75">
       <c r="C14" s="52" t="s">
         <v>52</v>
       </c>
@@ -5688,7 +5666,7 @@
       <c r="G14" s="51"/>
       <c r="H14" s="51"/>
     </row>
-    <row r="15" spans="3:8" ht="16.5">
+    <row r="15" spans="3:8" ht="15.75">
       <c r="C15" s="52" t="s">
         <v>53</v>
       </c>
@@ -5698,7 +5676,7 @@
       <c r="G15" s="51"/>
       <c r="H15" s="51"/>
     </row>
-    <row r="16" spans="3:8" ht="17.25" thickBot="1">
+    <row r="16" spans="3:8" ht="16.5" thickBot="1">
       <c r="C16" s="53" t="s">
         <v>54</v>
       </c>
@@ -5708,7 +5686,7 @@
       <c r="G16" s="54"/>
       <c r="H16" s="54"/>
     </row>
-    <row r="17" spans="3:8" ht="17.25" thickBot="1">
+    <row r="17" spans="3:8" ht="16.5" thickBot="1">
       <c r="C17" s="55" t="s">
         <v>20</v>
       </c>
@@ -5741,7 +5719,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AT35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -5751,32 +5729,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:46" ht="60.75" customHeight="1">
-      <c r="A1" s="89" t="s">
+      <c r="A1" s="88" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="89"/>
-      <c r="C1" s="89"/>
-      <c r="D1" s="89"/>
-      <c r="E1" s="89"/>
-      <c r="F1" s="89"/>
-      <c r="G1" s="89"/>
-      <c r="H1" s="89"/>
-      <c r="I1" s="89"/>
-      <c r="J1" s="89"/>
-      <c r="K1" s="89"/>
-      <c r="L1" s="89"/>
-      <c r="M1" s="89"/>
-      <c r="N1" s="89"/>
-      <c r="O1" s="89"/>
-      <c r="P1" s="89"/>
-      <c r="Q1" s="89"/>
-      <c r="R1" s="89"/>
-      <c r="S1" s="89"/>
-      <c r="T1" s="89"/>
-      <c r="U1" s="89"/>
-      <c r="V1" s="89"/>
-      <c r="W1" s="89"/>
-      <c r="X1" s="89"/>
+      <c r="B1" s="88"/>
+      <c r="C1" s="88"/>
+      <c r="D1" s="88"/>
+      <c r="E1" s="88"/>
+      <c r="F1" s="88"/>
+      <c r="G1" s="88"/>
+      <c r="H1" s="88"/>
+      <c r="I1" s="88"/>
+      <c r="J1" s="88"/>
+      <c r="K1" s="88"/>
+      <c r="L1" s="88"/>
+      <c r="M1" s="88"/>
+      <c r="N1" s="88"/>
+      <c r="O1" s="88"/>
+      <c r="P1" s="88"/>
+      <c r="Q1" s="88"/>
+      <c r="R1" s="88"/>
+      <c r="S1" s="88"/>
+      <c r="T1" s="88"/>
+      <c r="U1" s="88"/>
+      <c r="V1" s="88"/>
+      <c r="W1" s="88"/>
+      <c r="X1" s="88"/>
     </row>
     <row r="2" spans="1:46" ht="45" customHeight="1">
       <c r="A2" s="3" t="s">
@@ -6975,10 +6953,10 @@
       </c>
     </row>
     <row r="31" spans="1:24">
-      <c r="A31" s="90" t="s">
+      <c r="A31" s="89" t="s">
         <v>20</v>
       </c>
-      <c r="B31" s="90"/>
+      <c r="B31" s="89"/>
       <c r="C31" s="13">
         <f>SUM(C3:C30)</f>
         <v>19992.27</v>
@@ -7091,7 +7069,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AT36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -7101,32 +7079,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:46" ht="60.75" customHeight="1">
-      <c r="A1" s="92" t="s">
+      <c r="A1" s="91" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="92"/>
-      <c r="C1" s="92"/>
-      <c r="D1" s="92"/>
-      <c r="E1" s="92"/>
-      <c r="F1" s="92"/>
-      <c r="G1" s="92"/>
-      <c r="H1" s="92"/>
-      <c r="I1" s="92"/>
-      <c r="J1" s="92"/>
-      <c r="K1" s="92"/>
-      <c r="L1" s="92"/>
-      <c r="M1" s="92"/>
-      <c r="N1" s="92"/>
-      <c r="O1" s="92"/>
-      <c r="P1" s="92"/>
-      <c r="Q1" s="92"/>
-      <c r="R1" s="92"/>
-      <c r="S1" s="92"/>
-      <c r="T1" s="92"/>
-      <c r="U1" s="92"/>
-      <c r="V1" s="92"/>
-      <c r="W1" s="92"/>
-      <c r="X1" s="92"/>
+      <c r="B1" s="91"/>
+      <c r="C1" s="91"/>
+      <c r="D1" s="91"/>
+      <c r="E1" s="91"/>
+      <c r="F1" s="91"/>
+      <c r="G1" s="91"/>
+      <c r="H1" s="91"/>
+      <c r="I1" s="91"/>
+      <c r="J1" s="91"/>
+      <c r="K1" s="91"/>
+      <c r="L1" s="91"/>
+      <c r="M1" s="91"/>
+      <c r="N1" s="91"/>
+      <c r="O1" s="91"/>
+      <c r="P1" s="91"/>
+      <c r="Q1" s="91"/>
+      <c r="R1" s="91"/>
+      <c r="S1" s="91"/>
+      <c r="T1" s="91"/>
+      <c r="U1" s="91"/>
+      <c r="V1" s="91"/>
+      <c r="W1" s="91"/>
+      <c r="X1" s="91"/>
     </row>
     <row r="2" spans="1:46" ht="45" customHeight="1">
       <c r="A2" s="30" t="s">
@@ -8337,10 +8315,10 @@
       <c r="X31" s="31"/>
     </row>
     <row r="32" spans="1:24">
-      <c r="A32" s="91" t="s">
+      <c r="A32" s="90" t="s">
         <v>20</v>
       </c>
-      <c r="B32" s="91"/>
+      <c r="B32" s="90"/>
       <c r="C32" s="28">
         <f>SUM(C3:C31)</f>
         <v>16843.349999999999</v>
@@ -8453,7 +8431,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AU41"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -8463,33 +8441,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:47" ht="60.75" customHeight="1">
-      <c r="A1" s="92" t="s">
+      <c r="A1" s="91" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="92"/>
-      <c r="C1" s="92"/>
-      <c r="D1" s="92"/>
-      <c r="E1" s="92"/>
-      <c r="F1" s="92"/>
-      <c r="G1" s="92"/>
-      <c r="H1" s="92"/>
-      <c r="I1" s="92"/>
-      <c r="J1" s="92"/>
-      <c r="K1" s="92"/>
-      <c r="L1" s="92"/>
-      <c r="M1" s="92"/>
-      <c r="N1" s="92"/>
-      <c r="O1" s="92"/>
-      <c r="P1" s="92"/>
-      <c r="Q1" s="92"/>
-      <c r="R1" s="92"/>
-      <c r="S1" s="92"/>
-      <c r="T1" s="92"/>
-      <c r="U1" s="92"/>
-      <c r="V1" s="92"/>
-      <c r="W1" s="92"/>
-      <c r="X1" s="92"/>
-      <c r="Y1" s="92"/>
+      <c r="B1" s="91"/>
+      <c r="C1" s="91"/>
+      <c r="D1" s="91"/>
+      <c r="E1" s="91"/>
+      <c r="F1" s="91"/>
+      <c r="G1" s="91"/>
+      <c r="H1" s="91"/>
+      <c r="I1" s="91"/>
+      <c r="J1" s="91"/>
+      <c r="K1" s="91"/>
+      <c r="L1" s="91"/>
+      <c r="M1" s="91"/>
+      <c r="N1" s="91"/>
+      <c r="O1" s="91"/>
+      <c r="P1" s="91"/>
+      <c r="Q1" s="91"/>
+      <c r="R1" s="91"/>
+      <c r="S1" s="91"/>
+      <c r="T1" s="91"/>
+      <c r="U1" s="91"/>
+      <c r="V1" s="91"/>
+      <c r="W1" s="91"/>
+      <c r="X1" s="91"/>
+      <c r="Y1" s="91"/>
     </row>
     <row r="2" spans="1:47" ht="45" customHeight="1">
       <c r="A2" s="30" t="s">
@@ -9307,10 +9285,10 @@
       <c r="Y19" s="43"/>
     </row>
     <row r="20" spans="1:27">
-      <c r="A20" s="94" t="s">
+      <c r="A20" s="93" t="s">
         <v>35</v>
       </c>
-      <c r="B20" s="95"/>
+      <c r="B20" s="94"/>
       <c r="C20" s="45">
         <f>SUM(C3:C19)</f>
         <v>12278.83</v>
@@ -10030,10 +10008,10 @@
       <c r="Y35" s="43"/>
     </row>
     <row r="36" spans="1:25">
-      <c r="A36" s="94" t="s">
+      <c r="A36" s="93" t="s">
         <v>36</v>
       </c>
-      <c r="B36" s="95"/>
+      <c r="B36" s="94"/>
       <c r="C36" s="45">
         <f>SUM(C21:C35)</f>
         <v>11057.89</v>
@@ -10128,10 +10106,10 @@
       </c>
     </row>
     <row r="37" spans="1:25" ht="31.5" customHeight="1">
-      <c r="A37" s="93" t="s">
+      <c r="A37" s="92" t="s">
         <v>37</v>
       </c>
-      <c r="B37" s="93"/>
+      <c r="B37" s="92"/>
       <c r="C37" s="48">
         <f>SUM(C20,C36)</f>
         <v>23336.720000000001</v>
@@ -10251,7 +10229,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AU40"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -10261,33 +10239,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:47" ht="60.75" customHeight="1">
-      <c r="A1" s="96" t="s">
+      <c r="A1" s="95" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="96"/>
-      <c r="C1" s="96"/>
-      <c r="D1" s="96"/>
-      <c r="E1" s="96"/>
-      <c r="F1" s="96"/>
-      <c r="G1" s="96"/>
-      <c r="H1" s="96"/>
-      <c r="I1" s="96"/>
-      <c r="J1" s="96"/>
-      <c r="K1" s="96"/>
-      <c r="L1" s="96"/>
-      <c r="M1" s="96"/>
-      <c r="N1" s="96"/>
-      <c r="O1" s="96"/>
-      <c r="P1" s="96"/>
-      <c r="Q1" s="96"/>
-      <c r="R1" s="96"/>
-      <c r="S1" s="96"/>
-      <c r="T1" s="96"/>
-      <c r="U1" s="96"/>
-      <c r="V1" s="96"/>
-      <c r="W1" s="96"/>
-      <c r="X1" s="96"/>
-      <c r="Y1" s="96"/>
+      <c r="B1" s="95"/>
+      <c r="C1" s="95"/>
+      <c r="D1" s="95"/>
+      <c r="E1" s="95"/>
+      <c r="F1" s="95"/>
+      <c r="G1" s="95"/>
+      <c r="H1" s="95"/>
+      <c r="I1" s="95"/>
+      <c r="J1" s="95"/>
+      <c r="K1" s="95"/>
+      <c r="L1" s="95"/>
+      <c r="M1" s="95"/>
+      <c r="N1" s="95"/>
+      <c r="O1" s="95"/>
+      <c r="P1" s="95"/>
+      <c r="Q1" s="95"/>
+      <c r="R1" s="95"/>
+      <c r="S1" s="95"/>
+      <c r="T1" s="95"/>
+      <c r="U1" s="95"/>
+      <c r="V1" s="95"/>
+      <c r="W1" s="95"/>
+      <c r="X1" s="95"/>
+      <c r="Y1" s="95"/>
     </row>
     <row r="2" spans="1:47" ht="45" customHeight="1">
       <c r="A2" s="59" t="s">
@@ -10997,10 +10975,10 @@
       <c r="Y17" s="65"/>
     </row>
     <row r="18" spans="1:27">
-      <c r="A18" s="97" t="s">
+      <c r="A18" s="96" t="s">
         <v>35</v>
       </c>
-      <c r="B18" s="97"/>
+      <c r="B18" s="96"/>
       <c r="C18" s="73">
         <f t="shared" ref="C18:X18" si="1">SUM(C3:C17)</f>
         <v>8428.35</v>
@@ -11753,10 +11731,10 @@
       <c r="Y34" s="69"/>
     </row>
     <row r="35" spans="1:25">
-      <c r="A35" s="97" t="s">
+      <c r="A35" s="96" t="s">
         <v>36</v>
       </c>
-      <c r="B35" s="97"/>
+      <c r="B35" s="96"/>
       <c r="C35" s="73">
         <f>SUM(C19:C34)</f>
         <v>10739.46</v>
@@ -11851,10 +11829,10 @@
       </c>
     </row>
     <row r="36" spans="1:25" ht="31.5" customHeight="1">
-      <c r="A36" s="98" t="s">
+      <c r="A36" s="97" t="s">
         <v>37</v>
       </c>
-      <c r="B36" s="98"/>
+      <c r="B36" s="97"/>
       <c r="C36" s="70">
         <f>SUM(C18,C35)</f>
         <v>19167.809999999998</v>
@@ -11982,7 +11960,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AU40"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -11992,33 +11970,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:47" ht="60.75" customHeight="1">
-      <c r="A1" s="99" t="s">
+      <c r="A1" s="98" t="s">
         <v>58</v>
       </c>
-      <c r="B1" s="99"/>
-      <c r="C1" s="99"/>
-      <c r="D1" s="99"/>
-      <c r="E1" s="99"/>
-      <c r="F1" s="99"/>
-      <c r="G1" s="99"/>
-      <c r="H1" s="99"/>
-      <c r="I1" s="99"/>
-      <c r="J1" s="99"/>
-      <c r="K1" s="99"/>
-      <c r="L1" s="99"/>
-      <c r="M1" s="99"/>
-      <c r="N1" s="99"/>
-      <c r="O1" s="99"/>
-      <c r="P1" s="99"/>
-      <c r="Q1" s="99"/>
-      <c r="R1" s="99"/>
-      <c r="S1" s="99"/>
-      <c r="T1" s="99"/>
-      <c r="U1" s="99"/>
-      <c r="V1" s="99"/>
-      <c r="W1" s="99"/>
-      <c r="X1" s="99"/>
-      <c r="Y1" s="99"/>
+      <c r="B1" s="98"/>
+      <c r="C1" s="98"/>
+      <c r="D1" s="98"/>
+      <c r="E1" s="98"/>
+      <c r="F1" s="98"/>
+      <c r="G1" s="98"/>
+      <c r="H1" s="98"/>
+      <c r="I1" s="98"/>
+      <c r="J1" s="98"/>
+      <c r="K1" s="98"/>
+      <c r="L1" s="98"/>
+      <c r="M1" s="98"/>
+      <c r="N1" s="98"/>
+      <c r="O1" s="98"/>
+      <c r="P1" s="98"/>
+      <c r="Q1" s="98"/>
+      <c r="R1" s="98"/>
+      <c r="S1" s="98"/>
+      <c r="T1" s="98"/>
+      <c r="U1" s="98"/>
+      <c r="V1" s="98"/>
+      <c r="W1" s="98"/>
+      <c r="X1" s="98"/>
+      <c r="Y1" s="98"/>
     </row>
     <row r="2" spans="1:47" ht="45" customHeight="1">
       <c r="A2" s="76" t="s">
@@ -12757,10 +12735,10 @@
       <c r="Y17" s="65"/>
     </row>
     <row r="18" spans="1:27">
-      <c r="A18" s="100" t="s">
+      <c r="A18" s="99" t="s">
         <v>35</v>
       </c>
-      <c r="B18" s="100"/>
+      <c r="B18" s="99"/>
       <c r="C18" s="79">
         <f t="shared" ref="C18:X18" si="1">SUM(C3:C17)</f>
         <v>7904</v>
@@ -13408,10 +13386,10 @@
       <c r="Y34" s="69"/>
     </row>
     <row r="35" spans="1:25">
-      <c r="A35" s="100" t="s">
+      <c r="A35" s="99" t="s">
         <v>36</v>
       </c>
-      <c r="B35" s="100"/>
+      <c r="B35" s="99"/>
       <c r="C35" s="79">
         <f>SUM(C19:C34)</f>
         <v>0</v>
@@ -13506,10 +13484,10 @@
       </c>
     </row>
     <row r="36" spans="1:25" ht="31.5" customHeight="1">
-      <c r="A36" s="101" t="s">
+      <c r="A36" s="100" t="s">
         <v>37</v>
       </c>
-      <c r="B36" s="101"/>
+      <c r="B36" s="100"/>
       <c r="C36" s="74">
         <f>SUM(C18,C35)</f>
         <v>7904</v>
@@ -13637,7 +13615,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AU42"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -13647,33 +13625,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:47" ht="60.75" customHeight="1">
-      <c r="A1" s="102" t="s">
+      <c r="A1" s="101" t="s">
         <v>59</v>
       </c>
-      <c r="B1" s="102"/>
-      <c r="C1" s="102"/>
-      <c r="D1" s="102"/>
-      <c r="E1" s="102"/>
-      <c r="F1" s="102"/>
-      <c r="G1" s="102"/>
-      <c r="H1" s="102"/>
-      <c r="I1" s="102"/>
-      <c r="J1" s="102"/>
-      <c r="K1" s="102"/>
-      <c r="L1" s="102"/>
-      <c r="M1" s="102"/>
-      <c r="N1" s="102"/>
-      <c r="O1" s="102"/>
-      <c r="P1" s="102"/>
-      <c r="Q1" s="102"/>
-      <c r="R1" s="102"/>
-      <c r="S1" s="102"/>
-      <c r="T1" s="102"/>
-      <c r="U1" s="102"/>
-      <c r="V1" s="102"/>
-      <c r="W1" s="102"/>
-      <c r="X1" s="102"/>
-      <c r="Y1" s="102"/>
+      <c r="B1" s="101"/>
+      <c r="C1" s="101"/>
+      <c r="D1" s="101"/>
+      <c r="E1" s="101"/>
+      <c r="F1" s="101"/>
+      <c r="G1" s="101"/>
+      <c r="H1" s="101"/>
+      <c r="I1" s="101"/>
+      <c r="J1" s="101"/>
+      <c r="K1" s="101"/>
+      <c r="L1" s="101"/>
+      <c r="M1" s="101"/>
+      <c r="N1" s="101"/>
+      <c r="O1" s="101"/>
+      <c r="P1" s="101"/>
+      <c r="Q1" s="101"/>
+      <c r="R1" s="101"/>
+      <c r="S1" s="101"/>
+      <c r="T1" s="101"/>
+      <c r="U1" s="101"/>
+      <c r="V1" s="101"/>
+      <c r="W1" s="101"/>
+      <c r="X1" s="101"/>
+      <c r="Y1" s="101"/>
     </row>
     <row r="2" spans="1:47" ht="45" customHeight="1">
       <c r="A2" s="76" t="s">
@@ -13820,7 +13798,7 @@
         <f>(94085+57723.67)/2</f>
         <v>75904.334999999992</v>
       </c>
-      <c r="Y3" s="104"/>
+      <c r="Y3" s="103"/>
     </row>
     <row r="4" spans="1:47" ht="15.75">
       <c r="A4" s="66">
@@ -13868,8 +13846,8 @@
         <f>SUM(C4:V4)</f>
         <v>10533.31</v>
       </c>
-      <c r="X4" s="107"/>
-      <c r="Y4" s="105"/>
+      <c r="X4" s="106"/>
+      <c r="Y4" s="104"/>
     </row>
     <row r="5" spans="1:47" ht="15.75">
       <c r="A5" s="62">
@@ -13907,8 +13885,8 @@
         <f t="shared" ref="W5:W19" si="0">SUM(C5:V5)</f>
         <v>1455</v>
       </c>
-      <c r="X5" s="108"/>
-      <c r="Y5" s="105"/>
+      <c r="X5" s="107"/>
+      <c r="Y5" s="104"/>
     </row>
     <row r="6" spans="1:47" ht="15.75">
       <c r="A6" s="66">
@@ -13947,8 +13925,8 @@
         <f t="shared" si="0"/>
         <v>1803.8400000000001</v>
       </c>
-      <c r="X6" s="108"/>
-      <c r="Y6" s="105"/>
+      <c r="X6" s="107"/>
+      <c r="Y6" s="104"/>
     </row>
     <row r="7" spans="1:47" ht="15" customHeight="1">
       <c r="A7" s="62">
@@ -13990,8 +13968,8 @@
         <f t="shared" si="0"/>
         <v>3302.61</v>
       </c>
-      <c r="X7" s="108"/>
-      <c r="Y7" s="105"/>
+      <c r="X7" s="107"/>
+      <c r="Y7" s="104"/>
     </row>
     <row r="8" spans="1:47" ht="15.75">
       <c r="A8" s="66">
@@ -14031,8 +14009,8 @@
         <f t="shared" si="0"/>
         <v>2255</v>
       </c>
-      <c r="X8" s="108"/>
-      <c r="Y8" s="105"/>
+      <c r="X8" s="107"/>
+      <c r="Y8" s="104"/>
     </row>
     <row r="9" spans="1:47" ht="15.75">
       <c r="A9" s="62">
@@ -14069,8 +14047,8 @@
         <f t="shared" si="0"/>
         <v>1095</v>
       </c>
-      <c r="X9" s="108"/>
-      <c r="Y9" s="105"/>
+      <c r="X9" s="107"/>
+      <c r="Y9" s="104"/>
     </row>
     <row r="10" spans="1:47" ht="15.75">
       <c r="A10" s="66">
@@ -14112,8 +14090,8 @@
         <f t="shared" si="0"/>
         <v>4914</v>
       </c>
-      <c r="X10" s="108"/>
-      <c r="Y10" s="105"/>
+      <c r="X10" s="107"/>
+      <c r="Y10" s="104"/>
     </row>
     <row r="11" spans="1:47" ht="15.75">
       <c r="A11" s="62">
@@ -14151,8 +14129,8 @@
         <f t="shared" si="0"/>
         <v>4632.68</v>
       </c>
-      <c r="X11" s="108"/>
-      <c r="Y11" s="105"/>
+      <c r="X11" s="107"/>
+      <c r="Y11" s="104"/>
     </row>
     <row r="12" spans="1:47" ht="15.75">
       <c r="A12" s="66">
@@ -14187,8 +14165,8 @@
         <f t="shared" si="0"/>
         <v>4475</v>
       </c>
-      <c r="X12" s="108"/>
-      <c r="Y12" s="105"/>
+      <c r="X12" s="107"/>
+      <c r="Y12" s="104"/>
     </row>
     <row r="13" spans="1:47" ht="15.75">
       <c r="A13" s="62">
@@ -14227,8 +14205,8 @@
         <f t="shared" si="0"/>
         <v>4015.63</v>
       </c>
-      <c r="X13" s="108"/>
-      <c r="Y13" s="105"/>
+      <c r="X13" s="107"/>
+      <c r="Y13" s="104"/>
     </row>
     <row r="14" spans="1:47" ht="15.75">
       <c r="A14" s="66">
@@ -14268,7 +14246,7 @@
         <f>37634-14878.51</f>
         <v>22755.489999999998</v>
       </c>
-      <c r="Y14" s="105"/>
+      <c r="Y14" s="104"/>
     </row>
     <row r="15" spans="1:47" ht="15.75">
       <c r="A15" s="62">
@@ -14312,8 +14290,8 @@
         <f t="shared" si="0"/>
         <v>4096.9799999999996</v>
       </c>
-      <c r="X15" s="108"/>
-      <c r="Y15" s="105"/>
+      <c r="X15" s="107"/>
+      <c r="Y15" s="104"/>
     </row>
     <row r="16" spans="1:47" ht="15.75">
       <c r="A16" s="66">
@@ -14343,19 +14321,17 @@
       <c r="Q16" s="72"/>
       <c r="R16" s="72"/>
       <c r="S16" s="72"/>
-      <c r="T16" s="88">
+      <c r="T16" s="72">
         <v>1100</v>
       </c>
-      <c r="U16" s="88">
-        <v>4000</v>
-      </c>
+      <c r="U16" s="109"/>
       <c r="V16" s="72"/>
       <c r="W16" s="72">
         <f t="shared" si="0"/>
-        <v>6593</v>
-      </c>
-      <c r="X16" s="108"/>
-      <c r="Y16" s="105"/>
+        <v>2593</v>
+      </c>
+      <c r="X16" s="107"/>
+      <c r="Y16" s="104"/>
     </row>
     <row r="17" spans="1:27" ht="15.75">
       <c r="A17" s="62">
@@ -14380,22 +14356,18 @@
       <c r="P17" s="71"/>
       <c r="Q17" s="71"/>
       <c r="R17" s="71"/>
-      <c r="S17" s="71"/>
-      <c r="T17" s="88">
-        <v>10000</v>
-      </c>
-      <c r="U17" s="88">
-        <v>4000</v>
-      </c>
-      <c r="V17" s="88">
-        <v>7500</v>
-      </c>
+      <c r="S17" s="71">
+        <v>700</v>
+      </c>
+      <c r="T17" s="71"/>
+      <c r="U17" s="71"/>
+      <c r="V17" s="71"/>
       <c r="W17" s="71">
         <f t="shared" si="0"/>
-        <v>21500</v>
-      </c>
-      <c r="X17" s="108"/>
-      <c r="Y17" s="105"/>
+        <v>700</v>
+      </c>
+      <c r="X17" s="107"/>
+      <c r="Y17" s="104"/>
     </row>
     <row r="18" spans="1:27" ht="15.75">
       <c r="A18" s="66">
@@ -14405,7 +14377,9 @@
         <v>5</v>
       </c>
       <c r="C18" s="72"/>
-      <c r="D18" s="72"/>
+      <c r="D18" s="72">
+        <v>2018.8</v>
+      </c>
       <c r="E18" s="72"/>
       <c r="F18" s="72"/>
       <c r="G18" s="72"/>
@@ -14420,19 +14394,20 @@
       <c r="P18" s="72"/>
       <c r="Q18" s="72"/>
       <c r="R18" s="72"/>
-      <c r="S18" s="72"/>
-      <c r="T18" s="88">
-        <f>17000</f>
-        <v>17000</v>
-      </c>
-      <c r="U18" s="72"/>
+      <c r="S18" s="72">
+        <v>499</v>
+      </c>
+      <c r="T18" s="109"/>
+      <c r="U18" s="72">
+        <v>8000</v>
+      </c>
       <c r="V18" s="72"/>
       <c r="W18" s="72">
         <f t="shared" si="0"/>
-        <v>17000</v>
-      </c>
-      <c r="X18" s="108"/>
-      <c r="Y18" s="105"/>
+        <v>10517.8</v>
+      </c>
+      <c r="X18" s="107"/>
+      <c r="Y18" s="104"/>
     </row>
     <row r="19" spans="1:27" ht="15.75">
       <c r="A19" s="62">
@@ -14442,7 +14417,9 @@
         <v>6</v>
       </c>
       <c r="C19" s="71"/>
-      <c r="D19" s="71"/>
+      <c r="D19" s="71">
+        <v>2376.09</v>
+      </c>
       <c r="E19" s="71"/>
       <c r="F19" s="71"/>
       <c r="G19" s="71"/>
@@ -14460,19 +14437,22 @@
       <c r="S19" s="71"/>
       <c r="T19" s="71"/>
       <c r="U19" s="71"/>
-      <c r="V19" s="71"/>
+      <c r="V19" s="71">
+        <f>83+760+400+6869+83+83+1800+850+1033.84+1423+1349+694+83+6000+1800+305</f>
+        <v>23615.84</v>
+      </c>
       <c r="W19" s="71">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="X19" s="109"/>
-      <c r="Y19" s="106"/>
+        <v>25991.93</v>
+      </c>
+      <c r="X19" s="108"/>
+      <c r="Y19" s="105"/>
     </row>
     <row r="20" spans="1:27" ht="14.25" customHeight="1">
-      <c r="A20" s="100" t="s">
+      <c r="A20" s="99" t="s">
         <v>35</v>
       </c>
-      <c r="B20" s="100"/>
+      <c r="B20" s="99"/>
       <c r="C20" s="79">
         <f t="shared" ref="C20:X20" si="1">SUM(C3:C17)</f>
         <v>10242.99</v>
@@ -14539,23 +14519,23 @@
       </c>
       <c r="S20" s="79">
         <f t="shared" si="1"/>
-        <v>4572.63</v>
+        <v>5272.63</v>
       </c>
       <c r="T20" s="79">
         <f t="shared" si="1"/>
-        <v>12288</v>
+        <v>2288</v>
       </c>
       <c r="U20" s="79">
         <f t="shared" si="1"/>
-        <v>8000</v>
+        <v>0</v>
       </c>
       <c r="V20" s="79">
         <f t="shared" si="1"/>
-        <v>8450</v>
+        <v>950</v>
       </c>
       <c r="W20" s="82">
         <f t="shared" si="1"/>
-        <v>86994.829999999987</v>
+        <v>62194.829999999987</v>
       </c>
       <c r="X20" s="83">
         <f t="shared" si="1"/>
@@ -14563,7 +14543,7 @@
       </c>
       <c r="Y20" s="84">
         <f>X20-W20</f>
-        <v>11664.994999999995</v>
+        <v>36464.994999999995</v>
       </c>
     </row>
     <row r="21" spans="1:27" ht="15.75">
@@ -14595,7 +14575,7 @@
       <c r="V21" s="71"/>
       <c r="W21" s="71"/>
       <c r="X21" s="64"/>
-      <c r="Y21" s="104"/>
+      <c r="Y21" s="103"/>
     </row>
     <row r="22" spans="1:27" ht="15.75">
       <c r="A22" s="66">
@@ -14625,8 +14605,8 @@
       <c r="U22" s="72"/>
       <c r="V22" s="72"/>
       <c r="W22" s="72"/>
-      <c r="X22" s="107"/>
-      <c r="Y22" s="105"/>
+      <c r="X22" s="106"/>
+      <c r="Y22" s="104"/>
       <c r="AA22" s="44"/>
     </row>
     <row r="23" spans="1:27" ht="15.75">
@@ -14657,8 +14637,8 @@
       <c r="U23" s="71"/>
       <c r="V23" s="71"/>
       <c r="W23" s="71"/>
-      <c r="X23" s="108"/>
-      <c r="Y23" s="105"/>
+      <c r="X23" s="107"/>
+      <c r="Y23" s="104"/>
     </row>
     <row r="24" spans="1:27" ht="15.75">
       <c r="A24" s="66">
@@ -14688,8 +14668,8 @@
       <c r="U24" s="72"/>
       <c r="V24" s="72"/>
       <c r="W24" s="72"/>
-      <c r="X24" s="108"/>
-      <c r="Y24" s="105"/>
+      <c r="X24" s="107"/>
+      <c r="Y24" s="104"/>
     </row>
     <row r="25" spans="1:27" ht="15.75">
       <c r="A25" s="62">
@@ -14719,8 +14699,8 @@
       <c r="U25" s="71"/>
       <c r="V25" s="71"/>
       <c r="W25" s="71"/>
-      <c r="X25" s="108"/>
-      <c r="Y25" s="105"/>
+      <c r="X25" s="107"/>
+      <c r="Y25" s="104"/>
     </row>
     <row r="26" spans="1:27" ht="15.75">
       <c r="A26" s="66">
@@ -14750,8 +14730,8 @@
       <c r="U26" s="72"/>
       <c r="V26" s="72"/>
       <c r="W26" s="72"/>
-      <c r="X26" s="108"/>
-      <c r="Y26" s="105"/>
+      <c r="X26" s="107"/>
+      <c r="Y26" s="104"/>
     </row>
     <row r="27" spans="1:27" ht="15.75">
       <c r="A27" s="62">
@@ -14781,8 +14761,8 @@
       <c r="U27" s="71"/>
       <c r="V27" s="71"/>
       <c r="W27" s="71"/>
-      <c r="X27" s="108"/>
-      <c r="Y27" s="105"/>
+      <c r="X27" s="107"/>
+      <c r="Y27" s="104"/>
     </row>
     <row r="28" spans="1:27" ht="15.75">
       <c r="A28" s="66">
@@ -14812,8 +14792,8 @@
       <c r="U28" s="72"/>
       <c r="V28" s="72"/>
       <c r="W28" s="72"/>
-      <c r="X28" s="108"/>
-      <c r="Y28" s="105"/>
+      <c r="X28" s="107"/>
+      <c r="Y28" s="104"/>
     </row>
     <row r="29" spans="1:27" ht="15.75">
       <c r="A29" s="62">
@@ -14843,8 +14823,8 @@
       <c r="U29" s="71"/>
       <c r="V29" s="71"/>
       <c r="W29" s="71"/>
-      <c r="X29" s="108"/>
-      <c r="Y29" s="105"/>
+      <c r="X29" s="107"/>
+      <c r="Y29" s="104"/>
     </row>
     <row r="30" spans="1:27" ht="15.75">
       <c r="A30" s="66">
@@ -14874,8 +14854,8 @@
       <c r="U30" s="72"/>
       <c r="V30" s="72"/>
       <c r="W30" s="72"/>
-      <c r="X30" s="108"/>
-      <c r="Y30" s="105"/>
+      <c r="X30" s="107"/>
+      <c r="Y30" s="104"/>
     </row>
     <row r="31" spans="1:27" ht="15.75">
       <c r="A31" s="62">
@@ -14905,8 +14885,8 @@
       <c r="U31" s="71"/>
       <c r="V31" s="71"/>
       <c r="W31" s="71"/>
-      <c r="X31" s="108"/>
-      <c r="Y31" s="105"/>
+      <c r="X31" s="107"/>
+      <c r="Y31" s="104"/>
     </row>
     <row r="32" spans="1:27" ht="15.75">
       <c r="A32" s="66">
@@ -14936,8 +14916,8 @@
       <c r="U32" s="72"/>
       <c r="V32" s="72"/>
       <c r="W32" s="72"/>
-      <c r="X32" s="108"/>
-      <c r="Y32" s="105"/>
+      <c r="X32" s="107"/>
+      <c r="Y32" s="104"/>
     </row>
     <row r="33" spans="1:25" ht="15.75">
       <c r="A33" s="62">
@@ -14967,8 +14947,8 @@
       <c r="U33" s="71"/>
       <c r="V33" s="71"/>
       <c r="W33" s="71"/>
-      <c r="X33" s="108"/>
-      <c r="Y33" s="105"/>
+      <c r="X33" s="107"/>
+      <c r="Y33" s="104"/>
     </row>
     <row r="34" spans="1:25" ht="15.75">
       <c r="A34" s="66">
@@ -14998,8 +14978,8 @@
       <c r="U34" s="72"/>
       <c r="V34" s="72"/>
       <c r="W34" s="72"/>
-      <c r="X34" s="108"/>
-      <c r="Y34" s="105"/>
+      <c r="X34" s="107"/>
+      <c r="Y34" s="104"/>
     </row>
     <row r="35" spans="1:25" ht="15.75">
       <c r="A35" s="62">
@@ -15029,8 +15009,8 @@
       <c r="U35" s="71"/>
       <c r="V35" s="71"/>
       <c r="W35" s="71"/>
-      <c r="X35" s="108"/>
-      <c r="Y35" s="105"/>
+      <c r="X35" s="107"/>
+      <c r="Y35" s="104"/>
     </row>
     <row r="36" spans="1:25" ht="15.75">
       <c r="A36" s="66">
@@ -15060,14 +15040,14 @@
       <c r="U36" s="72"/>
       <c r="V36" s="72"/>
       <c r="W36" s="72"/>
-      <c r="X36" s="109"/>
-      <c r="Y36" s="106"/>
+      <c r="X36" s="108"/>
+      <c r="Y36" s="105"/>
     </row>
     <row r="37" spans="1:25">
-      <c r="A37" s="100" t="s">
+      <c r="A37" s="99" t="s">
         <v>36</v>
       </c>
-      <c r="B37" s="100"/>
+      <c r="B37" s="99"/>
       <c r="C37" s="79">
         <f>SUM(C21:C36)</f>
         <v>0</v>
@@ -15162,10 +15142,10 @@
       </c>
     </row>
     <row r="38" spans="1:25" ht="31.5" customHeight="1">
-      <c r="A38" s="103" t="s">
+      <c r="A38" s="102" t="s">
         <v>37</v>
       </c>
-      <c r="B38" s="103"/>
+      <c r="B38" s="102"/>
       <c r="C38" s="78">
         <f>SUM(C20,C37)</f>
         <v>10242.99</v>
@@ -15232,23 +15212,23 @@
       </c>
       <c r="S38" s="78">
         <f>SUM(S20,S37)</f>
-        <v>4572.63</v>
+        <v>5272.63</v>
       </c>
       <c r="T38" s="78">
         <f t="shared" si="3"/>
-        <v>12288</v>
+        <v>2288</v>
       </c>
       <c r="U38" s="78">
         <f t="shared" si="3"/>
-        <v>8000</v>
+        <v>0</v>
       </c>
       <c r="V38" s="78">
         <f t="shared" si="3"/>
-        <v>8450</v>
+        <v>950</v>
       </c>
       <c r="W38" s="86">
         <f t="shared" si="3"/>
-        <v>86994.829999999987</v>
+        <v>62194.829999999987</v>
       </c>
       <c r="X38" s="86">
         <f>SUM(X20,X37)</f>
@@ -15256,7 +15236,7 @@
       </c>
       <c r="Y38" s="87">
         <f>SUM(Y20,Y37)</f>
-        <v>11664.994999999995</v>
+        <v>36464.994999999995</v>
       </c>
     </row>
     <row r="42" spans="1:25">

--- a/Другое/2026/Доходы-Расходы_copy.xlsx
+++ b/Другое/2026/Доходы-Расходы_copy.xlsx
@@ -1,8 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="6" rupBuild="4507"/>
+  <workbookPr filterPrivacy="1"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="6"/>
   </bookViews>
@@ -14,10 +14,11 @@
     <sheet name="Май 2026" sheetId="6" r:id="rId5"/>
     <sheet name=" Июнь 2026" sheetId="7" r:id="rId6"/>
     <sheet name="Июль 2026" sheetId="8" r:id="rId7"/>
+    <sheet name="Август 2026" sheetId="9" r:id="rId8"/>
   </sheets>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+  <calcPr calcId="125725"/>
+  <extLst xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
@@ -30,7 +31,7 @@
     <author>Автор</author>
   </authors>
   <commentList>
-    <comment ref="S3" authorId="0" shapeId="0">
+    <comment ref="S3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -57,7 +58,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P11" authorId="0" shapeId="0">
+    <comment ref="P11" authorId="0">
       <text>
         <r>
           <rPr>
@@ -84,7 +85,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R16" authorId="0" shapeId="0">
+    <comment ref="R16" authorId="0">
       <text>
         <r>
           <rPr>
@@ -111,7 +112,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P20" authorId="0" shapeId="0">
+    <comment ref="P20" authorId="0">
       <text>
         <r>
           <rPr>
@@ -137,7 +138,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P24" authorId="0" shapeId="0">
+    <comment ref="P24" authorId="0">
       <text>
         <r>
           <rPr>
@@ -163,7 +164,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H25" authorId="0" shapeId="0">
+    <comment ref="H25" authorId="0">
       <text>
         <r>
           <rPr>
@@ -190,7 +191,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J25" authorId="0" shapeId="0">
+    <comment ref="J25" authorId="0">
       <text>
         <r>
           <rPr>
@@ -216,7 +217,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J26" authorId="0" shapeId="0">
+    <comment ref="J26" authorId="0">
       <text>
         <r>
           <rPr>
@@ -242,7 +243,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L26" authorId="0" shapeId="0">
+    <comment ref="L26" authorId="0">
       <text>
         <r>
           <rPr>
@@ -268,7 +269,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P26" authorId="0" shapeId="0">
+    <comment ref="P26" authorId="0">
       <text>
         <r>
           <rPr>
@@ -294,7 +295,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J27" authorId="0" shapeId="0">
+    <comment ref="J27" authorId="0">
       <text>
         <r>
           <rPr>
@@ -330,7 +331,7 @@
     <author>Автор</author>
   </authors>
   <commentList>
-    <comment ref="R3" authorId="0" shapeId="0">
+    <comment ref="R3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -356,7 +357,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F4" authorId="0" shapeId="0">
+    <comment ref="F4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -382,7 +383,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R4" authorId="0" shapeId="0">
+    <comment ref="R4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -409,7 +410,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S4" authorId="0" shapeId="0">
+    <comment ref="S4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -435,7 +436,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T4" authorId="0" shapeId="0">
+    <comment ref="T4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -461,7 +462,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G5" authorId="0" shapeId="0">
+    <comment ref="G5" authorId="0">
       <text>
         <r>
           <rPr>
@@ -487,7 +488,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P5" authorId="0" shapeId="0">
+    <comment ref="P5" authorId="0">
       <text>
         <r>
           <rPr>
@@ -513,7 +514,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P6" authorId="0" shapeId="0">
+    <comment ref="P6" authorId="0">
       <text>
         <r>
           <rPr>
@@ -540,7 +541,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S10" authorId="0" shapeId="0">
+    <comment ref="S10" authorId="0">
       <text>
         <r>
           <rPr>
@@ -566,7 +567,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A11" authorId="0" shapeId="0">
+    <comment ref="A11" authorId="0">
       <text>
         <r>
           <rPr>
@@ -592,7 +593,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R18" authorId="0" shapeId="0">
+    <comment ref="R18" authorId="0">
       <text>
         <r>
           <rPr>
@@ -619,7 +620,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S18" authorId="0" shapeId="0">
+    <comment ref="S18" authorId="0">
       <text>
         <r>
           <rPr>
@@ -645,7 +646,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R19" authorId="0" shapeId="0">
+    <comment ref="R19" authorId="0">
       <text>
         <r>
           <rPr>
@@ -672,7 +673,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S19" authorId="0" shapeId="0">
+    <comment ref="S19" authorId="0">
       <text>
         <r>
           <rPr>
@@ -698,7 +699,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S20" authorId="0" shapeId="0">
+    <comment ref="S20" authorId="0">
       <text>
         <r>
           <rPr>
@@ -724,7 +725,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T20" authorId="0" shapeId="0">
+    <comment ref="T20" authorId="0">
       <text>
         <r>
           <rPr>
@@ -750,7 +751,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S22" authorId="0" shapeId="0">
+    <comment ref="S22" authorId="0">
       <text>
         <r>
           <rPr>
@@ -776,7 +777,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S26" authorId="0" shapeId="0">
+    <comment ref="S26" authorId="0">
       <text>
         <r>
           <rPr>
@@ -812,7 +813,7 @@
     <author>Автор</author>
   </authors>
   <commentList>
-    <comment ref="Q3" authorId="0" shapeId="0">
+    <comment ref="Q3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -828,7 +829,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S3" authorId="0" shapeId="0">
+    <comment ref="S3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -855,7 +856,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T3" authorId="0" shapeId="0">
+    <comment ref="T3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -882,7 +883,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="U3" authorId="0" shapeId="0">
+    <comment ref="U3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -908,7 +909,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H4" authorId="0" shapeId="0">
+    <comment ref="H4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -934,7 +935,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K4" authorId="0" shapeId="0">
+    <comment ref="K4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -960,7 +961,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N4" authorId="0" shapeId="0">
+    <comment ref="N4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -986,7 +987,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q4" authorId="0" shapeId="0">
+    <comment ref="Q4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1013,7 +1014,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S4" authorId="0" shapeId="0">
+    <comment ref="S4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1040,7 +1041,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="U4" authorId="0" shapeId="0">
+    <comment ref="U4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1067,7 +1068,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V4" authorId="0" shapeId="0">
+    <comment ref="V4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1093,7 +1094,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I5" authorId="0" shapeId="0">
+    <comment ref="I5" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1120,7 +1121,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S5" authorId="0" shapeId="0">
+    <comment ref="S5" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1146,7 +1147,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K6" authorId="0" shapeId="0">
+    <comment ref="K6" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1173,7 +1174,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S6" authorId="0" shapeId="0">
+    <comment ref="S6" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1200,7 +1201,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H8" authorId="0" shapeId="0">
+    <comment ref="H8" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1216,7 +1217,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E10" authorId="0" shapeId="0">
+    <comment ref="E10" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1243,7 +1244,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X11" authorId="0" shapeId="0">
+    <comment ref="X11" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1270,7 +1271,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X12" authorId="0" shapeId="0">
+    <comment ref="X12" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1296,7 +1297,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H14" authorId="0" shapeId="0">
+    <comment ref="H14" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1323,7 +1324,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H15" authorId="0" shapeId="0">
+    <comment ref="H15" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1339,7 +1340,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T15" authorId="0" shapeId="0">
+    <comment ref="T15" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1354,7 +1355,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E17" authorId="0" shapeId="0">
+    <comment ref="E17" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1380,7 +1381,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q17" authorId="0" shapeId="0">
+    <comment ref="Q17" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1406,7 +1407,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S19" authorId="0" shapeId="0">
+    <comment ref="S19" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1432,7 +1433,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S21" authorId="0" shapeId="0">
+    <comment ref="S21" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1459,7 +1460,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T21" authorId="0" shapeId="0">
+    <comment ref="T21" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1485,7 +1486,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F22" authorId="0" shapeId="0">
+    <comment ref="F22" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1511,7 +1512,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H22" authorId="0" shapeId="0">
+    <comment ref="H22" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1537,7 +1538,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T22" authorId="0" shapeId="0">
+    <comment ref="T22" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1563,7 +1564,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E24" authorId="0" shapeId="0">
+    <comment ref="E24" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1590,7 +1591,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F25" authorId="0" shapeId="0">
+    <comment ref="F25" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1617,7 +1618,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E27" authorId="0" shapeId="0">
+    <comment ref="E27" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1644,7 +1645,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H29" authorId="0" shapeId="0">
+    <comment ref="H29" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1670,7 +1671,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S29" authorId="0" shapeId="0">
+    <comment ref="S29" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1696,7 +1697,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F30" authorId="0" shapeId="0">
+    <comment ref="F30" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1722,7 +1723,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X30" authorId="0" shapeId="0">
+    <comment ref="X30" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1748,7 +1749,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H31" authorId="0" shapeId="0">
+    <comment ref="H31" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1774,7 +1775,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S33" authorId="0" shapeId="0">
+    <comment ref="S33" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1800,7 +1801,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X35" authorId="0" shapeId="0">
+    <comment ref="X35" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1836,7 +1837,7 @@
     <author>Автор</author>
   </authors>
   <commentList>
-    <comment ref="S3" authorId="0" shapeId="0">
+    <comment ref="S3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1862,7 +1863,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T3" authorId="0" shapeId="0">
+    <comment ref="T3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1889,7 +1890,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H4" authorId="0" shapeId="0">
+    <comment ref="H4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1915,7 +1916,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F5" authorId="0" shapeId="0">
+    <comment ref="F5" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1941,7 +1942,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S5" authorId="0" shapeId="0">
+    <comment ref="S5" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1967,7 +1968,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H6" authorId="0" shapeId="0">
+    <comment ref="H6" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1993,7 +1994,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K7" authorId="0" shapeId="0">
+    <comment ref="K7" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2019,7 +2020,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X7" authorId="0" shapeId="0">
+    <comment ref="X7" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2045,7 +2046,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K8" authorId="0" shapeId="0">
+    <comment ref="K8" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2071,7 +2072,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K9" authorId="0" shapeId="0">
+    <comment ref="K9" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2097,7 +2098,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F10" authorId="0" shapeId="0">
+    <comment ref="F10" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2124,7 +2125,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H11" authorId="0" shapeId="0">
+    <comment ref="H11" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2150,7 +2151,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H13" authorId="0" shapeId="0">
+    <comment ref="H13" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2177,7 +2178,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q19" authorId="0" shapeId="0">
+    <comment ref="Q19" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2203,7 +2204,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S19" authorId="0" shapeId="0">
+    <comment ref="S19" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2229,7 +2230,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T20" authorId="0" shapeId="0">
+    <comment ref="T20" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2256,7 +2257,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H21" authorId="0" shapeId="0">
+    <comment ref="H21" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2282,7 +2283,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T21" authorId="0" shapeId="0">
+    <comment ref="T21" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2309,7 +2310,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X21" authorId="0" shapeId="0">
+    <comment ref="X21" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2335,7 +2336,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J24" authorId="0" shapeId="0">
+    <comment ref="J24" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2361,7 +2362,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S24" authorId="0" shapeId="0">
+    <comment ref="S24" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2387,7 +2388,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V25" authorId="0" shapeId="0">
+    <comment ref="V25" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2413,7 +2414,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H27" authorId="0" shapeId="0">
+    <comment ref="H27" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2439,7 +2440,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S27" authorId="0" shapeId="0">
+    <comment ref="S27" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2465,7 +2466,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H28" authorId="0" shapeId="0">
+    <comment ref="H28" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2491,7 +2492,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V28" authorId="0" shapeId="0">
+    <comment ref="V28" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2518,7 +2519,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X28" authorId="0" shapeId="0">
+    <comment ref="X28" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2544,7 +2545,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E29" authorId="0" shapeId="0">
+    <comment ref="E29" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2570,7 +2571,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X29" authorId="0" shapeId="0">
+    <comment ref="X29" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2596,7 +2597,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S31" authorId="0" shapeId="0">
+    <comment ref="S31" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2622,7 +2623,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S33" authorId="0" shapeId="0">
+    <comment ref="S33" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2648,7 +2649,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X34" authorId="0" shapeId="0">
+    <comment ref="X34" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2685,7 +2686,7 @@
     <author>Автор</author>
   </authors>
   <commentList>
-    <comment ref="F3" authorId="0" shapeId="0">
+    <comment ref="F3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2711,7 +2712,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H3" authorId="0" shapeId="0">
+    <comment ref="H3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2737,7 +2738,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S3" authorId="0" shapeId="0">
+    <comment ref="S3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2763,7 +2764,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T3" authorId="0" shapeId="0">
+    <comment ref="T3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2789,7 +2790,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V3" authorId="0" shapeId="0">
+    <comment ref="V3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2815,7 +2816,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H4" authorId="0" shapeId="0">
+    <comment ref="H4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2841,7 +2842,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N4" authorId="0" shapeId="0">
+    <comment ref="N4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2867,7 +2868,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q4" authorId="0" shapeId="0">
+    <comment ref="Q4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2893,7 +2894,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S4" authorId="0" shapeId="0">
+    <comment ref="S4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2919,7 +2920,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H5" authorId="0" shapeId="0">
+    <comment ref="H5" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2945,7 +2946,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T5" authorId="0" shapeId="0">
+    <comment ref="T5" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2971,7 +2972,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F6" authorId="0" shapeId="0">
+    <comment ref="F6" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2997,7 +2998,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H6" authorId="0" shapeId="0">
+    <comment ref="H6" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3023,7 +3024,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T6" authorId="0" shapeId="0">
+    <comment ref="T6" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3049,7 +3050,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q7" authorId="0" shapeId="0">
+    <comment ref="Q7" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3075,7 +3076,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F8" authorId="0" shapeId="0">
+    <comment ref="F8" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3101,7 +3102,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q8" authorId="0" shapeId="0">
+    <comment ref="Q8" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3127,7 +3128,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S8" authorId="0" shapeId="0">
+    <comment ref="S8" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3153,7 +3154,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q9" authorId="0" shapeId="0">
+    <comment ref="Q9" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3179,7 +3180,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X9" authorId="0" shapeId="0">
+    <comment ref="X9" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3205,7 +3206,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E10" authorId="0" shapeId="0">
+    <comment ref="E10" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3231,7 +3232,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E11" authorId="0" shapeId="0">
+    <comment ref="E11" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3257,7 +3258,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I11" authorId="0" shapeId="0">
+    <comment ref="I11" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3283,7 +3284,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q12" authorId="0" shapeId="0">
+    <comment ref="Q12" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3310,7 +3311,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q13" authorId="0" shapeId="0">
+    <comment ref="Q13" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3336,7 +3337,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S13" authorId="0" shapeId="0">
+    <comment ref="S13" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3362,7 +3363,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X14" authorId="0" shapeId="0">
+    <comment ref="X14" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3388,7 +3389,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X16" authorId="0" shapeId="0">
+    <comment ref="X16" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3414,7 +3415,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H17" authorId="0" shapeId="0">
+    <comment ref="H17" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3441,7 +3442,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S17" authorId="0" shapeId="0">
+    <comment ref="S17" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3467,7 +3468,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T17" authorId="0" shapeId="0">
+    <comment ref="T17" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3493,7 +3494,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H19" authorId="0" shapeId="0">
+    <comment ref="H19" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3519,7 +3520,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N19" authorId="0" shapeId="0">
+    <comment ref="N19" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3555,7 +3556,7 @@
     <author>Автор</author>
   </authors>
   <commentList>
-    <comment ref="Q3" authorId="0" shapeId="0">
+    <comment ref="Q3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3582,7 +3583,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S3" authorId="0" shapeId="0">
+    <comment ref="S3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3608,7 +3609,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H4" authorId="0" shapeId="0">
+    <comment ref="H4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3634,7 +3635,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S5" authorId="0" shapeId="0">
+    <comment ref="S5" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3661,7 +3662,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V6" authorId="0" shapeId="0">
+    <comment ref="V6" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3687,7 +3688,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F7" authorId="0" shapeId="0">
+    <comment ref="F7" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3713,7 +3714,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q8" authorId="0" shapeId="0">
+    <comment ref="Q8" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3740,7 +3741,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S8" authorId="0" shapeId="0">
+    <comment ref="S8" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3767,7 +3768,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S9" authorId="0" shapeId="0">
+    <comment ref="S9" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3793,7 +3794,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E10" authorId="0" shapeId="0">
+    <comment ref="E10" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3819,7 +3820,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S10" authorId="0" shapeId="0">
+    <comment ref="S10" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3845,7 +3846,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q12" authorId="0" shapeId="0">
+    <comment ref="Q12" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3871,7 +3872,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q13" authorId="0" shapeId="0">
+    <comment ref="Q13" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3898,7 +3899,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S13" authorId="0" shapeId="0">
+    <comment ref="S13" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3924,7 +3925,34 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q15" authorId="0" shapeId="0">
+    <comment ref="Y14" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Премия
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="Q15" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3950,7 +3978,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S15" authorId="0" shapeId="0">
+    <comment ref="S15" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3976,7 +4004,33 @@
         </r>
       </text>
     </comment>
-    <comment ref="F16" authorId="0" shapeId="0">
+    <comment ref="E16" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Хочука</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F16" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4002,7 +4056,34 @@
         </r>
       </text>
     </comment>
-    <comment ref="T16" authorId="0" shapeId="0">
+    <comment ref="M16" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Отказ на ламоде
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="T16" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4017,7 +4098,33 @@
         </r>
       </text>
     </comment>
-    <comment ref="S17" authorId="0" shapeId="0">
+    <comment ref="M17" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Рубашка Henderson</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="S17" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4041,7 +4148,85 @@
         </r>
       </text>
     </comment>
-    <comment ref="S18" authorId="0" shapeId="0">
+    <comment ref="T17" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Средства для волос</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="U17" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Простава на работе в связи с уходом из отдела</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="Y17" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Мама скинула на МСК</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="S18" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4065,7 +4250,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="U18" authorId="0" shapeId="0">
+    <comment ref="U18" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4089,7 +4274,33 @@
         </r>
       </text>
     </comment>
-    <comment ref="V19" authorId="0" shapeId="0">
+    <comment ref="E19" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Хочука</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="V19" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4110,6 +4321,1380 @@
           </rPr>
           <t xml:space="preserve">
 Поездка в МСК к Кулику на ДР</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="Y19" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Батя скинул, когда были в МСК</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F21" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+БАБЛ ТИ и ПОКЕ</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="T21" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+КНИГИ
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F23" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+ПОКЕ</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="S23" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Долями за орнамент</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F24" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+ПОКЕ и БАБЛ ТИ</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H25" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Вкусно и Точка</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="V25" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Пейнтбол</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E27" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Хочука</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="V27" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Книги по строительству</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="Y27" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Подарок от мамы на ДР</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="S28" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Яндекс Ппюс</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="T28" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Простава на работе</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="Q29" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Завтрак для Ани</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="Q30" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+На такси</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments7.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Автор</author>
+  </authors>
+  <commentList>
+    <comment ref="Q3" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Компенсация за ВПЧ
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="S3" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Яндекс Плюс</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H4" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Завтрак в 1/2</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="S5" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+ВК музыка
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="V6" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Покупка ЧТИВО</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F7" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Промясо</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="Q8" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Поке + бабл ти
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="S8" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Долями за орнамент
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="S9" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+T2</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E10" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Макдоналдс</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="S10" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+ВПН</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="Q12" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Ане на таблетки</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="Q13" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Извинительный букет
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="S13" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Долями - за журнальчик орнамент</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="Q15" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+За такси + вино</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="S15" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+t2</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F16" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Обед</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="T16" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Парикмахерская</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="S17" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Интернет</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="Y17" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Мама скинула на МСК</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="S18" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Яндекс Плюс</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="U18" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Подарок Кулику</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E19" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Хочука</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="V19" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Поездка в МСК к Кулику на ДР</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="Y19" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Батя скинул, когда были в МСК</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F21" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+БАБЛ ТИ и ПОКЕ</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="T21" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+КНИГИ
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F23" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+ПОКЕ</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="S23" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Долями за орнамент</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F24" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+ПОКЕ и БАБЛ ТИ</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H25" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Вкусно и Точка</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="V25" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Пейнтбол</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E27" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Хочука</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="V27" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Книги по строительству</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="Y27" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Подарок от мамы на ДР</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="S28" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Яндекс Ппюс</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="T28" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Простава на работе</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="Q29" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Завтрак для Ани</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="Q30" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+На такси</t>
         </r>
       </text>
     </comment>
@@ -4118,7 +5703,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="66">
   <si>
     <t>Число</t>
   </si>
@@ -4300,15 +5885,33 @@
   <si>
     <t>Доходы - Расходы Июль 2026</t>
   </si>
+  <si>
+    <t>Арестованные средства</t>
+  </si>
+  <si>
+    <t>Сводные итоги за июль 2026 г.</t>
+  </si>
+  <si>
+    <t>Заработал</t>
+  </si>
+  <si>
+    <t>Взял в долг</t>
+  </si>
+  <si>
+    <t>Потратил всего</t>
+  </si>
+  <si>
+    <t>Потратил на еду</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;₽&quot;"/>
   </numFmts>
-  <fonts count="32">
+  <fonts count="38">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4547,8 +6150,51 @@
       <name val="Tahoma"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Franklin Gothic Demi"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Franklin Gothic Demi"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Franklin Gothic Demi"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Bahnschrift"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Bahnschrift"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
   </fonts>
-  <fills count="21">
+  <fills count="32">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -4669,8 +6315,74 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFA8A8A"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC00000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC09200"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF273C18"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDD7D7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDF0C8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="15">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -4866,11 +6578,81 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1" tint="0.34998626667073579"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="1" tint="0.34998626667073579"/>
+      </top>
+      <bottom style="thin">
+        <color theme="1" tint="0.34998626667073579"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="1" tint="0.34998626667073579"/>
+      </right>
+      <top style="thin">
+        <color theme="1" tint="0.34998626667073579"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="1" tint="0.34998626667073579"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="1" tint="0.34998626667073579"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color theme="1" tint="0.34998626667073579"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF134873"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF134873"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="110">
+  <cellXfs count="141">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -5066,7 +6848,6 @@
     <xf numFmtId="164" fontId="27" fillId="19" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="27" fillId="19" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="21" fillId="19" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -5077,6 +6858,9 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="20" fillId="19" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="20" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -5124,32 +6908,113 @@
     <xf numFmtId="0" fontId="29" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="22" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="7" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="17" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="23" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="23" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="27" fillId="19" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="23" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="23" fillId="23" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="27" fillId="19" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="23" fillId="21" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="6" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="29" fillId="6" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="14" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="28" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="23" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="29" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="34" fillId="24" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="34" fillId="23" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="34" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="29" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="29" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="23" fillId="22" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="34" fillId="11" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="34" fillId="11" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="30" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="37" fillId="17" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="31" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="23" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="23" fillId="20" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
+    <xf numFmtId="164" fontId="36" fillId="31" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="10">
+  <dxfs count="12">
+    <dxf>
+      <font>
+        <color rgb="FF57B418"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC00000"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF57B418"/>
@@ -5204,16 +7069,16 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFFA8A8A"/>
+      <color rgb="FFFDD7D7"/>
+      <color rgb="FFDDF0C8"/>
+      <color rgb="FF273C18"/>
+      <color rgb="FFC09200"/>
+      <color rgb="FF2E471D"/>
+      <color rgb="FFEC1606"/>
       <color rgb="FF062D4E"/>
       <color rgb="FFD5DA08"/>
       <color rgb="FF57B418"/>
-      <color rgb="FFFF8585"/>
-      <color rgb="FF6C0000"/>
-      <color rgb="FFEC1606"/>
-      <color rgb="FFF4B79E"/>
-      <color rgb="FF094679"/>
-      <color rgb="FF7BB7E9"/>
-      <color rgb="FF3179E3"/>
     </mruColors>
   </colors>
   <extLst>
@@ -5482,14 +7347,14 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="C3:H17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -5523,7 +7388,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="3:8" ht="15.75">
+    <row r="5" spans="3:8" ht="16.5">
       <c r="C5" s="52" t="s">
         <v>43</v>
       </c>
@@ -5543,7 +7408,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="6" spans="3:8" ht="15.75">
+    <row r="6" spans="3:8" ht="16.5">
       <c r="C6" s="52" t="s">
         <v>44</v>
       </c>
@@ -5564,7 +7429,7 @@
         <v>1260.5599999999977</v>
       </c>
     </row>
-    <row r="7" spans="3:8" ht="15.75">
+    <row r="7" spans="3:8" ht="16.5">
       <c r="C7" s="52" t="s">
         <v>45</v>
       </c>
@@ -5585,7 +7450,7 @@
         <v>-11931.300000000003</v>
       </c>
     </row>
-    <row r="8" spans="3:8" ht="15.75">
+    <row r="8" spans="3:8" ht="16.5">
       <c r="C8" s="52" t="s">
         <v>46</v>
       </c>
@@ -5606,7 +7471,7 @@
         <v>59.059999999997672</v>
       </c>
     </row>
-    <row r="9" spans="3:8" ht="15.75">
+    <row r="9" spans="3:8" ht="16.5">
       <c r="C9" s="52" t="s">
         <v>47</v>
       </c>
@@ -5616,7 +7481,7 @@
       <c r="G9" s="51"/>
       <c r="H9" s="51"/>
     </row>
-    <row r="10" spans="3:8" ht="15.75">
+    <row r="10" spans="3:8" ht="16.5">
       <c r="C10" s="52" t="s">
         <v>48</v>
       </c>
@@ -5626,7 +7491,7 @@
       <c r="G10" s="51"/>
       <c r="H10" s="51"/>
     </row>
-    <row r="11" spans="3:8" ht="15.75">
+    <row r="11" spans="3:8" ht="16.5">
       <c r="C11" s="52" t="s">
         <v>49</v>
       </c>
@@ -5636,7 +7501,7 @@
       <c r="G11" s="51"/>
       <c r="H11" s="51"/>
     </row>
-    <row r="12" spans="3:8" ht="15.75">
+    <row r="12" spans="3:8" ht="16.5">
       <c r="C12" s="52" t="s">
         <v>50</v>
       </c>
@@ -5646,7 +7511,7 @@
       <c r="G12" s="51"/>
       <c r="H12" s="51"/>
     </row>
-    <row r="13" spans="3:8" ht="15.75">
+    <row r="13" spans="3:8" ht="16.5">
       <c r="C13" s="52" t="s">
         <v>51</v>
       </c>
@@ -5656,7 +7521,7 @@
       <c r="G13" s="51"/>
       <c r="H13" s="51"/>
     </row>
-    <row r="14" spans="3:8" ht="15.75">
+    <row r="14" spans="3:8" ht="16.5">
       <c r="C14" s="52" t="s">
         <v>52</v>
       </c>
@@ -5666,7 +7531,7 @@
       <c r="G14" s="51"/>
       <c r="H14" s="51"/>
     </row>
-    <row r="15" spans="3:8" ht="15.75">
+    <row r="15" spans="3:8" ht="16.5">
       <c r="C15" s="52" t="s">
         <v>53</v>
       </c>
@@ -5676,7 +7541,7 @@
       <c r="G15" s="51"/>
       <c r="H15" s="51"/>
     </row>
-    <row r="16" spans="3:8" ht="16.5" thickBot="1">
+    <row r="16" spans="3:8" ht="17.25" thickBot="1">
       <c r="C16" s="53" t="s">
         <v>54</v>
       </c>
@@ -5686,7 +7551,7 @@
       <c r="G16" s="54"/>
       <c r="H16" s="54"/>
     </row>
-    <row r="17" spans="3:8" ht="16.5" thickBot="1">
+    <row r="17" spans="3:8" ht="17.25" thickBot="1">
       <c r="C17" s="55" t="s">
         <v>20</v>
       </c>
@@ -5698,18 +7563,18 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="H5:H16">
-    <cfRule type="expression" dxfId="9" priority="3">
+    <cfRule type="expression" dxfId="11" priority="3">
       <formula>H5&lt;0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="4">
+    <cfRule type="expression" dxfId="10" priority="4">
       <formula>H5&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H17">
-    <cfRule type="expression" dxfId="7" priority="1">
+    <cfRule type="expression" dxfId="9" priority="1">
       <formula>H17&lt;0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="2">
+    <cfRule type="expression" dxfId="8" priority="2">
       <formula>H17&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5719,7 +7584,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AT35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -7069,7 +8934,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AT36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -8431,7 +10296,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AU41"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -10229,7 +12094,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AU40"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -11946,10 +13811,10 @@
     <mergeCell ref="A36:B36"/>
   </mergeCells>
   <conditionalFormatting sqref="Y18:Y36">
-    <cfRule type="expression" dxfId="5" priority="1">
+    <cfRule type="expression" dxfId="7" priority="1">
       <formula>Y18&lt;0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="2">
+    <cfRule type="expression" dxfId="6" priority="2">
       <formula>Y18&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11960,7 +13825,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AU40"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -13601,10 +15466,10 @@
     <mergeCell ref="A36:B36"/>
   </mergeCells>
   <conditionalFormatting sqref="Y18:Y36">
-    <cfRule type="expression" dxfId="3" priority="1">
+    <cfRule type="expression" dxfId="5" priority="1">
       <formula>Y18&lt;0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="2">
+    <cfRule type="expression" dxfId="4" priority="2">
       <formula>Y18&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13615,16 +15480,18 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AU42"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AV42"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="25" width="20.7109375" style="2" customWidth="1"/>
-    <col min="26" max="37" width="12.7109375" style="2" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="26" width="20.7109375" style="2" customWidth="1"/>
+    <col min="27" max="32" width="12.7109375" style="2" customWidth="1"/>
+    <col min="33" max="33" width="16.140625" style="2" customWidth="1"/>
+    <col min="34" max="38" width="12.7109375" style="2" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:47" ht="60.75" customHeight="1">
+    <row r="1" spans="1:48" ht="60.75" customHeight="1">
       <c r="A1" s="101" t="s">
         <v>59</v>
       </c>
@@ -13652,36 +15519,37 @@
       <c r="W1" s="101"/>
       <c r="X1" s="101"/>
       <c r="Y1" s="101"/>
-    </row>
-    <row r="2" spans="1:47" ht="45" customHeight="1">
+      <c r="Z1" s="101"/>
+    </row>
+    <row r="2" spans="1:48" ht="45" customHeight="1">
       <c r="A2" s="76" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="76" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="76" t="s">
+      <c r="C2" s="117" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="76" t="s">
+      <c r="D2" s="117" t="s">
         <v>29</v>
       </c>
-      <c r="E2" s="76" t="s">
+      <c r="E2" s="117" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="76" t="s">
+      <c r="F2" s="117" t="s">
         <v>33</v>
       </c>
-      <c r="G2" s="76" t="s">
+      <c r="G2" s="117" t="s">
         <v>34</v>
       </c>
-      <c r="H2" s="76" t="s">
+      <c r="H2" s="117" t="s">
         <v>11</v>
       </c>
-      <c r="I2" s="76" t="s">
+      <c r="I2" s="117" t="s">
         <v>30</v>
       </c>
-      <c r="J2" s="76" t="s">
+      <c r="J2" s="117" t="s">
         <v>12</v>
       </c>
       <c r="K2" s="76" t="s">
@@ -13717,19 +15585,21 @@
       <c r="U2" s="76" t="s">
         <v>25</v>
       </c>
-      <c r="V2" s="76" t="s">
+      <c r="V2" s="118" t="s">
         <v>26</v>
       </c>
-      <c r="W2" s="81" t="s">
+      <c r="W2" s="121" t="s">
         <v>22</v>
       </c>
-      <c r="X2" s="81" t="s">
+      <c r="X2" s="125" t="s">
+        <v>60</v>
+      </c>
+      <c r="Y2" s="126" t="s">
         <v>19</v>
       </c>
-      <c r="Y2" s="81" t="s">
+      <c r="Z2" s="132" t="s">
         <v>21</v>
       </c>
-      <c r="Z2" s="1"/>
       <c r="AA2" s="1"/>
       <c r="AB2" s="1"/>
       <c r="AC2" s="1"/>
@@ -13751,8 +15621,9 @@
       <c r="AS2" s="1"/>
       <c r="AT2" s="1"/>
       <c r="AU2" s="1"/>
-    </row>
-    <row r="3" spans="1:47" ht="15.75">
+      <c r="AV2" s="1"/>
+    </row>
+    <row r="3" spans="1:48" ht="15.75">
       <c r="A3" s="62">
         <v>3</v>
       </c>
@@ -13789,18 +15660,21 @@
       </c>
       <c r="T3" s="71"/>
       <c r="U3" s="71"/>
-      <c r="V3" s="71"/>
-      <c r="W3" s="71">
+      <c r="V3" s="105"/>
+      <c r="W3" s="122">
         <f>SUM(C3:V3)</f>
         <v>14049</v>
       </c>
-      <c r="X3" s="64">
-        <f>(94085+57723.67)/2</f>
-        <v>75904.334999999992</v>
-      </c>
-      <c r="Y3" s="103"/>
-    </row>
-    <row r="4" spans="1:47" ht="15.75">
+      <c r="X3" s="124">
+        <v>72082.179999999993</v>
+      </c>
+      <c r="Y3" s="133">
+        <f>(94085+57723.67)</f>
+        <v>151808.66999999998</v>
+      </c>
+      <c r="Z3" s="123"/>
+    </row>
+    <row r="4" spans="1:48" ht="15.75">
       <c r="A4" s="66">
         <v>4</v>
       </c>
@@ -13841,15 +15715,16 @@
         <v>398</v>
       </c>
       <c r="U4" s="72"/>
-      <c r="V4" s="72"/>
-      <c r="W4" s="72">
+      <c r="V4" s="106"/>
+      <c r="W4" s="122">
         <f>SUM(C4:V4)</f>
         <v>10533.31</v>
       </c>
-      <c r="X4" s="106"/>
-      <c r="Y4" s="104"/>
-    </row>
-    <row r="5" spans="1:47" ht="15.75">
+      <c r="X4" s="124"/>
+      <c r="Y4" s="127"/>
+      <c r="Z4" s="123"/>
+    </row>
+    <row r="5" spans="1:48" ht="15.75">
       <c r="A5" s="62">
         <v>5</v>
       </c>
@@ -13880,15 +15755,16 @@
       </c>
       <c r="T5" s="71"/>
       <c r="U5" s="71"/>
-      <c r="V5" s="71"/>
-      <c r="W5" s="71">
+      <c r="V5" s="105"/>
+      <c r="W5" s="122">
         <f t="shared" ref="W5:W19" si="0">SUM(C5:V5)</f>
         <v>1455</v>
       </c>
-      <c r="X5" s="107"/>
-      <c r="Y5" s="104"/>
-    </row>
-    <row r="6" spans="1:47" ht="15.75">
+      <c r="X5" s="124"/>
+      <c r="Y5" s="127"/>
+      <c r="Z5" s="123"/>
+    </row>
+    <row r="6" spans="1:48" ht="15.75">
       <c r="A6" s="66">
         <v>6</v>
       </c>
@@ -13918,17 +15794,18 @@
       <c r="S6" s="72"/>
       <c r="T6" s="72"/>
       <c r="U6" s="72"/>
-      <c r="V6" s="72">
+      <c r="V6" s="106">
         <v>950</v>
       </c>
-      <c r="W6" s="72">
+      <c r="W6" s="122">
         <f t="shared" si="0"/>
         <v>1803.8400000000001</v>
       </c>
-      <c r="X6" s="107"/>
-      <c r="Y6" s="104"/>
-    </row>
-    <row r="7" spans="1:47" ht="15" customHeight="1">
+      <c r="X6" s="124"/>
+      <c r="Y6" s="127"/>
+      <c r="Z6" s="123"/>
+    </row>
+    <row r="7" spans="1:48" ht="15" customHeight="1">
       <c r="A7" s="62">
         <v>7</v>
       </c>
@@ -13963,15 +15840,16 @@
       <c r="S7" s="71"/>
       <c r="T7" s="71"/>
       <c r="U7" s="71"/>
-      <c r="V7" s="71"/>
-      <c r="W7" s="71">
+      <c r="V7" s="105"/>
+      <c r="W7" s="122">
         <f t="shared" si="0"/>
         <v>3302.61</v>
       </c>
-      <c r="X7" s="107"/>
-      <c r="Y7" s="104"/>
-    </row>
-    <row r="8" spans="1:47" ht="15.75">
+      <c r="X7" s="124"/>
+      <c r="Y7" s="127"/>
+      <c r="Z7" s="123"/>
+    </row>
+    <row r="8" spans="1:48" ht="15.75">
       <c r="A8" s="66">
         <v>8</v>
       </c>
@@ -14004,15 +15882,23 @@
       </c>
       <c r="T8" s="72"/>
       <c r="U8" s="72"/>
-      <c r="V8" s="72"/>
-      <c r="W8" s="72">
+      <c r="V8" s="106"/>
+      <c r="W8" s="122">
         <f t="shared" si="0"/>
         <v>2255</v>
       </c>
-      <c r="X8" s="107"/>
-      <c r="Y8" s="104"/>
-    </row>
-    <row r="9" spans="1:47" ht="15.75">
+      <c r="X8" s="124"/>
+      <c r="Y8" s="127"/>
+      <c r="Z8" s="123"/>
+      <c r="AC8" s="138" t="s">
+        <v>61</v>
+      </c>
+      <c r="AD8" s="138"/>
+      <c r="AE8" s="138"/>
+      <c r="AF8" s="138"/>
+      <c r="AG8" s="138"/>
+    </row>
+    <row r="9" spans="1:48" ht="15.75">
       <c r="A9" s="62">
         <v>9</v>
       </c>
@@ -14042,15 +15928,21 @@
       </c>
       <c r="T9" s="71"/>
       <c r="U9" s="71"/>
-      <c r="V9" s="71"/>
-      <c r="W9" s="71">
+      <c r="V9" s="105"/>
+      <c r="W9" s="122">
         <f t="shared" si="0"/>
         <v>1095</v>
       </c>
-      <c r="X9" s="107"/>
-      <c r="Y9" s="104"/>
-    </row>
-    <row r="10" spans="1:47" ht="15.75">
+      <c r="X9" s="124"/>
+      <c r="Y9" s="127"/>
+      <c r="Z9" s="123"/>
+      <c r="AC9" s="138"/>
+      <c r="AD9" s="138"/>
+      <c r="AE9" s="138"/>
+      <c r="AF9" s="138"/>
+      <c r="AG9" s="138"/>
+    </row>
+    <row r="10" spans="1:48" ht="15.75">
       <c r="A10" s="66">
         <v>10</v>
       </c>
@@ -14085,15 +15977,21 @@
         <v>790</v>
       </c>
       <c r="U10" s="72"/>
-      <c r="V10" s="72"/>
-      <c r="W10" s="72">
+      <c r="V10" s="106"/>
+      <c r="W10" s="122">
         <f t="shared" si="0"/>
         <v>4914</v>
       </c>
-      <c r="X10" s="107"/>
-      <c r="Y10" s="104"/>
-    </row>
-    <row r="11" spans="1:47" ht="15.75">
+      <c r="X10" s="124"/>
+      <c r="Y10" s="127"/>
+      <c r="Z10" s="123"/>
+      <c r="AC10" s="138"/>
+      <c r="AD10" s="138"/>
+      <c r="AE10" s="138"/>
+      <c r="AF10" s="138"/>
+      <c r="AG10" s="138"/>
+    </row>
+    <row r="11" spans="1:48" ht="15.75">
       <c r="A11" s="62">
         <v>11</v>
       </c>
@@ -14124,15 +16022,26 @@
       <c r="S11" s="71"/>
       <c r="T11" s="71"/>
       <c r="U11" s="71"/>
-      <c r="V11" s="71"/>
-      <c r="W11" s="71">
+      <c r="V11" s="105"/>
+      <c r="W11" s="122">
         <f t="shared" si="0"/>
         <v>4632.68</v>
       </c>
-      <c r="X11" s="107"/>
-      <c r="Y11" s="104"/>
-    </row>
-    <row r="12" spans="1:47" ht="15.75">
+      <c r="X11" s="124"/>
+      <c r="Y11" s="127"/>
+      <c r="Z11" s="123"/>
+      <c r="AC11" s="139" t="s">
+        <v>62</v>
+      </c>
+      <c r="AD11" s="139"/>
+      <c r="AE11" s="139"/>
+      <c r="AF11" s="139"/>
+      <c r="AG11" s="140">
+        <f>Y3+Y14+Y21</f>
+        <v>226341.31</v>
+      </c>
+    </row>
+    <row r="12" spans="1:48" ht="15.75">
       <c r="A12" s="66">
         <v>12</v>
       </c>
@@ -14160,15 +16069,26 @@
       <c r="S12" s="72"/>
       <c r="T12" s="72"/>
       <c r="U12" s="72"/>
-      <c r="V12" s="72"/>
-      <c r="W12" s="72">
+      <c r="V12" s="106"/>
+      <c r="W12" s="122">
         <f t="shared" si="0"/>
         <v>4475</v>
       </c>
-      <c r="X12" s="107"/>
-      <c r="Y12" s="104"/>
-    </row>
-    <row r="13" spans="1:47" ht="15.75">
+      <c r="X12" s="124"/>
+      <c r="Y12" s="127"/>
+      <c r="Z12" s="123"/>
+      <c r="AC12" s="139" t="s">
+        <v>55</v>
+      </c>
+      <c r="AD12" s="139"/>
+      <c r="AE12" s="139"/>
+      <c r="AF12" s="139"/>
+      <c r="AG12" s="140">
+        <f>Y27</f>
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:48" ht="15.75">
       <c r="A13" s="62">
         <v>13</v>
       </c>
@@ -14200,15 +16120,1909 @@
       </c>
       <c r="T13" s="71"/>
       <c r="U13" s="71"/>
-      <c r="V13" s="71"/>
-      <c r="W13" s="71">
+      <c r="V13" s="105"/>
+      <c r="W13" s="122">
         <f t="shared" si="0"/>
         <v>4015.63</v>
       </c>
-      <c r="X13" s="107"/>
-      <c r="Y13" s="104"/>
-    </row>
-    <row r="14" spans="1:47" ht="15.75">
+      <c r="X13" s="124"/>
+      <c r="Y13" s="127"/>
+      <c r="Z13" s="123"/>
+      <c r="AC13" s="139" t="s">
+        <v>63</v>
+      </c>
+      <c r="AD13" s="139"/>
+      <c r="AE13" s="139"/>
+      <c r="AF13" s="139"/>
+      <c r="AG13" s="140">
+        <f>Y17+Y19</f>
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:48" ht="15.75">
+      <c r="A14" s="66">
+        <v>14</v>
+      </c>
+      <c r="B14" s="67" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="72">
+        <f>219+2054.78</f>
+        <v>2273.7800000000002</v>
+      </c>
+      <c r="D14" s="72"/>
+      <c r="E14" s="72"/>
+      <c r="F14" s="72"/>
+      <c r="G14" s="72"/>
+      <c r="H14" s="72"/>
+      <c r="I14" s="72"/>
+      <c r="J14" s="72"/>
+      <c r="K14" s="72"/>
+      <c r="L14" s="72"/>
+      <c r="M14" s="72"/>
+      <c r="N14" s="72"/>
+      <c r="O14" s="72"/>
+      <c r="P14" s="72"/>
+      <c r="Q14" s="72"/>
+      <c r="R14" s="72"/>
+      <c r="S14" s="72"/>
+      <c r="T14" s="72"/>
+      <c r="U14" s="72"/>
+      <c r="V14" s="106"/>
+      <c r="W14" s="122">
+        <f t="shared" si="0"/>
+        <v>2273.7800000000002</v>
+      </c>
+      <c r="X14" s="124">
+        <v>14878.51</v>
+      </c>
+      <c r="Y14" s="133">
+        <v>37634</v>
+      </c>
+      <c r="Z14" s="123"/>
+      <c r="AC14" s="139" t="s">
+        <v>64</v>
+      </c>
+      <c r="AD14" s="139"/>
+      <c r="AE14" s="139"/>
+      <c r="AF14" s="139"/>
+      <c r="AG14" s="140">
+        <f>W38</f>
+        <v>167654.87</v>
+      </c>
+    </row>
+    <row r="15" spans="1:48" ht="15.75">
+      <c r="A15" s="62">
+        <v>15</v>
+      </c>
+      <c r="B15" s="63" t="s">
+        <v>2</v>
+      </c>
+      <c r="C15" s="71">
+        <v>364</v>
+      </c>
+      <c r="D15" s="71">
+        <v>584</v>
+      </c>
+      <c r="E15" s="71"/>
+      <c r="F15" s="71"/>
+      <c r="G15" s="71"/>
+      <c r="H15" s="71"/>
+      <c r="I15" s="71"/>
+      <c r="J15" s="71"/>
+      <c r="K15" s="71"/>
+      <c r="L15" s="71"/>
+      <c r="M15" s="71"/>
+      <c r="N15" s="71"/>
+      <c r="O15" s="71">
+        <v>328</v>
+      </c>
+      <c r="P15" s="71"/>
+      <c r="Q15" s="71">
+        <f>1500+1120.98</f>
+        <v>2620.98</v>
+      </c>
+      <c r="R15" s="71"/>
+      <c r="S15" s="71">
+        <v>200</v>
+      </c>
+      <c r="T15" s="71"/>
+      <c r="U15" s="71"/>
+      <c r="V15" s="105"/>
+      <c r="W15" s="122">
+        <f t="shared" si="0"/>
+        <v>4096.9799999999996</v>
+      </c>
+      <c r="X15" s="124"/>
+      <c r="Y15" s="127"/>
+      <c r="Z15" s="123"/>
+      <c r="AC15" s="139" t="s">
+        <v>65</v>
+      </c>
+      <c r="AD15" s="139"/>
+      <c r="AE15" s="139"/>
+      <c r="AF15" s="139"/>
+      <c r="AG15" s="140">
+        <f>SUM(C38:H38)</f>
+        <v>47166.55</v>
+      </c>
+    </row>
+    <row r="16" spans="1:48" ht="15.75">
+      <c r="A16" s="66">
+        <v>16</v>
+      </c>
+      <c r="B16" s="67" t="s">
+        <v>3</v>
+      </c>
+      <c r="C16" s="72"/>
+      <c r="D16" s="72"/>
+      <c r="E16" s="72">
+        <v>2850</v>
+      </c>
+      <c r="F16" s="72">
+        <v>1080</v>
+      </c>
+      <c r="G16" s="72"/>
+      <c r="H16" s="72"/>
+      <c r="I16" s="72"/>
+      <c r="J16" s="72"/>
+      <c r="K16" s="72"/>
+      <c r="L16" s="72"/>
+      <c r="M16" s="72">
+        <v>598</v>
+      </c>
+      <c r="N16" s="72"/>
+      <c r="O16" s="72">
+        <v>413</v>
+      </c>
+      <c r="P16" s="72"/>
+      <c r="Q16" s="72"/>
+      <c r="R16" s="72"/>
+      <c r="S16" s="72"/>
+      <c r="T16" s="72">
+        <v>1200</v>
+      </c>
+      <c r="U16" s="87"/>
+      <c r="V16" s="106"/>
+      <c r="W16" s="122">
+        <f t="shared" si="0"/>
+        <v>6141</v>
+      </c>
+      <c r="X16" s="124"/>
+      <c r="Y16" s="127"/>
+      <c r="Z16" s="123"/>
+    </row>
+    <row r="17" spans="1:28" ht="15.75">
+      <c r="A17" s="62">
+        <v>17</v>
+      </c>
+      <c r="B17" s="63" t="s">
+        <v>4</v>
+      </c>
+      <c r="C17" s="71">
+        <f>700</f>
+        <v>700</v>
+      </c>
+      <c r="D17" s="71"/>
+      <c r="E17" s="71"/>
+      <c r="F17" s="71"/>
+      <c r="G17" s="71"/>
+      <c r="H17" s="71"/>
+      <c r="I17" s="71"/>
+      <c r="J17" s="71"/>
+      <c r="K17" s="71"/>
+      <c r="L17" s="71"/>
+      <c r="M17" s="71">
+        <v>7899</v>
+      </c>
+      <c r="N17" s="71"/>
+      <c r="O17" s="71">
+        <f>220</f>
+        <v>220</v>
+      </c>
+      <c r="P17" s="71"/>
+      <c r="Q17" s="71"/>
+      <c r="R17" s="71"/>
+      <c r="S17" s="71">
+        <v>700</v>
+      </c>
+      <c r="T17" s="71">
+        <v>800</v>
+      </c>
+      <c r="U17" s="71">
+        <f>1825+2217+2419</f>
+        <v>6461</v>
+      </c>
+      <c r="V17" s="105"/>
+      <c r="W17" s="122">
+        <f t="shared" si="0"/>
+        <v>16780</v>
+      </c>
+      <c r="X17" s="124"/>
+      <c r="Y17" s="134">
+        <v>15000</v>
+      </c>
+      <c r="Z17" s="123"/>
+    </row>
+    <row r="18" spans="1:28" ht="15.75">
+      <c r="A18" s="66">
+        <v>18</v>
+      </c>
+      <c r="B18" s="67" t="s">
+        <v>5</v>
+      </c>
+      <c r="C18" s="72"/>
+      <c r="D18" s="72">
+        <v>2018.8</v>
+      </c>
+      <c r="E18" s="72"/>
+      <c r="F18" s="72"/>
+      <c r="G18" s="72"/>
+      <c r="H18" s="72"/>
+      <c r="I18" s="72"/>
+      <c r="J18" s="72"/>
+      <c r="K18" s="72"/>
+      <c r="L18" s="72"/>
+      <c r="M18" s="72"/>
+      <c r="N18" s="72"/>
+      <c r="O18" s="72"/>
+      <c r="P18" s="72"/>
+      <c r="Q18" s="72"/>
+      <c r="R18" s="72"/>
+      <c r="S18" s="72">
+        <v>499</v>
+      </c>
+      <c r="T18" s="87"/>
+      <c r="U18" s="72">
+        <v>8000</v>
+      </c>
+      <c r="V18" s="106"/>
+      <c r="W18" s="122">
+        <f t="shared" si="0"/>
+        <v>10517.8</v>
+      </c>
+      <c r="X18" s="124"/>
+      <c r="Y18" s="127"/>
+      <c r="Z18" s="123"/>
+    </row>
+    <row r="19" spans="1:28" ht="15.75">
+      <c r="A19" s="62">
+        <v>19</v>
+      </c>
+      <c r="B19" s="63" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" s="71"/>
+      <c r="D19" s="71">
+        <v>2376.09</v>
+      </c>
+      <c r="E19" s="71">
+        <v>3600</v>
+      </c>
+      <c r="F19" s="71"/>
+      <c r="G19" s="71"/>
+      <c r="H19" s="71"/>
+      <c r="I19" s="71"/>
+      <c r="J19" s="71"/>
+      <c r="K19" s="71"/>
+      <c r="L19" s="71"/>
+      <c r="M19" s="71"/>
+      <c r="N19" s="71"/>
+      <c r="O19" s="71"/>
+      <c r="P19" s="71"/>
+      <c r="Q19" s="71"/>
+      <c r="R19" s="71"/>
+      <c r="S19" s="71"/>
+      <c r="T19" s="71"/>
+      <c r="U19" s="71"/>
+      <c r="V19" s="105">
+        <f>83+760+400+6869+83+83+1800+850+1033.84+1423+1349+694+83+6000+1800+305</f>
+        <v>23615.84</v>
+      </c>
+      <c r="W19" s="122">
+        <f t="shared" si="0"/>
+        <v>29591.93</v>
+      </c>
+      <c r="X19" s="124"/>
+      <c r="Y19" s="134">
+        <v>10000</v>
+      </c>
+      <c r="Z19" s="123"/>
+    </row>
+    <row r="20" spans="1:28" ht="14.25" customHeight="1">
+      <c r="A20" s="99" t="s">
+        <v>35</v>
+      </c>
+      <c r="B20" s="99"/>
+      <c r="C20" s="79">
+        <f t="shared" ref="C20:Y20" si="1">SUM(C3:C17)</f>
+        <v>10942.99</v>
+      </c>
+      <c r="D20" s="79">
+        <f t="shared" si="1"/>
+        <v>5525.25</v>
+      </c>
+      <c r="E20" s="79">
+        <f t="shared" si="1"/>
+        <v>5350</v>
+      </c>
+      <c r="F20" s="79">
+        <f t="shared" si="1"/>
+        <v>2040</v>
+      </c>
+      <c r="G20" s="79">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H20" s="79">
+        <f t="shared" si="1"/>
+        <v>3760</v>
+      </c>
+      <c r="I20" s="79">
+        <f t="shared" si="1"/>
+        <v>2320.98</v>
+      </c>
+      <c r="J20" s="79">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K20" s="79">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="L20" s="79">
+        <f t="shared" si="1"/>
+        <v>3150</v>
+      </c>
+      <c r="M20" s="79">
+        <f t="shared" si="1"/>
+        <v>8497</v>
+      </c>
+      <c r="N20" s="79">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="O20" s="79">
+        <f t="shared" si="1"/>
+        <v>3219</v>
+      </c>
+      <c r="P20" s="79">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q20" s="79">
+        <f t="shared" si="1"/>
+        <v>21145.98</v>
+      </c>
+      <c r="R20" s="79">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S20" s="79">
+        <f t="shared" si="1"/>
+        <v>5272.63</v>
+      </c>
+      <c r="T20" s="79">
+        <f t="shared" si="1"/>
+        <v>3188</v>
+      </c>
+      <c r="U20" s="79">
+        <f t="shared" si="1"/>
+        <v>6461</v>
+      </c>
+      <c r="V20" s="119">
+        <f t="shared" si="1"/>
+        <v>950</v>
+      </c>
+      <c r="W20" s="128">
+        <f>SUM(W3:W19)</f>
+        <v>121932.56</v>
+      </c>
+      <c r="X20" s="129">
+        <f>SUM(X3:X19)</f>
+        <v>86960.689999999988</v>
+      </c>
+      <c r="Y20" s="135">
+        <f>SUM(Y3:Y19)</f>
+        <v>214442.66999999998</v>
+      </c>
+      <c r="Z20" s="130">
+        <f>Y20-W20-X20</f>
+        <v>5549.4199999999983</v>
+      </c>
+    </row>
+    <row r="21" spans="1:28" ht="15.75">
+      <c r="A21" s="62">
+        <v>20</v>
+      </c>
+      <c r="B21" s="63" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="71">
+        <v>44</v>
+      </c>
+      <c r="D21" s="71"/>
+      <c r="E21" s="71"/>
+      <c r="F21" s="71">
+        <v>1770</v>
+      </c>
+      <c r="G21" s="71"/>
+      <c r="H21" s="71"/>
+      <c r="I21" s="71"/>
+      <c r="J21" s="71"/>
+      <c r="K21" s="71"/>
+      <c r="L21" s="71"/>
+      <c r="M21" s="71"/>
+      <c r="N21" s="71"/>
+      <c r="O21" s="71">
+        <v>572</v>
+      </c>
+      <c r="P21" s="71"/>
+      <c r="Q21" s="71">
+        <v>3400</v>
+      </c>
+      <c r="R21" s="71"/>
+      <c r="S21" s="71"/>
+      <c r="T21" s="71">
+        <v>856</v>
+      </c>
+      <c r="U21" s="71"/>
+      <c r="V21" s="105"/>
+      <c r="W21" s="122">
+        <f>SUM(C21:V21)</f>
+        <v>6642</v>
+      </c>
+      <c r="X21" s="124"/>
+      <c r="Y21" s="133">
+        <v>36898.639999999999</v>
+      </c>
+      <c r="Z21" s="123"/>
+    </row>
+    <row r="22" spans="1:28" ht="15.75">
+      <c r="A22" s="66">
+        <v>21</v>
+      </c>
+      <c r="B22" s="67" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="72">
+        <f>80</f>
+        <v>80</v>
+      </c>
+      <c r="D22" s="72">
+        <v>883</v>
+      </c>
+      <c r="E22" s="72"/>
+      <c r="F22" s="72"/>
+      <c r="G22" s="72"/>
+      <c r="H22" s="72"/>
+      <c r="I22" s="72"/>
+      <c r="J22" s="72"/>
+      <c r="K22" s="72"/>
+      <c r="L22" s="72"/>
+      <c r="M22" s="72"/>
+      <c r="N22" s="72"/>
+      <c r="O22" s="72">
+        <v>334</v>
+      </c>
+      <c r="P22" s="72"/>
+      <c r="Q22" s="72"/>
+      <c r="R22" s="72"/>
+      <c r="S22" s="72"/>
+      <c r="T22" s="72">
+        <v>79</v>
+      </c>
+      <c r="U22" s="72"/>
+      <c r="V22" s="106"/>
+      <c r="W22" s="122">
+        <f t="shared" ref="W22:W36" si="2">SUM(C22:V22)</f>
+        <v>1376</v>
+      </c>
+      <c r="X22" s="124">
+        <v>23662.84</v>
+      </c>
+      <c r="Y22" s="127"/>
+      <c r="Z22" s="123"/>
+      <c r="AB22" s="44"/>
+    </row>
+    <row r="23" spans="1:28" ht="15.75">
+      <c r="A23" s="62">
+        <v>22</v>
+      </c>
+      <c r="B23" s="63" t="s">
+        <v>2</v>
+      </c>
+      <c r="C23" s="71"/>
+      <c r="D23" s="71">
+        <v>162</v>
+      </c>
+      <c r="E23" s="71"/>
+      <c r="F23" s="71">
+        <v>690</v>
+      </c>
+      <c r="G23" s="71"/>
+      <c r="H23" s="71"/>
+      <c r="I23" s="71"/>
+      <c r="J23" s="71"/>
+      <c r="K23" s="71"/>
+      <c r="L23" s="71"/>
+      <c r="M23" s="71"/>
+      <c r="N23" s="71"/>
+      <c r="O23" s="71">
+        <v>325</v>
+      </c>
+      <c r="P23" s="71"/>
+      <c r="Q23" s="71"/>
+      <c r="R23" s="71"/>
+      <c r="S23" s="71">
+        <v>843</v>
+      </c>
+      <c r="T23" s="71"/>
+      <c r="U23" s="71"/>
+      <c r="V23" s="105"/>
+      <c r="W23" s="122">
+        <f t="shared" si="2"/>
+        <v>2020</v>
+      </c>
+      <c r="X23" s="124"/>
+      <c r="Y23" s="127"/>
+      <c r="Z23" s="123"/>
+    </row>
+    <row r="24" spans="1:28" ht="15.75">
+      <c r="A24" s="66">
+        <v>23</v>
+      </c>
+      <c r="B24" s="67" t="s">
+        <v>3</v>
+      </c>
+      <c r="C24" s="72"/>
+      <c r="D24" s="72">
+        <v>192</v>
+      </c>
+      <c r="E24" s="72"/>
+      <c r="F24" s="72">
+        <v>1960</v>
+      </c>
+      <c r="G24" s="72"/>
+      <c r="H24" s="72"/>
+      <c r="I24" s="72"/>
+      <c r="J24" s="72"/>
+      <c r="K24" s="72"/>
+      <c r="L24" s="72"/>
+      <c r="M24" s="72"/>
+      <c r="N24" s="72"/>
+      <c r="O24" s="72">
+        <f>537+185</f>
+        <v>722</v>
+      </c>
+      <c r="P24" s="72"/>
+      <c r="Q24" s="72">
+        <v>1000</v>
+      </c>
+      <c r="R24" s="72"/>
+      <c r="S24" s="72"/>
+      <c r="T24" s="72"/>
+      <c r="U24" s="72"/>
+      <c r="V24" s="106"/>
+      <c r="W24" s="122">
+        <f t="shared" si="2"/>
+        <v>3874</v>
+      </c>
+      <c r="X24" s="124"/>
+      <c r="Y24" s="127"/>
+      <c r="Z24" s="123"/>
+    </row>
+    <row r="25" spans="1:28" ht="15.75">
+      <c r="A25" s="62">
+        <v>24</v>
+      </c>
+      <c r="B25" s="63" t="s">
+        <v>4</v>
+      </c>
+      <c r="C25" s="71"/>
+      <c r="D25" s="71">
+        <f>1377+2099.31-149</f>
+        <v>3327.31</v>
+      </c>
+      <c r="E25" s="71"/>
+      <c r="F25" s="71"/>
+      <c r="G25" s="71"/>
+      <c r="H25" s="71">
+        <v>2414</v>
+      </c>
+      <c r="I25" s="71"/>
+      <c r="J25" s="71"/>
+      <c r="K25" s="71"/>
+      <c r="L25" s="71"/>
+      <c r="M25" s="71"/>
+      <c r="N25" s="71"/>
+      <c r="O25" s="71"/>
+      <c r="P25" s="71">
+        <v>152</v>
+      </c>
+      <c r="Q25" s="71"/>
+      <c r="R25" s="71"/>
+      <c r="S25" s="71"/>
+      <c r="T25" s="71"/>
+      <c r="U25" s="71"/>
+      <c r="V25" s="105">
+        <v>2000</v>
+      </c>
+      <c r="W25" s="122">
+        <f t="shared" si="2"/>
+        <v>7893.3099999999995</v>
+      </c>
+      <c r="X25" s="124"/>
+      <c r="Y25" s="127"/>
+      <c r="Z25" s="123"/>
+    </row>
+    <row r="26" spans="1:28" ht="15.75">
+      <c r="A26" s="66">
+        <v>25</v>
+      </c>
+      <c r="B26" s="67" t="s">
+        <v>5</v>
+      </c>
+      <c r="C26" s="72">
+        <v>3084</v>
+      </c>
+      <c r="D26" s="72">
+        <v>245</v>
+      </c>
+      <c r="E26" s="72"/>
+      <c r="F26" s="72"/>
+      <c r="G26" s="72"/>
+      <c r="H26" s="72"/>
+      <c r="I26" s="72"/>
+      <c r="J26" s="72"/>
+      <c r="K26" s="72"/>
+      <c r="L26" s="72"/>
+      <c r="M26" s="72"/>
+      <c r="N26" s="72"/>
+      <c r="O26" s="72"/>
+      <c r="P26" s="72"/>
+      <c r="Q26" s="72"/>
+      <c r="R26" s="72"/>
+      <c r="S26" s="72"/>
+      <c r="T26" s="72"/>
+      <c r="U26" s="72"/>
+      <c r="V26" s="106"/>
+      <c r="W26" s="122">
+        <f t="shared" si="2"/>
+        <v>3329</v>
+      </c>
+      <c r="X26" s="124"/>
+      <c r="Y26" s="127"/>
+      <c r="Z26" s="123"/>
+    </row>
+    <row r="27" spans="1:28" ht="15.75">
+      <c r="A27" s="62">
+        <v>26</v>
+      </c>
+      <c r="B27" s="63" t="s">
+        <v>6</v>
+      </c>
+      <c r="C27" s="71">
+        <v>185</v>
+      </c>
+      <c r="D27" s="71">
+        <v>1332</v>
+      </c>
+      <c r="E27" s="71">
+        <v>3180</v>
+      </c>
+      <c r="F27" s="71"/>
+      <c r="G27" s="71"/>
+      <c r="H27" s="71"/>
+      <c r="I27" s="71"/>
+      <c r="J27" s="71"/>
+      <c r="K27" s="71"/>
+      <c r="L27" s="71"/>
+      <c r="M27" s="71"/>
+      <c r="N27" s="71"/>
+      <c r="O27" s="71"/>
+      <c r="P27" s="71"/>
+      <c r="Q27" s="71"/>
+      <c r="R27" s="71"/>
+      <c r="S27" s="71"/>
+      <c r="T27" s="71"/>
+      <c r="U27" s="71"/>
+      <c r="V27" s="105">
+        <v>2800</v>
+      </c>
+      <c r="W27" s="122">
+        <f t="shared" si="2"/>
+        <v>7497</v>
+      </c>
+      <c r="X27" s="124"/>
+      <c r="Y27" s="137">
+        <v>20000</v>
+      </c>
+      <c r="Z27" s="123"/>
+    </row>
+    <row r="28" spans="1:28" ht="15.75">
+      <c r="A28" s="66">
+        <v>27</v>
+      </c>
+      <c r="B28" s="67" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" s="72"/>
+      <c r="D28" s="72"/>
+      <c r="E28" s="72"/>
+      <c r="F28" s="72"/>
+      <c r="G28" s="72"/>
+      <c r="H28" s="72"/>
+      <c r="I28" s="72"/>
+      <c r="J28" s="72"/>
+      <c r="K28" s="72"/>
+      <c r="L28" s="72"/>
+      <c r="M28" s="72"/>
+      <c r="N28" s="72"/>
+      <c r="O28" s="72"/>
+      <c r="P28" s="72">
+        <v>338</v>
+      </c>
+      <c r="Q28" s="72"/>
+      <c r="R28" s="72"/>
+      <c r="S28" s="72">
+        <v>249</v>
+      </c>
+      <c r="T28" s="72">
+        <f>3790+3780+3004</f>
+        <v>10574</v>
+      </c>
+      <c r="U28" s="72"/>
+      <c r="V28" s="106"/>
+      <c r="W28" s="122">
+        <f t="shared" si="2"/>
+        <v>11161</v>
+      </c>
+      <c r="X28" s="124"/>
+      <c r="Y28" s="127"/>
+      <c r="Z28" s="123"/>
+    </row>
+    <row r="29" spans="1:28" ht="15.75">
+      <c r="A29" s="62">
+        <v>28</v>
+      </c>
+      <c r="B29" s="63" t="s">
+        <v>8</v>
+      </c>
+      <c r="C29" s="71"/>
+      <c r="D29" s="71"/>
+      <c r="E29" s="71"/>
+      <c r="F29" s="71"/>
+      <c r="G29" s="71"/>
+      <c r="H29" s="71"/>
+      <c r="I29" s="71"/>
+      <c r="J29" s="71"/>
+      <c r="K29" s="71"/>
+      <c r="L29" s="71"/>
+      <c r="M29" s="71"/>
+      <c r="N29" s="71"/>
+      <c r="O29" s="71"/>
+      <c r="P29" s="71">
+        <v>307</v>
+      </c>
+      <c r="Q29" s="71">
+        <v>1223</v>
+      </c>
+      <c r="R29" s="71"/>
+      <c r="S29" s="71"/>
+      <c r="T29" s="71"/>
+      <c r="U29" s="71"/>
+      <c r="V29" s="105"/>
+      <c r="W29" s="122">
+        <f t="shared" si="2"/>
+        <v>1530</v>
+      </c>
+      <c r="X29" s="124"/>
+      <c r="Y29" s="127"/>
+      <c r="Z29" s="123"/>
+    </row>
+    <row r="30" spans="1:28" ht="15.75">
+      <c r="A30" s="66">
+        <v>29</v>
+      </c>
+      <c r="B30" s="67" t="s">
+        <v>2</v>
+      </c>
+      <c r="C30" s="72"/>
+      <c r="D30" s="72"/>
+      <c r="E30" s="72"/>
+      <c r="F30" s="72"/>
+      <c r="G30" s="72"/>
+      <c r="H30" s="72"/>
+      <c r="I30" s="72"/>
+      <c r="J30" s="72"/>
+      <c r="K30" s="72"/>
+      <c r="L30" s="72"/>
+      <c r="M30" s="72"/>
+      <c r="N30" s="72"/>
+      <c r="O30" s="72"/>
+      <c r="P30" s="72"/>
+      <c r="Q30" s="72">
+        <v>400</v>
+      </c>
+      <c r="R30" s="72"/>
+      <c r="S30" s="72"/>
+      <c r="T30" s="72"/>
+      <c r="U30" s="72"/>
+      <c r="V30" s="106"/>
+      <c r="W30" s="122">
+        <f t="shared" si="2"/>
+        <v>400</v>
+      </c>
+      <c r="X30" s="124"/>
+      <c r="Y30" s="127"/>
+      <c r="Z30" s="123"/>
+    </row>
+    <row r="31" spans="1:28" ht="15.75">
+      <c r="A31" s="62">
+        <v>30</v>
+      </c>
+      <c r="B31" s="63" t="s">
+        <v>3</v>
+      </c>
+      <c r="C31" s="71"/>
+      <c r="D31" s="71"/>
+      <c r="E31" s="71"/>
+      <c r="F31" s="71"/>
+      <c r="G31" s="71"/>
+      <c r="H31" s="71"/>
+      <c r="I31" s="71"/>
+      <c r="J31" s="71"/>
+      <c r="K31" s="71"/>
+      <c r="L31" s="71"/>
+      <c r="M31" s="71"/>
+      <c r="N31" s="71"/>
+      <c r="O31" s="71"/>
+      <c r="P31" s="71"/>
+      <c r="Q31" s="71"/>
+      <c r="R31" s="71"/>
+      <c r="S31" s="71"/>
+      <c r="T31" s="71"/>
+      <c r="U31" s="71"/>
+      <c r="V31" s="105"/>
+      <c r="W31" s="122">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="X31" s="124"/>
+      <c r="Y31" s="127"/>
+      <c r="Z31" s="123"/>
+    </row>
+    <row r="32" spans="1:28" ht="15.75">
+      <c r="A32" s="66">
+        <v>31</v>
+      </c>
+      <c r="B32" s="67" t="s">
+        <v>4</v>
+      </c>
+      <c r="C32" s="72"/>
+      <c r="D32" s="72"/>
+      <c r="E32" s="72"/>
+      <c r="F32" s="72"/>
+      <c r="G32" s="72"/>
+      <c r="H32" s="72"/>
+      <c r="I32" s="72"/>
+      <c r="J32" s="72"/>
+      <c r="K32" s="72"/>
+      <c r="L32" s="72"/>
+      <c r="M32" s="72"/>
+      <c r="N32" s="72"/>
+      <c r="O32" s="72"/>
+      <c r="P32" s="72"/>
+      <c r="Q32" s="72"/>
+      <c r="R32" s="72"/>
+      <c r="S32" s="72"/>
+      <c r="T32" s="72"/>
+      <c r="U32" s="72"/>
+      <c r="V32" s="106"/>
+      <c r="W32" s="122">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="X32" s="124"/>
+      <c r="Y32" s="127"/>
+      <c r="Z32" s="123"/>
+    </row>
+    <row r="33" spans="1:26" ht="15.75">
+      <c r="A33" s="62">
+        <v>1</v>
+      </c>
+      <c r="B33" s="63" t="s">
+        <v>5</v>
+      </c>
+      <c r="C33" s="71"/>
+      <c r="D33" s="71"/>
+      <c r="E33" s="71"/>
+      <c r="F33" s="71"/>
+      <c r="G33" s="71"/>
+      <c r="H33" s="71"/>
+      <c r="I33" s="71"/>
+      <c r="J33" s="71"/>
+      <c r="K33" s="71"/>
+      <c r="L33" s="71"/>
+      <c r="M33" s="71"/>
+      <c r="N33" s="71"/>
+      <c r="O33" s="71"/>
+      <c r="P33" s="71"/>
+      <c r="Q33" s="71"/>
+      <c r="R33" s="71"/>
+      <c r="S33" s="71"/>
+      <c r="T33" s="71"/>
+      <c r="U33" s="71"/>
+      <c r="V33" s="105"/>
+      <c r="W33" s="122">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="X33" s="124"/>
+      <c r="Y33" s="127"/>
+      <c r="Z33" s="123"/>
+    </row>
+    <row r="34" spans="1:26" ht="15.75">
+      <c r="A34" s="66">
+        <v>2</v>
+      </c>
+      <c r="B34" s="67" t="s">
+        <v>6</v>
+      </c>
+      <c r="C34" s="72"/>
+      <c r="D34" s="72"/>
+      <c r="E34" s="72"/>
+      <c r="F34" s="72"/>
+      <c r="G34" s="72"/>
+      <c r="H34" s="72"/>
+      <c r="I34" s="72"/>
+      <c r="J34" s="72"/>
+      <c r="K34" s="72"/>
+      <c r="L34" s="72"/>
+      <c r="M34" s="72"/>
+      <c r="N34" s="72"/>
+      <c r="O34" s="72"/>
+      <c r="P34" s="72"/>
+      <c r="Q34" s="72"/>
+      <c r="R34" s="72"/>
+      <c r="S34" s="72"/>
+      <c r="T34" s="72"/>
+      <c r="U34" s="72"/>
+      <c r="V34" s="106"/>
+      <c r="W34" s="122">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="X34" s="124"/>
+      <c r="Y34" s="127"/>
+      <c r="Z34" s="123"/>
+    </row>
+    <row r="35" spans="1:26" ht="15.75">
+      <c r="A35" s="62">
+        <v>3</v>
+      </c>
+      <c r="B35" s="63" t="s">
+        <v>7</v>
+      </c>
+      <c r="C35" s="71"/>
+      <c r="D35" s="71"/>
+      <c r="E35" s="71"/>
+      <c r="F35" s="71"/>
+      <c r="G35" s="71"/>
+      <c r="H35" s="71"/>
+      <c r="I35" s="71"/>
+      <c r="J35" s="71"/>
+      <c r="K35" s="71"/>
+      <c r="L35" s="71"/>
+      <c r="M35" s="71"/>
+      <c r="N35" s="71"/>
+      <c r="O35" s="71"/>
+      <c r="P35" s="71"/>
+      <c r="Q35" s="71"/>
+      <c r="R35" s="71"/>
+      <c r="S35" s="71"/>
+      <c r="T35" s="71"/>
+      <c r="U35" s="71"/>
+      <c r="V35" s="105"/>
+      <c r="W35" s="122">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="X35" s="124"/>
+      <c r="Y35" s="127"/>
+      <c r="Z35" s="123"/>
+    </row>
+    <row r="36" spans="1:26" ht="15.75">
+      <c r="A36" s="66">
+        <v>4</v>
+      </c>
+      <c r="B36" s="67" t="s">
+        <v>8</v>
+      </c>
+      <c r="C36" s="72"/>
+      <c r="D36" s="72"/>
+      <c r="E36" s="72"/>
+      <c r="F36" s="72"/>
+      <c r="G36" s="72"/>
+      <c r="H36" s="72"/>
+      <c r="I36" s="72"/>
+      <c r="J36" s="72"/>
+      <c r="K36" s="72"/>
+      <c r="L36" s="72"/>
+      <c r="M36" s="72"/>
+      <c r="N36" s="72"/>
+      <c r="O36" s="72"/>
+      <c r="P36" s="72"/>
+      <c r="Q36" s="72"/>
+      <c r="R36" s="72"/>
+      <c r="S36" s="72"/>
+      <c r="T36" s="72"/>
+      <c r="U36" s="72"/>
+      <c r="V36" s="106"/>
+      <c r="W36" s="122">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="X36" s="124"/>
+      <c r="Y36" s="127"/>
+      <c r="Z36" s="123"/>
+    </row>
+    <row r="37" spans="1:26">
+      <c r="A37" s="99" t="s">
+        <v>36</v>
+      </c>
+      <c r="B37" s="99"/>
+      <c r="C37" s="79">
+        <f>SUM(C21:C36)</f>
+        <v>3393</v>
+      </c>
+      <c r="D37" s="79">
+        <f t="shared" ref="D37:V37" si="3">SUM(D21:D36)</f>
+        <v>6141.3099999999995</v>
+      </c>
+      <c r="E37" s="79">
+        <f t="shared" si="3"/>
+        <v>3180</v>
+      </c>
+      <c r="F37" s="79">
+        <f t="shared" si="3"/>
+        <v>4420</v>
+      </c>
+      <c r="G37" s="79">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H37" s="79">
+        <f t="shared" si="3"/>
+        <v>2414</v>
+      </c>
+      <c r="I37" s="79">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J37" s="79">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K37" s="79">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L37" s="79">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M37" s="79">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N37" s="79">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="O37" s="79">
+        <f t="shared" si="3"/>
+        <v>1953</v>
+      </c>
+      <c r="P37" s="79">
+        <f t="shared" si="3"/>
+        <v>797</v>
+      </c>
+      <c r="Q37" s="79">
+        <f t="shared" si="3"/>
+        <v>6023</v>
+      </c>
+      <c r="R37" s="79">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="S37" s="79">
+        <f t="shared" si="3"/>
+        <v>1092</v>
+      </c>
+      <c r="T37" s="79">
+        <f>SUM(T21:T36)</f>
+        <v>11509</v>
+      </c>
+      <c r="U37" s="79">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="V37" s="119">
+        <f t="shared" si="3"/>
+        <v>4800</v>
+      </c>
+      <c r="W37" s="128">
+        <f>SUM(W21:W36)</f>
+        <v>45722.31</v>
+      </c>
+      <c r="X37" s="129">
+        <f>SUM(X21:X36)</f>
+        <v>23662.84</v>
+      </c>
+      <c r="Y37" s="135">
+        <f>SUM(Y21:Y36)</f>
+        <v>56898.64</v>
+      </c>
+      <c r="Z37" s="131">
+        <f>Y37-W37-X37</f>
+        <v>-12486.509999999998</v>
+      </c>
+    </row>
+    <row r="38" spans="1:26" ht="31.5" customHeight="1">
+      <c r="A38" s="102" t="s">
+        <v>37</v>
+      </c>
+      <c r="B38" s="102"/>
+      <c r="C38" s="78">
+        <f>SUM(C20,C37)</f>
+        <v>14335.99</v>
+      </c>
+      <c r="D38" s="78">
+        <f t="shared" ref="D38:W38" si="4">SUM(D20,D37)</f>
+        <v>11666.56</v>
+      </c>
+      <c r="E38" s="78">
+        <f t="shared" si="4"/>
+        <v>8530</v>
+      </c>
+      <c r="F38" s="78">
+        <f t="shared" si="4"/>
+        <v>6460</v>
+      </c>
+      <c r="G38" s="78">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H38" s="78">
+        <f t="shared" si="4"/>
+        <v>6174</v>
+      </c>
+      <c r="I38" s="78">
+        <f t="shared" si="4"/>
+        <v>2320.98</v>
+      </c>
+      <c r="J38" s="78">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K38" s="78">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="L38" s="78">
+        <f t="shared" si="4"/>
+        <v>3150</v>
+      </c>
+      <c r="M38" s="78">
+        <f t="shared" si="4"/>
+        <v>8497</v>
+      </c>
+      <c r="N38" s="78">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="O38" s="78">
+        <f t="shared" si="4"/>
+        <v>5172</v>
+      </c>
+      <c r="P38" s="78">
+        <f t="shared" si="4"/>
+        <v>797</v>
+      </c>
+      <c r="Q38" s="78">
+        <f t="shared" si="4"/>
+        <v>27168.98</v>
+      </c>
+      <c r="R38" s="78">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S38" s="78">
+        <f>SUM(S20,S37)</f>
+        <v>6364.63</v>
+      </c>
+      <c r="T38" s="78">
+        <f t="shared" si="4"/>
+        <v>14697</v>
+      </c>
+      <c r="U38" s="78">
+        <f t="shared" si="4"/>
+        <v>6461</v>
+      </c>
+      <c r="V38" s="120">
+        <f t="shared" si="4"/>
+        <v>5750</v>
+      </c>
+      <c r="W38" s="128">
+        <f t="shared" si="4"/>
+        <v>167654.87</v>
+      </c>
+      <c r="X38" s="129">
+        <f>SUM(X20,X37)</f>
+        <v>110623.52999999998</v>
+      </c>
+      <c r="Y38" s="136">
+        <f>SUM(Y20,Y37)</f>
+        <v>271341.31</v>
+      </c>
+      <c r="Z38" s="70">
+        <f>SUM(Z20,Z37)</f>
+        <v>-6937.09</v>
+      </c>
+    </row>
+    <row r="42" spans="1:26">
+      <c r="B42" s="6"/>
+      <c r="C42" s="6"/>
+      <c r="D42" s="6"/>
+      <c r="E42" s="6"/>
+      <c r="F42" s="6"/>
+      <c r="G42" s="6"/>
+      <c r="H42" s="6"/>
+      <c r="I42" s="6"/>
+      <c r="J42" s="6"/>
+      <c r="K42" s="6"/>
+    </row>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="AC14:AF14"/>
+    <mergeCell ref="AC15:AF15"/>
+    <mergeCell ref="AC8:AG10"/>
+    <mergeCell ref="AC11:AF11"/>
+    <mergeCell ref="AC12:AF12"/>
+    <mergeCell ref="AC13:AF13"/>
+    <mergeCell ref="A1:Z1"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="Z3:Z19"/>
+    <mergeCell ref="Z21:Z36"/>
+  </mergeCells>
+  <conditionalFormatting sqref="Z20:Z21 Z37:Z38">
+    <cfRule type="expression" dxfId="1" priority="1">
+      <formula>Z20&lt;0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="0" priority="2">
+      <formula>Z20&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AV42"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="26" width="20.7109375" style="2" customWidth="1"/>
+    <col min="27" max="38" width="12.7109375" style="2" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:48" ht="60.75" customHeight="1">
+      <c r="A1" s="101" t="s">
+        <v>59</v>
+      </c>
+      <c r="B1" s="101"/>
+      <c r="C1" s="101"/>
+      <c r="D1" s="101"/>
+      <c r="E1" s="101"/>
+      <c r="F1" s="101"/>
+      <c r="G1" s="101"/>
+      <c r="H1" s="101"/>
+      <c r="I1" s="101"/>
+      <c r="J1" s="101"/>
+      <c r="K1" s="101"/>
+      <c r="L1" s="101"/>
+      <c r="M1" s="101"/>
+      <c r="N1" s="101"/>
+      <c r="O1" s="101"/>
+      <c r="P1" s="101"/>
+      <c r="Q1" s="101"/>
+      <c r="R1" s="101"/>
+      <c r="S1" s="101"/>
+      <c r="T1" s="101"/>
+      <c r="U1" s="101"/>
+      <c r="V1" s="101"/>
+      <c r="W1" s="101"/>
+      <c r="X1" s="101"/>
+      <c r="Y1" s="101"/>
+      <c r="Z1" s="101"/>
+    </row>
+    <row r="2" spans="1:48" ht="45" customHeight="1">
+      <c r="A2" s="76" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="116" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="116" t="s">
+        <v>29</v>
+      </c>
+      <c r="E2" s="116" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="116" t="s">
+        <v>33</v>
+      </c>
+      <c r="G2" s="116" t="s">
+        <v>34</v>
+      </c>
+      <c r="H2" s="116" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="115" t="s">
+        <v>30</v>
+      </c>
+      <c r="J2" s="115" t="s">
+        <v>12</v>
+      </c>
+      <c r="K2" s="76" t="s">
+        <v>24</v>
+      </c>
+      <c r="L2" s="76" t="s">
+        <v>23</v>
+      </c>
+      <c r="M2" s="76" t="s">
+        <v>13</v>
+      </c>
+      <c r="N2" s="76" t="s">
+        <v>14</v>
+      </c>
+      <c r="O2" s="76" t="s">
+        <v>15</v>
+      </c>
+      <c r="P2" s="76" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q2" s="76" t="s">
+        <v>28</v>
+      </c>
+      <c r="R2" s="76" t="s">
+        <v>17</v>
+      </c>
+      <c r="S2" s="76" t="s">
+        <v>18</v>
+      </c>
+      <c r="T2" s="76" t="s">
+        <v>25</v>
+      </c>
+      <c r="U2" s="76" t="s">
+        <v>25</v>
+      </c>
+      <c r="V2" s="76" t="s">
+        <v>26</v>
+      </c>
+      <c r="W2" s="103" t="s">
+        <v>60</v>
+      </c>
+      <c r="X2" s="81" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y2" s="81" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z2" s="81" t="s">
+        <v>21</v>
+      </c>
+      <c r="AA2" s="1"/>
+      <c r="AB2" s="1"/>
+      <c r="AC2" s="1"/>
+      <c r="AD2" s="1"/>
+      <c r="AE2" s="1"/>
+      <c r="AF2" s="1"/>
+      <c r="AG2" s="1"/>
+      <c r="AH2" s="1"/>
+      <c r="AI2" s="1"/>
+      <c r="AJ2" s="1"/>
+      <c r="AK2" s="1"/>
+      <c r="AL2" s="1"/>
+      <c r="AM2" s="1"/>
+      <c r="AN2" s="1"/>
+      <c r="AO2" s="1"/>
+      <c r="AP2" s="1"/>
+      <c r="AQ2" s="1"/>
+      <c r="AR2" s="1"/>
+      <c r="AS2" s="1"/>
+      <c r="AT2" s="1"/>
+      <c r="AU2" s="1"/>
+      <c r="AV2" s="1"/>
+    </row>
+    <row r="3" spans="1:48" ht="15.75">
+      <c r="A3" s="62">
+        <v>3</v>
+      </c>
+      <c r="B3" s="63" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="71">
+        <f>100</f>
+        <v>100</v>
+      </c>
+      <c r="D3" s="71"/>
+      <c r="E3" s="71"/>
+      <c r="F3" s="71"/>
+      <c r="G3" s="71"/>
+      <c r="H3" s="71"/>
+      <c r="I3" s="71"/>
+      <c r="J3" s="71"/>
+      <c r="K3" s="71"/>
+      <c r="L3" s="71">
+        <f>150+3000</f>
+        <v>3150</v>
+      </c>
+      <c r="M3" s="71"/>
+      <c r="N3" s="71"/>
+      <c r="O3" s="71"/>
+      <c r="P3" s="71"/>
+      <c r="Q3" s="71">
+        <f>10000</f>
+        <v>10000</v>
+      </c>
+      <c r="R3" s="71"/>
+      <c r="S3" s="71">
+        <v>799</v>
+      </c>
+      <c r="T3" s="71"/>
+      <c r="U3" s="71"/>
+      <c r="V3" s="71"/>
+      <c r="W3" s="71"/>
+      <c r="X3" s="105">
+        <f>SUM(C3:V3)</f>
+        <v>14049</v>
+      </c>
+      <c r="Y3" s="114">
+        <f>(94085+57723.67)/2</f>
+        <v>75904.334999999992</v>
+      </c>
+      <c r="Z3" s="107"/>
+    </row>
+    <row r="4" spans="1:48" ht="15.75">
+      <c r="A4" s="66">
+        <v>4</v>
+      </c>
+      <c r="B4" s="67" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="72">
+        <v>528.91999999999996</v>
+      </c>
+      <c r="D4" s="72">
+        <f>403+3617.41</f>
+        <v>4020.41</v>
+      </c>
+      <c r="E4" s="72"/>
+      <c r="F4" s="72"/>
+      <c r="G4" s="72"/>
+      <c r="H4" s="72">
+        <f>3760</f>
+        <v>3760</v>
+      </c>
+      <c r="I4" s="72">
+        <v>1320.98</v>
+      </c>
+      <c r="J4" s="72"/>
+      <c r="K4" s="72"/>
+      <c r="L4" s="72"/>
+      <c r="M4" s="72"/>
+      <c r="N4" s="72"/>
+      <c r="O4" s="72">
+        <f>290+215</f>
+        <v>505</v>
+      </c>
+      <c r="P4" s="72"/>
+      <c r="Q4" s="72"/>
+      <c r="R4" s="72"/>
+      <c r="S4" s="72"/>
+      <c r="T4" s="72">
+        <v>398</v>
+      </c>
+      <c r="U4" s="72"/>
+      <c r="V4" s="72"/>
+      <c r="W4" s="72"/>
+      <c r="X4" s="106">
+        <f>SUM(C4:V4)</f>
+        <v>10533.31</v>
+      </c>
+      <c r="Y4" s="111"/>
+      <c r="Z4" s="108"/>
+    </row>
+    <row r="5" spans="1:48" ht="15.75">
+      <c r="A5" s="62">
+        <v>5</v>
+      </c>
+      <c r="B5" s="63" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="71">
+        <f>441+815</f>
+        <v>1256</v>
+      </c>
+      <c r="D5" s="71"/>
+      <c r="E5" s="71"/>
+      <c r="F5" s="71"/>
+      <c r="G5" s="71"/>
+      <c r="H5" s="71"/>
+      <c r="I5" s="71"/>
+      <c r="J5" s="71"/>
+      <c r="K5" s="71"/>
+      <c r="L5" s="71"/>
+      <c r="M5" s="71"/>
+      <c r="N5" s="71"/>
+      <c r="O5" s="71"/>
+      <c r="P5" s="71"/>
+      <c r="Q5" s="71"/>
+      <c r="R5" s="71"/>
+      <c r="S5" s="71">
+        <v>199</v>
+      </c>
+      <c r="T5" s="71"/>
+      <c r="U5" s="71"/>
+      <c r="V5" s="71"/>
+      <c r="W5" s="71"/>
+      <c r="X5" s="105">
+        <f t="shared" ref="X5:X19" si="0">SUM(C5:V5)</f>
+        <v>1455</v>
+      </c>
+      <c r="Y5" s="111"/>
+      <c r="Z5" s="108"/>
+    </row>
+    <row r="6" spans="1:48" ht="15.75">
+      <c r="A6" s="66">
+        <v>6</v>
+      </c>
+      <c r="B6" s="67" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="72"/>
+      <c r="D6" s="72">
+        <v>628.84</v>
+      </c>
+      <c r="E6" s="72"/>
+      <c r="F6" s="72"/>
+      <c r="G6" s="72"/>
+      <c r="H6" s="72"/>
+      <c r="I6" s="72"/>
+      <c r="J6" s="72"/>
+      <c r="K6" s="72"/>
+      <c r="L6" s="72"/>
+      <c r="M6" s="72"/>
+      <c r="N6" s="72"/>
+      <c r="O6" s="72">
+        <v>225</v>
+      </c>
+      <c r="P6" s="72"/>
+      <c r="Q6" s="72"/>
+      <c r="R6" s="72"/>
+      <c r="S6" s="72"/>
+      <c r="T6" s="72"/>
+      <c r="U6" s="72"/>
+      <c r="V6" s="72">
+        <v>950</v>
+      </c>
+      <c r="W6" s="72"/>
+      <c r="X6" s="106">
+        <f t="shared" si="0"/>
+        <v>1803.8400000000001</v>
+      </c>
+      <c r="Y6" s="111"/>
+      <c r="Z6" s="108"/>
+    </row>
+    <row r="7" spans="1:48" ht="15" customHeight="1">
+      <c r="A7" s="62">
+        <v>7</v>
+      </c>
+      <c r="B7" s="63" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="71">
+        <f>1534.21+320.4</f>
+        <v>1854.6100000000001</v>
+      </c>
+      <c r="D7" s="71">
+        <v>292</v>
+      </c>
+      <c r="E7" s="71"/>
+      <c r="F7" s="71">
+        <v>960</v>
+      </c>
+      <c r="G7" s="71"/>
+      <c r="H7" s="71"/>
+      <c r="I7" s="71"/>
+      <c r="J7" s="71"/>
+      <c r="K7" s="71"/>
+      <c r="L7" s="71"/>
+      <c r="M7" s="71"/>
+      <c r="N7" s="71"/>
+      <c r="O7" s="71">
+        <v>196</v>
+      </c>
+      <c r="P7" s="71"/>
+      <c r="Q7" s="71"/>
+      <c r="R7" s="71"/>
+      <c r="S7" s="71"/>
+      <c r="T7" s="71"/>
+      <c r="U7" s="71"/>
+      <c r="V7" s="71"/>
+      <c r="W7" s="71"/>
+      <c r="X7" s="105">
+        <f t="shared" si="0"/>
+        <v>3302.61</v>
+      </c>
+      <c r="Y7" s="111"/>
+      <c r="Z7" s="108"/>
+    </row>
+    <row r="8" spans="1:48" ht="15.75">
+      <c r="A8" s="66">
+        <v>8</v>
+      </c>
+      <c r="B8" s="67" t="s">
+        <v>2</v>
+      </c>
+      <c r="C8" s="72">
+        <v>233</v>
+      </c>
+      <c r="D8" s="72"/>
+      <c r="E8" s="72"/>
+      <c r="F8" s="72"/>
+      <c r="G8" s="72"/>
+      <c r="H8" s="72"/>
+      <c r="I8" s="72"/>
+      <c r="J8" s="72"/>
+      <c r="K8" s="72"/>
+      <c r="L8" s="72"/>
+      <c r="M8" s="72"/>
+      <c r="N8" s="72"/>
+      <c r="O8" s="72"/>
+      <c r="P8" s="72"/>
+      <c r="Q8" s="72">
+        <f>490+690</f>
+        <v>1180</v>
+      </c>
+      <c r="R8" s="72"/>
+      <c r="S8" s="72">
+        <v>842</v>
+      </c>
+      <c r="T8" s="72"/>
+      <c r="U8" s="72"/>
+      <c r="V8" s="72"/>
+      <c r="W8" s="72"/>
+      <c r="X8" s="106">
+        <f t="shared" si="0"/>
+        <v>2255</v>
+      </c>
+      <c r="Y8" s="111"/>
+      <c r="Z8" s="108"/>
+    </row>
+    <row r="9" spans="1:48" ht="15.75">
+      <c r="A9" s="62">
+        <v>9</v>
+      </c>
+      <c r="B9" s="63" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9" s="71"/>
+      <c r="D9" s="71"/>
+      <c r="E9" s="71"/>
+      <c r="F9" s="71"/>
+      <c r="G9" s="71"/>
+      <c r="H9" s="71"/>
+      <c r="I9" s="71"/>
+      <c r="J9" s="71"/>
+      <c r="K9" s="71"/>
+      <c r="L9" s="71"/>
+      <c r="M9" s="71"/>
+      <c r="N9" s="71"/>
+      <c r="O9" s="71">
+        <v>395</v>
+      </c>
+      <c r="P9" s="71"/>
+      <c r="Q9" s="71"/>
+      <c r="R9" s="71"/>
+      <c r="S9" s="71">
+        <v>700</v>
+      </c>
+      <c r="T9" s="71"/>
+      <c r="U9" s="71"/>
+      <c r="V9" s="71"/>
+      <c r="W9" s="71"/>
+      <c r="X9" s="105">
+        <f t="shared" si="0"/>
+        <v>1095</v>
+      </c>
+      <c r="Y9" s="111"/>
+      <c r="Z9" s="108"/>
+    </row>
+    <row r="10" spans="1:48" ht="15.75">
+      <c r="A10" s="66">
+        <v>10</v>
+      </c>
+      <c r="B10" s="67" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" s="72"/>
+      <c r="D10" s="72"/>
+      <c r="E10" s="72">
+        <v>2500</v>
+      </c>
+      <c r="F10" s="72"/>
+      <c r="G10" s="72"/>
+      <c r="H10" s="72"/>
+      <c r="I10" s="72"/>
+      <c r="J10" s="72"/>
+      <c r="K10" s="72"/>
+      <c r="L10" s="72"/>
+      <c r="M10" s="72"/>
+      <c r="N10" s="72"/>
+      <c r="O10" s="72">
+        <f>473+161</f>
+        <v>634</v>
+      </c>
+      <c r="P10" s="72"/>
+      <c r="Q10" s="72"/>
+      <c r="R10" s="72"/>
+      <c r="S10" s="72">
+        <v>990</v>
+      </c>
+      <c r="T10" s="72">
+        <v>790</v>
+      </c>
+      <c r="U10" s="72"/>
+      <c r="V10" s="72"/>
+      <c r="W10" s="72"/>
+      <c r="X10" s="106">
+        <f t="shared" si="0"/>
+        <v>4914</v>
+      </c>
+      <c r="Y10" s="111"/>
+      <c r="Z10" s="108"/>
+    </row>
+    <row r="11" spans="1:48" ht="15.75">
+      <c r="A11" s="62">
+        <v>11</v>
+      </c>
+      <c r="B11" s="63" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="71">
+        <f>132.68+3500</f>
+        <v>3632.68</v>
+      </c>
+      <c r="D11" s="71"/>
+      <c r="E11" s="71"/>
+      <c r="F11" s="71"/>
+      <c r="G11" s="71"/>
+      <c r="H11" s="71"/>
+      <c r="I11" s="71">
+        <v>1000</v>
+      </c>
+      <c r="J11" s="71"/>
+      <c r="K11" s="71"/>
+      <c r="L11" s="71"/>
+      <c r="M11" s="71"/>
+      <c r="N11" s="71"/>
+      <c r="O11" s="71"/>
+      <c r="P11" s="71"/>
+      <c r="Q11" s="71"/>
+      <c r="R11" s="71"/>
+      <c r="S11" s="71"/>
+      <c r="T11" s="71"/>
+      <c r="U11" s="71"/>
+      <c r="V11" s="71"/>
+      <c r="W11" s="71"/>
+      <c r="X11" s="105">
+        <f t="shared" si="0"/>
+        <v>4632.68</v>
+      </c>
+      <c r="Y11" s="111"/>
+      <c r="Z11" s="108"/>
+    </row>
+    <row r="12" spans="1:48" ht="15.75">
+      <c r="A12" s="66">
+        <v>12</v>
+      </c>
+      <c r="B12" s="67" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="72"/>
+      <c r="D12" s="72"/>
+      <c r="E12" s="72"/>
+      <c r="F12" s="72"/>
+      <c r="G12" s="72"/>
+      <c r="H12" s="72"/>
+      <c r="I12" s="72"/>
+      <c r="J12" s="72"/>
+      <c r="K12" s="72"/>
+      <c r="L12" s="72"/>
+      <c r="M12" s="72"/>
+      <c r="N12" s="72"/>
+      <c r="O12" s="72"/>
+      <c r="P12" s="72"/>
+      <c r="Q12" s="72">
+        <v>4475</v>
+      </c>
+      <c r="R12" s="72"/>
+      <c r="S12" s="72"/>
+      <c r="T12" s="72"/>
+      <c r="U12" s="72"/>
+      <c r="V12" s="72"/>
+      <c r="W12" s="72"/>
+      <c r="X12" s="106">
+        <f t="shared" si="0"/>
+        <v>4475</v>
+      </c>
+      <c r="Y12" s="111"/>
+      <c r="Z12" s="108"/>
+    </row>
+    <row r="13" spans="1:48" ht="15.75">
+      <c r="A13" s="62">
+        <v>13</v>
+      </c>
+      <c r="B13" s="63" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="71"/>
+      <c r="D13" s="71"/>
+      <c r="E13" s="71"/>
+      <c r="F13" s="71"/>
+      <c r="G13" s="71"/>
+      <c r="H13" s="71"/>
+      <c r="I13" s="71"/>
+      <c r="J13" s="71"/>
+      <c r="K13" s="71"/>
+      <c r="L13" s="71"/>
+      <c r="M13" s="71"/>
+      <c r="N13" s="71"/>
+      <c r="O13" s="71">
+        <v>303</v>
+      </c>
+      <c r="P13" s="71"/>
+      <c r="Q13" s="71">
+        <v>2870</v>
+      </c>
+      <c r="R13" s="71"/>
+      <c r="S13" s="71">
+        <v>842.63</v>
+      </c>
+      <c r="T13" s="71"/>
+      <c r="U13" s="71"/>
+      <c r="V13" s="71"/>
+      <c r="W13" s="71"/>
+      <c r="X13" s="105">
+        <f t="shared" si="0"/>
+        <v>4015.63</v>
+      </c>
+      <c r="Y13" s="111"/>
+      <c r="Z13" s="108"/>
+    </row>
+    <row r="14" spans="1:48" ht="15.75">
       <c r="A14" s="66">
         <v>14</v>
       </c>
@@ -14238,17 +18052,18 @@
       <c r="T14" s="72"/>
       <c r="U14" s="72"/>
       <c r="V14" s="72"/>
-      <c r="W14" s="72">
+      <c r="W14" s="72"/>
+      <c r="X14" s="106">
         <f t="shared" si="0"/>
         <v>2273.7800000000002</v>
       </c>
-      <c r="X14" s="64">
+      <c r="Y14" s="114">
         <f>37634-14878.51</f>
         <v>22755.489999999998</v>
       </c>
-      <c r="Y14" s="104"/>
-    </row>
-    <row r="15" spans="1:47" ht="15.75">
+      <c r="Z14" s="108"/>
+    </row>
+    <row r="15" spans="1:48" ht="15.75">
       <c r="A15" s="62">
         <v>15</v>
       </c>
@@ -14286,14 +18101,15 @@
       <c r="T15" s="71"/>
       <c r="U15" s="71"/>
       <c r="V15" s="71"/>
-      <c r="W15" s="71">
+      <c r="W15" s="71"/>
+      <c r="X15" s="105">
         <f t="shared" si="0"/>
         <v>4096.9799999999996</v>
       </c>
-      <c r="X15" s="107"/>
-      <c r="Y15" s="104"/>
-    </row>
-    <row r="16" spans="1:47" ht="15.75">
+      <c r="Y15" s="111"/>
+      <c r="Z15" s="108"/>
+    </row>
+    <row r="16" spans="1:48" ht="15.75">
       <c r="A16" s="66">
         <v>16</v>
       </c>
@@ -14324,16 +18140,17 @@
       <c r="T16" s="72">
         <v>1100</v>
       </c>
-      <c r="U16" s="109"/>
+      <c r="U16" s="87"/>
       <c r="V16" s="72"/>
-      <c r="W16" s="72">
+      <c r="W16" s="72"/>
+      <c r="X16" s="106">
         <f t="shared" si="0"/>
         <v>2593</v>
       </c>
-      <c r="X16" s="107"/>
-      <c r="Y16" s="104"/>
-    </row>
-    <row r="17" spans="1:27" ht="15.75">
+      <c r="Y16" s="111"/>
+      <c r="Z16" s="108"/>
+    </row>
+    <row r="17" spans="1:28" ht="15.75">
       <c r="A17" s="62">
         <v>17</v>
       </c>
@@ -14362,14 +18179,17 @@
       <c r="T17" s="71"/>
       <c r="U17" s="71"/>
       <c r="V17" s="71"/>
-      <c r="W17" s="71">
+      <c r="W17" s="71"/>
+      <c r="X17" s="105">
         <f t="shared" si="0"/>
         <v>700</v>
       </c>
-      <c r="X17" s="107"/>
-      <c r="Y17" s="104"/>
-    </row>
-    <row r="18" spans="1:27" ht="15.75">
+      <c r="Y17" s="112">
+        <v>15000</v>
+      </c>
+      <c r="Z17" s="108"/>
+    </row>
+    <row r="18" spans="1:28" ht="15.75">
       <c r="A18" s="66">
         <v>18</v>
       </c>
@@ -14397,19 +18217,20 @@
       <c r="S18" s="72">
         <v>499</v>
       </c>
-      <c r="T18" s="109"/>
+      <c r="T18" s="87"/>
       <c r="U18" s="72">
         <v>8000</v>
       </c>
       <c r="V18" s="72"/>
-      <c r="W18" s="72">
+      <c r="W18" s="72"/>
+      <c r="X18" s="106">
         <f t="shared" si="0"/>
         <v>10517.8</v>
       </c>
-      <c r="X18" s="107"/>
-      <c r="Y18" s="104"/>
-    </row>
-    <row r="19" spans="1:27" ht="15.75">
+      <c r="Y18" s="111"/>
+      <c r="Z18" s="108"/>
+    </row>
+    <row r="19" spans="1:28" ht="15.75">
       <c r="A19" s="62">
         <v>19</v>
       </c>
@@ -14420,7 +18241,9 @@
       <c r="D19" s="71">
         <v>2376.09</v>
       </c>
-      <c r="E19" s="71"/>
+      <c r="E19" s="71">
+        <v>3600</v>
+      </c>
       <c r="F19" s="71"/>
       <c r="G19" s="71"/>
       <c r="H19" s="71"/>
@@ -14441,20 +18264,23 @@
         <f>83+760+400+6869+83+83+1800+850+1033.84+1423+1349+694+83+6000+1800+305</f>
         <v>23615.84</v>
       </c>
-      <c r="W19" s="71">
+      <c r="W19" s="71"/>
+      <c r="X19" s="105">
         <f t="shared" si="0"/>
-        <v>25991.93</v>
-      </c>
-      <c r="X19" s="108"/>
-      <c r="Y19" s="105"/>
-    </row>
-    <row r="20" spans="1:27" ht="14.25" customHeight="1">
+        <v>29591.93</v>
+      </c>
+      <c r="Y19" s="112">
+        <v>10000</v>
+      </c>
+      <c r="Z19" s="109"/>
+    </row>
+    <row r="20" spans="1:28" ht="14.25" customHeight="1">
       <c r="A20" s="99" t="s">
         <v>35</v>
       </c>
       <c r="B20" s="99"/>
       <c r="C20" s="79">
-        <f t="shared" ref="C20:X20" si="1">SUM(C3:C17)</f>
+        <f t="shared" ref="C20:Y20" si="1">SUM(C3:C17)</f>
         <v>10242.99</v>
       </c>
       <c r="D20" s="79">
@@ -14533,30 +18359,35 @@
         <f t="shared" si="1"/>
         <v>950</v>
       </c>
-      <c r="W20" s="82">
+      <c r="W20" s="79"/>
+      <c r="X20" s="82">
         <f t="shared" si="1"/>
         <v>62194.829999999987</v>
       </c>
-      <c r="X20" s="83">
+      <c r="Y20" s="113">
         <f t="shared" si="1"/>
-        <v>98659.824999999983</v>
-      </c>
-      <c r="Y20" s="84">
-        <f>X20-W20</f>
-        <v>36464.994999999995</v>
-      </c>
-    </row>
-    <row r="21" spans="1:27" ht="15.75">
+        <v>113659.82499999998</v>
+      </c>
+      <c r="Z20" s="83">
+        <f>Y20-X20</f>
+        <v>51464.994999999995</v>
+      </c>
+    </row>
+    <row r="21" spans="1:28" ht="15.75">
       <c r="A21" s="62">
         <v>20</v>
       </c>
       <c r="B21" s="63" t="s">
-        <v>5</v>
-      </c>
-      <c r="C21" s="71"/>
+        <v>7</v>
+      </c>
+      <c r="C21" s="71">
+        <v>44</v>
+      </c>
       <c r="D21" s="71"/>
       <c r="E21" s="71"/>
-      <c r="F21" s="71"/>
+      <c r="F21" s="71">
+        <v>1770</v>
+      </c>
       <c r="G21" s="71"/>
       <c r="H21" s="71"/>
       <c r="I21" s="71"/>
@@ -14565,27 +18396,41 @@
       <c r="L21" s="71"/>
       <c r="M21" s="71"/>
       <c r="N21" s="71"/>
-      <c r="O21" s="71"/>
+      <c r="O21" s="71">
+        <v>572</v>
+      </c>
       <c r="P21" s="71"/>
-      <c r="Q21" s="71"/>
+      <c r="Q21" s="71">
+        <v>3400</v>
+      </c>
       <c r="R21" s="71"/>
       <c r="S21" s="71"/>
-      <c r="T21" s="71"/>
+      <c r="T21" s="71">
+        <v>856</v>
+      </c>
       <c r="U21" s="71"/>
       <c r="V21" s="71"/>
       <c r="W21" s="71"/>
-      <c r="X21" s="64"/>
-      <c r="Y21" s="103"/>
-    </row>
-    <row r="22" spans="1:27" ht="15.75">
+      <c r="X21" s="105"/>
+      <c r="Y21" s="114">
+        <v>36898.639999999999</v>
+      </c>
+      <c r="Z21" s="107"/>
+    </row>
+    <row r="22" spans="1:28" ht="15.75">
       <c r="A22" s="66">
         <v>21</v>
       </c>
       <c r="B22" s="67" t="s">
-        <v>6</v>
-      </c>
-      <c r="C22" s="72"/>
-      <c r="D22" s="72"/>
+        <v>8</v>
+      </c>
+      <c r="C22" s="72">
+        <f>80</f>
+        <v>80</v>
+      </c>
+      <c r="D22" s="72">
+        <v>883</v>
+      </c>
       <c r="E22" s="72"/>
       <c r="F22" s="72"/>
       <c r="G22" s="72"/>
@@ -14596,30 +18441,41 @@
       <c r="L22" s="72"/>
       <c r="M22" s="72"/>
       <c r="N22" s="72"/>
-      <c r="O22" s="72"/>
+      <c r="O22" s="72">
+        <v>334</v>
+      </c>
       <c r="P22" s="72"/>
       <c r="Q22" s="72"/>
       <c r="R22" s="72"/>
       <c r="S22" s="72"/>
-      <c r="T22" s="72"/>
+      <c r="T22" s="72">
+        <v>79</v>
+      </c>
       <c r="U22" s="72"/>
       <c r="V22" s="72"/>
-      <c r="W22" s="72"/>
+      <c r="W22" s="104">
+        <v>23662.84</v>
+      </c>
       <c r="X22" s="106"/>
-      <c r="Y22" s="104"/>
-      <c r="AA22" s="44"/>
-    </row>
-    <row r="23" spans="1:27" ht="15.75">
+      <c r="Y22" s="111"/>
+      <c r="Z22" s="108"/>
+      <c r="AB22" s="44"/>
+    </row>
+    <row r="23" spans="1:28" ht="15.75">
       <c r="A23" s="62">
         <v>22</v>
       </c>
       <c r="B23" s="63" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C23" s="71"/>
-      <c r="D23" s="71"/>
+      <c r="D23" s="71">
+        <v>162</v>
+      </c>
       <c r="E23" s="71"/>
-      <c r="F23" s="71"/>
+      <c r="F23" s="71">
+        <v>690</v>
+      </c>
       <c r="G23" s="71"/>
       <c r="H23" s="71"/>
       <c r="I23" s="71"/>
@@ -14628,29 +18484,38 @@
       <c r="L23" s="71"/>
       <c r="M23" s="71"/>
       <c r="N23" s="71"/>
-      <c r="O23" s="71"/>
+      <c r="O23" s="71">
+        <v>325</v>
+      </c>
       <c r="P23" s="71"/>
       <c r="Q23" s="71"/>
       <c r="R23" s="71"/>
-      <c r="S23" s="71"/>
+      <c r="S23" s="71">
+        <v>843</v>
+      </c>
       <c r="T23" s="71"/>
       <c r="U23" s="71"/>
       <c r="V23" s="71"/>
       <c r="W23" s="71"/>
-      <c r="X23" s="107"/>
-      <c r="Y23" s="104"/>
-    </row>
-    <row r="24" spans="1:27" ht="15.75">
+      <c r="X23" s="105"/>
+      <c r="Y23" s="111"/>
+      <c r="Z23" s="108"/>
+    </row>
+    <row r="24" spans="1:28" ht="15.75">
       <c r="A24" s="66">
         <v>23</v>
       </c>
       <c r="B24" s="67" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C24" s="72"/>
-      <c r="D24" s="72"/>
+      <c r="D24" s="72">
+        <v>192</v>
+      </c>
       <c r="E24" s="72"/>
-      <c r="F24" s="72"/>
+      <c r="F24" s="72">
+        <v>1960</v>
+      </c>
       <c r="G24" s="72"/>
       <c r="H24" s="72"/>
       <c r="I24" s="72"/>
@@ -14659,31 +18524,42 @@
       <c r="L24" s="72"/>
       <c r="M24" s="72"/>
       <c r="N24" s="72"/>
-      <c r="O24" s="72"/>
+      <c r="O24" s="72">
+        <f>537+185</f>
+        <v>722</v>
+      </c>
       <c r="P24" s="72"/>
-      <c r="Q24" s="72"/>
+      <c r="Q24" s="72">
+        <v>1000</v>
+      </c>
       <c r="R24" s="72"/>
       <c r="S24" s="72"/>
       <c r="T24" s="72"/>
       <c r="U24" s="72"/>
       <c r="V24" s="72"/>
       <c r="W24" s="72"/>
-      <c r="X24" s="107"/>
-      <c r="Y24" s="104"/>
-    </row>
-    <row r="25" spans="1:27" ht="15.75">
+      <c r="X24" s="106"/>
+      <c r="Y24" s="111"/>
+      <c r="Z24" s="108"/>
+    </row>
+    <row r="25" spans="1:28" ht="15.75">
       <c r="A25" s="62">
         <v>24</v>
       </c>
       <c r="B25" s="63" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C25" s="71"/>
-      <c r="D25" s="71"/>
+      <c r="D25" s="71">
+        <f>1377+2099.31-149</f>
+        <v>3327.31</v>
+      </c>
       <c r="E25" s="71"/>
       <c r="F25" s="71"/>
       <c r="G25" s="71"/>
-      <c r="H25" s="71"/>
+      <c r="H25" s="71">
+        <v>2414</v>
+      </c>
       <c r="I25" s="71"/>
       <c r="J25" s="71"/>
       <c r="K25" s="71"/>
@@ -14691,26 +18567,35 @@
       <c r="M25" s="71"/>
       <c r="N25" s="71"/>
       <c r="O25" s="71"/>
-      <c r="P25" s="71"/>
+      <c r="P25" s="71">
+        <v>152</v>
+      </c>
       <c r="Q25" s="71"/>
       <c r="R25" s="71"/>
       <c r="S25" s="71"/>
       <c r="T25" s="71"/>
       <c r="U25" s="71"/>
-      <c r="V25" s="71"/>
+      <c r="V25" s="71">
+        <v>2000</v>
+      </c>
       <c r="W25" s="71"/>
-      <c r="X25" s="107"/>
-      <c r="Y25" s="104"/>
-    </row>
-    <row r="26" spans="1:27" ht="15.75">
+      <c r="X25" s="105"/>
+      <c r="Y25" s="111"/>
+      <c r="Z25" s="108"/>
+    </row>
+    <row r="26" spans="1:28" ht="15.75">
       <c r="A26" s="66">
         <v>25</v>
       </c>
       <c r="B26" s="67" t="s">
-        <v>3</v>
-      </c>
-      <c r="C26" s="72"/>
-      <c r="D26" s="72"/>
+        <v>5</v>
+      </c>
+      <c r="C26" s="72">
+        <v>3084</v>
+      </c>
+      <c r="D26" s="72">
+        <v>245</v>
+      </c>
       <c r="E26" s="72"/>
       <c r="F26" s="72"/>
       <c r="G26" s="72"/>
@@ -14730,19 +18615,26 @@
       <c r="U26" s="72"/>
       <c r="V26" s="72"/>
       <c r="W26" s="72"/>
-      <c r="X26" s="107"/>
-      <c r="Y26" s="104"/>
-    </row>
-    <row r="27" spans="1:27" ht="15.75">
+      <c r="X26" s="106"/>
+      <c r="Y26" s="111"/>
+      <c r="Z26" s="108"/>
+    </row>
+    <row r="27" spans="1:28" ht="15.75">
       <c r="A27" s="62">
         <v>26</v>
       </c>
       <c r="B27" s="63" t="s">
-        <v>4</v>
-      </c>
-      <c r="C27" s="71"/>
-      <c r="D27" s="71"/>
-      <c r="E27" s="71"/>
+        <v>6</v>
+      </c>
+      <c r="C27" s="71">
+        <v>185</v>
+      </c>
+      <c r="D27" s="71">
+        <v>1332</v>
+      </c>
+      <c r="E27" s="71">
+        <v>3180</v>
+      </c>
       <c r="F27" s="71"/>
       <c r="G27" s="71"/>
       <c r="H27" s="71"/>
@@ -14759,17 +18651,22 @@
       <c r="S27" s="71"/>
       <c r="T27" s="71"/>
       <c r="U27" s="71"/>
-      <c r="V27" s="71"/>
+      <c r="V27" s="71">
+        <v>2800</v>
+      </c>
       <c r="W27" s="71"/>
-      <c r="X27" s="107"/>
-      <c r="Y27" s="104"/>
-    </row>
-    <row r="28" spans="1:27" ht="15.75">
+      <c r="X27" s="105"/>
+      <c r="Y27" s="114">
+        <v>20000</v>
+      </c>
+      <c r="Z27" s="108"/>
+    </row>
+    <row r="28" spans="1:28" ht="15.75">
       <c r="A28" s="66">
         <v>27</v>
       </c>
       <c r="B28" s="67" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C28" s="72"/>
       <c r="D28" s="72"/>
@@ -14784,23 +18681,31 @@
       <c r="M28" s="72"/>
       <c r="N28" s="72"/>
       <c r="O28" s="72"/>
-      <c r="P28" s="72"/>
+      <c r="P28" s="72">
+        <v>338</v>
+      </c>
       <c r="Q28" s="72"/>
       <c r="R28" s="72"/>
-      <c r="S28" s="72"/>
-      <c r="T28" s="72"/>
+      <c r="S28" s="72">
+        <v>249</v>
+      </c>
+      <c r="T28" s="72">
+        <f>3790+3780+3004</f>
+        <v>10574</v>
+      </c>
       <c r="U28" s="72"/>
       <c r="V28" s="72"/>
       <c r="W28" s="72"/>
-      <c r="X28" s="107"/>
-      <c r="Y28" s="104"/>
-    </row>
-    <row r="29" spans="1:27" ht="15.75">
+      <c r="X28" s="106"/>
+      <c r="Y28" s="111"/>
+      <c r="Z28" s="108"/>
+    </row>
+    <row r="29" spans="1:28" ht="15.75">
       <c r="A29" s="62">
         <v>28</v>
       </c>
       <c r="B29" s="63" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C29" s="71"/>
       <c r="D29" s="71"/>
@@ -14815,23 +18720,28 @@
       <c r="M29" s="71"/>
       <c r="N29" s="71"/>
       <c r="O29" s="71"/>
-      <c r="P29" s="71"/>
-      <c r="Q29" s="71"/>
+      <c r="P29" s="71">
+        <v>307</v>
+      </c>
+      <c r="Q29" s="71">
+        <v>1223</v>
+      </c>
       <c r="R29" s="71"/>
       <c r="S29" s="71"/>
       <c r="T29" s="71"/>
       <c r="U29" s="71"/>
       <c r="V29" s="71"/>
       <c r="W29" s="71"/>
-      <c r="X29" s="107"/>
-      <c r="Y29" s="104"/>
-    </row>
-    <row r="30" spans="1:27" ht="15.75">
+      <c r="X29" s="105"/>
+      <c r="Y29" s="111"/>
+      <c r="Z29" s="108"/>
+    </row>
+    <row r="30" spans="1:28" ht="15.75">
       <c r="A30" s="66">
         <v>29</v>
       </c>
       <c r="B30" s="67" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C30" s="72"/>
       <c r="D30" s="72"/>
@@ -14847,22 +18757,25 @@
       <c r="N30" s="72"/>
       <c r="O30" s="72"/>
       <c r="P30" s="72"/>
-      <c r="Q30" s="72"/>
+      <c r="Q30" s="72">
+        <v>400</v>
+      </c>
       <c r="R30" s="72"/>
       <c r="S30" s="72"/>
       <c r="T30" s="72"/>
       <c r="U30" s="72"/>
       <c r="V30" s="72"/>
       <c r="W30" s="72"/>
-      <c r="X30" s="107"/>
-      <c r="Y30" s="104"/>
-    </row>
-    <row r="31" spans="1:27" ht="15.75">
+      <c r="X30" s="106"/>
+      <c r="Y30" s="111"/>
+      <c r="Z30" s="108"/>
+    </row>
+    <row r="31" spans="1:28" ht="15.75">
       <c r="A31" s="62">
         <v>30</v>
       </c>
       <c r="B31" s="63" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C31" s="71"/>
       <c r="D31" s="71"/>
@@ -14885,15 +18798,16 @@
       <c r="U31" s="71"/>
       <c r="V31" s="71"/>
       <c r="W31" s="71"/>
-      <c r="X31" s="107"/>
-      <c r="Y31" s="104"/>
-    </row>
-    <row r="32" spans="1:27" ht="15.75">
+      <c r="X31" s="105"/>
+      <c r="Y31" s="111"/>
+      <c r="Z31" s="108"/>
+    </row>
+    <row r="32" spans="1:28" ht="15.75">
       <c r="A32" s="66">
         <v>31</v>
       </c>
       <c r="B32" s="67" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C32" s="72"/>
       <c r="D32" s="72"/>
@@ -14916,15 +18830,16 @@
       <c r="U32" s="72"/>
       <c r="V32" s="72"/>
       <c r="W32" s="72"/>
-      <c r="X32" s="107"/>
-      <c r="Y32" s="104"/>
-    </row>
-    <row r="33" spans="1:25" ht="15.75">
+      <c r="X32" s="106"/>
+      <c r="Y32" s="111"/>
+      <c r="Z32" s="108"/>
+    </row>
+    <row r="33" spans="1:26" ht="15.75">
       <c r="A33" s="62">
         <v>1</v>
       </c>
       <c r="B33" s="63" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C33" s="71"/>
       <c r="D33" s="71"/>
@@ -14947,15 +18862,16 @@
       <c r="U33" s="71"/>
       <c r="V33" s="71"/>
       <c r="W33" s="71"/>
-      <c r="X33" s="107"/>
-      <c r="Y33" s="104"/>
-    </row>
-    <row r="34" spans="1:25" ht="15.75">
+      <c r="X33" s="105"/>
+      <c r="Y33" s="111"/>
+      <c r="Z33" s="108"/>
+    </row>
+    <row r="34" spans="1:26" ht="15.75">
       <c r="A34" s="66">
         <v>2</v>
       </c>
       <c r="B34" s="67" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C34" s="72"/>
       <c r="D34" s="72"/>
@@ -14978,15 +18894,16 @@
       <c r="U34" s="72"/>
       <c r="V34" s="72"/>
       <c r="W34" s="72"/>
-      <c r="X34" s="107"/>
-      <c r="Y34" s="104"/>
-    </row>
-    <row r="35" spans="1:25" ht="15.75">
+      <c r="X34" s="106"/>
+      <c r="Y34" s="111"/>
+      <c r="Z34" s="108"/>
+    </row>
+    <row r="35" spans="1:26" ht="15.75">
       <c r="A35" s="62">
         <v>3</v>
       </c>
       <c r="B35" s="63" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C35" s="71"/>
       <c r="D35" s="71"/>
@@ -15009,15 +18926,16 @@
       <c r="U35" s="71"/>
       <c r="V35" s="71"/>
       <c r="W35" s="71"/>
-      <c r="X35" s="107"/>
-      <c r="Y35" s="104"/>
-    </row>
-    <row r="36" spans="1:25" ht="15.75">
+      <c r="X35" s="105"/>
+      <c r="Y35" s="111"/>
+      <c r="Z35" s="108"/>
+    </row>
+    <row r="36" spans="1:26" ht="15.75">
       <c r="A36" s="66">
         <v>4</v>
       </c>
       <c r="B36" s="67" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C36" s="72"/>
       <c r="D36" s="72"/>
@@ -15040,29 +18958,30 @@
       <c r="U36" s="72"/>
       <c r="V36" s="72"/>
       <c r="W36" s="72"/>
-      <c r="X36" s="108"/>
-      <c r="Y36" s="105"/>
-    </row>
-    <row r="37" spans="1:25">
+      <c r="X36" s="106"/>
+      <c r="Y36" s="111"/>
+      <c r="Z36" s="109"/>
+    </row>
+    <row r="37" spans="1:26">
       <c r="A37" s="99" t="s">
         <v>36</v>
       </c>
       <c r="B37" s="99"/>
       <c r="C37" s="79">
         <f>SUM(C21:C36)</f>
-        <v>0</v>
+        <v>3393</v>
       </c>
       <c r="D37" s="79">
         <f t="shared" ref="D37:V37" si="2">SUM(D21:D36)</f>
-        <v>0</v>
+        <v>6141.3099999999995</v>
       </c>
       <c r="E37" s="79">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3180</v>
       </c>
       <c r="F37" s="79">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>4420</v>
       </c>
       <c r="G37" s="79">
         <f t="shared" si="2"/>
@@ -15070,7 +18989,7 @@
       </c>
       <c r="H37" s="79">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2414</v>
       </c>
       <c r="I37" s="79">
         <f t="shared" si="2"/>
@@ -15098,15 +19017,15 @@
       </c>
       <c r="O37" s="79">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1953</v>
       </c>
       <c r="P37" s="79">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>797</v>
       </c>
       <c r="Q37" s="79">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>6023</v>
       </c>
       <c r="R37" s="79">
         <f t="shared" si="2"/>
@@ -15114,11 +19033,11 @@
       </c>
       <c r="S37" s="79">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1092</v>
       </c>
       <c r="T37" s="79">
         <f>SUM(T21:T36)</f>
-        <v>0</v>
+        <v>11509</v>
       </c>
       <c r="U37" s="79">
         <f t="shared" si="2"/>
@@ -15126,41 +19045,42 @@
       </c>
       <c r="V37" s="79">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="W37" s="82">
-        <f>SUM(W21:W36)</f>
-        <v>0</v>
-      </c>
-      <c r="X37" s="83">
+        <v>4800</v>
+      </c>
+      <c r="W37" s="79"/>
+      <c r="X37" s="82">
         <f>SUM(X21:X36)</f>
         <v>0</v>
       </c>
-      <c r="Y37" s="85">
-        <f>X37-W37</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:25" ht="31.5" customHeight="1">
+      <c r="Y37" s="110">
+        <f>SUM(Y21:Y36)</f>
+        <v>56898.64</v>
+      </c>
+      <c r="Z37" s="84">
+        <f>Y37-X37</f>
+        <v>56898.64</v>
+      </c>
+    </row>
+    <row r="38" spans="1:26" ht="31.5" customHeight="1">
       <c r="A38" s="102" t="s">
         <v>37</v>
       </c>
       <c r="B38" s="102"/>
       <c r="C38" s="78">
         <f>SUM(C20,C37)</f>
-        <v>10242.99</v>
+        <v>13635.99</v>
       </c>
       <c r="D38" s="78">
-        <f t="shared" ref="D38:W38" si="3">SUM(D20,D37)</f>
-        <v>5525.25</v>
+        <f t="shared" ref="D38:X38" si="3">SUM(D20,D37)</f>
+        <v>11666.56</v>
       </c>
       <c r="E38" s="78">
         <f t="shared" si="3"/>
-        <v>2500</v>
+        <v>5680</v>
       </c>
       <c r="F38" s="78">
         <f t="shared" si="3"/>
-        <v>2040</v>
+        <v>6460</v>
       </c>
       <c r="G38" s="78">
         <f t="shared" si="3"/>
@@ -15168,7 +19088,7 @@
       </c>
       <c r="H38" s="78">
         <f t="shared" si="3"/>
-        <v>3760</v>
+        <v>6174</v>
       </c>
       <c r="I38" s="78">
         <f t="shared" si="3"/>
@@ -15196,15 +19116,15 @@
       </c>
       <c r="O38" s="78">
         <f t="shared" si="3"/>
-        <v>2999</v>
+        <v>4952</v>
       </c>
       <c r="P38" s="78">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>797</v>
       </c>
       <c r="Q38" s="78">
         <f t="shared" si="3"/>
-        <v>21145.98</v>
+        <v>27168.98</v>
       </c>
       <c r="R38" s="78">
         <f t="shared" si="3"/>
@@ -15212,11 +19132,11 @@
       </c>
       <c r="S38" s="78">
         <f>SUM(S20,S37)</f>
-        <v>5272.63</v>
+        <v>6364.63</v>
       </c>
       <c r="T38" s="78">
         <f t="shared" si="3"/>
-        <v>2288</v>
+        <v>13797</v>
       </c>
       <c r="U38" s="78">
         <f t="shared" si="3"/>
@@ -15224,22 +19144,23 @@
       </c>
       <c r="V38" s="78">
         <f t="shared" si="3"/>
-        <v>950</v>
-      </c>
-      <c r="W38" s="86">
+        <v>5750</v>
+      </c>
+      <c r="W38" s="78"/>
+      <c r="X38" s="85">
         <f t="shared" si="3"/>
         <v>62194.829999999987</v>
       </c>
-      <c r="X38" s="86">
-        <f>SUM(X20,X37)</f>
-        <v>98659.824999999983</v>
-      </c>
-      <c r="Y38" s="87">
+      <c r="Y38" s="85">
         <f>SUM(Y20,Y37)</f>
-        <v>36464.994999999995</v>
-      </c>
-    </row>
-    <row r="42" spans="1:25">
+        <v>170558.46499999997</v>
+      </c>
+      <c r="Z38" s="86">
+        <f>SUM(Z20,Z37)</f>
+        <v>108363.63499999999</v>
+      </c>
+    </row>
+    <row r="42" spans="1:26">
       <c r="B42" s="6"/>
       <c r="C42" s="6"/>
       <c r="D42" s="6"/>
@@ -15252,23 +19173,20 @@
       <c r="K42" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="A1:Y1"/>
+  <mergeCells count="6">
+    <mergeCell ref="A1:Z1"/>
+    <mergeCell ref="Z3:Z19"/>
     <mergeCell ref="A20:B20"/>
+    <mergeCell ref="Z21:Z36"/>
     <mergeCell ref="A37:B37"/>
     <mergeCell ref="A38:B38"/>
-    <mergeCell ref="Y3:Y19"/>
-    <mergeCell ref="Y21:Y36"/>
-    <mergeCell ref="X22:X36"/>
-    <mergeCell ref="X4:X13"/>
-    <mergeCell ref="X15:X19"/>
   </mergeCells>
-  <conditionalFormatting sqref="Y20:Y21 Y37:Y38">
-    <cfRule type="expression" dxfId="1" priority="1">
-      <formula>Y20&lt;0</formula>
+  <conditionalFormatting sqref="Z20:Z21 Z37:Z38">
+    <cfRule type="expression" dxfId="3" priority="1">
+      <formula>Z20&lt;0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="2">
-      <formula>Y20&gt;0</formula>
+    <cfRule type="expression" dxfId="2" priority="2">
+      <formula>Z20&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Другое/2026/Доходы-Расходы_copy.xlsx
+++ b/Другое/2026/Доходы-Расходы_copy.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="6" rupBuild="4507"/>
   <workbookPr filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="6"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="Сводная" sheetId="5" r:id="rId1"/>
@@ -4705,1005 +4705,8 @@
 </comments>
 </file>
 
-<file path=xl/comments7.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Автор</author>
-  </authors>
-  <commentList>
-    <comment ref="Q3" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="204"/>
-          </rPr>
-          <t>Автор:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="204"/>
-          </rPr>
-          <t xml:space="preserve">
-Компенсация за ВПЧ
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="S3" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="204"/>
-          </rPr>
-          <t>Автор:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="204"/>
-          </rPr>
-          <t xml:space="preserve">
-Яндекс Плюс</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="H4" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="204"/>
-          </rPr>
-          <t>Автор:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="204"/>
-          </rPr>
-          <t xml:space="preserve">
-Завтрак в 1/2</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="S5" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="204"/>
-          </rPr>
-          <t>Автор:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="204"/>
-          </rPr>
-          <t xml:space="preserve">
-ВК музыка
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="V6" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="204"/>
-          </rPr>
-          <t>Автор:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="204"/>
-          </rPr>
-          <t xml:space="preserve">
-Покупка ЧТИВО</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F7" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="204"/>
-          </rPr>
-          <t>Автор:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="204"/>
-          </rPr>
-          <t xml:space="preserve">
-Промясо</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="Q8" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="204"/>
-          </rPr>
-          <t>Автор:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="204"/>
-          </rPr>
-          <t xml:space="preserve">
-Поке + бабл ти
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="S8" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="204"/>
-          </rPr>
-          <t>Автор:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="204"/>
-          </rPr>
-          <t xml:space="preserve">
-Долями за орнамент
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="S9" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="204"/>
-          </rPr>
-          <t>Автор:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="204"/>
-          </rPr>
-          <t xml:space="preserve">
-T2</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E10" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="204"/>
-          </rPr>
-          <t>Автор:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="204"/>
-          </rPr>
-          <t xml:space="preserve">
-Макдоналдс</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="S10" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="204"/>
-          </rPr>
-          <t>Автор:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="204"/>
-          </rPr>
-          <t xml:space="preserve">
-ВПН</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="Q12" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="204"/>
-          </rPr>
-          <t>Автор:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="204"/>
-          </rPr>
-          <t xml:space="preserve">
-Ане на таблетки</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="Q13" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="204"/>
-          </rPr>
-          <t>Автор:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="204"/>
-          </rPr>
-          <t xml:space="preserve">
-Извинительный букет
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="S13" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="204"/>
-          </rPr>
-          <t>Автор:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="204"/>
-          </rPr>
-          <t xml:space="preserve">
-Долями - за журнальчик орнамент</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="Q15" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="204"/>
-          </rPr>
-          <t>Автор:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="204"/>
-          </rPr>
-          <t xml:space="preserve">
-За такси + вино</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="S15" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="204"/>
-          </rPr>
-          <t>Автор:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="204"/>
-          </rPr>
-          <t xml:space="preserve">
-t2</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F16" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="204"/>
-          </rPr>
-          <t>Автор:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="204"/>
-          </rPr>
-          <t xml:space="preserve">
-Обед</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="T16" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="204"/>
-          </rPr>
-          <t>Парикмахерская</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="S17" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t>Автор:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">
-Интернет</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="Y17" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="204"/>
-          </rPr>
-          <t>Автор:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="204"/>
-          </rPr>
-          <t xml:space="preserve">
-Мама скинула на МСК</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="S18" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t>Автор:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">
-Яндекс Плюс</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="U18" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t>Автор:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">
-Подарок Кулику</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E19" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="204"/>
-          </rPr>
-          <t>Автор:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="204"/>
-          </rPr>
-          <t xml:space="preserve">
-Хочука</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="V19" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t>Автор:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">
-Поездка в МСК к Кулику на ДР</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="Y19" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="204"/>
-          </rPr>
-          <t>Батя скинул, когда были в МСК</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F21" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="204"/>
-          </rPr>
-          <t>Автор:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="204"/>
-          </rPr>
-          <t xml:space="preserve">
-БАБЛ ТИ и ПОКЕ</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="T21" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="204"/>
-          </rPr>
-          <t>Автор:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="204"/>
-          </rPr>
-          <t xml:space="preserve">
-КНИГИ
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F23" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="204"/>
-          </rPr>
-          <t>Автор:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="204"/>
-          </rPr>
-          <t xml:space="preserve">
-ПОКЕ</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="S23" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="204"/>
-          </rPr>
-          <t>Автор:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="204"/>
-          </rPr>
-          <t xml:space="preserve">
-Долями за орнамент</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F24" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="204"/>
-          </rPr>
-          <t>Автор:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="204"/>
-          </rPr>
-          <t xml:space="preserve">
-ПОКЕ и БАБЛ ТИ</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="H25" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="204"/>
-          </rPr>
-          <t>Автор:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="204"/>
-          </rPr>
-          <t xml:space="preserve">
-Вкусно и Точка</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="V25" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="204"/>
-          </rPr>
-          <t>Автор:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="204"/>
-          </rPr>
-          <t xml:space="preserve">
-Пейнтбол</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E27" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="204"/>
-          </rPr>
-          <t>Автор:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="204"/>
-          </rPr>
-          <t xml:space="preserve">
-Хочука</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="V27" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="204"/>
-          </rPr>
-          <t>Автор:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="204"/>
-          </rPr>
-          <t xml:space="preserve">
-Книги по строительству</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="Y27" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="204"/>
-          </rPr>
-          <t>Автор:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="204"/>
-          </rPr>
-          <t xml:space="preserve">
-Подарок от мамы на ДР</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="S28" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="204"/>
-          </rPr>
-          <t>Автор:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="204"/>
-          </rPr>
-          <t xml:space="preserve">
-Яндекс Ппюс</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="T28" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="204"/>
-          </rPr>
-          <t>Автор:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="204"/>
-          </rPr>
-          <t xml:space="preserve">
-Простава на работе</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="Q29" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="204"/>
-          </rPr>
-          <t>Автор:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">
-Завтрак для Ани</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="Q30" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t>Автор:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">
-На такси</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="67">
   <si>
     <t>Число</t>
   </si>
@@ -5903,6 +4906,31 @@
   <si>
     <t>Потратил на еду</t>
   </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Доходы - Расходы </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="20"/>
+        <color theme="5" tint="-0.24994659260841701"/>
+        <rFont val="Bernard MT Condensed"/>
+        <family val="1"/>
+      </rPr>
+      <t>Август</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="20"/>
+        <color theme="1" tint="4.9989318521683403E-2"/>
+        <rFont val="Bernard MT Condensed"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> 2026</t>
+    </r>
+  </si>
 </sst>
 </file>
 
@@ -5911,7 +4939,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;₽&quot;"/>
   </numFmts>
-  <fonts count="38">
+  <fonts count="41">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -6193,6 +5221,27 @@
       <family val="2"/>
       <charset val="204"/>
     </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color theme="1" tint="4.9989318521683403E-2"/>
+      <name val="Bernard MT Condensed"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color theme="5" tint="-0.24994659260841701"/>
+      <name val="Bernard MT Condensed"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1" tint="4.9989318521683403E-2"/>
+      <name val="Franklin Gothic Demi"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
   </fonts>
   <fills count="32">
     <fill>
@@ -6382,7 +5431,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="21">
+  <borders count="23">
     <border>
       <left/>
       <right/>
@@ -6648,11 +5697,35 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="1" tint="0.34998626667073579"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color theme="1" tint="0.34998626667073579"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="141">
+  <cellXfs count="147">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -6842,9 +5915,6 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="27" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="164" fontId="27" fillId="19" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -6863,6 +5933,65 @@
     <xf numFmtId="164" fontId="23" fillId="20" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="23" fillId="7" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="17" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="19" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="27" fillId="19" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="26" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="6" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="29" fillId="6" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="14" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="28" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="23" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="29" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="34" fillId="24" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="34" fillId="23" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="34" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="29" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="29" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="23" fillId="22" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="34" fillId="11" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="34" fillId="11" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="30" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="36" fillId="31" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -6902,23 +6031,20 @@
     <xf numFmtId="0" fontId="25" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="36" fillId="31" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="17" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="28" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="23" fillId="22" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="23" fillId="7" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="23" fillId="17" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="164" fontId="23" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="23" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -6929,77 +6055,42 @@
     <xf numFmtId="164" fontId="23" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="27" fillId="19" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="23" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="23" fillId="23" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="27" fillId="19" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="23" fillId="21" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="26" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="38" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="7" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="7" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="26" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="27" fillId="6" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="29" fillId="6" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="14" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="23" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="23" fillId="28" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="23" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="40" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="21" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="23" fillId="29" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="34" fillId="24" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="34" fillId="23" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="34" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="29" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="23" fillId="29" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="23" fillId="22" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="34" fillId="11" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="34" fillId="11" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="23" fillId="30" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="37" fillId="17" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="31" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="36" fillId="31" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="23" fillId="16" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="23" fillId="16" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="23" fillId="16" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -7347,7 +6438,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -7594,32 +6685,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:46" ht="60.75" customHeight="1">
-      <c r="A1" s="88" t="s">
+      <c r="A1" s="112" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="88"/>
-      <c r="C1" s="88"/>
-      <c r="D1" s="88"/>
-      <c r="E1" s="88"/>
-      <c r="F1" s="88"/>
-      <c r="G1" s="88"/>
-      <c r="H1" s="88"/>
-      <c r="I1" s="88"/>
-      <c r="J1" s="88"/>
-      <c r="K1" s="88"/>
-      <c r="L1" s="88"/>
-      <c r="M1" s="88"/>
-      <c r="N1" s="88"/>
-      <c r="O1" s="88"/>
-      <c r="P1" s="88"/>
-      <c r="Q1" s="88"/>
-      <c r="R1" s="88"/>
-      <c r="S1" s="88"/>
-      <c r="T1" s="88"/>
-      <c r="U1" s="88"/>
-      <c r="V1" s="88"/>
-      <c r="W1" s="88"/>
-      <c r="X1" s="88"/>
+      <c r="B1" s="112"/>
+      <c r="C1" s="112"/>
+      <c r="D1" s="112"/>
+      <c r="E1" s="112"/>
+      <c r="F1" s="112"/>
+      <c r="G1" s="112"/>
+      <c r="H1" s="112"/>
+      <c r="I1" s="112"/>
+      <c r="J1" s="112"/>
+      <c r="K1" s="112"/>
+      <c r="L1" s="112"/>
+      <c r="M1" s="112"/>
+      <c r="N1" s="112"/>
+      <c r="O1" s="112"/>
+      <c r="P1" s="112"/>
+      <c r="Q1" s="112"/>
+      <c r="R1" s="112"/>
+      <c r="S1" s="112"/>
+      <c r="T1" s="112"/>
+      <c r="U1" s="112"/>
+      <c r="V1" s="112"/>
+      <c r="W1" s="112"/>
+      <c r="X1" s="112"/>
     </row>
     <row r="2" spans="1:46" ht="45" customHeight="1">
       <c r="A2" s="3" t="s">
@@ -8818,10 +7909,10 @@
       </c>
     </row>
     <row r="31" spans="1:24">
-      <c r="A31" s="89" t="s">
+      <c r="A31" s="113" t="s">
         <v>20</v>
       </c>
-      <c r="B31" s="89"/>
+      <c r="B31" s="113"/>
       <c r="C31" s="13">
         <f>SUM(C3:C30)</f>
         <v>19992.27</v>
@@ -8944,32 +8035,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:46" ht="60.75" customHeight="1">
-      <c r="A1" s="91" t="s">
+      <c r="A1" s="115" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="91"/>
-      <c r="C1" s="91"/>
-      <c r="D1" s="91"/>
-      <c r="E1" s="91"/>
-      <c r="F1" s="91"/>
-      <c r="G1" s="91"/>
-      <c r="H1" s="91"/>
-      <c r="I1" s="91"/>
-      <c r="J1" s="91"/>
-      <c r="K1" s="91"/>
-      <c r="L1" s="91"/>
-      <c r="M1" s="91"/>
-      <c r="N1" s="91"/>
-      <c r="O1" s="91"/>
-      <c r="P1" s="91"/>
-      <c r="Q1" s="91"/>
-      <c r="R1" s="91"/>
-      <c r="S1" s="91"/>
-      <c r="T1" s="91"/>
-      <c r="U1" s="91"/>
-      <c r="V1" s="91"/>
-      <c r="W1" s="91"/>
-      <c r="X1" s="91"/>
+      <c r="B1" s="115"/>
+      <c r="C1" s="115"/>
+      <c r="D1" s="115"/>
+      <c r="E1" s="115"/>
+      <c r="F1" s="115"/>
+      <c r="G1" s="115"/>
+      <c r="H1" s="115"/>
+      <c r="I1" s="115"/>
+      <c r="J1" s="115"/>
+      <c r="K1" s="115"/>
+      <c r="L1" s="115"/>
+      <c r="M1" s="115"/>
+      <c r="N1" s="115"/>
+      <c r="O1" s="115"/>
+      <c r="P1" s="115"/>
+      <c r="Q1" s="115"/>
+      <c r="R1" s="115"/>
+      <c r="S1" s="115"/>
+      <c r="T1" s="115"/>
+      <c r="U1" s="115"/>
+      <c r="V1" s="115"/>
+      <c r="W1" s="115"/>
+      <c r="X1" s="115"/>
     </row>
     <row r="2" spans="1:46" ht="45" customHeight="1">
       <c r="A2" s="30" t="s">
@@ -10180,10 +9271,10 @@
       <c r="X31" s="31"/>
     </row>
     <row r="32" spans="1:24">
-      <c r="A32" s="90" t="s">
+      <c r="A32" s="114" t="s">
         <v>20</v>
       </c>
-      <c r="B32" s="90"/>
+      <c r="B32" s="114"/>
       <c r="C32" s="28">
         <f>SUM(C3:C31)</f>
         <v>16843.349999999999</v>
@@ -10306,33 +9397,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:47" ht="60.75" customHeight="1">
-      <c r="A1" s="91" t="s">
+      <c r="A1" s="115" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="91"/>
-      <c r="C1" s="91"/>
-      <c r="D1" s="91"/>
-      <c r="E1" s="91"/>
-      <c r="F1" s="91"/>
-      <c r="G1" s="91"/>
-      <c r="H1" s="91"/>
-      <c r="I1" s="91"/>
-      <c r="J1" s="91"/>
-      <c r="K1" s="91"/>
-      <c r="L1" s="91"/>
-      <c r="M1" s="91"/>
-      <c r="N1" s="91"/>
-      <c r="O1" s="91"/>
-      <c r="P1" s="91"/>
-      <c r="Q1" s="91"/>
-      <c r="R1" s="91"/>
-      <c r="S1" s="91"/>
-      <c r="T1" s="91"/>
-      <c r="U1" s="91"/>
-      <c r="V1" s="91"/>
-      <c r="W1" s="91"/>
-      <c r="X1" s="91"/>
-      <c r="Y1" s="91"/>
+      <c r="B1" s="115"/>
+      <c r="C1" s="115"/>
+      <c r="D1" s="115"/>
+      <c r="E1" s="115"/>
+      <c r="F1" s="115"/>
+      <c r="G1" s="115"/>
+      <c r="H1" s="115"/>
+      <c r="I1" s="115"/>
+      <c r="J1" s="115"/>
+      <c r="K1" s="115"/>
+      <c r="L1" s="115"/>
+      <c r="M1" s="115"/>
+      <c r="N1" s="115"/>
+      <c r="O1" s="115"/>
+      <c r="P1" s="115"/>
+      <c r="Q1" s="115"/>
+      <c r="R1" s="115"/>
+      <c r="S1" s="115"/>
+      <c r="T1" s="115"/>
+      <c r="U1" s="115"/>
+      <c r="V1" s="115"/>
+      <c r="W1" s="115"/>
+      <c r="X1" s="115"/>
+      <c r="Y1" s="115"/>
     </row>
     <row r="2" spans="1:47" ht="45" customHeight="1">
       <c r="A2" s="30" t="s">
@@ -11150,10 +10241,10 @@
       <c r="Y19" s="43"/>
     </row>
     <row r="20" spans="1:27">
-      <c r="A20" s="93" t="s">
+      <c r="A20" s="117" t="s">
         <v>35</v>
       </c>
-      <c r="B20" s="94"/>
+      <c r="B20" s="118"/>
       <c r="C20" s="45">
         <f>SUM(C3:C19)</f>
         <v>12278.83</v>
@@ -11873,10 +10964,10 @@
       <c r="Y35" s="43"/>
     </row>
     <row r="36" spans="1:25">
-      <c r="A36" s="93" t="s">
+      <c r="A36" s="117" t="s">
         <v>36</v>
       </c>
-      <c r="B36" s="94"/>
+      <c r="B36" s="118"/>
       <c r="C36" s="45">
         <f>SUM(C21:C35)</f>
         <v>11057.89</v>
@@ -11971,10 +11062,10 @@
       </c>
     </row>
     <row r="37" spans="1:25" ht="31.5" customHeight="1">
-      <c r="A37" s="92" t="s">
+      <c r="A37" s="116" t="s">
         <v>37</v>
       </c>
-      <c r="B37" s="92"/>
+      <c r="B37" s="116"/>
       <c r="C37" s="48">
         <f>SUM(C20,C36)</f>
         <v>23336.720000000001</v>
@@ -12104,33 +11195,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:47" ht="60.75" customHeight="1">
-      <c r="A1" s="95" t="s">
+      <c r="A1" s="119" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="95"/>
-      <c r="C1" s="95"/>
-      <c r="D1" s="95"/>
-      <c r="E1" s="95"/>
-      <c r="F1" s="95"/>
-      <c r="G1" s="95"/>
-      <c r="H1" s="95"/>
-      <c r="I1" s="95"/>
-      <c r="J1" s="95"/>
-      <c r="K1" s="95"/>
-      <c r="L1" s="95"/>
-      <c r="M1" s="95"/>
-      <c r="N1" s="95"/>
-      <c r="O1" s="95"/>
-      <c r="P1" s="95"/>
-      <c r="Q1" s="95"/>
-      <c r="R1" s="95"/>
-      <c r="S1" s="95"/>
-      <c r="T1" s="95"/>
-      <c r="U1" s="95"/>
-      <c r="V1" s="95"/>
-      <c r="W1" s="95"/>
-      <c r="X1" s="95"/>
-      <c r="Y1" s="95"/>
+      <c r="B1" s="119"/>
+      <c r="C1" s="119"/>
+      <c r="D1" s="119"/>
+      <c r="E1" s="119"/>
+      <c r="F1" s="119"/>
+      <c r="G1" s="119"/>
+      <c r="H1" s="119"/>
+      <c r="I1" s="119"/>
+      <c r="J1" s="119"/>
+      <c r="K1" s="119"/>
+      <c r="L1" s="119"/>
+      <c r="M1" s="119"/>
+      <c r="N1" s="119"/>
+      <c r="O1" s="119"/>
+      <c r="P1" s="119"/>
+      <c r="Q1" s="119"/>
+      <c r="R1" s="119"/>
+      <c r="S1" s="119"/>
+      <c r="T1" s="119"/>
+      <c r="U1" s="119"/>
+      <c r="V1" s="119"/>
+      <c r="W1" s="119"/>
+      <c r="X1" s="119"/>
+      <c r="Y1" s="119"/>
     </row>
     <row r="2" spans="1:47" ht="45" customHeight="1">
       <c r="A2" s="59" t="s">
@@ -12840,10 +11931,10 @@
       <c r="Y17" s="65"/>
     </row>
     <row r="18" spans="1:27">
-      <c r="A18" s="96" t="s">
+      <c r="A18" s="120" t="s">
         <v>35</v>
       </c>
-      <c r="B18" s="96"/>
+      <c r="B18" s="120"/>
       <c r="C18" s="73">
         <f t="shared" ref="C18:X18" si="1">SUM(C3:C17)</f>
         <v>8428.35</v>
@@ -13596,10 +12687,10 @@
       <c r="Y34" s="69"/>
     </row>
     <row r="35" spans="1:25">
-      <c r="A35" s="96" t="s">
+      <c r="A35" s="120" t="s">
         <v>36</v>
       </c>
-      <c r="B35" s="96"/>
+      <c r="B35" s="120"/>
       <c r="C35" s="73">
         <f>SUM(C19:C34)</f>
         <v>10739.46</v>
@@ -13694,10 +12785,10 @@
       </c>
     </row>
     <row r="36" spans="1:25" ht="31.5" customHeight="1">
-      <c r="A36" s="97" t="s">
+      <c r="A36" s="121" t="s">
         <v>37</v>
       </c>
-      <c r="B36" s="97"/>
+      <c r="B36" s="121"/>
       <c r="C36" s="70">
         <f>SUM(C18,C35)</f>
         <v>19167.809999999998</v>
@@ -13835,33 +12926,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:47" ht="60.75" customHeight="1">
-      <c r="A1" s="98" t="s">
+      <c r="A1" s="122" t="s">
         <v>58</v>
       </c>
-      <c r="B1" s="98"/>
-      <c r="C1" s="98"/>
-      <c r="D1" s="98"/>
-      <c r="E1" s="98"/>
-      <c r="F1" s="98"/>
-      <c r="G1" s="98"/>
-      <c r="H1" s="98"/>
-      <c r="I1" s="98"/>
-      <c r="J1" s="98"/>
-      <c r="K1" s="98"/>
-      <c r="L1" s="98"/>
-      <c r="M1" s="98"/>
-      <c r="N1" s="98"/>
-      <c r="O1" s="98"/>
-      <c r="P1" s="98"/>
-      <c r="Q1" s="98"/>
-      <c r="R1" s="98"/>
-      <c r="S1" s="98"/>
-      <c r="T1" s="98"/>
-      <c r="U1" s="98"/>
-      <c r="V1" s="98"/>
-      <c r="W1" s="98"/>
-      <c r="X1" s="98"/>
-      <c r="Y1" s="98"/>
+      <c r="B1" s="122"/>
+      <c r="C1" s="122"/>
+      <c r="D1" s="122"/>
+      <c r="E1" s="122"/>
+      <c r="F1" s="122"/>
+      <c r="G1" s="122"/>
+      <c r="H1" s="122"/>
+      <c r="I1" s="122"/>
+      <c r="J1" s="122"/>
+      <c r="K1" s="122"/>
+      <c r="L1" s="122"/>
+      <c r="M1" s="122"/>
+      <c r="N1" s="122"/>
+      <c r="O1" s="122"/>
+      <c r="P1" s="122"/>
+      <c r="Q1" s="122"/>
+      <c r="R1" s="122"/>
+      <c r="S1" s="122"/>
+      <c r="T1" s="122"/>
+      <c r="U1" s="122"/>
+      <c r="V1" s="122"/>
+      <c r="W1" s="122"/>
+      <c r="X1" s="122"/>
+      <c r="Y1" s="122"/>
     </row>
     <row r="2" spans="1:47" ht="45" customHeight="1">
       <c r="A2" s="76" t="s">
@@ -14600,10 +13691,10 @@
       <c r="Y17" s="65"/>
     </row>
     <row r="18" spans="1:27">
-      <c r="A18" s="99" t="s">
+      <c r="A18" s="123" t="s">
         <v>35</v>
       </c>
-      <c r="B18" s="99"/>
+      <c r="B18" s="123"/>
       <c r="C18" s="79">
         <f t="shared" ref="C18:X18" si="1">SUM(C3:C17)</f>
         <v>7904</v>
@@ -15251,10 +14342,10 @@
       <c r="Y34" s="69"/>
     </row>
     <row r="35" spans="1:25">
-      <c r="A35" s="99" t="s">
+      <c r="A35" s="123" t="s">
         <v>36</v>
       </c>
-      <c r="B35" s="99"/>
+      <c r="B35" s="123"/>
       <c r="C35" s="79">
         <f>SUM(C19:C34)</f>
         <v>0</v>
@@ -15349,10 +14440,10 @@
       </c>
     </row>
     <row r="36" spans="1:25" ht="31.5" customHeight="1">
-      <c r="A36" s="100" t="s">
+      <c r="A36" s="124" t="s">
         <v>37</v>
       </c>
-      <c r="B36" s="100"/>
+      <c r="B36" s="124"/>
       <c r="C36" s="74">
         <f>SUM(C18,C35)</f>
         <v>7904</v>
@@ -15492,34 +14583,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:48" ht="60.75" customHeight="1">
-      <c r="A1" s="101" t="s">
+      <c r="A1" s="127" t="s">
         <v>59</v>
       </c>
-      <c r="B1" s="101"/>
-      <c r="C1" s="101"/>
-      <c r="D1" s="101"/>
-      <c r="E1" s="101"/>
-      <c r="F1" s="101"/>
-      <c r="G1" s="101"/>
-      <c r="H1" s="101"/>
-      <c r="I1" s="101"/>
-      <c r="J1" s="101"/>
-      <c r="K1" s="101"/>
-      <c r="L1" s="101"/>
-      <c r="M1" s="101"/>
-      <c r="N1" s="101"/>
-      <c r="O1" s="101"/>
-      <c r="P1" s="101"/>
-      <c r="Q1" s="101"/>
-      <c r="R1" s="101"/>
-      <c r="S1" s="101"/>
-      <c r="T1" s="101"/>
-      <c r="U1" s="101"/>
-      <c r="V1" s="101"/>
-      <c r="W1" s="101"/>
-      <c r="X1" s="101"/>
-      <c r="Y1" s="101"/>
-      <c r="Z1" s="101"/>
+      <c r="B1" s="127"/>
+      <c r="C1" s="127"/>
+      <c r="D1" s="127"/>
+      <c r="E1" s="127"/>
+      <c r="F1" s="127"/>
+      <c r="G1" s="127"/>
+      <c r="H1" s="127"/>
+      <c r="I1" s="127"/>
+      <c r="J1" s="127"/>
+      <c r="K1" s="127"/>
+      <c r="L1" s="127"/>
+      <c r="M1" s="127"/>
+      <c r="N1" s="127"/>
+      <c r="O1" s="127"/>
+      <c r="P1" s="127"/>
+      <c r="Q1" s="127"/>
+      <c r="R1" s="127"/>
+      <c r="S1" s="127"/>
+      <c r="T1" s="127"/>
+      <c r="U1" s="127"/>
+      <c r="V1" s="127"/>
+      <c r="W1" s="127"/>
+      <c r="X1" s="127"/>
+      <c r="Y1" s="127"/>
+      <c r="Z1" s="127"/>
     </row>
     <row r="2" spans="1:48" ht="45" customHeight="1">
       <c r="A2" s="76" t="s">
@@ -15528,28 +14619,28 @@
       <c r="B2" s="76" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="117" t="s">
+      <c r="C2" s="91" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="117" t="s">
+      <c r="D2" s="91" t="s">
         <v>29</v>
       </c>
-      <c r="E2" s="117" t="s">
+      <c r="E2" s="91" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="117" t="s">
+      <c r="F2" s="91" t="s">
         <v>33</v>
       </c>
-      <c r="G2" s="117" t="s">
+      <c r="G2" s="91" t="s">
         <v>34</v>
       </c>
-      <c r="H2" s="117" t="s">
+      <c r="H2" s="91" t="s">
         <v>11</v>
       </c>
-      <c r="I2" s="117" t="s">
+      <c r="I2" s="91" t="s">
         <v>30</v>
       </c>
-      <c r="J2" s="117" t="s">
+      <c r="J2" s="91" t="s">
         <v>12</v>
       </c>
       <c r="K2" s="76" t="s">
@@ -15585,19 +14676,19 @@
       <c r="U2" s="76" t="s">
         <v>25</v>
       </c>
-      <c r="V2" s="118" t="s">
+      <c r="V2" s="92" t="s">
         <v>26</v>
       </c>
-      <c r="W2" s="121" t="s">
+      <c r="W2" s="95" t="s">
         <v>22</v>
       </c>
-      <c r="X2" s="125" t="s">
+      <c r="X2" s="98" t="s">
         <v>60</v>
       </c>
-      <c r="Y2" s="126" t="s">
+      <c r="Y2" s="99" t="s">
         <v>19</v>
       </c>
-      <c r="Z2" s="132" t="s">
+      <c r="Z2" s="105" t="s">
         <v>21</v>
       </c>
       <c r="AA2" s="1"/>
@@ -15660,19 +14751,19 @@
       </c>
       <c r="T3" s="71"/>
       <c r="U3" s="71"/>
-      <c r="V3" s="105"/>
-      <c r="W3" s="122">
+      <c r="V3" s="87"/>
+      <c r="W3" s="96">
         <f>SUM(C3:V3)</f>
         <v>14049</v>
       </c>
-      <c r="X3" s="124">
+      <c r="X3" s="97">
         <v>72082.179999999993</v>
       </c>
-      <c r="Y3" s="133">
+      <c r="Y3" s="106">
         <f>(94085+57723.67)</f>
         <v>151808.66999999998</v>
       </c>
-      <c r="Z3" s="123"/>
+      <c r="Z3" s="129"/>
     </row>
     <row r="4" spans="1:48" ht="15.75">
       <c r="A4" s="66">
@@ -15715,14 +14806,14 @@
         <v>398</v>
       </c>
       <c r="U4" s="72"/>
-      <c r="V4" s="106"/>
-      <c r="W4" s="122">
+      <c r="V4" s="88"/>
+      <c r="W4" s="96">
         <f>SUM(C4:V4)</f>
         <v>10533.31</v>
       </c>
-      <c r="X4" s="124"/>
-      <c r="Y4" s="127"/>
-      <c r="Z4" s="123"/>
+      <c r="X4" s="97"/>
+      <c r="Y4" s="100"/>
+      <c r="Z4" s="129"/>
     </row>
     <row r="5" spans="1:48" ht="15.75">
       <c r="A5" s="62">
@@ -15755,14 +14846,14 @@
       </c>
       <c r="T5" s="71"/>
       <c r="U5" s="71"/>
-      <c r="V5" s="105"/>
-      <c r="W5" s="122">
+      <c r="V5" s="87"/>
+      <c r="W5" s="96">
         <f t="shared" ref="W5:W19" si="0">SUM(C5:V5)</f>
         <v>1455</v>
       </c>
-      <c r="X5" s="124"/>
-      <c r="Y5" s="127"/>
-      <c r="Z5" s="123"/>
+      <c r="X5" s="97"/>
+      <c r="Y5" s="100"/>
+      <c r="Z5" s="129"/>
     </row>
     <row r="6" spans="1:48" ht="15.75">
       <c r="A6" s="66">
@@ -15794,16 +14885,16 @@
       <c r="S6" s="72"/>
       <c r="T6" s="72"/>
       <c r="U6" s="72"/>
-      <c r="V6" s="106">
+      <c r="V6" s="88">
         <v>950</v>
       </c>
-      <c r="W6" s="122">
+      <c r="W6" s="96">
         <f t="shared" si="0"/>
         <v>1803.8400000000001</v>
       </c>
-      <c r="X6" s="124"/>
-      <c r="Y6" s="127"/>
-      <c r="Z6" s="123"/>
+      <c r="X6" s="97"/>
+      <c r="Y6" s="100"/>
+      <c r="Z6" s="129"/>
     </row>
     <row r="7" spans="1:48" ht="15" customHeight="1">
       <c r="A7" s="62">
@@ -15840,14 +14931,14 @@
       <c r="S7" s="71"/>
       <c r="T7" s="71"/>
       <c r="U7" s="71"/>
-      <c r="V7" s="105"/>
-      <c r="W7" s="122">
+      <c r="V7" s="87"/>
+      <c r="W7" s="96">
         <f t="shared" si="0"/>
         <v>3302.61</v>
       </c>
-      <c r="X7" s="124"/>
-      <c r="Y7" s="127"/>
-      <c r="Z7" s="123"/>
+      <c r="X7" s="97"/>
+      <c r="Y7" s="100"/>
+      <c r="Z7" s="129"/>
     </row>
     <row r="8" spans="1:48" ht="15.75">
       <c r="A8" s="66">
@@ -15882,21 +14973,21 @@
       </c>
       <c r="T8" s="72"/>
       <c r="U8" s="72"/>
-      <c r="V8" s="106"/>
-      <c r="W8" s="122">
+      <c r="V8" s="88"/>
+      <c r="W8" s="96">
         <f t="shared" si="0"/>
         <v>2255</v>
       </c>
-      <c r="X8" s="124"/>
-      <c r="Y8" s="127"/>
-      <c r="Z8" s="123"/>
-      <c r="AC8" s="138" t="s">
+      <c r="X8" s="97"/>
+      <c r="Y8" s="100"/>
+      <c r="Z8" s="129"/>
+      <c r="AC8" s="126" t="s">
         <v>61</v>
       </c>
-      <c r="AD8" s="138"/>
-      <c r="AE8" s="138"/>
-      <c r="AF8" s="138"/>
-      <c r="AG8" s="138"/>
+      <c r="AD8" s="126"/>
+      <c r="AE8" s="126"/>
+      <c r="AF8" s="126"/>
+      <c r="AG8" s="126"/>
     </row>
     <row r="9" spans="1:48" ht="15.75">
       <c r="A9" s="62">
@@ -15928,19 +15019,19 @@
       </c>
       <c r="T9" s="71"/>
       <c r="U9" s="71"/>
-      <c r="V9" s="105"/>
-      <c r="W9" s="122">
+      <c r="V9" s="87"/>
+      <c r="W9" s="96">
         <f t="shared" si="0"/>
         <v>1095</v>
       </c>
-      <c r="X9" s="124"/>
-      <c r="Y9" s="127"/>
-      <c r="Z9" s="123"/>
-      <c r="AC9" s="138"/>
-      <c r="AD9" s="138"/>
-      <c r="AE9" s="138"/>
-      <c r="AF9" s="138"/>
-      <c r="AG9" s="138"/>
+      <c r="X9" s="97"/>
+      <c r="Y9" s="100"/>
+      <c r="Z9" s="129"/>
+      <c r="AC9" s="126"/>
+      <c r="AD9" s="126"/>
+      <c r="AE9" s="126"/>
+      <c r="AF9" s="126"/>
+      <c r="AG9" s="126"/>
     </row>
     <row r="10" spans="1:48" ht="15.75">
       <c r="A10" s="66">
@@ -15977,19 +15068,19 @@
         <v>790</v>
       </c>
       <c r="U10" s="72"/>
-      <c r="V10" s="106"/>
-      <c r="W10" s="122">
+      <c r="V10" s="88"/>
+      <c r="W10" s="96">
         <f t="shared" si="0"/>
         <v>4914</v>
       </c>
-      <c r="X10" s="124"/>
-      <c r="Y10" s="127"/>
-      <c r="Z10" s="123"/>
-      <c r="AC10" s="138"/>
-      <c r="AD10" s="138"/>
-      <c r="AE10" s="138"/>
-      <c r="AF10" s="138"/>
-      <c r="AG10" s="138"/>
+      <c r="X10" s="97"/>
+      <c r="Y10" s="100"/>
+      <c r="Z10" s="129"/>
+      <c r="AC10" s="126"/>
+      <c r="AD10" s="126"/>
+      <c r="AE10" s="126"/>
+      <c r="AF10" s="126"/>
+      <c r="AG10" s="126"/>
     </row>
     <row r="11" spans="1:48" ht="15.75">
       <c r="A11" s="62">
@@ -16022,21 +15113,21 @@
       <c r="S11" s="71"/>
       <c r="T11" s="71"/>
       <c r="U11" s="71"/>
-      <c r="V11" s="105"/>
-      <c r="W11" s="122">
+      <c r="V11" s="87"/>
+      <c r="W11" s="96">
         <f t="shared" si="0"/>
         <v>4632.68</v>
       </c>
-      <c r="X11" s="124"/>
-      <c r="Y11" s="127"/>
-      <c r="Z11" s="123"/>
-      <c r="AC11" s="139" t="s">
+      <c r="X11" s="97"/>
+      <c r="Y11" s="100"/>
+      <c r="Z11" s="129"/>
+      <c r="AC11" s="125" t="s">
         <v>62</v>
       </c>
-      <c r="AD11" s="139"/>
-      <c r="AE11" s="139"/>
-      <c r="AF11" s="139"/>
-      <c r="AG11" s="140">
+      <c r="AD11" s="125"/>
+      <c r="AE11" s="125"/>
+      <c r="AF11" s="125"/>
+      <c r="AG11" s="111">
         <f>Y3+Y14+Y21</f>
         <v>226341.31</v>
       </c>
@@ -16069,21 +15160,21 @@
       <c r="S12" s="72"/>
       <c r="T12" s="72"/>
       <c r="U12" s="72"/>
-      <c r="V12" s="106"/>
-      <c r="W12" s="122">
+      <c r="V12" s="88"/>
+      <c r="W12" s="96">
         <f t="shared" si="0"/>
         <v>4475</v>
       </c>
-      <c r="X12" s="124"/>
-      <c r="Y12" s="127"/>
-      <c r="Z12" s="123"/>
-      <c r="AC12" s="139" t="s">
+      <c r="X12" s="97"/>
+      <c r="Y12" s="100"/>
+      <c r="Z12" s="129"/>
+      <c r="AC12" s="125" t="s">
         <v>55</v>
       </c>
-      <c r="AD12" s="139"/>
-      <c r="AE12" s="139"/>
-      <c r="AF12" s="139"/>
-      <c r="AG12" s="140">
+      <c r="AD12" s="125"/>
+      <c r="AE12" s="125"/>
+      <c r="AF12" s="125"/>
+      <c r="AG12" s="111">
         <f>Y27</f>
         <v>20000</v>
       </c>
@@ -16120,21 +15211,21 @@
       </c>
       <c r="T13" s="71"/>
       <c r="U13" s="71"/>
-      <c r="V13" s="105"/>
-      <c r="W13" s="122">
+      <c r="V13" s="87"/>
+      <c r="W13" s="96">
         <f t="shared" si="0"/>
         <v>4015.63</v>
       </c>
-      <c r="X13" s="124"/>
-      <c r="Y13" s="127"/>
-      <c r="Z13" s="123"/>
-      <c r="AC13" s="139" t="s">
+      <c r="X13" s="97"/>
+      <c r="Y13" s="100"/>
+      <c r="Z13" s="129"/>
+      <c r="AC13" s="125" t="s">
         <v>63</v>
       </c>
-      <c r="AD13" s="139"/>
-      <c r="AE13" s="139"/>
-      <c r="AF13" s="139"/>
-      <c r="AG13" s="140">
+      <c r="AD13" s="125"/>
+      <c r="AE13" s="125"/>
+      <c r="AF13" s="125"/>
+      <c r="AG13" s="111">
         <f>Y17+Y19</f>
         <v>25000</v>
       </c>
@@ -16168,25 +15259,25 @@
       <c r="S14" s="72"/>
       <c r="T14" s="72"/>
       <c r="U14" s="72"/>
-      <c r="V14" s="106"/>
-      <c r="W14" s="122">
+      <c r="V14" s="88"/>
+      <c r="W14" s="96">
         <f t="shared" si="0"/>
         <v>2273.7800000000002</v>
       </c>
-      <c r="X14" s="124">
+      <c r="X14" s="97">
         <v>14878.51</v>
       </c>
-      <c r="Y14" s="133">
+      <c r="Y14" s="106">
         <v>37634</v>
       </c>
-      <c r="Z14" s="123"/>
-      <c r="AC14" s="139" t="s">
+      <c r="Z14" s="129"/>
+      <c r="AC14" s="125" t="s">
         <v>64</v>
       </c>
-      <c r="AD14" s="139"/>
-      <c r="AE14" s="139"/>
-      <c r="AF14" s="139"/>
-      <c r="AG14" s="140">
+      <c r="AD14" s="125"/>
+      <c r="AE14" s="125"/>
+      <c r="AF14" s="125"/>
+      <c r="AG14" s="111">
         <f>W38</f>
         <v>167654.87</v>
       </c>
@@ -16228,21 +15319,21 @@
       </c>
       <c r="T15" s="71"/>
       <c r="U15" s="71"/>
-      <c r="V15" s="105"/>
-      <c r="W15" s="122">
+      <c r="V15" s="87"/>
+      <c r="W15" s="96">
         <f t="shared" si="0"/>
         <v>4096.9799999999996</v>
       </c>
-      <c r="X15" s="124"/>
-      <c r="Y15" s="127"/>
-      <c r="Z15" s="123"/>
-      <c r="AC15" s="139" t="s">
+      <c r="X15" s="97"/>
+      <c r="Y15" s="100"/>
+      <c r="Z15" s="129"/>
+      <c r="AC15" s="125" t="s">
         <v>65</v>
       </c>
-      <c r="AD15" s="139"/>
-      <c r="AE15" s="139"/>
-      <c r="AF15" s="139"/>
-      <c r="AG15" s="140">
+      <c r="AD15" s="125"/>
+      <c r="AE15" s="125"/>
+      <c r="AF15" s="125"/>
+      <c r="AG15" s="111">
         <f>SUM(C38:H38)</f>
         <v>47166.55</v>
       </c>
@@ -16282,15 +15373,15 @@
       <c r="T16" s="72">
         <v>1200</v>
       </c>
-      <c r="U16" s="87"/>
-      <c r="V16" s="106"/>
-      <c r="W16" s="122">
+      <c r="U16" s="86"/>
+      <c r="V16" s="88"/>
+      <c r="W16" s="96">
         <f t="shared" si="0"/>
         <v>6141</v>
       </c>
-      <c r="X16" s="124"/>
-      <c r="Y16" s="127"/>
-      <c r="Z16" s="123"/>
+      <c r="X16" s="97"/>
+      <c r="Y16" s="100"/>
+      <c r="Z16" s="129"/>
     </row>
     <row r="17" spans="1:28" ht="15.75">
       <c r="A17" s="62">
@@ -16333,16 +15424,16 @@
         <f>1825+2217+2419</f>
         <v>6461</v>
       </c>
-      <c r="V17" s="105"/>
-      <c r="W17" s="122">
+      <c r="V17" s="87"/>
+      <c r="W17" s="96">
         <f t="shared" si="0"/>
         <v>16780</v>
       </c>
-      <c r="X17" s="124"/>
-      <c r="Y17" s="134">
+      <c r="X17" s="97"/>
+      <c r="Y17" s="107">
         <v>15000</v>
       </c>
-      <c r="Z17" s="123"/>
+      <c r="Z17" s="129"/>
     </row>
     <row r="18" spans="1:28" ht="15.75">
       <c r="A18" s="66">
@@ -16372,18 +15463,18 @@
       <c r="S18" s="72">
         <v>499</v>
       </c>
-      <c r="T18" s="87"/>
+      <c r="T18" s="86"/>
       <c r="U18" s="72">
         <v>8000</v>
       </c>
-      <c r="V18" s="106"/>
-      <c r="W18" s="122">
+      <c r="V18" s="88"/>
+      <c r="W18" s="96">
         <f t="shared" si="0"/>
         <v>10517.8</v>
       </c>
-      <c r="X18" s="124"/>
-      <c r="Y18" s="127"/>
-      <c r="Z18" s="123"/>
+      <c r="X18" s="97"/>
+      <c r="Y18" s="100"/>
+      <c r="Z18" s="129"/>
     </row>
     <row r="19" spans="1:28" ht="15.75">
       <c r="A19" s="62">
@@ -16415,27 +15506,27 @@
       <c r="S19" s="71"/>
       <c r="T19" s="71"/>
       <c r="U19" s="71"/>
-      <c r="V19" s="105">
+      <c r="V19" s="87">
         <f>83+760+400+6869+83+83+1800+850+1033.84+1423+1349+694+83+6000+1800+305</f>
         <v>23615.84</v>
       </c>
-      <c r="W19" s="122">
+      <c r="W19" s="96">
         <f t="shared" si="0"/>
         <v>29591.93</v>
       </c>
-      <c r="X19" s="124"/>
-      <c r="Y19" s="134">
+      <c r="X19" s="97"/>
+      <c r="Y19" s="107">
         <v>10000</v>
       </c>
-      <c r="Z19" s="123"/>
+      <c r="Z19" s="129"/>
     </row>
     <row r="20" spans="1:28" ht="14.25" customHeight="1">
-      <c r="A20" s="99" t="s">
+      <c r="A20" s="123" t="s">
         <v>35</v>
       </c>
-      <c r="B20" s="99"/>
+      <c r="B20" s="123"/>
       <c r="C20" s="79">
-        <f t="shared" ref="C20:Y20" si="1">SUM(C3:C17)</f>
+        <f t="shared" ref="C20:V20" si="1">SUM(C3:C17)</f>
         <v>10942.99</v>
       </c>
       <c r="D20" s="79">
@@ -16510,23 +15601,23 @@
         <f t="shared" si="1"/>
         <v>6461</v>
       </c>
-      <c r="V20" s="119">
+      <c r="V20" s="93">
         <f t="shared" si="1"/>
         <v>950</v>
       </c>
-      <c r="W20" s="128">
+      <c r="W20" s="101">
         <f>SUM(W3:W19)</f>
         <v>121932.56</v>
       </c>
-      <c r="X20" s="129">
+      <c r="X20" s="102">
         <f>SUM(X3:X19)</f>
         <v>86960.689999999988</v>
       </c>
-      <c r="Y20" s="135">
+      <c r="Y20" s="108">
         <f>SUM(Y3:Y19)</f>
         <v>214442.66999999998</v>
       </c>
-      <c r="Z20" s="130">
+      <c r="Z20" s="103">
         <f>Y20-W20-X20</f>
         <v>5549.4199999999983</v>
       </c>
@@ -16567,16 +15658,16 @@
         <v>856</v>
       </c>
       <c r="U21" s="71"/>
-      <c r="V21" s="105"/>
-      <c r="W21" s="122">
+      <c r="V21" s="87"/>
+      <c r="W21" s="96">
         <f>SUM(C21:V21)</f>
         <v>6642</v>
       </c>
-      <c r="X21" s="124"/>
-      <c r="Y21" s="133">
+      <c r="X21" s="97"/>
+      <c r="Y21" s="106">
         <v>36898.639999999999</v>
       </c>
-      <c r="Z21" s="123"/>
+      <c r="Z21" s="129"/>
     </row>
     <row r="22" spans="1:28" ht="15.75">
       <c r="A22" s="66">
@@ -16613,16 +15704,16 @@
         <v>79</v>
       </c>
       <c r="U22" s="72"/>
-      <c r="V22" s="106"/>
-      <c r="W22" s="122">
+      <c r="V22" s="88"/>
+      <c r="W22" s="96">
         <f t="shared" ref="W22:W36" si="2">SUM(C22:V22)</f>
         <v>1376</v>
       </c>
-      <c r="X22" s="124">
+      <c r="X22" s="97">
         <v>23662.84</v>
       </c>
-      <c r="Y22" s="127"/>
-      <c r="Z22" s="123"/>
+      <c r="Y22" s="100"/>
+      <c r="Z22" s="129"/>
       <c r="AB22" s="44"/>
     </row>
     <row r="23" spans="1:28" ht="15.75">
@@ -16659,14 +15750,14 @@
       </c>
       <c r="T23" s="71"/>
       <c r="U23" s="71"/>
-      <c r="V23" s="105"/>
-      <c r="W23" s="122">
+      <c r="V23" s="87"/>
+      <c r="W23" s="96">
         <f t="shared" si="2"/>
         <v>2020</v>
       </c>
-      <c r="X23" s="124"/>
-      <c r="Y23" s="127"/>
-      <c r="Z23" s="123"/>
+      <c r="X23" s="97"/>
+      <c r="Y23" s="100"/>
+      <c r="Z23" s="129"/>
     </row>
     <row r="24" spans="1:28" ht="15.75">
       <c r="A24" s="66">
@@ -16703,14 +15794,14 @@
       <c r="S24" s="72"/>
       <c r="T24" s="72"/>
       <c r="U24" s="72"/>
-      <c r="V24" s="106"/>
-      <c r="W24" s="122">
+      <c r="V24" s="88"/>
+      <c r="W24" s="96">
         <f t="shared" si="2"/>
         <v>3874</v>
       </c>
-      <c r="X24" s="124"/>
-      <c r="Y24" s="127"/>
-      <c r="Z24" s="123"/>
+      <c r="X24" s="97"/>
+      <c r="Y24" s="100"/>
+      <c r="Z24" s="129"/>
     </row>
     <row r="25" spans="1:28" ht="15.75">
       <c r="A25" s="62">
@@ -16745,16 +15836,16 @@
       <c r="S25" s="71"/>
       <c r="T25" s="71"/>
       <c r="U25" s="71"/>
-      <c r="V25" s="105">
+      <c r="V25" s="87">
         <v>2000</v>
       </c>
-      <c r="W25" s="122">
+      <c r="W25" s="96">
         <f t="shared" si="2"/>
         <v>7893.3099999999995</v>
       </c>
-      <c r="X25" s="124"/>
-      <c r="Y25" s="127"/>
-      <c r="Z25" s="123"/>
+      <c r="X25" s="97"/>
+      <c r="Y25" s="100"/>
+      <c r="Z25" s="129"/>
     </row>
     <row r="26" spans="1:28" ht="15.75">
       <c r="A26" s="66">
@@ -16786,14 +15877,14 @@
       <c r="S26" s="72"/>
       <c r="T26" s="72"/>
       <c r="U26" s="72"/>
-      <c r="V26" s="106"/>
-      <c r="W26" s="122">
+      <c r="V26" s="88"/>
+      <c r="W26" s="96">
         <f t="shared" si="2"/>
         <v>3329</v>
       </c>
-      <c r="X26" s="124"/>
-      <c r="Y26" s="127"/>
-      <c r="Z26" s="123"/>
+      <c r="X26" s="97"/>
+      <c r="Y26" s="100"/>
+      <c r="Z26" s="129"/>
     </row>
     <row r="27" spans="1:28" ht="15.75">
       <c r="A27" s="62">
@@ -16827,18 +15918,18 @@
       <c r="S27" s="71"/>
       <c r="T27" s="71"/>
       <c r="U27" s="71"/>
-      <c r="V27" s="105">
+      <c r="V27" s="87">
         <v>2800</v>
       </c>
-      <c r="W27" s="122">
+      <c r="W27" s="96">
         <f t="shared" si="2"/>
         <v>7497</v>
       </c>
-      <c r="X27" s="124"/>
-      <c r="Y27" s="137">
+      <c r="X27" s="97"/>
+      <c r="Y27" s="110">
         <v>20000</v>
       </c>
-      <c r="Z27" s="123"/>
+      <c r="Z27" s="129"/>
     </row>
     <row r="28" spans="1:28" ht="15.75">
       <c r="A28" s="66">
@@ -16873,14 +15964,14 @@
         <v>10574</v>
       </c>
       <c r="U28" s="72"/>
-      <c r="V28" s="106"/>
-      <c r="W28" s="122">
+      <c r="V28" s="88"/>
+      <c r="W28" s="96">
         <f t="shared" si="2"/>
         <v>11161</v>
       </c>
-      <c r="X28" s="124"/>
-      <c r="Y28" s="127"/>
-      <c r="Z28" s="123"/>
+      <c r="X28" s="97"/>
+      <c r="Y28" s="100"/>
+      <c r="Z28" s="129"/>
     </row>
     <row r="29" spans="1:28" ht="15.75">
       <c r="A29" s="62">
@@ -16912,14 +16003,14 @@
       <c r="S29" s="71"/>
       <c r="T29" s="71"/>
       <c r="U29" s="71"/>
-      <c r="V29" s="105"/>
-      <c r="W29" s="122">
+      <c r="V29" s="87"/>
+      <c r="W29" s="96">
         <f t="shared" si="2"/>
         <v>1530</v>
       </c>
-      <c r="X29" s="124"/>
-      <c r="Y29" s="127"/>
-      <c r="Z29" s="123"/>
+      <c r="X29" s="97"/>
+      <c r="Y29" s="100"/>
+      <c r="Z29" s="129"/>
     </row>
     <row r="30" spans="1:28" ht="15.75">
       <c r="A30" s="66">
@@ -16949,14 +16040,14 @@
       <c r="S30" s="72"/>
       <c r="T30" s="72"/>
       <c r="U30" s="72"/>
-      <c r="V30" s="106"/>
-      <c r="W30" s="122">
+      <c r="V30" s="88"/>
+      <c r="W30" s="96">
         <f t="shared" si="2"/>
         <v>400</v>
       </c>
-      <c r="X30" s="124"/>
-      <c r="Y30" s="127"/>
-      <c r="Z30" s="123"/>
+      <c r="X30" s="97"/>
+      <c r="Y30" s="100"/>
+      <c r="Z30" s="129"/>
     </row>
     <row r="31" spans="1:28" ht="15.75">
       <c r="A31" s="62">
@@ -16984,14 +16075,14 @@
       <c r="S31" s="71"/>
       <c r="T31" s="71"/>
       <c r="U31" s="71"/>
-      <c r="V31" s="105"/>
-      <c r="W31" s="122">
+      <c r="V31" s="87"/>
+      <c r="W31" s="96">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="X31" s="124"/>
-      <c r="Y31" s="127"/>
-      <c r="Z31" s="123"/>
+      <c r="X31" s="97"/>
+      <c r="Y31" s="100"/>
+      <c r="Z31" s="129"/>
     </row>
     <row r="32" spans="1:28" ht="15.75">
       <c r="A32" s="66">
@@ -17019,14 +16110,14 @@
       <c r="S32" s="72"/>
       <c r="T32" s="72"/>
       <c r="U32" s="72"/>
-      <c r="V32" s="106"/>
-      <c r="W32" s="122">
+      <c r="V32" s="88"/>
+      <c r="W32" s="96">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="X32" s="124"/>
-      <c r="Y32" s="127"/>
-      <c r="Z32" s="123"/>
+      <c r="X32" s="97"/>
+      <c r="Y32" s="100"/>
+      <c r="Z32" s="129"/>
     </row>
     <row r="33" spans="1:26" ht="15.75">
       <c r="A33" s="62">
@@ -17054,14 +16145,14 @@
       <c r="S33" s="71"/>
       <c r="T33" s="71"/>
       <c r="U33" s="71"/>
-      <c r="V33" s="105"/>
-      <c r="W33" s="122">
+      <c r="V33" s="87"/>
+      <c r="W33" s="96">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="X33" s="124"/>
-      <c r="Y33" s="127"/>
-      <c r="Z33" s="123"/>
+      <c r="X33" s="97"/>
+      <c r="Y33" s="100"/>
+      <c r="Z33" s="129"/>
     </row>
     <row r="34" spans="1:26" ht="15.75">
       <c r="A34" s="66">
@@ -17089,14 +16180,14 @@
       <c r="S34" s="72"/>
       <c r="T34" s="72"/>
       <c r="U34" s="72"/>
-      <c r="V34" s="106"/>
-      <c r="W34" s="122">
+      <c r="V34" s="88"/>
+      <c r="W34" s="96">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="X34" s="124"/>
-      <c r="Y34" s="127"/>
-      <c r="Z34" s="123"/>
+      <c r="X34" s="97"/>
+      <c r="Y34" s="100"/>
+      <c r="Z34" s="129"/>
     </row>
     <row r="35" spans="1:26" ht="15.75">
       <c r="A35" s="62">
@@ -17124,14 +16215,14 @@
       <c r="S35" s="71"/>
       <c r="T35" s="71"/>
       <c r="U35" s="71"/>
-      <c r="V35" s="105"/>
-      <c r="W35" s="122">
+      <c r="V35" s="87"/>
+      <c r="W35" s="96">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="X35" s="124"/>
-      <c r="Y35" s="127"/>
-      <c r="Z35" s="123"/>
+      <c r="X35" s="97"/>
+      <c r="Y35" s="100"/>
+      <c r="Z35" s="129"/>
     </row>
     <row r="36" spans="1:26" ht="15.75">
       <c r="A36" s="66">
@@ -17159,20 +16250,20 @@
       <c r="S36" s="72"/>
       <c r="T36" s="72"/>
       <c r="U36" s="72"/>
-      <c r="V36" s="106"/>
-      <c r="W36" s="122">
+      <c r="V36" s="88"/>
+      <c r="W36" s="96">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="X36" s="124"/>
-      <c r="Y36" s="127"/>
-      <c r="Z36" s="123"/>
+      <c r="X36" s="97"/>
+      <c r="Y36" s="100"/>
+      <c r="Z36" s="129"/>
     </row>
     <row r="37" spans="1:26">
-      <c r="A37" s="99" t="s">
+      <c r="A37" s="123" t="s">
         <v>36</v>
       </c>
-      <c r="B37" s="99"/>
+      <c r="B37" s="123"/>
       <c r="C37" s="79">
         <f>SUM(C21:C36)</f>
         <v>3393</v>
@@ -17249,32 +16340,32 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="V37" s="119">
+      <c r="V37" s="93">
         <f t="shared" si="3"/>
         <v>4800</v>
       </c>
-      <c r="W37" s="128">
+      <c r="W37" s="101">
         <f>SUM(W21:W36)</f>
         <v>45722.31</v>
       </c>
-      <c r="X37" s="129">
+      <c r="X37" s="102">
         <f>SUM(X21:X36)</f>
         <v>23662.84</v>
       </c>
-      <c r="Y37" s="135">
+      <c r="Y37" s="108">
         <f>SUM(Y21:Y36)</f>
         <v>56898.64</v>
       </c>
-      <c r="Z37" s="131">
+      <c r="Z37" s="104">
         <f>Y37-W37-X37</f>
         <v>-12486.509999999998</v>
       </c>
     </row>
     <row r="38" spans="1:26" ht="31.5" customHeight="1">
-      <c r="A38" s="102" t="s">
+      <c r="A38" s="128" t="s">
         <v>37</v>
       </c>
-      <c r="B38" s="102"/>
+      <c r="B38" s="128"/>
       <c r="C38" s="78">
         <f>SUM(C20,C37)</f>
         <v>14335.99</v>
@@ -17351,19 +16442,19 @@
         <f t="shared" si="4"/>
         <v>6461</v>
       </c>
-      <c r="V38" s="120">
+      <c r="V38" s="94">
         <f t="shared" si="4"/>
         <v>5750</v>
       </c>
-      <c r="W38" s="128">
+      <c r="W38" s="101">
         <f t="shared" si="4"/>
         <v>167654.87</v>
       </c>
-      <c r="X38" s="129">
+      <c r="X38" s="102">
         <f>SUM(X20,X37)</f>
         <v>110623.52999999998</v>
       </c>
-      <c r="Y38" s="136">
+      <c r="Y38" s="109">
         <f>SUM(Y20,Y37)</f>
         <v>271341.31</v>
       </c>
@@ -17386,24 +16477,24 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A1:Z1"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="Z3:Z19"/>
+    <mergeCell ref="Z21:Z36"/>
     <mergeCell ref="AC14:AF14"/>
     <mergeCell ref="AC15:AF15"/>
     <mergeCell ref="AC8:AG10"/>
     <mergeCell ref="AC11:AF11"/>
     <mergeCell ref="AC12:AF12"/>
     <mergeCell ref="AC13:AF13"/>
-    <mergeCell ref="A1:Z1"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="Z3:Z19"/>
-    <mergeCell ref="Z21:Z36"/>
   </mergeCells>
   <conditionalFormatting sqref="Z20:Z21 Z37:Z38">
-    <cfRule type="expression" dxfId="1" priority="1">
+    <cfRule type="expression" dxfId="3" priority="1">
       <formula>Z20&lt;0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="2">
+    <cfRule type="expression" dxfId="2" priority="2">
       <formula>Z20&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -17424,112 +16515,112 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:48" ht="60.75" customHeight="1">
-      <c r="A1" s="101" t="s">
-        <v>59</v>
-      </c>
-      <c r="B1" s="101"/>
-      <c r="C1" s="101"/>
-      <c r="D1" s="101"/>
-      <c r="E1" s="101"/>
-      <c r="F1" s="101"/>
-      <c r="G1" s="101"/>
-      <c r="H1" s="101"/>
-      <c r="I1" s="101"/>
-      <c r="J1" s="101"/>
-      <c r="K1" s="101"/>
-      <c r="L1" s="101"/>
-      <c r="M1" s="101"/>
-      <c r="N1" s="101"/>
-      <c r="O1" s="101"/>
-      <c r="P1" s="101"/>
-      <c r="Q1" s="101"/>
-      <c r="R1" s="101"/>
-      <c r="S1" s="101"/>
-      <c r="T1" s="101"/>
-      <c r="U1" s="101"/>
-      <c r="V1" s="101"/>
-      <c r="W1" s="101"/>
-      <c r="X1" s="101"/>
-      <c r="Y1" s="101"/>
-      <c r="Z1" s="101"/>
+      <c r="A1" s="133" t="s">
+        <v>66</v>
+      </c>
+      <c r="B1" s="133"/>
+      <c r="C1" s="133"/>
+      <c r="D1" s="133"/>
+      <c r="E1" s="133"/>
+      <c r="F1" s="133"/>
+      <c r="G1" s="133"/>
+      <c r="H1" s="133"/>
+      <c r="I1" s="133"/>
+      <c r="J1" s="133"/>
+      <c r="K1" s="133"/>
+      <c r="L1" s="133"/>
+      <c r="M1" s="133"/>
+      <c r="N1" s="133"/>
+      <c r="O1" s="133"/>
+      <c r="P1" s="133"/>
+      <c r="Q1" s="133"/>
+      <c r="R1" s="133"/>
+      <c r="S1" s="133"/>
+      <c r="T1" s="133"/>
+      <c r="U1" s="133"/>
+      <c r="V1" s="133"/>
+      <c r="W1" s="133"/>
+      <c r="X1" s="133"/>
+      <c r="Y1" s="133"/>
+      <c r="Z1" s="133"/>
     </row>
     <row r="2" spans="1:48" ht="45" customHeight="1">
-      <c r="A2" s="76" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="76" t="s">
+      <c r="A2" s="143" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="143" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="116" t="s">
+      <c r="C2" s="138" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="116" t="s">
+      <c r="D2" s="138" t="s">
         <v>29</v>
       </c>
-      <c r="E2" s="116" t="s">
+      <c r="E2" s="138" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="116" t="s">
+      <c r="F2" s="138" t="s">
         <v>33</v>
       </c>
-      <c r="G2" s="116" t="s">
+      <c r="G2" s="138" t="s">
         <v>34</v>
       </c>
-      <c r="H2" s="116" t="s">
+      <c r="H2" s="138" t="s">
         <v>11</v>
       </c>
-      <c r="I2" s="115" t="s">
+      <c r="I2" s="139" t="s">
         <v>30</v>
       </c>
-      <c r="J2" s="115" t="s">
+      <c r="J2" s="139" t="s">
         <v>12</v>
       </c>
-      <c r="K2" s="76" t="s">
+      <c r="K2" s="140" t="s">
         <v>24</v>
       </c>
-      <c r="L2" s="76" t="s">
+      <c r="L2" s="140" t="s">
         <v>23</v>
       </c>
-      <c r="M2" s="76" t="s">
+      <c r="M2" s="140" t="s">
         <v>13</v>
       </c>
-      <c r="N2" s="76" t="s">
+      <c r="N2" s="140" t="s">
         <v>14</v>
       </c>
-      <c r="O2" s="76" t="s">
+      <c r="O2" s="140" t="s">
         <v>15</v>
       </c>
-      <c r="P2" s="76" t="s">
+      <c r="P2" s="140" t="s">
         <v>16</v>
       </c>
-      <c r="Q2" s="76" t="s">
+      <c r="Q2" s="140" t="s">
         <v>28</v>
       </c>
-      <c r="R2" s="76" t="s">
+      <c r="R2" s="140" t="s">
         <v>17</v>
       </c>
-      <c r="S2" s="76" t="s">
+      <c r="S2" s="140" t="s">
         <v>18</v>
       </c>
-      <c r="T2" s="76" t="s">
+      <c r="T2" s="140" t="s">
         <v>25</v>
       </c>
-      <c r="U2" s="76" t="s">
+      <c r="U2" s="140" t="s">
         <v>25</v>
       </c>
-      <c r="V2" s="76" t="s">
+      <c r="V2" s="140" t="s">
         <v>26</v>
       </c>
-      <c r="W2" s="103" t="s">
+      <c r="W2" s="141" t="s">
         <v>60</v>
       </c>
-      <c r="X2" s="81" t="s">
+      <c r="X2" s="142" t="s">
         <v>22</v>
       </c>
-      <c r="Y2" s="81" t="s">
+      <c r="Y2" s="142" t="s">
         <v>19</v>
       </c>
-      <c r="Z2" s="81" t="s">
+      <c r="Z2" s="142" t="s">
         <v>21</v>
       </c>
       <c r="AA2" s="1"/>
@@ -17556,53 +16647,39 @@
       <c r="AV2" s="1"/>
     </row>
     <row r="3" spans="1:48" ht="15.75">
-      <c r="A3" s="62">
+      <c r="A3" s="134">
         <v>3</v>
       </c>
-      <c r="B3" s="63" t="s">
+      <c r="B3" s="135" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="71">
-        <f>100</f>
-        <v>100</v>
-      </c>
-      <c r="D3" s="71"/>
-      <c r="E3" s="71"/>
-      <c r="F3" s="71"/>
-      <c r="G3" s="71"/>
-      <c r="H3" s="71"/>
-      <c r="I3" s="71"/>
-      <c r="J3" s="71"/>
-      <c r="K3" s="71"/>
-      <c r="L3" s="71">
-        <f>150+3000</f>
-        <v>3150</v>
-      </c>
-      <c r="M3" s="71"/>
-      <c r="N3" s="71"/>
-      <c r="O3" s="71"/>
-      <c r="P3" s="71"/>
-      <c r="Q3" s="71">
-        <f>10000</f>
-        <v>10000</v>
-      </c>
-      <c r="R3" s="71"/>
-      <c r="S3" s="71">
-        <v>799</v>
-      </c>
-      <c r="T3" s="71"/>
-      <c r="U3" s="71"/>
-      <c r="V3" s="71"/>
-      <c r="W3" s="71"/>
-      <c r="X3" s="105">
+      <c r="C3" s="136"/>
+      <c r="D3" s="136"/>
+      <c r="E3" s="136"/>
+      <c r="F3" s="136"/>
+      <c r="G3" s="136"/>
+      <c r="H3" s="136"/>
+      <c r="I3" s="136"/>
+      <c r="J3" s="136"/>
+      <c r="K3" s="136"/>
+      <c r="L3" s="136"/>
+      <c r="M3" s="136"/>
+      <c r="N3" s="136"/>
+      <c r="O3" s="136"/>
+      <c r="P3" s="136"/>
+      <c r="Q3" s="136"/>
+      <c r="R3" s="136"/>
+      <c r="S3" s="136"/>
+      <c r="T3" s="136"/>
+      <c r="U3" s="136"/>
+      <c r="V3" s="136"/>
+      <c r="W3" s="136"/>
+      <c r="X3" s="137">
         <f>SUM(C3:V3)</f>
-        <v>14049</v>
-      </c>
-      <c r="Y3" s="114">
-        <f>(94085+57723.67)/2</f>
-        <v>75904.334999999992</v>
-      </c>
-      <c r="Z3" s="107"/>
+        <v>0</v>
+      </c>
+      <c r="Y3" s="144"/>
+      <c r="Z3" s="131"/>
     </row>
     <row r="4" spans="1:48" ht="15.75">
       <c r="A4" s="66">
@@ -17611,48 +16688,33 @@
       <c r="B4" s="67" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="72">
-        <v>528.91999999999996</v>
-      </c>
-      <c r="D4" s="72">
-        <f>403+3617.41</f>
-        <v>4020.41</v>
-      </c>
+      <c r="C4" s="72"/>
+      <c r="D4" s="72"/>
       <c r="E4" s="72"/>
       <c r="F4" s="72"/>
       <c r="G4" s="72"/>
-      <c r="H4" s="72">
-        <f>3760</f>
-        <v>3760</v>
-      </c>
-      <c r="I4" s="72">
-        <v>1320.98</v>
-      </c>
+      <c r="H4" s="72"/>
+      <c r="I4" s="72"/>
       <c r="J4" s="72"/>
       <c r="K4" s="72"/>
       <c r="L4" s="72"/>
       <c r="M4" s="72"/>
       <c r="N4" s="72"/>
-      <c r="O4" s="72">
-        <f>290+215</f>
-        <v>505</v>
-      </c>
+      <c r="O4" s="72"/>
       <c r="P4" s="72"/>
       <c r="Q4" s="72"/>
       <c r="R4" s="72"/>
       <c r="S4" s="72"/>
-      <c r="T4" s="72">
-        <v>398</v>
-      </c>
+      <c r="T4" s="72"/>
       <c r="U4" s="72"/>
       <c r="V4" s="72"/>
       <c r="W4" s="72"/>
-      <c r="X4" s="106">
+      <c r="X4" s="88">
         <f>SUM(C4:V4)</f>
-        <v>10533.31</v>
-      </c>
-      <c r="Y4" s="111"/>
-      <c r="Z4" s="108"/>
+        <v>0</v>
+      </c>
+      <c r="Y4" s="145"/>
+      <c r="Z4" s="131"/>
     </row>
     <row r="5" spans="1:48" ht="15.75">
       <c r="A5" s="62">
@@ -17661,10 +16723,7 @@
       <c r="B5" s="63" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="71">
-        <f>441+815</f>
-        <v>1256</v>
-      </c>
+      <c r="C5" s="71"/>
       <c r="D5" s="71"/>
       <c r="E5" s="71"/>
       <c r="F5" s="71"/>
@@ -17680,19 +16739,17 @@
       <c r="P5" s="71"/>
       <c r="Q5" s="71"/>
       <c r="R5" s="71"/>
-      <c r="S5" s="71">
-        <v>199</v>
-      </c>
+      <c r="S5" s="71"/>
       <c r="T5" s="71"/>
       <c r="U5" s="71"/>
       <c r="V5" s="71"/>
       <c r="W5" s="71"/>
-      <c r="X5" s="105">
+      <c r="X5" s="87">
         <f t="shared" ref="X5:X19" si="0">SUM(C5:V5)</f>
-        <v>1455</v>
-      </c>
-      <c r="Y5" s="111"/>
-      <c r="Z5" s="108"/>
+        <v>0</v>
+      </c>
+      <c r="Y5" s="145"/>
+      <c r="Z5" s="131"/>
     </row>
     <row r="6" spans="1:48" ht="15.75">
       <c r="A6" s="66">
@@ -17702,9 +16759,7 @@
         <v>7</v>
       </c>
       <c r="C6" s="72"/>
-      <c r="D6" s="72">
-        <v>628.84</v>
-      </c>
+      <c r="D6" s="72"/>
       <c r="E6" s="72"/>
       <c r="F6" s="72"/>
       <c r="G6" s="72"/>
@@ -17715,25 +16770,21 @@
       <c r="L6" s="72"/>
       <c r="M6" s="72"/>
       <c r="N6" s="72"/>
-      <c r="O6" s="72">
-        <v>225</v>
-      </c>
+      <c r="O6" s="72"/>
       <c r="P6" s="72"/>
       <c r="Q6" s="72"/>
       <c r="R6" s="72"/>
       <c r="S6" s="72"/>
       <c r="T6" s="72"/>
       <c r="U6" s="72"/>
-      <c r="V6" s="72">
-        <v>950</v>
-      </c>
+      <c r="V6" s="72"/>
       <c r="W6" s="72"/>
-      <c r="X6" s="106">
+      <c r="X6" s="88">
         <f t="shared" si="0"/>
-        <v>1803.8400000000001</v>
-      </c>
-      <c r="Y6" s="111"/>
-      <c r="Z6" s="108"/>
+        <v>0</v>
+      </c>
+      <c r="Y6" s="145"/>
+      <c r="Z6" s="131"/>
     </row>
     <row r="7" spans="1:48" ht="15" customHeight="1">
       <c r="A7" s="62">
@@ -17742,17 +16793,10 @@
       <c r="B7" s="63" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="71">
-        <f>1534.21+320.4</f>
-        <v>1854.6100000000001</v>
-      </c>
-      <c r="D7" s="71">
-        <v>292</v>
-      </c>
+      <c r="C7" s="71"/>
+      <c r="D7" s="71"/>
       <c r="E7" s="71"/>
-      <c r="F7" s="71">
-        <v>960</v>
-      </c>
+      <c r="F7" s="71"/>
       <c r="G7" s="71"/>
       <c r="H7" s="71"/>
       <c r="I7" s="71"/>
@@ -17761,9 +16805,7 @@
       <c r="L7" s="71"/>
       <c r="M7" s="71"/>
       <c r="N7" s="71"/>
-      <c r="O7" s="71">
-        <v>196</v>
-      </c>
+      <c r="O7" s="71"/>
       <c r="P7" s="71"/>
       <c r="Q7" s="71"/>
       <c r="R7" s="71"/>
@@ -17772,12 +16814,12 @@
       <c r="U7" s="71"/>
       <c r="V7" s="71"/>
       <c r="W7" s="71"/>
-      <c r="X7" s="105">
+      <c r="X7" s="87">
         <f t="shared" si="0"/>
-        <v>3302.61</v>
-      </c>
-      <c r="Y7" s="111"/>
-      <c r="Z7" s="108"/>
+        <v>0</v>
+      </c>
+      <c r="Y7" s="145"/>
+      <c r="Z7" s="131"/>
     </row>
     <row r="8" spans="1:48" ht="15.75">
       <c r="A8" s="66">
@@ -17786,9 +16828,7 @@
       <c r="B8" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="C8" s="72">
-        <v>233</v>
-      </c>
+      <c r="C8" s="72"/>
       <c r="D8" s="72"/>
       <c r="E8" s="72"/>
       <c r="F8" s="72"/>
@@ -17802,24 +16842,19 @@
       <c r="N8" s="72"/>
       <c r="O8" s="72"/>
       <c r="P8" s="72"/>
-      <c r="Q8" s="72">
-        <f>490+690</f>
-        <v>1180</v>
-      </c>
+      <c r="Q8" s="72"/>
       <c r="R8" s="72"/>
-      <c r="S8" s="72">
-        <v>842</v>
-      </c>
+      <c r="S8" s="72"/>
       <c r="T8" s="72"/>
       <c r="U8" s="72"/>
       <c r="V8" s="72"/>
       <c r="W8" s="72"/>
-      <c r="X8" s="106">
+      <c r="X8" s="88">
         <f t="shared" si="0"/>
-        <v>2255</v>
-      </c>
-      <c r="Y8" s="111"/>
-      <c r="Z8" s="108"/>
+        <v>0</v>
+      </c>
+      <c r="Y8" s="145"/>
+      <c r="Z8" s="131"/>
     </row>
     <row r="9" spans="1:48" ht="15.75">
       <c r="A9" s="62">
@@ -17840,25 +16875,21 @@
       <c r="L9" s="71"/>
       <c r="M9" s="71"/>
       <c r="N9" s="71"/>
-      <c r="O9" s="71">
-        <v>395</v>
-      </c>
+      <c r="O9" s="71"/>
       <c r="P9" s="71"/>
       <c r="Q9" s="71"/>
       <c r="R9" s="71"/>
-      <c r="S9" s="71">
-        <v>700</v>
-      </c>
+      <c r="S9" s="71"/>
       <c r="T9" s="71"/>
       <c r="U9" s="71"/>
       <c r="V9" s="71"/>
       <c r="W9" s="71"/>
-      <c r="X9" s="105">
+      <c r="X9" s="87">
         <f t="shared" si="0"/>
-        <v>1095</v>
-      </c>
-      <c r="Y9" s="111"/>
-      <c r="Z9" s="108"/>
+        <v>0</v>
+      </c>
+      <c r="Y9" s="145"/>
+      <c r="Z9" s="131"/>
     </row>
     <row r="10" spans="1:48" ht="15.75">
       <c r="A10" s="66">
@@ -17869,9 +16900,7 @@
       </c>
       <c r="C10" s="72"/>
       <c r="D10" s="72"/>
-      <c r="E10" s="72">
-        <v>2500</v>
-      </c>
+      <c r="E10" s="72"/>
       <c r="F10" s="72"/>
       <c r="G10" s="72"/>
       <c r="H10" s="72"/>
@@ -17881,28 +16910,21 @@
       <c r="L10" s="72"/>
       <c r="M10" s="72"/>
       <c r="N10" s="72"/>
-      <c r="O10" s="72">
-        <f>473+161</f>
-        <v>634</v>
-      </c>
+      <c r="O10" s="72"/>
       <c r="P10" s="72"/>
       <c r="Q10" s="72"/>
       <c r="R10" s="72"/>
-      <c r="S10" s="72">
-        <v>990</v>
-      </c>
-      <c r="T10" s="72">
-        <v>790</v>
-      </c>
+      <c r="S10" s="72"/>
+      <c r="T10" s="72"/>
       <c r="U10" s="72"/>
       <c r="V10" s="72"/>
       <c r="W10" s="72"/>
-      <c r="X10" s="106">
+      <c r="X10" s="88">
         <f t="shared" si="0"/>
-        <v>4914</v>
-      </c>
-      <c r="Y10" s="111"/>
-      <c r="Z10" s="108"/>
+        <v>0</v>
+      </c>
+      <c r="Y10" s="145"/>
+      <c r="Z10" s="131"/>
     </row>
     <row r="11" spans="1:48" ht="15.75">
       <c r="A11" s="62">
@@ -17911,18 +16933,13 @@
       <c r="B11" s="63" t="s">
         <v>5</v>
       </c>
-      <c r="C11" s="71">
-        <f>132.68+3500</f>
-        <v>3632.68</v>
-      </c>
+      <c r="C11" s="71"/>
       <c r="D11" s="71"/>
       <c r="E11" s="71"/>
       <c r="F11" s="71"/>
       <c r="G11" s="71"/>
       <c r="H11" s="71"/>
-      <c r="I11" s="71">
-        <v>1000</v>
-      </c>
+      <c r="I11" s="71"/>
       <c r="J11" s="71"/>
       <c r="K11" s="71"/>
       <c r="L11" s="71"/>
@@ -17937,12 +16954,12 @@
       <c r="U11" s="71"/>
       <c r="V11" s="71"/>
       <c r="W11" s="71"/>
-      <c r="X11" s="105">
+      <c r="X11" s="87">
         <f t="shared" si="0"/>
-        <v>4632.68</v>
-      </c>
-      <c r="Y11" s="111"/>
-      <c r="Z11" s="108"/>
+        <v>0</v>
+      </c>
+      <c r="Y11" s="145"/>
+      <c r="Z11" s="131"/>
     </row>
     <row r="12" spans="1:48" ht="15.75">
       <c r="A12" s="66">
@@ -17965,21 +16982,19 @@
       <c r="N12" s="72"/>
       <c r="O12" s="72"/>
       <c r="P12" s="72"/>
-      <c r="Q12" s="72">
-        <v>4475</v>
-      </c>
+      <c r="Q12" s="72"/>
       <c r="R12" s="72"/>
       <c r="S12" s="72"/>
       <c r="T12" s="72"/>
       <c r="U12" s="72"/>
       <c r="V12" s="72"/>
       <c r="W12" s="72"/>
-      <c r="X12" s="106">
+      <c r="X12" s="88">
         <f t="shared" si="0"/>
-        <v>4475</v>
-      </c>
-      <c r="Y12" s="111"/>
-      <c r="Z12" s="108"/>
+        <v>0</v>
+      </c>
+      <c r="Y12" s="145"/>
+      <c r="Z12" s="131"/>
     </row>
     <row r="13" spans="1:48" ht="15.75">
       <c r="A13" s="62">
@@ -18000,27 +17015,21 @@
       <c r="L13" s="71"/>
       <c r="M13" s="71"/>
       <c r="N13" s="71"/>
-      <c r="O13" s="71">
-        <v>303</v>
-      </c>
+      <c r="O13" s="71"/>
       <c r="P13" s="71"/>
-      <c r="Q13" s="71">
-        <v>2870</v>
-      </c>
+      <c r="Q13" s="71"/>
       <c r="R13" s="71"/>
-      <c r="S13" s="71">
-        <v>842.63</v>
-      </c>
+      <c r="S13" s="71"/>
       <c r="T13" s="71"/>
       <c r="U13" s="71"/>
       <c r="V13" s="71"/>
       <c r="W13" s="71"/>
-      <c r="X13" s="105">
+      <c r="X13" s="87">
         <f t="shared" si="0"/>
-        <v>4015.63</v>
-      </c>
-      <c r="Y13" s="111"/>
-      <c r="Z13" s="108"/>
+        <v>0</v>
+      </c>
+      <c r="Y13" s="145"/>
+      <c r="Z13" s="131"/>
     </row>
     <row r="14" spans="1:48" ht="15.75">
       <c r="A14" s="66">
@@ -18029,10 +17038,7 @@
       <c r="B14" s="67" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="72">
-        <f>219+2054.78</f>
-        <v>2273.7800000000002</v>
-      </c>
+      <c r="C14" s="72"/>
       <c r="D14" s="72"/>
       <c r="E14" s="72"/>
       <c r="F14" s="72"/>
@@ -18053,15 +17059,12 @@
       <c r="U14" s="72"/>
       <c r="V14" s="72"/>
       <c r="W14" s="72"/>
-      <c r="X14" s="106">
+      <c r="X14" s="88">
         <f t="shared" si="0"/>
-        <v>2273.7800000000002</v>
-      </c>
-      <c r="Y14" s="114">
-        <f>37634-14878.51</f>
-        <v>22755.489999999998</v>
-      </c>
-      <c r="Z14" s="108"/>
+        <v>0</v>
+      </c>
+      <c r="Y14" s="146"/>
+      <c r="Z14" s="131"/>
     </row>
     <row r="15" spans="1:48" ht="15.75">
       <c r="A15" s="62">
@@ -18070,12 +17073,8 @@
       <c r="B15" s="63" t="s">
         <v>2</v>
       </c>
-      <c r="C15" s="71">
-        <v>364</v>
-      </c>
-      <c r="D15" s="71">
-        <v>584</v>
-      </c>
+      <c r="C15" s="71"/>
+      <c r="D15" s="71"/>
       <c r="E15" s="71"/>
       <c r="F15" s="71"/>
       <c r="G15" s="71"/>
@@ -18086,28 +17085,21 @@
       <c r="L15" s="71"/>
       <c r="M15" s="71"/>
       <c r="N15" s="71"/>
-      <c r="O15" s="71">
-        <v>328</v>
-      </c>
+      <c r="O15" s="71"/>
       <c r="P15" s="71"/>
-      <c r="Q15" s="71">
-        <f>1500+1120.98</f>
-        <v>2620.98</v>
-      </c>
+      <c r="Q15" s="71"/>
       <c r="R15" s="71"/>
-      <c r="S15" s="71">
-        <v>200</v>
-      </c>
+      <c r="S15" s="71"/>
       <c r="T15" s="71"/>
       <c r="U15" s="71"/>
       <c r="V15" s="71"/>
       <c r="W15" s="71"/>
-      <c r="X15" s="105">
+      <c r="X15" s="87">
         <f t="shared" si="0"/>
-        <v>4096.9799999999996</v>
-      </c>
-      <c r="Y15" s="111"/>
-      <c r="Z15" s="108"/>
+        <v>0</v>
+      </c>
+      <c r="Y15" s="145"/>
+      <c r="Z15" s="131"/>
     </row>
     <row r="16" spans="1:48" ht="15.75">
       <c r="A16" s="66">
@@ -18119,9 +17111,7 @@
       <c r="C16" s="72"/>
       <c r="D16" s="72"/>
       <c r="E16" s="72"/>
-      <c r="F16" s="72">
-        <v>1080</v>
-      </c>
+      <c r="F16" s="72"/>
       <c r="G16" s="72"/>
       <c r="H16" s="72"/>
       <c r="I16" s="72"/>
@@ -18130,25 +17120,21 @@
       <c r="L16" s="72"/>
       <c r="M16" s="72"/>
       <c r="N16" s="72"/>
-      <c r="O16" s="72">
-        <v>413</v>
-      </c>
+      <c r="O16" s="72"/>
       <c r="P16" s="72"/>
       <c r="Q16" s="72"/>
       <c r="R16" s="72"/>
       <c r="S16" s="72"/>
-      <c r="T16" s="72">
-        <v>1100</v>
-      </c>
-      <c r="U16" s="87"/>
+      <c r="T16" s="72"/>
+      <c r="U16" s="86"/>
       <c r="V16" s="72"/>
       <c r="W16" s="72"/>
-      <c r="X16" s="106">
+      <c r="X16" s="88">
         <f t="shared" si="0"/>
-        <v>2593</v>
-      </c>
-      <c r="Y16" s="111"/>
-      <c r="Z16" s="108"/>
+        <v>0</v>
+      </c>
+      <c r="Y16" s="145"/>
+      <c r="Z16" s="131"/>
     </row>
     <row r="17" spans="1:28" ht="15.75">
       <c r="A17" s="62">
@@ -18173,21 +17159,17 @@
       <c r="P17" s="71"/>
       <c r="Q17" s="71"/>
       <c r="R17" s="71"/>
-      <c r="S17" s="71">
-        <v>700</v>
-      </c>
+      <c r="S17" s="71"/>
       <c r="T17" s="71"/>
       <c r="U17" s="71"/>
       <c r="V17" s="71"/>
       <c r="W17" s="71"/>
-      <c r="X17" s="105">
+      <c r="X17" s="87">
         <f t="shared" si="0"/>
-        <v>700</v>
-      </c>
-      <c r="Y17" s="112">
-        <v>15000</v>
-      </c>
-      <c r="Z17" s="108"/>
+        <v>0</v>
+      </c>
+      <c r="Y17" s="145"/>
+      <c r="Z17" s="131"/>
     </row>
     <row r="18" spans="1:28" ht="15.75">
       <c r="A18" s="66">
@@ -18197,9 +17179,7 @@
         <v>5</v>
       </c>
       <c r="C18" s="72"/>
-      <c r="D18" s="72">
-        <v>2018.8</v>
-      </c>
+      <c r="D18" s="72"/>
       <c r="E18" s="72"/>
       <c r="F18" s="72"/>
       <c r="G18" s="72"/>
@@ -18214,21 +17194,17 @@
       <c r="P18" s="72"/>
       <c r="Q18" s="72"/>
       <c r="R18" s="72"/>
-      <c r="S18" s="72">
-        <v>499</v>
-      </c>
-      <c r="T18" s="87"/>
-      <c r="U18" s="72">
-        <v>8000</v>
-      </c>
+      <c r="S18" s="72"/>
+      <c r="T18" s="86"/>
+      <c r="U18" s="72"/>
       <c r="V18" s="72"/>
       <c r="W18" s="72"/>
-      <c r="X18" s="106">
+      <c r="X18" s="88">
         <f t="shared" si="0"/>
-        <v>10517.8</v>
-      </c>
-      <c r="Y18" s="111"/>
-      <c r="Z18" s="108"/>
+        <v>0</v>
+      </c>
+      <c r="Y18" s="145"/>
+      <c r="Z18" s="131"/>
     </row>
     <row r="19" spans="1:28" ht="15.75">
       <c r="A19" s="62">
@@ -18238,12 +17214,8 @@
         <v>6</v>
       </c>
       <c r="C19" s="71"/>
-      <c r="D19" s="71">
-        <v>2376.09</v>
-      </c>
-      <c r="E19" s="71">
-        <v>3600</v>
-      </c>
+      <c r="D19" s="71"/>
+      <c r="E19" s="71"/>
       <c r="F19" s="71"/>
       <c r="G19" s="71"/>
       <c r="H19" s="71"/>
@@ -18260,40 +17232,35 @@
       <c r="S19" s="71"/>
       <c r="T19" s="71"/>
       <c r="U19" s="71"/>
-      <c r="V19" s="71">
-        <f>83+760+400+6869+83+83+1800+850+1033.84+1423+1349+694+83+6000+1800+305</f>
-        <v>23615.84</v>
-      </c>
+      <c r="V19" s="71"/>
       <c r="W19" s="71"/>
-      <c r="X19" s="105">
+      <c r="X19" s="87">
         <f t="shared" si="0"/>
-        <v>29591.93</v>
-      </c>
-      <c r="Y19" s="112">
-        <v>10000</v>
-      </c>
-      <c r="Z19" s="109"/>
+        <v>0</v>
+      </c>
+      <c r="Y19" s="145"/>
+      <c r="Z19" s="132"/>
     </row>
     <row r="20" spans="1:28" ht="14.25" customHeight="1">
-      <c r="A20" s="99" t="s">
+      <c r="A20" s="123" t="s">
         <v>35</v>
       </c>
-      <c r="B20" s="99"/>
+      <c r="B20" s="123"/>
       <c r="C20" s="79">
         <f t="shared" ref="C20:Y20" si="1">SUM(C3:C17)</f>
-        <v>10242.99</v>
+        <v>0</v>
       </c>
       <c r="D20" s="79">
         <f t="shared" si="1"/>
-        <v>5525.25</v>
+        <v>0</v>
       </c>
       <c r="E20" s="79">
         <f t="shared" si="1"/>
-        <v>2500</v>
+        <v>0</v>
       </c>
       <c r="F20" s="79">
         <f t="shared" si="1"/>
-        <v>2040</v>
+        <v>0</v>
       </c>
       <c r="G20" s="79">
         <f t="shared" si="1"/>
@@ -18301,11 +17268,11 @@
       </c>
       <c r="H20" s="79">
         <f t="shared" si="1"/>
-        <v>3760</v>
+        <v>0</v>
       </c>
       <c r="I20" s="79">
         <f t="shared" si="1"/>
-        <v>2320.98</v>
+        <v>0</v>
       </c>
       <c r="J20" s="79">
         <f t="shared" si="1"/>
@@ -18317,7 +17284,7 @@
       </c>
       <c r="L20" s="79">
         <f t="shared" si="1"/>
-        <v>3150</v>
+        <v>0</v>
       </c>
       <c r="M20" s="79">
         <f t="shared" si="1"/>
@@ -18329,7 +17296,7 @@
       </c>
       <c r="O20" s="79">
         <f t="shared" si="1"/>
-        <v>2999</v>
+        <v>0</v>
       </c>
       <c r="P20" s="79">
         <f t="shared" si="1"/>
@@ -18337,7 +17304,7 @@
       </c>
       <c r="Q20" s="79">
         <f t="shared" si="1"/>
-        <v>21145.98</v>
+        <v>0</v>
       </c>
       <c r="R20" s="79">
         <f t="shared" si="1"/>
@@ -18345,11 +17312,11 @@
       </c>
       <c r="S20" s="79">
         <f t="shared" si="1"/>
-        <v>5272.63</v>
+        <v>0</v>
       </c>
       <c r="T20" s="79">
         <f t="shared" si="1"/>
-        <v>2288</v>
+        <v>0</v>
       </c>
       <c r="U20" s="79">
         <f t="shared" si="1"/>
@@ -18357,20 +17324,20 @@
       </c>
       <c r="V20" s="79">
         <f t="shared" si="1"/>
-        <v>950</v>
+        <v>0</v>
       </c>
       <c r="W20" s="79"/>
-      <c r="X20" s="82">
+      <c r="X20" s="81">
         <f t="shared" si="1"/>
-        <v>62194.829999999987</v>
-      </c>
-      <c r="Y20" s="113">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="90">
         <f t="shared" si="1"/>
-        <v>113659.82499999998</v>
-      </c>
-      <c r="Z20" s="83">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="82">
         <f>Y20-X20</f>
-        <v>51464.994999999995</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:28" ht="15.75">
@@ -18380,14 +17347,10 @@
       <c r="B21" s="63" t="s">
         <v>7</v>
       </c>
-      <c r="C21" s="71">
-        <v>44</v>
-      </c>
+      <c r="C21" s="71"/>
       <c r="D21" s="71"/>
       <c r="E21" s="71"/>
-      <c r="F21" s="71">
-        <v>1770</v>
-      </c>
+      <c r="F21" s="71"/>
       <c r="G21" s="71"/>
       <c r="H21" s="71"/>
       <c r="I21" s="71"/>
@@ -18396,26 +17359,18 @@
       <c r="L21" s="71"/>
       <c r="M21" s="71"/>
       <c r="N21" s="71"/>
-      <c r="O21" s="71">
-        <v>572</v>
-      </c>
+      <c r="O21" s="71"/>
       <c r="P21" s="71"/>
-      <c r="Q21" s="71">
-        <v>3400</v>
-      </c>
+      <c r="Q21" s="71"/>
       <c r="R21" s="71"/>
       <c r="S21" s="71"/>
-      <c r="T21" s="71">
-        <v>856</v>
-      </c>
+      <c r="T21" s="71"/>
       <c r="U21" s="71"/>
       <c r="V21" s="71"/>
       <c r="W21" s="71"/>
-      <c r="X21" s="105"/>
-      <c r="Y21" s="114">
-        <v>36898.639999999999</v>
-      </c>
-      <c r="Z21" s="107"/>
+      <c r="X21" s="87"/>
+      <c r="Y21" s="146"/>
+      <c r="Z21" s="130"/>
     </row>
     <row r="22" spans="1:28" ht="15.75">
       <c r="A22" s="66">
@@ -18424,13 +17379,8 @@
       <c r="B22" s="67" t="s">
         <v>8</v>
       </c>
-      <c r="C22" s="72">
-        <f>80</f>
-        <v>80</v>
-      </c>
-      <c r="D22" s="72">
-        <v>883</v>
-      </c>
+      <c r="C22" s="72"/>
+      <c r="D22" s="72"/>
       <c r="E22" s="72"/>
       <c r="F22" s="72"/>
       <c r="G22" s="72"/>
@@ -18441,24 +17391,18 @@
       <c r="L22" s="72"/>
       <c r="M22" s="72"/>
       <c r="N22" s="72"/>
-      <c r="O22" s="72">
-        <v>334</v>
-      </c>
+      <c r="O22" s="72"/>
       <c r="P22" s="72"/>
       <c r="Q22" s="72"/>
       <c r="R22" s="72"/>
       <c r="S22" s="72"/>
-      <c r="T22" s="72">
-        <v>79</v>
-      </c>
+      <c r="T22" s="72"/>
       <c r="U22" s="72"/>
       <c r="V22" s="72"/>
-      <c r="W22" s="104">
-        <v>23662.84</v>
-      </c>
-      <c r="X22" s="106"/>
-      <c r="Y22" s="111"/>
-      <c r="Z22" s="108"/>
+      <c r="W22" s="72"/>
+      <c r="X22" s="88"/>
+      <c r="Y22" s="145"/>
+      <c r="Z22" s="131"/>
       <c r="AB22" s="44"/>
     </row>
     <row r="23" spans="1:28" ht="15.75">
@@ -18469,13 +17413,9 @@
         <v>2</v>
       </c>
       <c r="C23" s="71"/>
-      <c r="D23" s="71">
-        <v>162</v>
-      </c>
+      <c r="D23" s="71"/>
       <c r="E23" s="71"/>
-      <c r="F23" s="71">
-        <v>690</v>
-      </c>
+      <c r="F23" s="71"/>
       <c r="G23" s="71"/>
       <c r="H23" s="71"/>
       <c r="I23" s="71"/>
@@ -18484,22 +17424,18 @@
       <c r="L23" s="71"/>
       <c r="M23" s="71"/>
       <c r="N23" s="71"/>
-      <c r="O23" s="71">
-        <v>325</v>
-      </c>
+      <c r="O23" s="71"/>
       <c r="P23" s="71"/>
       <c r="Q23" s="71"/>
       <c r="R23" s="71"/>
-      <c r="S23" s="71">
-        <v>843</v>
-      </c>
+      <c r="S23" s="71"/>
       <c r="T23" s="71"/>
       <c r="U23" s="71"/>
       <c r="V23" s="71"/>
       <c r="W23" s="71"/>
-      <c r="X23" s="105"/>
-      <c r="Y23" s="111"/>
-      <c r="Z23" s="108"/>
+      <c r="X23" s="87"/>
+      <c r="Y23" s="145"/>
+      <c r="Z23" s="131"/>
     </row>
     <row r="24" spans="1:28" ht="15.75">
       <c r="A24" s="66">
@@ -18509,13 +17445,9 @@
         <v>3</v>
       </c>
       <c r="C24" s="72"/>
-      <c r="D24" s="72">
-        <v>192</v>
-      </c>
+      <c r="D24" s="72"/>
       <c r="E24" s="72"/>
-      <c r="F24" s="72">
-        <v>1960</v>
-      </c>
+      <c r="F24" s="72"/>
       <c r="G24" s="72"/>
       <c r="H24" s="72"/>
       <c r="I24" s="72"/>
@@ -18524,23 +17456,18 @@
       <c r="L24" s="72"/>
       <c r="M24" s="72"/>
       <c r="N24" s="72"/>
-      <c r="O24" s="72">
-        <f>537+185</f>
-        <v>722</v>
-      </c>
+      <c r="O24" s="72"/>
       <c r="P24" s="72"/>
-      <c r="Q24" s="72">
-        <v>1000</v>
-      </c>
+      <c r="Q24" s="72"/>
       <c r="R24" s="72"/>
       <c r="S24" s="72"/>
       <c r="T24" s="72"/>
       <c r="U24" s="72"/>
       <c r="V24" s="72"/>
       <c r="W24" s="72"/>
-      <c r="X24" s="106"/>
-      <c r="Y24" s="111"/>
-      <c r="Z24" s="108"/>
+      <c r="X24" s="88"/>
+      <c r="Y24" s="145"/>
+      <c r="Z24" s="131"/>
     </row>
     <row r="25" spans="1:28" ht="15.75">
       <c r="A25" s="62">
@@ -18550,16 +17477,11 @@
         <v>4</v>
       </c>
       <c r="C25" s="71"/>
-      <c r="D25" s="71">
-        <f>1377+2099.31-149</f>
-        <v>3327.31</v>
-      </c>
+      <c r="D25" s="71"/>
       <c r="E25" s="71"/>
       <c r="F25" s="71"/>
       <c r="G25" s="71"/>
-      <c r="H25" s="71">
-        <v>2414</v>
-      </c>
+      <c r="H25" s="71"/>
       <c r="I25" s="71"/>
       <c r="J25" s="71"/>
       <c r="K25" s="71"/>
@@ -18567,21 +17489,17 @@
       <c r="M25" s="71"/>
       <c r="N25" s="71"/>
       <c r="O25" s="71"/>
-      <c r="P25" s="71">
-        <v>152</v>
-      </c>
+      <c r="P25" s="71"/>
       <c r="Q25" s="71"/>
       <c r="R25" s="71"/>
       <c r="S25" s="71"/>
       <c r="T25" s="71"/>
       <c r="U25" s="71"/>
-      <c r="V25" s="71">
-        <v>2000</v>
-      </c>
+      <c r="V25" s="71"/>
       <c r="W25" s="71"/>
-      <c r="X25" s="105"/>
-      <c r="Y25" s="111"/>
-      <c r="Z25" s="108"/>
+      <c r="X25" s="87"/>
+      <c r="Y25" s="145"/>
+      <c r="Z25" s="131"/>
     </row>
     <row r="26" spans="1:28" ht="15.75">
       <c r="A26" s="66">
@@ -18590,12 +17508,8 @@
       <c r="B26" s="67" t="s">
         <v>5</v>
       </c>
-      <c r="C26" s="72">
-        <v>3084</v>
-      </c>
-      <c r="D26" s="72">
-        <v>245</v>
-      </c>
+      <c r="C26" s="72"/>
+      <c r="D26" s="72"/>
       <c r="E26" s="72"/>
       <c r="F26" s="72"/>
       <c r="G26" s="72"/>
@@ -18615,9 +17529,9 @@
       <c r="U26" s="72"/>
       <c r="V26" s="72"/>
       <c r="W26" s="72"/>
-      <c r="X26" s="106"/>
-      <c r="Y26" s="111"/>
-      <c r="Z26" s="108"/>
+      <c r="X26" s="88"/>
+      <c r="Y26" s="145"/>
+      <c r="Z26" s="131"/>
     </row>
     <row r="27" spans="1:28" ht="15.75">
       <c r="A27" s="62">
@@ -18626,15 +17540,9 @@
       <c r="B27" s="63" t="s">
         <v>6</v>
       </c>
-      <c r="C27" s="71">
-        <v>185</v>
-      </c>
-      <c r="D27" s="71">
-        <v>1332</v>
-      </c>
-      <c r="E27" s="71">
-        <v>3180</v>
-      </c>
+      <c r="C27" s="71"/>
+      <c r="D27" s="71"/>
+      <c r="E27" s="71"/>
       <c r="F27" s="71"/>
       <c r="G27" s="71"/>
       <c r="H27" s="71"/>
@@ -18651,15 +17559,11 @@
       <c r="S27" s="71"/>
       <c r="T27" s="71"/>
       <c r="U27" s="71"/>
-      <c r="V27" s="71">
-        <v>2800</v>
-      </c>
+      <c r="V27" s="71"/>
       <c r="W27" s="71"/>
-      <c r="X27" s="105"/>
-      <c r="Y27" s="114">
-        <v>20000</v>
-      </c>
-      <c r="Z27" s="108"/>
+      <c r="X27" s="87"/>
+      <c r="Y27" s="146"/>
+      <c r="Z27" s="131"/>
     </row>
     <row r="28" spans="1:28" ht="15.75">
       <c r="A28" s="66">
@@ -18681,24 +17585,17 @@
       <c r="M28" s="72"/>
       <c r="N28" s="72"/>
       <c r="O28" s="72"/>
-      <c r="P28" s="72">
-        <v>338</v>
-      </c>
+      <c r="P28" s="72"/>
       <c r="Q28" s="72"/>
       <c r="R28" s="72"/>
-      <c r="S28" s="72">
-        <v>249</v>
-      </c>
-      <c r="T28" s="72">
-        <f>3790+3780+3004</f>
-        <v>10574</v>
-      </c>
+      <c r="S28" s="72"/>
+      <c r="T28" s="72"/>
       <c r="U28" s="72"/>
       <c r="V28" s="72"/>
       <c r="W28" s="72"/>
-      <c r="X28" s="106"/>
-      <c r="Y28" s="111"/>
-      <c r="Z28" s="108"/>
+      <c r="X28" s="88"/>
+      <c r="Y28" s="145"/>
+      <c r="Z28" s="131"/>
     </row>
     <row r="29" spans="1:28" ht="15.75">
       <c r="A29" s="62">
@@ -18720,21 +17617,17 @@
       <c r="M29" s="71"/>
       <c r="N29" s="71"/>
       <c r="O29" s="71"/>
-      <c r="P29" s="71">
-        <v>307</v>
-      </c>
-      <c r="Q29" s="71">
-        <v>1223</v>
-      </c>
+      <c r="P29" s="71"/>
+      <c r="Q29" s="71"/>
       <c r="R29" s="71"/>
       <c r="S29" s="71"/>
       <c r="T29" s="71"/>
       <c r="U29" s="71"/>
       <c r="V29" s="71"/>
       <c r="W29" s="71"/>
-      <c r="X29" s="105"/>
-      <c r="Y29" s="111"/>
-      <c r="Z29" s="108"/>
+      <c r="X29" s="87"/>
+      <c r="Y29" s="145"/>
+      <c r="Z29" s="131"/>
     </row>
     <row r="30" spans="1:28" ht="15.75">
       <c r="A30" s="66">
@@ -18757,18 +17650,16 @@
       <c r="N30" s="72"/>
       <c r="O30" s="72"/>
       <c r="P30" s="72"/>
-      <c r="Q30" s="72">
-        <v>400</v>
-      </c>
+      <c r="Q30" s="72"/>
       <c r="R30" s="72"/>
       <c r="S30" s="72"/>
       <c r="T30" s="72"/>
       <c r="U30" s="72"/>
       <c r="V30" s="72"/>
       <c r="W30" s="72"/>
-      <c r="X30" s="106"/>
-      <c r="Y30" s="111"/>
-      <c r="Z30" s="108"/>
+      <c r="X30" s="88"/>
+      <c r="Y30" s="145"/>
+      <c r="Z30" s="131"/>
     </row>
     <row r="31" spans="1:28" ht="15.75">
       <c r="A31" s="62">
@@ -18798,9 +17689,9 @@
       <c r="U31" s="71"/>
       <c r="V31" s="71"/>
       <c r="W31" s="71"/>
-      <c r="X31" s="105"/>
-      <c r="Y31" s="111"/>
-      <c r="Z31" s="108"/>
+      <c r="X31" s="87"/>
+      <c r="Y31" s="145"/>
+      <c r="Z31" s="131"/>
     </row>
     <row r="32" spans="1:28" ht="15.75">
       <c r="A32" s="66">
@@ -18830,9 +17721,9 @@
       <c r="U32" s="72"/>
       <c r="V32" s="72"/>
       <c r="W32" s="72"/>
-      <c r="X32" s="106"/>
-      <c r="Y32" s="111"/>
-      <c r="Z32" s="108"/>
+      <c r="X32" s="88"/>
+      <c r="Y32" s="145"/>
+      <c r="Z32" s="131"/>
     </row>
     <row r="33" spans="1:26" ht="15.75">
       <c r="A33" s="62">
@@ -18862,9 +17753,9 @@
       <c r="U33" s="71"/>
       <c r="V33" s="71"/>
       <c r="W33" s="71"/>
-      <c r="X33" s="105"/>
-      <c r="Y33" s="111"/>
-      <c r="Z33" s="108"/>
+      <c r="X33" s="87"/>
+      <c r="Y33" s="145"/>
+      <c r="Z33" s="131"/>
     </row>
     <row r="34" spans="1:26" ht="15.75">
       <c r="A34" s="66">
@@ -18894,9 +17785,9 @@
       <c r="U34" s="72"/>
       <c r="V34" s="72"/>
       <c r="W34" s="72"/>
-      <c r="X34" s="106"/>
-      <c r="Y34" s="111"/>
-      <c r="Z34" s="108"/>
+      <c r="X34" s="88"/>
+      <c r="Y34" s="145"/>
+      <c r="Z34" s="131"/>
     </row>
     <row r="35" spans="1:26" ht="15.75">
       <c r="A35" s="62">
@@ -18926,9 +17817,9 @@
       <c r="U35" s="71"/>
       <c r="V35" s="71"/>
       <c r="W35" s="71"/>
-      <c r="X35" s="105"/>
-      <c r="Y35" s="111"/>
-      <c r="Z35" s="108"/>
+      <c r="X35" s="87"/>
+      <c r="Y35" s="145"/>
+      <c r="Z35" s="131"/>
     </row>
     <row r="36" spans="1:26" ht="15.75">
       <c r="A36" s="66">
@@ -18958,30 +17849,30 @@
       <c r="U36" s="72"/>
       <c r="V36" s="72"/>
       <c r="W36" s="72"/>
-      <c r="X36" s="106"/>
-      <c r="Y36" s="111"/>
-      <c r="Z36" s="109"/>
+      <c r="X36" s="88"/>
+      <c r="Y36" s="145"/>
+      <c r="Z36" s="132"/>
     </row>
     <row r="37" spans="1:26">
-      <c r="A37" s="99" t="s">
+      <c r="A37" s="123" t="s">
         <v>36</v>
       </c>
-      <c r="B37" s="99"/>
+      <c r="B37" s="123"/>
       <c r="C37" s="79">
         <f>SUM(C21:C36)</f>
-        <v>3393</v>
+        <v>0</v>
       </c>
       <c r="D37" s="79">
         <f t="shared" ref="D37:V37" si="2">SUM(D21:D36)</f>
-        <v>6141.3099999999995</v>
+        <v>0</v>
       </c>
       <c r="E37" s="79">
         <f t="shared" si="2"/>
-        <v>3180</v>
+        <v>0</v>
       </c>
       <c r="F37" s="79">
         <f t="shared" si="2"/>
-        <v>4420</v>
+        <v>0</v>
       </c>
       <c r="G37" s="79">
         <f t="shared" si="2"/>
@@ -18989,7 +17880,7 @@
       </c>
       <c r="H37" s="79">
         <f t="shared" si="2"/>
-        <v>2414</v>
+        <v>0</v>
       </c>
       <c r="I37" s="79">
         <f t="shared" si="2"/>
@@ -19017,15 +17908,15 @@
       </c>
       <c r="O37" s="79">
         <f t="shared" si="2"/>
-        <v>1953</v>
+        <v>0</v>
       </c>
       <c r="P37" s="79">
         <f t="shared" si="2"/>
-        <v>797</v>
+        <v>0</v>
       </c>
       <c r="Q37" s="79">
         <f t="shared" si="2"/>
-        <v>6023</v>
+        <v>0</v>
       </c>
       <c r="R37" s="79">
         <f t="shared" si="2"/>
@@ -19033,11 +17924,11 @@
       </c>
       <c r="S37" s="79">
         <f t="shared" si="2"/>
-        <v>1092</v>
+        <v>0</v>
       </c>
       <c r="T37" s="79">
         <f>SUM(T21:T36)</f>
-        <v>11509</v>
+        <v>0</v>
       </c>
       <c r="U37" s="79">
         <f t="shared" si="2"/>
@@ -19045,42 +17936,42 @@
       </c>
       <c r="V37" s="79">
         <f t="shared" si="2"/>
-        <v>4800</v>
+        <v>0</v>
       </c>
       <c r="W37" s="79"/>
-      <c r="X37" s="82">
+      <c r="X37" s="81">
         <f>SUM(X21:X36)</f>
         <v>0</v>
       </c>
-      <c r="Y37" s="110">
+      <c r="Y37" s="89">
         <f>SUM(Y21:Y36)</f>
-        <v>56898.64</v>
-      </c>
-      <c r="Z37" s="84">
+        <v>0</v>
+      </c>
+      <c r="Z37" s="83">
         <f>Y37-X37</f>
-        <v>56898.64</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:26" ht="31.5" customHeight="1">
-      <c r="A38" s="102" t="s">
+      <c r="A38" s="128" t="s">
         <v>37</v>
       </c>
-      <c r="B38" s="102"/>
+      <c r="B38" s="128"/>
       <c r="C38" s="78">
         <f>SUM(C20,C37)</f>
-        <v>13635.99</v>
+        <v>0</v>
       </c>
       <c r="D38" s="78">
         <f t="shared" ref="D38:X38" si="3">SUM(D20,D37)</f>
-        <v>11666.56</v>
+        <v>0</v>
       </c>
       <c r="E38" s="78">
         <f t="shared" si="3"/>
-        <v>5680</v>
+        <v>0</v>
       </c>
       <c r="F38" s="78">
         <f t="shared" si="3"/>
-        <v>6460</v>
+        <v>0</v>
       </c>
       <c r="G38" s="78">
         <f t="shared" si="3"/>
@@ -19088,11 +17979,11 @@
       </c>
       <c r="H38" s="78">
         <f t="shared" si="3"/>
-        <v>6174</v>
+        <v>0</v>
       </c>
       <c r="I38" s="78">
         <f t="shared" si="3"/>
-        <v>2320.98</v>
+        <v>0</v>
       </c>
       <c r="J38" s="78">
         <f t="shared" si="3"/>
@@ -19104,7 +17995,7 @@
       </c>
       <c r="L38" s="78">
         <f t="shared" si="3"/>
-        <v>3150</v>
+        <v>0</v>
       </c>
       <c r="M38" s="78">
         <f t="shared" si="3"/>
@@ -19116,15 +18007,15 @@
       </c>
       <c r="O38" s="78">
         <f t="shared" si="3"/>
-        <v>4952</v>
+        <v>0</v>
       </c>
       <c r="P38" s="78">
         <f t="shared" si="3"/>
-        <v>797</v>
+        <v>0</v>
       </c>
       <c r="Q38" s="78">
         <f t="shared" si="3"/>
-        <v>27168.98</v>
+        <v>0</v>
       </c>
       <c r="R38" s="78">
         <f t="shared" si="3"/>
@@ -19132,11 +18023,11 @@
       </c>
       <c r="S38" s="78">
         <f>SUM(S20,S37)</f>
-        <v>6364.63</v>
+        <v>0</v>
       </c>
       <c r="T38" s="78">
         <f t="shared" si="3"/>
-        <v>13797</v>
+        <v>0</v>
       </c>
       <c r="U38" s="78">
         <f t="shared" si="3"/>
@@ -19144,20 +18035,20 @@
       </c>
       <c r="V38" s="78">
         <f t="shared" si="3"/>
-        <v>5750</v>
+        <v>0</v>
       </c>
       <c r="W38" s="78"/>
-      <c r="X38" s="85">
+      <c r="X38" s="84">
         <f t="shared" si="3"/>
-        <v>62194.829999999987</v>
-      </c>
-      <c r="Y38" s="85">
+        <v>0</v>
+      </c>
+      <c r="Y38" s="84">
         <f>SUM(Y20,Y37)</f>
-        <v>170558.46499999997</v>
-      </c>
-      <c r="Z38" s="86">
+        <v>0</v>
+      </c>
+      <c r="Z38" s="85">
         <f>SUM(Z20,Z37)</f>
-        <v>108363.63499999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:26">
@@ -19174,23 +18065,22 @@
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="A38:B38"/>
     <mergeCell ref="A1:Z1"/>
     <mergeCell ref="Z3:Z19"/>
     <mergeCell ref="A20:B20"/>
     <mergeCell ref="Z21:Z36"/>
     <mergeCell ref="A37:B37"/>
-    <mergeCell ref="A38:B38"/>
   </mergeCells>
   <conditionalFormatting sqref="Z20:Z21 Z37:Z38">
-    <cfRule type="expression" dxfId="3" priority="1">
+    <cfRule type="expression" dxfId="1" priority="1">
       <formula>Z20&lt;0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="2">
+    <cfRule type="expression" dxfId="0" priority="2">
       <formula>Z20&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/Другое/2026/Доходы-Расходы_copy.xlsx
+++ b/Другое/2026/Доходы-Расходы_copy.xlsx
@@ -4705,8 +4705,304 @@
 </comments>
 </file>
 
+<file path=xl/comments7.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Автор</author>
+  </authors>
+  <commentList>
+    <comment ref="I4" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Поход в Ла джорджию</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="O4" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>t2</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="P4" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Вернул маме долг
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="X4" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">Купил на озоне 3 двд диска.
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="L5" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+1. 5 748,49 - УК Эталон
+2. 2 803,26 - Росатом (электричество)
+3. 2 329,44 - ЕРК (вода)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="Q5" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">Плата за сантехника
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="W5" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">Перевел за такси (она сама попросила)
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J6" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Макдоналдс</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I7" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Вьет Кук</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J7" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Смузи и лимонад в окошке в боне</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="O7" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">t2
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="Z7" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Билеты в IMAX в химках</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J8" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Макдоналдс</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="W8" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Ане на такси + торт + билеты в театр + вино + цветы</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N9" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">t2
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="P9" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">Илюхе за пейнтбол
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="83">
   <si>
     <t>Число</t>
   </si>
@@ -4915,8 +5211,9 @@
         <b/>
         <sz val="20"/>
         <color theme="5" tint="-0.24994659260841701"/>
-        <rFont val="Bernard MT Condensed"/>
-        <family val="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="204"/>
       </rPr>
       <t>Август</t>
     </r>
@@ -4925,11 +5222,60 @@
         <b/>
         <sz val="20"/>
         <color theme="1" tint="4.9989318521683403E-2"/>
-        <rFont val="Bernard MT Condensed"/>
-        <family val="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="204"/>
       </rPr>
       <t xml:space="preserve"> 2026</t>
     </r>
+  </si>
+  <si>
+    <t>ЕДА</t>
+  </si>
+  <si>
+    <t>Ярче</t>
+  </si>
+  <si>
+    <t>Магнит/Пятерочка</t>
+  </si>
+  <si>
+    <t>Перекресток</t>
+  </si>
+  <si>
+    <t>Доставка из ресторанов</t>
+  </si>
+  <si>
+    <t>Поход в ресторан</t>
+  </si>
+  <si>
+    <t>Поход в фаст фуд</t>
+  </si>
+  <si>
+    <t>Обеды</t>
+  </si>
+  <si>
+    <t>Базовые потребности (на которых не сэкономить)</t>
+  </si>
+  <si>
+    <t>Ежемесячные платежи</t>
+  </si>
+  <si>
+    <t>Дргое (форс-мажорное)</t>
+  </si>
+  <si>
+    <t>Отдых, развлечение, быт и излишки (все на чем в теории можно сэкономить)</t>
+  </si>
+  <si>
+    <t>Другое (покупки)</t>
+  </si>
+  <si>
+    <t>Друггое (развлечения)</t>
+  </si>
+  <si>
+    <t>ИТОГИ</t>
+  </si>
+  <si>
+    <t>Яндекс Лавка / Самокат</t>
   </si>
 </sst>
 </file>
@@ -4939,7 +5285,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;₽&quot;"/>
   </numFmts>
-  <fonts count="41">
+  <fonts count="46">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -5179,13 +5525,6 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Franklin Gothic Demi"/>
-      <family val="2"/>
-      <charset val="204"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <name val="Franklin Gothic Demi"/>
@@ -5222,28 +5561,73 @@
       <charset val="204"/>
     </font>
     <font>
-      <b/>
-      <sz val="20"/>
-      <color theme="1" tint="4.9989318521683403E-2"/>
-      <name val="Bernard MT Condensed"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="20"/>
-      <color theme="5" tint="-0.24994659260841701"/>
-      <name val="Bernard MT Condensed"/>
-      <family val="1"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1" tint="4.9989318521683403E-2"/>
       <name val="Franklin Gothic Demi"/>
       <family val="2"/>
       <charset val="204"/>
     </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color theme="1" tint="4.9989318521683403E-2"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color theme="5" tint="-0.24994659260841701"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1" tint="4.9989318521683403E-2"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="7" tint="-0.499984740745262"/>
+      <name val="Franklin Gothic Demi"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="9" tint="-0.499984740745262"/>
+      <name val="Franklin Gothic Demi"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Franklin Gothic Demi"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
   </fonts>
-  <fills count="32">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -5354,12 +5738,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF062D4E"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="2" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -5385,18 +5763,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC09200"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF273C18"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5430,8 +5796,50 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="23">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -5611,17 +6019,6 @@
         <color theme="1" tint="0.34998626667073579"/>
       </right>
       <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="1" tint="0.34998626667073579"/>
-      </left>
-      <right style="thin">
-        <color theme="1" tint="0.34998626667073579"/>
-      </right>
-      <top/>
       <bottom style="thin">
         <color theme="1" tint="0.34998626667073579"/>
       </bottom>
@@ -5656,37 +6053,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color theme="1" tint="0.34998626667073579"/>
-      </right>
-      <top style="thin">
-        <color theme="1" tint="0.34998626667073579"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="1" tint="0.34998626667073579"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="1" tint="0.34998626667073579"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color theme="1" tint="0.34998626667073579"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF134873"/>
       </left>
@@ -5712,10 +6078,23 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
@@ -5725,7 +6104,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="147">
+  <cellXfs count="164">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -5915,83 +6294,66 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="27" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="27" fillId="19" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="23" fillId="19" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="19" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="29" fillId="19" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="29" fillId="19" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="23" fillId="7" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="19" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="23" fillId="17" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="20" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="23" fillId="7" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="23" fillId="17" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="27" fillId="19" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="27" fillId="19" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="26" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="27" fillId="6" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="27" fillId="6" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="29" fillId="6" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="29" fillId="6" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="23" fillId="14" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="28" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="23" fillId="25" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="23" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="22" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="21" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="29" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="34" fillId="24" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="23" fillId="26" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="33" fillId="23" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="34" fillId="23" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="33" fillId="22" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="34" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="33" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="29" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="29" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="23" fillId="22" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="34" fillId="11" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="34" fillId="11" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="23" fillId="26" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="23" fillId="21" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="33" fillId="11" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="33" fillId="11" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="30" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="36" fillId="31" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="23" fillId="27" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="35" fillId="28" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -6031,12 +6393,6 @@
     <xf numFmtId="0" fontId="25" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="31" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="17" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="28" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -6046,51 +6402,129 @@
     <xf numFmtId="164" fontId="23" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="35" fillId="28" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="17" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="38" fillId="28" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="40" fillId="30" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="23" fillId="29" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="29" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="7" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="17" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="7" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="23" fillId="17" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="26" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="33" fillId="30" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="33" fillId="31" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="34" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="29" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="33" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="33" fillId="33" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="13" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="23" fillId="13" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="37" fillId="29" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="25" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="42" fillId="30" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="41" fillId="31" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="34" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="43" fillId="31" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="34" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="28" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="28" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="34" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="27" fillId="34" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="33" fillId="33" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="35" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="16" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="23" fillId="16" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="23" fillId="16" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="32" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="35" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="20" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="33" fillId="35" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="33" fillId="20" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -6438,7 +6872,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -6685,32 +7119,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:46" ht="60.75" customHeight="1">
-      <c r="A1" s="112" t="s">
+      <c r="A1" s="105" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="112"/>
-      <c r="C1" s="112"/>
-      <c r="D1" s="112"/>
-      <c r="E1" s="112"/>
-      <c r="F1" s="112"/>
-      <c r="G1" s="112"/>
-      <c r="H1" s="112"/>
-      <c r="I1" s="112"/>
-      <c r="J1" s="112"/>
-      <c r="K1" s="112"/>
-      <c r="L1" s="112"/>
-      <c r="M1" s="112"/>
-      <c r="N1" s="112"/>
-      <c r="O1" s="112"/>
-      <c r="P1" s="112"/>
-      <c r="Q1" s="112"/>
-      <c r="R1" s="112"/>
-      <c r="S1" s="112"/>
-      <c r="T1" s="112"/>
-      <c r="U1" s="112"/>
-      <c r="V1" s="112"/>
-      <c r="W1" s="112"/>
-      <c r="X1" s="112"/>
+      <c r="B1" s="105"/>
+      <c r="C1" s="105"/>
+      <c r="D1" s="105"/>
+      <c r="E1" s="105"/>
+      <c r="F1" s="105"/>
+      <c r="G1" s="105"/>
+      <c r="H1" s="105"/>
+      <c r="I1" s="105"/>
+      <c r="J1" s="105"/>
+      <c r="K1" s="105"/>
+      <c r="L1" s="105"/>
+      <c r="M1" s="105"/>
+      <c r="N1" s="105"/>
+      <c r="O1" s="105"/>
+      <c r="P1" s="105"/>
+      <c r="Q1" s="105"/>
+      <c r="R1" s="105"/>
+      <c r="S1" s="105"/>
+      <c r="T1" s="105"/>
+      <c r="U1" s="105"/>
+      <c r="V1" s="105"/>
+      <c r="W1" s="105"/>
+      <c r="X1" s="105"/>
     </row>
     <row r="2" spans="1:46" ht="45" customHeight="1">
       <c r="A2" s="3" t="s">
@@ -7909,10 +8343,10 @@
       </c>
     </row>
     <row r="31" spans="1:24">
-      <c r="A31" s="113" t="s">
+      <c r="A31" s="106" t="s">
         <v>20</v>
       </c>
-      <c r="B31" s="113"/>
+      <c r="B31" s="106"/>
       <c r="C31" s="13">
         <f>SUM(C3:C30)</f>
         <v>19992.27</v>
@@ -8035,32 +8469,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:46" ht="60.75" customHeight="1">
-      <c r="A1" s="115" t="s">
+      <c r="A1" s="108" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="115"/>
-      <c r="C1" s="115"/>
-      <c r="D1" s="115"/>
-      <c r="E1" s="115"/>
-      <c r="F1" s="115"/>
-      <c r="G1" s="115"/>
-      <c r="H1" s="115"/>
-      <c r="I1" s="115"/>
-      <c r="J1" s="115"/>
-      <c r="K1" s="115"/>
-      <c r="L1" s="115"/>
-      <c r="M1" s="115"/>
-      <c r="N1" s="115"/>
-      <c r="O1" s="115"/>
-      <c r="P1" s="115"/>
-      <c r="Q1" s="115"/>
-      <c r="R1" s="115"/>
-      <c r="S1" s="115"/>
-      <c r="T1" s="115"/>
-      <c r="U1" s="115"/>
-      <c r="V1" s="115"/>
-      <c r="W1" s="115"/>
-      <c r="X1" s="115"/>
+      <c r="B1" s="108"/>
+      <c r="C1" s="108"/>
+      <c r="D1" s="108"/>
+      <c r="E1" s="108"/>
+      <c r="F1" s="108"/>
+      <c r="G1" s="108"/>
+      <c r="H1" s="108"/>
+      <c r="I1" s="108"/>
+      <c r="J1" s="108"/>
+      <c r="K1" s="108"/>
+      <c r="L1" s="108"/>
+      <c r="M1" s="108"/>
+      <c r="N1" s="108"/>
+      <c r="O1" s="108"/>
+      <c r="P1" s="108"/>
+      <c r="Q1" s="108"/>
+      <c r="R1" s="108"/>
+      <c r="S1" s="108"/>
+      <c r="T1" s="108"/>
+      <c r="U1" s="108"/>
+      <c r="V1" s="108"/>
+      <c r="W1" s="108"/>
+      <c r="X1" s="108"/>
     </row>
     <row r="2" spans="1:46" ht="45" customHeight="1">
       <c r="A2" s="30" t="s">
@@ -9271,10 +9705,10 @@
       <c r="X31" s="31"/>
     </row>
     <row r="32" spans="1:24">
-      <c r="A32" s="114" t="s">
+      <c r="A32" s="107" t="s">
         <v>20</v>
       </c>
-      <c r="B32" s="114"/>
+      <c r="B32" s="107"/>
       <c r="C32" s="28">
         <f>SUM(C3:C31)</f>
         <v>16843.349999999999</v>
@@ -9397,33 +9831,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:47" ht="60.75" customHeight="1">
-      <c r="A1" s="115" t="s">
+      <c r="A1" s="108" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="115"/>
-      <c r="C1" s="115"/>
-      <c r="D1" s="115"/>
-      <c r="E1" s="115"/>
-      <c r="F1" s="115"/>
-      <c r="G1" s="115"/>
-      <c r="H1" s="115"/>
-      <c r="I1" s="115"/>
-      <c r="J1" s="115"/>
-      <c r="K1" s="115"/>
-      <c r="L1" s="115"/>
-      <c r="M1" s="115"/>
-      <c r="N1" s="115"/>
-      <c r="O1" s="115"/>
-      <c r="P1" s="115"/>
-      <c r="Q1" s="115"/>
-      <c r="R1" s="115"/>
-      <c r="S1" s="115"/>
-      <c r="T1" s="115"/>
-      <c r="U1" s="115"/>
-      <c r="V1" s="115"/>
-      <c r="W1" s="115"/>
-      <c r="X1" s="115"/>
-      <c r="Y1" s="115"/>
+      <c r="B1" s="108"/>
+      <c r="C1" s="108"/>
+      <c r="D1" s="108"/>
+      <c r="E1" s="108"/>
+      <c r="F1" s="108"/>
+      <c r="G1" s="108"/>
+      <c r="H1" s="108"/>
+      <c r="I1" s="108"/>
+      <c r="J1" s="108"/>
+      <c r="K1" s="108"/>
+      <c r="L1" s="108"/>
+      <c r="M1" s="108"/>
+      <c r="N1" s="108"/>
+      <c r="O1" s="108"/>
+      <c r="P1" s="108"/>
+      <c r="Q1" s="108"/>
+      <c r="R1" s="108"/>
+      <c r="S1" s="108"/>
+      <c r="T1" s="108"/>
+      <c r="U1" s="108"/>
+      <c r="V1" s="108"/>
+      <c r="W1" s="108"/>
+      <c r="X1" s="108"/>
+      <c r="Y1" s="108"/>
     </row>
     <row r="2" spans="1:47" ht="45" customHeight="1">
       <c r="A2" s="30" t="s">
@@ -10241,10 +10675,10 @@
       <c r="Y19" s="43"/>
     </row>
     <row r="20" spans="1:27">
-      <c r="A20" s="117" t="s">
+      <c r="A20" s="110" t="s">
         <v>35</v>
       </c>
-      <c r="B20" s="118"/>
+      <c r="B20" s="111"/>
       <c r="C20" s="45">
         <f>SUM(C3:C19)</f>
         <v>12278.83</v>
@@ -10964,10 +11398,10 @@
       <c r="Y35" s="43"/>
     </row>
     <row r="36" spans="1:25">
-      <c r="A36" s="117" t="s">
+      <c r="A36" s="110" t="s">
         <v>36</v>
       </c>
-      <c r="B36" s="118"/>
+      <c r="B36" s="111"/>
       <c r="C36" s="45">
         <f>SUM(C21:C35)</f>
         <v>11057.89</v>
@@ -11062,10 +11496,10 @@
       </c>
     </row>
     <row r="37" spans="1:25" ht="31.5" customHeight="1">
-      <c r="A37" s="116" t="s">
+      <c r="A37" s="109" t="s">
         <v>37</v>
       </c>
-      <c r="B37" s="116"/>
+      <c r="B37" s="109"/>
       <c r="C37" s="48">
         <f>SUM(C20,C36)</f>
         <v>23336.720000000001</v>
@@ -11195,33 +11629,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:47" ht="60.75" customHeight="1">
-      <c r="A1" s="119" t="s">
+      <c r="A1" s="112" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="119"/>
-      <c r="E1" s="119"/>
-      <c r="F1" s="119"/>
-      <c r="G1" s="119"/>
-      <c r="H1" s="119"/>
-      <c r="I1" s="119"/>
-      <c r="J1" s="119"/>
-      <c r="K1" s="119"/>
-      <c r="L1" s="119"/>
-      <c r="M1" s="119"/>
-      <c r="N1" s="119"/>
-      <c r="O1" s="119"/>
-      <c r="P1" s="119"/>
-      <c r="Q1" s="119"/>
-      <c r="R1" s="119"/>
-      <c r="S1" s="119"/>
-      <c r="T1" s="119"/>
-      <c r="U1" s="119"/>
-      <c r="V1" s="119"/>
-      <c r="W1" s="119"/>
-      <c r="X1" s="119"/>
-      <c r="Y1" s="119"/>
+      <c r="B1" s="112"/>
+      <c r="C1" s="112"/>
+      <c r="D1" s="112"/>
+      <c r="E1" s="112"/>
+      <c r="F1" s="112"/>
+      <c r="G1" s="112"/>
+      <c r="H1" s="112"/>
+      <c r="I1" s="112"/>
+      <c r="J1" s="112"/>
+      <c r="K1" s="112"/>
+      <c r="L1" s="112"/>
+      <c r="M1" s="112"/>
+      <c r="N1" s="112"/>
+      <c r="O1" s="112"/>
+      <c r="P1" s="112"/>
+      <c r="Q1" s="112"/>
+      <c r="R1" s="112"/>
+      <c r="S1" s="112"/>
+      <c r="T1" s="112"/>
+      <c r="U1" s="112"/>
+      <c r="V1" s="112"/>
+      <c r="W1" s="112"/>
+      <c r="X1" s="112"/>
+      <c r="Y1" s="112"/>
     </row>
     <row r="2" spans="1:47" ht="45" customHeight="1">
       <c r="A2" s="59" t="s">
@@ -11931,10 +12365,10 @@
       <c r="Y17" s="65"/>
     </row>
     <row r="18" spans="1:27">
-      <c r="A18" s="120" t="s">
+      <c r="A18" s="113" t="s">
         <v>35</v>
       </c>
-      <c r="B18" s="120"/>
+      <c r="B18" s="113"/>
       <c r="C18" s="73">
         <f t="shared" ref="C18:X18" si="1">SUM(C3:C17)</f>
         <v>8428.35</v>
@@ -12687,10 +13121,10 @@
       <c r="Y34" s="69"/>
     </row>
     <row r="35" spans="1:25">
-      <c r="A35" s="120" t="s">
+      <c r="A35" s="113" t="s">
         <v>36</v>
       </c>
-      <c r="B35" s="120"/>
+      <c r="B35" s="113"/>
       <c r="C35" s="73">
         <f>SUM(C19:C34)</f>
         <v>10739.46</v>
@@ -12785,10 +13219,10 @@
       </c>
     </row>
     <row r="36" spans="1:25" ht="31.5" customHeight="1">
-      <c r="A36" s="121" t="s">
+      <c r="A36" s="114" t="s">
         <v>37</v>
       </c>
-      <c r="B36" s="121"/>
+      <c r="B36" s="114"/>
       <c r="C36" s="70">
         <f>SUM(C18,C35)</f>
         <v>19167.809999999998</v>
@@ -12926,33 +13360,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:47" ht="60.75" customHeight="1">
-      <c r="A1" s="122" t="s">
+      <c r="A1" s="115" t="s">
         <v>58</v>
       </c>
-      <c r="B1" s="122"/>
-      <c r="C1" s="122"/>
-      <c r="D1" s="122"/>
-      <c r="E1" s="122"/>
-      <c r="F1" s="122"/>
-      <c r="G1" s="122"/>
-      <c r="H1" s="122"/>
-      <c r="I1" s="122"/>
-      <c r="J1" s="122"/>
-      <c r="K1" s="122"/>
-      <c r="L1" s="122"/>
-      <c r="M1" s="122"/>
-      <c r="N1" s="122"/>
-      <c r="O1" s="122"/>
-      <c r="P1" s="122"/>
-      <c r="Q1" s="122"/>
-      <c r="R1" s="122"/>
-      <c r="S1" s="122"/>
-      <c r="T1" s="122"/>
-      <c r="U1" s="122"/>
-      <c r="V1" s="122"/>
-      <c r="W1" s="122"/>
-      <c r="X1" s="122"/>
-      <c r="Y1" s="122"/>
+      <c r="B1" s="115"/>
+      <c r="C1" s="115"/>
+      <c r="D1" s="115"/>
+      <c r="E1" s="115"/>
+      <c r="F1" s="115"/>
+      <c r="G1" s="115"/>
+      <c r="H1" s="115"/>
+      <c r="I1" s="115"/>
+      <c r="J1" s="115"/>
+      <c r="K1" s="115"/>
+      <c r="L1" s="115"/>
+      <c r="M1" s="115"/>
+      <c r="N1" s="115"/>
+      <c r="O1" s="115"/>
+      <c r="P1" s="115"/>
+      <c r="Q1" s="115"/>
+      <c r="R1" s="115"/>
+      <c r="S1" s="115"/>
+      <c r="T1" s="115"/>
+      <c r="U1" s="115"/>
+      <c r="V1" s="115"/>
+      <c r="W1" s="115"/>
+      <c r="X1" s="115"/>
+      <c r="Y1" s="115"/>
     </row>
     <row r="2" spans="1:47" ht="45" customHeight="1">
       <c r="A2" s="76" t="s">
@@ -13691,10 +14125,10 @@
       <c r="Y17" s="65"/>
     </row>
     <row r="18" spans="1:27">
-      <c r="A18" s="123" t="s">
+      <c r="A18" s="116" t="s">
         <v>35</v>
       </c>
-      <c r="B18" s="123"/>
+      <c r="B18" s="116"/>
       <c r="C18" s="79">
         <f t="shared" ref="C18:X18" si="1">SUM(C3:C17)</f>
         <v>7904</v>
@@ -14342,10 +14776,10 @@
       <c r="Y34" s="69"/>
     </row>
     <row r="35" spans="1:25">
-      <c r="A35" s="123" t="s">
+      <c r="A35" s="116" t="s">
         <v>36</v>
       </c>
-      <c r="B35" s="123"/>
+      <c r="B35" s="116"/>
       <c r="C35" s="79">
         <f>SUM(C19:C34)</f>
         <v>0</v>
@@ -14440,10 +14874,10 @@
       </c>
     </row>
     <row r="36" spans="1:25" ht="31.5" customHeight="1">
-      <c r="A36" s="124" t="s">
+      <c r="A36" s="117" t="s">
         <v>37</v>
       </c>
-      <c r="B36" s="124"/>
+      <c r="B36" s="117"/>
       <c r="C36" s="74">
         <f>SUM(C18,C35)</f>
         <v>7904</v>
@@ -14583,34 +15017,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:48" ht="60.75" customHeight="1">
-      <c r="A1" s="127" t="s">
+      <c r="A1" s="118" t="s">
         <v>59</v>
       </c>
-      <c r="B1" s="127"/>
-      <c r="C1" s="127"/>
-      <c r="D1" s="127"/>
-      <c r="E1" s="127"/>
-      <c r="F1" s="127"/>
-      <c r="G1" s="127"/>
-      <c r="H1" s="127"/>
-      <c r="I1" s="127"/>
-      <c r="J1" s="127"/>
-      <c r="K1" s="127"/>
-      <c r="L1" s="127"/>
-      <c r="M1" s="127"/>
-      <c r="N1" s="127"/>
-      <c r="O1" s="127"/>
-      <c r="P1" s="127"/>
-      <c r="Q1" s="127"/>
-      <c r="R1" s="127"/>
-      <c r="S1" s="127"/>
-      <c r="T1" s="127"/>
-      <c r="U1" s="127"/>
-      <c r="V1" s="127"/>
-      <c r="W1" s="127"/>
-      <c r="X1" s="127"/>
-      <c r="Y1" s="127"/>
-      <c r="Z1" s="127"/>
+      <c r="B1" s="118"/>
+      <c r="C1" s="118"/>
+      <c r="D1" s="118"/>
+      <c r="E1" s="118"/>
+      <c r="F1" s="118"/>
+      <c r="G1" s="118"/>
+      <c r="H1" s="118"/>
+      <c r="I1" s="118"/>
+      <c r="J1" s="118"/>
+      <c r="K1" s="118"/>
+      <c r="L1" s="118"/>
+      <c r="M1" s="118"/>
+      <c r="N1" s="118"/>
+      <c r="O1" s="118"/>
+      <c r="P1" s="118"/>
+      <c r="Q1" s="118"/>
+      <c r="R1" s="118"/>
+      <c r="S1" s="118"/>
+      <c r="T1" s="118"/>
+      <c r="U1" s="118"/>
+      <c r="V1" s="118"/>
+      <c r="W1" s="118"/>
+      <c r="X1" s="118"/>
+      <c r="Y1" s="118"/>
+      <c r="Z1" s="118"/>
     </row>
     <row r="2" spans="1:48" ht="45" customHeight="1">
       <c r="A2" s="76" t="s">
@@ -14619,28 +15053,28 @@
       <c r="B2" s="76" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="91" t="s">
+      <c r="C2" s="84" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="91" t="s">
+      <c r="D2" s="84" t="s">
         <v>29</v>
       </c>
-      <c r="E2" s="91" t="s">
+      <c r="E2" s="84" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="91" t="s">
+      <c r="F2" s="84" t="s">
         <v>33</v>
       </c>
-      <c r="G2" s="91" t="s">
+      <c r="G2" s="84" t="s">
         <v>34</v>
       </c>
-      <c r="H2" s="91" t="s">
+      <c r="H2" s="84" t="s">
         <v>11</v>
       </c>
-      <c r="I2" s="91" t="s">
+      <c r="I2" s="84" t="s">
         <v>30</v>
       </c>
-      <c r="J2" s="91" t="s">
+      <c r="J2" s="84" t="s">
         <v>12</v>
       </c>
       <c r="K2" s="76" t="s">
@@ -14676,19 +15110,19 @@
       <c r="U2" s="76" t="s">
         <v>25</v>
       </c>
-      <c r="V2" s="92" t="s">
+      <c r="V2" s="85" t="s">
         <v>26</v>
       </c>
-      <c r="W2" s="95" t="s">
+      <c r="W2" s="88" t="s">
         <v>22</v>
       </c>
-      <c r="X2" s="98" t="s">
+      <c r="X2" s="91" t="s">
         <v>60</v>
       </c>
-      <c r="Y2" s="99" t="s">
+      <c r="Y2" s="92" t="s">
         <v>19</v>
       </c>
-      <c r="Z2" s="105" t="s">
+      <c r="Z2" s="98" t="s">
         <v>21</v>
       </c>
       <c r="AA2" s="1"/>
@@ -14751,19 +15185,19 @@
       </c>
       <c r="T3" s="71"/>
       <c r="U3" s="71"/>
-      <c r="V3" s="87"/>
-      <c r="W3" s="96">
+      <c r="V3" s="82"/>
+      <c r="W3" s="89">
         <f>SUM(C3:V3)</f>
         <v>14049</v>
       </c>
-      <c r="X3" s="97">
+      <c r="X3" s="90">
         <v>72082.179999999993</v>
       </c>
-      <c r="Y3" s="106">
+      <c r="Y3" s="99">
         <f>(94085+57723.67)</f>
         <v>151808.66999999998</v>
       </c>
-      <c r="Z3" s="129"/>
+      <c r="Z3" s="120"/>
     </row>
     <row r="4" spans="1:48" ht="15.75">
       <c r="A4" s="66">
@@ -14806,14 +15240,14 @@
         <v>398</v>
       </c>
       <c r="U4" s="72"/>
-      <c r="V4" s="88"/>
-      <c r="W4" s="96">
+      <c r="V4" s="83"/>
+      <c r="W4" s="89">
         <f>SUM(C4:V4)</f>
         <v>10533.31</v>
       </c>
-      <c r="X4" s="97"/>
-      <c r="Y4" s="100"/>
-      <c r="Z4" s="129"/>
+      <c r="X4" s="90"/>
+      <c r="Y4" s="93"/>
+      <c r="Z4" s="120"/>
     </row>
     <row r="5" spans="1:48" ht="15.75">
       <c r="A5" s="62">
@@ -14846,14 +15280,14 @@
       </c>
       <c r="T5" s="71"/>
       <c r="U5" s="71"/>
-      <c r="V5" s="87"/>
-      <c r="W5" s="96">
+      <c r="V5" s="82"/>
+      <c r="W5" s="89">
         <f t="shared" ref="W5:W19" si="0">SUM(C5:V5)</f>
         <v>1455</v>
       </c>
-      <c r="X5" s="97"/>
-      <c r="Y5" s="100"/>
-      <c r="Z5" s="129"/>
+      <c r="X5" s="90"/>
+      <c r="Y5" s="93"/>
+      <c r="Z5" s="120"/>
     </row>
     <row r="6" spans="1:48" ht="15.75">
       <c r="A6" s="66">
@@ -14885,16 +15319,16 @@
       <c r="S6" s="72"/>
       <c r="T6" s="72"/>
       <c r="U6" s="72"/>
-      <c r="V6" s="88">
+      <c r="V6" s="83">
         <v>950</v>
       </c>
-      <c r="W6" s="96">
+      <c r="W6" s="89">
         <f t="shared" si="0"/>
         <v>1803.8400000000001</v>
       </c>
-      <c r="X6" s="97"/>
-      <c r="Y6" s="100"/>
-      <c r="Z6" s="129"/>
+      <c r="X6" s="90"/>
+      <c r="Y6" s="93"/>
+      <c r="Z6" s="120"/>
     </row>
     <row r="7" spans="1:48" ht="15" customHeight="1">
       <c r="A7" s="62">
@@ -14931,14 +15365,14 @@
       <c r="S7" s="71"/>
       <c r="T7" s="71"/>
       <c r="U7" s="71"/>
-      <c r="V7" s="87"/>
-      <c r="W7" s="96">
+      <c r="V7" s="82"/>
+      <c r="W7" s="89">
         <f t="shared" si="0"/>
         <v>3302.61</v>
       </c>
-      <c r="X7" s="97"/>
-      <c r="Y7" s="100"/>
-      <c r="Z7" s="129"/>
+      <c r="X7" s="90"/>
+      <c r="Y7" s="93"/>
+      <c r="Z7" s="120"/>
     </row>
     <row r="8" spans="1:48" ht="15.75">
       <c r="A8" s="66">
@@ -14973,21 +15407,21 @@
       </c>
       <c r="T8" s="72"/>
       <c r="U8" s="72"/>
-      <c r="V8" s="88"/>
-      <c r="W8" s="96">
+      <c r="V8" s="83"/>
+      <c r="W8" s="89">
         <f t="shared" si="0"/>
         <v>2255</v>
       </c>
-      <c r="X8" s="97"/>
-      <c r="Y8" s="100"/>
-      <c r="Z8" s="129"/>
-      <c r="AC8" s="126" t="s">
+      <c r="X8" s="90"/>
+      <c r="Y8" s="93"/>
+      <c r="Z8" s="120"/>
+      <c r="AC8" s="122" t="s">
         <v>61</v>
       </c>
-      <c r="AD8" s="126"/>
-      <c r="AE8" s="126"/>
-      <c r="AF8" s="126"/>
-      <c r="AG8" s="126"/>
+      <c r="AD8" s="122"/>
+      <c r="AE8" s="122"/>
+      <c r="AF8" s="122"/>
+      <c r="AG8" s="122"/>
     </row>
     <row r="9" spans="1:48" ht="15.75">
       <c r="A9" s="62">
@@ -15019,19 +15453,19 @@
       </c>
       <c r="T9" s="71"/>
       <c r="U9" s="71"/>
-      <c r="V9" s="87"/>
-      <c r="W9" s="96">
+      <c r="V9" s="82"/>
+      <c r="W9" s="89">
         <f t="shared" si="0"/>
         <v>1095</v>
       </c>
-      <c r="X9" s="97"/>
-      <c r="Y9" s="100"/>
-      <c r="Z9" s="129"/>
-      <c r="AC9" s="126"/>
-      <c r="AD9" s="126"/>
-      <c r="AE9" s="126"/>
-      <c r="AF9" s="126"/>
-      <c r="AG9" s="126"/>
+      <c r="X9" s="90"/>
+      <c r="Y9" s="93"/>
+      <c r="Z9" s="120"/>
+      <c r="AC9" s="122"/>
+      <c r="AD9" s="122"/>
+      <c r="AE9" s="122"/>
+      <c r="AF9" s="122"/>
+      <c r="AG9" s="122"/>
     </row>
     <row r="10" spans="1:48" ht="15.75">
       <c r="A10" s="66">
@@ -15068,19 +15502,19 @@
         <v>790</v>
       </c>
       <c r="U10" s="72"/>
-      <c r="V10" s="88"/>
-      <c r="W10" s="96">
+      <c r="V10" s="83"/>
+      <c r="W10" s="89">
         <f t="shared" si="0"/>
         <v>4914</v>
       </c>
-      <c r="X10" s="97"/>
-      <c r="Y10" s="100"/>
-      <c r="Z10" s="129"/>
-      <c r="AC10" s="126"/>
-      <c r="AD10" s="126"/>
-      <c r="AE10" s="126"/>
-      <c r="AF10" s="126"/>
-      <c r="AG10" s="126"/>
+      <c r="X10" s="90"/>
+      <c r="Y10" s="93"/>
+      <c r="Z10" s="120"/>
+      <c r="AC10" s="122"/>
+      <c r="AD10" s="122"/>
+      <c r="AE10" s="122"/>
+      <c r="AF10" s="122"/>
+      <c r="AG10" s="122"/>
     </row>
     <row r="11" spans="1:48" ht="15.75">
       <c r="A11" s="62">
@@ -15113,21 +15547,21 @@
       <c r="S11" s="71"/>
       <c r="T11" s="71"/>
       <c r="U11" s="71"/>
-      <c r="V11" s="87"/>
-      <c r="W11" s="96">
+      <c r="V11" s="82"/>
+      <c r="W11" s="89">
         <f t="shared" si="0"/>
         <v>4632.68</v>
       </c>
-      <c r="X11" s="97"/>
-      <c r="Y11" s="100"/>
-      <c r="Z11" s="129"/>
-      <c r="AC11" s="125" t="s">
+      <c r="X11" s="90"/>
+      <c r="Y11" s="93"/>
+      <c r="Z11" s="120"/>
+      <c r="AC11" s="121" t="s">
         <v>62</v>
       </c>
-      <c r="AD11" s="125"/>
-      <c r="AE11" s="125"/>
-      <c r="AF11" s="125"/>
-      <c r="AG11" s="111">
+      <c r="AD11" s="121"/>
+      <c r="AE11" s="121"/>
+      <c r="AF11" s="121"/>
+      <c r="AG11" s="104">
         <f>Y3+Y14+Y21</f>
         <v>226341.31</v>
       </c>
@@ -15160,21 +15594,21 @@
       <c r="S12" s="72"/>
       <c r="T12" s="72"/>
       <c r="U12" s="72"/>
-      <c r="V12" s="88"/>
-      <c r="W12" s="96">
+      <c r="V12" s="83"/>
+      <c r="W12" s="89">
         <f t="shared" si="0"/>
         <v>4475</v>
       </c>
-      <c r="X12" s="97"/>
-      <c r="Y12" s="100"/>
-      <c r="Z12" s="129"/>
-      <c r="AC12" s="125" t="s">
+      <c r="X12" s="90"/>
+      <c r="Y12" s="93"/>
+      <c r="Z12" s="120"/>
+      <c r="AC12" s="121" t="s">
         <v>55</v>
       </c>
-      <c r="AD12" s="125"/>
-      <c r="AE12" s="125"/>
-      <c r="AF12" s="125"/>
-      <c r="AG12" s="111">
+      <c r="AD12" s="121"/>
+      <c r="AE12" s="121"/>
+      <c r="AF12" s="121"/>
+      <c r="AG12" s="104">
         <f>Y27</f>
         <v>20000</v>
       </c>
@@ -15211,21 +15645,21 @@
       </c>
       <c r="T13" s="71"/>
       <c r="U13" s="71"/>
-      <c r="V13" s="87"/>
-      <c r="W13" s="96">
+      <c r="V13" s="82"/>
+      <c r="W13" s="89">
         <f t="shared" si="0"/>
         <v>4015.63</v>
       </c>
-      <c r="X13" s="97"/>
-      <c r="Y13" s="100"/>
-      <c r="Z13" s="129"/>
-      <c r="AC13" s="125" t="s">
+      <c r="X13" s="90"/>
+      <c r="Y13" s="93"/>
+      <c r="Z13" s="120"/>
+      <c r="AC13" s="121" t="s">
         <v>63</v>
       </c>
-      <c r="AD13" s="125"/>
-      <c r="AE13" s="125"/>
-      <c r="AF13" s="125"/>
-      <c r="AG13" s="111">
+      <c r="AD13" s="121"/>
+      <c r="AE13" s="121"/>
+      <c r="AF13" s="121"/>
+      <c r="AG13" s="104">
         <f>Y17+Y19</f>
         <v>25000</v>
       </c>
@@ -15259,25 +15693,25 @@
       <c r="S14" s="72"/>
       <c r="T14" s="72"/>
       <c r="U14" s="72"/>
-      <c r="V14" s="88"/>
-      <c r="W14" s="96">
+      <c r="V14" s="83"/>
+      <c r="W14" s="89">
         <f t="shared" si="0"/>
         <v>2273.7800000000002</v>
       </c>
-      <c r="X14" s="97">
+      <c r="X14" s="90">
         <v>14878.51</v>
       </c>
-      <c r="Y14" s="106">
+      <c r="Y14" s="99">
         <v>37634</v>
       </c>
-      <c r="Z14" s="129"/>
-      <c r="AC14" s="125" t="s">
+      <c r="Z14" s="120"/>
+      <c r="AC14" s="121" t="s">
         <v>64</v>
       </c>
-      <c r="AD14" s="125"/>
-      <c r="AE14" s="125"/>
-      <c r="AF14" s="125"/>
-      <c r="AG14" s="111">
+      <c r="AD14" s="121"/>
+      <c r="AE14" s="121"/>
+      <c r="AF14" s="121"/>
+      <c r="AG14" s="104">
         <f>W38</f>
         <v>167654.87</v>
       </c>
@@ -15319,21 +15753,21 @@
       </c>
       <c r="T15" s="71"/>
       <c r="U15" s="71"/>
-      <c r="V15" s="87"/>
-      <c r="W15" s="96">
+      <c r="V15" s="82"/>
+      <c r="W15" s="89">
         <f t="shared" si="0"/>
         <v>4096.9799999999996</v>
       </c>
-      <c r="X15" s="97"/>
-      <c r="Y15" s="100"/>
-      <c r="Z15" s="129"/>
-      <c r="AC15" s="125" t="s">
+      <c r="X15" s="90"/>
+      <c r="Y15" s="93"/>
+      <c r="Z15" s="120"/>
+      <c r="AC15" s="121" t="s">
         <v>65</v>
       </c>
-      <c r="AD15" s="125"/>
-      <c r="AE15" s="125"/>
-      <c r="AF15" s="125"/>
-      <c r="AG15" s="111">
+      <c r="AD15" s="121"/>
+      <c r="AE15" s="121"/>
+      <c r="AF15" s="121"/>
+      <c r="AG15" s="104">
         <f>SUM(C38:H38)</f>
         <v>47166.55</v>
       </c>
@@ -15373,15 +15807,15 @@
       <c r="T16" s="72">
         <v>1200</v>
       </c>
-      <c r="U16" s="86"/>
-      <c r="V16" s="88"/>
-      <c r="W16" s="96">
+      <c r="U16" s="81"/>
+      <c r="V16" s="83"/>
+      <c r="W16" s="89">
         <f t="shared" si="0"/>
         <v>6141</v>
       </c>
-      <c r="X16" s="97"/>
-      <c r="Y16" s="100"/>
-      <c r="Z16" s="129"/>
+      <c r="X16" s="90"/>
+      <c r="Y16" s="93"/>
+      <c r="Z16" s="120"/>
     </row>
     <row r="17" spans="1:28" ht="15.75">
       <c r="A17" s="62">
@@ -15424,16 +15858,16 @@
         <f>1825+2217+2419</f>
         <v>6461</v>
       </c>
-      <c r="V17" s="87"/>
-      <c r="W17" s="96">
+      <c r="V17" s="82"/>
+      <c r="W17" s="89">
         <f t="shared" si="0"/>
         <v>16780</v>
       </c>
-      <c r="X17" s="97"/>
-      <c r="Y17" s="107">
+      <c r="X17" s="90"/>
+      <c r="Y17" s="100">
         <v>15000</v>
       </c>
-      <c r="Z17" s="129"/>
+      <c r="Z17" s="120"/>
     </row>
     <row r="18" spans="1:28" ht="15.75">
       <c r="A18" s="66">
@@ -15463,18 +15897,18 @@
       <c r="S18" s="72">
         <v>499</v>
       </c>
-      <c r="T18" s="86"/>
+      <c r="T18" s="81"/>
       <c r="U18" s="72">
         <v>8000</v>
       </c>
-      <c r="V18" s="88"/>
-      <c r="W18" s="96">
+      <c r="V18" s="83"/>
+      <c r="W18" s="89">
         <f t="shared" si="0"/>
         <v>10517.8</v>
       </c>
-      <c r="X18" s="97"/>
-      <c r="Y18" s="100"/>
-      <c r="Z18" s="129"/>
+      <c r="X18" s="90"/>
+      <c r="Y18" s="93"/>
+      <c r="Z18" s="120"/>
     </row>
     <row r="19" spans="1:28" ht="15.75">
       <c r="A19" s="62">
@@ -15506,25 +15940,25 @@
       <c r="S19" s="71"/>
       <c r="T19" s="71"/>
       <c r="U19" s="71"/>
-      <c r="V19" s="87">
+      <c r="V19" s="82">
         <f>83+760+400+6869+83+83+1800+850+1033.84+1423+1349+694+83+6000+1800+305</f>
         <v>23615.84</v>
       </c>
-      <c r="W19" s="96">
+      <c r="W19" s="89">
         <f t="shared" si="0"/>
         <v>29591.93</v>
       </c>
-      <c r="X19" s="97"/>
-      <c r="Y19" s="107">
+      <c r="X19" s="90"/>
+      <c r="Y19" s="100">
         <v>10000</v>
       </c>
-      <c r="Z19" s="129"/>
+      <c r="Z19" s="120"/>
     </row>
     <row r="20" spans="1:28" ht="14.25" customHeight="1">
-      <c r="A20" s="123" t="s">
+      <c r="A20" s="116" t="s">
         <v>35</v>
       </c>
-      <c r="B20" s="123"/>
+      <c r="B20" s="116"/>
       <c r="C20" s="79">
         <f t="shared" ref="C20:V20" si="1">SUM(C3:C17)</f>
         <v>10942.99</v>
@@ -15601,23 +16035,23 @@
         <f t="shared" si="1"/>
         <v>6461</v>
       </c>
-      <c r="V20" s="93">
+      <c r="V20" s="86">
         <f t="shared" si="1"/>
         <v>950</v>
       </c>
-      <c r="W20" s="101">
+      <c r="W20" s="94">
         <f>SUM(W3:W19)</f>
         <v>121932.56</v>
       </c>
-      <c r="X20" s="102">
+      <c r="X20" s="95">
         <f>SUM(X3:X19)</f>
         <v>86960.689999999988</v>
       </c>
-      <c r="Y20" s="108">
+      <c r="Y20" s="101">
         <f>SUM(Y3:Y19)</f>
         <v>214442.66999999998</v>
       </c>
-      <c r="Z20" s="103">
+      <c r="Z20" s="96">
         <f>Y20-W20-X20</f>
         <v>5549.4199999999983</v>
       </c>
@@ -15658,16 +16092,16 @@
         <v>856</v>
       </c>
       <c r="U21" s="71"/>
-      <c r="V21" s="87"/>
-      <c r="W21" s="96">
+      <c r="V21" s="82"/>
+      <c r="W21" s="89">
         <f>SUM(C21:V21)</f>
         <v>6642</v>
       </c>
-      <c r="X21" s="97"/>
-      <c r="Y21" s="106">
+      <c r="X21" s="90"/>
+      <c r="Y21" s="99">
         <v>36898.639999999999</v>
       </c>
-      <c r="Z21" s="129"/>
+      <c r="Z21" s="120"/>
     </row>
     <row r="22" spans="1:28" ht="15.75">
       <c r="A22" s="66">
@@ -15704,16 +16138,16 @@
         <v>79</v>
       </c>
       <c r="U22" s="72"/>
-      <c r="V22" s="88"/>
-      <c r="W22" s="96">
+      <c r="V22" s="83"/>
+      <c r="W22" s="89">
         <f t="shared" ref="W22:W36" si="2">SUM(C22:V22)</f>
         <v>1376</v>
       </c>
-      <c r="X22" s="97">
+      <c r="X22" s="90">
         <v>23662.84</v>
       </c>
-      <c r="Y22" s="100"/>
-      <c r="Z22" s="129"/>
+      <c r="Y22" s="93"/>
+      <c r="Z22" s="120"/>
       <c r="AB22" s="44"/>
     </row>
     <row r="23" spans="1:28" ht="15.75">
@@ -15750,14 +16184,14 @@
       </c>
       <c r="T23" s="71"/>
       <c r="U23" s="71"/>
-      <c r="V23" s="87"/>
-      <c r="W23" s="96">
+      <c r="V23" s="82"/>
+      <c r="W23" s="89">
         <f t="shared" si="2"/>
         <v>2020</v>
       </c>
-      <c r="X23" s="97"/>
-      <c r="Y23" s="100"/>
-      <c r="Z23" s="129"/>
+      <c r="X23" s="90"/>
+      <c r="Y23" s="93"/>
+      <c r="Z23" s="120"/>
     </row>
     <row r="24" spans="1:28" ht="15.75">
       <c r="A24" s="66">
@@ -15794,14 +16228,14 @@
       <c r="S24" s="72"/>
       <c r="T24" s="72"/>
       <c r="U24" s="72"/>
-      <c r="V24" s="88"/>
-      <c r="W24" s="96">
+      <c r="V24" s="83"/>
+      <c r="W24" s="89">
         <f t="shared" si="2"/>
         <v>3874</v>
       </c>
-      <c r="X24" s="97"/>
-      <c r="Y24" s="100"/>
-      <c r="Z24" s="129"/>
+      <c r="X24" s="90"/>
+      <c r="Y24" s="93"/>
+      <c r="Z24" s="120"/>
     </row>
     <row r="25" spans="1:28" ht="15.75">
       <c r="A25" s="62">
@@ -15836,16 +16270,16 @@
       <c r="S25" s="71"/>
       <c r="T25" s="71"/>
       <c r="U25" s="71"/>
-      <c r="V25" s="87">
+      <c r="V25" s="82">
         <v>2000</v>
       </c>
-      <c r="W25" s="96">
+      <c r="W25" s="89">
         <f t="shared" si="2"/>
         <v>7893.3099999999995</v>
       </c>
-      <c r="X25" s="97"/>
-      <c r="Y25" s="100"/>
-      <c r="Z25" s="129"/>
+      <c r="X25" s="90"/>
+      <c r="Y25" s="93"/>
+      <c r="Z25" s="120"/>
     </row>
     <row r="26" spans="1:28" ht="15.75">
       <c r="A26" s="66">
@@ -15877,14 +16311,14 @@
       <c r="S26" s="72"/>
       <c r="T26" s="72"/>
       <c r="U26" s="72"/>
-      <c r="V26" s="88"/>
-      <c r="W26" s="96">
+      <c r="V26" s="83"/>
+      <c r="W26" s="89">
         <f t="shared" si="2"/>
         <v>3329</v>
       </c>
-      <c r="X26" s="97"/>
-      <c r="Y26" s="100"/>
-      <c r="Z26" s="129"/>
+      <c r="X26" s="90"/>
+      <c r="Y26" s="93"/>
+      <c r="Z26" s="120"/>
     </row>
     <row r="27" spans="1:28" ht="15.75">
       <c r="A27" s="62">
@@ -15918,18 +16352,18 @@
       <c r="S27" s="71"/>
       <c r="T27" s="71"/>
       <c r="U27" s="71"/>
-      <c r="V27" s="87">
+      <c r="V27" s="82">
         <v>2800</v>
       </c>
-      <c r="W27" s="96">
+      <c r="W27" s="89">
         <f t="shared" si="2"/>
         <v>7497</v>
       </c>
-      <c r="X27" s="97"/>
-      <c r="Y27" s="110">
+      <c r="X27" s="90"/>
+      <c r="Y27" s="103">
         <v>20000</v>
       </c>
-      <c r="Z27" s="129"/>
+      <c r="Z27" s="120"/>
     </row>
     <row r="28" spans="1:28" ht="15.75">
       <c r="A28" s="66">
@@ -15964,14 +16398,14 @@
         <v>10574</v>
       </c>
       <c r="U28" s="72"/>
-      <c r="V28" s="88"/>
-      <c r="W28" s="96">
+      <c r="V28" s="83"/>
+      <c r="W28" s="89">
         <f t="shared" si="2"/>
         <v>11161</v>
       </c>
-      <c r="X28" s="97"/>
-      <c r="Y28" s="100"/>
-      <c r="Z28" s="129"/>
+      <c r="X28" s="90"/>
+      <c r="Y28" s="93"/>
+      <c r="Z28" s="120"/>
     </row>
     <row r="29" spans="1:28" ht="15.75">
       <c r="A29" s="62">
@@ -16003,14 +16437,14 @@
       <c r="S29" s="71"/>
       <c r="T29" s="71"/>
       <c r="U29" s="71"/>
-      <c r="V29" s="87"/>
-      <c r="W29" s="96">
+      <c r="V29" s="82"/>
+      <c r="W29" s="89">
         <f t="shared" si="2"/>
         <v>1530</v>
       </c>
-      <c r="X29" s="97"/>
-      <c r="Y29" s="100"/>
-      <c r="Z29" s="129"/>
+      <c r="X29" s="90"/>
+      <c r="Y29" s="93"/>
+      <c r="Z29" s="120"/>
     </row>
     <row r="30" spans="1:28" ht="15.75">
       <c r="A30" s="66">
@@ -16040,14 +16474,14 @@
       <c r="S30" s="72"/>
       <c r="T30" s="72"/>
       <c r="U30" s="72"/>
-      <c r="V30" s="88"/>
-      <c r="W30" s="96">
+      <c r="V30" s="83"/>
+      <c r="W30" s="89">
         <f t="shared" si="2"/>
         <v>400</v>
       </c>
-      <c r="X30" s="97"/>
-      <c r="Y30" s="100"/>
-      <c r="Z30" s="129"/>
+      <c r="X30" s="90"/>
+      <c r="Y30" s="93"/>
+      <c r="Z30" s="120"/>
     </row>
     <row r="31" spans="1:28" ht="15.75">
       <c r="A31" s="62">
@@ -16075,14 +16509,14 @@
       <c r="S31" s="71"/>
       <c r="T31" s="71"/>
       <c r="U31" s="71"/>
-      <c r="V31" s="87"/>
-      <c r="W31" s="96">
+      <c r="V31" s="82"/>
+      <c r="W31" s="89">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="X31" s="97"/>
-      <c r="Y31" s="100"/>
-      <c r="Z31" s="129"/>
+      <c r="X31" s="90"/>
+      <c r="Y31" s="93"/>
+      <c r="Z31" s="120"/>
     </row>
     <row r="32" spans="1:28" ht="15.75">
       <c r="A32" s="66">
@@ -16110,14 +16544,14 @@
       <c r="S32" s="72"/>
       <c r="T32" s="72"/>
       <c r="U32" s="72"/>
-      <c r="V32" s="88"/>
-      <c r="W32" s="96">
+      <c r="V32" s="83"/>
+      <c r="W32" s="89">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="X32" s="97"/>
-      <c r="Y32" s="100"/>
-      <c r="Z32" s="129"/>
+      <c r="X32" s="90"/>
+      <c r="Y32" s="93"/>
+      <c r="Z32" s="120"/>
     </row>
     <row r="33" spans="1:26" ht="15.75">
       <c r="A33" s="62">
@@ -16145,14 +16579,14 @@
       <c r="S33" s="71"/>
       <c r="T33" s="71"/>
       <c r="U33" s="71"/>
-      <c r="V33" s="87"/>
-      <c r="W33" s="96">
+      <c r="V33" s="82"/>
+      <c r="W33" s="89">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="X33" s="97"/>
-      <c r="Y33" s="100"/>
-      <c r="Z33" s="129"/>
+      <c r="X33" s="90"/>
+      <c r="Y33" s="93"/>
+      <c r="Z33" s="120"/>
     </row>
     <row r="34" spans="1:26" ht="15.75">
       <c r="A34" s="66">
@@ -16180,14 +16614,14 @@
       <c r="S34" s="72"/>
       <c r="T34" s="72"/>
       <c r="U34" s="72"/>
-      <c r="V34" s="88"/>
-      <c r="W34" s="96">
+      <c r="V34" s="83"/>
+      <c r="W34" s="89">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="X34" s="97"/>
-      <c r="Y34" s="100"/>
-      <c r="Z34" s="129"/>
+      <c r="X34" s="90"/>
+      <c r="Y34" s="93"/>
+      <c r="Z34" s="120"/>
     </row>
     <row r="35" spans="1:26" ht="15.75">
       <c r="A35" s="62">
@@ -16215,14 +16649,14 @@
       <c r="S35" s="71"/>
       <c r="T35" s="71"/>
       <c r="U35" s="71"/>
-      <c r="V35" s="87"/>
-      <c r="W35" s="96">
+      <c r="V35" s="82"/>
+      <c r="W35" s="89">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="X35" s="97"/>
-      <c r="Y35" s="100"/>
-      <c r="Z35" s="129"/>
+      <c r="X35" s="90"/>
+      <c r="Y35" s="93"/>
+      <c r="Z35" s="120"/>
     </row>
     <row r="36" spans="1:26" ht="15.75">
       <c r="A36" s="66">
@@ -16250,20 +16684,20 @@
       <c r="S36" s="72"/>
       <c r="T36" s="72"/>
       <c r="U36" s="72"/>
-      <c r="V36" s="88"/>
-      <c r="W36" s="96">
+      <c r="V36" s="83"/>
+      <c r="W36" s="89">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="X36" s="97"/>
-      <c r="Y36" s="100"/>
-      <c r="Z36" s="129"/>
+      <c r="X36" s="90"/>
+      <c r="Y36" s="93"/>
+      <c r="Z36" s="120"/>
     </row>
     <row r="37" spans="1:26">
-      <c r="A37" s="123" t="s">
+      <c r="A37" s="116" t="s">
         <v>36</v>
       </c>
-      <c r="B37" s="123"/>
+      <c r="B37" s="116"/>
       <c r="C37" s="79">
         <f>SUM(C21:C36)</f>
         <v>3393</v>
@@ -16340,32 +16774,32 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="V37" s="93">
+      <c r="V37" s="86">
         <f t="shared" si="3"/>
         <v>4800</v>
       </c>
-      <c r="W37" s="101">
+      <c r="W37" s="94">
         <f>SUM(W21:W36)</f>
         <v>45722.31</v>
       </c>
-      <c r="X37" s="102">
+      <c r="X37" s="95">
         <f>SUM(X21:X36)</f>
         <v>23662.84</v>
       </c>
-      <c r="Y37" s="108">
+      <c r="Y37" s="101">
         <f>SUM(Y21:Y36)</f>
         <v>56898.64</v>
       </c>
-      <c r="Z37" s="104">
+      <c r="Z37" s="97">
         <f>Y37-W37-X37</f>
         <v>-12486.509999999998</v>
       </c>
     </row>
     <row r="38" spans="1:26" ht="31.5" customHeight="1">
-      <c r="A38" s="128" t="s">
+      <c r="A38" s="119" t="s">
         <v>37</v>
       </c>
-      <c r="B38" s="128"/>
+      <c r="B38" s="119"/>
       <c r="C38" s="78">
         <f>SUM(C20,C37)</f>
         <v>14335.99</v>
@@ -16442,19 +16876,19 @@
         <f t="shared" si="4"/>
         <v>6461</v>
       </c>
-      <c r="V38" s="94">
+      <c r="V38" s="87">
         <f t="shared" si="4"/>
         <v>5750</v>
       </c>
-      <c r="W38" s="101">
+      <c r="W38" s="94">
         <f t="shared" si="4"/>
         <v>167654.87</v>
       </c>
-      <c r="X38" s="102">
+      <c r="X38" s="95">
         <f>SUM(X20,X37)</f>
         <v>110623.52999999998</v>
       </c>
-      <c r="Y38" s="109">
+      <c r="Y38" s="102">
         <f>SUM(Y20,Y37)</f>
         <v>271341.31</v>
       </c>
@@ -16477,18 +16911,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="AC14:AF14"/>
+    <mergeCell ref="AC15:AF15"/>
+    <mergeCell ref="AC8:AG10"/>
+    <mergeCell ref="AC11:AF11"/>
+    <mergeCell ref="AC12:AF12"/>
+    <mergeCell ref="AC13:AF13"/>
     <mergeCell ref="A1:Z1"/>
     <mergeCell ref="A20:B20"/>
     <mergeCell ref="A37:B37"/>
     <mergeCell ref="A38:B38"/>
     <mergeCell ref="Z3:Z19"/>
     <mergeCell ref="Z21:Z36"/>
-    <mergeCell ref="AC14:AF14"/>
-    <mergeCell ref="AC15:AF15"/>
-    <mergeCell ref="AC8:AG10"/>
-    <mergeCell ref="AC11:AF11"/>
-    <mergeCell ref="AC12:AF12"/>
-    <mergeCell ref="AC13:AF13"/>
   </mergeCells>
   <conditionalFormatting sqref="Z20:Z21 Z37:Z38">
     <cfRule type="expression" dxfId="3" priority="1">
@@ -16506,1581 +16940,1844 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AV42"/>
+  <dimension ref="A1:AZ41"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="26" width="20.7109375" style="2" customWidth="1"/>
-    <col min="27" max="38" width="12.7109375" style="2" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="30" width="20.7109375" style="2" customWidth="1"/>
+    <col min="31" max="42" width="12.7109375" style="2" customWidth="1"/>
+    <col min="43" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:48" ht="60.75" customHeight="1">
-      <c r="A1" s="133" t="s">
+    <row r="1" spans="1:52" ht="34.5" customHeight="1">
+      <c r="A1" s="123" t="s">
         <v>66</v>
       </c>
-      <c r="B1" s="133"/>
-      <c r="C1" s="133"/>
-      <c r="D1" s="133"/>
-      <c r="E1" s="133"/>
-      <c r="F1" s="133"/>
-      <c r="G1" s="133"/>
-      <c r="H1" s="133"/>
-      <c r="I1" s="133"/>
-      <c r="J1" s="133"/>
-      <c r="K1" s="133"/>
-      <c r="L1" s="133"/>
-      <c r="M1" s="133"/>
-      <c r="N1" s="133"/>
-      <c r="O1" s="133"/>
-      <c r="P1" s="133"/>
-      <c r="Q1" s="133"/>
-      <c r="R1" s="133"/>
-      <c r="S1" s="133"/>
-      <c r="T1" s="133"/>
-      <c r="U1" s="133"/>
-      <c r="V1" s="133"/>
-      <c r="W1" s="133"/>
-      <c r="X1" s="133"/>
-      <c r="Y1" s="133"/>
-      <c r="Z1" s="133"/>
-    </row>
-    <row r="2" spans="1:48" ht="45" customHeight="1">
-      <c r="A2" s="143" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="143" t="s">
+      <c r="B1" s="123"/>
+      <c r="C1" s="123"/>
+      <c r="D1" s="123"/>
+      <c r="E1" s="123"/>
+      <c r="F1" s="123"/>
+      <c r="G1" s="123"/>
+      <c r="H1" s="123"/>
+      <c r="I1" s="123"/>
+      <c r="J1" s="123"/>
+      <c r="K1" s="123"/>
+      <c r="L1" s="123"/>
+      <c r="M1" s="123"/>
+      <c r="N1" s="123"/>
+      <c r="O1" s="123"/>
+      <c r="P1" s="123"/>
+      <c r="Q1" s="123"/>
+      <c r="R1" s="123"/>
+      <c r="S1" s="123"/>
+      <c r="T1" s="123"/>
+      <c r="U1" s="123"/>
+      <c r="V1" s="123"/>
+      <c r="W1" s="123"/>
+      <c r="X1" s="123"/>
+      <c r="Y1" s="123"/>
+      <c r="Z1" s="123"/>
+      <c r="AA1" s="123"/>
+      <c r="AB1" s="123"/>
+      <c r="AC1" s="123"/>
+      <c r="AD1" s="123"/>
+    </row>
+    <row r="2" spans="1:52" ht="26.25">
+      <c r="A2" s="148"/>
+      <c r="B2" s="149"/>
+      <c r="C2" s="124" t="s">
+        <v>67</v>
+      </c>
+      <c r="D2" s="124"/>
+      <c r="E2" s="124"/>
+      <c r="F2" s="124"/>
+      <c r="G2" s="124"/>
+      <c r="H2" s="124"/>
+      <c r="I2" s="124"/>
+      <c r="J2" s="124"/>
+      <c r="K2" s="124"/>
+      <c r="L2" s="145" t="s">
+        <v>75</v>
+      </c>
+      <c r="M2" s="145"/>
+      <c r="N2" s="145"/>
+      <c r="O2" s="145"/>
+      <c r="P2" s="145"/>
+      <c r="Q2" s="145"/>
+      <c r="R2" s="146" t="s">
+        <v>78</v>
+      </c>
+      <c r="S2" s="146"/>
+      <c r="T2" s="146"/>
+      <c r="U2" s="146"/>
+      <c r="V2" s="146"/>
+      <c r="W2" s="146"/>
+      <c r="X2" s="146"/>
+      <c r="Y2" s="146"/>
+      <c r="Z2" s="146"/>
+      <c r="AA2" s="146"/>
+      <c r="AB2" s="147" t="s">
+        <v>81</v>
+      </c>
+      <c r="AC2" s="147"/>
+      <c r="AD2" s="147"/>
+    </row>
+    <row r="3" spans="1:52" ht="45" customHeight="1">
+      <c r="A3" s="141" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="141" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="138" t="s">
+      <c r="C3" s="142" t="s">
+        <v>68</v>
+      </c>
+      <c r="D3" s="142" t="s">
+        <v>69</v>
+      </c>
+      <c r="E3" s="142" t="s">
+        <v>70</v>
+      </c>
+      <c r="F3" s="142" t="s">
+        <v>29</v>
+      </c>
+      <c r="G3" s="142" t="s">
+        <v>82</v>
+      </c>
+      <c r="H3" s="142" t="s">
+        <v>71</v>
+      </c>
+      <c r="I3" s="142" t="s">
+        <v>72</v>
+      </c>
+      <c r="J3" s="142" t="s">
+        <v>73</v>
+      </c>
+      <c r="K3" s="142" t="s">
+        <v>74</v>
+      </c>
+      <c r="L3" s="143" t="s">
+        <v>24</v>
+      </c>
+      <c r="M3" s="143" t="s">
+        <v>14</v>
+      </c>
+      <c r="N3" s="143" t="s">
+        <v>76</v>
+      </c>
+      <c r="O3" s="143" t="s">
+        <v>25</v>
+      </c>
+      <c r="P3" s="143" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q3" s="143" t="s">
+        <v>77</v>
+      </c>
+      <c r="R3" s="144" t="s">
+        <v>30</v>
+      </c>
+      <c r="S3" s="144" t="s">
+        <v>23</v>
+      </c>
+      <c r="T3" s="144" t="s">
+        <v>13</v>
+      </c>
+      <c r="U3" s="144" t="s">
+        <v>15</v>
+      </c>
+      <c r="V3" s="144" t="s">
+        <v>16</v>
+      </c>
+      <c r="W3" s="144" t="s">
+        <v>28</v>
+      </c>
+      <c r="X3" s="144" t="s">
+        <v>79</v>
+      </c>
+      <c r="Y3" s="144" t="s">
+        <v>79</v>
+      </c>
+      <c r="Z3" s="144" t="s">
+        <v>80</v>
+      </c>
+      <c r="AA3" s="150" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB3" s="153" t="s">
+        <v>22</v>
+      </c>
+      <c r="AC3" s="154" t="s">
+        <v>19</v>
+      </c>
+      <c r="AD3" s="163" t="s">
+        <v>21</v>
+      </c>
+      <c r="AE3" s="1"/>
+      <c r="AF3" s="1"/>
+      <c r="AG3" s="1"/>
+      <c r="AH3" s="1"/>
+      <c r="AI3" s="1"/>
+      <c r="AJ3" s="1"/>
+      <c r="AK3" s="1"/>
+      <c r="AL3" s="1"/>
+      <c r="AM3" s="1"/>
+      <c r="AN3" s="1"/>
+      <c r="AO3" s="1"/>
+      <c r="AP3" s="1"/>
+      <c r="AQ3" s="1"/>
+      <c r="AR3" s="1"/>
+      <c r="AS3" s="1"/>
+      <c r="AT3" s="1"/>
+      <c r="AU3" s="1"/>
+      <c r="AV3" s="1"/>
+      <c r="AW3" s="1"/>
+      <c r="AX3" s="1"/>
+      <c r="AY3" s="1"/>
+      <c r="AZ3" s="1"/>
+    </row>
+    <row r="4" spans="1:52" ht="15.75">
+      <c r="A4" s="129">
+        <v>5</v>
+      </c>
+      <c r="B4" s="130" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="131">
+        <v>429.95</v>
+      </c>
+      <c r="D4" s="131"/>
+      <c r="E4" s="131"/>
+      <c r="F4" s="131"/>
+      <c r="G4" s="131"/>
+      <c r="H4" s="131"/>
+      <c r="I4" s="131">
+        <f>4660+545</f>
+        <v>5205</v>
+      </c>
+      <c r="J4" s="131"/>
+      <c r="K4" s="131"/>
+      <c r="L4" s="131"/>
+      <c r="M4" s="131"/>
+      <c r="N4" s="131"/>
+      <c r="O4" s="131">
+        <v>100</v>
+      </c>
+      <c r="P4" s="131">
+        <v>10000</v>
+      </c>
+      <c r="Q4" s="131"/>
+      <c r="R4" s="131"/>
+      <c r="S4" s="131"/>
+      <c r="T4" s="131"/>
+      <c r="U4" s="131"/>
+      <c r="V4" s="131"/>
+      <c r="W4" s="131"/>
+      <c r="X4" s="131">
+        <v>1237</v>
+      </c>
+      <c r="Y4" s="131"/>
+      <c r="Z4" s="131"/>
+      <c r="AA4" s="132"/>
+      <c r="AB4" s="155">
+        <f>SUM(C4:AA4)</f>
+        <v>16971.95</v>
+      </c>
+      <c r="AC4" s="140">
+        <f>37635+40252.26+18817.85</f>
+        <v>96705.110000000015</v>
+      </c>
+      <c r="AD4" s="156"/>
+    </row>
+    <row r="5" spans="1:52" ht="15.75">
+      <c r="A5" s="125">
+        <v>6</v>
+      </c>
+      <c r="B5" s="126" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="127"/>
+      <c r="D5" s="127"/>
+      <c r="E5" s="127"/>
+      <c r="F5" s="127">
+        <v>351</v>
+      </c>
+      <c r="G5" s="127"/>
+      <c r="H5" s="127"/>
+      <c r="I5" s="127"/>
+      <c r="J5" s="127"/>
+      <c r="K5" s="127"/>
+      <c r="L5" s="127">
+        <f>5748.49+2803.26+2306.38</f>
+        <v>10858.130000000001</v>
+      </c>
+      <c r="M5" s="127"/>
+      <c r="N5" s="127"/>
+      <c r="O5" s="127"/>
+      <c r="P5" s="127"/>
+      <c r="Q5" s="127">
+        <v>3500</v>
+      </c>
+      <c r="R5" s="127"/>
+      <c r="S5" s="127"/>
+      <c r="T5" s="127"/>
+      <c r="U5" s="127">
+        <v>294</v>
+      </c>
+      <c r="V5" s="127"/>
+      <c r="W5" s="127">
+        <v>1500</v>
+      </c>
+      <c r="X5" s="127"/>
+      <c r="Y5" s="127"/>
+      <c r="Z5" s="127"/>
+      <c r="AA5" s="128"/>
+      <c r="AB5" s="155">
+        <f>SUM(C5:AA5)</f>
+        <v>16503.13</v>
+      </c>
+      <c r="AC5" s="139"/>
+      <c r="AD5" s="156"/>
+    </row>
+    <row r="6" spans="1:52" ht="15.75">
+      <c r="A6" s="129">
+        <v>7</v>
+      </c>
+      <c r="B6" s="130" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="131"/>
+      <c r="D6" s="131"/>
+      <c r="E6" s="131"/>
+      <c r="F6" s="131"/>
+      <c r="G6" s="131"/>
+      <c r="H6" s="131"/>
+      <c r="I6" s="131"/>
+      <c r="J6" s="131">
+        <v>838</v>
+      </c>
+      <c r="K6" s="131"/>
+      <c r="L6" s="131"/>
+      <c r="M6" s="131"/>
+      <c r="N6" s="131"/>
+      <c r="O6" s="131"/>
+      <c r="P6" s="131"/>
+      <c r="Q6" s="131"/>
+      <c r="R6" s="131"/>
+      <c r="S6" s="131"/>
+      <c r="T6" s="131"/>
+      <c r="U6" s="131"/>
+      <c r="V6" s="131">
+        <v>158.61000000000001</v>
+      </c>
+      <c r="W6" s="131"/>
+      <c r="X6" s="131"/>
+      <c r="Y6" s="131"/>
+      <c r="Z6" s="131"/>
+      <c r="AA6" s="132"/>
+      <c r="AB6" s="155">
+        <f t="shared" ref="AB6:AB18" si="0">SUM(C6:AA6)</f>
+        <v>996.61</v>
+      </c>
+      <c r="AC6" s="139"/>
+      <c r="AD6" s="156"/>
+    </row>
+    <row r="7" spans="1:52" ht="15.75">
+      <c r="A7" s="125">
+        <v>8</v>
+      </c>
+      <c r="B7" s="126" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="127"/>
+      <c r="D7" s="127"/>
+      <c r="E7" s="127"/>
+      <c r="F7" s="127">
+        <v>1461</v>
+      </c>
+      <c r="G7" s="127">
+        <v>821</v>
+      </c>
+      <c r="H7" s="127"/>
+      <c r="I7" s="127">
+        <f>2510+220</f>
+        <v>2730</v>
+      </c>
+      <c r="J7" s="127">
+        <v>730</v>
+      </c>
+      <c r="K7" s="127"/>
+      <c r="L7" s="127"/>
+      <c r="M7" s="127"/>
+      <c r="N7" s="127"/>
+      <c r="O7" s="127">
+        <v>100</v>
+      </c>
+      <c r="P7" s="127"/>
+      <c r="Q7" s="127"/>
+      <c r="R7" s="127"/>
+      <c r="S7" s="127"/>
+      <c r="T7" s="127"/>
+      <c r="U7" s="127"/>
+      <c r="V7" s="127"/>
+      <c r="W7" s="127"/>
+      <c r="X7" s="127"/>
+      <c r="Y7" s="127"/>
+      <c r="Z7" s="127">
+        <v>2626</v>
+      </c>
+      <c r="AA7" s="128"/>
+      <c r="AB7" s="155">
+        <f t="shared" si="0"/>
+        <v>8468</v>
+      </c>
+      <c r="AC7" s="139"/>
+      <c r="AD7" s="156"/>
+    </row>
+    <row r="8" spans="1:52" ht="15" customHeight="1">
+      <c r="A8" s="129">
         <v>9</v>
       </c>
-      <c r="D2" s="138" t="s">
+      <c r="B8" s="130" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="131"/>
+      <c r="D8" s="131"/>
+      <c r="E8" s="131">
+        <v>2510</v>
+      </c>
+      <c r="F8" s="131"/>
+      <c r="G8" s="131"/>
+      <c r="H8" s="131"/>
+      <c r="I8" s="131"/>
+      <c r="J8" s="131">
+        <v>1534</v>
+      </c>
+      <c r="K8" s="131"/>
+      <c r="L8" s="131"/>
+      <c r="M8" s="131"/>
+      <c r="N8" s="131"/>
+      <c r="O8" s="131"/>
+      <c r="P8" s="131"/>
+      <c r="Q8" s="131"/>
+      <c r="R8" s="131"/>
+      <c r="S8" s="131"/>
+      <c r="T8" s="131"/>
+      <c r="U8" s="131"/>
+      <c r="V8" s="131"/>
+      <c r="W8" s="131">
+        <f>400+1115+3400+1409.98+1800</f>
+        <v>8124.98</v>
+      </c>
+      <c r="X8" s="131"/>
+      <c r="Y8" s="131"/>
+      <c r="Z8" s="131"/>
+      <c r="AA8" s="132"/>
+      <c r="AB8" s="155">
+        <f t="shared" si="0"/>
+        <v>12168.98</v>
+      </c>
+      <c r="AC8" s="139"/>
+      <c r="AD8" s="156"/>
+    </row>
+    <row r="9" spans="1:52" ht="15.75">
+      <c r="A9" s="125">
+        <v>10</v>
+      </c>
+      <c r="B9" s="126" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="127"/>
+      <c r="D9" s="127"/>
+      <c r="E9" s="127"/>
+      <c r="F9" s="127"/>
+      <c r="G9" s="127"/>
+      <c r="H9" s="127"/>
+      <c r="I9" s="127"/>
+      <c r="J9" s="127"/>
+      <c r="K9" s="127">
+        <v>1860</v>
+      </c>
+      <c r="L9" s="127"/>
+      <c r="M9" s="127"/>
+      <c r="N9" s="127">
+        <v>700</v>
+      </c>
+      <c r="O9" s="127"/>
+      <c r="P9" s="127">
+        <v>2000</v>
+      </c>
+      <c r="Q9" s="127"/>
+      <c r="R9" s="127"/>
+      <c r="S9" s="127"/>
+      <c r="T9" s="127"/>
+      <c r="U9" s="127">
+        <v>420</v>
+      </c>
+      <c r="V9" s="127"/>
+      <c r="W9" s="127"/>
+      <c r="X9" s="127"/>
+      <c r="Y9" s="127"/>
+      <c r="Z9" s="127"/>
+      <c r="AA9" s="128"/>
+      <c r="AB9" s="155">
+        <f t="shared" si="0"/>
+        <v>4980</v>
+      </c>
+      <c r="AC9" s="139"/>
+      <c r="AD9" s="156"/>
+    </row>
+    <row r="10" spans="1:52" ht="15.75">
+      <c r="A10" s="129">
+        <v>11</v>
+      </c>
+      <c r="B10" s="130" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="131"/>
+      <c r="D10" s="131"/>
+      <c r="E10" s="131"/>
+      <c r="F10" s="131"/>
+      <c r="G10" s="131"/>
+      <c r="H10" s="131"/>
+      <c r="I10" s="131"/>
+      <c r="J10" s="131"/>
+      <c r="K10" s="131"/>
+      <c r="L10" s="131"/>
+      <c r="M10" s="131"/>
+      <c r="N10" s="131"/>
+      <c r="O10" s="131"/>
+      <c r="P10" s="131"/>
+      <c r="Q10" s="131"/>
+      <c r="R10" s="131"/>
+      <c r="S10" s="131"/>
+      <c r="T10" s="131"/>
+      <c r="U10" s="131"/>
+      <c r="V10" s="131"/>
+      <c r="W10" s="131"/>
+      <c r="X10" s="131"/>
+      <c r="Y10" s="131"/>
+      <c r="Z10" s="131"/>
+      <c r="AA10" s="132"/>
+      <c r="AB10" s="155">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AC10" s="139"/>
+      <c r="AD10" s="156"/>
+    </row>
+    <row r="11" spans="1:52" ht="15.75">
+      <c r="A11" s="125">
+        <v>12</v>
+      </c>
+      <c r="B11" s="126" t="s">
+        <v>2</v>
+      </c>
+      <c r="C11" s="127"/>
+      <c r="D11" s="127"/>
+      <c r="E11" s="127"/>
+      <c r="F11" s="127"/>
+      <c r="G11" s="127"/>
+      <c r="H11" s="127"/>
+      <c r="I11" s="127"/>
+      <c r="J11" s="127"/>
+      <c r="K11" s="127"/>
+      <c r="L11" s="127"/>
+      <c r="M11" s="127"/>
+      <c r="N11" s="127"/>
+      <c r="O11" s="127"/>
+      <c r="P11" s="127"/>
+      <c r="Q11" s="127"/>
+      <c r="R11" s="127"/>
+      <c r="S11" s="127"/>
+      <c r="T11" s="127"/>
+      <c r="U11" s="127"/>
+      <c r="V11" s="127"/>
+      <c r="W11" s="127"/>
+      <c r="X11" s="127"/>
+      <c r="Y11" s="127"/>
+      <c r="Z11" s="127"/>
+      <c r="AA11" s="128"/>
+      <c r="AB11" s="155">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AC11" s="139"/>
+      <c r="AD11" s="156"/>
+    </row>
+    <row r="12" spans="1:52" ht="15.75">
+      <c r="A12" s="129">
+        <v>13</v>
+      </c>
+      <c r="B12" s="130" t="s">
+        <v>3</v>
+      </c>
+      <c r="C12" s="131"/>
+      <c r="D12" s="131"/>
+      <c r="E12" s="131"/>
+      <c r="F12" s="131"/>
+      <c r="G12" s="131"/>
+      <c r="H12" s="131"/>
+      <c r="I12" s="131"/>
+      <c r="J12" s="131"/>
+      <c r="K12" s="131"/>
+      <c r="L12" s="131"/>
+      <c r="M12" s="131"/>
+      <c r="N12" s="131"/>
+      <c r="O12" s="131"/>
+      <c r="P12" s="131"/>
+      <c r="Q12" s="131"/>
+      <c r="R12" s="131"/>
+      <c r="S12" s="131"/>
+      <c r="T12" s="131"/>
+      <c r="U12" s="131"/>
+      <c r="V12" s="131"/>
+      <c r="W12" s="131"/>
+      <c r="X12" s="131"/>
+      <c r="Y12" s="131"/>
+      <c r="Z12" s="131"/>
+      <c r="AA12" s="132"/>
+      <c r="AB12" s="155">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AC12" s="139"/>
+      <c r="AD12" s="156"/>
+    </row>
+    <row r="13" spans="1:52" ht="15.75">
+      <c r="A13" s="125">
+        <v>14</v>
+      </c>
+      <c r="B13" s="126" t="s">
+        <v>4</v>
+      </c>
+      <c r="C13" s="127"/>
+      <c r="D13" s="127"/>
+      <c r="E13" s="127"/>
+      <c r="F13" s="127"/>
+      <c r="G13" s="127"/>
+      <c r="H13" s="127"/>
+      <c r="I13" s="127"/>
+      <c r="J13" s="127"/>
+      <c r="K13" s="127"/>
+      <c r="L13" s="127"/>
+      <c r="M13" s="127"/>
+      <c r="N13" s="127"/>
+      <c r="O13" s="127"/>
+      <c r="P13" s="127"/>
+      <c r="Q13" s="127"/>
+      <c r="R13" s="127"/>
+      <c r="S13" s="127"/>
+      <c r="T13" s="127"/>
+      <c r="U13" s="127"/>
+      <c r="V13" s="127"/>
+      <c r="W13" s="127"/>
+      <c r="X13" s="127"/>
+      <c r="Y13" s="127"/>
+      <c r="Z13" s="127"/>
+      <c r="AA13" s="128"/>
+      <c r="AB13" s="155">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AC13" s="139"/>
+      <c r="AD13" s="156"/>
+    </row>
+    <row r="14" spans="1:52" ht="15.75">
+      <c r="A14" s="129">
+        <v>15</v>
+      </c>
+      <c r="B14" s="130" t="s">
+        <v>5</v>
+      </c>
+      <c r="C14" s="131"/>
+      <c r="D14" s="131"/>
+      <c r="E14" s="131"/>
+      <c r="F14" s="131"/>
+      <c r="G14" s="131"/>
+      <c r="H14" s="131"/>
+      <c r="I14" s="131"/>
+      <c r="J14" s="131"/>
+      <c r="K14" s="131"/>
+      <c r="L14" s="131"/>
+      <c r="M14" s="131"/>
+      <c r="N14" s="131"/>
+      <c r="O14" s="131"/>
+      <c r="P14" s="131"/>
+      <c r="Q14" s="131"/>
+      <c r="R14" s="131"/>
+      <c r="S14" s="131"/>
+      <c r="T14" s="131"/>
+      <c r="U14" s="131"/>
+      <c r="V14" s="131"/>
+      <c r="W14" s="131"/>
+      <c r="X14" s="131"/>
+      <c r="Y14" s="131"/>
+      <c r="Z14" s="131"/>
+      <c r="AA14" s="132"/>
+      <c r="AB14" s="155">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AC14" s="139"/>
+      <c r="AD14" s="156"/>
+    </row>
+    <row r="15" spans="1:52" ht="15.75">
+      <c r="A15" s="125">
+        <v>16</v>
+      </c>
+      <c r="B15" s="126" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15" s="127"/>
+      <c r="D15" s="127"/>
+      <c r="E15" s="127"/>
+      <c r="F15" s="127"/>
+      <c r="G15" s="127"/>
+      <c r="H15" s="127"/>
+      <c r="I15" s="127"/>
+      <c r="J15" s="127"/>
+      <c r="K15" s="127"/>
+      <c r="L15" s="127"/>
+      <c r="M15" s="127"/>
+      <c r="N15" s="127"/>
+      <c r="O15" s="127"/>
+      <c r="P15" s="127"/>
+      <c r="Q15" s="127"/>
+      <c r="R15" s="127"/>
+      <c r="S15" s="127"/>
+      <c r="T15" s="127"/>
+      <c r="U15" s="127"/>
+      <c r="V15" s="127"/>
+      <c r="W15" s="127"/>
+      <c r="X15" s="127"/>
+      <c r="Y15" s="127"/>
+      <c r="Z15" s="127"/>
+      <c r="AA15" s="128"/>
+      <c r="AB15" s="155">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AC15" s="140"/>
+      <c r="AD15" s="156"/>
+    </row>
+    <row r="16" spans="1:52" ht="15.75">
+      <c r="A16" s="129">
+        <v>17</v>
+      </c>
+      <c r="B16" s="130" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="131"/>
+      <c r="D16" s="131"/>
+      <c r="E16" s="131"/>
+      <c r="F16" s="131"/>
+      <c r="G16" s="131"/>
+      <c r="H16" s="131"/>
+      <c r="I16" s="131"/>
+      <c r="J16" s="131"/>
+      <c r="K16" s="131"/>
+      <c r="L16" s="131"/>
+      <c r="M16" s="131"/>
+      <c r="N16" s="131"/>
+      <c r="O16" s="131"/>
+      <c r="P16" s="131"/>
+      <c r="Q16" s="131"/>
+      <c r="R16" s="131"/>
+      <c r="S16" s="131"/>
+      <c r="T16" s="131"/>
+      <c r="U16" s="131"/>
+      <c r="V16" s="131"/>
+      <c r="W16" s="131"/>
+      <c r="X16" s="131"/>
+      <c r="Y16" s="131"/>
+      <c r="Z16" s="131"/>
+      <c r="AA16" s="132"/>
+      <c r="AB16" s="155">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AC16" s="139"/>
+      <c r="AD16" s="156"/>
+    </row>
+    <row r="17" spans="1:32" ht="15.75">
+      <c r="A17" s="125">
+        <v>18</v>
+      </c>
+      <c r="B17" s="126" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="127"/>
+      <c r="D17" s="127"/>
+      <c r="E17" s="127"/>
+      <c r="F17" s="127"/>
+      <c r="G17" s="127"/>
+      <c r="H17" s="127"/>
+      <c r="I17" s="127"/>
+      <c r="J17" s="127"/>
+      <c r="K17" s="127"/>
+      <c r="L17" s="127"/>
+      <c r="M17" s="127"/>
+      <c r="N17" s="127"/>
+      <c r="O17" s="127"/>
+      <c r="P17" s="127"/>
+      <c r="Q17" s="127"/>
+      <c r="R17" s="127"/>
+      <c r="S17" s="127"/>
+      <c r="T17" s="127"/>
+      <c r="U17" s="127"/>
+      <c r="V17" s="127"/>
+      <c r="W17" s="127"/>
+      <c r="X17" s="127"/>
+      <c r="Y17" s="127"/>
+      <c r="Z17" s="127"/>
+      <c r="AA17" s="128"/>
+      <c r="AB17" s="155">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AC17" s="139"/>
+      <c r="AD17" s="156"/>
+    </row>
+    <row r="18" spans="1:32" ht="15.75">
+      <c r="A18" s="129">
+        <v>19</v>
+      </c>
+      <c r="B18" s="130" t="s">
+        <v>2</v>
+      </c>
+      <c r="C18" s="131"/>
+      <c r="D18" s="131"/>
+      <c r="E18" s="131"/>
+      <c r="F18" s="131"/>
+      <c r="G18" s="131"/>
+      <c r="H18" s="131"/>
+      <c r="I18" s="131"/>
+      <c r="J18" s="131"/>
+      <c r="K18" s="131"/>
+      <c r="L18" s="131"/>
+      <c r="M18" s="131"/>
+      <c r="N18" s="131"/>
+      <c r="O18" s="131"/>
+      <c r="P18" s="131"/>
+      <c r="Q18" s="131"/>
+      <c r="R18" s="131"/>
+      <c r="S18" s="131"/>
+      <c r="T18" s="131"/>
+      <c r="U18" s="131"/>
+      <c r="V18" s="131"/>
+      <c r="W18" s="131"/>
+      <c r="X18" s="131"/>
+      <c r="Y18" s="131"/>
+      <c r="Z18" s="131"/>
+      <c r="AA18" s="132"/>
+      <c r="AB18" s="155">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AC18" s="139"/>
+      <c r="AD18" s="156"/>
+    </row>
+    <row r="19" spans="1:32" ht="14.25" customHeight="1">
+      <c r="A19" s="136" t="s">
+        <v>35</v>
+      </c>
+      <c r="B19" s="136"/>
+      <c r="C19" s="133">
+        <f>SUM(C4:C18)</f>
+        <v>429.95</v>
+      </c>
+      <c r="D19" s="133">
+        <f t="shared" ref="D19:AA19" si="1">SUM(D4:D18)</f>
+        <v>0</v>
+      </c>
+      <c r="E19" s="133">
+        <f t="shared" si="1"/>
+        <v>2510</v>
+      </c>
+      <c r="F19" s="133">
+        <f t="shared" si="1"/>
+        <v>1812</v>
+      </c>
+      <c r="G19" s="133">
+        <f t="shared" si="1"/>
+        <v>821</v>
+      </c>
+      <c r="H19" s="133">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I19" s="133">
+        <f t="shared" si="1"/>
+        <v>7935</v>
+      </c>
+      <c r="J19" s="133">
+        <f t="shared" si="1"/>
+        <v>3102</v>
+      </c>
+      <c r="K19" s="133">
+        <f t="shared" si="1"/>
+        <v>1860</v>
+      </c>
+      <c r="L19" s="134">
+        <f t="shared" si="1"/>
+        <v>10858.130000000001</v>
+      </c>
+      <c r="M19" s="134">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N19" s="134">
+        <f t="shared" si="1"/>
+        <v>700</v>
+      </c>
+      <c r="O19" s="134">
+        <f t="shared" si="1"/>
+        <v>200</v>
+      </c>
+      <c r="P19" s="134">
+        <f t="shared" si="1"/>
+        <v>12000</v>
+      </c>
+      <c r="Q19" s="134">
+        <f t="shared" si="1"/>
+        <v>3500</v>
+      </c>
+      <c r="R19" s="135">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S19" s="135">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T19" s="135">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="U19" s="135">
+        <f t="shared" si="1"/>
+        <v>714</v>
+      </c>
+      <c r="V19" s="135">
+        <f t="shared" si="1"/>
+        <v>158.61000000000001</v>
+      </c>
+      <c r="W19" s="135">
+        <f t="shared" si="1"/>
+        <v>9624.98</v>
+      </c>
+      <c r="X19" s="135">
+        <f t="shared" si="1"/>
+        <v>1237</v>
+      </c>
+      <c r="Y19" s="135">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z19" s="135">
+        <f t="shared" si="1"/>
+        <v>2626</v>
+      </c>
+      <c r="AA19" s="151">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AB19" s="157">
+        <f>SUM(AB4:AB18)</f>
+        <v>60088.67</v>
+      </c>
+      <c r="AC19" s="158">
+        <f>SUM(AC4:AC18)</f>
+        <v>96705.110000000015</v>
+      </c>
+      <c r="AD19" s="161">
+        <f>AC19-AB19</f>
+        <v>36616.440000000017</v>
+      </c>
+    </row>
+    <row r="20" spans="1:32" ht="15.75">
+      <c r="A20" s="129">
+        <v>20</v>
+      </c>
+      <c r="B20" s="130" t="s">
+        <v>3</v>
+      </c>
+      <c r="C20" s="131"/>
+      <c r="D20" s="131"/>
+      <c r="E20" s="131"/>
+      <c r="F20" s="131"/>
+      <c r="G20" s="131"/>
+      <c r="H20" s="131"/>
+      <c r="I20" s="131"/>
+      <c r="J20" s="131"/>
+      <c r="K20" s="131"/>
+      <c r="L20" s="131"/>
+      <c r="M20" s="131"/>
+      <c r="N20" s="131"/>
+      <c r="O20" s="131"/>
+      <c r="P20" s="131"/>
+      <c r="Q20" s="131"/>
+      <c r="R20" s="131"/>
+      <c r="S20" s="131"/>
+      <c r="T20" s="131"/>
+      <c r="U20" s="131"/>
+      <c r="V20" s="131"/>
+      <c r="W20" s="131"/>
+      <c r="X20" s="131"/>
+      <c r="Y20" s="131"/>
+      <c r="Z20" s="131"/>
+      <c r="AA20" s="132"/>
+      <c r="AB20" s="155">
+        <f>SUM(C20:AA20)</f>
+        <v>0</v>
+      </c>
+      <c r="AC20" s="140"/>
+      <c r="AD20" s="156"/>
+    </row>
+    <row r="21" spans="1:32" ht="15.75">
+      <c r="A21" s="125">
+        <v>21</v>
+      </c>
+      <c r="B21" s="126" t="s">
+        <v>4</v>
+      </c>
+      <c r="C21" s="127"/>
+      <c r="D21" s="127"/>
+      <c r="E21" s="127"/>
+      <c r="F21" s="127"/>
+      <c r="G21" s="127"/>
+      <c r="H21" s="127"/>
+      <c r="I21" s="127"/>
+      <c r="J21" s="127"/>
+      <c r="K21" s="127"/>
+      <c r="L21" s="127"/>
+      <c r="M21" s="127"/>
+      <c r="N21" s="127"/>
+      <c r="O21" s="127"/>
+      <c r="P21" s="127"/>
+      <c r="Q21" s="127"/>
+      <c r="R21" s="127"/>
+      <c r="S21" s="127"/>
+      <c r="T21" s="127"/>
+      <c r="U21" s="127"/>
+      <c r="V21" s="127"/>
+      <c r="W21" s="127"/>
+      <c r="X21" s="127"/>
+      <c r="Y21" s="127"/>
+      <c r="Z21" s="127"/>
+      <c r="AA21" s="128"/>
+      <c r="AB21" s="155">
+        <f>SUM(C21:AA21)</f>
+        <v>0</v>
+      </c>
+      <c r="AC21" s="139"/>
+      <c r="AD21" s="156"/>
+      <c r="AF21" s="44"/>
+    </row>
+    <row r="22" spans="1:32" ht="15.75">
+      <c r="A22" s="129">
+        <v>22</v>
+      </c>
+      <c r="B22" s="130" t="s">
+        <v>5</v>
+      </c>
+      <c r="C22" s="131"/>
+      <c r="D22" s="131"/>
+      <c r="E22" s="131"/>
+      <c r="F22" s="131"/>
+      <c r="G22" s="131"/>
+      <c r="H22" s="131"/>
+      <c r="I22" s="131"/>
+      <c r="J22" s="131"/>
+      <c r="K22" s="131"/>
+      <c r="L22" s="131"/>
+      <c r="M22" s="131"/>
+      <c r="N22" s="131"/>
+      <c r="O22" s="131"/>
+      <c r="P22" s="131"/>
+      <c r="Q22" s="131"/>
+      <c r="R22" s="131"/>
+      <c r="S22" s="131"/>
+      <c r="T22" s="131"/>
+      <c r="U22" s="131"/>
+      <c r="V22" s="131"/>
+      <c r="W22" s="131"/>
+      <c r="X22" s="131"/>
+      <c r="Y22" s="131"/>
+      <c r="Z22" s="131"/>
+      <c r="AA22" s="132"/>
+      <c r="AB22" s="155">
+        <f t="shared" ref="AB22:AB35" si="2">SUM(C22:AA22)</f>
+        <v>0</v>
+      </c>
+      <c r="AC22" s="139"/>
+      <c r="AD22" s="156"/>
+    </row>
+    <row r="23" spans="1:32" ht="15.75">
+      <c r="A23" s="125">
+        <v>23</v>
+      </c>
+      <c r="B23" s="126" t="s">
+        <v>6</v>
+      </c>
+      <c r="C23" s="127"/>
+      <c r="D23" s="127"/>
+      <c r="E23" s="127"/>
+      <c r="F23" s="127"/>
+      <c r="G23" s="127"/>
+      <c r="H23" s="127"/>
+      <c r="I23" s="127"/>
+      <c r="J23" s="127"/>
+      <c r="K23" s="127"/>
+      <c r="L23" s="127"/>
+      <c r="M23" s="127"/>
+      <c r="N23" s="127"/>
+      <c r="O23" s="127"/>
+      <c r="P23" s="127"/>
+      <c r="Q23" s="127"/>
+      <c r="R23" s="127"/>
+      <c r="S23" s="127"/>
+      <c r="T23" s="127"/>
+      <c r="U23" s="127"/>
+      <c r="V23" s="127"/>
+      <c r="W23" s="127"/>
+      <c r="X23" s="127"/>
+      <c r="Y23" s="127"/>
+      <c r="Z23" s="127"/>
+      <c r="AA23" s="128"/>
+      <c r="AB23" s="155">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AC23" s="139"/>
+      <c r="AD23" s="156"/>
+    </row>
+    <row r="24" spans="1:32" ht="15.75">
+      <c r="A24" s="129">
+        <v>24</v>
+      </c>
+      <c r="B24" s="130" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" s="131"/>
+      <c r="D24" s="131"/>
+      <c r="E24" s="131"/>
+      <c r="F24" s="131"/>
+      <c r="G24" s="131"/>
+      <c r="H24" s="131"/>
+      <c r="I24" s="131"/>
+      <c r="J24" s="131"/>
+      <c r="K24" s="131"/>
+      <c r="L24" s="131"/>
+      <c r="M24" s="131"/>
+      <c r="N24" s="131"/>
+      <c r="O24" s="131"/>
+      <c r="P24" s="131"/>
+      <c r="Q24" s="131"/>
+      <c r="R24" s="131"/>
+      <c r="S24" s="131"/>
+      <c r="T24" s="131"/>
+      <c r="U24" s="131"/>
+      <c r="V24" s="131"/>
+      <c r="W24" s="131"/>
+      <c r="X24" s="131"/>
+      <c r="Y24" s="131"/>
+      <c r="Z24" s="131"/>
+      <c r="AA24" s="132"/>
+      <c r="AB24" s="155">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AC24" s="139"/>
+      <c r="AD24" s="156"/>
+    </row>
+    <row r="25" spans="1:32" ht="15.75">
+      <c r="A25" s="125">
+        <v>25</v>
+      </c>
+      <c r="B25" s="126" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="127"/>
+      <c r="D25" s="127"/>
+      <c r="E25" s="127"/>
+      <c r="F25" s="127"/>
+      <c r="G25" s="127"/>
+      <c r="H25" s="127"/>
+      <c r="I25" s="127"/>
+      <c r="J25" s="127"/>
+      <c r="K25" s="127"/>
+      <c r="L25" s="127"/>
+      <c r="M25" s="127"/>
+      <c r="N25" s="127"/>
+      <c r="O25" s="127"/>
+      <c r="P25" s="127"/>
+      <c r="Q25" s="127"/>
+      <c r="R25" s="127"/>
+      <c r="S25" s="127"/>
+      <c r="T25" s="127"/>
+      <c r="U25" s="127"/>
+      <c r="V25" s="127"/>
+      <c r="W25" s="127"/>
+      <c r="X25" s="127"/>
+      <c r="Y25" s="127"/>
+      <c r="Z25" s="127"/>
+      <c r="AA25" s="128"/>
+      <c r="AB25" s="155">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AC25" s="139"/>
+      <c r="AD25" s="156"/>
+    </row>
+    <row r="26" spans="1:32" ht="15.75">
+      <c r="A26" s="129">
+        <v>26</v>
+      </c>
+      <c r="B26" s="130" t="s">
+        <v>2</v>
+      </c>
+      <c r="C26" s="131"/>
+      <c r="D26" s="131"/>
+      <c r="E26" s="131"/>
+      <c r="F26" s="131"/>
+      <c r="G26" s="131"/>
+      <c r="H26" s="131"/>
+      <c r="I26" s="131"/>
+      <c r="J26" s="131"/>
+      <c r="K26" s="131"/>
+      <c r="L26" s="131"/>
+      <c r="M26" s="131"/>
+      <c r="N26" s="131"/>
+      <c r="O26" s="131"/>
+      <c r="P26" s="131"/>
+      <c r="Q26" s="131"/>
+      <c r="R26" s="131"/>
+      <c r="S26" s="131"/>
+      <c r="T26" s="131"/>
+      <c r="U26" s="131"/>
+      <c r="V26" s="131"/>
+      <c r="W26" s="131"/>
+      <c r="X26" s="131"/>
+      <c r="Y26" s="131"/>
+      <c r="Z26" s="131"/>
+      <c r="AA26" s="132"/>
+      <c r="AB26" s="155">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AC26" s="140"/>
+      <c r="AD26" s="156"/>
+    </row>
+    <row r="27" spans="1:32" ht="15.75">
+      <c r="A27" s="125">
+        <v>27</v>
+      </c>
+      <c r="B27" s="126" t="s">
+        <v>3</v>
+      </c>
+      <c r="C27" s="127"/>
+      <c r="D27" s="127"/>
+      <c r="E27" s="127"/>
+      <c r="F27" s="127"/>
+      <c r="G27" s="127"/>
+      <c r="H27" s="127"/>
+      <c r="I27" s="127"/>
+      <c r="J27" s="127"/>
+      <c r="K27" s="127"/>
+      <c r="L27" s="127"/>
+      <c r="M27" s="127"/>
+      <c r="N27" s="127"/>
+      <c r="O27" s="127"/>
+      <c r="P27" s="127"/>
+      <c r="Q27" s="127"/>
+      <c r="R27" s="127"/>
+      <c r="S27" s="127"/>
+      <c r="T27" s="127"/>
+      <c r="U27" s="127"/>
+      <c r="V27" s="127"/>
+      <c r="W27" s="127"/>
+      <c r="X27" s="127"/>
+      <c r="Y27" s="127"/>
+      <c r="Z27" s="127"/>
+      <c r="AA27" s="128"/>
+      <c r="AB27" s="155">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AC27" s="139"/>
+      <c r="AD27" s="156"/>
+    </row>
+    <row r="28" spans="1:32" ht="15.75">
+      <c r="A28" s="129">
+        <v>28</v>
+      </c>
+      <c r="B28" s="130" t="s">
+        <v>4</v>
+      </c>
+      <c r="C28" s="131"/>
+      <c r="D28" s="131"/>
+      <c r="E28" s="131"/>
+      <c r="F28" s="131"/>
+      <c r="G28" s="131"/>
+      <c r="H28" s="131"/>
+      <c r="I28" s="131"/>
+      <c r="J28" s="131"/>
+      <c r="K28" s="131"/>
+      <c r="L28" s="131"/>
+      <c r="M28" s="131"/>
+      <c r="N28" s="131"/>
+      <c r="O28" s="131"/>
+      <c r="P28" s="131"/>
+      <c r="Q28" s="131"/>
+      <c r="R28" s="131"/>
+      <c r="S28" s="131"/>
+      <c r="T28" s="131"/>
+      <c r="U28" s="131"/>
+      <c r="V28" s="131"/>
+      <c r="W28" s="131"/>
+      <c r="X28" s="131"/>
+      <c r="Y28" s="131"/>
+      <c r="Z28" s="131"/>
+      <c r="AA28" s="132"/>
+      <c r="AB28" s="155">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AC28" s="139"/>
+      <c r="AD28" s="156"/>
+    </row>
+    <row r="29" spans="1:32" ht="15.75">
+      <c r="A29" s="125">
         <v>29</v>
       </c>
-      <c r="E2" s="138" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" s="138" t="s">
-        <v>33</v>
-      </c>
-      <c r="G2" s="138" t="s">
-        <v>34</v>
-      </c>
-      <c r="H2" s="138" t="s">
-        <v>11</v>
-      </c>
-      <c r="I2" s="139" t="s">
+      <c r="B29" s="126" t="s">
+        <v>5</v>
+      </c>
+      <c r="C29" s="127"/>
+      <c r="D29" s="127"/>
+      <c r="E29" s="127"/>
+      <c r="F29" s="127"/>
+      <c r="G29" s="127"/>
+      <c r="H29" s="127"/>
+      <c r="I29" s="127"/>
+      <c r="J29" s="127"/>
+      <c r="K29" s="127"/>
+      <c r="L29" s="127"/>
+      <c r="M29" s="127"/>
+      <c r="N29" s="127"/>
+      <c r="O29" s="127"/>
+      <c r="P29" s="127"/>
+      <c r="Q29" s="127"/>
+      <c r="R29" s="127"/>
+      <c r="S29" s="127"/>
+      <c r="T29" s="127"/>
+      <c r="U29" s="127"/>
+      <c r="V29" s="127"/>
+      <c r="W29" s="127"/>
+      <c r="X29" s="127"/>
+      <c r="Y29" s="127"/>
+      <c r="Z29" s="127"/>
+      <c r="AA29" s="128"/>
+      <c r="AB29" s="155">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AC29" s="139"/>
+      <c r="AD29" s="156"/>
+    </row>
+    <row r="30" spans="1:32" ht="15.75">
+      <c r="A30" s="129">
         <v>30</v>
       </c>
-      <c r="J2" s="139" t="s">
-        <v>12</v>
-      </c>
-      <c r="K2" s="140" t="s">
-        <v>24</v>
-      </c>
-      <c r="L2" s="140" t="s">
-        <v>23</v>
-      </c>
-      <c r="M2" s="140" t="s">
-        <v>13</v>
-      </c>
-      <c r="N2" s="140" t="s">
-        <v>14</v>
-      </c>
-      <c r="O2" s="140" t="s">
-        <v>15</v>
-      </c>
-      <c r="P2" s="140" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q2" s="140" t="s">
-        <v>28</v>
-      </c>
-      <c r="R2" s="140" t="s">
-        <v>17</v>
-      </c>
-      <c r="S2" s="140" t="s">
-        <v>18</v>
-      </c>
-      <c r="T2" s="140" t="s">
-        <v>25</v>
-      </c>
-      <c r="U2" s="140" t="s">
-        <v>25</v>
-      </c>
-      <c r="V2" s="140" t="s">
-        <v>26</v>
-      </c>
-      <c r="W2" s="141" t="s">
-        <v>60</v>
-      </c>
-      <c r="X2" s="142" t="s">
-        <v>22</v>
-      </c>
-      <c r="Y2" s="142" t="s">
-        <v>19</v>
-      </c>
-      <c r="Z2" s="142" t="s">
-        <v>21</v>
-      </c>
-      <c r="AA2" s="1"/>
-      <c r="AB2" s="1"/>
-      <c r="AC2" s="1"/>
-      <c r="AD2" s="1"/>
-      <c r="AE2" s="1"/>
-      <c r="AF2" s="1"/>
-      <c r="AG2" s="1"/>
-      <c r="AH2" s="1"/>
-      <c r="AI2" s="1"/>
-      <c r="AJ2" s="1"/>
-      <c r="AK2" s="1"/>
-      <c r="AL2" s="1"/>
-      <c r="AM2" s="1"/>
-      <c r="AN2" s="1"/>
-      <c r="AO2" s="1"/>
-      <c r="AP2" s="1"/>
-      <c r="AQ2" s="1"/>
-      <c r="AR2" s="1"/>
-      <c r="AS2" s="1"/>
-      <c r="AT2" s="1"/>
-      <c r="AU2" s="1"/>
-      <c r="AV2" s="1"/>
-    </row>
-    <row r="3" spans="1:48" ht="15.75">
-      <c r="A3" s="134">
+      <c r="B30" s="130" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" s="131"/>
+      <c r="D30" s="131"/>
+      <c r="E30" s="131"/>
+      <c r="F30" s="131"/>
+      <c r="G30" s="131"/>
+      <c r="H30" s="131"/>
+      <c r="I30" s="131"/>
+      <c r="J30" s="131"/>
+      <c r="K30" s="131"/>
+      <c r="L30" s="131"/>
+      <c r="M30" s="131"/>
+      <c r="N30" s="131"/>
+      <c r="O30" s="131"/>
+      <c r="P30" s="131"/>
+      <c r="Q30" s="131"/>
+      <c r="R30" s="131"/>
+      <c r="S30" s="131"/>
+      <c r="T30" s="131"/>
+      <c r="U30" s="131"/>
+      <c r="V30" s="131"/>
+      <c r="W30" s="131"/>
+      <c r="X30" s="131"/>
+      <c r="Y30" s="131"/>
+      <c r="Z30" s="131"/>
+      <c r="AA30" s="132"/>
+      <c r="AB30" s="155">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AC30" s="139"/>
+      <c r="AD30" s="156"/>
+    </row>
+    <row r="31" spans="1:32" ht="15.75">
+      <c r="A31" s="125">
+        <v>31</v>
+      </c>
+      <c r="B31" s="126" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31" s="127"/>
+      <c r="D31" s="127"/>
+      <c r="E31" s="127"/>
+      <c r="F31" s="127"/>
+      <c r="G31" s="127"/>
+      <c r="H31" s="127"/>
+      <c r="I31" s="127"/>
+      <c r="J31" s="127"/>
+      <c r="K31" s="127"/>
+      <c r="L31" s="127"/>
+      <c r="M31" s="127"/>
+      <c r="N31" s="127"/>
+      <c r="O31" s="127"/>
+      <c r="P31" s="127"/>
+      <c r="Q31" s="127"/>
+      <c r="R31" s="127"/>
+      <c r="S31" s="127"/>
+      <c r="T31" s="127"/>
+      <c r="U31" s="127"/>
+      <c r="V31" s="127"/>
+      <c r="W31" s="127"/>
+      <c r="X31" s="127"/>
+      <c r="Y31" s="127"/>
+      <c r="Z31" s="127"/>
+      <c r="AA31" s="128"/>
+      <c r="AB31" s="155">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AC31" s="139"/>
+      <c r="AD31" s="156"/>
+    </row>
+    <row r="32" spans="1:32" ht="15.75">
+      <c r="A32" s="129">
+        <v>1</v>
+      </c>
+      <c r="B32" s="130" t="s">
+        <v>8</v>
+      </c>
+      <c r="C32" s="131"/>
+      <c r="D32" s="131"/>
+      <c r="E32" s="131"/>
+      <c r="F32" s="131"/>
+      <c r="G32" s="131"/>
+      <c r="H32" s="131"/>
+      <c r="I32" s="131"/>
+      <c r="J32" s="131"/>
+      <c r="K32" s="131"/>
+      <c r="L32" s="131"/>
+      <c r="M32" s="131"/>
+      <c r="N32" s="131"/>
+      <c r="O32" s="131"/>
+      <c r="P32" s="131"/>
+      <c r="Q32" s="131"/>
+      <c r="R32" s="131"/>
+      <c r="S32" s="131"/>
+      <c r="T32" s="131"/>
+      <c r="U32" s="131"/>
+      <c r="V32" s="131"/>
+      <c r="W32" s="131"/>
+      <c r="X32" s="131"/>
+      <c r="Y32" s="131"/>
+      <c r="Z32" s="131"/>
+      <c r="AA32" s="132"/>
+      <c r="AB32" s="155">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AC32" s="139"/>
+      <c r="AD32" s="156"/>
+    </row>
+    <row r="33" spans="1:30" ht="15.75">
+      <c r="A33" s="125">
+        <v>2</v>
+      </c>
+      <c r="B33" s="126" t="s">
+        <v>2</v>
+      </c>
+      <c r="C33" s="127"/>
+      <c r="D33" s="127"/>
+      <c r="E33" s="127"/>
+      <c r="F33" s="127"/>
+      <c r="G33" s="127"/>
+      <c r="H33" s="127"/>
+      <c r="I33" s="127"/>
+      <c r="J33" s="127"/>
+      <c r="K33" s="127"/>
+      <c r="L33" s="127"/>
+      <c r="M33" s="127"/>
+      <c r="N33" s="127"/>
+      <c r="O33" s="127"/>
+      <c r="P33" s="127"/>
+      <c r="Q33" s="127"/>
+      <c r="R33" s="127"/>
+      <c r="S33" s="127"/>
+      <c r="T33" s="127"/>
+      <c r="U33" s="127"/>
+      <c r="V33" s="127"/>
+      <c r="W33" s="127"/>
+      <c r="X33" s="127"/>
+      <c r="Y33" s="127"/>
+      <c r="Z33" s="127"/>
+      <c r="AA33" s="128"/>
+      <c r="AB33" s="155">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AC33" s="139"/>
+      <c r="AD33" s="156"/>
+    </row>
+    <row r="34" spans="1:30" ht="15.75">
+      <c r="A34" s="129">
         <v>3</v>
       </c>
-      <c r="B3" s="135" t="s">
+      <c r="B34" s="130" t="s">
+        <v>3</v>
+      </c>
+      <c r="C34" s="131"/>
+      <c r="D34" s="131"/>
+      <c r="E34" s="131"/>
+      <c r="F34" s="131"/>
+      <c r="G34" s="131"/>
+      <c r="H34" s="131"/>
+      <c r="I34" s="131"/>
+      <c r="J34" s="131"/>
+      <c r="K34" s="131"/>
+      <c r="L34" s="131"/>
+      <c r="M34" s="131"/>
+      <c r="N34" s="131"/>
+      <c r="O34" s="131"/>
+      <c r="P34" s="131"/>
+      <c r="Q34" s="131"/>
+      <c r="R34" s="131"/>
+      <c r="S34" s="131"/>
+      <c r="T34" s="131"/>
+      <c r="U34" s="131"/>
+      <c r="V34" s="131"/>
+      <c r="W34" s="131"/>
+      <c r="X34" s="131"/>
+      <c r="Y34" s="131"/>
+      <c r="Z34" s="131"/>
+      <c r="AA34" s="132"/>
+      <c r="AB34" s="155">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AC34" s="139"/>
+      <c r="AD34" s="156"/>
+    </row>
+    <row r="35" spans="1:30" ht="15.75">
+      <c r="A35" s="125">
         <v>4</v>
       </c>
-      <c r="C3" s="136"/>
-      <c r="D3" s="136"/>
-      <c r="E3" s="136"/>
-      <c r="F3" s="136"/>
-      <c r="G3" s="136"/>
-      <c r="H3" s="136"/>
-      <c r="I3" s="136"/>
-      <c r="J3" s="136"/>
-      <c r="K3" s="136"/>
-      <c r="L3" s="136"/>
-      <c r="M3" s="136"/>
-      <c r="N3" s="136"/>
-      <c r="O3" s="136"/>
-      <c r="P3" s="136"/>
-      <c r="Q3" s="136"/>
-      <c r="R3" s="136"/>
-      <c r="S3" s="136"/>
-      <c r="T3" s="136"/>
-      <c r="U3" s="136"/>
-      <c r="V3" s="136"/>
-      <c r="W3" s="136"/>
-      <c r="X3" s="137">
-        <f>SUM(C3:V3)</f>
-        <v>0</v>
-      </c>
-      <c r="Y3" s="144"/>
-      <c r="Z3" s="131"/>
-    </row>
-    <row r="4" spans="1:48" ht="15.75">
-      <c r="A4" s="66">
+      <c r="B35" s="126" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="67" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="72"/>
-      <c r="D4" s="72"/>
-      <c r="E4" s="72"/>
-      <c r="F4" s="72"/>
-      <c r="G4" s="72"/>
-      <c r="H4" s="72"/>
-      <c r="I4" s="72"/>
-      <c r="J4" s="72"/>
-      <c r="K4" s="72"/>
-      <c r="L4" s="72"/>
-      <c r="M4" s="72"/>
-      <c r="N4" s="72"/>
-      <c r="O4" s="72"/>
-      <c r="P4" s="72"/>
-      <c r="Q4" s="72"/>
-      <c r="R4" s="72"/>
-      <c r="S4" s="72"/>
-      <c r="T4" s="72"/>
-      <c r="U4" s="72"/>
-      <c r="V4" s="72"/>
-      <c r="W4" s="72"/>
-      <c r="X4" s="88">
-        <f>SUM(C4:V4)</f>
-        <v>0</v>
-      </c>
-      <c r="Y4" s="145"/>
-      <c r="Z4" s="131"/>
-    </row>
-    <row r="5" spans="1:48" ht="15.75">
-      <c r="A5" s="62">
-        <v>5</v>
-      </c>
-      <c r="B5" s="63" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="71"/>
-      <c r="D5" s="71"/>
-      <c r="E5" s="71"/>
-      <c r="F5" s="71"/>
-      <c r="G5" s="71"/>
-      <c r="H5" s="71"/>
-      <c r="I5" s="71"/>
-      <c r="J5" s="71"/>
-      <c r="K5" s="71"/>
-      <c r="L5" s="71"/>
-      <c r="M5" s="71"/>
-      <c r="N5" s="71"/>
-      <c r="O5" s="71"/>
-      <c r="P5" s="71"/>
-      <c r="Q5" s="71"/>
-      <c r="R5" s="71"/>
-      <c r="S5" s="71"/>
-      <c r="T5" s="71"/>
-      <c r="U5" s="71"/>
-      <c r="V5" s="71"/>
-      <c r="W5" s="71"/>
-      <c r="X5" s="87">
-        <f t="shared" ref="X5:X19" si="0">SUM(C5:V5)</f>
-        <v>0</v>
-      </c>
-      <c r="Y5" s="145"/>
-      <c r="Z5" s="131"/>
-    </row>
-    <row r="6" spans="1:48" ht="15.75">
-      <c r="A6" s="66">
-        <v>6</v>
-      </c>
-      <c r="B6" s="67" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="72"/>
-      <c r="D6" s="72"/>
-      <c r="E6" s="72"/>
-      <c r="F6" s="72"/>
-      <c r="G6" s="72"/>
-      <c r="H6" s="72"/>
-      <c r="I6" s="72"/>
-      <c r="J6" s="72"/>
-      <c r="K6" s="72"/>
-      <c r="L6" s="72"/>
-      <c r="M6" s="72"/>
-      <c r="N6" s="72"/>
-      <c r="O6" s="72"/>
-      <c r="P6" s="72"/>
-      <c r="Q6" s="72"/>
-      <c r="R6" s="72"/>
-      <c r="S6" s="72"/>
-      <c r="T6" s="72"/>
-      <c r="U6" s="72"/>
-      <c r="V6" s="72"/>
-      <c r="W6" s="72"/>
-      <c r="X6" s="88">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Y6" s="145"/>
-      <c r="Z6" s="131"/>
-    </row>
-    <row r="7" spans="1:48" ht="15" customHeight="1">
-      <c r="A7" s="62">
-        <v>7</v>
-      </c>
-      <c r="B7" s="63" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" s="71"/>
-      <c r="D7" s="71"/>
-      <c r="E7" s="71"/>
-      <c r="F7" s="71"/>
-      <c r="G7" s="71"/>
-      <c r="H7" s="71"/>
-      <c r="I7" s="71"/>
-      <c r="J7" s="71"/>
-      <c r="K7" s="71"/>
-      <c r="L7" s="71"/>
-      <c r="M7" s="71"/>
-      <c r="N7" s="71"/>
-      <c r="O7" s="71"/>
-      <c r="P7" s="71"/>
-      <c r="Q7" s="71"/>
-      <c r="R7" s="71"/>
-      <c r="S7" s="71"/>
-      <c r="T7" s="71"/>
-      <c r="U7" s="71"/>
-      <c r="V7" s="71"/>
-      <c r="W7" s="71"/>
-      <c r="X7" s="87">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Y7" s="145"/>
-      <c r="Z7" s="131"/>
-    </row>
-    <row r="8" spans="1:48" ht="15.75">
-      <c r="A8" s="66">
-        <v>8</v>
-      </c>
-      <c r="B8" s="67" t="s">
-        <v>2</v>
-      </c>
-      <c r="C8" s="72"/>
-      <c r="D8" s="72"/>
-      <c r="E8" s="72"/>
-      <c r="F8" s="72"/>
-      <c r="G8" s="72"/>
-      <c r="H8" s="72"/>
-      <c r="I8" s="72"/>
-      <c r="J8" s="72"/>
-      <c r="K8" s="72"/>
-      <c r="L8" s="72"/>
-      <c r="M8" s="72"/>
-      <c r="N8" s="72"/>
-      <c r="O8" s="72"/>
-      <c r="P8" s="72"/>
-      <c r="Q8" s="72"/>
-      <c r="R8" s="72"/>
-      <c r="S8" s="72"/>
-      <c r="T8" s="72"/>
-      <c r="U8" s="72"/>
-      <c r="V8" s="72"/>
-      <c r="W8" s="72"/>
-      <c r="X8" s="88">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Y8" s="145"/>
-      <c r="Z8" s="131"/>
-    </row>
-    <row r="9" spans="1:48" ht="15.75">
-      <c r="A9" s="62">
-        <v>9</v>
-      </c>
-      <c r="B9" s="63" t="s">
-        <v>3</v>
-      </c>
-      <c r="C9" s="71"/>
-      <c r="D9" s="71"/>
-      <c r="E9" s="71"/>
-      <c r="F9" s="71"/>
-      <c r="G9" s="71"/>
-      <c r="H9" s="71"/>
-      <c r="I9" s="71"/>
-      <c r="J9" s="71"/>
-      <c r="K9" s="71"/>
-      <c r="L9" s="71"/>
-      <c r="M9" s="71"/>
-      <c r="N9" s="71"/>
-      <c r="O9" s="71"/>
-      <c r="P9" s="71"/>
-      <c r="Q9" s="71"/>
-      <c r="R9" s="71"/>
-      <c r="S9" s="71"/>
-      <c r="T9" s="71"/>
-      <c r="U9" s="71"/>
-      <c r="V9" s="71"/>
-      <c r="W9" s="71"/>
-      <c r="X9" s="87">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Y9" s="145"/>
-      <c r="Z9" s="131"/>
-    </row>
-    <row r="10" spans="1:48" ht="15.75">
-      <c r="A10" s="66">
-        <v>10</v>
-      </c>
-      <c r="B10" s="67" t="s">
-        <v>4</v>
-      </c>
-      <c r="C10" s="72"/>
-      <c r="D10" s="72"/>
-      <c r="E10" s="72"/>
-      <c r="F10" s="72"/>
-      <c r="G10" s="72"/>
-      <c r="H10" s="72"/>
-      <c r="I10" s="72"/>
-      <c r="J10" s="72"/>
-      <c r="K10" s="72"/>
-      <c r="L10" s="72"/>
-      <c r="M10" s="72"/>
-      <c r="N10" s="72"/>
-      <c r="O10" s="72"/>
-      <c r="P10" s="72"/>
-      <c r="Q10" s="72"/>
-      <c r="R10" s="72"/>
-      <c r="S10" s="72"/>
-      <c r="T10" s="72"/>
-      <c r="U10" s="72"/>
-      <c r="V10" s="72"/>
-      <c r="W10" s="72"/>
-      <c r="X10" s="88">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Y10" s="145"/>
-      <c r="Z10" s="131"/>
-    </row>
-    <row r="11" spans="1:48" ht="15.75">
-      <c r="A11" s="62">
-        <v>11</v>
-      </c>
-      <c r="B11" s="63" t="s">
-        <v>5</v>
-      </c>
-      <c r="C11" s="71"/>
-      <c r="D11" s="71"/>
-      <c r="E11" s="71"/>
-      <c r="F11" s="71"/>
-      <c r="G11" s="71"/>
-      <c r="H11" s="71"/>
-      <c r="I11" s="71"/>
-      <c r="J11" s="71"/>
-      <c r="K11" s="71"/>
-      <c r="L11" s="71"/>
-      <c r="M11" s="71"/>
-      <c r="N11" s="71"/>
-      <c r="O11" s="71"/>
-      <c r="P11" s="71"/>
-      <c r="Q11" s="71"/>
-      <c r="R11" s="71"/>
-      <c r="S11" s="71"/>
-      <c r="T11" s="71"/>
-      <c r="U11" s="71"/>
-      <c r="V11" s="71"/>
-      <c r="W11" s="71"/>
-      <c r="X11" s="87">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Y11" s="145"/>
-      <c r="Z11" s="131"/>
-    </row>
-    <row r="12" spans="1:48" ht="15.75">
-      <c r="A12" s="66">
-        <v>12</v>
-      </c>
-      <c r="B12" s="67" t="s">
-        <v>6</v>
-      </c>
-      <c r="C12" s="72"/>
-      <c r="D12" s="72"/>
-      <c r="E12" s="72"/>
-      <c r="F12" s="72"/>
-      <c r="G12" s="72"/>
-      <c r="H12" s="72"/>
-      <c r="I12" s="72"/>
-      <c r="J12" s="72"/>
-      <c r="K12" s="72"/>
-      <c r="L12" s="72"/>
-      <c r="M12" s="72"/>
-      <c r="N12" s="72"/>
-      <c r="O12" s="72"/>
-      <c r="P12" s="72"/>
-      <c r="Q12" s="72"/>
-      <c r="R12" s="72"/>
-      <c r="S12" s="72"/>
-      <c r="T12" s="72"/>
-      <c r="U12" s="72"/>
-      <c r="V12" s="72"/>
-      <c r="W12" s="72"/>
-      <c r="X12" s="88">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Y12" s="145"/>
-      <c r="Z12" s="131"/>
-    </row>
-    <row r="13" spans="1:48" ht="15.75">
-      <c r="A13" s="62">
-        <v>13</v>
-      </c>
-      <c r="B13" s="63" t="s">
-        <v>7</v>
-      </c>
-      <c r="C13" s="71"/>
-      <c r="D13" s="71"/>
-      <c r="E13" s="71"/>
-      <c r="F13" s="71"/>
-      <c r="G13" s="71"/>
-      <c r="H13" s="71"/>
-      <c r="I13" s="71"/>
-      <c r="J13" s="71"/>
-      <c r="K13" s="71"/>
-      <c r="L13" s="71"/>
-      <c r="M13" s="71"/>
-      <c r="N13" s="71"/>
-      <c r="O13" s="71"/>
-      <c r="P13" s="71"/>
-      <c r="Q13" s="71"/>
-      <c r="R13" s="71"/>
-      <c r="S13" s="71"/>
-      <c r="T13" s="71"/>
-      <c r="U13" s="71"/>
-      <c r="V13" s="71"/>
-      <c r="W13" s="71"/>
-      <c r="X13" s="87">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Y13" s="145"/>
-      <c r="Z13" s="131"/>
-    </row>
-    <row r="14" spans="1:48" ht="15.75">
-      <c r="A14" s="66">
-        <v>14</v>
-      </c>
-      <c r="B14" s="67" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" s="72"/>
-      <c r="D14" s="72"/>
-      <c r="E14" s="72"/>
-      <c r="F14" s="72"/>
-      <c r="G14" s="72"/>
-      <c r="H14" s="72"/>
-      <c r="I14" s="72"/>
-      <c r="J14" s="72"/>
-      <c r="K14" s="72"/>
-      <c r="L14" s="72"/>
-      <c r="M14" s="72"/>
-      <c r="N14" s="72"/>
-      <c r="O14" s="72"/>
-      <c r="P14" s="72"/>
-      <c r="Q14" s="72"/>
-      <c r="R14" s="72"/>
-      <c r="S14" s="72"/>
-      <c r="T14" s="72"/>
-      <c r="U14" s="72"/>
-      <c r="V14" s="72"/>
-      <c r="W14" s="72"/>
-      <c r="X14" s="88">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Y14" s="146"/>
-      <c r="Z14" s="131"/>
-    </row>
-    <row r="15" spans="1:48" ht="15.75">
-      <c r="A15" s="62">
-        <v>15</v>
-      </c>
-      <c r="B15" s="63" t="s">
-        <v>2</v>
-      </c>
-      <c r="C15" s="71"/>
-      <c r="D15" s="71"/>
-      <c r="E15" s="71"/>
-      <c r="F15" s="71"/>
-      <c r="G15" s="71"/>
-      <c r="H15" s="71"/>
-      <c r="I15" s="71"/>
-      <c r="J15" s="71"/>
-      <c r="K15" s="71"/>
-      <c r="L15" s="71"/>
-      <c r="M15" s="71"/>
-      <c r="N15" s="71"/>
-      <c r="O15" s="71"/>
-      <c r="P15" s="71"/>
-      <c r="Q15" s="71"/>
-      <c r="R15" s="71"/>
-      <c r="S15" s="71"/>
-      <c r="T15" s="71"/>
-      <c r="U15" s="71"/>
-      <c r="V15" s="71"/>
-      <c r="W15" s="71"/>
-      <c r="X15" s="87">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Y15" s="145"/>
-      <c r="Z15" s="131"/>
-    </row>
-    <row r="16" spans="1:48" ht="15.75">
-      <c r="A16" s="66">
-        <v>16</v>
-      </c>
-      <c r="B16" s="67" t="s">
-        <v>3</v>
-      </c>
-      <c r="C16" s="72"/>
-      <c r="D16" s="72"/>
-      <c r="E16" s="72"/>
-      <c r="F16" s="72"/>
-      <c r="G16" s="72"/>
-      <c r="H16" s="72"/>
-      <c r="I16" s="72"/>
-      <c r="J16" s="72"/>
-      <c r="K16" s="72"/>
-      <c r="L16" s="72"/>
-      <c r="M16" s="72"/>
-      <c r="N16" s="72"/>
-      <c r="O16" s="72"/>
-      <c r="P16" s="72"/>
-      <c r="Q16" s="72"/>
-      <c r="R16" s="72"/>
-      <c r="S16" s="72"/>
-      <c r="T16" s="72"/>
-      <c r="U16" s="86"/>
-      <c r="V16" s="72"/>
-      <c r="W16" s="72"/>
-      <c r="X16" s="88">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Y16" s="145"/>
-      <c r="Z16" s="131"/>
-    </row>
-    <row r="17" spans="1:28" ht="15.75">
-      <c r="A17" s="62">
-        <v>17</v>
-      </c>
-      <c r="B17" s="63" t="s">
-        <v>4</v>
-      </c>
-      <c r="C17" s="71"/>
-      <c r="D17" s="71"/>
-      <c r="E17" s="71"/>
-      <c r="F17" s="71"/>
-      <c r="G17" s="71"/>
-      <c r="H17" s="71"/>
-      <c r="I17" s="71"/>
-      <c r="J17" s="71"/>
-      <c r="K17" s="71"/>
-      <c r="L17" s="71"/>
-      <c r="M17" s="71"/>
-      <c r="N17" s="71"/>
-      <c r="O17" s="71"/>
-      <c r="P17" s="71"/>
-      <c r="Q17" s="71"/>
-      <c r="R17" s="71"/>
-      <c r="S17" s="71"/>
-      <c r="T17" s="71"/>
-      <c r="U17" s="71"/>
-      <c r="V17" s="71"/>
-      <c r="W17" s="71"/>
-      <c r="X17" s="87">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Y17" s="145"/>
-      <c r="Z17" s="131"/>
-    </row>
-    <row r="18" spans="1:28" ht="15.75">
-      <c r="A18" s="66">
-        <v>18</v>
-      </c>
-      <c r="B18" s="67" t="s">
-        <v>5</v>
-      </c>
-      <c r="C18" s="72"/>
-      <c r="D18" s="72"/>
-      <c r="E18" s="72"/>
-      <c r="F18" s="72"/>
-      <c r="G18" s="72"/>
-      <c r="H18" s="72"/>
-      <c r="I18" s="72"/>
-      <c r="J18" s="72"/>
-      <c r="K18" s="72"/>
-      <c r="L18" s="72"/>
-      <c r="M18" s="72"/>
-      <c r="N18" s="72"/>
-      <c r="O18" s="72"/>
-      <c r="P18" s="72"/>
-      <c r="Q18" s="72"/>
-      <c r="R18" s="72"/>
-      <c r="S18" s="72"/>
-      <c r="T18" s="86"/>
-      <c r="U18" s="72"/>
-      <c r="V18" s="72"/>
-      <c r="W18" s="72"/>
-      <c r="X18" s="88">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Y18" s="145"/>
-      <c r="Z18" s="131"/>
-    </row>
-    <row r="19" spans="1:28" ht="15.75">
-      <c r="A19" s="62">
-        <v>19</v>
-      </c>
-      <c r="B19" s="63" t="s">
-        <v>6</v>
-      </c>
-      <c r="C19" s="71"/>
-      <c r="D19" s="71"/>
-      <c r="E19" s="71"/>
-      <c r="F19" s="71"/>
-      <c r="G19" s="71"/>
-      <c r="H19" s="71"/>
-      <c r="I19" s="71"/>
-      <c r="J19" s="71"/>
-      <c r="K19" s="71"/>
-      <c r="L19" s="71"/>
-      <c r="M19" s="71"/>
-      <c r="N19" s="71"/>
-      <c r="O19" s="71"/>
-      <c r="P19" s="71"/>
-      <c r="Q19" s="71"/>
-      <c r="R19" s="71"/>
-      <c r="S19" s="71"/>
-      <c r="T19" s="71"/>
-      <c r="U19" s="71"/>
-      <c r="V19" s="71"/>
-      <c r="W19" s="71"/>
-      <c r="X19" s="87">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Y19" s="145"/>
-      <c r="Z19" s="132"/>
-    </row>
-    <row r="20" spans="1:28" ht="14.25" customHeight="1">
-      <c r="A20" s="123" t="s">
-        <v>35</v>
-      </c>
-      <c r="B20" s="123"/>
-      <c r="C20" s="79">
-        <f t="shared" ref="C20:Y20" si="1">SUM(C3:C17)</f>
-        <v>0</v>
-      </c>
-      <c r="D20" s="79">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E20" s="79">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F20" s="79">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G20" s="79">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H20" s="79">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I20" s="79">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J20" s="79">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K20" s="79">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L20" s="79">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="M20" s="79">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="N20" s="79">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="O20" s="79">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P20" s="79">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Q20" s="79">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="R20" s="79">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="S20" s="79">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="T20" s="79">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="U20" s="79">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="V20" s="79">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="W20" s="79"/>
-      <c r="X20" s="81">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Y20" s="90">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Z20" s="82">
-        <f>Y20-X20</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:28" ht="15.75">
-      <c r="A21" s="62">
-        <v>20</v>
-      </c>
-      <c r="B21" s="63" t="s">
-        <v>7</v>
-      </c>
-      <c r="C21" s="71"/>
-      <c r="D21" s="71"/>
-      <c r="E21" s="71"/>
-      <c r="F21" s="71"/>
-      <c r="G21" s="71"/>
-      <c r="H21" s="71"/>
-      <c r="I21" s="71"/>
-      <c r="J21" s="71"/>
-      <c r="K21" s="71"/>
-      <c r="L21" s="71"/>
-      <c r="M21" s="71"/>
-      <c r="N21" s="71"/>
-      <c r="O21" s="71"/>
-      <c r="P21" s="71"/>
-      <c r="Q21" s="71"/>
-      <c r="R21" s="71"/>
-      <c r="S21" s="71"/>
-      <c r="T21" s="71"/>
-      <c r="U21" s="71"/>
-      <c r="V21" s="71"/>
-      <c r="W21" s="71"/>
-      <c r="X21" s="87"/>
-      <c r="Y21" s="146"/>
-      <c r="Z21" s="130"/>
-    </row>
-    <row r="22" spans="1:28" ht="15.75">
-      <c r="A22" s="66">
-        <v>21</v>
-      </c>
-      <c r="B22" s="67" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="72"/>
-      <c r="D22" s="72"/>
-      <c r="E22" s="72"/>
-      <c r="F22" s="72"/>
-      <c r="G22" s="72"/>
-      <c r="H22" s="72"/>
-      <c r="I22" s="72"/>
-      <c r="J22" s="72"/>
-      <c r="K22" s="72"/>
-      <c r="L22" s="72"/>
-      <c r="M22" s="72"/>
-      <c r="N22" s="72"/>
-      <c r="O22" s="72"/>
-      <c r="P22" s="72"/>
-      <c r="Q22" s="72"/>
-      <c r="R22" s="72"/>
-      <c r="S22" s="72"/>
-      <c r="T22" s="72"/>
-      <c r="U22" s="72"/>
-      <c r="V22" s="72"/>
-      <c r="W22" s="72"/>
-      <c r="X22" s="88"/>
-      <c r="Y22" s="145"/>
-      <c r="Z22" s="131"/>
-      <c r="AB22" s="44"/>
-    </row>
-    <row r="23" spans="1:28" ht="15.75">
-      <c r="A23" s="62">
-        <v>22</v>
-      </c>
-      <c r="B23" s="63" t="s">
-        <v>2</v>
-      </c>
-      <c r="C23" s="71"/>
-      <c r="D23" s="71"/>
-      <c r="E23" s="71"/>
-      <c r="F23" s="71"/>
-      <c r="G23" s="71"/>
-      <c r="H23" s="71"/>
-      <c r="I23" s="71"/>
-      <c r="J23" s="71"/>
-      <c r="K23" s="71"/>
-      <c r="L23" s="71"/>
-      <c r="M23" s="71"/>
-      <c r="N23" s="71"/>
-      <c r="O23" s="71"/>
-      <c r="P23" s="71"/>
-      <c r="Q23" s="71"/>
-      <c r="R23" s="71"/>
-      <c r="S23" s="71"/>
-      <c r="T23" s="71"/>
-      <c r="U23" s="71"/>
-      <c r="V23" s="71"/>
-      <c r="W23" s="71"/>
-      <c r="X23" s="87"/>
-      <c r="Y23" s="145"/>
-      <c r="Z23" s="131"/>
-    </row>
-    <row r="24" spans="1:28" ht="15.75">
-      <c r="A24" s="66">
-        <v>23</v>
-      </c>
-      <c r="B24" s="67" t="s">
-        <v>3</v>
-      </c>
-      <c r="C24" s="72"/>
-      <c r="D24" s="72"/>
-      <c r="E24" s="72"/>
-      <c r="F24" s="72"/>
-      <c r="G24" s="72"/>
-      <c r="H24" s="72"/>
-      <c r="I24" s="72"/>
-      <c r="J24" s="72"/>
-      <c r="K24" s="72"/>
-      <c r="L24" s="72"/>
-      <c r="M24" s="72"/>
-      <c r="N24" s="72"/>
-      <c r="O24" s="72"/>
-      <c r="P24" s="72"/>
-      <c r="Q24" s="72"/>
-      <c r="R24" s="72"/>
-      <c r="S24" s="72"/>
-      <c r="T24" s="72"/>
-      <c r="U24" s="72"/>
-      <c r="V24" s="72"/>
-      <c r="W24" s="72"/>
-      <c r="X24" s="88"/>
-      <c r="Y24" s="145"/>
-      <c r="Z24" s="131"/>
-    </row>
-    <row r="25" spans="1:28" ht="15.75">
-      <c r="A25" s="62">
-        <v>24</v>
-      </c>
-      <c r="B25" s="63" t="s">
-        <v>4</v>
-      </c>
-      <c r="C25" s="71"/>
-      <c r="D25" s="71"/>
-      <c r="E25" s="71"/>
-      <c r="F25" s="71"/>
-      <c r="G25" s="71"/>
-      <c r="H25" s="71"/>
-      <c r="I25" s="71"/>
-      <c r="J25" s="71"/>
-      <c r="K25" s="71"/>
-      <c r="L25" s="71"/>
-      <c r="M25" s="71"/>
-      <c r="N25" s="71"/>
-      <c r="O25" s="71"/>
-      <c r="P25" s="71"/>
-      <c r="Q25" s="71"/>
-      <c r="R25" s="71"/>
-      <c r="S25" s="71"/>
-      <c r="T25" s="71"/>
-      <c r="U25" s="71"/>
-      <c r="V25" s="71"/>
-      <c r="W25" s="71"/>
-      <c r="X25" s="87"/>
-      <c r="Y25" s="145"/>
-      <c r="Z25" s="131"/>
-    </row>
-    <row r="26" spans="1:28" ht="15.75">
-      <c r="A26" s="66">
-        <v>25</v>
-      </c>
-      <c r="B26" s="67" t="s">
-        <v>5</v>
-      </c>
-      <c r="C26" s="72"/>
-      <c r="D26" s="72"/>
-      <c r="E26" s="72"/>
-      <c r="F26" s="72"/>
-      <c r="G26" s="72"/>
-      <c r="H26" s="72"/>
-      <c r="I26" s="72"/>
-      <c r="J26" s="72"/>
-      <c r="K26" s="72"/>
-      <c r="L26" s="72"/>
-      <c r="M26" s="72"/>
-      <c r="N26" s="72"/>
-      <c r="O26" s="72"/>
-      <c r="P26" s="72"/>
-      <c r="Q26" s="72"/>
-      <c r="R26" s="72"/>
-      <c r="S26" s="72"/>
-      <c r="T26" s="72"/>
-      <c r="U26" s="72"/>
-      <c r="V26" s="72"/>
-      <c r="W26" s="72"/>
-      <c r="X26" s="88"/>
-      <c r="Y26" s="145"/>
-      <c r="Z26" s="131"/>
-    </row>
-    <row r="27" spans="1:28" ht="15.75">
-      <c r="A27" s="62">
-        <v>26</v>
-      </c>
-      <c r="B27" s="63" t="s">
-        <v>6</v>
-      </c>
-      <c r="C27" s="71"/>
-      <c r="D27" s="71"/>
-      <c r="E27" s="71"/>
-      <c r="F27" s="71"/>
-      <c r="G27" s="71"/>
-      <c r="H27" s="71"/>
-      <c r="I27" s="71"/>
-      <c r="J27" s="71"/>
-      <c r="K27" s="71"/>
-      <c r="L27" s="71"/>
-      <c r="M27" s="71"/>
-      <c r="N27" s="71"/>
-      <c r="O27" s="71"/>
-      <c r="P27" s="71"/>
-      <c r="Q27" s="71"/>
-      <c r="R27" s="71"/>
-      <c r="S27" s="71"/>
-      <c r="T27" s="71"/>
-      <c r="U27" s="71"/>
-      <c r="V27" s="71"/>
-      <c r="W27" s="71"/>
-      <c r="X27" s="87"/>
-      <c r="Y27" s="146"/>
-      <c r="Z27" s="131"/>
-    </row>
-    <row r="28" spans="1:28" ht="15.75">
-      <c r="A28" s="66">
-        <v>27</v>
-      </c>
-      <c r="B28" s="67" t="s">
-        <v>7</v>
-      </c>
-      <c r="C28" s="72"/>
-      <c r="D28" s="72"/>
-      <c r="E28" s="72"/>
-      <c r="F28" s="72"/>
-      <c r="G28" s="72"/>
-      <c r="H28" s="72"/>
-      <c r="I28" s="72"/>
-      <c r="J28" s="72"/>
-      <c r="K28" s="72"/>
-      <c r="L28" s="72"/>
-      <c r="M28" s="72"/>
-      <c r="N28" s="72"/>
-      <c r="O28" s="72"/>
-      <c r="P28" s="72"/>
-      <c r="Q28" s="72"/>
-      <c r="R28" s="72"/>
-      <c r="S28" s="72"/>
-      <c r="T28" s="72"/>
-      <c r="U28" s="72"/>
-      <c r="V28" s="72"/>
-      <c r="W28" s="72"/>
-      <c r="X28" s="88"/>
-      <c r="Y28" s="145"/>
-      <c r="Z28" s="131"/>
-    </row>
-    <row r="29" spans="1:28" ht="15.75">
-      <c r="A29" s="62">
-        <v>28</v>
-      </c>
-      <c r="B29" s="63" t="s">
-        <v>8</v>
-      </c>
-      <c r="C29" s="71"/>
-      <c r="D29" s="71"/>
-      <c r="E29" s="71"/>
-      <c r="F29" s="71"/>
-      <c r="G29" s="71"/>
-      <c r="H29" s="71"/>
-      <c r="I29" s="71"/>
-      <c r="J29" s="71"/>
-      <c r="K29" s="71"/>
-      <c r="L29" s="71"/>
-      <c r="M29" s="71"/>
-      <c r="N29" s="71"/>
-      <c r="O29" s="71"/>
-      <c r="P29" s="71"/>
-      <c r="Q29" s="71"/>
-      <c r="R29" s="71"/>
-      <c r="S29" s="71"/>
-      <c r="T29" s="71"/>
-      <c r="U29" s="71"/>
-      <c r="V29" s="71"/>
-      <c r="W29" s="71"/>
-      <c r="X29" s="87"/>
-      <c r="Y29" s="145"/>
-      <c r="Z29" s="131"/>
-    </row>
-    <row r="30" spans="1:28" ht="15.75">
-      <c r="A30" s="66">
-        <v>29</v>
-      </c>
-      <c r="B30" s="67" t="s">
-        <v>2</v>
-      </c>
-      <c r="C30" s="72"/>
-      <c r="D30" s="72"/>
-      <c r="E30" s="72"/>
-      <c r="F30" s="72"/>
-      <c r="G30" s="72"/>
-      <c r="H30" s="72"/>
-      <c r="I30" s="72"/>
-      <c r="J30" s="72"/>
-      <c r="K30" s="72"/>
-      <c r="L30" s="72"/>
-      <c r="M30" s="72"/>
-      <c r="N30" s="72"/>
-      <c r="O30" s="72"/>
-      <c r="P30" s="72"/>
-      <c r="Q30" s="72"/>
-      <c r="R30" s="72"/>
-      <c r="S30" s="72"/>
-      <c r="T30" s="72"/>
-      <c r="U30" s="72"/>
-      <c r="V30" s="72"/>
-      <c r="W30" s="72"/>
-      <c r="X30" s="88"/>
-      <c r="Y30" s="145"/>
-      <c r="Z30" s="131"/>
-    </row>
-    <row r="31" spans="1:28" ht="15.75">
-      <c r="A31" s="62">
-        <v>30</v>
-      </c>
-      <c r="B31" s="63" t="s">
-        <v>3</v>
-      </c>
-      <c r="C31" s="71"/>
-      <c r="D31" s="71"/>
-      <c r="E31" s="71"/>
-      <c r="F31" s="71"/>
-      <c r="G31" s="71"/>
-      <c r="H31" s="71"/>
-      <c r="I31" s="71"/>
-      <c r="J31" s="71"/>
-      <c r="K31" s="71"/>
-      <c r="L31" s="71"/>
-      <c r="M31" s="71"/>
-      <c r="N31" s="71"/>
-      <c r="O31" s="71"/>
-      <c r="P31" s="71"/>
-      <c r="Q31" s="71"/>
-      <c r="R31" s="71"/>
-      <c r="S31" s="71"/>
-      <c r="T31" s="71"/>
-      <c r="U31" s="71"/>
-      <c r="V31" s="71"/>
-      <c r="W31" s="71"/>
-      <c r="X31" s="87"/>
-      <c r="Y31" s="145"/>
-      <c r="Z31" s="131"/>
-    </row>
-    <row r="32" spans="1:28" ht="15.75">
-      <c r="A32" s="66">
-        <v>31</v>
-      </c>
-      <c r="B32" s="67" t="s">
-        <v>4</v>
-      </c>
-      <c r="C32" s="72"/>
-      <c r="D32" s="72"/>
-      <c r="E32" s="72"/>
-      <c r="F32" s="72"/>
-      <c r="G32" s="72"/>
-      <c r="H32" s="72"/>
-      <c r="I32" s="72"/>
-      <c r="J32" s="72"/>
-      <c r="K32" s="72"/>
-      <c r="L32" s="72"/>
-      <c r="M32" s="72"/>
-      <c r="N32" s="72"/>
-      <c r="O32" s="72"/>
-      <c r="P32" s="72"/>
-      <c r="Q32" s="72"/>
-      <c r="R32" s="72"/>
-      <c r="S32" s="72"/>
-      <c r="T32" s="72"/>
-      <c r="U32" s="72"/>
-      <c r="V32" s="72"/>
-      <c r="W32" s="72"/>
-      <c r="X32" s="88"/>
-      <c r="Y32" s="145"/>
-      <c r="Z32" s="131"/>
-    </row>
-    <row r="33" spans="1:26" ht="15.75">
-      <c r="A33" s="62">
-        <v>1</v>
-      </c>
-      <c r="B33" s="63" t="s">
-        <v>5</v>
-      </c>
-      <c r="C33" s="71"/>
-      <c r="D33" s="71"/>
-      <c r="E33" s="71"/>
-      <c r="F33" s="71"/>
-      <c r="G33" s="71"/>
-      <c r="H33" s="71"/>
-      <c r="I33" s="71"/>
-      <c r="J33" s="71"/>
-      <c r="K33" s="71"/>
-      <c r="L33" s="71"/>
-      <c r="M33" s="71"/>
-      <c r="N33" s="71"/>
-      <c r="O33" s="71"/>
-      <c r="P33" s="71"/>
-      <c r="Q33" s="71"/>
-      <c r="R33" s="71"/>
-      <c r="S33" s="71"/>
-      <c r="T33" s="71"/>
-      <c r="U33" s="71"/>
-      <c r="V33" s="71"/>
-      <c r="W33" s="71"/>
-      <c r="X33" s="87"/>
-      <c r="Y33" s="145"/>
-      <c r="Z33" s="131"/>
-    </row>
-    <row r="34" spans="1:26" ht="15.75">
-      <c r="A34" s="66">
-        <v>2</v>
-      </c>
-      <c r="B34" s="67" t="s">
-        <v>6</v>
-      </c>
-      <c r="C34" s="72"/>
-      <c r="D34" s="72"/>
-      <c r="E34" s="72"/>
-      <c r="F34" s="72"/>
-      <c r="G34" s="72"/>
-      <c r="H34" s="72"/>
-      <c r="I34" s="72"/>
-      <c r="J34" s="72"/>
-      <c r="K34" s="72"/>
-      <c r="L34" s="72"/>
-      <c r="M34" s="72"/>
-      <c r="N34" s="72"/>
-      <c r="O34" s="72"/>
-      <c r="P34" s="72"/>
-      <c r="Q34" s="72"/>
-      <c r="R34" s="72"/>
-      <c r="S34" s="72"/>
-      <c r="T34" s="72"/>
-      <c r="U34" s="72"/>
-      <c r="V34" s="72"/>
-      <c r="W34" s="72"/>
-      <c r="X34" s="88"/>
-      <c r="Y34" s="145"/>
-      <c r="Z34" s="131"/>
-    </row>
-    <row r="35" spans="1:26" ht="15.75">
-      <c r="A35" s="62">
-        <v>3</v>
-      </c>
-      <c r="B35" s="63" t="s">
-        <v>7</v>
-      </c>
-      <c r="C35" s="71"/>
-      <c r="D35" s="71"/>
-      <c r="E35" s="71"/>
-      <c r="F35" s="71"/>
-      <c r="G35" s="71"/>
-      <c r="H35" s="71"/>
-      <c r="I35" s="71"/>
-      <c r="J35" s="71"/>
-      <c r="K35" s="71"/>
-      <c r="L35" s="71"/>
-      <c r="M35" s="71"/>
-      <c r="N35" s="71"/>
-      <c r="O35" s="71"/>
-      <c r="P35" s="71"/>
-      <c r="Q35" s="71"/>
-      <c r="R35" s="71"/>
-      <c r="S35" s="71"/>
-      <c r="T35" s="71"/>
-      <c r="U35" s="71"/>
-      <c r="V35" s="71"/>
-      <c r="W35" s="71"/>
-      <c r="X35" s="87"/>
-      <c r="Y35" s="145"/>
-      <c r="Z35" s="131"/>
-    </row>
-    <row r="36" spans="1:26" ht="15.75">
-      <c r="A36" s="66">
-        <v>4</v>
-      </c>
-      <c r="B36" s="67" t="s">
-        <v>8</v>
-      </c>
-      <c r="C36" s="72"/>
-      <c r="D36" s="72"/>
-      <c r="E36" s="72"/>
-      <c r="F36" s="72"/>
-      <c r="G36" s="72"/>
-      <c r="H36" s="72"/>
-      <c r="I36" s="72"/>
-      <c r="J36" s="72"/>
-      <c r="K36" s="72"/>
-      <c r="L36" s="72"/>
-      <c r="M36" s="72"/>
-      <c r="N36" s="72"/>
-      <c r="O36" s="72"/>
-      <c r="P36" s="72"/>
-      <c r="Q36" s="72"/>
-      <c r="R36" s="72"/>
-      <c r="S36" s="72"/>
-      <c r="T36" s="72"/>
-      <c r="U36" s="72"/>
-      <c r="V36" s="72"/>
-      <c r="W36" s="72"/>
-      <c r="X36" s="88"/>
-      <c r="Y36" s="145"/>
-      <c r="Z36" s="132"/>
-    </row>
-    <row r="37" spans="1:26">
-      <c r="A37" s="123" t="s">
+      <c r="C35" s="127"/>
+      <c r="D35" s="127"/>
+      <c r="E35" s="127"/>
+      <c r="F35" s="127"/>
+      <c r="G35" s="127"/>
+      <c r="H35" s="127"/>
+      <c r="I35" s="127"/>
+      <c r="J35" s="127"/>
+      <c r="K35" s="127"/>
+      <c r="L35" s="127"/>
+      <c r="M35" s="127"/>
+      <c r="N35" s="127"/>
+      <c r="O35" s="127"/>
+      <c r="P35" s="127"/>
+      <c r="Q35" s="127"/>
+      <c r="R35" s="127"/>
+      <c r="S35" s="127"/>
+      <c r="T35" s="127"/>
+      <c r="U35" s="127"/>
+      <c r="V35" s="127"/>
+      <c r="W35" s="127"/>
+      <c r="X35" s="127"/>
+      <c r="Y35" s="127"/>
+      <c r="Z35" s="127"/>
+      <c r="AA35" s="128"/>
+      <c r="AB35" s="155">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AC35" s="139"/>
+      <c r="AD35" s="156"/>
+    </row>
+    <row r="36" spans="1:30" ht="14.25" customHeight="1">
+      <c r="A36" s="136" t="s">
         <v>36</v>
       </c>
-      <c r="B37" s="123"/>
-      <c r="C37" s="79">
-        <f>SUM(C21:C36)</f>
-        <v>0</v>
-      </c>
-      <c r="D37" s="79">
-        <f t="shared" ref="D37:V37" si="2">SUM(D21:D36)</f>
-        <v>0</v>
-      </c>
-      <c r="E37" s="79">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="F37" s="79">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G37" s="79">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H37" s="79">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I37" s="79">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="J37" s="79">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K37" s="79">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="L37" s="79">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="M37" s="79">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="N37" s="79">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="O37" s="79">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="P37" s="79">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="Q37" s="79">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="R37" s="79">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="S37" s="79">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="T37" s="79">
-        <f>SUM(T21:T36)</f>
-        <v>0</v>
-      </c>
-      <c r="U37" s="79">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="V37" s="79">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="W37" s="79"/>
-      <c r="X37" s="81">
-        <f>SUM(X21:X36)</f>
-        <v>0</v>
-      </c>
-      <c r="Y37" s="89">
-        <f>SUM(Y21:Y36)</f>
-        <v>0</v>
-      </c>
-      <c r="Z37" s="83">
-        <f>Y37-X37</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:26" ht="31.5" customHeight="1">
-      <c r="A38" s="128" t="s">
+      <c r="B36" s="136"/>
+      <c r="C36" s="133">
+        <f>SUM(C20:C35)</f>
+        <v>0</v>
+      </c>
+      <c r="D36" s="133">
+        <f t="shared" ref="D36:K36" si="3">SUM(D20:D35)</f>
+        <v>0</v>
+      </c>
+      <c r="E36" s="133">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F36" s="133">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="G36" s="133">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H36" s="133">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I36" s="133">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J36" s="133">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K36" s="133">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L36" s="134">
+        <f>SUM(L20:L35)</f>
+        <v>0</v>
+      </c>
+      <c r="M36" s="134">
+        <f t="shared" ref="M36:Q36" si="4">SUM(M20:M35)</f>
+        <v>0</v>
+      </c>
+      <c r="N36" s="134">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="O36" s="134">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="P36" s="134">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Q36" s="134">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="R36" s="135">
+        <f>SUM(R20:R35)</f>
+        <v>0</v>
+      </c>
+      <c r="S36" s="135">
+        <f t="shared" ref="S36:AA36" si="5">SUM(S20:S35)</f>
+        <v>0</v>
+      </c>
+      <c r="T36" s="135">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="U36" s="135">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V36" s="135">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="W36" s="135">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="X36" s="135">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="Y36" s="135">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="Z36" s="135">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AA36" s="151">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AB36" s="157">
+        <f>SUM(AB20:AB35)</f>
+        <v>0</v>
+      </c>
+      <c r="AC36" s="158">
+        <f>SUM(AC20:AC35)</f>
+        <v>0</v>
+      </c>
+      <c r="AD36" s="161">
+        <f>AC36-AB36</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:30" ht="31.5" customHeight="1">
+      <c r="A37" s="137" t="s">
         <v>37</v>
       </c>
-      <c r="B38" s="128"/>
-      <c r="C38" s="78">
-        <f>SUM(C20,C37)</f>
-        <v>0</v>
-      </c>
-      <c r="D38" s="78">
-        <f t="shared" ref="D38:X38" si="3">SUM(D20,D37)</f>
-        <v>0</v>
-      </c>
-      <c r="E38" s="78">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="F38" s="78">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="G38" s="78">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="H38" s="78">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I38" s="78">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J38" s="78">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K38" s="78">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="L38" s="78">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="M38" s="78">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="N38" s="78">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="O38" s="78">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="P38" s="78">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="Q38" s="78">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="R38" s="78">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="S38" s="78">
-        <f>SUM(S20,S37)</f>
-        <v>0</v>
-      </c>
-      <c r="T38" s="78">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="U38" s="78">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="V38" s="78">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="W38" s="78"/>
-      <c r="X38" s="84">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="Y38" s="84">
-        <f>SUM(Y20,Y37)</f>
-        <v>0</v>
-      </c>
-      <c r="Z38" s="85">
-        <f>SUM(Z20,Z37)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:26">
-      <c r="B42" s="6"/>
-      <c r="C42" s="6"/>
-      <c r="D42" s="6"/>
-      <c r="E42" s="6"/>
-      <c r="F42" s="6"/>
-      <c r="G42" s="6"/>
-      <c r="H42" s="6"/>
-      <c r="I42" s="6"/>
-      <c r="J42" s="6"/>
-      <c r="K42" s="6"/>
+      <c r="B37" s="137"/>
+      <c r="C37" s="138">
+        <f>SUM(C19,C36)</f>
+        <v>429.95</v>
+      </c>
+      <c r="D37" s="138"/>
+      <c r="E37" s="138"/>
+      <c r="F37" s="138">
+        <f t="shared" ref="F37:AB37" si="6">SUM(F19,F36)</f>
+        <v>1812</v>
+      </c>
+      <c r="G37" s="138"/>
+      <c r="H37" s="138">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="I37" s="138">
+        <f t="shared" si="6"/>
+        <v>7935</v>
+      </c>
+      <c r="J37" s="138">
+        <f t="shared" si="6"/>
+        <v>3102</v>
+      </c>
+      <c r="K37" s="138">
+        <f t="shared" si="6"/>
+        <v>1860</v>
+      </c>
+      <c r="L37" s="138">
+        <f t="shared" si="6"/>
+        <v>10858.130000000001</v>
+      </c>
+      <c r="M37" s="138">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="N37" s="138">
+        <f t="shared" si="6"/>
+        <v>700</v>
+      </c>
+      <c r="O37" s="138"/>
+      <c r="P37" s="138"/>
+      <c r="Q37" s="138"/>
+      <c r="R37" s="138">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="S37" s="138"/>
+      <c r="T37" s="138">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U37" s="138">
+        <f t="shared" si="6"/>
+        <v>714</v>
+      </c>
+      <c r="V37" s="138">
+        <f t="shared" si="6"/>
+        <v>158.61000000000001</v>
+      </c>
+      <c r="W37" s="138">
+        <f t="shared" si="6"/>
+        <v>9624.98</v>
+      </c>
+      <c r="X37" s="138">
+        <f t="shared" si="6"/>
+        <v>1237</v>
+      </c>
+      <c r="Y37" s="138">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="Z37" s="138">
+        <f>SUM(Z19,Z36)</f>
+        <v>2626</v>
+      </c>
+      <c r="AA37" s="152">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AB37" s="159">
+        <f t="shared" si="6"/>
+        <v>60088.67</v>
+      </c>
+      <c r="AC37" s="160">
+        <f>SUM(AC19,AC36)</f>
+        <v>96705.110000000015</v>
+      </c>
+      <c r="AD37" s="162">
+        <f>SUM(AD19,AD36)</f>
+        <v>36616.440000000017</v>
+      </c>
+    </row>
+    <row r="41" spans="1:30">
+      <c r="B41" s="6"/>
+      <c r="C41" s="6"/>
+      <c r="D41" s="6"/>
+      <c r="E41" s="6"/>
+      <c r="F41" s="6"/>
+      <c r="G41" s="6"/>
+      <c r="H41" s="6"/>
+      <c r="I41" s="6"/>
+      <c r="J41" s="6"/>
+      <c r="K41" s="6"/>
+      <c r="L41" s="6"/>
+      <c r="M41" s="6"/>
+      <c r="N41" s="6"/>
+      <c r="O41" s="6"/>
+      <c r="P41" s="6"/>
+      <c r="Q41" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="A1:Z1"/>
-    <mergeCell ref="Z3:Z19"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="Z21:Z36"/>
+  <mergeCells count="11">
     <mergeCell ref="A37:B37"/>
+    <mergeCell ref="A1:AD1"/>
+    <mergeCell ref="AD4:AD18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="AD20:AD35"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="C2:K2"/>
+    <mergeCell ref="L2:Q2"/>
+    <mergeCell ref="R2:AA2"/>
+    <mergeCell ref="AB2:AD2"/>
+    <mergeCell ref="A2:B2"/>
   </mergeCells>
-  <conditionalFormatting sqref="Z20:Z21 Z37:Z38">
+  <conditionalFormatting sqref="AD19:AD20 AD36:AD37">
     <cfRule type="expression" dxfId="1" priority="1">
-      <formula>Z20&lt;0</formula>
+      <formula>AD19&lt;0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="0" priority="2">
-      <formula>Z20&gt;0</formula>
+      <formula>AD19&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/Другое/2026/Доходы-Расходы_copy.xlsx
+++ b/Другое/2026/Доходы-Расходы_copy.xlsx
@@ -4677,6 +4677,20 @@
         </r>
       </text>
     </comment>
+    <comment ref="F30" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Промясо
+</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="Q30" authorId="0">
       <text>
         <r>
@@ -4697,7 +4711,162 @@
             <charset val="1"/>
           </rPr>
           <t xml:space="preserve">
-На такси</t>
+На такси и еще на что-то</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="Y33" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Взял в долг у мамы.
+ЭТОТ ДОЛГ Я ОТДАЛ
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="S34" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Яндекс Плюс
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="T34" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>t2</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E35" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Яндекс лавка</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F35" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Феличита в обед</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="S35" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Литрес
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H36" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Феличита после работы</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="S36" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+ВК музыка</t>
         </r>
       </text>
     </comment>
@@ -4977,7 +5146,7 @@
             <family val="2"/>
             <charset val="204"/>
           </rPr>
-          <t xml:space="preserve">t2
+          <t xml:space="preserve">t2 + впн
 </t>
         </r>
       </text>
@@ -4993,6 +5162,34 @@
             <charset val="204"/>
           </rPr>
           <t xml:space="preserve">Илюхе за пейнтбол
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="Q10" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Сдал на ДР БГ
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="W10" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Купил ей поке и бабл ти
 </t>
         </r>
       </text>
@@ -6104,7 +6301,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="164">
+  <cellXfs count="165">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -6354,6 +6551,93 @@
     </xf>
     <xf numFmtId="164" fontId="23" fillId="27" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="35" fillId="28" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="29" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="29" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="17" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="17" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="33" fillId="30" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="33" fillId="31" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="34" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="33" fillId="33" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="13" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="23" fillId="13" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="37" fillId="29" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="30" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="31" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="34" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="34" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="34" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="33" fillId="33" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="35" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="32" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="35" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="20" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="33" fillId="35" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="33" fillId="20" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -6393,6 +6677,12 @@
     <xf numFmtId="0" fontId="25" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="35" fillId="28" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="17" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="28" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -6402,73 +6692,20 @@
     <xf numFmtId="164" fontId="23" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="28" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="17" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="33" fillId="33" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="38" fillId="28" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="30" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="23" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="23" fillId="29" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="23" fillId="29" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="23" fillId="17" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="23" fillId="17" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="33" fillId="30" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="33" fillId="31" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="27" fillId="34" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="29" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="33" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="33" fillId="33" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="23" fillId="13" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="23" fillId="13" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="37" fillId="29" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="30" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="31" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="34" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="40" fillId="30" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="43" fillId="31" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -6485,46 +6722,7 @@
     <xf numFmtId="0" fontId="38" fillId="28" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="34" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="27" fillId="34" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="33" fillId="33" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="35" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="20" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="23" fillId="32" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="23" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="27" fillId="35" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="27" fillId="20" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="33" fillId="35" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="33" fillId="20" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="21" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="164" fontId="23" fillId="20" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -6872,7 +7070,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -7119,32 +7317,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:46" ht="60.75" customHeight="1">
-      <c r="A1" s="105" t="s">
+      <c r="A1" s="136" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="105"/>
-      <c r="C1" s="105"/>
-      <c r="D1" s="105"/>
-      <c r="E1" s="105"/>
-      <c r="F1" s="105"/>
-      <c r="G1" s="105"/>
-      <c r="H1" s="105"/>
-      <c r="I1" s="105"/>
-      <c r="J1" s="105"/>
-      <c r="K1" s="105"/>
-      <c r="L1" s="105"/>
-      <c r="M1" s="105"/>
-      <c r="N1" s="105"/>
-      <c r="O1" s="105"/>
-      <c r="P1" s="105"/>
-      <c r="Q1" s="105"/>
-      <c r="R1" s="105"/>
-      <c r="S1" s="105"/>
-      <c r="T1" s="105"/>
-      <c r="U1" s="105"/>
-      <c r="V1" s="105"/>
-      <c r="W1" s="105"/>
-      <c r="X1" s="105"/>
+      <c r="B1" s="136"/>
+      <c r="C1" s="136"/>
+      <c r="D1" s="136"/>
+      <c r="E1" s="136"/>
+      <c r="F1" s="136"/>
+      <c r="G1" s="136"/>
+      <c r="H1" s="136"/>
+      <c r="I1" s="136"/>
+      <c r="J1" s="136"/>
+      <c r="K1" s="136"/>
+      <c r="L1" s="136"/>
+      <c r="M1" s="136"/>
+      <c r="N1" s="136"/>
+      <c r="O1" s="136"/>
+      <c r="P1" s="136"/>
+      <c r="Q1" s="136"/>
+      <c r="R1" s="136"/>
+      <c r="S1" s="136"/>
+      <c r="T1" s="136"/>
+      <c r="U1" s="136"/>
+      <c r="V1" s="136"/>
+      <c r="W1" s="136"/>
+      <c r="X1" s="136"/>
     </row>
     <row r="2" spans="1:46" ht="45" customHeight="1">
       <c r="A2" s="3" t="s">
@@ -8343,10 +8541,10 @@
       </c>
     </row>
     <row r="31" spans="1:24">
-      <c r="A31" s="106" t="s">
+      <c r="A31" s="137" t="s">
         <v>20</v>
       </c>
-      <c r="B31" s="106"/>
+      <c r="B31" s="137"/>
       <c r="C31" s="13">
         <f>SUM(C3:C30)</f>
         <v>19992.27</v>
@@ -8469,32 +8667,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:46" ht="60.75" customHeight="1">
-      <c r="A1" s="108" t="s">
+      <c r="A1" s="139" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="108"/>
-      <c r="C1" s="108"/>
-      <c r="D1" s="108"/>
-      <c r="E1" s="108"/>
-      <c r="F1" s="108"/>
-      <c r="G1" s="108"/>
-      <c r="H1" s="108"/>
-      <c r="I1" s="108"/>
-      <c r="J1" s="108"/>
-      <c r="K1" s="108"/>
-      <c r="L1" s="108"/>
-      <c r="M1" s="108"/>
-      <c r="N1" s="108"/>
-      <c r="O1" s="108"/>
-      <c r="P1" s="108"/>
-      <c r="Q1" s="108"/>
-      <c r="R1" s="108"/>
-      <c r="S1" s="108"/>
-      <c r="T1" s="108"/>
-      <c r="U1" s="108"/>
-      <c r="V1" s="108"/>
-      <c r="W1" s="108"/>
-      <c r="X1" s="108"/>
+      <c r="B1" s="139"/>
+      <c r="C1" s="139"/>
+      <c r="D1" s="139"/>
+      <c r="E1" s="139"/>
+      <c r="F1" s="139"/>
+      <c r="G1" s="139"/>
+      <c r="H1" s="139"/>
+      <c r="I1" s="139"/>
+      <c r="J1" s="139"/>
+      <c r="K1" s="139"/>
+      <c r="L1" s="139"/>
+      <c r="M1" s="139"/>
+      <c r="N1" s="139"/>
+      <c r="O1" s="139"/>
+      <c r="P1" s="139"/>
+      <c r="Q1" s="139"/>
+      <c r="R1" s="139"/>
+      <c r="S1" s="139"/>
+      <c r="T1" s="139"/>
+      <c r="U1" s="139"/>
+      <c r="V1" s="139"/>
+      <c r="W1" s="139"/>
+      <c r="X1" s="139"/>
     </row>
     <row r="2" spans="1:46" ht="45" customHeight="1">
       <c r="A2" s="30" t="s">
@@ -9705,10 +9903,10 @@
       <c r="X31" s="31"/>
     </row>
     <row r="32" spans="1:24">
-      <c r="A32" s="107" t="s">
+      <c r="A32" s="138" t="s">
         <v>20</v>
       </c>
-      <c r="B32" s="107"/>
+      <c r="B32" s="138"/>
       <c r="C32" s="28">
         <f>SUM(C3:C31)</f>
         <v>16843.349999999999</v>
@@ -9831,33 +10029,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:47" ht="60.75" customHeight="1">
-      <c r="A1" s="108" t="s">
+      <c r="A1" s="139" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="108"/>
-      <c r="C1" s="108"/>
-      <c r="D1" s="108"/>
-      <c r="E1" s="108"/>
-      <c r="F1" s="108"/>
-      <c r="G1" s="108"/>
-      <c r="H1" s="108"/>
-      <c r="I1" s="108"/>
-      <c r="J1" s="108"/>
-      <c r="K1" s="108"/>
-      <c r="L1" s="108"/>
-      <c r="M1" s="108"/>
-      <c r="N1" s="108"/>
-      <c r="O1" s="108"/>
-      <c r="P1" s="108"/>
-      <c r="Q1" s="108"/>
-      <c r="R1" s="108"/>
-      <c r="S1" s="108"/>
-      <c r="T1" s="108"/>
-      <c r="U1" s="108"/>
-      <c r="V1" s="108"/>
-      <c r="W1" s="108"/>
-      <c r="X1" s="108"/>
-      <c r="Y1" s="108"/>
+      <c r="B1" s="139"/>
+      <c r="C1" s="139"/>
+      <c r="D1" s="139"/>
+      <c r="E1" s="139"/>
+      <c r="F1" s="139"/>
+      <c r="G1" s="139"/>
+      <c r="H1" s="139"/>
+      <c r="I1" s="139"/>
+      <c r="J1" s="139"/>
+      <c r="K1" s="139"/>
+      <c r="L1" s="139"/>
+      <c r="M1" s="139"/>
+      <c r="N1" s="139"/>
+      <c r="O1" s="139"/>
+      <c r="P1" s="139"/>
+      <c r="Q1" s="139"/>
+      <c r="R1" s="139"/>
+      <c r="S1" s="139"/>
+      <c r="T1" s="139"/>
+      <c r="U1" s="139"/>
+      <c r="V1" s="139"/>
+      <c r="W1" s="139"/>
+      <c r="X1" s="139"/>
+      <c r="Y1" s="139"/>
     </row>
     <row r="2" spans="1:47" ht="45" customHeight="1">
       <c r="A2" s="30" t="s">
@@ -10675,10 +10873,10 @@
       <c r="Y19" s="43"/>
     </row>
     <row r="20" spans="1:27">
-      <c r="A20" s="110" t="s">
+      <c r="A20" s="141" t="s">
         <v>35</v>
       </c>
-      <c r="B20" s="111"/>
+      <c r="B20" s="142"/>
       <c r="C20" s="45">
         <f>SUM(C3:C19)</f>
         <v>12278.83</v>
@@ -11398,10 +11596,10 @@
       <c r="Y35" s="43"/>
     </row>
     <row r="36" spans="1:25">
-      <c r="A36" s="110" t="s">
+      <c r="A36" s="141" t="s">
         <v>36</v>
       </c>
-      <c r="B36" s="111"/>
+      <c r="B36" s="142"/>
       <c r="C36" s="45">
         <f>SUM(C21:C35)</f>
         <v>11057.89</v>
@@ -11496,10 +11694,10 @@
       </c>
     </row>
     <row r="37" spans="1:25" ht="31.5" customHeight="1">
-      <c r="A37" s="109" t="s">
+      <c r="A37" s="140" t="s">
         <v>37</v>
       </c>
-      <c r="B37" s="109"/>
+      <c r="B37" s="140"/>
       <c r="C37" s="48">
         <f>SUM(C20,C36)</f>
         <v>23336.720000000001</v>
@@ -11629,33 +11827,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:47" ht="60.75" customHeight="1">
-      <c r="A1" s="112" t="s">
+      <c r="A1" s="143" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="112"/>
-      <c r="C1" s="112"/>
-      <c r="D1" s="112"/>
-      <c r="E1" s="112"/>
-      <c r="F1" s="112"/>
-      <c r="G1" s="112"/>
-      <c r="H1" s="112"/>
-      <c r="I1" s="112"/>
-      <c r="J1" s="112"/>
-      <c r="K1" s="112"/>
-      <c r="L1" s="112"/>
-      <c r="M1" s="112"/>
-      <c r="N1" s="112"/>
-      <c r="O1" s="112"/>
-      <c r="P1" s="112"/>
-      <c r="Q1" s="112"/>
-      <c r="R1" s="112"/>
-      <c r="S1" s="112"/>
-      <c r="T1" s="112"/>
-      <c r="U1" s="112"/>
-      <c r="V1" s="112"/>
-      <c r="W1" s="112"/>
-      <c r="X1" s="112"/>
-      <c r="Y1" s="112"/>
+      <c r="B1" s="143"/>
+      <c r="C1" s="143"/>
+      <c r="D1" s="143"/>
+      <c r="E1" s="143"/>
+      <c r="F1" s="143"/>
+      <c r="G1" s="143"/>
+      <c r="H1" s="143"/>
+      <c r="I1" s="143"/>
+      <c r="J1" s="143"/>
+      <c r="K1" s="143"/>
+      <c r="L1" s="143"/>
+      <c r="M1" s="143"/>
+      <c r="N1" s="143"/>
+      <c r="O1" s="143"/>
+      <c r="P1" s="143"/>
+      <c r="Q1" s="143"/>
+      <c r="R1" s="143"/>
+      <c r="S1" s="143"/>
+      <c r="T1" s="143"/>
+      <c r="U1" s="143"/>
+      <c r="V1" s="143"/>
+      <c r="W1" s="143"/>
+      <c r="X1" s="143"/>
+      <c r="Y1" s="143"/>
     </row>
     <row r="2" spans="1:47" ht="45" customHeight="1">
       <c r="A2" s="59" t="s">
@@ -12365,10 +12563,10 @@
       <c r="Y17" s="65"/>
     </row>
     <row r="18" spans="1:27">
-      <c r="A18" s="113" t="s">
+      <c r="A18" s="144" t="s">
         <v>35</v>
       </c>
-      <c r="B18" s="113"/>
+      <c r="B18" s="144"/>
       <c r="C18" s="73">
         <f t="shared" ref="C18:X18" si="1">SUM(C3:C17)</f>
         <v>8428.35</v>
@@ -13121,10 +13319,10 @@
       <c r="Y34" s="69"/>
     </row>
     <row r="35" spans="1:25">
-      <c r="A35" s="113" t="s">
+      <c r="A35" s="144" t="s">
         <v>36</v>
       </c>
-      <c r="B35" s="113"/>
+      <c r="B35" s="144"/>
       <c r="C35" s="73">
         <f>SUM(C19:C34)</f>
         <v>10739.46</v>
@@ -13219,10 +13417,10 @@
       </c>
     </row>
     <row r="36" spans="1:25" ht="31.5" customHeight="1">
-      <c r="A36" s="114" t="s">
+      <c r="A36" s="145" t="s">
         <v>37</v>
       </c>
-      <c r="B36" s="114"/>
+      <c r="B36" s="145"/>
       <c r="C36" s="70">
         <f>SUM(C18,C35)</f>
         <v>19167.809999999998</v>
@@ -13360,33 +13558,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:47" ht="60.75" customHeight="1">
-      <c r="A1" s="115" t="s">
+      <c r="A1" s="146" t="s">
         <v>58</v>
       </c>
-      <c r="B1" s="115"/>
-      <c r="C1" s="115"/>
-      <c r="D1" s="115"/>
-      <c r="E1" s="115"/>
-      <c r="F1" s="115"/>
-      <c r="G1" s="115"/>
-      <c r="H1" s="115"/>
-      <c r="I1" s="115"/>
-      <c r="J1" s="115"/>
-      <c r="K1" s="115"/>
-      <c r="L1" s="115"/>
-      <c r="M1" s="115"/>
-      <c r="N1" s="115"/>
-      <c r="O1" s="115"/>
-      <c r="P1" s="115"/>
-      <c r="Q1" s="115"/>
-      <c r="R1" s="115"/>
-      <c r="S1" s="115"/>
-      <c r="T1" s="115"/>
-      <c r="U1" s="115"/>
-      <c r="V1" s="115"/>
-      <c r="W1" s="115"/>
-      <c r="X1" s="115"/>
-      <c r="Y1" s="115"/>
+      <c r="B1" s="146"/>
+      <c r="C1" s="146"/>
+      <c r="D1" s="146"/>
+      <c r="E1" s="146"/>
+      <c r="F1" s="146"/>
+      <c r="G1" s="146"/>
+      <c r="H1" s="146"/>
+      <c r="I1" s="146"/>
+      <c r="J1" s="146"/>
+      <c r="K1" s="146"/>
+      <c r="L1" s="146"/>
+      <c r="M1" s="146"/>
+      <c r="N1" s="146"/>
+      <c r="O1" s="146"/>
+      <c r="P1" s="146"/>
+      <c r="Q1" s="146"/>
+      <c r="R1" s="146"/>
+      <c r="S1" s="146"/>
+      <c r="T1" s="146"/>
+      <c r="U1" s="146"/>
+      <c r="V1" s="146"/>
+      <c r="W1" s="146"/>
+      <c r="X1" s="146"/>
+      <c r="Y1" s="146"/>
     </row>
     <row r="2" spans="1:47" ht="45" customHeight="1">
       <c r="A2" s="76" t="s">
@@ -14125,10 +14323,10 @@
       <c r="Y17" s="65"/>
     </row>
     <row r="18" spans="1:27">
-      <c r="A18" s="116" t="s">
+      <c r="A18" s="147" t="s">
         <v>35</v>
       </c>
-      <c r="B18" s="116"/>
+      <c r="B18" s="147"/>
       <c r="C18" s="79">
         <f t="shared" ref="C18:X18" si="1">SUM(C3:C17)</f>
         <v>7904</v>
@@ -14776,10 +14974,10 @@
       <c r="Y34" s="69"/>
     </row>
     <row r="35" spans="1:25">
-      <c r="A35" s="116" t="s">
+      <c r="A35" s="147" t="s">
         <v>36</v>
       </c>
-      <c r="B35" s="116"/>
+      <c r="B35" s="147"/>
       <c r="C35" s="79">
         <f>SUM(C19:C34)</f>
         <v>0</v>
@@ -14874,10 +15072,10 @@
       </c>
     </row>
     <row r="36" spans="1:25" ht="31.5" customHeight="1">
-      <c r="A36" s="117" t="s">
+      <c r="A36" s="148" t="s">
         <v>37</v>
       </c>
-      <c r="B36" s="117"/>
+      <c r="B36" s="148"/>
       <c r="C36" s="74">
         <f>SUM(C18,C35)</f>
         <v>7904</v>
@@ -15017,34 +15215,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:48" ht="60.75" customHeight="1">
-      <c r="A1" s="118" t="s">
+      <c r="A1" s="151" t="s">
         <v>59</v>
       </c>
-      <c r="B1" s="118"/>
-      <c r="C1" s="118"/>
-      <c r="D1" s="118"/>
-      <c r="E1" s="118"/>
-      <c r="F1" s="118"/>
-      <c r="G1" s="118"/>
-      <c r="H1" s="118"/>
-      <c r="I1" s="118"/>
-      <c r="J1" s="118"/>
-      <c r="K1" s="118"/>
-      <c r="L1" s="118"/>
-      <c r="M1" s="118"/>
-      <c r="N1" s="118"/>
-      <c r="O1" s="118"/>
-      <c r="P1" s="118"/>
-      <c r="Q1" s="118"/>
-      <c r="R1" s="118"/>
-      <c r="S1" s="118"/>
-      <c r="T1" s="118"/>
-      <c r="U1" s="118"/>
-      <c r="V1" s="118"/>
-      <c r="W1" s="118"/>
-      <c r="X1" s="118"/>
-      <c r="Y1" s="118"/>
-      <c r="Z1" s="118"/>
+      <c r="B1" s="151"/>
+      <c r="C1" s="151"/>
+      <c r="D1" s="151"/>
+      <c r="E1" s="151"/>
+      <c r="F1" s="151"/>
+      <c r="G1" s="151"/>
+      <c r="H1" s="151"/>
+      <c r="I1" s="151"/>
+      <c r="J1" s="151"/>
+      <c r="K1" s="151"/>
+      <c r="L1" s="151"/>
+      <c r="M1" s="151"/>
+      <c r="N1" s="151"/>
+      <c r="O1" s="151"/>
+      <c r="P1" s="151"/>
+      <c r="Q1" s="151"/>
+      <c r="R1" s="151"/>
+      <c r="S1" s="151"/>
+      <c r="T1" s="151"/>
+      <c r="U1" s="151"/>
+      <c r="V1" s="151"/>
+      <c r="W1" s="151"/>
+      <c r="X1" s="151"/>
+      <c r="Y1" s="151"/>
+      <c r="Z1" s="151"/>
     </row>
     <row r="2" spans="1:48" ht="45" customHeight="1">
       <c r="A2" s="76" t="s">
@@ -15197,7 +15395,7 @@
         <f>(94085+57723.67)</f>
         <v>151808.66999999998</v>
       </c>
-      <c r="Z3" s="120"/>
+      <c r="Z3" s="153"/>
     </row>
     <row r="4" spans="1:48" ht="15.75">
       <c r="A4" s="66">
@@ -15247,7 +15445,7 @@
       </c>
       <c r="X4" s="90"/>
       <c r="Y4" s="93"/>
-      <c r="Z4" s="120"/>
+      <c r="Z4" s="153"/>
     </row>
     <row r="5" spans="1:48" ht="15.75">
       <c r="A5" s="62">
@@ -15287,7 +15485,7 @@
       </c>
       <c r="X5" s="90"/>
       <c r="Y5" s="93"/>
-      <c r="Z5" s="120"/>
+      <c r="Z5" s="153"/>
     </row>
     <row r="6" spans="1:48" ht="15.75">
       <c r="A6" s="66">
@@ -15328,7 +15526,7 @@
       </c>
       <c r="X6" s="90"/>
       <c r="Y6" s="93"/>
-      <c r="Z6" s="120"/>
+      <c r="Z6" s="153"/>
     </row>
     <row r="7" spans="1:48" ht="15" customHeight="1">
       <c r="A7" s="62">
@@ -15372,7 +15570,7 @@
       </c>
       <c r="X7" s="90"/>
       <c r="Y7" s="93"/>
-      <c r="Z7" s="120"/>
+      <c r="Z7" s="153"/>
     </row>
     <row r="8" spans="1:48" ht="15.75">
       <c r="A8" s="66">
@@ -15414,14 +15612,14 @@
       </c>
       <c r="X8" s="90"/>
       <c r="Y8" s="93"/>
-      <c r="Z8" s="120"/>
-      <c r="AC8" s="122" t="s">
+      <c r="Z8" s="153"/>
+      <c r="AC8" s="150" t="s">
         <v>61</v>
       </c>
-      <c r="AD8" s="122"/>
-      <c r="AE8" s="122"/>
-      <c r="AF8" s="122"/>
-      <c r="AG8" s="122"/>
+      <c r="AD8" s="150"/>
+      <c r="AE8" s="150"/>
+      <c r="AF8" s="150"/>
+      <c r="AG8" s="150"/>
     </row>
     <row r="9" spans="1:48" ht="15.75">
       <c r="A9" s="62">
@@ -15460,12 +15658,12 @@
       </c>
       <c r="X9" s="90"/>
       <c r="Y9" s="93"/>
-      <c r="Z9" s="120"/>
-      <c r="AC9" s="122"/>
-      <c r="AD9" s="122"/>
-      <c r="AE9" s="122"/>
-      <c r="AF9" s="122"/>
-      <c r="AG9" s="122"/>
+      <c r="Z9" s="153"/>
+      <c r="AC9" s="150"/>
+      <c r="AD9" s="150"/>
+      <c r="AE9" s="150"/>
+      <c r="AF9" s="150"/>
+      <c r="AG9" s="150"/>
     </row>
     <row r="10" spans="1:48" ht="15.75">
       <c r="A10" s="66">
@@ -15509,12 +15707,12 @@
       </c>
       <c r="X10" s="90"/>
       <c r="Y10" s="93"/>
-      <c r="Z10" s="120"/>
-      <c r="AC10" s="122"/>
-      <c r="AD10" s="122"/>
-      <c r="AE10" s="122"/>
-      <c r="AF10" s="122"/>
-      <c r="AG10" s="122"/>
+      <c r="Z10" s="153"/>
+      <c r="AC10" s="150"/>
+      <c r="AD10" s="150"/>
+      <c r="AE10" s="150"/>
+      <c r="AF10" s="150"/>
+      <c r="AG10" s="150"/>
     </row>
     <row r="11" spans="1:48" ht="15.75">
       <c r="A11" s="62">
@@ -15554,13 +15752,13 @@
       </c>
       <c r="X11" s="90"/>
       <c r="Y11" s="93"/>
-      <c r="Z11" s="120"/>
-      <c r="AC11" s="121" t="s">
+      <c r="Z11" s="153"/>
+      <c r="AC11" s="149" t="s">
         <v>62</v>
       </c>
-      <c r="AD11" s="121"/>
-      <c r="AE11" s="121"/>
-      <c r="AF11" s="121"/>
+      <c r="AD11" s="149"/>
+      <c r="AE11" s="149"/>
+      <c r="AF11" s="149"/>
       <c r="AG11" s="104">
         <f>Y3+Y14+Y21</f>
         <v>226341.31</v>
@@ -15601,13 +15799,13 @@
       </c>
       <c r="X12" s="90"/>
       <c r="Y12" s="93"/>
-      <c r="Z12" s="120"/>
-      <c r="AC12" s="121" t="s">
+      <c r="Z12" s="153"/>
+      <c r="AC12" s="149" t="s">
         <v>55</v>
       </c>
-      <c r="AD12" s="121"/>
-      <c r="AE12" s="121"/>
-      <c r="AF12" s="121"/>
+      <c r="AD12" s="149"/>
+      <c r="AE12" s="149"/>
+      <c r="AF12" s="149"/>
       <c r="AG12" s="104">
         <f>Y27</f>
         <v>20000</v>
@@ -15652,13 +15850,13 @@
       </c>
       <c r="X13" s="90"/>
       <c r="Y13" s="93"/>
-      <c r="Z13" s="120"/>
-      <c r="AC13" s="121" t="s">
+      <c r="Z13" s="153"/>
+      <c r="AC13" s="149" t="s">
         <v>63</v>
       </c>
-      <c r="AD13" s="121"/>
-      <c r="AE13" s="121"/>
-      <c r="AF13" s="121"/>
+      <c r="AD13" s="149"/>
+      <c r="AE13" s="149"/>
+      <c r="AF13" s="149"/>
       <c r="AG13" s="104">
         <f>Y17+Y19</f>
         <v>25000</v>
@@ -15704,16 +15902,16 @@
       <c r="Y14" s="99">
         <v>37634</v>
       </c>
-      <c r="Z14" s="120"/>
-      <c r="AC14" s="121" t="s">
+      <c r="Z14" s="153"/>
+      <c r="AC14" s="149" t="s">
         <v>64</v>
       </c>
-      <c r="AD14" s="121"/>
-      <c r="AE14" s="121"/>
-      <c r="AF14" s="121"/>
+      <c r="AD14" s="149"/>
+      <c r="AE14" s="149"/>
+      <c r="AF14" s="149"/>
       <c r="AG14" s="104">
         <f>W38</f>
-        <v>167654.87</v>
+        <v>177971.36</v>
       </c>
     </row>
     <row r="15" spans="1:48" ht="15.75">
@@ -15760,16 +15958,16 @@
       </c>
       <c r="X15" s="90"/>
       <c r="Y15" s="93"/>
-      <c r="Z15" s="120"/>
-      <c r="AC15" s="121" t="s">
+      <c r="Z15" s="153"/>
+      <c r="AC15" s="149" t="s">
         <v>65</v>
       </c>
-      <c r="AD15" s="121"/>
-      <c r="AE15" s="121"/>
-      <c r="AF15" s="121"/>
+      <c r="AD15" s="149"/>
+      <c r="AE15" s="149"/>
+      <c r="AF15" s="149"/>
       <c r="AG15" s="104">
         <f>SUM(C38:H38)</f>
-        <v>47166.55</v>
+        <v>55416.04</v>
       </c>
     </row>
     <row r="16" spans="1:48" ht="15.75">
@@ -15815,7 +16013,7 @@
       </c>
       <c r="X16" s="90"/>
       <c r="Y16" s="93"/>
-      <c r="Z16" s="120"/>
+      <c r="Z16" s="153"/>
     </row>
     <row r="17" spans="1:28" ht="15.75">
       <c r="A17" s="62">
@@ -15867,7 +16065,7 @@
       <c r="Y17" s="100">
         <v>15000</v>
       </c>
-      <c r="Z17" s="120"/>
+      <c r="Z17" s="153"/>
     </row>
     <row r="18" spans="1:28" ht="15.75">
       <c r="A18" s="66">
@@ -15908,7 +16106,7 @@
       </c>
       <c r="X18" s="90"/>
       <c r="Y18" s="93"/>
-      <c r="Z18" s="120"/>
+      <c r="Z18" s="153"/>
     </row>
     <row r="19" spans="1:28" ht="15.75">
       <c r="A19" s="62">
@@ -15952,13 +16150,13 @@
       <c r="Y19" s="100">
         <v>10000</v>
       </c>
-      <c r="Z19" s="120"/>
+      <c r="Z19" s="153"/>
     </row>
     <row r="20" spans="1:28" ht="14.25" customHeight="1">
-      <c r="A20" s="116" t="s">
+      <c r="A20" s="147" t="s">
         <v>35</v>
       </c>
-      <c r="B20" s="116"/>
+      <c r="B20" s="147"/>
       <c r="C20" s="79">
         <f t="shared" ref="C20:V20" si="1">SUM(C3:C17)</f>
         <v>10942.99</v>
@@ -16101,7 +16299,7 @@
       <c r="Y21" s="99">
         <v>36898.639999999999</v>
       </c>
-      <c r="Z21" s="120"/>
+      <c r="Z21" s="153"/>
     </row>
     <row r="22" spans="1:28" ht="15.75">
       <c r="A22" s="66">
@@ -16147,7 +16345,7 @@
         <v>23662.84</v>
       </c>
       <c r="Y22" s="93"/>
-      <c r="Z22" s="120"/>
+      <c r="Z22" s="153"/>
       <c r="AB22" s="44"/>
     </row>
     <row r="23" spans="1:28" ht="15.75">
@@ -16191,7 +16389,7 @@
       </c>
       <c r="X23" s="90"/>
       <c r="Y23" s="93"/>
-      <c r="Z23" s="120"/>
+      <c r="Z23" s="153"/>
     </row>
     <row r="24" spans="1:28" ht="15.75">
       <c r="A24" s="66">
@@ -16235,7 +16433,7 @@
       </c>
       <c r="X24" s="90"/>
       <c r="Y24" s="93"/>
-      <c r="Z24" s="120"/>
+      <c r="Z24" s="153"/>
     </row>
     <row r="25" spans="1:28" ht="15.75">
       <c r="A25" s="62">
@@ -16279,7 +16477,7 @@
       </c>
       <c r="X25" s="90"/>
       <c r="Y25" s="93"/>
-      <c r="Z25" s="120"/>
+      <c r="Z25" s="153"/>
     </row>
     <row r="26" spans="1:28" ht="15.75">
       <c r="A26" s="66">
@@ -16318,7 +16516,7 @@
       </c>
       <c r="X26" s="90"/>
       <c r="Y26" s="93"/>
-      <c r="Z26" s="120"/>
+      <c r="Z26" s="153"/>
     </row>
     <row r="27" spans="1:28" ht="15.75">
       <c r="A27" s="62">
@@ -16363,7 +16561,7 @@
       <c r="Y27" s="103">
         <v>20000</v>
       </c>
-      <c r="Z27" s="120"/>
+      <c r="Z27" s="153"/>
     </row>
     <row r="28" spans="1:28" ht="15.75">
       <c r="A28" s="66">
@@ -16405,7 +16603,7 @@
       </c>
       <c r="X28" s="90"/>
       <c r="Y28" s="93"/>
-      <c r="Z28" s="120"/>
+      <c r="Z28" s="153"/>
     </row>
     <row r="29" spans="1:28" ht="15.75">
       <c r="A29" s="62">
@@ -16444,7 +16642,7 @@
       </c>
       <c r="X29" s="90"/>
       <c r="Y29" s="93"/>
-      <c r="Z29" s="120"/>
+      <c r="Z29" s="153"/>
     </row>
     <row r="30" spans="1:28" ht="15.75">
       <c r="A30" s="66">
@@ -16456,7 +16654,9 @@
       <c r="C30" s="72"/>
       <c r="D30" s="72"/>
       <c r="E30" s="72"/>
-      <c r="F30" s="72"/>
+      <c r="F30" s="72">
+        <v>1080</v>
+      </c>
       <c r="G30" s="72"/>
       <c r="H30" s="72"/>
       <c r="I30" s="72"/>
@@ -16468,7 +16668,8 @@
       <c r="O30" s="72"/>
       <c r="P30" s="72"/>
       <c r="Q30" s="72">
-        <v>400</v>
+        <f>400+300</f>
+        <v>700</v>
       </c>
       <c r="R30" s="72"/>
       <c r="S30" s="72"/>
@@ -16477,11 +16678,11 @@
       <c r="V30" s="83"/>
       <c r="W30" s="89">
         <f t="shared" si="2"/>
-        <v>400</v>
+        <v>1780</v>
       </c>
       <c r="X30" s="90"/>
       <c r="Y30" s="93"/>
-      <c r="Z30" s="120"/>
+      <c r="Z30" s="153"/>
     </row>
     <row r="31" spans="1:28" ht="15.75">
       <c r="A31" s="62">
@@ -16516,7 +16717,7 @@
       </c>
       <c r="X31" s="90"/>
       <c r="Y31" s="93"/>
-      <c r="Z31" s="120"/>
+      <c r="Z31" s="153"/>
     </row>
     <row r="32" spans="1:28" ht="15.75">
       <c r="A32" s="66">
@@ -16551,7 +16752,7 @@
       </c>
       <c r="X32" s="90"/>
       <c r="Y32" s="93"/>
-      <c r="Z32" s="120"/>
+      <c r="Z32" s="153"/>
     </row>
     <row r="33" spans="1:26" ht="15.75">
       <c r="A33" s="62">
@@ -16585,8 +16786,10 @@
         <v>0</v>
       </c>
       <c r="X33" s="90"/>
-      <c r="Y33" s="93"/>
-      <c r="Z33" s="120"/>
+      <c r="Y33" s="164">
+        <v>10000</v>
+      </c>
+      <c r="Z33" s="153"/>
     </row>
     <row r="34" spans="1:26" ht="15.75">
       <c r="A34" s="66">
@@ -16611,17 +16814,21 @@
       <c r="P34" s="72"/>
       <c r="Q34" s="72"/>
       <c r="R34" s="72"/>
-      <c r="S34" s="72"/>
-      <c r="T34" s="72"/>
+      <c r="S34" s="72">
+        <v>799</v>
+      </c>
+      <c r="T34" s="72">
+        <v>100</v>
+      </c>
       <c r="U34" s="72"/>
       <c r="V34" s="83"/>
       <c r="W34" s="89">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>899</v>
       </c>
       <c r="X34" s="90"/>
       <c r="Y34" s="93"/>
-      <c r="Z34" s="120"/>
+      <c r="Z34" s="153"/>
     </row>
     <row r="35" spans="1:26" ht="15.75">
       <c r="A35" s="62">
@@ -16632,8 +16839,13 @@
       </c>
       <c r="C35" s="71"/>
       <c r="D35" s="71"/>
-      <c r="E35" s="71"/>
-      <c r="F35" s="71"/>
+      <c r="E35" s="71">
+        <v>2327</v>
+      </c>
+      <c r="F35" s="71">
+        <f>1610+175.49</f>
+        <v>1785.49</v>
+      </c>
       <c r="G35" s="71"/>
       <c r="H35" s="71"/>
       <c r="I35" s="71"/>
@@ -16642,21 +16854,25 @@
       <c r="L35" s="71"/>
       <c r="M35" s="71"/>
       <c r="N35" s="71"/>
-      <c r="O35" s="71"/>
+      <c r="O35" s="71">
+        <v>270</v>
+      </c>
       <c r="P35" s="71"/>
       <c r="Q35" s="71"/>
       <c r="R35" s="71"/>
-      <c r="S35" s="71"/>
+      <c r="S35" s="71">
+        <v>399</v>
+      </c>
       <c r="T35" s="71"/>
       <c r="U35" s="71"/>
       <c r="V35" s="82"/>
       <c r="W35" s="89">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>4781.49</v>
       </c>
       <c r="X35" s="90"/>
       <c r="Y35" s="93"/>
-      <c r="Z35" s="120"/>
+      <c r="Z35" s="153"/>
     </row>
     <row r="36" spans="1:26" ht="15.75">
       <c r="A36" s="66">
@@ -16666,11 +16882,15 @@
         <v>8</v>
       </c>
       <c r="C36" s="72"/>
-      <c r="D36" s="72"/>
+      <c r="D36" s="72">
+        <v>327</v>
+      </c>
       <c r="E36" s="72"/>
       <c r="F36" s="72"/>
       <c r="G36" s="72"/>
-      <c r="H36" s="72"/>
+      <c r="H36" s="72">
+        <v>2730</v>
+      </c>
       <c r="I36" s="72"/>
       <c r="J36" s="72"/>
       <c r="K36" s="72"/>
@@ -16681,38 +16901,40 @@
       <c r="P36" s="72"/>
       <c r="Q36" s="72"/>
       <c r="R36" s="72"/>
-      <c r="S36" s="72"/>
+      <c r="S36" s="72">
+        <v>199</v>
+      </c>
       <c r="T36" s="72"/>
       <c r="U36" s="72"/>
       <c r="V36" s="83"/>
       <c r="W36" s="89">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3256</v>
       </c>
       <c r="X36" s="90"/>
       <c r="Y36" s="93"/>
-      <c r="Z36" s="120"/>
+      <c r="Z36" s="153"/>
     </row>
     <row r="37" spans="1:26">
-      <c r="A37" s="116" t="s">
+      <c r="A37" s="147" t="s">
         <v>36</v>
       </c>
-      <c r="B37" s="116"/>
+      <c r="B37" s="147"/>
       <c r="C37" s="79">
         <f>SUM(C21:C36)</f>
         <v>3393</v>
       </c>
       <c r="D37" s="79">
         <f t="shared" ref="D37:V37" si="3">SUM(D21:D36)</f>
-        <v>6141.3099999999995</v>
+        <v>6468.3099999999995</v>
       </c>
       <c r="E37" s="79">
         <f t="shared" si="3"/>
-        <v>3180</v>
+        <v>5507</v>
       </c>
       <c r="F37" s="79">
         <f t="shared" si="3"/>
-        <v>4420</v>
+        <v>7285.49</v>
       </c>
       <c r="G37" s="79">
         <f t="shared" si="3"/>
@@ -16720,7 +16942,7 @@
       </c>
       <c r="H37" s="79">
         <f t="shared" si="3"/>
-        <v>2414</v>
+        <v>5144</v>
       </c>
       <c r="I37" s="79">
         <f t="shared" si="3"/>
@@ -16748,7 +16970,7 @@
       </c>
       <c r="O37" s="79">
         <f t="shared" si="3"/>
-        <v>1953</v>
+        <v>2223</v>
       </c>
       <c r="P37" s="79">
         <f t="shared" si="3"/>
@@ -16756,7 +16978,7 @@
       </c>
       <c r="Q37" s="79">
         <f t="shared" si="3"/>
-        <v>6023</v>
+        <v>6323</v>
       </c>
       <c r="R37" s="79">
         <f t="shared" si="3"/>
@@ -16764,11 +16986,11 @@
       </c>
       <c r="S37" s="79">
         <f t="shared" si="3"/>
-        <v>1092</v>
+        <v>2489</v>
       </c>
       <c r="T37" s="79">
         <f>SUM(T21:T36)</f>
-        <v>11509</v>
+        <v>11609</v>
       </c>
       <c r="U37" s="79">
         <f t="shared" si="3"/>
@@ -16780,7 +17002,7 @@
       </c>
       <c r="W37" s="94">
         <f>SUM(W21:W36)</f>
-        <v>45722.31</v>
+        <v>56038.799999999996</v>
       </c>
       <c r="X37" s="95">
         <f>SUM(X21:X36)</f>
@@ -16788,33 +17010,33 @@
       </c>
       <c r="Y37" s="101">
         <f>SUM(Y21:Y36)</f>
-        <v>56898.64</v>
+        <v>66898.64</v>
       </c>
       <c r="Z37" s="97">
         <f>Y37-W37-X37</f>
-        <v>-12486.509999999998</v>
+        <v>-12802.999999999996</v>
       </c>
     </row>
     <row r="38" spans="1:26" ht="31.5" customHeight="1">
-      <c r="A38" s="119" t="s">
+      <c r="A38" s="152" t="s">
         <v>37</v>
       </c>
-      <c r="B38" s="119"/>
+      <c r="B38" s="152"/>
       <c r="C38" s="78">
         <f>SUM(C20,C37)</f>
         <v>14335.99</v>
       </c>
       <c r="D38" s="78">
         <f t="shared" ref="D38:W38" si="4">SUM(D20,D37)</f>
-        <v>11666.56</v>
+        <v>11993.56</v>
       </c>
       <c r="E38" s="78">
         <f t="shared" si="4"/>
-        <v>8530</v>
+        <v>10857</v>
       </c>
       <c r="F38" s="78">
         <f t="shared" si="4"/>
-        <v>6460</v>
+        <v>9325.49</v>
       </c>
       <c r="G38" s="78">
         <f t="shared" si="4"/>
@@ -16822,7 +17044,7 @@
       </c>
       <c r="H38" s="78">
         <f t="shared" si="4"/>
-        <v>6174</v>
+        <v>8904</v>
       </c>
       <c r="I38" s="78">
         <f t="shared" si="4"/>
@@ -16850,7 +17072,7 @@
       </c>
       <c r="O38" s="78">
         <f t="shared" si="4"/>
-        <v>5172</v>
+        <v>5442</v>
       </c>
       <c r="P38" s="78">
         <f t="shared" si="4"/>
@@ -16858,7 +17080,7 @@
       </c>
       <c r="Q38" s="78">
         <f t="shared" si="4"/>
-        <v>27168.98</v>
+        <v>27468.98</v>
       </c>
       <c r="R38" s="78">
         <f t="shared" si="4"/>
@@ -16866,11 +17088,11 @@
       </c>
       <c r="S38" s="78">
         <f>SUM(S20,S37)</f>
-        <v>6364.63</v>
+        <v>7761.63</v>
       </c>
       <c r="T38" s="78">
         <f t="shared" si="4"/>
-        <v>14697</v>
+        <v>14797</v>
       </c>
       <c r="U38" s="78">
         <f t="shared" si="4"/>
@@ -16882,7 +17104,7 @@
       </c>
       <c r="W38" s="94">
         <f t="shared" si="4"/>
-        <v>167654.87</v>
+        <v>177971.36</v>
       </c>
       <c r="X38" s="95">
         <f>SUM(X20,X37)</f>
@@ -16890,11 +17112,11 @@
       </c>
       <c r="Y38" s="102">
         <f>SUM(Y20,Y37)</f>
-        <v>271341.31</v>
+        <v>281341.31</v>
       </c>
       <c r="Z38" s="70">
         <f>SUM(Z20,Z37)</f>
-        <v>-6937.09</v>
+        <v>-7253.5799999999981</v>
       </c>
     </row>
     <row r="42" spans="1:26">
@@ -16911,24 +17133,24 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A1:Z1"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="Z3:Z19"/>
+    <mergeCell ref="Z21:Z36"/>
     <mergeCell ref="AC14:AF14"/>
     <mergeCell ref="AC15:AF15"/>
     <mergeCell ref="AC8:AG10"/>
     <mergeCell ref="AC11:AF11"/>
     <mergeCell ref="AC12:AF12"/>
     <mergeCell ref="AC13:AF13"/>
-    <mergeCell ref="A1:Z1"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="Z3:Z19"/>
-    <mergeCell ref="Z21:Z36"/>
   </mergeCells>
   <conditionalFormatting sqref="Z20:Z21 Z37:Z38">
-    <cfRule type="expression" dxfId="3" priority="1">
+    <cfRule type="expression" dxfId="1" priority="1">
       <formula>Z20&lt;0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="2">
+    <cfRule type="expression" dxfId="0" priority="2">
       <formula>Z20&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16949,168 +17171,168 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:52" ht="34.5" customHeight="1">
-      <c r="A1" s="123" t="s">
+      <c r="A1" s="155" t="s">
         <v>66</v>
       </c>
-      <c r="B1" s="123"/>
-      <c r="C1" s="123"/>
-      <c r="D1" s="123"/>
-      <c r="E1" s="123"/>
-      <c r="F1" s="123"/>
-      <c r="G1" s="123"/>
-      <c r="H1" s="123"/>
-      <c r="I1" s="123"/>
-      <c r="J1" s="123"/>
-      <c r="K1" s="123"/>
-      <c r="L1" s="123"/>
-      <c r="M1" s="123"/>
-      <c r="N1" s="123"/>
-      <c r="O1" s="123"/>
-      <c r="P1" s="123"/>
-      <c r="Q1" s="123"/>
-      <c r="R1" s="123"/>
-      <c r="S1" s="123"/>
-      <c r="T1" s="123"/>
-      <c r="U1" s="123"/>
-      <c r="V1" s="123"/>
-      <c r="W1" s="123"/>
-      <c r="X1" s="123"/>
-      <c r="Y1" s="123"/>
-      <c r="Z1" s="123"/>
-      <c r="AA1" s="123"/>
-      <c r="AB1" s="123"/>
-      <c r="AC1" s="123"/>
-      <c r="AD1" s="123"/>
+      <c r="B1" s="155"/>
+      <c r="C1" s="155"/>
+      <c r="D1" s="155"/>
+      <c r="E1" s="155"/>
+      <c r="F1" s="155"/>
+      <c r="G1" s="155"/>
+      <c r="H1" s="155"/>
+      <c r="I1" s="155"/>
+      <c r="J1" s="155"/>
+      <c r="K1" s="155"/>
+      <c r="L1" s="155"/>
+      <c r="M1" s="155"/>
+      <c r="N1" s="155"/>
+      <c r="O1" s="155"/>
+      <c r="P1" s="155"/>
+      <c r="Q1" s="155"/>
+      <c r="R1" s="155"/>
+      <c r="S1" s="155"/>
+      <c r="T1" s="155"/>
+      <c r="U1" s="155"/>
+      <c r="V1" s="155"/>
+      <c r="W1" s="155"/>
+      <c r="X1" s="155"/>
+      <c r="Y1" s="155"/>
+      <c r="Z1" s="155"/>
+      <c r="AA1" s="155"/>
+      <c r="AB1" s="155"/>
+      <c r="AC1" s="155"/>
+      <c r="AD1" s="155"/>
     </row>
     <row r="2" spans="1:52" ht="26.25">
-      <c r="A2" s="148"/>
-      <c r="B2" s="149"/>
-      <c r="C2" s="124" t="s">
+      <c r="A2" s="162"/>
+      <c r="B2" s="163"/>
+      <c r="C2" s="158" t="s">
         <v>67</v>
       </c>
-      <c r="D2" s="124"/>
-      <c r="E2" s="124"/>
-      <c r="F2" s="124"/>
-      <c r="G2" s="124"/>
-      <c r="H2" s="124"/>
-      <c r="I2" s="124"/>
-      <c r="J2" s="124"/>
-      <c r="K2" s="124"/>
-      <c r="L2" s="145" t="s">
+      <c r="D2" s="158"/>
+      <c r="E2" s="158"/>
+      <c r="F2" s="158"/>
+      <c r="G2" s="158"/>
+      <c r="H2" s="158"/>
+      <c r="I2" s="158"/>
+      <c r="J2" s="158"/>
+      <c r="K2" s="158"/>
+      <c r="L2" s="159" t="s">
         <v>75</v>
       </c>
-      <c r="M2" s="145"/>
-      <c r="N2" s="145"/>
-      <c r="O2" s="145"/>
-      <c r="P2" s="145"/>
-      <c r="Q2" s="145"/>
-      <c r="R2" s="146" t="s">
+      <c r="M2" s="159"/>
+      <c r="N2" s="159"/>
+      <c r="O2" s="159"/>
+      <c r="P2" s="159"/>
+      <c r="Q2" s="159"/>
+      <c r="R2" s="160" t="s">
         <v>78</v>
       </c>
-      <c r="S2" s="146"/>
-      <c r="T2" s="146"/>
-      <c r="U2" s="146"/>
-      <c r="V2" s="146"/>
-      <c r="W2" s="146"/>
-      <c r="X2" s="146"/>
-      <c r="Y2" s="146"/>
-      <c r="Z2" s="146"/>
-      <c r="AA2" s="146"/>
-      <c r="AB2" s="147" t="s">
+      <c r="S2" s="160"/>
+      <c r="T2" s="160"/>
+      <c r="U2" s="160"/>
+      <c r="V2" s="160"/>
+      <c r="W2" s="160"/>
+      <c r="X2" s="160"/>
+      <c r="Y2" s="160"/>
+      <c r="Z2" s="160"/>
+      <c r="AA2" s="160"/>
+      <c r="AB2" s="161" t="s">
         <v>81</v>
       </c>
-      <c r="AC2" s="147"/>
-      <c r="AD2" s="147"/>
+      <c r="AC2" s="161"/>
+      <c r="AD2" s="161"/>
     </row>
     <row r="3" spans="1:52" ht="45" customHeight="1">
-      <c r="A3" s="141" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="141" t="s">
+      <c r="A3" s="119" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="119" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="142" t="s">
+      <c r="C3" s="120" t="s">
         <v>68</v>
       </c>
-      <c r="D3" s="142" t="s">
+      <c r="D3" s="120" t="s">
         <v>69</v>
       </c>
-      <c r="E3" s="142" t="s">
+      <c r="E3" s="120" t="s">
         <v>70</v>
       </c>
-      <c r="F3" s="142" t="s">
+      <c r="F3" s="120" t="s">
         <v>29</v>
       </c>
-      <c r="G3" s="142" t="s">
+      <c r="G3" s="120" t="s">
         <v>82</v>
       </c>
-      <c r="H3" s="142" t="s">
+      <c r="H3" s="120" t="s">
         <v>71</v>
       </c>
-      <c r="I3" s="142" t="s">
+      <c r="I3" s="120" t="s">
         <v>72</v>
       </c>
-      <c r="J3" s="142" t="s">
+      <c r="J3" s="120" t="s">
         <v>73</v>
       </c>
-      <c r="K3" s="142" t="s">
+      <c r="K3" s="120" t="s">
         <v>74</v>
       </c>
-      <c r="L3" s="143" t="s">
+      <c r="L3" s="121" t="s">
         <v>24</v>
       </c>
-      <c r="M3" s="143" t="s">
+      <c r="M3" s="121" t="s">
         <v>14</v>
       </c>
-      <c r="N3" s="143" t="s">
+      <c r="N3" s="121" t="s">
         <v>76</v>
       </c>
-      <c r="O3" s="143" t="s">
+      <c r="O3" s="121" t="s">
         <v>25</v>
       </c>
-      <c r="P3" s="143" t="s">
+      <c r="P3" s="121" t="s">
         <v>25</v>
       </c>
-      <c r="Q3" s="143" t="s">
+      <c r="Q3" s="121" t="s">
         <v>77</v>
       </c>
-      <c r="R3" s="144" t="s">
+      <c r="R3" s="122" t="s">
         <v>30</v>
       </c>
-      <c r="S3" s="144" t="s">
+      <c r="S3" s="122" t="s">
         <v>23</v>
       </c>
-      <c r="T3" s="144" t="s">
+      <c r="T3" s="122" t="s">
         <v>13</v>
       </c>
-      <c r="U3" s="144" t="s">
+      <c r="U3" s="122" t="s">
         <v>15</v>
       </c>
-      <c r="V3" s="144" t="s">
+      <c r="V3" s="122" t="s">
         <v>16</v>
       </c>
-      <c r="W3" s="144" t="s">
+      <c r="W3" s="122" t="s">
         <v>28</v>
       </c>
-      <c r="X3" s="144" t="s">
+      <c r="X3" s="122" t="s">
         <v>79</v>
       </c>
-      <c r="Y3" s="144" t="s">
+      <c r="Y3" s="122" t="s">
         <v>79</v>
       </c>
-      <c r="Z3" s="144" t="s">
+      <c r="Z3" s="122" t="s">
         <v>80</v>
       </c>
-      <c r="AA3" s="150" t="s">
+      <c r="AA3" s="123" t="s">
         <v>26</v>
       </c>
-      <c r="AB3" s="153" t="s">
+      <c r="AB3" s="126" t="s">
         <v>22</v>
       </c>
-      <c r="AC3" s="154" t="s">
+      <c r="AC3" s="127" t="s">
         <v>19</v>
       </c>
-      <c r="AD3" s="163" t="s">
+      <c r="AD3" s="135" t="s">
         <v>21</v>
       </c>
       <c r="AE3" s="1"/>
@@ -17137,1603 +17359,1610 @@
       <c r="AZ3" s="1"/>
     </row>
     <row r="4" spans="1:52" ht="15.75">
-      <c r="A4" s="129">
+      <c r="A4" s="109">
         <v>5</v>
       </c>
-      <c r="B4" s="130" t="s">
+      <c r="B4" s="110" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="131">
+      <c r="C4" s="111">
         <v>429.95</v>
       </c>
-      <c r="D4" s="131"/>
-      <c r="E4" s="131"/>
-      <c r="F4" s="131"/>
-      <c r="G4" s="131"/>
-      <c r="H4" s="131"/>
-      <c r="I4" s="131">
+      <c r="D4" s="111"/>
+      <c r="E4" s="111"/>
+      <c r="F4" s="111"/>
+      <c r="G4" s="111"/>
+      <c r="H4" s="111"/>
+      <c r="I4" s="111">
         <f>4660+545</f>
         <v>5205</v>
       </c>
-      <c r="J4" s="131"/>
-      <c r="K4" s="131"/>
-      <c r="L4" s="131"/>
-      <c r="M4" s="131"/>
-      <c r="N4" s="131"/>
-      <c r="O4" s="131">
+      <c r="J4" s="111"/>
+      <c r="K4" s="111"/>
+      <c r="L4" s="111"/>
+      <c r="M4" s="111"/>
+      <c r="N4" s="111"/>
+      <c r="O4" s="111">
         <v>100</v>
       </c>
-      <c r="P4" s="131">
+      <c r="P4" s="111">
         <v>10000</v>
       </c>
-      <c r="Q4" s="131"/>
-      <c r="R4" s="131"/>
-      <c r="S4" s="131"/>
-      <c r="T4" s="131"/>
-      <c r="U4" s="131"/>
-      <c r="V4" s="131"/>
-      <c r="W4" s="131"/>
-      <c r="X4" s="131">
+      <c r="Q4" s="111"/>
+      <c r="R4" s="111"/>
+      <c r="S4" s="111"/>
+      <c r="T4" s="111"/>
+      <c r="U4" s="111"/>
+      <c r="V4" s="111"/>
+      <c r="W4" s="111"/>
+      <c r="X4" s="111">
         <v>1237</v>
       </c>
-      <c r="Y4" s="131"/>
-      <c r="Z4" s="131"/>
-      <c r="AA4" s="132"/>
-      <c r="AB4" s="155">
+      <c r="Y4" s="111"/>
+      <c r="Z4" s="111"/>
+      <c r="AA4" s="112"/>
+      <c r="AB4" s="128">
         <f>SUM(C4:AA4)</f>
         <v>16971.95</v>
       </c>
-      <c r="AC4" s="140">
+      <c r="AC4" s="118">
         <f>37635+40252.26+18817.85</f>
         <v>96705.110000000015</v>
       </c>
       <c r="AD4" s="156"/>
     </row>
     <row r="5" spans="1:52" ht="15.75">
-      <c r="A5" s="125">
+      <c r="A5" s="105">
         <v>6</v>
       </c>
-      <c r="B5" s="126" t="s">
+      <c r="B5" s="106" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="127"/>
-      <c r="D5" s="127"/>
-      <c r="E5" s="127"/>
-      <c r="F5" s="127">
+      <c r="C5" s="107"/>
+      <c r="D5" s="107"/>
+      <c r="E5" s="107"/>
+      <c r="F5" s="107">
         <v>351</v>
       </c>
-      <c r="G5" s="127"/>
-      <c r="H5" s="127"/>
-      <c r="I5" s="127"/>
-      <c r="J5" s="127"/>
-      <c r="K5" s="127"/>
-      <c r="L5" s="127">
+      <c r="G5" s="107"/>
+      <c r="H5" s="107"/>
+      <c r="I5" s="107"/>
+      <c r="J5" s="107"/>
+      <c r="K5" s="107"/>
+      <c r="L5" s="107">
         <f>5748.49+2803.26+2306.38</f>
         <v>10858.130000000001</v>
       </c>
-      <c r="M5" s="127"/>
-      <c r="N5" s="127"/>
-      <c r="O5" s="127"/>
-      <c r="P5" s="127"/>
-      <c r="Q5" s="127">
+      <c r="M5" s="107"/>
+      <c r="N5" s="107"/>
+      <c r="O5" s="107"/>
+      <c r="P5" s="107"/>
+      <c r="Q5" s="107">
         <v>3500</v>
       </c>
-      <c r="R5" s="127"/>
-      <c r="S5" s="127"/>
-      <c r="T5" s="127"/>
-      <c r="U5" s="127">
+      <c r="R5" s="107"/>
+      <c r="S5" s="107"/>
+      <c r="T5" s="107"/>
+      <c r="U5" s="107">
         <v>294</v>
       </c>
-      <c r="V5" s="127"/>
-      <c r="W5" s="127">
+      <c r="V5" s="107"/>
+      <c r="W5" s="107">
         <v>1500</v>
       </c>
-      <c r="X5" s="127"/>
-      <c r="Y5" s="127"/>
-      <c r="Z5" s="127"/>
-      <c r="AA5" s="128"/>
-      <c r="AB5" s="155">
+      <c r="X5" s="107"/>
+      <c r="Y5" s="107"/>
+      <c r="Z5" s="107"/>
+      <c r="AA5" s="108"/>
+      <c r="AB5" s="128">
         <f>SUM(C5:AA5)</f>
         <v>16503.13</v>
       </c>
-      <c r="AC5" s="139"/>
+      <c r="AC5" s="117"/>
       <c r="AD5" s="156"/>
     </row>
     <row r="6" spans="1:52" ht="15.75">
-      <c r="A6" s="129">
+      <c r="A6" s="109">
         <v>7</v>
       </c>
-      <c r="B6" s="130" t="s">
+      <c r="B6" s="110" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="131"/>
-      <c r="D6" s="131"/>
-      <c r="E6" s="131"/>
-      <c r="F6" s="131"/>
-      <c r="G6" s="131"/>
-      <c r="H6" s="131"/>
-      <c r="I6" s="131"/>
-      <c r="J6" s="131">
+      <c r="C6" s="111"/>
+      <c r="D6" s="111"/>
+      <c r="E6" s="111"/>
+      <c r="F6" s="111"/>
+      <c r="G6" s="111"/>
+      <c r="H6" s="111"/>
+      <c r="I6" s="111"/>
+      <c r="J6" s="111">
         <v>838</v>
       </c>
-      <c r="K6" s="131"/>
-      <c r="L6" s="131"/>
-      <c r="M6" s="131"/>
-      <c r="N6" s="131"/>
-      <c r="O6" s="131"/>
-      <c r="P6" s="131"/>
-      <c r="Q6" s="131"/>
-      <c r="R6" s="131"/>
-      <c r="S6" s="131"/>
-      <c r="T6" s="131"/>
-      <c r="U6" s="131"/>
-      <c r="V6" s="131">
+      <c r="K6" s="111"/>
+      <c r="L6" s="111"/>
+      <c r="M6" s="111"/>
+      <c r="N6" s="111"/>
+      <c r="O6" s="111"/>
+      <c r="P6" s="111"/>
+      <c r="Q6" s="111"/>
+      <c r="R6" s="111"/>
+      <c r="S6" s="111"/>
+      <c r="T6" s="111"/>
+      <c r="U6" s="111"/>
+      <c r="V6" s="111">
         <v>158.61000000000001</v>
       </c>
-      <c r="W6" s="131"/>
-      <c r="X6" s="131"/>
-      <c r="Y6" s="131"/>
-      <c r="Z6" s="131"/>
-      <c r="AA6" s="132"/>
-      <c r="AB6" s="155">
+      <c r="W6" s="111"/>
+      <c r="X6" s="111"/>
+      <c r="Y6" s="111"/>
+      <c r="Z6" s="111"/>
+      <c r="AA6" s="112"/>
+      <c r="AB6" s="128">
         <f t="shared" ref="AB6:AB18" si="0">SUM(C6:AA6)</f>
         <v>996.61</v>
       </c>
-      <c r="AC6" s="139"/>
+      <c r="AC6" s="117"/>
       <c r="AD6" s="156"/>
     </row>
     <row r="7" spans="1:52" ht="15.75">
-      <c r="A7" s="125">
+      <c r="A7" s="105">
         <v>8</v>
       </c>
-      <c r="B7" s="126" t="s">
+      <c r="B7" s="106" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="127"/>
-      <c r="D7" s="127"/>
-      <c r="E7" s="127"/>
-      <c r="F7" s="127">
+      <c r="C7" s="107"/>
+      <c r="D7" s="107"/>
+      <c r="E7" s="107"/>
+      <c r="F7" s="107">
         <v>1461</v>
       </c>
-      <c r="G7" s="127">
+      <c r="G7" s="107">
         <v>821</v>
       </c>
-      <c r="H7" s="127"/>
-      <c r="I7" s="127">
+      <c r="H7" s="107"/>
+      <c r="I7" s="107">
         <f>2510+220</f>
         <v>2730</v>
       </c>
-      <c r="J7" s="127">
+      <c r="J7" s="107">
         <v>730</v>
       </c>
-      <c r="K7" s="127"/>
-      <c r="L7" s="127"/>
-      <c r="M7" s="127"/>
-      <c r="N7" s="127"/>
-      <c r="O7" s="127">
+      <c r="K7" s="107"/>
+      <c r="L7" s="107"/>
+      <c r="M7" s="107"/>
+      <c r="N7" s="107"/>
+      <c r="O7" s="107">
         <v>100</v>
       </c>
-      <c r="P7" s="127"/>
-      <c r="Q7" s="127"/>
-      <c r="R7" s="127"/>
-      <c r="S7" s="127"/>
-      <c r="T7" s="127"/>
-      <c r="U7" s="127"/>
-      <c r="V7" s="127"/>
-      <c r="W7" s="127"/>
-      <c r="X7" s="127"/>
-      <c r="Y7" s="127"/>
-      <c r="Z7" s="127">
+      <c r="P7" s="107"/>
+      <c r="Q7" s="107"/>
+      <c r="R7" s="107"/>
+      <c r="S7" s="107"/>
+      <c r="T7" s="107"/>
+      <c r="U7" s="107"/>
+      <c r="V7" s="107"/>
+      <c r="W7" s="107"/>
+      <c r="X7" s="107"/>
+      <c r="Y7" s="107"/>
+      <c r="Z7" s="107">
         <v>2626</v>
       </c>
-      <c r="AA7" s="128"/>
-      <c r="AB7" s="155">
+      <c r="AA7" s="108"/>
+      <c r="AB7" s="128">
         <f t="shared" si="0"/>
         <v>8468</v>
       </c>
-      <c r="AC7" s="139"/>
+      <c r="AC7" s="117"/>
       <c r="AD7" s="156"/>
     </row>
     <row r="8" spans="1:52" ht="15" customHeight="1">
-      <c r="A8" s="129">
+      <c r="A8" s="109">
         <v>9</v>
       </c>
-      <c r="B8" s="130" t="s">
+      <c r="B8" s="110" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="131"/>
-      <c r="D8" s="131"/>
-      <c r="E8" s="131">
+      <c r="C8" s="111"/>
+      <c r="D8" s="111"/>
+      <c r="E8" s="111">
         <v>2510</v>
       </c>
-      <c r="F8" s="131"/>
-      <c r="G8" s="131"/>
-      <c r="H8" s="131"/>
-      <c r="I8" s="131"/>
-      <c r="J8" s="131">
+      <c r="F8" s="111"/>
+      <c r="G8" s="111"/>
+      <c r="H8" s="111"/>
+      <c r="I8" s="111"/>
+      <c r="J8" s="111">
         <v>1534</v>
       </c>
-      <c r="K8" s="131"/>
-      <c r="L8" s="131"/>
-      <c r="M8" s="131"/>
-      <c r="N8" s="131"/>
-      <c r="O8" s="131"/>
-      <c r="P8" s="131"/>
-      <c r="Q8" s="131"/>
-      <c r="R8" s="131"/>
-      <c r="S8" s="131"/>
-      <c r="T8" s="131"/>
-      <c r="U8" s="131"/>
-      <c r="V8" s="131"/>
-      <c r="W8" s="131">
+      <c r="K8" s="111"/>
+      <c r="L8" s="111"/>
+      <c r="M8" s="111"/>
+      <c r="N8" s="111"/>
+      <c r="O8" s="111"/>
+      <c r="P8" s="111"/>
+      <c r="Q8" s="111"/>
+      <c r="R8" s="111"/>
+      <c r="S8" s="111"/>
+      <c r="T8" s="111"/>
+      <c r="U8" s="111"/>
+      <c r="V8" s="111"/>
+      <c r="W8" s="111">
         <f>400+1115+3400+1409.98+1800</f>
         <v>8124.98</v>
       </c>
-      <c r="X8" s="131"/>
-      <c r="Y8" s="131"/>
-      <c r="Z8" s="131"/>
-      <c r="AA8" s="132"/>
-      <c r="AB8" s="155">
+      <c r="X8" s="111"/>
+      <c r="Y8" s="111"/>
+      <c r="Z8" s="111"/>
+      <c r="AA8" s="112"/>
+      <c r="AB8" s="128">
         <f t="shared" si="0"/>
         <v>12168.98</v>
       </c>
-      <c r="AC8" s="139"/>
+      <c r="AC8" s="117"/>
       <c r="AD8" s="156"/>
     </row>
     <row r="9" spans="1:52" ht="15.75">
-      <c r="A9" s="125">
+      <c r="A9" s="105">
         <v>10</v>
       </c>
-      <c r="B9" s="126" t="s">
+      <c r="B9" s="106" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="127"/>
-      <c r="D9" s="127"/>
-      <c r="E9" s="127"/>
-      <c r="F9" s="127"/>
-      <c r="G9" s="127"/>
-      <c r="H9" s="127"/>
-      <c r="I9" s="127"/>
-      <c r="J9" s="127"/>
-      <c r="K9" s="127">
+      <c r="C9" s="107"/>
+      <c r="D9" s="107"/>
+      <c r="E9" s="107"/>
+      <c r="F9" s="107"/>
+      <c r="G9" s="107"/>
+      <c r="H9" s="107"/>
+      <c r="I9" s="107"/>
+      <c r="J9" s="107"/>
+      <c r="K9" s="107">
         <v>1860</v>
       </c>
-      <c r="L9" s="127"/>
-      <c r="M9" s="127"/>
-      <c r="N9" s="127">
-        <v>700</v>
-      </c>
-      <c r="O9" s="127"/>
-      <c r="P9" s="127">
+      <c r="L9" s="107"/>
+      <c r="M9" s="107"/>
+      <c r="N9" s="107">
+        <f>700+990</f>
+        <v>1690</v>
+      </c>
+      <c r="O9" s="107"/>
+      <c r="P9" s="107">
         <v>2000</v>
       </c>
-      <c r="Q9" s="127"/>
-      <c r="R9" s="127"/>
-      <c r="S9" s="127"/>
-      <c r="T9" s="127"/>
-      <c r="U9" s="127">
+      <c r="Q9" s="107"/>
+      <c r="R9" s="107"/>
+      <c r="S9" s="107"/>
+      <c r="T9" s="107"/>
+      <c r="U9" s="107">
         <v>420</v>
       </c>
-      <c r="V9" s="127"/>
-      <c r="W9" s="127"/>
-      <c r="X9" s="127"/>
-      <c r="Y9" s="127"/>
-      <c r="Z9" s="127"/>
-      <c r="AA9" s="128"/>
-      <c r="AB9" s="155">
+      <c r="V9" s="107"/>
+      <c r="W9" s="107"/>
+      <c r="X9" s="107"/>
+      <c r="Y9" s="107"/>
+      <c r="Z9" s="107"/>
+      <c r="AA9" s="108"/>
+      <c r="AB9" s="128">
         <f t="shared" si="0"/>
-        <v>4980</v>
-      </c>
-      <c r="AC9" s="139"/>
+        <v>5970</v>
+      </c>
+      <c r="AC9" s="117"/>
       <c r="AD9" s="156"/>
     </row>
     <row r="10" spans="1:52" ht="15.75">
-      <c r="A10" s="129">
+      <c r="A10" s="109">
         <v>11</v>
       </c>
-      <c r="B10" s="130" t="s">
+      <c r="B10" s="110" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="131"/>
-      <c r="D10" s="131"/>
-      <c r="E10" s="131"/>
-      <c r="F10" s="131"/>
-      <c r="G10" s="131"/>
-      <c r="H10" s="131"/>
-      <c r="I10" s="131"/>
-      <c r="J10" s="131"/>
-      <c r="K10" s="131"/>
-      <c r="L10" s="131"/>
-      <c r="M10" s="131"/>
-      <c r="N10" s="131"/>
-      <c r="O10" s="131"/>
-      <c r="P10" s="131"/>
-      <c r="Q10" s="131"/>
-      <c r="R10" s="131"/>
-      <c r="S10" s="131"/>
-      <c r="T10" s="131"/>
-      <c r="U10" s="131"/>
-      <c r="V10" s="131"/>
-      <c r="W10" s="131"/>
-      <c r="X10" s="131"/>
-      <c r="Y10" s="131"/>
-      <c r="Z10" s="131"/>
-      <c r="AA10" s="132"/>
-      <c r="AB10" s="155">
+      <c r="C10" s="111"/>
+      <c r="D10" s="111"/>
+      <c r="E10" s="111"/>
+      <c r="F10" s="111"/>
+      <c r="G10" s="111"/>
+      <c r="H10" s="111"/>
+      <c r="I10" s="111"/>
+      <c r="J10" s="111"/>
+      <c r="K10" s="111"/>
+      <c r="L10" s="111"/>
+      <c r="M10" s="111"/>
+      <c r="N10" s="111"/>
+      <c r="O10" s="111"/>
+      <c r="P10" s="111"/>
+      <c r="Q10" s="111">
+        <v>500</v>
+      </c>
+      <c r="R10" s="111"/>
+      <c r="S10" s="111"/>
+      <c r="T10" s="111"/>
+      <c r="U10" s="111">
+        <v>207</v>
+      </c>
+      <c r="V10" s="111"/>
+      <c r="W10" s="111">
+        <v>1180</v>
+      </c>
+      <c r="X10" s="111"/>
+      <c r="Y10" s="111"/>
+      <c r="Z10" s="111"/>
+      <c r="AA10" s="112"/>
+      <c r="AB10" s="128">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AC10" s="139"/>
+        <v>1887</v>
+      </c>
+      <c r="AC10" s="117"/>
       <c r="AD10" s="156"/>
     </row>
     <row r="11" spans="1:52" ht="15.75">
-      <c r="A11" s="125">
+      <c r="A11" s="105">
         <v>12</v>
       </c>
-      <c r="B11" s="126" t="s">
+      <c r="B11" s="106" t="s">
         <v>2</v>
       </c>
-      <c r="C11" s="127"/>
-      <c r="D11" s="127"/>
-      <c r="E11" s="127"/>
-      <c r="F11" s="127"/>
-      <c r="G11" s="127"/>
-      <c r="H11" s="127"/>
-      <c r="I11" s="127"/>
-      <c r="J11" s="127"/>
-      <c r="K11" s="127"/>
-      <c r="L11" s="127"/>
-      <c r="M11" s="127"/>
-      <c r="N11" s="127"/>
-      <c r="O11" s="127"/>
-      <c r="P11" s="127"/>
-      <c r="Q11" s="127"/>
-      <c r="R11" s="127"/>
-      <c r="S11" s="127"/>
-      <c r="T11" s="127"/>
-      <c r="U11" s="127"/>
-      <c r="V11" s="127"/>
-      <c r="W11" s="127"/>
-      <c r="X11" s="127"/>
-      <c r="Y11" s="127"/>
-      <c r="Z11" s="127"/>
-      <c r="AA11" s="128"/>
-      <c r="AB11" s="155">
+      <c r="C11" s="107"/>
+      <c r="D11" s="107"/>
+      <c r="E11" s="107"/>
+      <c r="F11" s="107"/>
+      <c r="G11" s="107"/>
+      <c r="H11" s="107"/>
+      <c r="I11" s="107"/>
+      <c r="J11" s="107"/>
+      <c r="K11" s="107"/>
+      <c r="L11" s="107"/>
+      <c r="M11" s="107"/>
+      <c r="N11" s="107"/>
+      <c r="O11" s="107"/>
+      <c r="P11" s="107"/>
+      <c r="Q11" s="107"/>
+      <c r="R11" s="107"/>
+      <c r="S11" s="107"/>
+      <c r="T11" s="107"/>
+      <c r="U11" s="107"/>
+      <c r="V11" s="107"/>
+      <c r="W11" s="107"/>
+      <c r="X11" s="107"/>
+      <c r="Y11" s="107"/>
+      <c r="Z11" s="107"/>
+      <c r="AA11" s="108"/>
+      <c r="AB11" s="128">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AC11" s="139"/>
+      <c r="AC11" s="117"/>
       <c r="AD11" s="156"/>
     </row>
     <row r="12" spans="1:52" ht="15.75">
-      <c r="A12" s="129">
+      <c r="A12" s="109">
         <v>13</v>
       </c>
-      <c r="B12" s="130" t="s">
+      <c r="B12" s="110" t="s">
         <v>3</v>
       </c>
-      <c r="C12" s="131"/>
-      <c r="D12" s="131"/>
-      <c r="E12" s="131"/>
-      <c r="F12" s="131"/>
-      <c r="G12" s="131"/>
-      <c r="H12" s="131"/>
-      <c r="I12" s="131"/>
-      <c r="J12" s="131"/>
-      <c r="K12" s="131"/>
-      <c r="L12" s="131"/>
-      <c r="M12" s="131"/>
-      <c r="N12" s="131"/>
-      <c r="O12" s="131"/>
-      <c r="P12" s="131"/>
-      <c r="Q12" s="131"/>
-      <c r="R12" s="131"/>
-      <c r="S12" s="131"/>
-      <c r="T12" s="131"/>
-      <c r="U12" s="131"/>
-      <c r="V12" s="131"/>
-      <c r="W12" s="131"/>
-      <c r="X12" s="131"/>
-      <c r="Y12" s="131"/>
-      <c r="Z12" s="131"/>
-      <c r="AA12" s="132"/>
-      <c r="AB12" s="155">
+      <c r="C12" s="111"/>
+      <c r="D12" s="111"/>
+      <c r="E12" s="111"/>
+      <c r="F12" s="111"/>
+      <c r="G12" s="111"/>
+      <c r="H12" s="111"/>
+      <c r="I12" s="111"/>
+      <c r="J12" s="111"/>
+      <c r="K12" s="111"/>
+      <c r="L12" s="111"/>
+      <c r="M12" s="111"/>
+      <c r="N12" s="111"/>
+      <c r="O12" s="111"/>
+      <c r="P12" s="111"/>
+      <c r="Q12" s="111"/>
+      <c r="R12" s="111"/>
+      <c r="S12" s="111"/>
+      <c r="T12" s="111"/>
+      <c r="U12" s="111"/>
+      <c r="V12" s="111"/>
+      <c r="W12" s="111"/>
+      <c r="X12" s="111"/>
+      <c r="Y12" s="111"/>
+      <c r="Z12" s="111"/>
+      <c r="AA12" s="112"/>
+      <c r="AB12" s="128">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AC12" s="139"/>
+      <c r="AC12" s="117"/>
       <c r="AD12" s="156"/>
     </row>
     <row r="13" spans="1:52" ht="15.75">
-      <c r="A13" s="125">
+      <c r="A13" s="105">
         <v>14</v>
       </c>
-      <c r="B13" s="126" t="s">
+      <c r="B13" s="106" t="s">
         <v>4</v>
       </c>
-      <c r="C13" s="127"/>
-      <c r="D13" s="127"/>
-      <c r="E13" s="127"/>
-      <c r="F13" s="127"/>
-      <c r="G13" s="127"/>
-      <c r="H13" s="127"/>
-      <c r="I13" s="127"/>
-      <c r="J13" s="127"/>
-      <c r="K13" s="127"/>
-      <c r="L13" s="127"/>
-      <c r="M13" s="127"/>
-      <c r="N13" s="127"/>
-      <c r="O13" s="127"/>
-      <c r="P13" s="127"/>
-      <c r="Q13" s="127"/>
-      <c r="R13" s="127"/>
-      <c r="S13" s="127"/>
-      <c r="T13" s="127"/>
-      <c r="U13" s="127"/>
-      <c r="V13" s="127"/>
-      <c r="W13" s="127"/>
-      <c r="X13" s="127"/>
-      <c r="Y13" s="127"/>
-      <c r="Z13" s="127"/>
-      <c r="AA13" s="128"/>
-      <c r="AB13" s="155">
+      <c r="C13" s="107"/>
+      <c r="D13" s="107"/>
+      <c r="E13" s="107"/>
+      <c r="F13" s="107"/>
+      <c r="G13" s="107"/>
+      <c r="H13" s="107"/>
+      <c r="I13" s="107"/>
+      <c r="J13" s="107"/>
+      <c r="K13" s="107"/>
+      <c r="L13" s="107"/>
+      <c r="M13" s="107"/>
+      <c r="N13" s="107"/>
+      <c r="O13" s="107"/>
+      <c r="P13" s="107"/>
+      <c r="Q13" s="107"/>
+      <c r="R13" s="107"/>
+      <c r="S13" s="107"/>
+      <c r="T13" s="107"/>
+      <c r="U13" s="107"/>
+      <c r="V13" s="107"/>
+      <c r="W13" s="107"/>
+      <c r="X13" s="107"/>
+      <c r="Y13" s="107"/>
+      <c r="Z13" s="107"/>
+      <c r="AA13" s="108"/>
+      <c r="AB13" s="128">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AC13" s="139"/>
+      <c r="AC13" s="117"/>
       <c r="AD13" s="156"/>
     </row>
     <row r="14" spans="1:52" ht="15.75">
-      <c r="A14" s="129">
+      <c r="A14" s="109">
         <v>15</v>
       </c>
-      <c r="B14" s="130" t="s">
+      <c r="B14" s="110" t="s">
         <v>5</v>
       </c>
-      <c r="C14" s="131"/>
-      <c r="D14" s="131"/>
-      <c r="E14" s="131"/>
-      <c r="F14" s="131"/>
-      <c r="G14" s="131"/>
-      <c r="H14" s="131"/>
-      <c r="I14" s="131"/>
-      <c r="J14" s="131"/>
-      <c r="K14" s="131"/>
-      <c r="L14" s="131"/>
-      <c r="M14" s="131"/>
-      <c r="N14" s="131"/>
-      <c r="O14" s="131"/>
-      <c r="P14" s="131"/>
-      <c r="Q14" s="131"/>
-      <c r="R14" s="131"/>
-      <c r="S14" s="131"/>
-      <c r="T14" s="131"/>
-      <c r="U14" s="131"/>
-      <c r="V14" s="131"/>
-      <c r="W14" s="131"/>
-      <c r="X14" s="131"/>
-      <c r="Y14" s="131"/>
-      <c r="Z14" s="131"/>
-      <c r="AA14" s="132"/>
-      <c r="AB14" s="155">
+      <c r="C14" s="111"/>
+      <c r="D14" s="111"/>
+      <c r="E14" s="111"/>
+      <c r="F14" s="111"/>
+      <c r="G14" s="111"/>
+      <c r="H14" s="111"/>
+      <c r="I14" s="111"/>
+      <c r="J14" s="111"/>
+      <c r="K14" s="111"/>
+      <c r="L14" s="111"/>
+      <c r="M14" s="111"/>
+      <c r="N14" s="111"/>
+      <c r="O14" s="111"/>
+      <c r="P14" s="111"/>
+      <c r="Q14" s="111"/>
+      <c r="R14" s="111"/>
+      <c r="S14" s="111"/>
+      <c r="T14" s="111"/>
+      <c r="U14" s="111"/>
+      <c r="V14" s="111"/>
+      <c r="W14" s="111"/>
+      <c r="X14" s="111"/>
+      <c r="Y14" s="111"/>
+      <c r="Z14" s="111"/>
+      <c r="AA14" s="112"/>
+      <c r="AB14" s="128">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AC14" s="139"/>
+      <c r="AC14" s="117"/>
       <c r="AD14" s="156"/>
     </row>
     <row r="15" spans="1:52" ht="15.75">
-      <c r="A15" s="125">
+      <c r="A15" s="105">
         <v>16</v>
       </c>
-      <c r="B15" s="126" t="s">
+      <c r="B15" s="106" t="s">
         <v>6</v>
       </c>
-      <c r="C15" s="127"/>
-      <c r="D15" s="127"/>
-      <c r="E15" s="127"/>
-      <c r="F15" s="127"/>
-      <c r="G15" s="127"/>
-      <c r="H15" s="127"/>
-      <c r="I15" s="127"/>
-      <c r="J15" s="127"/>
-      <c r="K15" s="127"/>
-      <c r="L15" s="127"/>
-      <c r="M15" s="127"/>
-      <c r="N15" s="127"/>
-      <c r="O15" s="127"/>
-      <c r="P15" s="127"/>
-      <c r="Q15" s="127"/>
-      <c r="R15" s="127"/>
-      <c r="S15" s="127"/>
-      <c r="T15" s="127"/>
-      <c r="U15" s="127"/>
-      <c r="V15" s="127"/>
-      <c r="W15" s="127"/>
-      <c r="X15" s="127"/>
-      <c r="Y15" s="127"/>
-      <c r="Z15" s="127"/>
-      <c r="AA15" s="128"/>
-      <c r="AB15" s="155">
+      <c r="C15" s="107"/>
+      <c r="D15" s="107"/>
+      <c r="E15" s="107"/>
+      <c r="F15" s="107"/>
+      <c r="G15" s="107"/>
+      <c r="H15" s="107"/>
+      <c r="I15" s="107"/>
+      <c r="J15" s="107"/>
+      <c r="K15" s="107"/>
+      <c r="L15" s="107"/>
+      <c r="M15" s="107"/>
+      <c r="N15" s="107"/>
+      <c r="O15" s="107"/>
+      <c r="P15" s="107"/>
+      <c r="Q15" s="107"/>
+      <c r="R15" s="107"/>
+      <c r="S15" s="107"/>
+      <c r="T15" s="107"/>
+      <c r="U15" s="107"/>
+      <c r="V15" s="107"/>
+      <c r="W15" s="107"/>
+      <c r="X15" s="107"/>
+      <c r="Y15" s="107"/>
+      <c r="Z15" s="107"/>
+      <c r="AA15" s="108"/>
+      <c r="AB15" s="128">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AC15" s="140"/>
+      <c r="AC15" s="118"/>
       <c r="AD15" s="156"/>
     </row>
     <row r="16" spans="1:52" ht="15.75">
-      <c r="A16" s="129">
+      <c r="A16" s="109">
         <v>17</v>
       </c>
-      <c r="B16" s="130" t="s">
+      <c r="B16" s="110" t="s">
         <v>7</v>
       </c>
-      <c r="C16" s="131"/>
-      <c r="D16" s="131"/>
-      <c r="E16" s="131"/>
-      <c r="F16" s="131"/>
-      <c r="G16" s="131"/>
-      <c r="H16" s="131"/>
-      <c r="I16" s="131"/>
-      <c r="J16" s="131"/>
-      <c r="K16" s="131"/>
-      <c r="L16" s="131"/>
-      <c r="M16" s="131"/>
-      <c r="N16" s="131"/>
-      <c r="O16" s="131"/>
-      <c r="P16" s="131"/>
-      <c r="Q16" s="131"/>
-      <c r="R16" s="131"/>
-      <c r="S16" s="131"/>
-      <c r="T16" s="131"/>
-      <c r="U16" s="131"/>
-      <c r="V16" s="131"/>
-      <c r="W16" s="131"/>
-      <c r="X16" s="131"/>
-      <c r="Y16" s="131"/>
-      <c r="Z16" s="131"/>
-      <c r="AA16" s="132"/>
-      <c r="AB16" s="155">
+      <c r="C16" s="111"/>
+      <c r="D16" s="111"/>
+      <c r="E16" s="111"/>
+      <c r="F16" s="111"/>
+      <c r="G16" s="111"/>
+      <c r="H16" s="111"/>
+      <c r="I16" s="111"/>
+      <c r="J16" s="111"/>
+      <c r="K16" s="111"/>
+      <c r="L16" s="111"/>
+      <c r="M16" s="111"/>
+      <c r="N16" s="111"/>
+      <c r="O16" s="111"/>
+      <c r="P16" s="111"/>
+      <c r="Q16" s="111"/>
+      <c r="R16" s="111"/>
+      <c r="S16" s="111"/>
+      <c r="T16" s="111"/>
+      <c r="U16" s="111"/>
+      <c r="V16" s="111"/>
+      <c r="W16" s="111"/>
+      <c r="X16" s="111"/>
+      <c r="Y16" s="111"/>
+      <c r="Z16" s="111"/>
+      <c r="AA16" s="112"/>
+      <c r="AB16" s="128">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AC16" s="139"/>
+      <c r="AC16" s="117"/>
       <c r="AD16" s="156"/>
     </row>
     <row r="17" spans="1:32" ht="15.75">
-      <c r="A17" s="125">
+      <c r="A17" s="105">
         <v>18</v>
       </c>
-      <c r="B17" s="126" t="s">
+      <c r="B17" s="106" t="s">
         <v>8</v>
       </c>
-      <c r="C17" s="127"/>
-      <c r="D17" s="127"/>
-      <c r="E17" s="127"/>
-      <c r="F17" s="127"/>
-      <c r="G17" s="127"/>
-      <c r="H17" s="127"/>
-      <c r="I17" s="127"/>
-      <c r="J17" s="127"/>
-      <c r="K17" s="127"/>
-      <c r="L17" s="127"/>
-      <c r="M17" s="127"/>
-      <c r="N17" s="127"/>
-      <c r="O17" s="127"/>
-      <c r="P17" s="127"/>
-      <c r="Q17" s="127"/>
-      <c r="R17" s="127"/>
-      <c r="S17" s="127"/>
-      <c r="T17" s="127"/>
-      <c r="U17" s="127"/>
-      <c r="V17" s="127"/>
-      <c r="W17" s="127"/>
-      <c r="X17" s="127"/>
-      <c r="Y17" s="127"/>
-      <c r="Z17" s="127"/>
-      <c r="AA17" s="128"/>
-      <c r="AB17" s="155">
+      <c r="C17" s="107"/>
+      <c r="D17" s="107"/>
+      <c r="E17" s="107"/>
+      <c r="F17" s="107"/>
+      <c r="G17" s="107"/>
+      <c r="H17" s="107"/>
+      <c r="I17" s="107"/>
+      <c r="J17" s="107"/>
+      <c r="K17" s="107"/>
+      <c r="L17" s="107"/>
+      <c r="M17" s="107"/>
+      <c r="N17" s="107"/>
+      <c r="O17" s="107"/>
+      <c r="P17" s="107"/>
+      <c r="Q17" s="107"/>
+      <c r="R17" s="107"/>
+      <c r="S17" s="107"/>
+      <c r="T17" s="107"/>
+      <c r="U17" s="107"/>
+      <c r="V17" s="107"/>
+      <c r="W17" s="107"/>
+      <c r="X17" s="107"/>
+      <c r="Y17" s="107"/>
+      <c r="Z17" s="107"/>
+      <c r="AA17" s="108"/>
+      <c r="AB17" s="128">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AC17" s="139"/>
+      <c r="AC17" s="117"/>
       <c r="AD17" s="156"/>
     </row>
     <row r="18" spans="1:32" ht="15.75">
-      <c r="A18" s="129">
+      <c r="A18" s="109">
         <v>19</v>
       </c>
-      <c r="B18" s="130" t="s">
+      <c r="B18" s="110" t="s">
         <v>2</v>
       </c>
-      <c r="C18" s="131"/>
-      <c r="D18" s="131"/>
-      <c r="E18" s="131"/>
-      <c r="F18" s="131"/>
-      <c r="G18" s="131"/>
-      <c r="H18" s="131"/>
-      <c r="I18" s="131"/>
-      <c r="J18" s="131"/>
-      <c r="K18" s="131"/>
-      <c r="L18" s="131"/>
-      <c r="M18" s="131"/>
-      <c r="N18" s="131"/>
-      <c r="O18" s="131"/>
-      <c r="P18" s="131"/>
-      <c r="Q18" s="131"/>
-      <c r="R18" s="131"/>
-      <c r="S18" s="131"/>
-      <c r="T18" s="131"/>
-      <c r="U18" s="131"/>
-      <c r="V18" s="131"/>
-      <c r="W18" s="131"/>
-      <c r="X18" s="131"/>
-      <c r="Y18" s="131"/>
-      <c r="Z18" s="131"/>
-      <c r="AA18" s="132"/>
-      <c r="AB18" s="155">
+      <c r="C18" s="111"/>
+      <c r="D18" s="111"/>
+      <c r="E18" s="111"/>
+      <c r="F18" s="111"/>
+      <c r="G18" s="111"/>
+      <c r="H18" s="111"/>
+      <c r="I18" s="111"/>
+      <c r="J18" s="111"/>
+      <c r="K18" s="111"/>
+      <c r="L18" s="111"/>
+      <c r="M18" s="111"/>
+      <c r="N18" s="111"/>
+      <c r="O18" s="111"/>
+      <c r="P18" s="111"/>
+      <c r="Q18" s="111"/>
+      <c r="R18" s="111"/>
+      <c r="S18" s="111"/>
+      <c r="T18" s="111"/>
+      <c r="U18" s="111"/>
+      <c r="V18" s="111"/>
+      <c r="W18" s="111"/>
+      <c r="X18" s="111"/>
+      <c r="Y18" s="111"/>
+      <c r="Z18" s="111"/>
+      <c r="AA18" s="112"/>
+      <c r="AB18" s="128">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AC18" s="139"/>
+      <c r="AC18" s="117"/>
       <c r="AD18" s="156"/>
     </row>
     <row r="19" spans="1:32" ht="14.25" customHeight="1">
-      <c r="A19" s="136" t="s">
+      <c r="A19" s="157" t="s">
         <v>35</v>
       </c>
-      <c r="B19" s="136"/>
-      <c r="C19" s="133">
+      <c r="B19" s="157"/>
+      <c r="C19" s="113">
         <f>SUM(C4:C18)</f>
         <v>429.95</v>
       </c>
-      <c r="D19" s="133">
+      <c r="D19" s="113">
         <f t="shared" ref="D19:AA19" si="1">SUM(D4:D18)</f>
         <v>0</v>
       </c>
-      <c r="E19" s="133">
+      <c r="E19" s="113">
         <f t="shared" si="1"/>
         <v>2510</v>
       </c>
-      <c r="F19" s="133">
+      <c r="F19" s="113">
         <f t="shared" si="1"/>
         <v>1812</v>
       </c>
-      <c r="G19" s="133">
+      <c r="G19" s="113">
         <f t="shared" si="1"/>
         <v>821</v>
       </c>
-      <c r="H19" s="133">
+      <c r="H19" s="113">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I19" s="133">
+      <c r="I19" s="113">
         <f t="shared" si="1"/>
         <v>7935</v>
       </c>
-      <c r="J19" s="133">
+      <c r="J19" s="113">
         <f t="shared" si="1"/>
         <v>3102</v>
       </c>
-      <c r="K19" s="133">
+      <c r="K19" s="113">
         <f t="shared" si="1"/>
         <v>1860</v>
       </c>
-      <c r="L19" s="134">
+      <c r="L19" s="114">
         <f t="shared" si="1"/>
         <v>10858.130000000001</v>
       </c>
-      <c r="M19" s="134">
+      <c r="M19" s="114">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N19" s="134">
+      <c r="N19" s="114">
         <f t="shared" si="1"/>
-        <v>700</v>
-      </c>
-      <c r="O19" s="134">
+        <v>1690</v>
+      </c>
+      <c r="O19" s="114">
         <f t="shared" si="1"/>
         <v>200</v>
       </c>
-      <c r="P19" s="134">
+      <c r="P19" s="114">
         <f t="shared" si="1"/>
         <v>12000</v>
       </c>
-      <c r="Q19" s="134">
+      <c r="Q19" s="114">
         <f t="shared" si="1"/>
-        <v>3500</v>
-      </c>
-      <c r="R19" s="135">
+        <v>4000</v>
+      </c>
+      <c r="R19" s="115">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="S19" s="135">
+      <c r="S19" s="115">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="T19" s="135">
+      <c r="T19" s="115">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="U19" s="135">
+      <c r="U19" s="115">
         <f t="shared" si="1"/>
-        <v>714</v>
-      </c>
-      <c r="V19" s="135">
+        <v>921</v>
+      </c>
+      <c r="V19" s="115">
         <f t="shared" si="1"/>
         <v>158.61000000000001</v>
       </c>
-      <c r="W19" s="135">
+      <c r="W19" s="115">
         <f t="shared" si="1"/>
-        <v>9624.98</v>
-      </c>
-      <c r="X19" s="135">
+        <v>10804.98</v>
+      </c>
+      <c r="X19" s="115">
         <f t="shared" si="1"/>
         <v>1237</v>
       </c>
-      <c r="Y19" s="135">
+      <c r="Y19" s="115">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Z19" s="135">
+      <c r="Z19" s="115">
         <f t="shared" si="1"/>
         <v>2626</v>
       </c>
-      <c r="AA19" s="151">
+      <c r="AA19" s="124">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AB19" s="157">
+      <c r="AB19" s="129">
         <f>SUM(AB4:AB18)</f>
-        <v>60088.67</v>
-      </c>
-      <c r="AC19" s="158">
+        <v>62965.67</v>
+      </c>
+      <c r="AC19" s="130">
         <f>SUM(AC4:AC18)</f>
         <v>96705.110000000015</v>
       </c>
-      <c r="AD19" s="161">
+      <c r="AD19" s="133">
         <f>AC19-AB19</f>
-        <v>36616.440000000017</v>
+        <v>33739.440000000017</v>
       </c>
     </row>
     <row r="20" spans="1:32" ht="15.75">
-      <c r="A20" s="129">
+      <c r="A20" s="109">
         <v>20</v>
       </c>
-      <c r="B20" s="130" t="s">
+      <c r="B20" s="110" t="s">
         <v>3</v>
       </c>
-      <c r="C20" s="131"/>
-      <c r="D20" s="131"/>
-      <c r="E20" s="131"/>
-      <c r="F20" s="131"/>
-      <c r="G20" s="131"/>
-      <c r="H20" s="131"/>
-      <c r="I20" s="131"/>
-      <c r="J20" s="131"/>
-      <c r="K20" s="131"/>
-      <c r="L20" s="131"/>
-      <c r="M20" s="131"/>
-      <c r="N20" s="131"/>
-      <c r="O20" s="131"/>
-      <c r="P20" s="131"/>
-      <c r="Q20" s="131"/>
-      <c r="R20" s="131"/>
-      <c r="S20" s="131"/>
-      <c r="T20" s="131"/>
-      <c r="U20" s="131"/>
-      <c r="V20" s="131"/>
-      <c r="W20" s="131"/>
-      <c r="X20" s="131"/>
-      <c r="Y20" s="131"/>
-      <c r="Z20" s="131"/>
-      <c r="AA20" s="132"/>
-      <c r="AB20" s="155">
+      <c r="C20" s="111"/>
+      <c r="D20" s="111"/>
+      <c r="E20" s="111"/>
+      <c r="F20" s="111"/>
+      <c r="G20" s="111"/>
+      <c r="H20" s="111"/>
+      <c r="I20" s="111"/>
+      <c r="J20" s="111"/>
+      <c r="K20" s="111"/>
+      <c r="L20" s="111"/>
+      <c r="M20" s="111"/>
+      <c r="N20" s="111"/>
+      <c r="O20" s="111"/>
+      <c r="P20" s="111"/>
+      <c r="Q20" s="111"/>
+      <c r="R20" s="111"/>
+      <c r="S20" s="111"/>
+      <c r="T20" s="111"/>
+      <c r="U20" s="111"/>
+      <c r="V20" s="111"/>
+      <c r="W20" s="111"/>
+      <c r="X20" s="111"/>
+      <c r="Y20" s="111"/>
+      <c r="Z20" s="111"/>
+      <c r="AA20" s="112"/>
+      <c r="AB20" s="128">
         <f>SUM(C20:AA20)</f>
         <v>0</v>
       </c>
-      <c r="AC20" s="140"/>
+      <c r="AC20" s="118"/>
       <c r="AD20" s="156"/>
     </row>
     <row r="21" spans="1:32" ht="15.75">
-      <c r="A21" s="125">
+      <c r="A21" s="105">
         <v>21</v>
       </c>
-      <c r="B21" s="126" t="s">
+      <c r="B21" s="106" t="s">
         <v>4</v>
       </c>
-      <c r="C21" s="127"/>
-      <c r="D21" s="127"/>
-      <c r="E21" s="127"/>
-      <c r="F21" s="127"/>
-      <c r="G21" s="127"/>
-      <c r="H21" s="127"/>
-      <c r="I21" s="127"/>
-      <c r="J21" s="127"/>
-      <c r="K21" s="127"/>
-      <c r="L21" s="127"/>
-      <c r="M21" s="127"/>
-      <c r="N21" s="127"/>
-      <c r="O21" s="127"/>
-      <c r="P21" s="127"/>
-      <c r="Q21" s="127"/>
-      <c r="R21" s="127"/>
-      <c r="S21" s="127"/>
-      <c r="T21" s="127"/>
-      <c r="U21" s="127"/>
-      <c r="V21" s="127"/>
-      <c r="W21" s="127"/>
-      <c r="X21" s="127"/>
-      <c r="Y21" s="127"/>
-      <c r="Z21" s="127"/>
-      <c r="AA21" s="128"/>
-      <c r="AB21" s="155">
+      <c r="C21" s="107"/>
+      <c r="D21" s="107"/>
+      <c r="E21" s="107"/>
+      <c r="F21" s="107"/>
+      <c r="G21" s="107"/>
+      <c r="H21" s="107"/>
+      <c r="I21" s="107"/>
+      <c r="J21" s="107"/>
+      <c r="K21" s="107"/>
+      <c r="L21" s="107"/>
+      <c r="M21" s="107"/>
+      <c r="N21" s="107"/>
+      <c r="O21" s="107"/>
+      <c r="P21" s="107"/>
+      <c r="Q21" s="107"/>
+      <c r="R21" s="107"/>
+      <c r="S21" s="107"/>
+      <c r="T21" s="107"/>
+      <c r="U21" s="107"/>
+      <c r="V21" s="107"/>
+      <c r="W21" s="107"/>
+      <c r="X21" s="107"/>
+      <c r="Y21" s="107"/>
+      <c r="Z21" s="107"/>
+      <c r="AA21" s="108"/>
+      <c r="AB21" s="128">
         <f>SUM(C21:AA21)</f>
         <v>0</v>
       </c>
-      <c r="AC21" s="139"/>
+      <c r="AC21" s="117"/>
       <c r="AD21" s="156"/>
       <c r="AF21" s="44"/>
     </row>
     <row r="22" spans="1:32" ht="15.75">
-      <c r="A22" s="129">
+      <c r="A22" s="109">
         <v>22</v>
       </c>
-      <c r="B22" s="130" t="s">
+      <c r="B22" s="110" t="s">
         <v>5</v>
       </c>
-      <c r="C22" s="131"/>
-      <c r="D22" s="131"/>
-      <c r="E22" s="131"/>
-      <c r="F22" s="131"/>
-      <c r="G22" s="131"/>
-      <c r="H22" s="131"/>
-      <c r="I22" s="131"/>
-      <c r="J22" s="131"/>
-      <c r="K22" s="131"/>
-      <c r="L22" s="131"/>
-      <c r="M22" s="131"/>
-      <c r="N22" s="131"/>
-      <c r="O22" s="131"/>
-      <c r="P22" s="131"/>
-      <c r="Q22" s="131"/>
-      <c r="R22" s="131"/>
-      <c r="S22" s="131"/>
-      <c r="T22" s="131"/>
-      <c r="U22" s="131"/>
-      <c r="V22" s="131"/>
-      <c r="W22" s="131"/>
-      <c r="X22" s="131"/>
-      <c r="Y22" s="131"/>
-      <c r="Z22" s="131"/>
-      <c r="AA22" s="132"/>
-      <c r="AB22" s="155">
+      <c r="C22" s="111"/>
+      <c r="D22" s="111"/>
+      <c r="E22" s="111"/>
+      <c r="F22" s="111"/>
+      <c r="G22" s="111"/>
+      <c r="H22" s="111"/>
+      <c r="I22" s="111"/>
+      <c r="J22" s="111"/>
+      <c r="K22" s="111"/>
+      <c r="L22" s="111"/>
+      <c r="M22" s="111"/>
+      <c r="N22" s="111"/>
+      <c r="O22" s="111"/>
+      <c r="P22" s="111"/>
+      <c r="Q22" s="111"/>
+      <c r="R22" s="111"/>
+      <c r="S22" s="111"/>
+      <c r="T22" s="111"/>
+      <c r="U22" s="111"/>
+      <c r="V22" s="111"/>
+      <c r="W22" s="111"/>
+      <c r="X22" s="111"/>
+      <c r="Y22" s="111"/>
+      <c r="Z22" s="111"/>
+      <c r="AA22" s="112"/>
+      <c r="AB22" s="128">
         <f t="shared" ref="AB22:AB35" si="2">SUM(C22:AA22)</f>
         <v>0</v>
       </c>
-      <c r="AC22" s="139"/>
+      <c r="AC22" s="117"/>
       <c r="AD22" s="156"/>
     </row>
     <row r="23" spans="1:32" ht="15.75">
-      <c r="A23" s="125">
+      <c r="A23" s="105">
         <v>23</v>
       </c>
-      <c r="B23" s="126" t="s">
+      <c r="B23" s="106" t="s">
         <v>6</v>
       </c>
-      <c r="C23" s="127"/>
-      <c r="D23" s="127"/>
-      <c r="E23" s="127"/>
-      <c r="F23" s="127"/>
-      <c r="G23" s="127"/>
-      <c r="H23" s="127"/>
-      <c r="I23" s="127"/>
-      <c r="J23" s="127"/>
-      <c r="K23" s="127"/>
-      <c r="L23" s="127"/>
-      <c r="M23" s="127"/>
-      <c r="N23" s="127"/>
-      <c r="O23" s="127"/>
-      <c r="P23" s="127"/>
-      <c r="Q23" s="127"/>
-      <c r="R23" s="127"/>
-      <c r="S23" s="127"/>
-      <c r="T23" s="127"/>
-      <c r="U23" s="127"/>
-      <c r="V23" s="127"/>
-      <c r="W23" s="127"/>
-      <c r="X23" s="127"/>
-      <c r="Y23" s="127"/>
-      <c r="Z23" s="127"/>
-      <c r="AA23" s="128"/>
-      <c r="AB23" s="155">
+      <c r="C23" s="107"/>
+      <c r="D23" s="107"/>
+      <c r="E23" s="107"/>
+      <c r="F23" s="107"/>
+      <c r="G23" s="107"/>
+      <c r="H23" s="107"/>
+      <c r="I23" s="107"/>
+      <c r="J23" s="107"/>
+      <c r="K23" s="107"/>
+      <c r="L23" s="107"/>
+      <c r="M23" s="107"/>
+      <c r="N23" s="107"/>
+      <c r="O23" s="107"/>
+      <c r="P23" s="107"/>
+      <c r="Q23" s="107"/>
+      <c r="R23" s="107"/>
+      <c r="S23" s="107"/>
+      <c r="T23" s="107"/>
+      <c r="U23" s="107"/>
+      <c r="V23" s="107"/>
+      <c r="W23" s="107"/>
+      <c r="X23" s="107"/>
+      <c r="Y23" s="107"/>
+      <c r="Z23" s="107"/>
+      <c r="AA23" s="108"/>
+      <c r="AB23" s="128">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AC23" s="139"/>
+      <c r="AC23" s="117"/>
       <c r="AD23" s="156"/>
     </row>
     <row r="24" spans="1:32" ht="15.75">
-      <c r="A24" s="129">
+      <c r="A24" s="109">
         <v>24</v>
       </c>
-      <c r="B24" s="130" t="s">
+      <c r="B24" s="110" t="s">
         <v>7</v>
       </c>
-      <c r="C24" s="131"/>
-      <c r="D24" s="131"/>
-      <c r="E24" s="131"/>
-      <c r="F24" s="131"/>
-      <c r="G24" s="131"/>
-      <c r="H24" s="131"/>
-      <c r="I24" s="131"/>
-      <c r="J24" s="131"/>
-      <c r="K24" s="131"/>
-      <c r="L24" s="131"/>
-      <c r="M24" s="131"/>
-      <c r="N24" s="131"/>
-      <c r="O24" s="131"/>
-      <c r="P24" s="131"/>
-      <c r="Q24" s="131"/>
-      <c r="R24" s="131"/>
-      <c r="S24" s="131"/>
-      <c r="T24" s="131"/>
-      <c r="U24" s="131"/>
-      <c r="V24" s="131"/>
-      <c r="W24" s="131"/>
-      <c r="X24" s="131"/>
-      <c r="Y24" s="131"/>
-      <c r="Z24" s="131"/>
-      <c r="AA24" s="132"/>
-      <c r="AB24" s="155">
+      <c r="C24" s="111"/>
+      <c r="D24" s="111"/>
+      <c r="E24" s="111"/>
+      <c r="F24" s="111"/>
+      <c r="G24" s="111"/>
+      <c r="H24" s="111"/>
+      <c r="I24" s="111"/>
+      <c r="J24" s="111"/>
+      <c r="K24" s="111"/>
+      <c r="L24" s="111"/>
+      <c r="M24" s="111"/>
+      <c r="N24" s="111"/>
+      <c r="O24" s="111"/>
+      <c r="P24" s="111"/>
+      <c r="Q24" s="111"/>
+      <c r="R24" s="111"/>
+      <c r="S24" s="111"/>
+      <c r="T24" s="111"/>
+      <c r="U24" s="111"/>
+      <c r="V24" s="111"/>
+      <c r="W24" s="111"/>
+      <c r="X24" s="111"/>
+      <c r="Y24" s="111"/>
+      <c r="Z24" s="111"/>
+      <c r="AA24" s="112"/>
+      <c r="AB24" s="128">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AC24" s="139"/>
+      <c r="AC24" s="117"/>
       <c r="AD24" s="156"/>
     </row>
     <row r="25" spans="1:32" ht="15.75">
-      <c r="A25" s="125">
+      <c r="A25" s="105">
         <v>25</v>
       </c>
-      <c r="B25" s="126" t="s">
+      <c r="B25" s="106" t="s">
         <v>8</v>
       </c>
-      <c r="C25" s="127"/>
-      <c r="D25" s="127"/>
-      <c r="E25" s="127"/>
-      <c r="F25" s="127"/>
-      <c r="G25" s="127"/>
-      <c r="H25" s="127"/>
-      <c r="I25" s="127"/>
-      <c r="J25" s="127"/>
-      <c r="K25" s="127"/>
-      <c r="L25" s="127"/>
-      <c r="M25" s="127"/>
-      <c r="N25" s="127"/>
-      <c r="O25" s="127"/>
-      <c r="P25" s="127"/>
-      <c r="Q25" s="127"/>
-      <c r="R25" s="127"/>
-      <c r="S25" s="127"/>
-      <c r="T25" s="127"/>
-      <c r="U25" s="127"/>
-      <c r="V25" s="127"/>
-      <c r="W25" s="127"/>
-      <c r="X25" s="127"/>
-      <c r="Y25" s="127"/>
-      <c r="Z25" s="127"/>
-      <c r="AA25" s="128"/>
-      <c r="AB25" s="155">
+      <c r="C25" s="107"/>
+      <c r="D25" s="107"/>
+      <c r="E25" s="107"/>
+      <c r="F25" s="107"/>
+      <c r="G25" s="107"/>
+      <c r="H25" s="107"/>
+      <c r="I25" s="107"/>
+      <c r="J25" s="107"/>
+      <c r="K25" s="107"/>
+      <c r="L25" s="107"/>
+      <c r="M25" s="107"/>
+      <c r="N25" s="107"/>
+      <c r="O25" s="107"/>
+      <c r="P25" s="107"/>
+      <c r="Q25" s="107"/>
+      <c r="R25" s="107"/>
+      <c r="S25" s="107"/>
+      <c r="T25" s="107"/>
+      <c r="U25" s="107"/>
+      <c r="V25" s="107"/>
+      <c r="W25" s="107"/>
+      <c r="X25" s="107"/>
+      <c r="Y25" s="107"/>
+      <c r="Z25" s="107"/>
+      <c r="AA25" s="108"/>
+      <c r="AB25" s="128">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AC25" s="139"/>
+      <c r="AC25" s="117"/>
       <c r="AD25" s="156"/>
     </row>
     <row r="26" spans="1:32" ht="15.75">
-      <c r="A26" s="129">
+      <c r="A26" s="109">
         <v>26</v>
       </c>
-      <c r="B26" s="130" t="s">
+      <c r="B26" s="110" t="s">
         <v>2</v>
       </c>
-      <c r="C26" s="131"/>
-      <c r="D26" s="131"/>
-      <c r="E26" s="131"/>
-      <c r="F26" s="131"/>
-      <c r="G26" s="131"/>
-      <c r="H26" s="131"/>
-      <c r="I26" s="131"/>
-      <c r="J26" s="131"/>
-      <c r="K26" s="131"/>
-      <c r="L26" s="131"/>
-      <c r="M26" s="131"/>
-      <c r="N26" s="131"/>
-      <c r="O26" s="131"/>
-      <c r="P26" s="131"/>
-      <c r="Q26" s="131"/>
-      <c r="R26" s="131"/>
-      <c r="S26" s="131"/>
-      <c r="T26" s="131"/>
-      <c r="U26" s="131"/>
-      <c r="V26" s="131"/>
-      <c r="W26" s="131"/>
-      <c r="X26" s="131"/>
-      <c r="Y26" s="131"/>
-      <c r="Z26" s="131"/>
-      <c r="AA26" s="132"/>
-      <c r="AB26" s="155">
+      <c r="C26" s="111"/>
+      <c r="D26" s="111"/>
+      <c r="E26" s="111"/>
+      <c r="F26" s="111"/>
+      <c r="G26" s="111"/>
+      <c r="H26" s="111"/>
+      <c r="I26" s="111"/>
+      <c r="J26" s="111"/>
+      <c r="K26" s="111"/>
+      <c r="L26" s="111"/>
+      <c r="M26" s="111"/>
+      <c r="N26" s="111"/>
+      <c r="O26" s="111"/>
+      <c r="P26" s="111"/>
+      <c r="Q26" s="111"/>
+      <c r="R26" s="111"/>
+      <c r="S26" s="111"/>
+      <c r="T26" s="111"/>
+      <c r="U26" s="111"/>
+      <c r="V26" s="111"/>
+      <c r="W26" s="111"/>
+      <c r="X26" s="111"/>
+      <c r="Y26" s="111"/>
+      <c r="Z26" s="111"/>
+      <c r="AA26" s="112"/>
+      <c r="AB26" s="128">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AC26" s="140"/>
+      <c r="AC26" s="118"/>
       <c r="AD26" s="156"/>
     </row>
     <row r="27" spans="1:32" ht="15.75">
-      <c r="A27" s="125">
+      <c r="A27" s="105">
         <v>27</v>
       </c>
-      <c r="B27" s="126" t="s">
+      <c r="B27" s="106" t="s">
         <v>3</v>
       </c>
-      <c r="C27" s="127"/>
-      <c r="D27" s="127"/>
-      <c r="E27" s="127"/>
-      <c r="F27" s="127"/>
-      <c r="G27" s="127"/>
-      <c r="H27" s="127"/>
-      <c r="I27" s="127"/>
-      <c r="J27" s="127"/>
-      <c r="K27" s="127"/>
-      <c r="L27" s="127"/>
-      <c r="M27" s="127"/>
-      <c r="N27" s="127"/>
-      <c r="O27" s="127"/>
-      <c r="P27" s="127"/>
-      <c r="Q27" s="127"/>
-      <c r="R27" s="127"/>
-      <c r="S27" s="127"/>
-      <c r="T27" s="127"/>
-      <c r="U27" s="127"/>
-      <c r="V27" s="127"/>
-      <c r="W27" s="127"/>
-      <c r="X27" s="127"/>
-      <c r="Y27" s="127"/>
-      <c r="Z27" s="127"/>
-      <c r="AA27" s="128"/>
-      <c r="AB27" s="155">
+      <c r="C27" s="107"/>
+      <c r="D27" s="107"/>
+      <c r="E27" s="107"/>
+      <c r="F27" s="107"/>
+      <c r="G27" s="107"/>
+      <c r="H27" s="107"/>
+      <c r="I27" s="107"/>
+      <c r="J27" s="107"/>
+      <c r="K27" s="107"/>
+      <c r="L27" s="107"/>
+      <c r="M27" s="107"/>
+      <c r="N27" s="107"/>
+      <c r="O27" s="107"/>
+      <c r="P27" s="107"/>
+      <c r="Q27" s="107"/>
+      <c r="R27" s="107"/>
+      <c r="S27" s="107"/>
+      <c r="T27" s="107"/>
+      <c r="U27" s="107"/>
+      <c r="V27" s="107"/>
+      <c r="W27" s="107"/>
+      <c r="X27" s="107"/>
+      <c r="Y27" s="107"/>
+      <c r="Z27" s="107"/>
+      <c r="AA27" s="108"/>
+      <c r="AB27" s="128">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AC27" s="139"/>
+      <c r="AC27" s="117"/>
       <c r="AD27" s="156"/>
     </row>
     <row r="28" spans="1:32" ht="15.75">
-      <c r="A28" s="129">
+      <c r="A28" s="109">
         <v>28</v>
       </c>
-      <c r="B28" s="130" t="s">
+      <c r="B28" s="110" t="s">
         <v>4</v>
       </c>
-      <c r="C28" s="131"/>
-      <c r="D28" s="131"/>
-      <c r="E28" s="131"/>
-      <c r="F28" s="131"/>
-      <c r="G28" s="131"/>
-      <c r="H28" s="131"/>
-      <c r="I28" s="131"/>
-      <c r="J28" s="131"/>
-      <c r="K28" s="131"/>
-      <c r="L28" s="131"/>
-      <c r="M28" s="131"/>
-      <c r="N28" s="131"/>
-      <c r="O28" s="131"/>
-      <c r="P28" s="131"/>
-      <c r="Q28" s="131"/>
-      <c r="R28" s="131"/>
-      <c r="S28" s="131"/>
-      <c r="T28" s="131"/>
-      <c r="U28" s="131"/>
-      <c r="V28" s="131"/>
-      <c r="W28" s="131"/>
-      <c r="X28" s="131"/>
-      <c r="Y28" s="131"/>
-      <c r="Z28" s="131"/>
-      <c r="AA28" s="132"/>
-      <c r="AB28" s="155">
+      <c r="C28" s="111"/>
+      <c r="D28" s="111"/>
+      <c r="E28" s="111"/>
+      <c r="F28" s="111"/>
+      <c r="G28" s="111"/>
+      <c r="H28" s="111"/>
+      <c r="I28" s="111"/>
+      <c r="J28" s="111"/>
+      <c r="K28" s="111"/>
+      <c r="L28" s="111"/>
+      <c r="M28" s="111"/>
+      <c r="N28" s="111"/>
+      <c r="O28" s="111"/>
+      <c r="P28" s="111"/>
+      <c r="Q28" s="111"/>
+      <c r="R28" s="111"/>
+      <c r="S28" s="111"/>
+      <c r="T28" s="111"/>
+      <c r="U28" s="111"/>
+      <c r="V28" s="111"/>
+      <c r="W28" s="111"/>
+      <c r="X28" s="111"/>
+      <c r="Y28" s="111"/>
+      <c r="Z28" s="111"/>
+      <c r="AA28" s="112"/>
+      <c r="AB28" s="128">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AC28" s="139"/>
+      <c r="AC28" s="117"/>
       <c r="AD28" s="156"/>
     </row>
     <row r="29" spans="1:32" ht="15.75">
-      <c r="A29" s="125">
+      <c r="A29" s="105">
         <v>29</v>
       </c>
-      <c r="B29" s="126" t="s">
+      <c r="B29" s="106" t="s">
         <v>5</v>
       </c>
-      <c r="C29" s="127"/>
-      <c r="D29" s="127"/>
-      <c r="E29" s="127"/>
-      <c r="F29" s="127"/>
-      <c r="G29" s="127"/>
-      <c r="H29" s="127"/>
-      <c r="I29" s="127"/>
-      <c r="J29" s="127"/>
-      <c r="K29" s="127"/>
-      <c r="L29" s="127"/>
-      <c r="M29" s="127"/>
-      <c r="N29" s="127"/>
-      <c r="O29" s="127"/>
-      <c r="P29" s="127"/>
-      <c r="Q29" s="127"/>
-      <c r="R29" s="127"/>
-      <c r="S29" s="127"/>
-      <c r="T29" s="127"/>
-      <c r="U29" s="127"/>
-      <c r="V29" s="127"/>
-      <c r="W29" s="127"/>
-      <c r="X29" s="127"/>
-      <c r="Y29" s="127"/>
-      <c r="Z29" s="127"/>
-      <c r="AA29" s="128"/>
-      <c r="AB29" s="155">
+      <c r="C29" s="107"/>
+      <c r="D29" s="107"/>
+      <c r="E29" s="107"/>
+      <c r="F29" s="107"/>
+      <c r="G29" s="107"/>
+      <c r="H29" s="107"/>
+      <c r="I29" s="107"/>
+      <c r="J29" s="107"/>
+      <c r="K29" s="107"/>
+      <c r="L29" s="107"/>
+      <c r="M29" s="107"/>
+      <c r="N29" s="107"/>
+      <c r="O29" s="107"/>
+      <c r="P29" s="107"/>
+      <c r="Q29" s="107"/>
+      <c r="R29" s="107"/>
+      <c r="S29" s="107"/>
+      <c r="T29" s="107"/>
+      <c r="U29" s="107"/>
+      <c r="V29" s="107"/>
+      <c r="W29" s="107"/>
+      <c r="X29" s="107"/>
+      <c r="Y29" s="107"/>
+      <c r="Z29" s="107"/>
+      <c r="AA29" s="108"/>
+      <c r="AB29" s="128">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AC29" s="139"/>
+      <c r="AC29" s="117"/>
       <c r="AD29" s="156"/>
     </row>
     <row r="30" spans="1:32" ht="15.75">
-      <c r="A30" s="129">
+      <c r="A30" s="109">
         <v>30</v>
       </c>
-      <c r="B30" s="130" t="s">
+      <c r="B30" s="110" t="s">
         <v>6</v>
       </c>
-      <c r="C30" s="131"/>
-      <c r="D30" s="131"/>
-      <c r="E30" s="131"/>
-      <c r="F30" s="131"/>
-      <c r="G30" s="131"/>
-      <c r="H30" s="131"/>
-      <c r="I30" s="131"/>
-      <c r="J30" s="131"/>
-      <c r="K30" s="131"/>
-      <c r="L30" s="131"/>
-      <c r="M30" s="131"/>
-      <c r="N30" s="131"/>
-      <c r="O30" s="131"/>
-      <c r="P30" s="131"/>
-      <c r="Q30" s="131"/>
-      <c r="R30" s="131"/>
-      <c r="S30" s="131"/>
-      <c r="T30" s="131"/>
-      <c r="U30" s="131"/>
-      <c r="V30" s="131"/>
-      <c r="W30" s="131"/>
-      <c r="X30" s="131"/>
-      <c r="Y30" s="131"/>
-      <c r="Z30" s="131"/>
-      <c r="AA30" s="132"/>
-      <c r="AB30" s="155">
+      <c r="C30" s="111"/>
+      <c r="D30" s="111"/>
+      <c r="E30" s="111"/>
+      <c r="F30" s="111"/>
+      <c r="G30" s="111"/>
+      <c r="H30" s="111"/>
+      <c r="I30" s="111"/>
+      <c r="J30" s="111"/>
+      <c r="K30" s="111"/>
+      <c r="L30" s="111"/>
+      <c r="M30" s="111"/>
+      <c r="N30" s="111"/>
+      <c r="O30" s="111"/>
+      <c r="P30" s="111"/>
+      <c r="Q30" s="111"/>
+      <c r="R30" s="111"/>
+      <c r="S30" s="111"/>
+      <c r="T30" s="111"/>
+      <c r="U30" s="111"/>
+      <c r="V30" s="111"/>
+      <c r="W30" s="111"/>
+      <c r="X30" s="111"/>
+      <c r="Y30" s="111"/>
+      <c r="Z30" s="111"/>
+      <c r="AA30" s="112"/>
+      <c r="AB30" s="128">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AC30" s="139"/>
+      <c r="AC30" s="117"/>
       <c r="AD30" s="156"/>
     </row>
     <row r="31" spans="1:32" ht="15.75">
-      <c r="A31" s="125">
+      <c r="A31" s="105">
         <v>31</v>
       </c>
-      <c r="B31" s="126" t="s">
+      <c r="B31" s="106" t="s">
         <v>7</v>
       </c>
-      <c r="C31" s="127"/>
-      <c r="D31" s="127"/>
-      <c r="E31" s="127"/>
-      <c r="F31" s="127"/>
-      <c r="G31" s="127"/>
-      <c r="H31" s="127"/>
-      <c r="I31" s="127"/>
-      <c r="J31" s="127"/>
-      <c r="K31" s="127"/>
-      <c r="L31" s="127"/>
-      <c r="M31" s="127"/>
-      <c r="N31" s="127"/>
-      <c r="O31" s="127"/>
-      <c r="P31" s="127"/>
-      <c r="Q31" s="127"/>
-      <c r="R31" s="127"/>
-      <c r="S31" s="127"/>
-      <c r="T31" s="127"/>
-      <c r="U31" s="127"/>
-      <c r="V31" s="127"/>
-      <c r="W31" s="127"/>
-      <c r="X31" s="127"/>
-      <c r="Y31" s="127"/>
-      <c r="Z31" s="127"/>
-      <c r="AA31" s="128"/>
-      <c r="AB31" s="155">
+      <c r="C31" s="107"/>
+      <c r="D31" s="107"/>
+      <c r="E31" s="107"/>
+      <c r="F31" s="107"/>
+      <c r="G31" s="107"/>
+      <c r="H31" s="107"/>
+      <c r="I31" s="107"/>
+      <c r="J31" s="107"/>
+      <c r="K31" s="107"/>
+      <c r="L31" s="107"/>
+      <c r="M31" s="107"/>
+      <c r="N31" s="107"/>
+      <c r="O31" s="107"/>
+      <c r="P31" s="107"/>
+      <c r="Q31" s="107"/>
+      <c r="R31" s="107"/>
+      <c r="S31" s="107"/>
+      <c r="T31" s="107"/>
+      <c r="U31" s="107"/>
+      <c r="V31" s="107"/>
+      <c r="W31" s="107"/>
+      <c r="X31" s="107"/>
+      <c r="Y31" s="107"/>
+      <c r="Z31" s="107"/>
+      <c r="AA31" s="108"/>
+      <c r="AB31" s="128">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AC31" s="139"/>
+      <c r="AC31" s="117"/>
       <c r="AD31" s="156"/>
     </row>
     <row r="32" spans="1:32" ht="15.75">
-      <c r="A32" s="129">
+      <c r="A32" s="109">
         <v>1</v>
       </c>
-      <c r="B32" s="130" t="s">
+      <c r="B32" s="110" t="s">
         <v>8</v>
       </c>
-      <c r="C32" s="131"/>
-      <c r="D32" s="131"/>
-      <c r="E32" s="131"/>
-      <c r="F32" s="131"/>
-      <c r="G32" s="131"/>
-      <c r="H32" s="131"/>
-      <c r="I32" s="131"/>
-      <c r="J32" s="131"/>
-      <c r="K32" s="131"/>
-      <c r="L32" s="131"/>
-      <c r="M32" s="131"/>
-      <c r="N32" s="131"/>
-      <c r="O32" s="131"/>
-      <c r="P32" s="131"/>
-      <c r="Q32" s="131"/>
-      <c r="R32" s="131"/>
-      <c r="S32" s="131"/>
-      <c r="T32" s="131"/>
-      <c r="U32" s="131"/>
-      <c r="V32" s="131"/>
-      <c r="W32" s="131"/>
-      <c r="X32" s="131"/>
-      <c r="Y32" s="131"/>
-      <c r="Z32" s="131"/>
-      <c r="AA32" s="132"/>
-      <c r="AB32" s="155">
+      <c r="C32" s="111"/>
+      <c r="D32" s="111"/>
+      <c r="E32" s="111"/>
+      <c r="F32" s="111"/>
+      <c r="G32" s="111"/>
+      <c r="H32" s="111"/>
+      <c r="I32" s="111"/>
+      <c r="J32" s="111"/>
+      <c r="K32" s="111"/>
+      <c r="L32" s="111"/>
+      <c r="M32" s="111"/>
+      <c r="N32" s="111"/>
+      <c r="O32" s="111"/>
+      <c r="P32" s="111"/>
+      <c r="Q32" s="111"/>
+      <c r="R32" s="111"/>
+      <c r="S32" s="111"/>
+      <c r="T32" s="111"/>
+      <c r="U32" s="111"/>
+      <c r="V32" s="111"/>
+      <c r="W32" s="111"/>
+      <c r="X32" s="111"/>
+      <c r="Y32" s="111"/>
+      <c r="Z32" s="111"/>
+      <c r="AA32" s="112"/>
+      <c r="AB32" s="128">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AC32" s="139"/>
+      <c r="AC32" s="117"/>
       <c r="AD32" s="156"/>
     </row>
     <row r="33" spans="1:30" ht="15.75">
-      <c r="A33" s="125">
+      <c r="A33" s="105">
         <v>2</v>
       </c>
-      <c r="B33" s="126" t="s">
+      <c r="B33" s="106" t="s">
         <v>2</v>
       </c>
-      <c r="C33" s="127"/>
-      <c r="D33" s="127"/>
-      <c r="E33" s="127"/>
-      <c r="F33" s="127"/>
-      <c r="G33" s="127"/>
-      <c r="H33" s="127"/>
-      <c r="I33" s="127"/>
-      <c r="J33" s="127"/>
-      <c r="K33" s="127"/>
-      <c r="L33" s="127"/>
-      <c r="M33" s="127"/>
-      <c r="N33" s="127"/>
-      <c r="O33" s="127"/>
-      <c r="P33" s="127"/>
-      <c r="Q33" s="127"/>
-      <c r="R33" s="127"/>
-      <c r="S33" s="127"/>
-      <c r="T33" s="127"/>
-      <c r="U33" s="127"/>
-      <c r="V33" s="127"/>
-      <c r="W33" s="127"/>
-      <c r="X33" s="127"/>
-      <c r="Y33" s="127"/>
-      <c r="Z33" s="127"/>
-      <c r="AA33" s="128"/>
-      <c r="AB33" s="155">
+      <c r="C33" s="107"/>
+      <c r="D33" s="107"/>
+      <c r="E33" s="107"/>
+      <c r="F33" s="107"/>
+      <c r="G33" s="107"/>
+      <c r="H33" s="107"/>
+      <c r="I33" s="107"/>
+      <c r="J33" s="107"/>
+      <c r="K33" s="107"/>
+      <c r="L33" s="107"/>
+      <c r="M33" s="107"/>
+      <c r="N33" s="107"/>
+      <c r="O33" s="107"/>
+      <c r="P33" s="107"/>
+      <c r="Q33" s="107"/>
+      <c r="R33" s="107"/>
+      <c r="S33" s="107"/>
+      <c r="T33" s="107"/>
+      <c r="U33" s="107"/>
+      <c r="V33" s="107"/>
+      <c r="W33" s="107"/>
+      <c r="X33" s="107"/>
+      <c r="Y33" s="107"/>
+      <c r="Z33" s="107"/>
+      <c r="AA33" s="108"/>
+      <c r="AB33" s="128">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AC33" s="139"/>
+      <c r="AC33" s="117"/>
       <c r="AD33" s="156"/>
     </row>
     <row r="34" spans="1:30" ht="15.75">
-      <c r="A34" s="129">
+      <c r="A34" s="109">
         <v>3</v>
       </c>
-      <c r="B34" s="130" t="s">
+      <c r="B34" s="110" t="s">
         <v>3</v>
       </c>
-      <c r="C34" s="131"/>
-      <c r="D34" s="131"/>
-      <c r="E34" s="131"/>
-      <c r="F34" s="131"/>
-      <c r="G34" s="131"/>
-      <c r="H34" s="131"/>
-      <c r="I34" s="131"/>
-      <c r="J34" s="131"/>
-      <c r="K34" s="131"/>
-      <c r="L34" s="131"/>
-      <c r="M34" s="131"/>
-      <c r="N34" s="131"/>
-      <c r="O34" s="131"/>
-      <c r="P34" s="131"/>
-      <c r="Q34" s="131"/>
-      <c r="R34" s="131"/>
-      <c r="S34" s="131"/>
-      <c r="T34" s="131"/>
-      <c r="U34" s="131"/>
-      <c r="V34" s="131"/>
-      <c r="W34" s="131"/>
-      <c r="X34" s="131"/>
-      <c r="Y34" s="131"/>
-      <c r="Z34" s="131"/>
-      <c r="AA34" s="132"/>
-      <c r="AB34" s="155">
+      <c r="C34" s="111"/>
+      <c r="D34" s="111"/>
+      <c r="E34" s="111"/>
+      <c r="F34" s="111"/>
+      <c r="G34" s="111"/>
+      <c r="H34" s="111"/>
+      <c r="I34" s="111"/>
+      <c r="J34" s="111"/>
+      <c r="K34" s="111"/>
+      <c r="L34" s="111"/>
+      <c r="M34" s="111"/>
+      <c r="N34" s="111"/>
+      <c r="O34" s="111"/>
+      <c r="P34" s="111"/>
+      <c r="Q34" s="111"/>
+      <c r="R34" s="111"/>
+      <c r="S34" s="111"/>
+      <c r="T34" s="111"/>
+      <c r="U34" s="111"/>
+      <c r="V34" s="111"/>
+      <c r="W34" s="111"/>
+      <c r="X34" s="111"/>
+      <c r="Y34" s="111"/>
+      <c r="Z34" s="111"/>
+      <c r="AA34" s="112"/>
+      <c r="AB34" s="128">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AC34" s="139"/>
+      <c r="AC34" s="117"/>
       <c r="AD34" s="156"/>
     </row>
     <row r="35" spans="1:30" ht="15.75">
-      <c r="A35" s="125">
+      <c r="A35" s="105">
         <v>4</v>
       </c>
-      <c r="B35" s="126" t="s">
+      <c r="B35" s="106" t="s">
         <v>4</v>
       </c>
-      <c r="C35" s="127"/>
-      <c r="D35" s="127"/>
-      <c r="E35" s="127"/>
-      <c r="F35" s="127"/>
-      <c r="G35" s="127"/>
-      <c r="H35" s="127"/>
-      <c r="I35" s="127"/>
-      <c r="J35" s="127"/>
-      <c r="K35" s="127"/>
-      <c r="L35" s="127"/>
-      <c r="M35" s="127"/>
-      <c r="N35" s="127"/>
-      <c r="O35" s="127"/>
-      <c r="P35" s="127"/>
-      <c r="Q35" s="127"/>
-      <c r="R35" s="127"/>
-      <c r="S35" s="127"/>
-      <c r="T35" s="127"/>
-      <c r="U35" s="127"/>
-      <c r="V35" s="127"/>
-      <c r="W35" s="127"/>
-      <c r="X35" s="127"/>
-      <c r="Y35" s="127"/>
-      <c r="Z35" s="127"/>
-      <c r="AA35" s="128"/>
-      <c r="AB35" s="155">
+      <c r="C35" s="107"/>
+      <c r="D35" s="107"/>
+      <c r="E35" s="107"/>
+      <c r="F35" s="107"/>
+      <c r="G35" s="107"/>
+      <c r="H35" s="107"/>
+      <c r="I35" s="107"/>
+      <c r="J35" s="107"/>
+      <c r="K35" s="107"/>
+      <c r="L35" s="107"/>
+      <c r="M35" s="107"/>
+      <c r="N35" s="107"/>
+      <c r="O35" s="107"/>
+      <c r="P35" s="107"/>
+      <c r="Q35" s="107"/>
+      <c r="R35" s="107"/>
+      <c r="S35" s="107"/>
+      <c r="T35" s="107"/>
+      <c r="U35" s="107"/>
+      <c r="V35" s="107"/>
+      <c r="W35" s="107"/>
+      <c r="X35" s="107"/>
+      <c r="Y35" s="107"/>
+      <c r="Z35" s="107"/>
+      <c r="AA35" s="108"/>
+      <c r="AB35" s="128">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AC35" s="139"/>
+      <c r="AC35" s="117"/>
       <c r="AD35" s="156"/>
     </row>
     <row r="36" spans="1:30" ht="14.25" customHeight="1">
-      <c r="A36" s="136" t="s">
+      <c r="A36" s="157" t="s">
         <v>36</v>
       </c>
-      <c r="B36" s="136"/>
-      <c r="C36" s="133">
+      <c r="B36" s="157"/>
+      <c r="C36" s="113">
         <f>SUM(C20:C35)</f>
         <v>0</v>
       </c>
-      <c r="D36" s="133">
+      <c r="D36" s="113">
         <f t="shared" ref="D36:K36" si="3">SUM(D20:D35)</f>
         <v>0</v>
       </c>
-      <c r="E36" s="133">
+      <c r="E36" s="113">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F36" s="133">
+      <c r="F36" s="113">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G36" s="133">
+      <c r="G36" s="113">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="H36" s="133">
+      <c r="H36" s="113">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I36" s="133">
+      <c r="I36" s="113">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J36" s="133">
+      <c r="J36" s="113">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K36" s="133">
+      <c r="K36" s="113">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L36" s="134">
+      <c r="L36" s="114">
         <f>SUM(L20:L35)</f>
         <v>0</v>
       </c>
-      <c r="M36" s="134">
+      <c r="M36" s="114">
         <f t="shared" ref="M36:Q36" si="4">SUM(M20:M35)</f>
         <v>0</v>
       </c>
-      <c r="N36" s="134">
+      <c r="N36" s="114">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="O36" s="134">
+      <c r="O36" s="114">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="P36" s="134">
+      <c r="P36" s="114">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="Q36" s="134">
+      <c r="Q36" s="114">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="R36" s="135">
+      <c r="R36" s="115">
         <f>SUM(R20:R35)</f>
         <v>0</v>
       </c>
-      <c r="S36" s="135">
+      <c r="S36" s="115">
         <f t="shared" ref="S36:AA36" si="5">SUM(S20:S35)</f>
         <v>0</v>
       </c>
-      <c r="T36" s="135">
+      <c r="T36" s="115">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="U36" s="135">
+      <c r="U36" s="115">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="V36" s="135">
+      <c r="V36" s="115">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="W36" s="135">
+      <c r="W36" s="115">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="X36" s="135">
+      <c r="X36" s="115">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="Y36" s="135">
+      <c r="Y36" s="115">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="Z36" s="135">
+      <c r="Z36" s="115">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AA36" s="151">
+      <c r="AA36" s="124">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AB36" s="157">
+      <c r="AB36" s="129">
         <f>SUM(AB20:AB35)</f>
         <v>0</v>
       </c>
-      <c r="AC36" s="158">
+      <c r="AC36" s="130">
         <f>SUM(AC20:AC35)</f>
         <v>0</v>
       </c>
-      <c r="AD36" s="161">
+      <c r="AD36" s="133">
         <f>AC36-AB36</f>
         <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:30" ht="31.5" customHeight="1">
-      <c r="A37" s="137" t="s">
+      <c r="A37" s="154" t="s">
         <v>37</v>
       </c>
-      <c r="B37" s="137"/>
-      <c r="C37" s="138">
+      <c r="B37" s="154"/>
+      <c r="C37" s="116">
         <f>SUM(C19,C36)</f>
         <v>429.95</v>
       </c>
-      <c r="D37" s="138"/>
-      <c r="E37" s="138"/>
-      <c r="F37" s="138">
+      <c r="D37" s="116"/>
+      <c r="E37" s="116"/>
+      <c r="F37" s="116">
         <f t="shared" ref="F37:AB37" si="6">SUM(F19,F36)</f>
         <v>1812</v>
       </c>
-      <c r="G37" s="138"/>
-      <c r="H37" s="138">
+      <c r="G37" s="116"/>
+      <c r="H37" s="116">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="I37" s="138">
+      <c r="I37" s="116">
         <f t="shared" si="6"/>
         <v>7935</v>
       </c>
-      <c r="J37" s="138">
+      <c r="J37" s="116">
         <f t="shared" si="6"/>
         <v>3102</v>
       </c>
-      <c r="K37" s="138">
+      <c r="K37" s="116">
         <f t="shared" si="6"/>
         <v>1860</v>
       </c>
-      <c r="L37" s="138">
+      <c r="L37" s="116">
         <f t="shared" si="6"/>
         <v>10858.130000000001</v>
       </c>
-      <c r="M37" s="138">
+      <c r="M37" s="116">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="N37" s="138">
+      <c r="N37" s="116">
         <f t="shared" si="6"/>
-        <v>700</v>
-      </c>
-      <c r="O37" s="138"/>
-      <c r="P37" s="138"/>
-      <c r="Q37" s="138"/>
-      <c r="R37" s="138">
+        <v>1690</v>
+      </c>
+      <c r="O37" s="116"/>
+      <c r="P37" s="116"/>
+      <c r="Q37" s="116"/>
+      <c r="R37" s="116">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="S37" s="138"/>
-      <c r="T37" s="138">
+      <c r="S37" s="116"/>
+      <c r="T37" s="116">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="U37" s="138">
+      <c r="U37" s="116">
         <f t="shared" si="6"/>
-        <v>714</v>
-      </c>
-      <c r="V37" s="138">
+        <v>921</v>
+      </c>
+      <c r="V37" s="116">
         <f t="shared" si="6"/>
         <v>158.61000000000001</v>
       </c>
-      <c r="W37" s="138">
+      <c r="W37" s="116">
         <f t="shared" si="6"/>
-        <v>9624.98</v>
-      </c>
-      <c r="X37" s="138">
+        <v>10804.98</v>
+      </c>
+      <c r="X37" s="116">
         <f t="shared" si="6"/>
         <v>1237</v>
       </c>
-      <c r="Y37" s="138">
+      <c r="Y37" s="116">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="Z37" s="138">
+      <c r="Z37" s="116">
         <f>SUM(Z19,Z36)</f>
         <v>2626</v>
       </c>
-      <c r="AA37" s="152">
+      <c r="AA37" s="125">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AB37" s="159">
+      <c r="AB37" s="131">
         <f t="shared" si="6"/>
-        <v>60088.67</v>
-      </c>
-      <c r="AC37" s="160">
+        <v>62965.67</v>
+      </c>
+      <c r="AC37" s="132">
         <f>SUM(AC19,AC36)</f>
         <v>96705.110000000015</v>
       </c>
-      <c r="AD37" s="162">
+      <c r="AD37" s="134">
         <f>SUM(AD19,AD36)</f>
-        <v>36616.440000000017</v>
+        <v>33739.440000000017</v>
       </c>
     </row>
     <row r="41" spans="1:30">
@@ -18769,10 +18998,10 @@
     <mergeCell ref="A2:B2"/>
   </mergeCells>
   <conditionalFormatting sqref="AD19:AD20 AD36:AD37">
-    <cfRule type="expression" dxfId="1" priority="1">
+    <cfRule type="expression" dxfId="3" priority="1">
       <formula>AD19&lt;0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="2">
+    <cfRule type="expression" dxfId="2" priority="2">
       <formula>AD19&gt;0</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Другое/2026/Доходы-Расходы_copy.xlsx
+++ b/Другое/2026/Доходы-Расходы_copy.xlsx
@@ -1,8 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="6" rupBuild="4507"/>
-  <workbookPr filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="7"/>
   </bookViews>
@@ -16,9 +16,9 @@
     <sheet name="Июль 2026" sheetId="8" r:id="rId7"/>
     <sheet name="Август 2026" sheetId="9" r:id="rId8"/>
   </sheets>
-  <calcPr calcId="125725"/>
-  <extLst xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main">
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+  <calcPr calcId="162913"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
@@ -31,7 +31,7 @@
     <author>Автор</author>
   </authors>
   <commentList>
-    <comment ref="S3" authorId="0">
+    <comment ref="S3" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -58,7 +58,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P11" authorId="0">
+    <comment ref="P11" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -85,7 +85,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R16" authorId="0">
+    <comment ref="R16" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -112,7 +112,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P20" authorId="0">
+    <comment ref="P20" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -138,7 +138,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P24" authorId="0">
+    <comment ref="P24" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -164,7 +164,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H25" authorId="0">
+    <comment ref="H25" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -191,7 +191,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J25" authorId="0">
+    <comment ref="J25" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -217,7 +217,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J26" authorId="0">
+    <comment ref="J26" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -243,7 +243,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L26" authorId="0">
+    <comment ref="L26" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -269,7 +269,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P26" authorId="0">
+    <comment ref="P26" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -295,7 +295,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J27" authorId="0">
+    <comment ref="J27" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -331,7 +331,7 @@
     <author>Автор</author>
   </authors>
   <commentList>
-    <comment ref="R3" authorId="0">
+    <comment ref="R3" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -357,7 +357,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F4" authorId="0">
+    <comment ref="F4" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -383,7 +383,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R4" authorId="0">
+    <comment ref="R4" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -410,7 +410,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S4" authorId="0">
+    <comment ref="S4" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -436,7 +436,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T4" authorId="0">
+    <comment ref="T4" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -462,7 +462,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G5" authorId="0">
+    <comment ref="G5" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -488,7 +488,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P5" authorId="0">
+    <comment ref="P5" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -514,7 +514,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P6" authorId="0">
+    <comment ref="P6" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -541,7 +541,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S10" authorId="0">
+    <comment ref="S10" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -567,7 +567,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A11" authorId="0">
+    <comment ref="A11" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -593,7 +593,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R18" authorId="0">
+    <comment ref="R18" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -620,7 +620,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S18" authorId="0">
+    <comment ref="S18" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -646,7 +646,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R19" authorId="0">
+    <comment ref="R19" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -673,7 +673,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S19" authorId="0">
+    <comment ref="S19" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -699,7 +699,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S20" authorId="0">
+    <comment ref="S20" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -725,7 +725,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T20" authorId="0">
+    <comment ref="T20" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -751,7 +751,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S22" authorId="0">
+    <comment ref="S22" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -777,7 +777,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S26" authorId="0">
+    <comment ref="S26" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -813,7 +813,7 @@
     <author>Автор</author>
   </authors>
   <commentList>
-    <comment ref="Q3" authorId="0">
+    <comment ref="Q3" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -829,7 +829,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S3" authorId="0">
+    <comment ref="S3" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -856,7 +856,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T3" authorId="0">
+    <comment ref="T3" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -883,7 +883,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="U3" authorId="0">
+    <comment ref="U3" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -909,7 +909,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H4" authorId="0">
+    <comment ref="H4" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -935,7 +935,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K4" authorId="0">
+    <comment ref="K4" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -961,7 +961,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N4" authorId="0">
+    <comment ref="N4" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -987,7 +987,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q4" authorId="0">
+    <comment ref="Q4" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1014,7 +1014,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S4" authorId="0">
+    <comment ref="S4" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1041,7 +1041,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="U4" authorId="0">
+    <comment ref="U4" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1068,7 +1068,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V4" authorId="0">
+    <comment ref="V4" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1094,7 +1094,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I5" authorId="0">
+    <comment ref="I5" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1121,7 +1121,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S5" authorId="0">
+    <comment ref="S5" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1147,7 +1147,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K6" authorId="0">
+    <comment ref="K6" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1174,7 +1174,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S6" authorId="0">
+    <comment ref="S6" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1201,7 +1201,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H8" authorId="0">
+    <comment ref="H8" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1217,7 +1217,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E10" authorId="0">
+    <comment ref="E10" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1244,7 +1244,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X11" authorId="0">
+    <comment ref="X11" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1271,7 +1271,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X12" authorId="0">
+    <comment ref="X12" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1297,7 +1297,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H14" authorId="0">
+    <comment ref="H14" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1324,7 +1324,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H15" authorId="0">
+    <comment ref="H15" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1340,7 +1340,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T15" authorId="0">
+    <comment ref="T15" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1355,7 +1355,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E17" authorId="0">
+    <comment ref="E17" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1381,7 +1381,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q17" authorId="0">
+    <comment ref="Q17" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1407,7 +1407,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S19" authorId="0">
+    <comment ref="S19" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1433,7 +1433,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S21" authorId="0">
+    <comment ref="S21" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1460,7 +1460,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T21" authorId="0">
+    <comment ref="T21" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1486,7 +1486,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F22" authorId="0">
+    <comment ref="F22" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1512,7 +1512,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H22" authorId="0">
+    <comment ref="H22" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1538,7 +1538,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T22" authorId="0">
+    <comment ref="T22" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1564,7 +1564,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E24" authorId="0">
+    <comment ref="E24" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1591,7 +1591,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F25" authorId="0">
+    <comment ref="F25" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1618,7 +1618,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E27" authorId="0">
+    <comment ref="E27" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1645,7 +1645,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H29" authorId="0">
+    <comment ref="H29" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1671,7 +1671,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S29" authorId="0">
+    <comment ref="S29" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1697,7 +1697,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F30" authorId="0">
+    <comment ref="F30" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1723,7 +1723,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X30" authorId="0">
+    <comment ref="X30" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1749,7 +1749,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H31" authorId="0">
+    <comment ref="H31" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1775,7 +1775,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S33" authorId="0">
+    <comment ref="S33" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1801,7 +1801,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X35" authorId="0">
+    <comment ref="X35" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1837,7 +1837,7 @@
     <author>Автор</author>
   </authors>
   <commentList>
-    <comment ref="S3" authorId="0">
+    <comment ref="S3" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1863,7 +1863,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T3" authorId="0">
+    <comment ref="T3" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1890,7 +1890,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H4" authorId="0">
+    <comment ref="H4" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1916,7 +1916,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F5" authorId="0">
+    <comment ref="F5" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1942,7 +1942,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S5" authorId="0">
+    <comment ref="S5" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1968,7 +1968,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H6" authorId="0">
+    <comment ref="H6" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1994,7 +1994,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K7" authorId="0">
+    <comment ref="K7" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -2020,7 +2020,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X7" authorId="0">
+    <comment ref="X7" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -2046,7 +2046,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K8" authorId="0">
+    <comment ref="K8" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -2072,7 +2072,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K9" authorId="0">
+    <comment ref="K9" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -2098,7 +2098,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F10" authorId="0">
+    <comment ref="F10" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -2125,7 +2125,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H11" authorId="0">
+    <comment ref="H11" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -2151,7 +2151,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H13" authorId="0">
+    <comment ref="H13" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -2178,7 +2178,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q19" authorId="0">
+    <comment ref="Q19" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -2204,7 +2204,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S19" authorId="0">
+    <comment ref="S19" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -2230,7 +2230,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T20" authorId="0">
+    <comment ref="T20" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -2257,7 +2257,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H21" authorId="0">
+    <comment ref="H21" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -2283,7 +2283,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T21" authorId="0">
+    <comment ref="T21" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -2310,7 +2310,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X21" authorId="0">
+    <comment ref="X21" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -2336,7 +2336,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J24" authorId="0">
+    <comment ref="J24" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -2362,7 +2362,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S24" authorId="0">
+    <comment ref="S24" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -2388,7 +2388,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V25" authorId="0">
+    <comment ref="V25" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -2414,7 +2414,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H27" authorId="0">
+    <comment ref="H27" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -2440,7 +2440,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S27" authorId="0">
+    <comment ref="S27" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -2466,7 +2466,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H28" authorId="0">
+    <comment ref="H28" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -2492,7 +2492,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V28" authorId="0">
+    <comment ref="V28" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -2519,7 +2519,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X28" authorId="0">
+    <comment ref="X28" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -2545,7 +2545,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E29" authorId="0">
+    <comment ref="E29" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -2571,7 +2571,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X29" authorId="0">
+    <comment ref="X29" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -2597,7 +2597,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S31" authorId="0">
+    <comment ref="S31" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -2623,7 +2623,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S33" authorId="0">
+    <comment ref="S33" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -2649,7 +2649,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X34" authorId="0">
+    <comment ref="X34" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -2686,7 +2686,7 @@
     <author>Автор</author>
   </authors>
   <commentList>
-    <comment ref="F3" authorId="0">
+    <comment ref="F3" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -2712,7 +2712,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H3" authorId="0">
+    <comment ref="H3" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -2738,7 +2738,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S3" authorId="0">
+    <comment ref="S3" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -2764,7 +2764,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T3" authorId="0">
+    <comment ref="T3" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -2790,7 +2790,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V3" authorId="0">
+    <comment ref="V3" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -2816,7 +2816,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H4" authorId="0">
+    <comment ref="H4" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -2842,7 +2842,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N4" authorId="0">
+    <comment ref="N4" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -2868,7 +2868,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q4" authorId="0">
+    <comment ref="Q4" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -2894,7 +2894,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S4" authorId="0">
+    <comment ref="S4" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -2920,7 +2920,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H5" authorId="0">
+    <comment ref="H5" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -2946,7 +2946,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T5" authorId="0">
+    <comment ref="T5" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -2972,7 +2972,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F6" authorId="0">
+    <comment ref="F6" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -2998,7 +2998,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H6" authorId="0">
+    <comment ref="H6" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -3024,7 +3024,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T6" authorId="0">
+    <comment ref="T6" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -3050,7 +3050,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q7" authorId="0">
+    <comment ref="Q7" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -3076,7 +3076,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F8" authorId="0">
+    <comment ref="F8" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -3102,7 +3102,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q8" authorId="0">
+    <comment ref="Q8" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -3128,7 +3128,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S8" authorId="0">
+    <comment ref="S8" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -3154,7 +3154,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q9" authorId="0">
+    <comment ref="Q9" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -3180,7 +3180,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X9" authorId="0">
+    <comment ref="X9" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -3206,7 +3206,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E10" authorId="0">
+    <comment ref="E10" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -3232,7 +3232,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E11" authorId="0">
+    <comment ref="E11" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -3258,7 +3258,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I11" authorId="0">
+    <comment ref="I11" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -3284,7 +3284,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q12" authorId="0">
+    <comment ref="Q12" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -3311,7 +3311,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q13" authorId="0">
+    <comment ref="Q13" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -3337,7 +3337,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S13" authorId="0">
+    <comment ref="S13" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -3363,7 +3363,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X14" authorId="0">
+    <comment ref="X14" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -3389,7 +3389,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X16" authorId="0">
+    <comment ref="X16" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -3415,7 +3415,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H17" authorId="0">
+    <comment ref="H17" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -3442,7 +3442,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S17" authorId="0">
+    <comment ref="S17" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -3468,7 +3468,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T17" authorId="0">
+    <comment ref="T17" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -3494,7 +3494,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H19" authorId="0">
+    <comment ref="H19" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -3520,7 +3520,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N19" authorId="0">
+    <comment ref="N19" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -3556,7 +3556,7 @@
     <author>Автор</author>
   </authors>
   <commentList>
-    <comment ref="Q3" authorId="0">
+    <comment ref="Q3" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -3583,7 +3583,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S3" authorId="0">
+    <comment ref="S3" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -3609,7 +3609,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H4" authorId="0">
+    <comment ref="H4" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -3635,7 +3635,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S5" authorId="0">
+    <comment ref="S5" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -3662,7 +3662,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V6" authorId="0">
+    <comment ref="V6" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -3688,7 +3688,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F7" authorId="0">
+    <comment ref="F7" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -3714,7 +3714,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q8" authorId="0">
+    <comment ref="Q8" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -3741,7 +3741,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S8" authorId="0">
+    <comment ref="S8" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -3768,7 +3768,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S9" authorId="0">
+    <comment ref="S9" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -3794,7 +3794,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E10" authorId="0">
+    <comment ref="E10" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -3820,7 +3820,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S10" authorId="0">
+    <comment ref="S10" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -3846,7 +3846,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q12" authorId="0">
+    <comment ref="Q12" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -3872,7 +3872,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q13" authorId="0">
+    <comment ref="Q13" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -3899,7 +3899,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S13" authorId="0">
+    <comment ref="S13" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -3925,7 +3925,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Y14" authorId="0">
+    <comment ref="Y14" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -3952,7 +3952,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q15" authorId="0">
+    <comment ref="Q15" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -3978,7 +3978,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S15" authorId="0">
+    <comment ref="S15" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -4004,7 +4004,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E16" authorId="0">
+    <comment ref="E16" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -4030,7 +4030,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F16" authorId="0">
+    <comment ref="F16" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -4056,7 +4056,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M16" authorId="0">
+    <comment ref="M16" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -4083,7 +4083,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T16" authorId="0">
+    <comment ref="T16" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -4098,7 +4098,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M17" authorId="0">
+    <comment ref="M17" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -4124,7 +4124,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S17" authorId="0">
+    <comment ref="S17" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -4148,7 +4148,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T17" authorId="0">
+    <comment ref="T17" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -4174,7 +4174,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="U17" authorId="0">
+    <comment ref="U17" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -4200,7 +4200,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Y17" authorId="0">
+    <comment ref="Y17" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -4226,7 +4226,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S18" authorId="0">
+    <comment ref="S18" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -4250,7 +4250,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="U18" authorId="0">
+    <comment ref="U18" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -4274,7 +4274,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E19" authorId="0">
+    <comment ref="E19" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -4300,7 +4300,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V19" authorId="0">
+    <comment ref="V19" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -4324,7 +4324,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Y19" authorId="0">
+    <comment ref="Y19" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -4339,7 +4339,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F21" authorId="0">
+    <comment ref="F21" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -4365,7 +4365,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T21" authorId="0">
+    <comment ref="T21" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -4392,7 +4392,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F23" authorId="0">
+    <comment ref="F23" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -4418,7 +4418,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S23" authorId="0">
+    <comment ref="S23" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -4444,7 +4444,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F24" authorId="0">
+    <comment ref="F24" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -4470,7 +4470,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H25" authorId="0">
+    <comment ref="H25" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -4496,7 +4496,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V25" authorId="0">
+    <comment ref="V25" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -4522,7 +4522,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E27" authorId="0">
+    <comment ref="E27" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -4548,7 +4548,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V27" authorId="0">
+    <comment ref="V27" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -4574,7 +4574,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Y27" authorId="0">
+    <comment ref="Y27" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -4600,7 +4600,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S28" authorId="0">
+    <comment ref="S28" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -4626,7 +4626,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T28" authorId="0">
+    <comment ref="T28" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -4652,7 +4652,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q29" authorId="0">
+    <comment ref="Q29" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -4677,7 +4677,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F30" authorId="0">
+    <comment ref="F30" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -4691,7 +4691,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q30" authorId="0">
+    <comment ref="Q30" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -4715,7 +4715,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Y33" authorId="0">
+    <comment ref="Y33" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -4730,7 +4730,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S34" authorId="0">
+    <comment ref="S34" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -4745,7 +4745,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T34" authorId="0">
+    <comment ref="T34" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -4759,7 +4759,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E35" authorId="0">
+    <comment ref="E35" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -4773,7 +4773,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F35" authorId="0">
+    <comment ref="F35" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -4797,7 +4797,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S35" authorId="0">
+    <comment ref="S35" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -4822,7 +4822,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H36" authorId="0">
+    <comment ref="H36" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -4846,7 +4846,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S36" authorId="0">
+    <comment ref="S36" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -4880,7 +4880,7 @@
     <author>Автор</author>
   </authors>
   <commentList>
-    <comment ref="I4" authorId="0">
+    <comment ref="I4" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -4895,7 +4895,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O4" authorId="0">
+    <comment ref="O4" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -4909,7 +4909,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P4" authorId="0">
+    <comment ref="P4" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -4936,7 +4936,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X4" authorId="0">
+    <comment ref="X4" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -4951,7 +4951,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L5" authorId="0">
+    <comment ref="L5" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -4979,7 +4979,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q5" authorId="0">
+    <comment ref="Q5" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -4994,7 +4994,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W5" authorId="0">
+    <comment ref="W5" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -5009,7 +5009,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J6" authorId="0">
+    <comment ref="J6" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -5035,7 +5035,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I7" authorId="0">
+    <comment ref="I7" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -5050,7 +5050,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J7" authorId="0">
+    <comment ref="J7" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -5065,7 +5065,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O7" authorId="0">
+    <comment ref="O7" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -5080,7 +5080,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Z7" authorId="0">
+    <comment ref="Z7" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -5095,7 +5095,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J8" authorId="0">
+    <comment ref="J8" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -5121,7 +5121,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W8" authorId="0">
+    <comment ref="W8" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -5136,7 +5136,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N9" authorId="0">
+    <comment ref="N9" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -5151,7 +5151,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P9" authorId="0">
+    <comment ref="P9" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -5166,7 +5166,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q10" authorId="0">
+    <comment ref="Q10" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -5180,7 +5180,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W10" authorId="0">
+    <comment ref="W10" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -5189,8 +5189,177 @@
             <rFont val="Tahoma"/>
             <charset val="1"/>
           </rPr>
-          <t xml:space="preserve">Купил ей поке и бабл ти
+          <t xml:space="preserve">поке и бабл ти
 </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="X10" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Списали на долбанном сайте для редактирования картинок с помощью ИИ</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="W11" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+На такси
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K12" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Лапшичка</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="W12" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Книга + ягоды во вкусвилле + поке и бабл ти</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I13" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Обед в феличите</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="W13" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Цветы + такси</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="W14" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Автор:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Вино для Ани с Фаиной + отказ Ани на ламоде</t>
         </r>
       </text>
     </comment>
@@ -5478,7 +5647,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;₽&quot;"/>
   </numFmts>
@@ -6638,6 +6807,7 @@
     <xf numFmtId="0" fontId="45" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="23" fillId="20" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -6677,12 +6847,6 @@
     <xf numFmtId="0" fontId="25" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="28" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="17" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="28" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -6690,6 +6854,12 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="23" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="28" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="17" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="33" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -6722,7 +6892,6 @@
     <xf numFmtId="0" fontId="38" fillId="28" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="20" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -7070,14 +7239,14 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="C3:H17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -7111,7 +7280,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="3:8" ht="16.5">
+    <row r="5" spans="3:8" ht="15.75">
       <c r="C5" s="52" t="s">
         <v>43</v>
       </c>
@@ -7131,7 +7300,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="6" spans="3:8" ht="16.5">
+    <row r="6" spans="3:8" ht="15.75">
       <c r="C6" s="52" t="s">
         <v>44</v>
       </c>
@@ -7152,7 +7321,7 @@
         <v>1260.5599999999977</v>
       </c>
     </row>
-    <row r="7" spans="3:8" ht="16.5">
+    <row r="7" spans="3:8" ht="15.75">
       <c r="C7" s="52" t="s">
         <v>45</v>
       </c>
@@ -7173,7 +7342,7 @@
         <v>-11931.300000000003</v>
       </c>
     </row>
-    <row r="8" spans="3:8" ht="16.5">
+    <row r="8" spans="3:8" ht="15.75">
       <c r="C8" s="52" t="s">
         <v>46</v>
       </c>
@@ -7194,7 +7363,7 @@
         <v>59.059999999997672</v>
       </c>
     </row>
-    <row r="9" spans="3:8" ht="16.5">
+    <row r="9" spans="3:8" ht="15.75">
       <c r="C9" s="52" t="s">
         <v>47</v>
       </c>
@@ -7204,7 +7373,7 @@
       <c r="G9" s="51"/>
       <c r="H9" s="51"/>
     </row>
-    <row r="10" spans="3:8" ht="16.5">
+    <row r="10" spans="3:8" ht="15.75">
       <c r="C10" s="52" t="s">
         <v>48</v>
       </c>
@@ -7214,7 +7383,7 @@
       <c r="G10" s="51"/>
       <c r="H10" s="51"/>
     </row>
-    <row r="11" spans="3:8" ht="16.5">
+    <row r="11" spans="3:8" ht="15.75">
       <c r="C11" s="52" t="s">
         <v>49</v>
       </c>
@@ -7224,7 +7393,7 @@
       <c r="G11" s="51"/>
       <c r="H11" s="51"/>
     </row>
-    <row r="12" spans="3:8" ht="16.5">
+    <row r="12" spans="3:8" ht="15.75">
       <c r="C12" s="52" t="s">
         <v>50</v>
       </c>
@@ -7234,7 +7403,7 @@
       <c r="G12" s="51"/>
       <c r="H12" s="51"/>
     </row>
-    <row r="13" spans="3:8" ht="16.5">
+    <row r="13" spans="3:8" ht="15.75">
       <c r="C13" s="52" t="s">
         <v>51</v>
       </c>
@@ -7244,7 +7413,7 @@
       <c r="G13" s="51"/>
       <c r="H13" s="51"/>
     </row>
-    <row r="14" spans="3:8" ht="16.5">
+    <row r="14" spans="3:8" ht="15.75">
       <c r="C14" s="52" t="s">
         <v>52</v>
       </c>
@@ -7254,7 +7423,7 @@
       <c r="G14" s="51"/>
       <c r="H14" s="51"/>
     </row>
-    <row r="15" spans="3:8" ht="16.5">
+    <row r="15" spans="3:8" ht="15.75">
       <c r="C15" s="52" t="s">
         <v>53</v>
       </c>
@@ -7264,7 +7433,7 @@
       <c r="G15" s="51"/>
       <c r="H15" s="51"/>
     </row>
-    <row r="16" spans="3:8" ht="17.25" thickBot="1">
+    <row r="16" spans="3:8" ht="16.5" thickBot="1">
       <c r="C16" s="53" t="s">
         <v>54</v>
       </c>
@@ -7274,7 +7443,7 @@
       <c r="G16" s="54"/>
       <c r="H16" s="54"/>
     </row>
-    <row r="17" spans="3:8" ht="17.25" thickBot="1">
+    <row r="17" spans="3:8" ht="16.5" thickBot="1">
       <c r="C17" s="55" t="s">
         <v>20</v>
       </c>
@@ -7307,7 +7476,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AT35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -7317,32 +7486,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:46" ht="60.75" customHeight="1">
-      <c r="A1" s="136" t="s">
+      <c r="A1" s="137" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="136"/>
-      <c r="C1" s="136"/>
-      <c r="D1" s="136"/>
-      <c r="E1" s="136"/>
-      <c r="F1" s="136"/>
-      <c r="G1" s="136"/>
-      <c r="H1" s="136"/>
-      <c r="I1" s="136"/>
-      <c r="J1" s="136"/>
-      <c r="K1" s="136"/>
-      <c r="L1" s="136"/>
-      <c r="M1" s="136"/>
-      <c r="N1" s="136"/>
-      <c r="O1" s="136"/>
-      <c r="P1" s="136"/>
-      <c r="Q1" s="136"/>
-      <c r="R1" s="136"/>
-      <c r="S1" s="136"/>
-      <c r="T1" s="136"/>
-      <c r="U1" s="136"/>
-      <c r="V1" s="136"/>
-      <c r="W1" s="136"/>
-      <c r="X1" s="136"/>
+      <c r="B1" s="137"/>
+      <c r="C1" s="137"/>
+      <c r="D1" s="137"/>
+      <c r="E1" s="137"/>
+      <c r="F1" s="137"/>
+      <c r="G1" s="137"/>
+      <c r="H1" s="137"/>
+      <c r="I1" s="137"/>
+      <c r="J1" s="137"/>
+      <c r="K1" s="137"/>
+      <c r="L1" s="137"/>
+      <c r="M1" s="137"/>
+      <c r="N1" s="137"/>
+      <c r="O1" s="137"/>
+      <c r="P1" s="137"/>
+      <c r="Q1" s="137"/>
+      <c r="R1" s="137"/>
+      <c r="S1" s="137"/>
+      <c r="T1" s="137"/>
+      <c r="U1" s="137"/>
+      <c r="V1" s="137"/>
+      <c r="W1" s="137"/>
+      <c r="X1" s="137"/>
     </row>
     <row r="2" spans="1:46" ht="45" customHeight="1">
       <c r="A2" s="3" t="s">
@@ -8541,10 +8710,10 @@
       </c>
     </row>
     <row r="31" spans="1:24">
-      <c r="A31" s="137" t="s">
+      <c r="A31" s="138" t="s">
         <v>20</v>
       </c>
-      <c r="B31" s="137"/>
+      <c r="B31" s="138"/>
       <c r="C31" s="13">
         <f>SUM(C3:C30)</f>
         <v>19992.27</v>
@@ -8657,7 +8826,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AT36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -8667,32 +8836,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:46" ht="60.75" customHeight="1">
-      <c r="A1" s="139" t="s">
+      <c r="A1" s="140" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="139"/>
-      <c r="C1" s="139"/>
-      <c r="D1" s="139"/>
-      <c r="E1" s="139"/>
-      <c r="F1" s="139"/>
-      <c r="G1" s="139"/>
-      <c r="H1" s="139"/>
-      <c r="I1" s="139"/>
-      <c r="J1" s="139"/>
-      <c r="K1" s="139"/>
-      <c r="L1" s="139"/>
-      <c r="M1" s="139"/>
-      <c r="N1" s="139"/>
-      <c r="O1" s="139"/>
-      <c r="P1" s="139"/>
-      <c r="Q1" s="139"/>
-      <c r="R1" s="139"/>
-      <c r="S1" s="139"/>
-      <c r="T1" s="139"/>
-      <c r="U1" s="139"/>
-      <c r="V1" s="139"/>
-      <c r="W1" s="139"/>
-      <c r="X1" s="139"/>
+      <c r="B1" s="140"/>
+      <c r="C1" s="140"/>
+      <c r="D1" s="140"/>
+      <c r="E1" s="140"/>
+      <c r="F1" s="140"/>
+      <c r="G1" s="140"/>
+      <c r="H1" s="140"/>
+      <c r="I1" s="140"/>
+      <c r="J1" s="140"/>
+      <c r="K1" s="140"/>
+      <c r="L1" s="140"/>
+      <c r="M1" s="140"/>
+      <c r="N1" s="140"/>
+      <c r="O1" s="140"/>
+      <c r="P1" s="140"/>
+      <c r="Q1" s="140"/>
+      <c r="R1" s="140"/>
+      <c r="S1" s="140"/>
+      <c r="T1" s="140"/>
+      <c r="U1" s="140"/>
+      <c r="V1" s="140"/>
+      <c r="W1" s="140"/>
+      <c r="X1" s="140"/>
     </row>
     <row r="2" spans="1:46" ht="45" customHeight="1">
       <c r="A2" s="30" t="s">
@@ -9903,10 +10072,10 @@
       <c r="X31" s="31"/>
     </row>
     <row r="32" spans="1:24">
-      <c r="A32" s="138" t="s">
+      <c r="A32" s="139" t="s">
         <v>20</v>
       </c>
-      <c r="B32" s="138"/>
+      <c r="B32" s="139"/>
       <c r="C32" s="28">
         <f>SUM(C3:C31)</f>
         <v>16843.349999999999</v>
@@ -10019,7 +10188,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AU41"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -10029,33 +10198,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:47" ht="60.75" customHeight="1">
-      <c r="A1" s="139" t="s">
+      <c r="A1" s="140" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="139"/>
-      <c r="C1" s="139"/>
-      <c r="D1" s="139"/>
-      <c r="E1" s="139"/>
-      <c r="F1" s="139"/>
-      <c r="G1" s="139"/>
-      <c r="H1" s="139"/>
-      <c r="I1" s="139"/>
-      <c r="J1" s="139"/>
-      <c r="K1" s="139"/>
-      <c r="L1" s="139"/>
-      <c r="M1" s="139"/>
-      <c r="N1" s="139"/>
-      <c r="O1" s="139"/>
-      <c r="P1" s="139"/>
-      <c r="Q1" s="139"/>
-      <c r="R1" s="139"/>
-      <c r="S1" s="139"/>
-      <c r="T1" s="139"/>
-      <c r="U1" s="139"/>
-      <c r="V1" s="139"/>
-      <c r="W1" s="139"/>
-      <c r="X1" s="139"/>
-      <c r="Y1" s="139"/>
+      <c r="B1" s="140"/>
+      <c r="C1" s="140"/>
+      <c r="D1" s="140"/>
+      <c r="E1" s="140"/>
+      <c r="F1" s="140"/>
+      <c r="G1" s="140"/>
+      <c r="H1" s="140"/>
+      <c r="I1" s="140"/>
+      <c r="J1" s="140"/>
+      <c r="K1" s="140"/>
+      <c r="L1" s="140"/>
+      <c r="M1" s="140"/>
+      <c r="N1" s="140"/>
+      <c r="O1" s="140"/>
+      <c r="P1" s="140"/>
+      <c r="Q1" s="140"/>
+      <c r="R1" s="140"/>
+      <c r="S1" s="140"/>
+      <c r="T1" s="140"/>
+      <c r="U1" s="140"/>
+      <c r="V1" s="140"/>
+      <c r="W1" s="140"/>
+      <c r="X1" s="140"/>
+      <c r="Y1" s="140"/>
     </row>
     <row r="2" spans="1:47" ht="45" customHeight="1">
       <c r="A2" s="30" t="s">
@@ -10873,10 +11042,10 @@
       <c r="Y19" s="43"/>
     </row>
     <row r="20" spans="1:27">
-      <c r="A20" s="141" t="s">
+      <c r="A20" s="142" t="s">
         <v>35</v>
       </c>
-      <c r="B20" s="142"/>
+      <c r="B20" s="143"/>
       <c r="C20" s="45">
         <f>SUM(C3:C19)</f>
         <v>12278.83</v>
@@ -11596,10 +11765,10 @@
       <c r="Y35" s="43"/>
     </row>
     <row r="36" spans="1:25">
-      <c r="A36" s="141" t="s">
+      <c r="A36" s="142" t="s">
         <v>36</v>
       </c>
-      <c r="B36" s="142"/>
+      <c r="B36" s="143"/>
       <c r="C36" s="45">
         <f>SUM(C21:C35)</f>
         <v>11057.89</v>
@@ -11694,10 +11863,10 @@
       </c>
     </row>
     <row r="37" spans="1:25" ht="31.5" customHeight="1">
-      <c r="A37" s="140" t="s">
+      <c r="A37" s="141" t="s">
         <v>37</v>
       </c>
-      <c r="B37" s="140"/>
+      <c r="B37" s="141"/>
       <c r="C37" s="48">
         <f>SUM(C20,C36)</f>
         <v>23336.720000000001</v>
@@ -11817,7 +11986,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AU40"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -11827,33 +11996,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:47" ht="60.75" customHeight="1">
-      <c r="A1" s="143" t="s">
+      <c r="A1" s="144" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="143"/>
-      <c r="C1" s="143"/>
-      <c r="D1" s="143"/>
-      <c r="E1" s="143"/>
-      <c r="F1" s="143"/>
-      <c r="G1" s="143"/>
-      <c r="H1" s="143"/>
-      <c r="I1" s="143"/>
-      <c r="J1" s="143"/>
-      <c r="K1" s="143"/>
-      <c r="L1" s="143"/>
-      <c r="M1" s="143"/>
-      <c r="N1" s="143"/>
-      <c r="O1" s="143"/>
-      <c r="P1" s="143"/>
-      <c r="Q1" s="143"/>
-      <c r="R1" s="143"/>
-      <c r="S1" s="143"/>
-      <c r="T1" s="143"/>
-      <c r="U1" s="143"/>
-      <c r="V1" s="143"/>
-      <c r="W1" s="143"/>
-      <c r="X1" s="143"/>
-      <c r="Y1" s="143"/>
+      <c r="B1" s="144"/>
+      <c r="C1" s="144"/>
+      <c r="D1" s="144"/>
+      <c r="E1" s="144"/>
+      <c r="F1" s="144"/>
+      <c r="G1" s="144"/>
+      <c r="H1" s="144"/>
+      <c r="I1" s="144"/>
+      <c r="J1" s="144"/>
+      <c r="K1" s="144"/>
+      <c r="L1" s="144"/>
+      <c r="M1" s="144"/>
+      <c r="N1" s="144"/>
+      <c r="O1" s="144"/>
+      <c r="P1" s="144"/>
+      <c r="Q1" s="144"/>
+      <c r="R1" s="144"/>
+      <c r="S1" s="144"/>
+      <c r="T1" s="144"/>
+      <c r="U1" s="144"/>
+      <c r="V1" s="144"/>
+      <c r="W1" s="144"/>
+      <c r="X1" s="144"/>
+      <c r="Y1" s="144"/>
     </row>
     <row r="2" spans="1:47" ht="45" customHeight="1">
       <c r="A2" s="59" t="s">
@@ -12563,10 +12732,10 @@
       <c r="Y17" s="65"/>
     </row>
     <row r="18" spans="1:27">
-      <c r="A18" s="144" t="s">
+      <c r="A18" s="145" t="s">
         <v>35</v>
       </c>
-      <c r="B18" s="144"/>
+      <c r="B18" s="145"/>
       <c r="C18" s="73">
         <f t="shared" ref="C18:X18" si="1">SUM(C3:C17)</f>
         <v>8428.35</v>
@@ -13319,10 +13488,10 @@
       <c r="Y34" s="69"/>
     </row>
     <row r="35" spans="1:25">
-      <c r="A35" s="144" t="s">
+      <c r="A35" s="145" t="s">
         <v>36</v>
       </c>
-      <c r="B35" s="144"/>
+      <c r="B35" s="145"/>
       <c r="C35" s="73">
         <f>SUM(C19:C34)</f>
         <v>10739.46</v>
@@ -13417,10 +13586,10 @@
       </c>
     </row>
     <row r="36" spans="1:25" ht="31.5" customHeight="1">
-      <c r="A36" s="145" t="s">
+      <c r="A36" s="146" t="s">
         <v>37</v>
       </c>
-      <c r="B36" s="145"/>
+      <c r="B36" s="146"/>
       <c r="C36" s="70">
         <f>SUM(C18,C35)</f>
         <v>19167.809999999998</v>
@@ -13548,7 +13717,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AU40"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -13558,33 +13727,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:47" ht="60.75" customHeight="1">
-      <c r="A1" s="146" t="s">
+      <c r="A1" s="147" t="s">
         <v>58</v>
       </c>
-      <c r="B1" s="146"/>
-      <c r="C1" s="146"/>
-      <c r="D1" s="146"/>
-      <c r="E1" s="146"/>
-      <c r="F1" s="146"/>
-      <c r="G1" s="146"/>
-      <c r="H1" s="146"/>
-      <c r="I1" s="146"/>
-      <c r="J1" s="146"/>
-      <c r="K1" s="146"/>
-      <c r="L1" s="146"/>
-      <c r="M1" s="146"/>
-      <c r="N1" s="146"/>
-      <c r="O1" s="146"/>
-      <c r="P1" s="146"/>
-      <c r="Q1" s="146"/>
-      <c r="R1" s="146"/>
-      <c r="S1" s="146"/>
-      <c r="T1" s="146"/>
-      <c r="U1" s="146"/>
-      <c r="V1" s="146"/>
-      <c r="W1" s="146"/>
-      <c r="X1" s="146"/>
-      <c r="Y1" s="146"/>
+      <c r="B1" s="147"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="147"/>
+      <c r="G1" s="147"/>
+      <c r="H1" s="147"/>
+      <c r="I1" s="147"/>
+      <c r="J1" s="147"/>
+      <c r="K1" s="147"/>
+      <c r="L1" s="147"/>
+      <c r="M1" s="147"/>
+      <c r="N1" s="147"/>
+      <c r="O1" s="147"/>
+      <c r="P1" s="147"/>
+      <c r="Q1" s="147"/>
+      <c r="R1" s="147"/>
+      <c r="S1" s="147"/>
+      <c r="T1" s="147"/>
+      <c r="U1" s="147"/>
+      <c r="V1" s="147"/>
+      <c r="W1" s="147"/>
+      <c r="X1" s="147"/>
+      <c r="Y1" s="147"/>
     </row>
     <row r="2" spans="1:47" ht="45" customHeight="1">
       <c r="A2" s="76" t="s">
@@ -14323,10 +14492,10 @@
       <c r="Y17" s="65"/>
     </row>
     <row r="18" spans="1:27">
-      <c r="A18" s="147" t="s">
+      <c r="A18" s="148" t="s">
         <v>35</v>
       </c>
-      <c r="B18" s="147"/>
+      <c r="B18" s="148"/>
       <c r="C18" s="79">
         <f t="shared" ref="C18:X18" si="1">SUM(C3:C17)</f>
         <v>7904</v>
@@ -14974,10 +15143,10 @@
       <c r="Y34" s="69"/>
     </row>
     <row r="35" spans="1:25">
-      <c r="A35" s="147" t="s">
+      <c r="A35" s="148" t="s">
         <v>36</v>
       </c>
-      <c r="B35" s="147"/>
+      <c r="B35" s="148"/>
       <c r="C35" s="79">
         <f>SUM(C19:C34)</f>
         <v>0</v>
@@ -15072,10 +15241,10 @@
       </c>
     </row>
     <row r="36" spans="1:25" ht="31.5" customHeight="1">
-      <c r="A36" s="148" t="s">
+      <c r="A36" s="149" t="s">
         <v>37</v>
       </c>
-      <c r="B36" s="148"/>
+      <c r="B36" s="149"/>
       <c r="C36" s="74">
         <f>SUM(C18,C35)</f>
         <v>7904</v>
@@ -15203,7 +15372,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AV42"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -15215,34 +15384,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:48" ht="60.75" customHeight="1">
-      <c r="A1" s="151" t="s">
+      <c r="A1" s="150" t="s">
         <v>59</v>
       </c>
-      <c r="B1" s="151"/>
-      <c r="C1" s="151"/>
-      <c r="D1" s="151"/>
-      <c r="E1" s="151"/>
-      <c r="F1" s="151"/>
-      <c r="G1" s="151"/>
-      <c r="H1" s="151"/>
-      <c r="I1" s="151"/>
-      <c r="J1" s="151"/>
-      <c r="K1" s="151"/>
-      <c r="L1" s="151"/>
-      <c r="M1" s="151"/>
-      <c r="N1" s="151"/>
-      <c r="O1" s="151"/>
-      <c r="P1" s="151"/>
-      <c r="Q1" s="151"/>
-      <c r="R1" s="151"/>
-      <c r="S1" s="151"/>
-      <c r="T1" s="151"/>
-      <c r="U1" s="151"/>
-      <c r="V1" s="151"/>
-      <c r="W1" s="151"/>
-      <c r="X1" s="151"/>
-      <c r="Y1" s="151"/>
-      <c r="Z1" s="151"/>
+      <c r="B1" s="150"/>
+      <c r="C1" s="150"/>
+      <c r="D1" s="150"/>
+      <c r="E1" s="150"/>
+      <c r="F1" s="150"/>
+      <c r="G1" s="150"/>
+      <c r="H1" s="150"/>
+      <c r="I1" s="150"/>
+      <c r="J1" s="150"/>
+      <c r="K1" s="150"/>
+      <c r="L1" s="150"/>
+      <c r="M1" s="150"/>
+      <c r="N1" s="150"/>
+      <c r="O1" s="150"/>
+      <c r="P1" s="150"/>
+      <c r="Q1" s="150"/>
+      <c r="R1" s="150"/>
+      <c r="S1" s="150"/>
+      <c r="T1" s="150"/>
+      <c r="U1" s="150"/>
+      <c r="V1" s="150"/>
+      <c r="W1" s="150"/>
+      <c r="X1" s="150"/>
+      <c r="Y1" s="150"/>
+      <c r="Z1" s="150"/>
     </row>
     <row r="2" spans="1:48" ht="45" customHeight="1">
       <c r="A2" s="76" t="s">
@@ -15395,7 +15564,7 @@
         <f>(94085+57723.67)</f>
         <v>151808.66999999998</v>
       </c>
-      <c r="Z3" s="153"/>
+      <c r="Z3" s="152"/>
     </row>
     <row r="4" spans="1:48" ht="15.75">
       <c r="A4" s="66">
@@ -15445,7 +15614,7 @@
       </c>
       <c r="X4" s="90"/>
       <c r="Y4" s="93"/>
-      <c r="Z4" s="153"/>
+      <c r="Z4" s="152"/>
     </row>
     <row r="5" spans="1:48" ht="15.75">
       <c r="A5" s="62">
@@ -15485,7 +15654,7 @@
       </c>
       <c r="X5" s="90"/>
       <c r="Y5" s="93"/>
-      <c r="Z5" s="153"/>
+      <c r="Z5" s="152"/>
     </row>
     <row r="6" spans="1:48" ht="15.75">
       <c r="A6" s="66">
@@ -15526,7 +15695,7 @@
       </c>
       <c r="X6" s="90"/>
       <c r="Y6" s="93"/>
-      <c r="Z6" s="153"/>
+      <c r="Z6" s="152"/>
     </row>
     <row r="7" spans="1:48" ht="15" customHeight="1">
       <c r="A7" s="62">
@@ -15570,7 +15739,7 @@
       </c>
       <c r="X7" s="90"/>
       <c r="Y7" s="93"/>
-      <c r="Z7" s="153"/>
+      <c r="Z7" s="152"/>
     </row>
     <row r="8" spans="1:48" ht="15.75">
       <c r="A8" s="66">
@@ -15612,14 +15781,14 @@
       </c>
       <c r="X8" s="90"/>
       <c r="Y8" s="93"/>
-      <c r="Z8" s="153"/>
-      <c r="AC8" s="150" t="s">
+      <c r="Z8" s="152"/>
+      <c r="AC8" s="154" t="s">
         <v>61</v>
       </c>
-      <c r="AD8" s="150"/>
-      <c r="AE8" s="150"/>
-      <c r="AF8" s="150"/>
-      <c r="AG8" s="150"/>
+      <c r="AD8" s="154"/>
+      <c r="AE8" s="154"/>
+      <c r="AF8" s="154"/>
+      <c r="AG8" s="154"/>
     </row>
     <row r="9" spans="1:48" ht="15.75">
       <c r="A9" s="62">
@@ -15658,12 +15827,12 @@
       </c>
       <c r="X9" s="90"/>
       <c r="Y9" s="93"/>
-      <c r="Z9" s="153"/>
-      <c r="AC9" s="150"/>
-      <c r="AD9" s="150"/>
-      <c r="AE9" s="150"/>
-      <c r="AF9" s="150"/>
-      <c r="AG9" s="150"/>
+      <c r="Z9" s="152"/>
+      <c r="AC9" s="154"/>
+      <c r="AD9" s="154"/>
+      <c r="AE9" s="154"/>
+      <c r="AF9" s="154"/>
+      <c r="AG9" s="154"/>
     </row>
     <row r="10" spans="1:48" ht="15.75">
       <c r="A10" s="66">
@@ -15707,12 +15876,12 @@
       </c>
       <c r="X10" s="90"/>
       <c r="Y10" s="93"/>
-      <c r="Z10" s="153"/>
-      <c r="AC10" s="150"/>
-      <c r="AD10" s="150"/>
-      <c r="AE10" s="150"/>
-      <c r="AF10" s="150"/>
-      <c r="AG10" s="150"/>
+      <c r="Z10" s="152"/>
+      <c r="AC10" s="154"/>
+      <c r="AD10" s="154"/>
+      <c r="AE10" s="154"/>
+      <c r="AF10" s="154"/>
+      <c r="AG10" s="154"/>
     </row>
     <row r="11" spans="1:48" ht="15.75">
       <c r="A11" s="62">
@@ -15752,13 +15921,13 @@
       </c>
       <c r="X11" s="90"/>
       <c r="Y11" s="93"/>
-      <c r="Z11" s="153"/>
-      <c r="AC11" s="149" t="s">
+      <c r="Z11" s="152"/>
+      <c r="AC11" s="153" t="s">
         <v>62</v>
       </c>
-      <c r="AD11" s="149"/>
-      <c r="AE11" s="149"/>
-      <c r="AF11" s="149"/>
+      <c r="AD11" s="153"/>
+      <c r="AE11" s="153"/>
+      <c r="AF11" s="153"/>
       <c r="AG11" s="104">
         <f>Y3+Y14+Y21</f>
         <v>226341.31</v>
@@ -15799,13 +15968,13 @@
       </c>
       <c r="X12" s="90"/>
       <c r="Y12" s="93"/>
-      <c r="Z12" s="153"/>
-      <c r="AC12" s="149" t="s">
+      <c r="Z12" s="152"/>
+      <c r="AC12" s="153" t="s">
         <v>55</v>
       </c>
-      <c r="AD12" s="149"/>
-      <c r="AE12" s="149"/>
-      <c r="AF12" s="149"/>
+      <c r="AD12" s="153"/>
+      <c r="AE12" s="153"/>
+      <c r="AF12" s="153"/>
       <c r="AG12" s="104">
         <f>Y27</f>
         <v>20000</v>
@@ -15850,13 +16019,13 @@
       </c>
       <c r="X13" s="90"/>
       <c r="Y13" s="93"/>
-      <c r="Z13" s="153"/>
-      <c r="AC13" s="149" t="s">
+      <c r="Z13" s="152"/>
+      <c r="AC13" s="153" t="s">
         <v>63</v>
       </c>
-      <c r="AD13" s="149"/>
-      <c r="AE13" s="149"/>
-      <c r="AF13" s="149"/>
+      <c r="AD13" s="153"/>
+      <c r="AE13" s="153"/>
+      <c r="AF13" s="153"/>
       <c r="AG13" s="104">
         <f>Y17+Y19</f>
         <v>25000</v>
@@ -15902,13 +16071,13 @@
       <c r="Y14" s="99">
         <v>37634</v>
       </c>
-      <c r="Z14" s="153"/>
-      <c r="AC14" s="149" t="s">
+      <c r="Z14" s="152"/>
+      <c r="AC14" s="153" t="s">
         <v>64</v>
       </c>
-      <c r="AD14" s="149"/>
-      <c r="AE14" s="149"/>
-      <c r="AF14" s="149"/>
+      <c r="AD14" s="153"/>
+      <c r="AE14" s="153"/>
+      <c r="AF14" s="153"/>
       <c r="AG14" s="104">
         <f>W38</f>
         <v>177971.36</v>
@@ -15958,13 +16127,13 @@
       </c>
       <c r="X15" s="90"/>
       <c r="Y15" s="93"/>
-      <c r="Z15" s="153"/>
-      <c r="AC15" s="149" t="s">
+      <c r="Z15" s="152"/>
+      <c r="AC15" s="153" t="s">
         <v>65</v>
       </c>
-      <c r="AD15" s="149"/>
-      <c r="AE15" s="149"/>
-      <c r="AF15" s="149"/>
+      <c r="AD15" s="153"/>
+      <c r="AE15" s="153"/>
+      <c r="AF15" s="153"/>
       <c r="AG15" s="104">
         <f>SUM(C38:H38)</f>
         <v>55416.04</v>
@@ -16013,7 +16182,7 @@
       </c>
       <c r="X16" s="90"/>
       <c r="Y16" s="93"/>
-      <c r="Z16" s="153"/>
+      <c r="Z16" s="152"/>
     </row>
     <row r="17" spans="1:28" ht="15.75">
       <c r="A17" s="62">
@@ -16065,7 +16234,7 @@
       <c r="Y17" s="100">
         <v>15000</v>
       </c>
-      <c r="Z17" s="153"/>
+      <c r="Z17" s="152"/>
     </row>
     <row r="18" spans="1:28" ht="15.75">
       <c r="A18" s="66">
@@ -16106,7 +16275,7 @@
       </c>
       <c r="X18" s="90"/>
       <c r="Y18" s="93"/>
-      <c r="Z18" s="153"/>
+      <c r="Z18" s="152"/>
     </row>
     <row r="19" spans="1:28" ht="15.75">
       <c r="A19" s="62">
@@ -16150,13 +16319,13 @@
       <c r="Y19" s="100">
         <v>10000</v>
       </c>
-      <c r="Z19" s="153"/>
+      <c r="Z19" s="152"/>
     </row>
     <row r="20" spans="1:28" ht="14.25" customHeight="1">
-      <c r="A20" s="147" t="s">
+      <c r="A20" s="148" t="s">
         <v>35</v>
       </c>
-      <c r="B20" s="147"/>
+      <c r="B20" s="148"/>
       <c r="C20" s="79">
         <f t="shared" ref="C20:V20" si="1">SUM(C3:C17)</f>
         <v>10942.99</v>
@@ -16299,7 +16468,7 @@
       <c r="Y21" s="99">
         <v>36898.639999999999</v>
       </c>
-      <c r="Z21" s="153"/>
+      <c r="Z21" s="152"/>
     </row>
     <row r="22" spans="1:28" ht="15.75">
       <c r="A22" s="66">
@@ -16345,7 +16514,7 @@
         <v>23662.84</v>
       </c>
       <c r="Y22" s="93"/>
-      <c r="Z22" s="153"/>
+      <c r="Z22" s="152"/>
       <c r="AB22" s="44"/>
     </row>
     <row r="23" spans="1:28" ht="15.75">
@@ -16389,7 +16558,7 @@
       </c>
       <c r="X23" s="90"/>
       <c r="Y23" s="93"/>
-      <c r="Z23" s="153"/>
+      <c r="Z23" s="152"/>
     </row>
     <row r="24" spans="1:28" ht="15.75">
       <c r="A24" s="66">
@@ -16433,7 +16602,7 @@
       </c>
       <c r="X24" s="90"/>
       <c r="Y24" s="93"/>
-      <c r="Z24" s="153"/>
+      <c r="Z24" s="152"/>
     </row>
     <row r="25" spans="1:28" ht="15.75">
       <c r="A25" s="62">
@@ -16477,7 +16646,7 @@
       </c>
       <c r="X25" s="90"/>
       <c r="Y25" s="93"/>
-      <c r="Z25" s="153"/>
+      <c r="Z25" s="152"/>
     </row>
     <row r="26" spans="1:28" ht="15.75">
       <c r="A26" s="66">
@@ -16516,7 +16685,7 @@
       </c>
       <c r="X26" s="90"/>
       <c r="Y26" s="93"/>
-      <c r="Z26" s="153"/>
+      <c r="Z26" s="152"/>
     </row>
     <row r="27" spans="1:28" ht="15.75">
       <c r="A27" s="62">
@@ -16561,7 +16730,7 @@
       <c r="Y27" s="103">
         <v>20000</v>
       </c>
-      <c r="Z27" s="153"/>
+      <c r="Z27" s="152"/>
     </row>
     <row r="28" spans="1:28" ht="15.75">
       <c r="A28" s="66">
@@ -16603,7 +16772,7 @@
       </c>
       <c r="X28" s="90"/>
       <c r="Y28" s="93"/>
-      <c r="Z28" s="153"/>
+      <c r="Z28" s="152"/>
     </row>
     <row r="29" spans="1:28" ht="15.75">
       <c r="A29" s="62">
@@ -16642,7 +16811,7 @@
       </c>
       <c r="X29" s="90"/>
       <c r="Y29" s="93"/>
-      <c r="Z29" s="153"/>
+      <c r="Z29" s="152"/>
     </row>
     <row r="30" spans="1:28" ht="15.75">
       <c r="A30" s="66">
@@ -16682,7 +16851,7 @@
       </c>
       <c r="X30" s="90"/>
       <c r="Y30" s="93"/>
-      <c r="Z30" s="153"/>
+      <c r="Z30" s="152"/>
     </row>
     <row r="31" spans="1:28" ht="15.75">
       <c r="A31" s="62">
@@ -16717,7 +16886,7 @@
       </c>
       <c r="X31" s="90"/>
       <c r="Y31" s="93"/>
-      <c r="Z31" s="153"/>
+      <c r="Z31" s="152"/>
     </row>
     <row r="32" spans="1:28" ht="15.75">
       <c r="A32" s="66">
@@ -16752,7 +16921,7 @@
       </c>
       <c r="X32" s="90"/>
       <c r="Y32" s="93"/>
-      <c r="Z32" s="153"/>
+      <c r="Z32" s="152"/>
     </row>
     <row r="33" spans="1:26" ht="15.75">
       <c r="A33" s="62">
@@ -16786,10 +16955,10 @@
         <v>0</v>
       </c>
       <c r="X33" s="90"/>
-      <c r="Y33" s="164">
+      <c r="Y33" s="136">
         <v>10000</v>
       </c>
-      <c r="Z33" s="153"/>
+      <c r="Z33" s="152"/>
     </row>
     <row r="34" spans="1:26" ht="15.75">
       <c r="A34" s="66">
@@ -16828,7 +16997,7 @@
       </c>
       <c r="X34" s="90"/>
       <c r="Y34" s="93"/>
-      <c r="Z34" s="153"/>
+      <c r="Z34" s="152"/>
     </row>
     <row r="35" spans="1:26" ht="15.75">
       <c r="A35" s="62">
@@ -16872,7 +17041,7 @@
       </c>
       <c r="X35" s="90"/>
       <c r="Y35" s="93"/>
-      <c r="Z35" s="153"/>
+      <c r="Z35" s="152"/>
     </row>
     <row r="36" spans="1:26" ht="15.75">
       <c r="A36" s="66">
@@ -16913,13 +17082,13 @@
       </c>
       <c r="X36" s="90"/>
       <c r="Y36" s="93"/>
-      <c r="Z36" s="153"/>
+      <c r="Z36" s="152"/>
     </row>
     <row r="37" spans="1:26">
-      <c r="A37" s="147" t="s">
+      <c r="A37" s="148" t="s">
         <v>36</v>
       </c>
-      <c r="B37" s="147"/>
+      <c r="B37" s="148"/>
       <c r="C37" s="79">
         <f>SUM(C21:C36)</f>
         <v>3393</v>
@@ -17018,10 +17187,10 @@
       </c>
     </row>
     <row r="38" spans="1:26" ht="31.5" customHeight="1">
-      <c r="A38" s="152" t="s">
+      <c r="A38" s="151" t="s">
         <v>37</v>
       </c>
-      <c r="B38" s="152"/>
+      <c r="B38" s="151"/>
       <c r="C38" s="78">
         <f>SUM(C20,C37)</f>
         <v>14335.99</v>
@@ -17133,24 +17302,24 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="AC14:AF14"/>
+    <mergeCell ref="AC15:AF15"/>
+    <mergeCell ref="AC8:AG10"/>
+    <mergeCell ref="AC11:AF11"/>
+    <mergeCell ref="AC12:AF12"/>
+    <mergeCell ref="AC13:AF13"/>
     <mergeCell ref="A1:Z1"/>
     <mergeCell ref="A20:B20"/>
     <mergeCell ref="A37:B37"/>
     <mergeCell ref="A38:B38"/>
     <mergeCell ref="Z3:Z19"/>
     <mergeCell ref="Z21:Z36"/>
-    <mergeCell ref="AC14:AF14"/>
-    <mergeCell ref="AC15:AF15"/>
-    <mergeCell ref="AC8:AG10"/>
-    <mergeCell ref="AC11:AF11"/>
-    <mergeCell ref="AC12:AF12"/>
-    <mergeCell ref="AC13:AF13"/>
   </mergeCells>
   <conditionalFormatting sqref="Z20:Z21 Z37:Z38">
-    <cfRule type="expression" dxfId="1" priority="1">
+    <cfRule type="expression" dxfId="3" priority="1">
       <formula>Z20&lt;0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="2">
+    <cfRule type="expression" dxfId="2" priority="2">
       <formula>Z20&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -17161,7 +17330,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AZ41"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -17171,78 +17340,78 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:52" ht="34.5" customHeight="1">
-      <c r="A1" s="155" t="s">
+      <c r="A1" s="156" t="s">
         <v>66</v>
       </c>
-      <c r="B1" s="155"/>
-      <c r="C1" s="155"/>
-      <c r="D1" s="155"/>
-      <c r="E1" s="155"/>
-      <c r="F1" s="155"/>
-      <c r="G1" s="155"/>
-      <c r="H1" s="155"/>
-      <c r="I1" s="155"/>
-      <c r="J1" s="155"/>
-      <c r="K1" s="155"/>
-      <c r="L1" s="155"/>
-      <c r="M1" s="155"/>
-      <c r="N1" s="155"/>
-      <c r="O1" s="155"/>
-      <c r="P1" s="155"/>
-      <c r="Q1" s="155"/>
-      <c r="R1" s="155"/>
-      <c r="S1" s="155"/>
-      <c r="T1" s="155"/>
-      <c r="U1" s="155"/>
-      <c r="V1" s="155"/>
-      <c r="W1" s="155"/>
-      <c r="X1" s="155"/>
-      <c r="Y1" s="155"/>
-      <c r="Z1" s="155"/>
-      <c r="AA1" s="155"/>
-      <c r="AB1" s="155"/>
-      <c r="AC1" s="155"/>
-      <c r="AD1" s="155"/>
+      <c r="B1" s="156"/>
+      <c r="C1" s="156"/>
+      <c r="D1" s="156"/>
+      <c r="E1" s="156"/>
+      <c r="F1" s="156"/>
+      <c r="G1" s="156"/>
+      <c r="H1" s="156"/>
+      <c r="I1" s="156"/>
+      <c r="J1" s="156"/>
+      <c r="K1" s="156"/>
+      <c r="L1" s="156"/>
+      <c r="M1" s="156"/>
+      <c r="N1" s="156"/>
+      <c r="O1" s="156"/>
+      <c r="P1" s="156"/>
+      <c r="Q1" s="156"/>
+      <c r="R1" s="156"/>
+      <c r="S1" s="156"/>
+      <c r="T1" s="156"/>
+      <c r="U1" s="156"/>
+      <c r="V1" s="156"/>
+      <c r="W1" s="156"/>
+      <c r="X1" s="156"/>
+      <c r="Y1" s="156"/>
+      <c r="Z1" s="156"/>
+      <c r="AA1" s="156"/>
+      <c r="AB1" s="156"/>
+      <c r="AC1" s="156"/>
+      <c r="AD1" s="156"/>
     </row>
     <row r="2" spans="1:52" ht="26.25">
-      <c r="A2" s="162"/>
-      <c r="B2" s="163"/>
-      <c r="C2" s="158" t="s">
+      <c r="A2" s="163"/>
+      <c r="B2" s="164"/>
+      <c r="C2" s="159" t="s">
         <v>67</v>
       </c>
-      <c r="D2" s="158"/>
-      <c r="E2" s="158"/>
-      <c r="F2" s="158"/>
-      <c r="G2" s="158"/>
-      <c r="H2" s="158"/>
-      <c r="I2" s="158"/>
-      <c r="J2" s="158"/>
-      <c r="K2" s="158"/>
-      <c r="L2" s="159" t="s">
+      <c r="D2" s="159"/>
+      <c r="E2" s="159"/>
+      <c r="F2" s="159"/>
+      <c r="G2" s="159"/>
+      <c r="H2" s="159"/>
+      <c r="I2" s="159"/>
+      <c r="J2" s="159"/>
+      <c r="K2" s="159"/>
+      <c r="L2" s="160" t="s">
         <v>75</v>
       </c>
-      <c r="M2" s="159"/>
-      <c r="N2" s="159"/>
-      <c r="O2" s="159"/>
-      <c r="P2" s="159"/>
-      <c r="Q2" s="159"/>
-      <c r="R2" s="160" t="s">
+      <c r="M2" s="160"/>
+      <c r="N2" s="160"/>
+      <c r="O2" s="160"/>
+      <c r="P2" s="160"/>
+      <c r="Q2" s="160"/>
+      <c r="R2" s="161" t="s">
         <v>78</v>
       </c>
-      <c r="S2" s="160"/>
-      <c r="T2" s="160"/>
-      <c r="U2" s="160"/>
-      <c r="V2" s="160"/>
-      <c r="W2" s="160"/>
-      <c r="X2" s="160"/>
-      <c r="Y2" s="160"/>
-      <c r="Z2" s="160"/>
-      <c r="AA2" s="160"/>
-      <c r="AB2" s="161" t="s">
+      <c r="S2" s="161"/>
+      <c r="T2" s="161"/>
+      <c r="U2" s="161"/>
+      <c r="V2" s="161"/>
+      <c r="W2" s="161"/>
+      <c r="X2" s="161"/>
+      <c r="Y2" s="161"/>
+      <c r="Z2" s="161"/>
+      <c r="AA2" s="161"/>
+      <c r="AB2" s="162" t="s">
         <v>81</v>
       </c>
-      <c r="AC2" s="161"/>
-      <c r="AD2" s="161"/>
+      <c r="AC2" s="162"/>
+      <c r="AD2" s="162"/>
     </row>
     <row r="3" spans="1:52" ht="45" customHeight="1">
       <c r="A3" s="119" t="s">
@@ -17409,7 +17578,7 @@
         <f>37635+40252.26+18817.85</f>
         <v>96705.110000000015</v>
       </c>
-      <c r="AD4" s="156"/>
+      <c r="AD4" s="157"/>
     </row>
     <row r="5" spans="1:52" ht="15.75">
       <c r="A5" s="105">
@@ -17459,7 +17628,7 @@
         <v>16503.13</v>
       </c>
       <c r="AC5" s="117"/>
-      <c r="AD5" s="156"/>
+      <c r="AD5" s="157"/>
     </row>
     <row r="6" spans="1:52" ht="15.75">
       <c r="A6" s="109">
@@ -17502,7 +17671,7 @@
         <v>996.61</v>
       </c>
       <c r="AC6" s="117"/>
-      <c r="AD6" s="156"/>
+      <c r="AD6" s="157"/>
     </row>
     <row r="7" spans="1:52" ht="15.75">
       <c r="A7" s="105">
@@ -17554,7 +17723,7 @@
         <v>8468</v>
       </c>
       <c r="AC7" s="117"/>
-      <c r="AD7" s="156"/>
+      <c r="AD7" s="157"/>
     </row>
     <row r="8" spans="1:52" ht="15" customHeight="1">
       <c r="A8" s="109">
@@ -17600,7 +17769,7 @@
         <v>12168.98</v>
       </c>
       <c r="AC8" s="117"/>
-      <c r="AD8" s="156"/>
+      <c r="AD8" s="157"/>
     </row>
     <row r="9" spans="1:52" ht="15.75">
       <c r="A9" s="105">
@@ -17648,7 +17817,7 @@
         <v>5970</v>
       </c>
       <c r="AC9" s="117"/>
-      <c r="AD9" s="156"/>
+      <c r="AD9" s="157"/>
     </row>
     <row r="10" spans="1:52" ht="15.75">
       <c r="A10" s="109">
@@ -17678,22 +17847,25 @@
       <c r="S10" s="111"/>
       <c r="T10" s="111"/>
       <c r="U10" s="111">
-        <v>207</v>
+        <f>207+380</f>
+        <v>587</v>
       </c>
       <c r="V10" s="111"/>
       <c r="W10" s="111">
         <v>1180</v>
       </c>
-      <c r="X10" s="111"/>
+      <c r="X10" s="111">
+        <v>990</v>
+      </c>
       <c r="Y10" s="111"/>
       <c r="Z10" s="111"/>
       <c r="AA10" s="112"/>
       <c r="AB10" s="128">
         <f t="shared" si="0"/>
-        <v>1887</v>
+        <v>3257</v>
       </c>
       <c r="AC10" s="117"/>
-      <c r="AD10" s="156"/>
+      <c r="AD10" s="157"/>
     </row>
     <row r="11" spans="1:52" ht="15.75">
       <c r="A11" s="105">
@@ -17705,7 +17877,10 @@
       <c r="C11" s="107"/>
       <c r="D11" s="107"/>
       <c r="E11" s="107"/>
-      <c r="F11" s="107"/>
+      <c r="F11" s="107">
+        <f>210+424</f>
+        <v>634</v>
+      </c>
       <c r="G11" s="107"/>
       <c r="H11" s="107"/>
       <c r="I11" s="107"/>
@@ -17722,17 +17897,19 @@
       <c r="T11" s="107"/>
       <c r="U11" s="107"/>
       <c r="V11" s="107"/>
-      <c r="W11" s="107"/>
+      <c r="W11" s="107">
+        <v>400</v>
+      </c>
       <c r="X11" s="107"/>
       <c r="Y11" s="107"/>
       <c r="Z11" s="107"/>
       <c r="AA11" s="108"/>
       <c r="AB11" s="128">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1034</v>
       </c>
       <c r="AC11" s="117"/>
-      <c r="AD11" s="156"/>
+      <c r="AD11" s="157"/>
     </row>
     <row r="12" spans="1:52" ht="15.75">
       <c r="A12" s="109">
@@ -17749,7 +17926,9 @@
       <c r="H12" s="111"/>
       <c r="I12" s="111"/>
       <c r="J12" s="111"/>
-      <c r="K12" s="111"/>
+      <c r="K12" s="111">
+        <v>420</v>
+      </c>
       <c r="L12" s="111"/>
       <c r="M12" s="111"/>
       <c r="N12" s="111"/>
@@ -17759,19 +17938,25 @@
       <c r="R12" s="111"/>
       <c r="S12" s="111"/>
       <c r="T12" s="111"/>
-      <c r="U12" s="111"/>
+      <c r="U12" s="111">
+        <f>399+300</f>
+        <v>699</v>
+      </c>
       <c r="V12" s="111"/>
-      <c r="W12" s="111"/>
+      <c r="W12" s="111">
+        <f>517+1080+787+83</f>
+        <v>2467</v>
+      </c>
       <c r="X12" s="111"/>
       <c r="Y12" s="111"/>
       <c r="Z12" s="111"/>
       <c r="AA12" s="112"/>
       <c r="AB12" s="128">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3586</v>
       </c>
       <c r="AC12" s="117"/>
-      <c r="AD12" s="156"/>
+      <c r="AD12" s="157"/>
     </row>
     <row r="13" spans="1:52" ht="15.75">
       <c r="A13" s="105">
@@ -17786,7 +17971,10 @@
       <c r="F13" s="107"/>
       <c r="G13" s="107"/>
       <c r="H13" s="107"/>
-      <c r="I13" s="107"/>
+      <c r="I13" s="107">
+        <f>2220+250</f>
+        <v>2470</v>
+      </c>
       <c r="J13" s="107"/>
       <c r="K13" s="107"/>
       <c r="L13" s="107"/>
@@ -17798,19 +17986,24 @@
       <c r="R13" s="107"/>
       <c r="S13" s="107"/>
       <c r="T13" s="107"/>
-      <c r="U13" s="107"/>
+      <c r="U13" s="107">
+        <v>384</v>
+      </c>
       <c r="V13" s="107"/>
-      <c r="W13" s="107"/>
+      <c r="W13" s="107">
+        <f>2720+315</f>
+        <v>3035</v>
+      </c>
       <c r="X13" s="107"/>
       <c r="Y13" s="107"/>
       <c r="Z13" s="107"/>
       <c r="AA13" s="108"/>
       <c r="AB13" s="128">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>5889</v>
       </c>
       <c r="AC13" s="117"/>
-      <c r="AD13" s="156"/>
+      <c r="AD13" s="157"/>
     </row>
     <row r="14" spans="1:52" ht="15.75">
       <c r="A14" s="109">
@@ -17819,7 +18012,9 @@
       <c r="B14" s="110" t="s">
         <v>5</v>
       </c>
-      <c r="C14" s="111"/>
+      <c r="C14" s="111">
+        <v>973.94</v>
+      </c>
       <c r="D14" s="111"/>
       <c r="E14" s="111"/>
       <c r="F14" s="111"/>
@@ -17839,17 +18034,20 @@
       <c r="T14" s="111"/>
       <c r="U14" s="111"/>
       <c r="V14" s="111"/>
-      <c r="W14" s="111"/>
+      <c r="W14" s="111">
+        <f>1319.99</f>
+        <v>1319.99</v>
+      </c>
       <c r="X14" s="111"/>
       <c r="Y14" s="111"/>
       <c r="Z14" s="111"/>
       <c r="AA14" s="112"/>
       <c r="AB14" s="128">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2293.9300000000003</v>
       </c>
       <c r="AC14" s="117"/>
-      <c r="AD14" s="156"/>
+      <c r="AD14" s="157"/>
     </row>
     <row r="15" spans="1:52" ht="15.75">
       <c r="A15" s="105">
@@ -17888,7 +18086,7 @@
         <v>0</v>
       </c>
       <c r="AC15" s="118"/>
-      <c r="AD15" s="156"/>
+      <c r="AD15" s="157"/>
     </row>
     <row r="16" spans="1:52" ht="15.75">
       <c r="A16" s="109">
@@ -17927,7 +18125,7 @@
         <v>0</v>
       </c>
       <c r="AC16" s="117"/>
-      <c r="AD16" s="156"/>
+      <c r="AD16" s="157"/>
     </row>
     <row r="17" spans="1:32" ht="15.75">
       <c r="A17" s="105">
@@ -17966,7 +18164,7 @@
         <v>0</v>
       </c>
       <c r="AC17" s="117"/>
-      <c r="AD17" s="156"/>
+      <c r="AD17" s="157"/>
     </row>
     <row r="18" spans="1:32" ht="15.75">
       <c r="A18" s="109">
@@ -18005,16 +18203,16 @@
         <v>0</v>
       </c>
       <c r="AC18" s="117"/>
-      <c r="AD18" s="156"/>
+      <c r="AD18" s="157"/>
     </row>
     <row r="19" spans="1:32" ht="14.25" customHeight="1">
-      <c r="A19" s="157" t="s">
+      <c r="A19" s="158" t="s">
         <v>35</v>
       </c>
-      <c r="B19" s="157"/>
+      <c r="B19" s="158"/>
       <c r="C19" s="113">
         <f>SUM(C4:C18)</f>
-        <v>429.95</v>
+        <v>1403.89</v>
       </c>
       <c r="D19" s="113">
         <f t="shared" ref="D19:AA19" si="1">SUM(D4:D18)</f>
@@ -18026,7 +18224,7 @@
       </c>
       <c r="F19" s="113">
         <f t="shared" si="1"/>
-        <v>1812</v>
+        <v>2446</v>
       </c>
       <c r="G19" s="113">
         <f t="shared" si="1"/>
@@ -18038,7 +18236,7 @@
       </c>
       <c r="I19" s="113">
         <f t="shared" si="1"/>
-        <v>7935</v>
+        <v>10405</v>
       </c>
       <c r="J19" s="113">
         <f t="shared" si="1"/>
@@ -18046,7 +18244,7 @@
       </c>
       <c r="K19" s="113">
         <f t="shared" si="1"/>
-        <v>1860</v>
+        <v>2280</v>
       </c>
       <c r="L19" s="114">
         <f t="shared" si="1"/>
@@ -18086,7 +18284,7 @@
       </c>
       <c r="U19" s="115">
         <f t="shared" si="1"/>
-        <v>921</v>
+        <v>2384</v>
       </c>
       <c r="V19" s="115">
         <f t="shared" si="1"/>
@@ -18094,11 +18292,11 @@
       </c>
       <c r="W19" s="115">
         <f t="shared" si="1"/>
-        <v>10804.98</v>
+        <v>18026.97</v>
       </c>
       <c r="X19" s="115">
         <f t="shared" si="1"/>
-        <v>1237</v>
+        <v>2227</v>
       </c>
       <c r="Y19" s="115">
         <f t="shared" si="1"/>
@@ -18114,7 +18312,7 @@
       </c>
       <c r="AB19" s="129">
         <f>SUM(AB4:AB18)</f>
-        <v>62965.67</v>
+        <v>77138.600000000006</v>
       </c>
       <c r="AC19" s="130">
         <f>SUM(AC4:AC18)</f>
@@ -18122,7 +18320,7 @@
       </c>
       <c r="AD19" s="133">
         <f>AC19-AB19</f>
-        <v>33739.440000000017</v>
+        <v>19566.510000000009</v>
       </c>
     </row>
     <row r="20" spans="1:32" ht="15.75">
@@ -18162,7 +18360,7 @@
         <v>0</v>
       </c>
       <c r="AC20" s="118"/>
-      <c r="AD20" s="156"/>
+      <c r="AD20" s="157"/>
     </row>
     <row r="21" spans="1:32" ht="15.75">
       <c r="A21" s="105">
@@ -18201,7 +18399,7 @@
         <v>0</v>
       </c>
       <c r="AC21" s="117"/>
-      <c r="AD21" s="156"/>
+      <c r="AD21" s="157"/>
       <c r="AF21" s="44"/>
     </row>
     <row r="22" spans="1:32" ht="15.75">
@@ -18241,7 +18439,7 @@
         <v>0</v>
       </c>
       <c r="AC22" s="117"/>
-      <c r="AD22" s="156"/>
+      <c r="AD22" s="157"/>
     </row>
     <row r="23" spans="1:32" ht="15.75">
       <c r="A23" s="105">
@@ -18280,7 +18478,7 @@
         <v>0</v>
       </c>
       <c r="AC23" s="117"/>
-      <c r="AD23" s="156"/>
+      <c r="AD23" s="157"/>
     </row>
     <row r="24" spans="1:32" ht="15.75">
       <c r="A24" s="109">
@@ -18319,7 +18517,7 @@
         <v>0</v>
       </c>
       <c r="AC24" s="117"/>
-      <c r="AD24" s="156"/>
+      <c r="AD24" s="157"/>
     </row>
     <row r="25" spans="1:32" ht="15.75">
       <c r="A25" s="105">
@@ -18358,7 +18556,7 @@
         <v>0</v>
       </c>
       <c r="AC25" s="117"/>
-      <c r="AD25" s="156"/>
+      <c r="AD25" s="157"/>
     </row>
     <row r="26" spans="1:32" ht="15.75">
       <c r="A26" s="109">
@@ -18397,7 +18595,7 @@
         <v>0</v>
       </c>
       <c r="AC26" s="118"/>
-      <c r="AD26" s="156"/>
+      <c r="AD26" s="157"/>
     </row>
     <row r="27" spans="1:32" ht="15.75">
       <c r="A27" s="105">
@@ -18436,7 +18634,7 @@
         <v>0</v>
       </c>
       <c r="AC27" s="117"/>
-      <c r="AD27" s="156"/>
+      <c r="AD27" s="157"/>
     </row>
     <row r="28" spans="1:32" ht="15.75">
       <c r="A28" s="109">
@@ -18475,7 +18673,7 @@
         <v>0</v>
       </c>
       <c r="AC28" s="117"/>
-      <c r="AD28" s="156"/>
+      <c r="AD28" s="157"/>
     </row>
     <row r="29" spans="1:32" ht="15.75">
       <c r="A29" s="105">
@@ -18514,7 +18712,7 @@
         <v>0</v>
       </c>
       <c r="AC29" s="117"/>
-      <c r="AD29" s="156"/>
+      <c r="AD29" s="157"/>
     </row>
     <row r="30" spans="1:32" ht="15.75">
       <c r="A30" s="109">
@@ -18553,7 +18751,7 @@
         <v>0</v>
       </c>
       <c r="AC30" s="117"/>
-      <c r="AD30" s="156"/>
+      <c r="AD30" s="157"/>
     </row>
     <row r="31" spans="1:32" ht="15.75">
       <c r="A31" s="105">
@@ -18592,7 +18790,7 @@
         <v>0</v>
       </c>
       <c r="AC31" s="117"/>
-      <c r="AD31" s="156"/>
+      <c r="AD31" s="157"/>
     </row>
     <row r="32" spans="1:32" ht="15.75">
       <c r="A32" s="109">
@@ -18631,7 +18829,7 @@
         <v>0</v>
       </c>
       <c r="AC32" s="117"/>
-      <c r="AD32" s="156"/>
+      <c r="AD32" s="157"/>
     </row>
     <row r="33" spans="1:30" ht="15.75">
       <c r="A33" s="105">
@@ -18670,7 +18868,7 @@
         <v>0</v>
       </c>
       <c r="AC33" s="117"/>
-      <c r="AD33" s="156"/>
+      <c r="AD33" s="157"/>
     </row>
     <row r="34" spans="1:30" ht="15.75">
       <c r="A34" s="109">
@@ -18709,7 +18907,7 @@
         <v>0</v>
       </c>
       <c r="AC34" s="117"/>
-      <c r="AD34" s="156"/>
+      <c r="AD34" s="157"/>
     </row>
     <row r="35" spans="1:30" ht="15.75">
       <c r="A35" s="105">
@@ -18748,13 +18946,13 @@
         <v>0</v>
       </c>
       <c r="AC35" s="117"/>
-      <c r="AD35" s="156"/>
+      <c r="AD35" s="157"/>
     </row>
     <row r="36" spans="1:30" ht="14.25" customHeight="1">
-      <c r="A36" s="157" t="s">
+      <c r="A36" s="158" t="s">
         <v>36</v>
       </c>
-      <c r="B36" s="157"/>
+      <c r="B36" s="158"/>
       <c r="C36" s="113">
         <f>SUM(C20:C35)</f>
         <v>0</v>
@@ -18869,19 +19067,19 @@
       </c>
     </row>
     <row r="37" spans="1:30" ht="31.5" customHeight="1">
-      <c r="A37" s="154" t="s">
+      <c r="A37" s="155" t="s">
         <v>37</v>
       </c>
-      <c r="B37" s="154"/>
+      <c r="B37" s="155"/>
       <c r="C37" s="116">
         <f>SUM(C19,C36)</f>
-        <v>429.95</v>
+        <v>1403.89</v>
       </c>
       <c r="D37" s="116"/>
       <c r="E37" s="116"/>
       <c r="F37" s="116">
         <f t="shared" ref="F37:AB37" si="6">SUM(F19,F36)</f>
-        <v>1812</v>
+        <v>2446</v>
       </c>
       <c r="G37" s="116"/>
       <c r="H37" s="116">
@@ -18890,7 +19088,7 @@
       </c>
       <c r="I37" s="116">
         <f t="shared" si="6"/>
-        <v>7935</v>
+        <v>10405</v>
       </c>
       <c r="J37" s="116">
         <f t="shared" si="6"/>
@@ -18898,7 +19096,7 @@
       </c>
       <c r="K37" s="116">
         <f t="shared" si="6"/>
-        <v>1860</v>
+        <v>2280</v>
       </c>
       <c r="L37" s="116">
         <f t="shared" si="6"/>
@@ -18926,7 +19124,7 @@
       </c>
       <c r="U37" s="116">
         <f t="shared" si="6"/>
-        <v>921</v>
+        <v>2384</v>
       </c>
       <c r="V37" s="116">
         <f t="shared" si="6"/>
@@ -18934,11 +19132,11 @@
       </c>
       <c r="W37" s="116">
         <f t="shared" si="6"/>
-        <v>10804.98</v>
+        <v>18026.97</v>
       </c>
       <c r="X37" s="116">
         <f t="shared" si="6"/>
-        <v>1237</v>
+        <v>2227</v>
       </c>
       <c r="Y37" s="116">
         <f t="shared" si="6"/>
@@ -18954,7 +19152,7 @@
       </c>
       <c r="AB37" s="131">
         <f t="shared" si="6"/>
-        <v>62965.67</v>
+        <v>77138.600000000006</v>
       </c>
       <c r="AC37" s="132">
         <f>SUM(AC19,AC36)</f>
@@ -18962,7 +19160,7 @@
       </c>
       <c r="AD37" s="134">
         <f>SUM(AD19,AD36)</f>
-        <v>33739.440000000017</v>
+        <v>19566.510000000009</v>
       </c>
     </row>
     <row r="41" spans="1:30">
@@ -18998,10 +19196,10 @@
     <mergeCell ref="A2:B2"/>
   </mergeCells>
   <conditionalFormatting sqref="AD19:AD20 AD36:AD37">
-    <cfRule type="expression" dxfId="3" priority="1">
+    <cfRule type="expression" dxfId="1" priority="1">
       <formula>AD19&lt;0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="2">
+    <cfRule type="expression" dxfId="0" priority="2">
       <formula>AD19&gt;0</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Другое/2026/Доходы-Расходы_copy.xlsx
+++ b/Другое/2026/Доходы-Расходы_copy.xlsx
@@ -1,8 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="6" rupBuild="4507"/>
+  <workbookPr filterPrivacy="1"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="7"/>
   </bookViews>
@@ -16,9 +16,9 @@
     <sheet name="Июль 2026" sheetId="8" r:id="rId7"/>
     <sheet name="Август 2026" sheetId="9" r:id="rId8"/>
   </sheets>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+  <calcPr calcId="125725"/>
+  <extLst xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
@@ -31,7 +31,7 @@
     <author>Автор</author>
   </authors>
   <commentList>
-    <comment ref="S3" authorId="0" shapeId="0">
+    <comment ref="S3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -58,7 +58,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P11" authorId="0" shapeId="0">
+    <comment ref="P11" authorId="0">
       <text>
         <r>
           <rPr>
@@ -85,7 +85,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R16" authorId="0" shapeId="0">
+    <comment ref="R16" authorId="0">
       <text>
         <r>
           <rPr>
@@ -112,7 +112,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P20" authorId="0" shapeId="0">
+    <comment ref="P20" authorId="0">
       <text>
         <r>
           <rPr>
@@ -138,7 +138,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P24" authorId="0" shapeId="0">
+    <comment ref="P24" authorId="0">
       <text>
         <r>
           <rPr>
@@ -164,7 +164,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H25" authorId="0" shapeId="0">
+    <comment ref="H25" authorId="0">
       <text>
         <r>
           <rPr>
@@ -191,7 +191,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J25" authorId="0" shapeId="0">
+    <comment ref="J25" authorId="0">
       <text>
         <r>
           <rPr>
@@ -217,7 +217,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J26" authorId="0" shapeId="0">
+    <comment ref="J26" authorId="0">
       <text>
         <r>
           <rPr>
@@ -243,7 +243,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L26" authorId="0" shapeId="0">
+    <comment ref="L26" authorId="0">
       <text>
         <r>
           <rPr>
@@ -269,7 +269,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P26" authorId="0" shapeId="0">
+    <comment ref="P26" authorId="0">
       <text>
         <r>
           <rPr>
@@ -295,7 +295,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J27" authorId="0" shapeId="0">
+    <comment ref="J27" authorId="0">
       <text>
         <r>
           <rPr>
@@ -331,7 +331,7 @@
     <author>Автор</author>
   </authors>
   <commentList>
-    <comment ref="R3" authorId="0" shapeId="0">
+    <comment ref="R3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -357,7 +357,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F4" authorId="0" shapeId="0">
+    <comment ref="F4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -383,7 +383,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R4" authorId="0" shapeId="0">
+    <comment ref="R4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -410,7 +410,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S4" authorId="0" shapeId="0">
+    <comment ref="S4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -436,7 +436,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T4" authorId="0" shapeId="0">
+    <comment ref="T4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -462,7 +462,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G5" authorId="0" shapeId="0">
+    <comment ref="G5" authorId="0">
       <text>
         <r>
           <rPr>
@@ -488,7 +488,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P5" authorId="0" shapeId="0">
+    <comment ref="P5" authorId="0">
       <text>
         <r>
           <rPr>
@@ -514,7 +514,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P6" authorId="0" shapeId="0">
+    <comment ref="P6" authorId="0">
       <text>
         <r>
           <rPr>
@@ -541,7 +541,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S10" authorId="0" shapeId="0">
+    <comment ref="S10" authorId="0">
       <text>
         <r>
           <rPr>
@@ -567,7 +567,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A11" authorId="0" shapeId="0">
+    <comment ref="A11" authorId="0">
       <text>
         <r>
           <rPr>
@@ -593,7 +593,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R18" authorId="0" shapeId="0">
+    <comment ref="R18" authorId="0">
       <text>
         <r>
           <rPr>
@@ -620,7 +620,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S18" authorId="0" shapeId="0">
+    <comment ref="S18" authorId="0">
       <text>
         <r>
           <rPr>
@@ -646,7 +646,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R19" authorId="0" shapeId="0">
+    <comment ref="R19" authorId="0">
       <text>
         <r>
           <rPr>
@@ -673,7 +673,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S19" authorId="0" shapeId="0">
+    <comment ref="S19" authorId="0">
       <text>
         <r>
           <rPr>
@@ -699,7 +699,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S20" authorId="0" shapeId="0">
+    <comment ref="S20" authorId="0">
       <text>
         <r>
           <rPr>
@@ -725,7 +725,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T20" authorId="0" shapeId="0">
+    <comment ref="T20" authorId="0">
       <text>
         <r>
           <rPr>
@@ -751,7 +751,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S22" authorId="0" shapeId="0">
+    <comment ref="S22" authorId="0">
       <text>
         <r>
           <rPr>
@@ -777,7 +777,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S26" authorId="0" shapeId="0">
+    <comment ref="S26" authorId="0">
       <text>
         <r>
           <rPr>
@@ -813,7 +813,7 @@
     <author>Автор</author>
   </authors>
   <commentList>
-    <comment ref="Q3" authorId="0" shapeId="0">
+    <comment ref="Q3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -829,7 +829,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S3" authorId="0" shapeId="0">
+    <comment ref="S3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -856,7 +856,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T3" authorId="0" shapeId="0">
+    <comment ref="T3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -883,7 +883,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="U3" authorId="0" shapeId="0">
+    <comment ref="U3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -909,7 +909,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H4" authorId="0" shapeId="0">
+    <comment ref="H4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -935,7 +935,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K4" authorId="0" shapeId="0">
+    <comment ref="K4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -961,7 +961,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N4" authorId="0" shapeId="0">
+    <comment ref="N4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -987,7 +987,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q4" authorId="0" shapeId="0">
+    <comment ref="Q4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1014,7 +1014,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S4" authorId="0" shapeId="0">
+    <comment ref="S4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1041,7 +1041,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="U4" authorId="0" shapeId="0">
+    <comment ref="U4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1068,7 +1068,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V4" authorId="0" shapeId="0">
+    <comment ref="V4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1094,7 +1094,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I5" authorId="0" shapeId="0">
+    <comment ref="I5" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1121,7 +1121,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S5" authorId="0" shapeId="0">
+    <comment ref="S5" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1147,7 +1147,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K6" authorId="0" shapeId="0">
+    <comment ref="K6" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1174,7 +1174,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S6" authorId="0" shapeId="0">
+    <comment ref="S6" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1201,7 +1201,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H8" authorId="0" shapeId="0">
+    <comment ref="H8" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1217,7 +1217,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E10" authorId="0" shapeId="0">
+    <comment ref="E10" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1244,7 +1244,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X11" authorId="0" shapeId="0">
+    <comment ref="X11" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1271,7 +1271,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X12" authorId="0" shapeId="0">
+    <comment ref="X12" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1297,7 +1297,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H14" authorId="0" shapeId="0">
+    <comment ref="H14" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1324,7 +1324,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H15" authorId="0" shapeId="0">
+    <comment ref="H15" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1340,7 +1340,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T15" authorId="0" shapeId="0">
+    <comment ref="T15" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1355,7 +1355,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E17" authorId="0" shapeId="0">
+    <comment ref="E17" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1381,7 +1381,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q17" authorId="0" shapeId="0">
+    <comment ref="Q17" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1407,7 +1407,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S19" authorId="0" shapeId="0">
+    <comment ref="S19" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1433,7 +1433,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S21" authorId="0" shapeId="0">
+    <comment ref="S21" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1460,7 +1460,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T21" authorId="0" shapeId="0">
+    <comment ref="T21" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1486,7 +1486,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F22" authorId="0" shapeId="0">
+    <comment ref="F22" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1512,7 +1512,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H22" authorId="0" shapeId="0">
+    <comment ref="H22" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1538,7 +1538,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T22" authorId="0" shapeId="0">
+    <comment ref="T22" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1564,7 +1564,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E24" authorId="0" shapeId="0">
+    <comment ref="E24" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1591,7 +1591,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F25" authorId="0" shapeId="0">
+    <comment ref="F25" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1618,7 +1618,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E27" authorId="0" shapeId="0">
+    <comment ref="E27" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1645,7 +1645,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H29" authorId="0" shapeId="0">
+    <comment ref="H29" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1671,7 +1671,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S29" authorId="0" shapeId="0">
+    <comment ref="S29" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1697,7 +1697,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F30" authorId="0" shapeId="0">
+    <comment ref="F30" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1723,7 +1723,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X30" authorId="0" shapeId="0">
+    <comment ref="X30" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1749,7 +1749,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H31" authorId="0" shapeId="0">
+    <comment ref="H31" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1775,7 +1775,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S33" authorId="0" shapeId="0">
+    <comment ref="S33" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1801,7 +1801,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X35" authorId="0" shapeId="0">
+    <comment ref="X35" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1837,7 +1837,7 @@
     <author>Автор</author>
   </authors>
   <commentList>
-    <comment ref="S3" authorId="0" shapeId="0">
+    <comment ref="S3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1863,7 +1863,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T3" authorId="0" shapeId="0">
+    <comment ref="T3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1890,7 +1890,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H4" authorId="0" shapeId="0">
+    <comment ref="H4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1916,7 +1916,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F5" authorId="0" shapeId="0">
+    <comment ref="F5" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1942,7 +1942,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S5" authorId="0" shapeId="0">
+    <comment ref="S5" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1968,7 +1968,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H6" authorId="0" shapeId="0">
+    <comment ref="H6" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1994,7 +1994,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K7" authorId="0" shapeId="0">
+    <comment ref="K7" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2020,7 +2020,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X7" authorId="0" shapeId="0">
+    <comment ref="X7" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2046,7 +2046,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K8" authorId="0" shapeId="0">
+    <comment ref="K8" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2072,7 +2072,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K9" authorId="0" shapeId="0">
+    <comment ref="K9" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2098,7 +2098,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F10" authorId="0" shapeId="0">
+    <comment ref="F10" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2125,7 +2125,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H11" authorId="0" shapeId="0">
+    <comment ref="H11" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2151,7 +2151,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H13" authorId="0" shapeId="0">
+    <comment ref="H13" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2178,7 +2178,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q19" authorId="0" shapeId="0">
+    <comment ref="Q19" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2204,7 +2204,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S19" authorId="0" shapeId="0">
+    <comment ref="S19" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2230,7 +2230,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T20" authorId="0" shapeId="0">
+    <comment ref="T20" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2257,7 +2257,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H21" authorId="0" shapeId="0">
+    <comment ref="H21" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2283,7 +2283,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T21" authorId="0" shapeId="0">
+    <comment ref="T21" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2310,7 +2310,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X21" authorId="0" shapeId="0">
+    <comment ref="X21" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2336,7 +2336,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J24" authorId="0" shapeId="0">
+    <comment ref="J24" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2362,7 +2362,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S24" authorId="0" shapeId="0">
+    <comment ref="S24" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2388,7 +2388,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V25" authorId="0" shapeId="0">
+    <comment ref="V25" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2414,7 +2414,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H27" authorId="0" shapeId="0">
+    <comment ref="H27" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2440,7 +2440,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S27" authorId="0" shapeId="0">
+    <comment ref="S27" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2466,7 +2466,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H28" authorId="0" shapeId="0">
+    <comment ref="H28" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2492,7 +2492,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V28" authorId="0" shapeId="0">
+    <comment ref="V28" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2519,7 +2519,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X28" authorId="0" shapeId="0">
+    <comment ref="X28" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2545,7 +2545,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E29" authorId="0" shapeId="0">
+    <comment ref="E29" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2571,7 +2571,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X29" authorId="0" shapeId="0">
+    <comment ref="X29" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2597,7 +2597,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S31" authorId="0" shapeId="0">
+    <comment ref="S31" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2623,7 +2623,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S33" authorId="0" shapeId="0">
+    <comment ref="S33" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2649,7 +2649,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X34" authorId="0" shapeId="0">
+    <comment ref="X34" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2686,7 +2686,7 @@
     <author>Автор</author>
   </authors>
   <commentList>
-    <comment ref="F3" authorId="0" shapeId="0">
+    <comment ref="F3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2712,7 +2712,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H3" authorId="0" shapeId="0">
+    <comment ref="H3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2738,7 +2738,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S3" authorId="0" shapeId="0">
+    <comment ref="S3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2764,7 +2764,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T3" authorId="0" shapeId="0">
+    <comment ref="T3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2790,7 +2790,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V3" authorId="0" shapeId="0">
+    <comment ref="V3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2816,7 +2816,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H4" authorId="0" shapeId="0">
+    <comment ref="H4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2842,7 +2842,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N4" authorId="0" shapeId="0">
+    <comment ref="N4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2868,7 +2868,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q4" authorId="0" shapeId="0">
+    <comment ref="Q4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2894,7 +2894,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S4" authorId="0" shapeId="0">
+    <comment ref="S4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2920,7 +2920,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H5" authorId="0" shapeId="0">
+    <comment ref="H5" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2946,7 +2946,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T5" authorId="0" shapeId="0">
+    <comment ref="T5" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2972,7 +2972,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F6" authorId="0" shapeId="0">
+    <comment ref="F6" authorId="0">
       <text>
         <r>
           <rPr>
@@ -2998,7 +2998,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H6" authorId="0" shapeId="0">
+    <comment ref="H6" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3024,7 +3024,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T6" authorId="0" shapeId="0">
+    <comment ref="T6" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3050,7 +3050,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q7" authorId="0" shapeId="0">
+    <comment ref="Q7" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3076,7 +3076,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F8" authorId="0" shapeId="0">
+    <comment ref="F8" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3102,7 +3102,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q8" authorId="0" shapeId="0">
+    <comment ref="Q8" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3128,7 +3128,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S8" authorId="0" shapeId="0">
+    <comment ref="S8" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3154,7 +3154,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q9" authorId="0" shapeId="0">
+    <comment ref="Q9" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3180,7 +3180,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X9" authorId="0" shapeId="0">
+    <comment ref="X9" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3206,7 +3206,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E10" authorId="0" shapeId="0">
+    <comment ref="E10" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3232,7 +3232,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E11" authorId="0" shapeId="0">
+    <comment ref="E11" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3258,7 +3258,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I11" authorId="0" shapeId="0">
+    <comment ref="I11" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3284,7 +3284,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q12" authorId="0" shapeId="0">
+    <comment ref="Q12" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3311,7 +3311,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q13" authorId="0" shapeId="0">
+    <comment ref="Q13" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3337,7 +3337,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S13" authorId="0" shapeId="0">
+    <comment ref="S13" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3363,7 +3363,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X14" authorId="0" shapeId="0">
+    <comment ref="X14" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3389,7 +3389,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X16" authorId="0" shapeId="0">
+    <comment ref="X16" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3415,7 +3415,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H17" authorId="0" shapeId="0">
+    <comment ref="H17" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3442,7 +3442,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S17" authorId="0" shapeId="0">
+    <comment ref="S17" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3468,7 +3468,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T17" authorId="0" shapeId="0">
+    <comment ref="T17" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3494,7 +3494,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H19" authorId="0" shapeId="0">
+    <comment ref="H19" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3520,7 +3520,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N19" authorId="0" shapeId="0">
+    <comment ref="N19" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3556,7 +3556,7 @@
     <author>Автор</author>
   </authors>
   <commentList>
-    <comment ref="Q3" authorId="0" shapeId="0">
+    <comment ref="Q3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3583,7 +3583,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S3" authorId="0" shapeId="0">
+    <comment ref="S3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3609,7 +3609,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H4" authorId="0" shapeId="0">
+    <comment ref="H4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3635,7 +3635,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S5" authorId="0" shapeId="0">
+    <comment ref="S5" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3662,7 +3662,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V6" authorId="0" shapeId="0">
+    <comment ref="V6" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3688,7 +3688,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F7" authorId="0" shapeId="0">
+    <comment ref="F7" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3714,7 +3714,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q8" authorId="0" shapeId="0">
+    <comment ref="Q8" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3741,7 +3741,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S8" authorId="0" shapeId="0">
+    <comment ref="S8" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3768,7 +3768,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S9" authorId="0" shapeId="0">
+    <comment ref="S9" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3794,7 +3794,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E10" authorId="0" shapeId="0">
+    <comment ref="E10" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3820,7 +3820,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S10" authorId="0" shapeId="0">
+    <comment ref="S10" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3846,7 +3846,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q12" authorId="0" shapeId="0">
+    <comment ref="Q12" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3872,7 +3872,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q13" authorId="0" shapeId="0">
+    <comment ref="Q13" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3899,7 +3899,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S13" authorId="0" shapeId="0">
+    <comment ref="S13" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3925,7 +3925,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Y14" authorId="0" shapeId="0">
+    <comment ref="Y14" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3952,7 +3952,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q15" authorId="0" shapeId="0">
+    <comment ref="Q15" authorId="0">
       <text>
         <r>
           <rPr>
@@ -3978,7 +3978,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S15" authorId="0" shapeId="0">
+    <comment ref="S15" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4004,7 +4004,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E16" authorId="0" shapeId="0">
+    <comment ref="E16" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4030,7 +4030,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F16" authorId="0" shapeId="0">
+    <comment ref="F16" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4056,7 +4056,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M16" authorId="0" shapeId="0">
+    <comment ref="M16" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4083,7 +4083,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T16" authorId="0" shapeId="0">
+    <comment ref="T16" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4098,7 +4098,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M17" authorId="0" shapeId="0">
+    <comment ref="M17" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4124,7 +4124,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S17" authorId="0" shapeId="0">
+    <comment ref="S17" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4148,7 +4148,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T17" authorId="0" shapeId="0">
+    <comment ref="T17" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4174,7 +4174,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="U17" authorId="0" shapeId="0">
+    <comment ref="U17" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4200,7 +4200,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Y17" authorId="0" shapeId="0">
+    <comment ref="Y17" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4226,7 +4226,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S18" authorId="0" shapeId="0">
+    <comment ref="S18" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4250,7 +4250,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="U18" authorId="0" shapeId="0">
+    <comment ref="U18" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4274,7 +4274,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E19" authorId="0" shapeId="0">
+    <comment ref="E19" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4300,7 +4300,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V19" authorId="0" shapeId="0">
+    <comment ref="V19" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4324,7 +4324,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Y19" authorId="0" shapeId="0">
+    <comment ref="Y19" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4339,7 +4339,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F21" authorId="0" shapeId="0">
+    <comment ref="F21" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4365,7 +4365,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T21" authorId="0" shapeId="0">
+    <comment ref="T21" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4392,7 +4392,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F23" authorId="0" shapeId="0">
+    <comment ref="F23" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4418,7 +4418,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S23" authorId="0" shapeId="0">
+    <comment ref="S23" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4444,7 +4444,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F24" authorId="0" shapeId="0">
+    <comment ref="F24" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4470,7 +4470,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H25" authorId="0" shapeId="0">
+    <comment ref="H25" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4496,7 +4496,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V25" authorId="0" shapeId="0">
+    <comment ref="V25" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4522,7 +4522,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E27" authorId="0" shapeId="0">
+    <comment ref="E27" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4548,7 +4548,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V27" authorId="0" shapeId="0">
+    <comment ref="V27" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4574,7 +4574,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Y27" authorId="0" shapeId="0">
+    <comment ref="Y27" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4600,7 +4600,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S28" authorId="0" shapeId="0">
+    <comment ref="S28" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4626,7 +4626,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T28" authorId="0" shapeId="0">
+    <comment ref="T28" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4652,7 +4652,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q29" authorId="0" shapeId="0">
+    <comment ref="Q29" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4677,7 +4677,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F30" authorId="0" shapeId="0">
+    <comment ref="F30" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4691,7 +4691,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q30" authorId="0" shapeId="0">
+    <comment ref="Q30" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4715,7 +4715,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Y33" authorId="0" shapeId="0">
+    <comment ref="Y33" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4730,7 +4730,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S34" authorId="0" shapeId="0">
+    <comment ref="S34" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4745,7 +4745,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T34" authorId="0" shapeId="0">
+    <comment ref="T34" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4759,7 +4759,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E35" authorId="0" shapeId="0">
+    <comment ref="E35" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4773,7 +4773,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F35" authorId="0" shapeId="0">
+    <comment ref="F35" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4797,7 +4797,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S35" authorId="0" shapeId="0">
+    <comment ref="S35" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4822,7 +4822,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H36" authorId="0" shapeId="0">
+    <comment ref="H36" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4846,7 +4846,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S36" authorId="0" shapeId="0">
+    <comment ref="S36" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4880,7 +4880,7 @@
     <author>Автор</author>
   </authors>
   <commentList>
-    <comment ref="I4" authorId="0" shapeId="0">
+    <comment ref="I4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4895,7 +4895,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O4" authorId="0" shapeId="0">
+    <comment ref="O4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4909,7 +4909,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P4" authorId="0" shapeId="0">
+    <comment ref="P4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4936,7 +4936,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X4" authorId="0" shapeId="0">
+    <comment ref="X4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4951,7 +4951,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L5" authorId="0" shapeId="0">
+    <comment ref="L5" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4979,7 +4979,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q5" authorId="0" shapeId="0">
+    <comment ref="Q5" authorId="0">
       <text>
         <r>
           <rPr>
@@ -4994,7 +4994,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W5" authorId="0" shapeId="0">
+    <comment ref="W5" authorId="0">
       <text>
         <r>
           <rPr>
@@ -5009,7 +5009,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J6" authorId="0" shapeId="0">
+    <comment ref="J6" authorId="0">
       <text>
         <r>
           <rPr>
@@ -5035,7 +5035,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I7" authorId="0" shapeId="0">
+    <comment ref="I7" authorId="0">
       <text>
         <r>
           <rPr>
@@ -5050,7 +5050,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J7" authorId="0" shapeId="0">
+    <comment ref="J7" authorId="0">
       <text>
         <r>
           <rPr>
@@ -5065,7 +5065,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O7" authorId="0" shapeId="0">
+    <comment ref="O7" authorId="0">
       <text>
         <r>
           <rPr>
@@ -5080,22 +5080,23 @@
         </r>
       </text>
     </comment>
-    <comment ref="Z7" authorId="0" shapeId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="204"/>
-          </rPr>
-          <t>Билеты в IMAX в химках</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="J8" authorId="0" shapeId="0">
+    <comment ref="Z7" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Билеты в IMAX в химках.
+Я их купил, а потом вернул</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J8" authorId="0">
       <text>
         <r>
           <rPr>
@@ -5121,7 +5122,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W8" authorId="0" shapeId="0">
+    <comment ref="W8" authorId="0">
       <text>
         <r>
           <rPr>
@@ -5136,7 +5137,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N9" authorId="0" shapeId="0">
+    <comment ref="N9" authorId="0">
       <text>
         <r>
           <rPr>
@@ -5151,7 +5152,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P9" authorId="0" shapeId="0">
+    <comment ref="P9" authorId="0">
       <text>
         <r>
           <rPr>
@@ -5166,7 +5167,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q10" authorId="0" shapeId="0">
+    <comment ref="Q10" authorId="0">
       <text>
         <r>
           <rPr>
@@ -5180,7 +5181,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W10" authorId="0" shapeId="0">
+    <comment ref="W10" authorId="0">
       <text>
         <r>
           <rPr>
@@ -5194,7 +5195,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X10" authorId="0" shapeId="0">
+    <comment ref="X10" authorId="0">
       <text>
         <r>
           <rPr>
@@ -5218,7 +5219,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W11" authorId="0" shapeId="0">
+    <comment ref="W11" authorId="0">
       <text>
         <r>
           <rPr>
@@ -5243,7 +5244,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K12" authorId="0" shapeId="0">
+    <comment ref="K12" authorId="0">
       <text>
         <r>
           <rPr>
@@ -5267,7 +5268,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W12" authorId="0" shapeId="0">
+    <comment ref="W12" authorId="0">
       <text>
         <r>
           <rPr>
@@ -5291,7 +5292,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I13" authorId="0" shapeId="0">
+    <comment ref="I13" authorId="0">
       <text>
         <r>
           <rPr>
@@ -5315,7 +5316,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W13" authorId="0" shapeId="0">
+    <comment ref="W13" authorId="0">
       <text>
         <r>
           <rPr>
@@ -5339,7 +5340,22 @@
         </r>
       </text>
     </comment>
-    <comment ref="W14" authorId="0" shapeId="0">
+    <comment ref="H14" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Хочука (на Меня, Аню и Фаину)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="W14" authorId="0">
       <text>
         <r>
           <rPr>
@@ -5360,6 +5376,198 @@
           </rPr>
           <t xml:space="preserve">
 Вино для Ани с Фаиной + отказ Ани на ламоде</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D15" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>хлеб в амбаре</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J15" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Шаурма в глобусе
++ вкусно и точка</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="W15" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Коктейль в Энике
++ дублика ключа</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="X15" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Списали на долбанном сайте для редактирования картинок (я наконец-то понял, что это мошенники)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="Z15" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Аэрохоккей с гошей и сашей</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I16" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Феличета на обеде</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N16" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Домашний интернет
++ яндекс плюс</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="X16" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Фотки на загран</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="X18" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Гель для волос</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K20" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Купил себе поке и бабл ти</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="W20" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Перевел Ане, потому что она попросила
++ 1000 на поке</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I21" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Поход в феличету на обед</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AC21" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Мама дала в долг на брюки
+</t>
         </r>
       </text>
     </comment>
@@ -5647,7 +5855,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;₽&quot;"/>
   </numFmts>
@@ -6470,7 +6678,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="165">
+  <cellXfs count="166">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -6892,6 +7100,7 @@
     <xf numFmtId="0" fontId="38" fillId="28" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="23" fillId="21" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -7239,14 +7448,14 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="C3:H17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -7280,7 +7489,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="3:8" ht="15.75">
+    <row r="5" spans="3:8" ht="16.5">
       <c r="C5" s="52" t="s">
         <v>43</v>
       </c>
@@ -7300,7 +7509,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="6" spans="3:8" ht="15.75">
+    <row r="6" spans="3:8" ht="16.5">
       <c r="C6" s="52" t="s">
         <v>44</v>
       </c>
@@ -7321,7 +7530,7 @@
         <v>1260.5599999999977</v>
       </c>
     </row>
-    <row r="7" spans="3:8" ht="15.75">
+    <row r="7" spans="3:8" ht="16.5">
       <c r="C7" s="52" t="s">
         <v>45</v>
       </c>
@@ -7342,7 +7551,7 @@
         <v>-11931.300000000003</v>
       </c>
     </row>
-    <row r="8" spans="3:8" ht="15.75">
+    <row r="8" spans="3:8" ht="16.5">
       <c r="C8" s="52" t="s">
         <v>46</v>
       </c>
@@ -7363,7 +7572,7 @@
         <v>59.059999999997672</v>
       </c>
     </row>
-    <row r="9" spans="3:8" ht="15.75">
+    <row r="9" spans="3:8" ht="16.5">
       <c r="C9" s="52" t="s">
         <v>47</v>
       </c>
@@ -7373,7 +7582,7 @@
       <c r="G9" s="51"/>
       <c r="H9" s="51"/>
     </row>
-    <row r="10" spans="3:8" ht="15.75">
+    <row r="10" spans="3:8" ht="16.5">
       <c r="C10" s="52" t="s">
         <v>48</v>
       </c>
@@ -7383,7 +7592,7 @@
       <c r="G10" s="51"/>
       <c r="H10" s="51"/>
     </row>
-    <row r="11" spans="3:8" ht="15.75">
+    <row r="11" spans="3:8" ht="16.5">
       <c r="C11" s="52" t="s">
         <v>49</v>
       </c>
@@ -7393,7 +7602,7 @@
       <c r="G11" s="51"/>
       <c r="H11" s="51"/>
     </row>
-    <row r="12" spans="3:8" ht="15.75">
+    <row r="12" spans="3:8" ht="16.5">
       <c r="C12" s="52" t="s">
         <v>50</v>
       </c>
@@ -7403,7 +7612,7 @@
       <c r="G12" s="51"/>
       <c r="H12" s="51"/>
     </row>
-    <row r="13" spans="3:8" ht="15.75">
+    <row r="13" spans="3:8" ht="16.5">
       <c r="C13" s="52" t="s">
         <v>51</v>
       </c>
@@ -7413,7 +7622,7 @@
       <c r="G13" s="51"/>
       <c r="H13" s="51"/>
     </row>
-    <row r="14" spans="3:8" ht="15.75">
+    <row r="14" spans="3:8" ht="16.5">
       <c r="C14" s="52" t="s">
         <v>52</v>
       </c>
@@ -7423,7 +7632,7 @@
       <c r="G14" s="51"/>
       <c r="H14" s="51"/>
     </row>
-    <row r="15" spans="3:8" ht="15.75">
+    <row r="15" spans="3:8" ht="16.5">
       <c r="C15" s="52" t="s">
         <v>53</v>
       </c>
@@ -7433,7 +7642,7 @@
       <c r="G15" s="51"/>
       <c r="H15" s="51"/>
     </row>
-    <row r="16" spans="3:8" ht="16.5" thickBot="1">
+    <row r="16" spans="3:8" ht="17.25" thickBot="1">
       <c r="C16" s="53" t="s">
         <v>54</v>
       </c>
@@ -7443,7 +7652,7 @@
       <c r="G16" s="54"/>
       <c r="H16" s="54"/>
     </row>
-    <row r="17" spans="3:8" ht="16.5" thickBot="1">
+    <row r="17" spans="3:8" ht="17.25" thickBot="1">
       <c r="C17" s="55" t="s">
         <v>20</v>
       </c>
@@ -7476,7 +7685,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AT35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -8826,7 +9035,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AT36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -10188,7 +10397,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AU41"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -11986,7 +12195,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AU40"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -13717,7 +13926,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AU40"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -15372,7 +15581,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AV42"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -17330,7 +17539,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AZ41"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -17715,12 +17924,13 @@
       <c r="X7" s="107"/>
       <c r="Y7" s="107"/>
       <c r="Z7" s="107">
-        <v>2626</v>
+        <f>2626-2500</f>
+        <v>126</v>
       </c>
       <c r="AA7" s="108"/>
       <c r="AB7" s="128">
         <f t="shared" si="0"/>
-        <v>8468</v>
+        <v>5968</v>
       </c>
       <c r="AC7" s="117"/>
       <c r="AD7" s="157"/>
@@ -18019,7 +18229,9 @@
       <c r="E14" s="111"/>
       <c r="F14" s="111"/>
       <c r="G14" s="111"/>
-      <c r="H14" s="111"/>
+      <c r="H14" s="111">
+        <v>4470</v>
+      </c>
       <c r="I14" s="111"/>
       <c r="J14" s="111"/>
       <c r="K14" s="111"/>
@@ -18035,8 +18247,8 @@
       <c r="U14" s="111"/>
       <c r="V14" s="111"/>
       <c r="W14" s="111">
-        <f>1319.99</f>
-        <v>1319.99</v>
+        <f>1319.99+329</f>
+        <v>1648.99</v>
       </c>
       <c r="X14" s="111"/>
       <c r="Y14" s="111"/>
@@ -18044,7 +18256,7 @@
       <c r="AA14" s="112"/>
       <c r="AB14" s="128">
         <f t="shared" si="0"/>
-        <v>2293.9300000000003</v>
+        <v>7092.93</v>
       </c>
       <c r="AC14" s="117"/>
       <c r="AD14" s="157"/>
@@ -18057,13 +18269,18 @@
         <v>6</v>
       </c>
       <c r="C15" s="107"/>
-      <c r="D15" s="107"/>
+      <c r="D15" s="107">
+        <v>97.3</v>
+      </c>
       <c r="E15" s="107"/>
       <c r="F15" s="107"/>
       <c r="G15" s="107"/>
       <c r="H15" s="107"/>
       <c r="I15" s="107"/>
-      <c r="J15" s="107"/>
+      <c r="J15" s="107">
+        <f>539.98+147+1271</f>
+        <v>1957.98</v>
+      </c>
       <c r="K15" s="107"/>
       <c r="L15" s="107"/>
       <c r="M15" s="107"/>
@@ -18075,15 +18292,25 @@
       <c r="S15" s="107"/>
       <c r="T15" s="107"/>
       <c r="U15" s="107"/>
-      <c r="V15" s="107"/>
-      <c r="W15" s="107"/>
-      <c r="X15" s="107"/>
+      <c r="V15" s="107">
+        <v>2049</v>
+      </c>
+      <c r="W15" s="107">
+        <f>490+380</f>
+        <v>870</v>
+      </c>
+      <c r="X15" s="107">
+        <v>990</v>
+      </c>
       <c r="Y15" s="107"/>
-      <c r="Z15" s="107"/>
+      <c r="Z15" s="107">
+        <f>170+170+170+170</f>
+        <v>680</v>
+      </c>
       <c r="AA15" s="108"/>
       <c r="AB15" s="128">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>6644.2800000000007</v>
       </c>
       <c r="AC15" s="118"/>
       <c r="AD15" s="157"/>
@@ -18099,14 +18326,22 @@
       <c r="D16" s="111"/>
       <c r="E16" s="111"/>
       <c r="F16" s="111"/>
-      <c r="G16" s="111"/>
+      <c r="G16" s="111">
+        <f>354+1199</f>
+        <v>1553</v>
+      </c>
       <c r="H16" s="111"/>
-      <c r="I16" s="111"/>
+      <c r="I16" s="111">
+        <v>1710</v>
+      </c>
       <c r="J16" s="111"/>
       <c r="K16" s="111"/>
       <c r="L16" s="111"/>
       <c r="M16" s="111"/>
-      <c r="N16" s="111"/>
+      <c r="N16" s="111">
+        <f>700+499</f>
+        <v>1199</v>
+      </c>
       <c r="O16" s="111"/>
       <c r="P16" s="111"/>
       <c r="Q16" s="111"/>
@@ -18114,15 +18349,19 @@
       <c r="S16" s="111"/>
       <c r="T16" s="111"/>
       <c r="U16" s="111"/>
-      <c r="V16" s="111"/>
+      <c r="V16" s="111">
+        <v>313.19</v>
+      </c>
       <c r="W16" s="111"/>
-      <c r="X16" s="111"/>
+      <c r="X16" s="111">
+        <v>330</v>
+      </c>
       <c r="Y16" s="111"/>
       <c r="Z16" s="111"/>
       <c r="AA16" s="112"/>
       <c r="AB16" s="128">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>5105.1899999999996</v>
       </c>
       <c r="AC16" s="117"/>
       <c r="AD16" s="157"/>
@@ -18153,7 +18392,9 @@
       <c r="S17" s="107"/>
       <c r="T17" s="107"/>
       <c r="U17" s="107"/>
-      <c r="V17" s="107"/>
+      <c r="V17" s="107">
+        <v>280.97000000000003</v>
+      </c>
       <c r="W17" s="107"/>
       <c r="X17" s="107"/>
       <c r="Y17" s="107"/>
@@ -18161,7 +18402,7 @@
       <c r="AA17" s="108"/>
       <c r="AB17" s="128">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>280.97000000000003</v>
       </c>
       <c r="AC17" s="117"/>
       <c r="AD17" s="157"/>
@@ -18191,16 +18432,22 @@
       <c r="R18" s="111"/>
       <c r="S18" s="111"/>
       <c r="T18" s="111"/>
-      <c r="U18" s="111"/>
+      <c r="U18" s="111">
+        <f>382+190</f>
+        <v>572</v>
+      </c>
       <c r="V18" s="111"/>
       <c r="W18" s="111"/>
-      <c r="X18" s="111"/>
+      <c r="X18" s="111">
+        <f>384.98</f>
+        <v>384.98</v>
+      </c>
       <c r="Y18" s="111"/>
       <c r="Z18" s="111"/>
       <c r="AA18" s="112"/>
       <c r="AB18" s="128">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>956.98</v>
       </c>
       <c r="AC18" s="117"/>
       <c r="AD18" s="157"/>
@@ -18216,7 +18463,7 @@
       </c>
       <c r="D19" s="113">
         <f t="shared" ref="D19:AA19" si="1">SUM(D4:D18)</f>
-        <v>0</v>
+        <v>97.3</v>
       </c>
       <c r="E19" s="113">
         <f t="shared" si="1"/>
@@ -18228,19 +18475,19 @@
       </c>
       <c r="G19" s="113">
         <f t="shared" si="1"/>
-        <v>821</v>
+        <v>2374</v>
       </c>
       <c r="H19" s="113">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>4470</v>
       </c>
       <c r="I19" s="113">
         <f t="shared" si="1"/>
-        <v>10405</v>
+        <v>12115</v>
       </c>
       <c r="J19" s="113">
         <f t="shared" si="1"/>
-        <v>3102</v>
+        <v>5059.9799999999996</v>
       </c>
       <c r="K19" s="113">
         <f t="shared" si="1"/>
@@ -18256,7 +18503,7 @@
       </c>
       <c r="N19" s="114">
         <f t="shared" si="1"/>
-        <v>1690</v>
+        <v>2889</v>
       </c>
       <c r="O19" s="114">
         <f t="shared" si="1"/>
@@ -18284,19 +18531,19 @@
       </c>
       <c r="U19" s="115">
         <f t="shared" si="1"/>
-        <v>2384</v>
+        <v>2956</v>
       </c>
       <c r="V19" s="115">
         <f t="shared" si="1"/>
-        <v>158.61000000000001</v>
+        <v>2801.7700000000004</v>
       </c>
       <c r="W19" s="115">
         <f t="shared" si="1"/>
-        <v>18026.97</v>
+        <v>19225.97</v>
       </c>
       <c r="X19" s="115">
         <f t="shared" si="1"/>
-        <v>2227</v>
+        <v>3931.98</v>
       </c>
       <c r="Y19" s="115">
         <f t="shared" si="1"/>
@@ -18304,7 +18551,7 @@
       </c>
       <c r="Z19" s="115">
         <f t="shared" si="1"/>
-        <v>2626</v>
+        <v>806</v>
       </c>
       <c r="AA19" s="124">
         <f t="shared" si="1"/>
@@ -18312,7 +18559,7 @@
       </c>
       <c r="AB19" s="129">
         <f>SUM(AB4:AB18)</f>
-        <v>77138.600000000006</v>
+        <v>92425.02</v>
       </c>
       <c r="AC19" s="130">
         <f>SUM(AC4:AC18)</f>
@@ -18320,7 +18567,7 @@
       </c>
       <c r="AD19" s="133">
         <f>AC19-AB19</f>
-        <v>19566.510000000009</v>
+        <v>4280.0900000000111</v>
       </c>
     </row>
     <row r="20" spans="1:32" ht="15.75">
@@ -18330,36 +18577,54 @@
       <c r="B20" s="110" t="s">
         <v>3</v>
       </c>
-      <c r="C20" s="111"/>
-      <c r="D20" s="111"/>
+      <c r="C20" s="111">
+        <f>1527.91-1000</f>
+        <v>527.91000000000008</v>
+      </c>
+      <c r="D20" s="111">
+        <f>399.97</f>
+        <v>399.97</v>
+      </c>
       <c r="E20" s="111"/>
       <c r="F20" s="111"/>
       <c r="G20" s="111"/>
       <c r="H20" s="111"/>
       <c r="I20" s="111"/>
       <c r="J20" s="111"/>
-      <c r="K20" s="111"/>
+      <c r="K20" s="111">
+        <f>880</f>
+        <v>880</v>
+      </c>
       <c r="L20" s="111"/>
       <c r="M20" s="111"/>
       <c r="N20" s="111"/>
       <c r="O20" s="111"/>
       <c r="P20" s="111"/>
       <c r="Q20" s="111"/>
-      <c r="R20" s="111"/>
+      <c r="R20" s="111">
+        <v>1000</v>
+      </c>
       <c r="S20" s="111"/>
       <c r="T20" s="111"/>
-      <c r="U20" s="111"/>
+      <c r="U20" s="111">
+        <v>311</v>
+      </c>
       <c r="V20" s="111"/>
-      <c r="W20" s="111"/>
+      <c r="W20" s="111">
+        <f>2000+1000</f>
+        <v>3000</v>
+      </c>
       <c r="X20" s="111"/>
       <c r="Y20" s="111"/>
       <c r="Z20" s="111"/>
       <c r="AA20" s="112"/>
       <c r="AB20" s="128">
         <f>SUM(C20:AA20)</f>
-        <v>0</v>
-      </c>
-      <c r="AC20" s="118"/>
+        <v>6118.88</v>
+      </c>
+      <c r="AC20" s="118">
+        <v>36738.04</v>
+      </c>
       <c r="AD20" s="157"/>
     </row>
     <row r="21" spans="1:32" ht="15.75">
@@ -18370,12 +18635,20 @@
         <v>4</v>
       </c>
       <c r="C21" s="107"/>
-      <c r="D21" s="107"/>
+      <c r="D21" s="107">
+        <f>231+493.2</f>
+        <v>724.2</v>
+      </c>
       <c r="E21" s="107"/>
-      <c r="F21" s="107"/>
+      <c r="F21" s="107">
+        <v>104</v>
+      </c>
       <c r="G21" s="107"/>
       <c r="H21" s="107"/>
-      <c r="I21" s="107"/>
+      <c r="I21" s="107">
+        <f>170+1740</f>
+        <v>1910</v>
+      </c>
       <c r="J21" s="107"/>
       <c r="K21" s="107"/>
       <c r="L21" s="107"/>
@@ -18387,7 +18660,9 @@
       <c r="R21" s="107"/>
       <c r="S21" s="107"/>
       <c r="T21" s="107"/>
-      <c r="U21" s="107"/>
+      <c r="U21" s="107">
+        <v>243</v>
+      </c>
       <c r="V21" s="107"/>
       <c r="W21" s="107"/>
       <c r="X21" s="107"/>
@@ -18396,9 +18671,11 @@
       <c r="AA21" s="108"/>
       <c r="AB21" s="128">
         <f>SUM(C21:AA21)</f>
-        <v>0</v>
-      </c>
-      <c r="AC21" s="117"/>
+        <v>2981.2</v>
+      </c>
+      <c r="AC21" s="165">
+        <v>10000</v>
+      </c>
       <c r="AD21" s="157"/>
       <c r="AF21" s="44"/>
     </row>
@@ -18955,11 +19232,11 @@
       <c r="B36" s="158"/>
       <c r="C36" s="113">
         <f>SUM(C20:C35)</f>
-        <v>0</v>
+        <v>527.91000000000008</v>
       </c>
       <c r="D36" s="113">
         <f t="shared" ref="D36:K36" si="3">SUM(D20:D35)</f>
-        <v>0</v>
+        <v>1124.17</v>
       </c>
       <c r="E36" s="113">
         <f t="shared" si="3"/>
@@ -18967,7 +19244,7 @@
       </c>
       <c r="F36" s="113">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="G36" s="113">
         <f t="shared" si="3"/>
@@ -18979,7 +19256,7 @@
       </c>
       <c r="I36" s="113">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1910</v>
       </c>
       <c r="J36" s="113">
         <f t="shared" si="3"/>
@@ -18987,7 +19264,7 @@
       </c>
       <c r="K36" s="113">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>880</v>
       </c>
       <c r="L36" s="114">
         <f>SUM(L20:L35)</f>
@@ -19015,7 +19292,7 @@
       </c>
       <c r="R36" s="115">
         <f>SUM(R20:R35)</f>
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="S36" s="115">
         <f t="shared" ref="S36:AA36" si="5">SUM(S20:S35)</f>
@@ -19027,7 +19304,7 @@
       </c>
       <c r="U36" s="115">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>554</v>
       </c>
       <c r="V36" s="115">
         <f t="shared" si="5"/>
@@ -19035,7 +19312,7 @@
       </c>
       <c r="W36" s="115">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="X36" s="115">
         <f t="shared" si="5"/>
@@ -19055,15 +19332,15 @@
       </c>
       <c r="AB36" s="129">
         <f>SUM(AB20:AB35)</f>
-        <v>0</v>
+        <v>9100.08</v>
       </c>
       <c r="AC36" s="130">
         <f>SUM(AC20:AC35)</f>
-        <v>0</v>
+        <v>46738.04</v>
       </c>
       <c r="AD36" s="133">
         <f>AC36-AB36</f>
-        <v>0</v>
+        <v>37637.96</v>
       </c>
     </row>
     <row r="37" spans="1:30" ht="31.5" customHeight="1">
@@ -19073,30 +19350,30 @@
       <c r="B37" s="155"/>
       <c r="C37" s="116">
         <f>SUM(C19,C36)</f>
-        <v>1403.89</v>
+        <v>1931.8000000000002</v>
       </c>
       <c r="D37" s="116"/>
       <c r="E37" s="116"/>
       <c r="F37" s="116">
         <f t="shared" ref="F37:AB37" si="6">SUM(F19,F36)</f>
-        <v>2446</v>
+        <v>2550</v>
       </c>
       <c r="G37" s="116"/>
       <c r="H37" s="116">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>4470</v>
       </c>
       <c r="I37" s="116">
         <f t="shared" si="6"/>
-        <v>10405</v>
+        <v>14025</v>
       </c>
       <c r="J37" s="116">
         <f t="shared" si="6"/>
-        <v>3102</v>
+        <v>5059.9799999999996</v>
       </c>
       <c r="K37" s="116">
         <f t="shared" si="6"/>
-        <v>2280</v>
+        <v>3160</v>
       </c>
       <c r="L37" s="116">
         <f t="shared" si="6"/>
@@ -19108,14 +19385,14 @@
       </c>
       <c r="N37" s="116">
         <f t="shared" si="6"/>
-        <v>1690</v>
+        <v>2889</v>
       </c>
       <c r="O37" s="116"/>
       <c r="P37" s="116"/>
       <c r="Q37" s="116"/>
       <c r="R37" s="116">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="S37" s="116"/>
       <c r="T37" s="116">
@@ -19124,19 +19401,19 @@
       </c>
       <c r="U37" s="116">
         <f t="shared" si="6"/>
-        <v>2384</v>
+        <v>3510</v>
       </c>
       <c r="V37" s="116">
         <f t="shared" si="6"/>
-        <v>158.61000000000001</v>
+        <v>2801.7700000000004</v>
       </c>
       <c r="W37" s="116">
         <f t="shared" si="6"/>
-        <v>18026.97</v>
+        <v>22225.97</v>
       </c>
       <c r="X37" s="116">
         <f t="shared" si="6"/>
-        <v>2227</v>
+        <v>3931.98</v>
       </c>
       <c r="Y37" s="116">
         <f t="shared" si="6"/>
@@ -19144,7 +19421,7 @@
       </c>
       <c r="Z37" s="116">
         <f>SUM(Z19,Z36)</f>
-        <v>2626</v>
+        <v>806</v>
       </c>
       <c r="AA37" s="125">
         <f t="shared" si="6"/>
@@ -19152,15 +19429,15 @@
       </c>
       <c r="AB37" s="131">
         <f t="shared" si="6"/>
-        <v>77138.600000000006</v>
+        <v>101525.1</v>
       </c>
       <c r="AC37" s="132">
         <f>SUM(AC19,AC36)</f>
-        <v>96705.110000000015</v>
+        <v>143443.15000000002</v>
       </c>
       <c r="AD37" s="134">
         <f>SUM(AD19,AD36)</f>
-        <v>19566.510000000009</v>
+        <v>41918.05000000001</v>
       </c>
     </row>
     <row r="41" spans="1:30">

--- a/Другое/2026/Доходы-Расходы_copy.xlsx
+++ b/Другое/2026/Доходы-Расходы_copy.xlsx
@@ -5568,6 +5568,100 @@
           </rPr>
           <t xml:space="preserve">Мама дала в долг на брюки
 </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J23" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Мак завтрак
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="W23" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Отказ Ани на ламоде
++ цветы</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H24" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Хочука</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K24" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Обед в феличите</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K25" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Обед во вьет куке</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="W25" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Мы поругались и Аня просто с утра сказала "Переведи мне 6к"</t>
         </r>
       </text>
     </comment>
@@ -7016,6 +7110,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="23" fillId="20" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="23" fillId="21" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -7055,6 +7150,12 @@
     <xf numFmtId="0" fontId="25" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="35" fillId="28" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="17" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="28" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -7062,12 +7163,6 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="23" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="28" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="17" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="33" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -7100,7 +7195,6 @@
     <xf numFmtId="0" fontId="38" fillId="28" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="21" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -7448,7 +7542,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -7695,32 +7789,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:46" ht="60.75" customHeight="1">
-      <c r="A1" s="137" t="s">
+      <c r="A1" s="138" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="137"/>
-      <c r="C1" s="137"/>
-      <c r="D1" s="137"/>
-      <c r="E1" s="137"/>
-      <c r="F1" s="137"/>
-      <c r="G1" s="137"/>
-      <c r="H1" s="137"/>
-      <c r="I1" s="137"/>
-      <c r="J1" s="137"/>
-      <c r="K1" s="137"/>
-      <c r="L1" s="137"/>
-      <c r="M1" s="137"/>
-      <c r="N1" s="137"/>
-      <c r="O1" s="137"/>
-      <c r="P1" s="137"/>
-      <c r="Q1" s="137"/>
-      <c r="R1" s="137"/>
-      <c r="S1" s="137"/>
-      <c r="T1" s="137"/>
-      <c r="U1" s="137"/>
-      <c r="V1" s="137"/>
-      <c r="W1" s="137"/>
-      <c r="X1" s="137"/>
+      <c r="B1" s="138"/>
+      <c r="C1" s="138"/>
+      <c r="D1" s="138"/>
+      <c r="E1" s="138"/>
+      <c r="F1" s="138"/>
+      <c r="G1" s="138"/>
+      <c r="H1" s="138"/>
+      <c r="I1" s="138"/>
+      <c r="J1" s="138"/>
+      <c r="K1" s="138"/>
+      <c r="L1" s="138"/>
+      <c r="M1" s="138"/>
+      <c r="N1" s="138"/>
+      <c r="O1" s="138"/>
+      <c r="P1" s="138"/>
+      <c r="Q1" s="138"/>
+      <c r="R1" s="138"/>
+      <c r="S1" s="138"/>
+      <c r="T1" s="138"/>
+      <c r="U1" s="138"/>
+      <c r="V1" s="138"/>
+      <c r="W1" s="138"/>
+      <c r="X1" s="138"/>
     </row>
     <row r="2" spans="1:46" ht="45" customHeight="1">
       <c r="A2" s="3" t="s">
@@ -8919,10 +9013,10 @@
       </c>
     </row>
     <row r="31" spans="1:24">
-      <c r="A31" s="138" t="s">
+      <c r="A31" s="139" t="s">
         <v>20</v>
       </c>
-      <c r="B31" s="138"/>
+      <c r="B31" s="139"/>
       <c r="C31" s="13">
         <f>SUM(C3:C30)</f>
         <v>19992.27</v>
@@ -9045,32 +9139,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:46" ht="60.75" customHeight="1">
-      <c r="A1" s="140" t="s">
+      <c r="A1" s="141" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="140"/>
-      <c r="C1" s="140"/>
-      <c r="D1" s="140"/>
-      <c r="E1" s="140"/>
-      <c r="F1" s="140"/>
-      <c r="G1" s="140"/>
-      <c r="H1" s="140"/>
-      <c r="I1" s="140"/>
-      <c r="J1" s="140"/>
-      <c r="K1" s="140"/>
-      <c r="L1" s="140"/>
-      <c r="M1" s="140"/>
-      <c r="N1" s="140"/>
-      <c r="O1" s="140"/>
-      <c r="P1" s="140"/>
-      <c r="Q1" s="140"/>
-      <c r="R1" s="140"/>
-      <c r="S1" s="140"/>
-      <c r="T1" s="140"/>
-      <c r="U1" s="140"/>
-      <c r="V1" s="140"/>
-      <c r="W1" s="140"/>
-      <c r="X1" s="140"/>
+      <c r="B1" s="141"/>
+      <c r="C1" s="141"/>
+      <c r="D1" s="141"/>
+      <c r="E1" s="141"/>
+      <c r="F1" s="141"/>
+      <c r="G1" s="141"/>
+      <c r="H1" s="141"/>
+      <c r="I1" s="141"/>
+      <c r="J1" s="141"/>
+      <c r="K1" s="141"/>
+      <c r="L1" s="141"/>
+      <c r="M1" s="141"/>
+      <c r="N1" s="141"/>
+      <c r="O1" s="141"/>
+      <c r="P1" s="141"/>
+      <c r="Q1" s="141"/>
+      <c r="R1" s="141"/>
+      <c r="S1" s="141"/>
+      <c r="T1" s="141"/>
+      <c r="U1" s="141"/>
+      <c r="V1" s="141"/>
+      <c r="W1" s="141"/>
+      <c r="X1" s="141"/>
     </row>
     <row r="2" spans="1:46" ht="45" customHeight="1">
       <c r="A2" s="30" t="s">
@@ -10281,10 +10375,10 @@
       <c r="X31" s="31"/>
     </row>
     <row r="32" spans="1:24">
-      <c r="A32" s="139" t="s">
+      <c r="A32" s="140" t="s">
         <v>20</v>
       </c>
-      <c r="B32" s="139"/>
+      <c r="B32" s="140"/>
       <c r="C32" s="28">
         <f>SUM(C3:C31)</f>
         <v>16843.349999999999</v>
@@ -10407,33 +10501,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:47" ht="60.75" customHeight="1">
-      <c r="A1" s="140" t="s">
+      <c r="A1" s="141" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="140"/>
-      <c r="C1" s="140"/>
-      <c r="D1" s="140"/>
-      <c r="E1" s="140"/>
-      <c r="F1" s="140"/>
-      <c r="G1" s="140"/>
-      <c r="H1" s="140"/>
-      <c r="I1" s="140"/>
-      <c r="J1" s="140"/>
-      <c r="K1" s="140"/>
-      <c r="L1" s="140"/>
-      <c r="M1" s="140"/>
-      <c r="N1" s="140"/>
-      <c r="O1" s="140"/>
-      <c r="P1" s="140"/>
-      <c r="Q1" s="140"/>
-      <c r="R1" s="140"/>
-      <c r="S1" s="140"/>
-      <c r="T1" s="140"/>
-      <c r="U1" s="140"/>
-      <c r="V1" s="140"/>
-      <c r="W1" s="140"/>
-      <c r="X1" s="140"/>
-      <c r="Y1" s="140"/>
+      <c r="B1" s="141"/>
+      <c r="C1" s="141"/>
+      <c r="D1" s="141"/>
+      <c r="E1" s="141"/>
+      <c r="F1" s="141"/>
+      <c r="G1" s="141"/>
+      <c r="H1" s="141"/>
+      <c r="I1" s="141"/>
+      <c r="J1" s="141"/>
+      <c r="K1" s="141"/>
+      <c r="L1" s="141"/>
+      <c r="M1" s="141"/>
+      <c r="N1" s="141"/>
+      <c r="O1" s="141"/>
+      <c r="P1" s="141"/>
+      <c r="Q1" s="141"/>
+      <c r="R1" s="141"/>
+      <c r="S1" s="141"/>
+      <c r="T1" s="141"/>
+      <c r="U1" s="141"/>
+      <c r="V1" s="141"/>
+      <c r="W1" s="141"/>
+      <c r="X1" s="141"/>
+      <c r="Y1" s="141"/>
     </row>
     <row r="2" spans="1:47" ht="45" customHeight="1">
       <c r="A2" s="30" t="s">
@@ -11251,10 +11345,10 @@
       <c r="Y19" s="43"/>
     </row>
     <row r="20" spans="1:27">
-      <c r="A20" s="142" t="s">
+      <c r="A20" s="143" t="s">
         <v>35</v>
       </c>
-      <c r="B20" s="143"/>
+      <c r="B20" s="144"/>
       <c r="C20" s="45">
         <f>SUM(C3:C19)</f>
         <v>12278.83</v>
@@ -11974,10 +12068,10 @@
       <c r="Y35" s="43"/>
     </row>
     <row r="36" spans="1:25">
-      <c r="A36" s="142" t="s">
+      <c r="A36" s="143" t="s">
         <v>36</v>
       </c>
-      <c r="B36" s="143"/>
+      <c r="B36" s="144"/>
       <c r="C36" s="45">
         <f>SUM(C21:C35)</f>
         <v>11057.89</v>
@@ -12072,10 +12166,10 @@
       </c>
     </row>
     <row r="37" spans="1:25" ht="31.5" customHeight="1">
-      <c r="A37" s="141" t="s">
+      <c r="A37" s="142" t="s">
         <v>37</v>
       </c>
-      <c r="B37" s="141"/>
+      <c r="B37" s="142"/>
       <c r="C37" s="48">
         <f>SUM(C20,C36)</f>
         <v>23336.720000000001</v>
@@ -12205,33 +12299,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:47" ht="60.75" customHeight="1">
-      <c r="A1" s="144" t="s">
+      <c r="A1" s="145" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="144"/>
-      <c r="C1" s="144"/>
-      <c r="D1" s="144"/>
-      <c r="E1" s="144"/>
-      <c r="F1" s="144"/>
-      <c r="G1" s="144"/>
-      <c r="H1" s="144"/>
-      <c r="I1" s="144"/>
-      <c r="J1" s="144"/>
-      <c r="K1" s="144"/>
-      <c r="L1" s="144"/>
-      <c r="M1" s="144"/>
-      <c r="N1" s="144"/>
-      <c r="O1" s="144"/>
-      <c r="P1" s="144"/>
-      <c r="Q1" s="144"/>
-      <c r="R1" s="144"/>
-      <c r="S1" s="144"/>
-      <c r="T1" s="144"/>
-      <c r="U1" s="144"/>
-      <c r="V1" s="144"/>
-      <c r="W1" s="144"/>
-      <c r="X1" s="144"/>
-      <c r="Y1" s="144"/>
+      <c r="B1" s="145"/>
+      <c r="C1" s="145"/>
+      <c r="D1" s="145"/>
+      <c r="E1" s="145"/>
+      <c r="F1" s="145"/>
+      <c r="G1" s="145"/>
+      <c r="H1" s="145"/>
+      <c r="I1" s="145"/>
+      <c r="J1" s="145"/>
+      <c r="K1" s="145"/>
+      <c r="L1" s="145"/>
+      <c r="M1" s="145"/>
+      <c r="N1" s="145"/>
+      <c r="O1" s="145"/>
+      <c r="P1" s="145"/>
+      <c r="Q1" s="145"/>
+      <c r="R1" s="145"/>
+      <c r="S1" s="145"/>
+      <c r="T1" s="145"/>
+      <c r="U1" s="145"/>
+      <c r="V1" s="145"/>
+      <c r="W1" s="145"/>
+      <c r="X1" s="145"/>
+      <c r="Y1" s="145"/>
     </row>
     <row r="2" spans="1:47" ht="45" customHeight="1">
       <c r="A2" s="59" t="s">
@@ -12941,10 +13035,10 @@
       <c r="Y17" s="65"/>
     </row>
     <row r="18" spans="1:27">
-      <c r="A18" s="145" t="s">
+      <c r="A18" s="146" t="s">
         <v>35</v>
       </c>
-      <c r="B18" s="145"/>
+      <c r="B18" s="146"/>
       <c r="C18" s="73">
         <f t="shared" ref="C18:X18" si="1">SUM(C3:C17)</f>
         <v>8428.35</v>
@@ -13697,10 +13791,10 @@
       <c r="Y34" s="69"/>
     </row>
     <row r="35" spans="1:25">
-      <c r="A35" s="145" t="s">
+      <c r="A35" s="146" t="s">
         <v>36</v>
       </c>
-      <c r="B35" s="145"/>
+      <c r="B35" s="146"/>
       <c r="C35" s="73">
         <f>SUM(C19:C34)</f>
         <v>10739.46</v>
@@ -13795,10 +13889,10 @@
       </c>
     </row>
     <row r="36" spans="1:25" ht="31.5" customHeight="1">
-      <c r="A36" s="146" t="s">
+      <c r="A36" s="147" t="s">
         <v>37</v>
       </c>
-      <c r="B36" s="146"/>
+      <c r="B36" s="147"/>
       <c r="C36" s="70">
         <f>SUM(C18,C35)</f>
         <v>19167.809999999998</v>
@@ -13936,33 +14030,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:47" ht="60.75" customHeight="1">
-      <c r="A1" s="147" t="s">
+      <c r="A1" s="148" t="s">
         <v>58</v>
       </c>
-      <c r="B1" s="147"/>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="147"/>
-      <c r="F1" s="147"/>
-      <c r="G1" s="147"/>
-      <c r="H1" s="147"/>
-      <c r="I1" s="147"/>
-      <c r="J1" s="147"/>
-      <c r="K1" s="147"/>
-      <c r="L1" s="147"/>
-      <c r="M1" s="147"/>
-      <c r="N1" s="147"/>
-      <c r="O1" s="147"/>
-      <c r="P1" s="147"/>
-      <c r="Q1" s="147"/>
-      <c r="R1" s="147"/>
-      <c r="S1" s="147"/>
-      <c r="T1" s="147"/>
-      <c r="U1" s="147"/>
-      <c r="V1" s="147"/>
-      <c r="W1" s="147"/>
-      <c r="X1" s="147"/>
-      <c r="Y1" s="147"/>
+      <c r="B1" s="148"/>
+      <c r="C1" s="148"/>
+      <c r="D1" s="148"/>
+      <c r="E1" s="148"/>
+      <c r="F1" s="148"/>
+      <c r="G1" s="148"/>
+      <c r="H1" s="148"/>
+      <c r="I1" s="148"/>
+      <c r="J1" s="148"/>
+      <c r="K1" s="148"/>
+      <c r="L1" s="148"/>
+      <c r="M1" s="148"/>
+      <c r="N1" s="148"/>
+      <c r="O1" s="148"/>
+      <c r="P1" s="148"/>
+      <c r="Q1" s="148"/>
+      <c r="R1" s="148"/>
+      <c r="S1" s="148"/>
+      <c r="T1" s="148"/>
+      <c r="U1" s="148"/>
+      <c r="V1" s="148"/>
+      <c r="W1" s="148"/>
+      <c r="X1" s="148"/>
+      <c r="Y1" s="148"/>
     </row>
     <row r="2" spans="1:47" ht="45" customHeight="1">
       <c r="A2" s="76" t="s">
@@ -14701,10 +14795,10 @@
       <c r="Y17" s="65"/>
     </row>
     <row r="18" spans="1:27">
-      <c r="A18" s="148" t="s">
+      <c r="A18" s="149" t="s">
         <v>35</v>
       </c>
-      <c r="B18" s="148"/>
+      <c r="B18" s="149"/>
       <c r="C18" s="79">
         <f t="shared" ref="C18:X18" si="1">SUM(C3:C17)</f>
         <v>7904</v>
@@ -15352,10 +15446,10 @@
       <c r="Y34" s="69"/>
     </row>
     <row r="35" spans="1:25">
-      <c r="A35" s="148" t="s">
+      <c r="A35" s="149" t="s">
         <v>36</v>
       </c>
-      <c r="B35" s="148"/>
+      <c r="B35" s="149"/>
       <c r="C35" s="79">
         <f>SUM(C19:C34)</f>
         <v>0</v>
@@ -15450,10 +15544,10 @@
       </c>
     </row>
     <row r="36" spans="1:25" ht="31.5" customHeight="1">
-      <c r="A36" s="149" t="s">
+      <c r="A36" s="150" t="s">
         <v>37</v>
       </c>
-      <c r="B36" s="149"/>
+      <c r="B36" s="150"/>
       <c r="C36" s="74">
         <f>SUM(C18,C35)</f>
         <v>7904</v>
@@ -15593,34 +15687,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:48" ht="60.75" customHeight="1">
-      <c r="A1" s="150" t="s">
+      <c r="A1" s="153" t="s">
         <v>59</v>
       </c>
-      <c r="B1" s="150"/>
-      <c r="C1" s="150"/>
-      <c r="D1" s="150"/>
-      <c r="E1" s="150"/>
-      <c r="F1" s="150"/>
-      <c r="G1" s="150"/>
-      <c r="H1" s="150"/>
-      <c r="I1" s="150"/>
-      <c r="J1" s="150"/>
-      <c r="K1" s="150"/>
-      <c r="L1" s="150"/>
-      <c r="M1" s="150"/>
-      <c r="N1" s="150"/>
-      <c r="O1" s="150"/>
-      <c r="P1" s="150"/>
-      <c r="Q1" s="150"/>
-      <c r="R1" s="150"/>
-      <c r="S1" s="150"/>
-      <c r="T1" s="150"/>
-      <c r="U1" s="150"/>
-      <c r="V1" s="150"/>
-      <c r="W1" s="150"/>
-      <c r="X1" s="150"/>
-      <c r="Y1" s="150"/>
-      <c r="Z1" s="150"/>
+      <c r="B1" s="153"/>
+      <c r="C1" s="153"/>
+      <c r="D1" s="153"/>
+      <c r="E1" s="153"/>
+      <c r="F1" s="153"/>
+      <c r="G1" s="153"/>
+      <c r="H1" s="153"/>
+      <c r="I1" s="153"/>
+      <c r="J1" s="153"/>
+      <c r="K1" s="153"/>
+      <c r="L1" s="153"/>
+      <c r="M1" s="153"/>
+      <c r="N1" s="153"/>
+      <c r="O1" s="153"/>
+      <c r="P1" s="153"/>
+      <c r="Q1" s="153"/>
+      <c r="R1" s="153"/>
+      <c r="S1" s="153"/>
+      <c r="T1" s="153"/>
+      <c r="U1" s="153"/>
+      <c r="V1" s="153"/>
+      <c r="W1" s="153"/>
+      <c r="X1" s="153"/>
+      <c r="Y1" s="153"/>
+      <c r="Z1" s="153"/>
     </row>
     <row r="2" spans="1:48" ht="45" customHeight="1">
       <c r="A2" s="76" t="s">
@@ -15773,7 +15867,7 @@
         <f>(94085+57723.67)</f>
         <v>151808.66999999998</v>
       </c>
-      <c r="Z3" s="152"/>
+      <c r="Z3" s="155"/>
     </row>
     <row r="4" spans="1:48" ht="15.75">
       <c r="A4" s="66">
@@ -15823,7 +15917,7 @@
       </c>
       <c r="X4" s="90"/>
       <c r="Y4" s="93"/>
-      <c r="Z4" s="152"/>
+      <c r="Z4" s="155"/>
     </row>
     <row r="5" spans="1:48" ht="15.75">
       <c r="A5" s="62">
@@ -15863,7 +15957,7 @@
       </c>
       <c r="X5" s="90"/>
       <c r="Y5" s="93"/>
-      <c r="Z5" s="152"/>
+      <c r="Z5" s="155"/>
     </row>
     <row r="6" spans="1:48" ht="15.75">
       <c r="A6" s="66">
@@ -15904,7 +15998,7 @@
       </c>
       <c r="X6" s="90"/>
       <c r="Y6" s="93"/>
-      <c r="Z6" s="152"/>
+      <c r="Z6" s="155"/>
     </row>
     <row r="7" spans="1:48" ht="15" customHeight="1">
       <c r="A7" s="62">
@@ -15948,7 +16042,7 @@
       </c>
       <c r="X7" s="90"/>
       <c r="Y7" s="93"/>
-      <c r="Z7" s="152"/>
+      <c r="Z7" s="155"/>
     </row>
     <row r="8" spans="1:48" ht="15.75">
       <c r="A8" s="66">
@@ -15990,14 +16084,14 @@
       </c>
       <c r="X8" s="90"/>
       <c r="Y8" s="93"/>
-      <c r="Z8" s="152"/>
-      <c r="AC8" s="154" t="s">
+      <c r="Z8" s="155"/>
+      <c r="AC8" s="152" t="s">
         <v>61</v>
       </c>
-      <c r="AD8" s="154"/>
-      <c r="AE8" s="154"/>
-      <c r="AF8" s="154"/>
-      <c r="AG8" s="154"/>
+      <c r="AD8" s="152"/>
+      <c r="AE8" s="152"/>
+      <c r="AF8" s="152"/>
+      <c r="AG8" s="152"/>
     </row>
     <row r="9" spans="1:48" ht="15.75">
       <c r="A9" s="62">
@@ -16036,12 +16130,12 @@
       </c>
       <c r="X9" s="90"/>
       <c r="Y9" s="93"/>
-      <c r="Z9" s="152"/>
-      <c r="AC9" s="154"/>
-      <c r="AD9" s="154"/>
-      <c r="AE9" s="154"/>
-      <c r="AF9" s="154"/>
-      <c r="AG9" s="154"/>
+      <c r="Z9" s="155"/>
+      <c r="AC9" s="152"/>
+      <c r="AD9" s="152"/>
+      <c r="AE9" s="152"/>
+      <c r="AF9" s="152"/>
+      <c r="AG9" s="152"/>
     </row>
     <row r="10" spans="1:48" ht="15.75">
       <c r="A10" s="66">
@@ -16085,12 +16179,12 @@
       </c>
       <c r="X10" s="90"/>
       <c r="Y10" s="93"/>
-      <c r="Z10" s="152"/>
-      <c r="AC10" s="154"/>
-      <c r="AD10" s="154"/>
-      <c r="AE10" s="154"/>
-      <c r="AF10" s="154"/>
-      <c r="AG10" s="154"/>
+      <c r="Z10" s="155"/>
+      <c r="AC10" s="152"/>
+      <c r="AD10" s="152"/>
+      <c r="AE10" s="152"/>
+      <c r="AF10" s="152"/>
+      <c r="AG10" s="152"/>
     </row>
     <row r="11" spans="1:48" ht="15.75">
       <c r="A11" s="62">
@@ -16130,13 +16224,13 @@
       </c>
       <c r="X11" s="90"/>
       <c r="Y11" s="93"/>
-      <c r="Z11" s="152"/>
-      <c r="AC11" s="153" t="s">
+      <c r="Z11" s="155"/>
+      <c r="AC11" s="151" t="s">
         <v>62</v>
       </c>
-      <c r="AD11" s="153"/>
-      <c r="AE11" s="153"/>
-      <c r="AF11" s="153"/>
+      <c r="AD11" s="151"/>
+      <c r="AE11" s="151"/>
+      <c r="AF11" s="151"/>
       <c r="AG11" s="104">
         <f>Y3+Y14+Y21</f>
         <v>226341.31</v>
@@ -16177,13 +16271,13 @@
       </c>
       <c r="X12" s="90"/>
       <c r="Y12" s="93"/>
-      <c r="Z12" s="152"/>
-      <c r="AC12" s="153" t="s">
+      <c r="Z12" s="155"/>
+      <c r="AC12" s="151" t="s">
         <v>55</v>
       </c>
-      <c r="AD12" s="153"/>
-      <c r="AE12" s="153"/>
-      <c r="AF12" s="153"/>
+      <c r="AD12" s="151"/>
+      <c r="AE12" s="151"/>
+      <c r="AF12" s="151"/>
       <c r="AG12" s="104">
         <f>Y27</f>
         <v>20000</v>
@@ -16228,13 +16322,13 @@
       </c>
       <c r="X13" s="90"/>
       <c r="Y13" s="93"/>
-      <c r="Z13" s="152"/>
-      <c r="AC13" s="153" t="s">
+      <c r="Z13" s="155"/>
+      <c r="AC13" s="151" t="s">
         <v>63</v>
       </c>
-      <c r="AD13" s="153"/>
-      <c r="AE13" s="153"/>
-      <c r="AF13" s="153"/>
+      <c r="AD13" s="151"/>
+      <c r="AE13" s="151"/>
+      <c r="AF13" s="151"/>
       <c r="AG13" s="104">
         <f>Y17+Y19</f>
         <v>25000</v>
@@ -16280,13 +16374,13 @@
       <c r="Y14" s="99">
         <v>37634</v>
       </c>
-      <c r="Z14" s="152"/>
-      <c r="AC14" s="153" t="s">
+      <c r="Z14" s="155"/>
+      <c r="AC14" s="151" t="s">
         <v>64</v>
       </c>
-      <c r="AD14" s="153"/>
-      <c r="AE14" s="153"/>
-      <c r="AF14" s="153"/>
+      <c r="AD14" s="151"/>
+      <c r="AE14" s="151"/>
+      <c r="AF14" s="151"/>
       <c r="AG14" s="104">
         <f>W38</f>
         <v>177971.36</v>
@@ -16336,13 +16430,13 @@
       </c>
       <c r="X15" s="90"/>
       <c r="Y15" s="93"/>
-      <c r="Z15" s="152"/>
-      <c r="AC15" s="153" t="s">
+      <c r="Z15" s="155"/>
+      <c r="AC15" s="151" t="s">
         <v>65</v>
       </c>
-      <c r="AD15" s="153"/>
-      <c r="AE15" s="153"/>
-      <c r="AF15" s="153"/>
+      <c r="AD15" s="151"/>
+      <c r="AE15" s="151"/>
+      <c r="AF15" s="151"/>
       <c r="AG15" s="104">
         <f>SUM(C38:H38)</f>
         <v>55416.04</v>
@@ -16391,7 +16485,7 @@
       </c>
       <c r="X16" s="90"/>
       <c r="Y16" s="93"/>
-      <c r="Z16" s="152"/>
+      <c r="Z16" s="155"/>
     </row>
     <row r="17" spans="1:28" ht="15.75">
       <c r="A17" s="62">
@@ -16443,7 +16537,7 @@
       <c r="Y17" s="100">
         <v>15000</v>
       </c>
-      <c r="Z17" s="152"/>
+      <c r="Z17" s="155"/>
     </row>
     <row r="18" spans="1:28" ht="15.75">
       <c r="A18" s="66">
@@ -16484,7 +16578,7 @@
       </c>
       <c r="X18" s="90"/>
       <c r="Y18" s="93"/>
-      <c r="Z18" s="152"/>
+      <c r="Z18" s="155"/>
     </row>
     <row r="19" spans="1:28" ht="15.75">
       <c r="A19" s="62">
@@ -16528,13 +16622,13 @@
       <c r="Y19" s="100">
         <v>10000</v>
       </c>
-      <c r="Z19" s="152"/>
+      <c r="Z19" s="155"/>
     </row>
     <row r="20" spans="1:28" ht="14.25" customHeight="1">
-      <c r="A20" s="148" t="s">
+      <c r="A20" s="149" t="s">
         <v>35</v>
       </c>
-      <c r="B20" s="148"/>
+      <c r="B20" s="149"/>
       <c r="C20" s="79">
         <f t="shared" ref="C20:V20" si="1">SUM(C3:C17)</f>
         <v>10942.99</v>
@@ -16677,7 +16771,7 @@
       <c r="Y21" s="99">
         <v>36898.639999999999</v>
       </c>
-      <c r="Z21" s="152"/>
+      <c r="Z21" s="155"/>
     </row>
     <row r="22" spans="1:28" ht="15.75">
       <c r="A22" s="66">
@@ -16723,7 +16817,7 @@
         <v>23662.84</v>
       </c>
       <c r="Y22" s="93"/>
-      <c r="Z22" s="152"/>
+      <c r="Z22" s="155"/>
       <c r="AB22" s="44"/>
     </row>
     <row r="23" spans="1:28" ht="15.75">
@@ -16767,7 +16861,7 @@
       </c>
       <c r="X23" s="90"/>
       <c r="Y23" s="93"/>
-      <c r="Z23" s="152"/>
+      <c r="Z23" s="155"/>
     </row>
     <row r="24" spans="1:28" ht="15.75">
       <c r="A24" s="66">
@@ -16811,7 +16905,7 @@
       </c>
       <c r="X24" s="90"/>
       <c r="Y24" s="93"/>
-      <c r="Z24" s="152"/>
+      <c r="Z24" s="155"/>
     </row>
     <row r="25" spans="1:28" ht="15.75">
       <c r="A25" s="62">
@@ -16855,7 +16949,7 @@
       </c>
       <c r="X25" s="90"/>
       <c r="Y25" s="93"/>
-      <c r="Z25" s="152"/>
+      <c r="Z25" s="155"/>
     </row>
     <row r="26" spans="1:28" ht="15.75">
       <c r="A26" s="66">
@@ -16894,7 +16988,7 @@
       </c>
       <c r="X26" s="90"/>
       <c r="Y26" s="93"/>
-      <c r="Z26" s="152"/>
+      <c r="Z26" s="155"/>
     </row>
     <row r="27" spans="1:28" ht="15.75">
       <c r="A27" s="62">
@@ -16939,7 +17033,7 @@
       <c r="Y27" s="103">
         <v>20000</v>
       </c>
-      <c r="Z27" s="152"/>
+      <c r="Z27" s="155"/>
     </row>
     <row r="28" spans="1:28" ht="15.75">
       <c r="A28" s="66">
@@ -16981,7 +17075,7 @@
       </c>
       <c r="X28" s="90"/>
       <c r="Y28" s="93"/>
-      <c r="Z28" s="152"/>
+      <c r="Z28" s="155"/>
     </row>
     <row r="29" spans="1:28" ht="15.75">
       <c r="A29" s="62">
@@ -17020,7 +17114,7 @@
       </c>
       <c r="X29" s="90"/>
       <c r="Y29" s="93"/>
-      <c r="Z29" s="152"/>
+      <c r="Z29" s="155"/>
     </row>
     <row r="30" spans="1:28" ht="15.75">
       <c r="A30" s="66">
@@ -17060,7 +17154,7 @@
       </c>
       <c r="X30" s="90"/>
       <c r="Y30" s="93"/>
-      <c r="Z30" s="152"/>
+      <c r="Z30" s="155"/>
     </row>
     <row r="31" spans="1:28" ht="15.75">
       <c r="A31" s="62">
@@ -17095,7 +17189,7 @@
       </c>
       <c r="X31" s="90"/>
       <c r="Y31" s="93"/>
-      <c r="Z31" s="152"/>
+      <c r="Z31" s="155"/>
     </row>
     <row r="32" spans="1:28" ht="15.75">
       <c r="A32" s="66">
@@ -17130,7 +17224,7 @@
       </c>
       <c r="X32" s="90"/>
       <c r="Y32" s="93"/>
-      <c r="Z32" s="152"/>
+      <c r="Z32" s="155"/>
     </row>
     <row r="33" spans="1:26" ht="15.75">
       <c r="A33" s="62">
@@ -17167,7 +17261,7 @@
       <c r="Y33" s="136">
         <v>10000</v>
       </c>
-      <c r="Z33" s="152"/>
+      <c r="Z33" s="155"/>
     </row>
     <row r="34" spans="1:26" ht="15.75">
       <c r="A34" s="66">
@@ -17206,7 +17300,7 @@
       </c>
       <c r="X34" s="90"/>
       <c r="Y34" s="93"/>
-      <c r="Z34" s="152"/>
+      <c r="Z34" s="155"/>
     </row>
     <row r="35" spans="1:26" ht="15.75">
       <c r="A35" s="62">
@@ -17250,7 +17344,7 @@
       </c>
       <c r="X35" s="90"/>
       <c r="Y35" s="93"/>
-      <c r="Z35" s="152"/>
+      <c r="Z35" s="155"/>
     </row>
     <row r="36" spans="1:26" ht="15.75">
       <c r="A36" s="66">
@@ -17291,13 +17385,13 @@
       </c>
       <c r="X36" s="90"/>
       <c r="Y36" s="93"/>
-      <c r="Z36" s="152"/>
+      <c r="Z36" s="155"/>
     </row>
     <row r="37" spans="1:26">
-      <c r="A37" s="148" t="s">
+      <c r="A37" s="149" t="s">
         <v>36</v>
       </c>
-      <c r="B37" s="148"/>
+      <c r="B37" s="149"/>
       <c r="C37" s="79">
         <f>SUM(C21:C36)</f>
         <v>3393</v>
@@ -17396,10 +17490,10 @@
       </c>
     </row>
     <row r="38" spans="1:26" ht="31.5" customHeight="1">
-      <c r="A38" s="151" t="s">
+      <c r="A38" s="154" t="s">
         <v>37</v>
       </c>
-      <c r="B38" s="151"/>
+      <c r="B38" s="154"/>
       <c r="C38" s="78">
         <f>SUM(C20,C37)</f>
         <v>14335.99</v>
@@ -17511,18 +17605,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A1:Z1"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="Z3:Z19"/>
+    <mergeCell ref="Z21:Z36"/>
     <mergeCell ref="AC14:AF14"/>
     <mergeCell ref="AC15:AF15"/>
     <mergeCell ref="AC8:AG10"/>
     <mergeCell ref="AC11:AF11"/>
     <mergeCell ref="AC12:AF12"/>
     <mergeCell ref="AC13:AF13"/>
-    <mergeCell ref="A1:Z1"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="Z3:Z19"/>
-    <mergeCell ref="Z21:Z36"/>
   </mergeCells>
   <conditionalFormatting sqref="Z20:Z21 Z37:Z38">
     <cfRule type="expression" dxfId="3" priority="1">
@@ -17549,78 +17643,78 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:52" ht="34.5" customHeight="1">
-      <c r="A1" s="156" t="s">
+      <c r="A1" s="157" t="s">
         <v>66</v>
       </c>
-      <c r="B1" s="156"/>
-      <c r="C1" s="156"/>
-      <c r="D1" s="156"/>
-      <c r="E1" s="156"/>
-      <c r="F1" s="156"/>
-      <c r="G1" s="156"/>
-      <c r="H1" s="156"/>
-      <c r="I1" s="156"/>
-      <c r="J1" s="156"/>
-      <c r="K1" s="156"/>
-      <c r="L1" s="156"/>
-      <c r="M1" s="156"/>
-      <c r="N1" s="156"/>
-      <c r="O1" s="156"/>
-      <c r="P1" s="156"/>
-      <c r="Q1" s="156"/>
-      <c r="R1" s="156"/>
-      <c r="S1" s="156"/>
-      <c r="T1" s="156"/>
-      <c r="U1" s="156"/>
-      <c r="V1" s="156"/>
-      <c r="W1" s="156"/>
-      <c r="X1" s="156"/>
-      <c r="Y1" s="156"/>
-      <c r="Z1" s="156"/>
-      <c r="AA1" s="156"/>
-      <c r="AB1" s="156"/>
-      <c r="AC1" s="156"/>
-      <c r="AD1" s="156"/>
+      <c r="B1" s="157"/>
+      <c r="C1" s="157"/>
+      <c r="D1" s="157"/>
+      <c r="E1" s="157"/>
+      <c r="F1" s="157"/>
+      <c r="G1" s="157"/>
+      <c r="H1" s="157"/>
+      <c r="I1" s="157"/>
+      <c r="J1" s="157"/>
+      <c r="K1" s="157"/>
+      <c r="L1" s="157"/>
+      <c r="M1" s="157"/>
+      <c r="N1" s="157"/>
+      <c r="O1" s="157"/>
+      <c r="P1" s="157"/>
+      <c r="Q1" s="157"/>
+      <c r="R1" s="157"/>
+      <c r="S1" s="157"/>
+      <c r="T1" s="157"/>
+      <c r="U1" s="157"/>
+      <c r="V1" s="157"/>
+      <c r="W1" s="157"/>
+      <c r="X1" s="157"/>
+      <c r="Y1" s="157"/>
+      <c r="Z1" s="157"/>
+      <c r="AA1" s="157"/>
+      <c r="AB1" s="157"/>
+      <c r="AC1" s="157"/>
+      <c r="AD1" s="157"/>
     </row>
     <row r="2" spans="1:52" ht="26.25">
-      <c r="A2" s="163"/>
-      <c r="B2" s="164"/>
-      <c r="C2" s="159" t="s">
+      <c r="A2" s="164"/>
+      <c r="B2" s="165"/>
+      <c r="C2" s="160" t="s">
         <v>67</v>
       </c>
-      <c r="D2" s="159"/>
-      <c r="E2" s="159"/>
-      <c r="F2" s="159"/>
-      <c r="G2" s="159"/>
-      <c r="H2" s="159"/>
-      <c r="I2" s="159"/>
-      <c r="J2" s="159"/>
-      <c r="K2" s="159"/>
-      <c r="L2" s="160" t="s">
+      <c r="D2" s="160"/>
+      <c r="E2" s="160"/>
+      <c r="F2" s="160"/>
+      <c r="G2" s="160"/>
+      <c r="H2" s="160"/>
+      <c r="I2" s="160"/>
+      <c r="J2" s="160"/>
+      <c r="K2" s="160"/>
+      <c r="L2" s="161" t="s">
         <v>75</v>
       </c>
-      <c r="M2" s="160"/>
-      <c r="N2" s="160"/>
-      <c r="O2" s="160"/>
-      <c r="P2" s="160"/>
-      <c r="Q2" s="160"/>
-      <c r="R2" s="161" t="s">
+      <c r="M2" s="161"/>
+      <c r="N2" s="161"/>
+      <c r="O2" s="161"/>
+      <c r="P2" s="161"/>
+      <c r="Q2" s="161"/>
+      <c r="R2" s="162" t="s">
         <v>78</v>
       </c>
-      <c r="S2" s="161"/>
-      <c r="T2" s="161"/>
-      <c r="U2" s="161"/>
-      <c r="V2" s="161"/>
-      <c r="W2" s="161"/>
-      <c r="X2" s="161"/>
-      <c r="Y2" s="161"/>
-      <c r="Z2" s="161"/>
-      <c r="AA2" s="161"/>
-      <c r="AB2" s="162" t="s">
+      <c r="S2" s="162"/>
+      <c r="T2" s="162"/>
+      <c r="U2" s="162"/>
+      <c r="V2" s="162"/>
+      <c r="W2" s="162"/>
+      <c r="X2" s="162"/>
+      <c r="Y2" s="162"/>
+      <c r="Z2" s="162"/>
+      <c r="AA2" s="162"/>
+      <c r="AB2" s="163" t="s">
         <v>81</v>
       </c>
-      <c r="AC2" s="162"/>
-      <c r="AD2" s="162"/>
+      <c r="AC2" s="163"/>
+      <c r="AD2" s="163"/>
     </row>
     <row r="3" spans="1:52" ht="45" customHeight="1">
       <c r="A3" s="119" t="s">
@@ -17787,7 +17881,7 @@
         <f>37635+40252.26+18817.85</f>
         <v>96705.110000000015</v>
       </c>
-      <c r="AD4" s="157"/>
+      <c r="AD4" s="158"/>
     </row>
     <row r="5" spans="1:52" ht="15.75">
       <c r="A5" s="105">
@@ -17837,7 +17931,7 @@
         <v>16503.13</v>
       </c>
       <c r="AC5" s="117"/>
-      <c r="AD5" s="157"/>
+      <c r="AD5" s="158"/>
     </row>
     <row r="6" spans="1:52" ht="15.75">
       <c r="A6" s="109">
@@ -17880,7 +17974,7 @@
         <v>996.61</v>
       </c>
       <c r="AC6" s="117"/>
-      <c r="AD6" s="157"/>
+      <c r="AD6" s="158"/>
     </row>
     <row r="7" spans="1:52" ht="15.75">
       <c r="A7" s="105">
@@ -17933,7 +18027,7 @@
         <v>5968</v>
       </c>
       <c r="AC7" s="117"/>
-      <c r="AD7" s="157"/>
+      <c r="AD7" s="158"/>
     </row>
     <row r="8" spans="1:52" ht="15" customHeight="1">
       <c r="A8" s="109">
@@ -17979,7 +18073,7 @@
         <v>12168.98</v>
       </c>
       <c r="AC8" s="117"/>
-      <c r="AD8" s="157"/>
+      <c r="AD8" s="158"/>
     </row>
     <row r="9" spans="1:52" ht="15.75">
       <c r="A9" s="105">
@@ -18027,7 +18121,7 @@
         <v>5970</v>
       </c>
       <c r="AC9" s="117"/>
-      <c r="AD9" s="157"/>
+      <c r="AD9" s="158"/>
     </row>
     <row r="10" spans="1:52" ht="15.75">
       <c r="A10" s="109">
@@ -18075,7 +18169,7 @@
         <v>3257</v>
       </c>
       <c r="AC10" s="117"/>
-      <c r="AD10" s="157"/>
+      <c r="AD10" s="158"/>
     </row>
     <row r="11" spans="1:52" ht="15.75">
       <c r="A11" s="105">
@@ -18119,7 +18213,7 @@
         <v>1034</v>
       </c>
       <c r="AC11" s="117"/>
-      <c r="AD11" s="157"/>
+      <c r="AD11" s="158"/>
     </row>
     <row r="12" spans="1:52" ht="15.75">
       <c r="A12" s="109">
@@ -18166,7 +18260,7 @@
         <v>3586</v>
       </c>
       <c r="AC12" s="117"/>
-      <c r="AD12" s="157"/>
+      <c r="AD12" s="158"/>
     </row>
     <row r="13" spans="1:52" ht="15.75">
       <c r="A13" s="105">
@@ -18213,7 +18307,7 @@
         <v>5889</v>
       </c>
       <c r="AC13" s="117"/>
-      <c r="AD13" s="157"/>
+      <c r="AD13" s="158"/>
     </row>
     <row r="14" spans="1:52" ht="15.75">
       <c r="A14" s="109">
@@ -18259,7 +18353,7 @@
         <v>7092.93</v>
       </c>
       <c r="AC14" s="117"/>
-      <c r="AD14" s="157"/>
+      <c r="AD14" s="158"/>
     </row>
     <row r="15" spans="1:52" ht="15.75">
       <c r="A15" s="105">
@@ -18313,7 +18407,7 @@
         <v>6644.2800000000007</v>
       </c>
       <c r="AC15" s="118"/>
-      <c r="AD15" s="157"/>
+      <c r="AD15" s="158"/>
     </row>
     <row r="16" spans="1:52" ht="15.75">
       <c r="A16" s="109">
@@ -18364,7 +18458,7 @@
         <v>5105.1899999999996</v>
       </c>
       <c r="AC16" s="117"/>
-      <c r="AD16" s="157"/>
+      <c r="AD16" s="158"/>
     </row>
     <row r="17" spans="1:32" ht="15.75">
       <c r="A17" s="105">
@@ -18405,7 +18499,7 @@
         <v>280.97000000000003</v>
       </c>
       <c r="AC17" s="117"/>
-      <c r="AD17" s="157"/>
+      <c r="AD17" s="158"/>
     </row>
     <row r="18" spans="1:32" ht="15.75">
       <c r="A18" s="109">
@@ -18450,13 +18544,13 @@
         <v>956.98</v>
       </c>
       <c r="AC18" s="117"/>
-      <c r="AD18" s="157"/>
+      <c r="AD18" s="158"/>
     </row>
     <row r="19" spans="1:32" ht="14.25" customHeight="1">
-      <c r="A19" s="158" t="s">
+      <c r="A19" s="159" t="s">
         <v>35</v>
       </c>
-      <c r="B19" s="158"/>
+      <c r="B19" s="159"/>
       <c r="C19" s="113">
         <f>SUM(C4:C18)</f>
         <v>1403.89</v>
@@ -18625,7 +18719,7 @@
       <c r="AC20" s="118">
         <v>36738.04</v>
       </c>
-      <c r="AD20" s="157"/>
+      <c r="AD20" s="158"/>
     </row>
     <row r="21" spans="1:32" ht="15.75">
       <c r="A21" s="105">
@@ -18673,10 +18767,10 @@
         <f>SUM(C21:AA21)</f>
         <v>2981.2</v>
       </c>
-      <c r="AC21" s="165">
+      <c r="AC21" s="137">
         <v>10000</v>
       </c>
-      <c r="AD21" s="157"/>
+      <c r="AD21" s="158"/>
       <c r="AF21" s="44"/>
     </row>
     <row r="22" spans="1:32" ht="15.75">
@@ -18716,7 +18810,7 @@
         <v>0</v>
       </c>
       <c r="AC22" s="117"/>
-      <c r="AD22" s="157"/>
+      <c r="AD22" s="158"/>
     </row>
     <row r="23" spans="1:32" ht="15.75">
       <c r="A23" s="105">
@@ -18732,7 +18826,10 @@
       <c r="G23" s="107"/>
       <c r="H23" s="107"/>
       <c r="I23" s="107"/>
-      <c r="J23" s="107"/>
+      <c r="J23" s="107">
+        <f>1357+194+197</f>
+        <v>1748</v>
+      </c>
       <c r="K23" s="107"/>
       <c r="L23" s="107"/>
       <c r="M23" s="107"/>
@@ -18740,22 +18837,31 @@
       <c r="O23" s="107"/>
       <c r="P23" s="107"/>
       <c r="Q23" s="107"/>
-      <c r="R23" s="107"/>
+      <c r="R23" s="107">
+        <f>798.27</f>
+        <v>798.27</v>
+      </c>
       <c r="S23" s="107"/>
       <c r="T23" s="107"/>
       <c r="U23" s="107"/>
-      <c r="V23" s="107"/>
-      <c r="W23" s="107"/>
+      <c r="V23" s="107">
+        <f>1707.5-201.49</f>
+        <v>1506.01</v>
+      </c>
+      <c r="W23" s="107">
+        <f>329+2500</f>
+        <v>2829</v>
+      </c>
       <c r="X23" s="107"/>
       <c r="Y23" s="107"/>
       <c r="Z23" s="107"/>
       <c r="AA23" s="108"/>
       <c r="AB23" s="128">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>6881.28</v>
       </c>
       <c r="AC23" s="117"/>
-      <c r="AD23" s="157"/>
+      <c r="AD23" s="158"/>
     </row>
     <row r="24" spans="1:32" ht="15.75">
       <c r="A24" s="109">
@@ -18764,15 +18870,25 @@
       <c r="B24" s="110" t="s">
         <v>7</v>
       </c>
-      <c r="C24" s="111"/>
-      <c r="D24" s="111"/>
+      <c r="C24" s="111">
+        <v>785.88</v>
+      </c>
+      <c r="D24" s="111">
+        <f>589.98</f>
+        <v>589.98</v>
+      </c>
       <c r="E24" s="111"/>
       <c r="F24" s="111"/>
       <c r="G24" s="111"/>
-      <c r="H24" s="111"/>
+      <c r="H24" s="111">
+        <v>2450</v>
+      </c>
       <c r="I24" s="111"/>
       <c r="J24" s="111"/>
-      <c r="K24" s="111"/>
+      <c r="K24" s="111">
+        <f>1800+196.2</f>
+        <v>1996.2</v>
+      </c>
       <c r="L24" s="111"/>
       <c r="M24" s="111"/>
       <c r="N24" s="111"/>
@@ -18783,7 +18899,9 @@
       <c r="S24" s="111"/>
       <c r="T24" s="111"/>
       <c r="U24" s="111"/>
-      <c r="V24" s="111"/>
+      <c r="V24" s="111">
+        <v>304.63</v>
+      </c>
       <c r="W24" s="111"/>
       <c r="X24" s="111"/>
       <c r="Y24" s="111"/>
@@ -18791,10 +18909,10 @@
       <c r="AA24" s="112"/>
       <c r="AB24" s="128">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>6126.6900000000005</v>
       </c>
       <c r="AC24" s="117"/>
-      <c r="AD24" s="157"/>
+      <c r="AD24" s="158"/>
     </row>
     <row r="25" spans="1:32" ht="15.75">
       <c r="A25" s="105">
@@ -18811,7 +18929,10 @@
       <c r="H25" s="107"/>
       <c r="I25" s="107"/>
       <c r="J25" s="107"/>
-      <c r="K25" s="107"/>
+      <c r="K25" s="107">
+        <f>1640+110</f>
+        <v>1750</v>
+      </c>
       <c r="L25" s="107"/>
       <c r="M25" s="107"/>
       <c r="N25" s="107"/>
@@ -18823,17 +18944,19 @@
       <c r="T25" s="107"/>
       <c r="U25" s="107"/>
       <c r="V25" s="107"/>
-      <c r="W25" s="107"/>
+      <c r="W25" s="107">
+        <v>6000</v>
+      </c>
       <c r="X25" s="107"/>
       <c r="Y25" s="107"/>
       <c r="Z25" s="107"/>
       <c r="AA25" s="108"/>
       <c r="AB25" s="128">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>7750</v>
       </c>
       <c r="AC25" s="117"/>
-      <c r="AD25" s="157"/>
+      <c r="AD25" s="158"/>
     </row>
     <row r="26" spans="1:32" ht="15.75">
       <c r="A26" s="109">
@@ -18872,7 +18995,7 @@
         <v>0</v>
       </c>
       <c r="AC26" s="118"/>
-      <c r="AD26" s="157"/>
+      <c r="AD26" s="158"/>
     </row>
     <row r="27" spans="1:32" ht="15.75">
       <c r="A27" s="105">
@@ -18911,7 +19034,7 @@
         <v>0</v>
       </c>
       <c r="AC27" s="117"/>
-      <c r="AD27" s="157"/>
+      <c r="AD27" s="158"/>
     </row>
     <row r="28" spans="1:32" ht="15.75">
       <c r="A28" s="109">
@@ -18950,7 +19073,7 @@
         <v>0</v>
       </c>
       <c r="AC28" s="117"/>
-      <c r="AD28" s="157"/>
+      <c r="AD28" s="158"/>
     </row>
     <row r="29" spans="1:32" ht="15.75">
       <c r="A29" s="105">
@@ -18989,7 +19112,7 @@
         <v>0</v>
       </c>
       <c r="AC29" s="117"/>
-      <c r="AD29" s="157"/>
+      <c r="AD29" s="158"/>
     </row>
     <row r="30" spans="1:32" ht="15.75">
       <c r="A30" s="109">
@@ -19028,7 +19151,7 @@
         <v>0</v>
       </c>
       <c r="AC30" s="117"/>
-      <c r="AD30" s="157"/>
+      <c r="AD30" s="158"/>
     </row>
     <row r="31" spans="1:32" ht="15.75">
       <c r="A31" s="105">
@@ -19067,7 +19190,7 @@
         <v>0</v>
       </c>
       <c r="AC31" s="117"/>
-      <c r="AD31" s="157"/>
+      <c r="AD31" s="158"/>
     </row>
     <row r="32" spans="1:32" ht="15.75">
       <c r="A32" s="109">
@@ -19106,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="AC32" s="117"/>
-      <c r="AD32" s="157"/>
+      <c r="AD32" s="158"/>
     </row>
     <row r="33" spans="1:30" ht="15.75">
       <c r="A33" s="105">
@@ -19145,7 +19268,7 @@
         <v>0</v>
       </c>
       <c r="AC33" s="117"/>
-      <c r="AD33" s="157"/>
+      <c r="AD33" s="158"/>
     </row>
     <row r="34" spans="1:30" ht="15.75">
       <c r="A34" s="109">
@@ -19184,7 +19307,7 @@
         <v>0</v>
       </c>
       <c r="AC34" s="117"/>
-      <c r="AD34" s="157"/>
+      <c r="AD34" s="158"/>
     </row>
     <row r="35" spans="1:30" ht="15.75">
       <c r="A35" s="105">
@@ -19223,20 +19346,20 @@
         <v>0</v>
       </c>
       <c r="AC35" s="117"/>
-      <c r="AD35" s="157"/>
+      <c r="AD35" s="158"/>
     </row>
     <row r="36" spans="1:30" ht="14.25" customHeight="1">
-      <c r="A36" s="158" t="s">
+      <c r="A36" s="159" t="s">
         <v>36</v>
       </c>
-      <c r="B36" s="158"/>
+      <c r="B36" s="159"/>
       <c r="C36" s="113">
         <f>SUM(C20:C35)</f>
-        <v>527.91000000000008</v>
+        <v>1313.79</v>
       </c>
       <c r="D36" s="113">
         <f t="shared" ref="D36:K36" si="3">SUM(D20:D35)</f>
-        <v>1124.17</v>
+        <v>1714.15</v>
       </c>
       <c r="E36" s="113">
         <f t="shared" si="3"/>
@@ -19252,7 +19375,7 @@
       </c>
       <c r="H36" s="113">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>2450</v>
       </c>
       <c r="I36" s="113">
         <f t="shared" si="3"/>
@@ -19260,11 +19383,11 @@
       </c>
       <c r="J36" s="113">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1748</v>
       </c>
       <c r="K36" s="113">
         <f t="shared" si="3"/>
-        <v>880</v>
+        <v>4626.2</v>
       </c>
       <c r="L36" s="114">
         <f>SUM(L20:L35)</f>
@@ -19292,7 +19415,7 @@
       </c>
       <c r="R36" s="115">
         <f>SUM(R20:R35)</f>
-        <v>1000</v>
+        <v>1798.27</v>
       </c>
       <c r="S36" s="115">
         <f t="shared" ref="S36:AA36" si="5">SUM(S20:S35)</f>
@@ -19308,11 +19431,11 @@
       </c>
       <c r="V36" s="115">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1810.6399999999999</v>
       </c>
       <c r="W36" s="115">
         <f t="shared" si="5"/>
-        <v>3000</v>
+        <v>11829</v>
       </c>
       <c r="X36" s="115">
         <f t="shared" si="5"/>
@@ -19332,7 +19455,7 @@
       </c>
       <c r="AB36" s="129">
         <f>SUM(AB20:AB35)</f>
-        <v>9100.08</v>
+        <v>29858.050000000003</v>
       </c>
       <c r="AC36" s="130">
         <f>SUM(AC20:AC35)</f>
@@ -19340,17 +19463,17 @@
       </c>
       <c r="AD36" s="133">
         <f>AC36-AB36</f>
-        <v>37637.96</v>
+        <v>16879.989999999998</v>
       </c>
     </row>
     <row r="37" spans="1:30" ht="31.5" customHeight="1">
-      <c r="A37" s="155" t="s">
+      <c r="A37" s="156" t="s">
         <v>37</v>
       </c>
-      <c r="B37" s="155"/>
+      <c r="B37" s="156"/>
       <c r="C37" s="116">
         <f>SUM(C19,C36)</f>
-        <v>1931.8000000000002</v>
+        <v>2717.6800000000003</v>
       </c>
       <c r="D37" s="116"/>
       <c r="E37" s="116"/>
@@ -19361,7 +19484,7 @@
       <c r="G37" s="116"/>
       <c r="H37" s="116">
         <f t="shared" si="6"/>
-        <v>4470</v>
+        <v>6920</v>
       </c>
       <c r="I37" s="116">
         <f t="shared" si="6"/>
@@ -19369,11 +19492,11 @@
       </c>
       <c r="J37" s="116">
         <f t="shared" si="6"/>
-        <v>5059.9799999999996</v>
+        <v>6807.98</v>
       </c>
       <c r="K37" s="116">
         <f t="shared" si="6"/>
-        <v>3160</v>
+        <v>6906.2</v>
       </c>
       <c r="L37" s="116">
         <f t="shared" si="6"/>
@@ -19392,7 +19515,7 @@
       <c r="Q37" s="116"/>
       <c r="R37" s="116">
         <f t="shared" si="6"/>
-        <v>1000</v>
+        <v>1798.27</v>
       </c>
       <c r="S37" s="116"/>
       <c r="T37" s="116">
@@ -19405,11 +19528,11 @@
       </c>
       <c r="V37" s="116">
         <f t="shared" si="6"/>
-        <v>2801.7700000000004</v>
+        <v>4612.41</v>
       </c>
       <c r="W37" s="116">
         <f t="shared" si="6"/>
-        <v>22225.97</v>
+        <v>31054.97</v>
       </c>
       <c r="X37" s="116">
         <f t="shared" si="6"/>
@@ -19429,7 +19552,7 @@
       </c>
       <c r="AB37" s="131">
         <f t="shared" si="6"/>
-        <v>101525.1</v>
+        <v>122283.07</v>
       </c>
       <c r="AC37" s="132">
         <f>SUM(AC19,AC36)</f>
@@ -19437,7 +19560,7 @@
       </c>
       <c r="AD37" s="134">
         <f>SUM(AD19,AD36)</f>
-        <v>41918.05000000001</v>
+        <v>21160.080000000009</v>
       </c>
     </row>
     <row r="41" spans="1:30">

--- a/Другое/2026/Доходы-Расходы_copy.xlsx
+++ b/Другое/2026/Доходы-Расходы_copy.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="6" rupBuild="4507"/>
   <workbookPr filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="7"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="Сводная" sheetId="5" r:id="rId1"/>
@@ -5665,12 +5665,296 @@
         </r>
       </text>
     </comment>
+    <comment ref="N26" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Яндекс Плюс
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="W26" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Цветы + что-то еще
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="X26" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Чтиво журнал</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K27" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Промясо
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="X27" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Ручки в Читай городе
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="W28" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Бабл ти энд поке
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="Z28" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Пейнтбол
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J29" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Вкусно и точка</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="Z29" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Поход в кино на Одиссею
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AC29" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Мама перевела за бенз
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J30" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Вкусно и Точка
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N30" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Яндекс Плюс</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K31" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Обед во вьет кук</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K32" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Бабл ти энд Поке
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="W32" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Не помню на что
++ на колготки</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N33" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Литрес
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="W34" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>На такси и покушать
+И вычитаем 500 руб, которые она скинула 1 сентября</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AC34" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Взял в долг у мамы
+</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="451" uniqueCount="83">
   <si>
     <t>Число</t>
   </si>
@@ -7150,12 +7434,6 @@
     <xf numFmtId="0" fontId="25" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="28" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="17" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="28" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -7163,6 +7441,12 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="23" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="28" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="17" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="33" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -7542,7 +7826,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -15687,34 +15971,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:48" ht="60.75" customHeight="1">
-      <c r="A1" s="153" t="s">
+      <c r="A1" s="151" t="s">
         <v>59</v>
       </c>
-      <c r="B1" s="153"/>
-      <c r="C1" s="153"/>
-      <c r="D1" s="153"/>
-      <c r="E1" s="153"/>
-      <c r="F1" s="153"/>
-      <c r="G1" s="153"/>
-      <c r="H1" s="153"/>
-      <c r="I1" s="153"/>
-      <c r="J1" s="153"/>
-      <c r="K1" s="153"/>
-      <c r="L1" s="153"/>
-      <c r="M1" s="153"/>
-      <c r="N1" s="153"/>
-      <c r="O1" s="153"/>
-      <c r="P1" s="153"/>
-      <c r="Q1" s="153"/>
-      <c r="R1" s="153"/>
-      <c r="S1" s="153"/>
-      <c r="T1" s="153"/>
-      <c r="U1" s="153"/>
-      <c r="V1" s="153"/>
-      <c r="W1" s="153"/>
-      <c r="X1" s="153"/>
-      <c r="Y1" s="153"/>
-      <c r="Z1" s="153"/>
+      <c r="B1" s="151"/>
+      <c r="C1" s="151"/>
+      <c r="D1" s="151"/>
+      <c r="E1" s="151"/>
+      <c r="F1" s="151"/>
+      <c r="G1" s="151"/>
+      <c r="H1" s="151"/>
+      <c r="I1" s="151"/>
+      <c r="J1" s="151"/>
+      <c r="K1" s="151"/>
+      <c r="L1" s="151"/>
+      <c r="M1" s="151"/>
+      <c r="N1" s="151"/>
+      <c r="O1" s="151"/>
+      <c r="P1" s="151"/>
+      <c r="Q1" s="151"/>
+      <c r="R1" s="151"/>
+      <c r="S1" s="151"/>
+      <c r="T1" s="151"/>
+      <c r="U1" s="151"/>
+      <c r="V1" s="151"/>
+      <c r="W1" s="151"/>
+      <c r="X1" s="151"/>
+      <c r="Y1" s="151"/>
+      <c r="Z1" s="151"/>
     </row>
     <row r="2" spans="1:48" ht="45" customHeight="1">
       <c r="A2" s="76" t="s">
@@ -15867,7 +16151,7 @@
         <f>(94085+57723.67)</f>
         <v>151808.66999999998</v>
       </c>
-      <c r="Z3" s="155"/>
+      <c r="Z3" s="153"/>
     </row>
     <row r="4" spans="1:48" ht="15.75">
       <c r="A4" s="66">
@@ -15917,7 +16201,7 @@
       </c>
       <c r="X4" s="90"/>
       <c r="Y4" s="93"/>
-      <c r="Z4" s="155"/>
+      <c r="Z4" s="153"/>
     </row>
     <row r="5" spans="1:48" ht="15.75">
       <c r="A5" s="62">
@@ -15957,7 +16241,7 @@
       </c>
       <c r="X5" s="90"/>
       <c r="Y5" s="93"/>
-      <c r="Z5" s="155"/>
+      <c r="Z5" s="153"/>
     </row>
     <row r="6" spans="1:48" ht="15.75">
       <c r="A6" s="66">
@@ -15998,7 +16282,7 @@
       </c>
       <c r="X6" s="90"/>
       <c r="Y6" s="93"/>
-      <c r="Z6" s="155"/>
+      <c r="Z6" s="153"/>
     </row>
     <row r="7" spans="1:48" ht="15" customHeight="1">
       <c r="A7" s="62">
@@ -16042,7 +16326,7 @@
       </c>
       <c r="X7" s="90"/>
       <c r="Y7" s="93"/>
-      <c r="Z7" s="155"/>
+      <c r="Z7" s="153"/>
     </row>
     <row r="8" spans="1:48" ht="15.75">
       <c r="A8" s="66">
@@ -16084,14 +16368,14 @@
       </c>
       <c r="X8" s="90"/>
       <c r="Y8" s="93"/>
-      <c r="Z8" s="155"/>
-      <c r="AC8" s="152" t="s">
+      <c r="Z8" s="153"/>
+      <c r="AC8" s="155" t="s">
         <v>61</v>
       </c>
-      <c r="AD8" s="152"/>
-      <c r="AE8" s="152"/>
-      <c r="AF8" s="152"/>
-      <c r="AG8" s="152"/>
+      <c r="AD8" s="155"/>
+      <c r="AE8" s="155"/>
+      <c r="AF8" s="155"/>
+      <c r="AG8" s="155"/>
     </row>
     <row r="9" spans="1:48" ht="15.75">
       <c r="A9" s="62">
@@ -16130,12 +16414,12 @@
       </c>
       <c r="X9" s="90"/>
       <c r="Y9" s="93"/>
-      <c r="Z9" s="155"/>
-      <c r="AC9" s="152"/>
-      <c r="AD9" s="152"/>
-      <c r="AE9" s="152"/>
-      <c r="AF9" s="152"/>
-      <c r="AG9" s="152"/>
+      <c r="Z9" s="153"/>
+      <c r="AC9" s="155"/>
+      <c r="AD9" s="155"/>
+      <c r="AE9" s="155"/>
+      <c r="AF9" s="155"/>
+      <c r="AG9" s="155"/>
     </row>
     <row r="10" spans="1:48" ht="15.75">
       <c r="A10" s="66">
@@ -16179,12 +16463,12 @@
       </c>
       <c r="X10" s="90"/>
       <c r="Y10" s="93"/>
-      <c r="Z10" s="155"/>
-      <c r="AC10" s="152"/>
-      <c r="AD10" s="152"/>
-      <c r="AE10" s="152"/>
-      <c r="AF10" s="152"/>
-      <c r="AG10" s="152"/>
+      <c r="Z10" s="153"/>
+      <c r="AC10" s="155"/>
+      <c r="AD10" s="155"/>
+      <c r="AE10" s="155"/>
+      <c r="AF10" s="155"/>
+      <c r="AG10" s="155"/>
     </row>
     <row r="11" spans="1:48" ht="15.75">
       <c r="A11" s="62">
@@ -16224,13 +16508,13 @@
       </c>
       <c r="X11" s="90"/>
       <c r="Y11" s="93"/>
-      <c r="Z11" s="155"/>
-      <c r="AC11" s="151" t="s">
+      <c r="Z11" s="153"/>
+      <c r="AC11" s="154" t="s">
         <v>62</v>
       </c>
-      <c r="AD11" s="151"/>
-      <c r="AE11" s="151"/>
-      <c r="AF11" s="151"/>
+      <c r="AD11" s="154"/>
+      <c r="AE11" s="154"/>
+      <c r="AF11" s="154"/>
       <c r="AG11" s="104">
         <f>Y3+Y14+Y21</f>
         <v>226341.31</v>
@@ -16271,13 +16555,13 @@
       </c>
       <c r="X12" s="90"/>
       <c r="Y12" s="93"/>
-      <c r="Z12" s="155"/>
-      <c r="AC12" s="151" t="s">
+      <c r="Z12" s="153"/>
+      <c r="AC12" s="154" t="s">
         <v>55</v>
       </c>
-      <c r="AD12" s="151"/>
-      <c r="AE12" s="151"/>
-      <c r="AF12" s="151"/>
+      <c r="AD12" s="154"/>
+      <c r="AE12" s="154"/>
+      <c r="AF12" s="154"/>
       <c r="AG12" s="104">
         <f>Y27</f>
         <v>20000</v>
@@ -16322,13 +16606,13 @@
       </c>
       <c r="X13" s="90"/>
       <c r="Y13" s="93"/>
-      <c r="Z13" s="155"/>
-      <c r="AC13" s="151" t="s">
+      <c r="Z13" s="153"/>
+      <c r="AC13" s="154" t="s">
         <v>63</v>
       </c>
-      <c r="AD13" s="151"/>
-      <c r="AE13" s="151"/>
-      <c r="AF13" s="151"/>
+      <c r="AD13" s="154"/>
+      <c r="AE13" s="154"/>
+      <c r="AF13" s="154"/>
       <c r="AG13" s="104">
         <f>Y17+Y19</f>
         <v>25000</v>
@@ -16374,13 +16658,13 @@
       <c r="Y14" s="99">
         <v>37634</v>
       </c>
-      <c r="Z14" s="155"/>
-      <c r="AC14" s="151" t="s">
+      <c r="Z14" s="153"/>
+      <c r="AC14" s="154" t="s">
         <v>64</v>
       </c>
-      <c r="AD14" s="151"/>
-      <c r="AE14" s="151"/>
-      <c r="AF14" s="151"/>
+      <c r="AD14" s="154"/>
+      <c r="AE14" s="154"/>
+      <c r="AF14" s="154"/>
       <c r="AG14" s="104">
         <f>W38</f>
         <v>177971.36</v>
@@ -16430,13 +16714,13 @@
       </c>
       <c r="X15" s="90"/>
       <c r="Y15" s="93"/>
-      <c r="Z15" s="155"/>
-      <c r="AC15" s="151" t="s">
+      <c r="Z15" s="153"/>
+      <c r="AC15" s="154" t="s">
         <v>65</v>
       </c>
-      <c r="AD15" s="151"/>
-      <c r="AE15" s="151"/>
-      <c r="AF15" s="151"/>
+      <c r="AD15" s="154"/>
+      <c r="AE15" s="154"/>
+      <c r="AF15" s="154"/>
       <c r="AG15" s="104">
         <f>SUM(C38:H38)</f>
         <v>55416.04</v>
@@ -16485,7 +16769,7 @@
       </c>
       <c r="X16" s="90"/>
       <c r="Y16" s="93"/>
-      <c r="Z16" s="155"/>
+      <c r="Z16" s="153"/>
     </row>
     <row r="17" spans="1:28" ht="15.75">
       <c r="A17" s="62">
@@ -16537,7 +16821,7 @@
       <c r="Y17" s="100">
         <v>15000</v>
       </c>
-      <c r="Z17" s="155"/>
+      <c r="Z17" s="153"/>
     </row>
     <row r="18" spans="1:28" ht="15.75">
       <c r="A18" s="66">
@@ -16578,7 +16862,7 @@
       </c>
       <c r="X18" s="90"/>
       <c r="Y18" s="93"/>
-      <c r="Z18" s="155"/>
+      <c r="Z18" s="153"/>
     </row>
     <row r="19" spans="1:28" ht="15.75">
       <c r="A19" s="62">
@@ -16622,7 +16906,7 @@
       <c r="Y19" s="100">
         <v>10000</v>
       </c>
-      <c r="Z19" s="155"/>
+      <c r="Z19" s="153"/>
     </row>
     <row r="20" spans="1:28" ht="14.25" customHeight="1">
       <c r="A20" s="149" t="s">
@@ -16771,7 +17055,7 @@
       <c r="Y21" s="99">
         <v>36898.639999999999</v>
       </c>
-      <c r="Z21" s="155"/>
+      <c r="Z21" s="153"/>
     </row>
     <row r="22" spans="1:28" ht="15.75">
       <c r="A22" s="66">
@@ -16817,7 +17101,7 @@
         <v>23662.84</v>
       </c>
       <c r="Y22" s="93"/>
-      <c r="Z22" s="155"/>
+      <c r="Z22" s="153"/>
       <c r="AB22" s="44"/>
     </row>
     <row r="23" spans="1:28" ht="15.75">
@@ -16861,7 +17145,7 @@
       </c>
       <c r="X23" s="90"/>
       <c r="Y23" s="93"/>
-      <c r="Z23" s="155"/>
+      <c r="Z23" s="153"/>
     </row>
     <row r="24" spans="1:28" ht="15.75">
       <c r="A24" s="66">
@@ -16905,7 +17189,7 @@
       </c>
       <c r="X24" s="90"/>
       <c r="Y24" s="93"/>
-      <c r="Z24" s="155"/>
+      <c r="Z24" s="153"/>
     </row>
     <row r="25" spans="1:28" ht="15.75">
       <c r="A25" s="62">
@@ -16949,7 +17233,7 @@
       </c>
       <c r="X25" s="90"/>
       <c r="Y25" s="93"/>
-      <c r="Z25" s="155"/>
+      <c r="Z25" s="153"/>
     </row>
     <row r="26" spans="1:28" ht="15.75">
       <c r="A26" s="66">
@@ -16988,7 +17272,7 @@
       </c>
       <c r="X26" s="90"/>
       <c r="Y26" s="93"/>
-      <c r="Z26" s="155"/>
+      <c r="Z26" s="153"/>
     </row>
     <row r="27" spans="1:28" ht="15.75">
       <c r="A27" s="62">
@@ -17033,7 +17317,7 @@
       <c r="Y27" s="103">
         <v>20000</v>
       </c>
-      <c r="Z27" s="155"/>
+      <c r="Z27" s="153"/>
     </row>
     <row r="28" spans="1:28" ht="15.75">
       <c r="A28" s="66">
@@ -17075,7 +17359,7 @@
       </c>
       <c r="X28" s="90"/>
       <c r="Y28" s="93"/>
-      <c r="Z28" s="155"/>
+      <c r="Z28" s="153"/>
     </row>
     <row r="29" spans="1:28" ht="15.75">
       <c r="A29" s="62">
@@ -17114,7 +17398,7 @@
       </c>
       <c r="X29" s="90"/>
       <c r="Y29" s="93"/>
-      <c r="Z29" s="155"/>
+      <c r="Z29" s="153"/>
     </row>
     <row r="30" spans="1:28" ht="15.75">
       <c r="A30" s="66">
@@ -17154,7 +17438,7 @@
       </c>
       <c r="X30" s="90"/>
       <c r="Y30" s="93"/>
-      <c r="Z30" s="155"/>
+      <c r="Z30" s="153"/>
     </row>
     <row r="31" spans="1:28" ht="15.75">
       <c r="A31" s="62">
@@ -17189,7 +17473,7 @@
       </c>
       <c r="X31" s="90"/>
       <c r="Y31" s="93"/>
-      <c r="Z31" s="155"/>
+      <c r="Z31" s="153"/>
     </row>
     <row r="32" spans="1:28" ht="15.75">
       <c r="A32" s="66">
@@ -17224,7 +17508,7 @@
       </c>
       <c r="X32" s="90"/>
       <c r="Y32" s="93"/>
-      <c r="Z32" s="155"/>
+      <c r="Z32" s="153"/>
     </row>
     <row r="33" spans="1:26" ht="15.75">
       <c r="A33" s="62">
@@ -17261,7 +17545,7 @@
       <c r="Y33" s="136">
         <v>10000</v>
       </c>
-      <c r="Z33" s="155"/>
+      <c r="Z33" s="153"/>
     </row>
     <row r="34" spans="1:26" ht="15.75">
       <c r="A34" s="66">
@@ -17300,7 +17584,7 @@
       </c>
       <c r="X34" s="90"/>
       <c r="Y34" s="93"/>
-      <c r="Z34" s="155"/>
+      <c r="Z34" s="153"/>
     </row>
     <row r="35" spans="1:26" ht="15.75">
       <c r="A35" s="62">
@@ -17344,7 +17628,7 @@
       </c>
       <c r="X35" s="90"/>
       <c r="Y35" s="93"/>
-      <c r="Z35" s="155"/>
+      <c r="Z35" s="153"/>
     </row>
     <row r="36" spans="1:26" ht="15.75">
       <c r="A36" s="66">
@@ -17385,7 +17669,7 @@
       </c>
       <c r="X36" s="90"/>
       <c r="Y36" s="93"/>
-      <c r="Z36" s="155"/>
+      <c r="Z36" s="153"/>
     </row>
     <row r="37" spans="1:26">
       <c r="A37" s="149" t="s">
@@ -17490,10 +17774,10 @@
       </c>
     </row>
     <row r="38" spans="1:26" ht="31.5" customHeight="1">
-      <c r="A38" s="154" t="s">
+      <c r="A38" s="152" t="s">
         <v>37</v>
       </c>
-      <c r="B38" s="154"/>
+      <c r="B38" s="152"/>
       <c r="C38" s="78">
         <f>SUM(C20,C37)</f>
         <v>14335.99</v>
@@ -17605,18 +17889,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="AC14:AF14"/>
+    <mergeCell ref="AC15:AF15"/>
+    <mergeCell ref="AC8:AG10"/>
+    <mergeCell ref="AC11:AF11"/>
+    <mergeCell ref="AC12:AF12"/>
+    <mergeCell ref="AC13:AF13"/>
     <mergeCell ref="A1:Z1"/>
     <mergeCell ref="A20:B20"/>
     <mergeCell ref="A37:B37"/>
     <mergeCell ref="A38:B38"/>
     <mergeCell ref="Z3:Z19"/>
     <mergeCell ref="Z21:Z36"/>
-    <mergeCell ref="AC14:AF14"/>
-    <mergeCell ref="AC15:AF15"/>
-    <mergeCell ref="AC8:AG10"/>
-    <mergeCell ref="AC11:AF11"/>
-    <mergeCell ref="AC12:AF12"/>
-    <mergeCell ref="AC13:AF13"/>
   </mergeCells>
   <conditionalFormatting sqref="Z20:Z21 Z37:Z38">
     <cfRule type="expression" dxfId="3" priority="1">
@@ -17634,7 +17918,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AZ41"/>
+  <dimension ref="A1:AZ40"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="30" width="20.7109375" style="2" customWidth="1"/>
@@ -18806,7 +19090,7 @@
       <c r="Z22" s="111"/>
       <c r="AA22" s="112"/>
       <c r="AB22" s="128">
-        <f t="shared" ref="AB22:AB35" si="2">SUM(C22:AA22)</f>
+        <f t="shared" ref="AB22:AB34" si="2">SUM(C22:AA22)</f>
         <v>0</v>
       </c>
       <c r="AC22" s="117"/>
@@ -18976,7 +19260,10 @@
       <c r="K26" s="111"/>
       <c r="L26" s="111"/>
       <c r="M26" s="111"/>
-      <c r="N26" s="111"/>
+      <c r="N26" s="111">
+        <f>249</f>
+        <v>249</v>
+      </c>
       <c r="O26" s="111"/>
       <c r="P26" s="111"/>
       <c r="Q26" s="111"/>
@@ -18985,14 +19272,19 @@
       <c r="T26" s="111"/>
       <c r="U26" s="111"/>
       <c r="V26" s="111"/>
-      <c r="W26" s="111"/>
-      <c r="X26" s="111"/>
+      <c r="W26" s="111">
+        <f>704+500+400</f>
+        <v>1604</v>
+      </c>
+      <c r="X26" s="111">
+        <v>950</v>
+      </c>
       <c r="Y26" s="111"/>
       <c r="Z26" s="111"/>
       <c r="AA26" s="112"/>
       <c r="AB26" s="128">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2803</v>
       </c>
       <c r="AC26" s="118"/>
       <c r="AD26" s="158"/>
@@ -19004,7 +19296,9 @@
       <c r="B27" s="106" t="s">
         <v>3</v>
       </c>
-      <c r="C27" s="107"/>
+      <c r="C27" s="107">
+        <v>149.96</v>
+      </c>
       <c r="D27" s="107"/>
       <c r="E27" s="107"/>
       <c r="F27" s="107"/>
@@ -19012,7 +19306,10 @@
       <c r="H27" s="107"/>
       <c r="I27" s="107"/>
       <c r="J27" s="107"/>
-      <c r="K27" s="107"/>
+      <c r="K27" s="107">
+        <f>1240</f>
+        <v>1240</v>
+      </c>
       <c r="L27" s="107"/>
       <c r="M27" s="107"/>
       <c r="N27" s="107"/>
@@ -19022,16 +19319,20 @@
       <c r="R27" s="107"/>
       <c r="S27" s="107"/>
       <c r="T27" s="107"/>
-      <c r="U27" s="107"/>
+      <c r="U27" s="107">
+        <v>313</v>
+      </c>
       <c r="V27" s="107"/>
       <c r="W27" s="107"/>
-      <c r="X27" s="107"/>
+      <c r="X27" s="107">
+        <v>386</v>
+      </c>
       <c r="Y27" s="107"/>
       <c r="Z27" s="107"/>
       <c r="AA27" s="108"/>
       <c r="AB27" s="128">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2088.96</v>
       </c>
       <c r="AC27" s="117"/>
       <c r="AD27" s="158"/>
@@ -19061,16 +19362,23 @@
       <c r="R28" s="111"/>
       <c r="S28" s="111"/>
       <c r="T28" s="111"/>
-      <c r="U28" s="111"/>
+      <c r="U28" s="111">
+        <v>288</v>
+      </c>
       <c r="V28" s="111"/>
-      <c r="W28" s="111"/>
+      <c r="W28" s="111">
+        <f>1180</f>
+        <v>1180</v>
+      </c>
       <c r="X28" s="111"/>
       <c r="Y28" s="111"/>
-      <c r="Z28" s="111"/>
+      <c r="Z28" s="111">
+        <v>2000</v>
+      </c>
       <c r="AA28" s="112"/>
       <c r="AB28" s="128">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3468</v>
       </c>
       <c r="AC28" s="117"/>
       <c r="AD28" s="158"/>
@@ -19082,14 +19390,23 @@
       <c r="B29" s="106" t="s">
         <v>5</v>
       </c>
-      <c r="C29" s="107"/>
-      <c r="D29" s="107"/>
+      <c r="C29" s="107">
+        <f>705.95</f>
+        <v>705.95</v>
+      </c>
+      <c r="D29" s="107">
+        <f>329.99+356.95+143.98</f>
+        <v>830.92000000000007</v>
+      </c>
       <c r="E29" s="107"/>
       <c r="F29" s="107"/>
       <c r="G29" s="107"/>
       <c r="H29" s="107"/>
       <c r="I29" s="107"/>
-      <c r="J29" s="107"/>
+      <c r="J29" s="107">
+        <f>841</f>
+        <v>841</v>
+      </c>
       <c r="K29" s="107"/>
       <c r="L29" s="107"/>
       <c r="M29" s="107"/>
@@ -19105,13 +19422,18 @@
       <c r="W29" s="107"/>
       <c r="X29" s="107"/>
       <c r="Y29" s="107"/>
-      <c r="Z29" s="107"/>
+      <c r="Z29" s="107">
+        <f>1580</f>
+        <v>1580</v>
+      </c>
       <c r="AA29" s="108"/>
       <c r="AB29" s="128">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AC29" s="117"/>
+        <v>3957.87</v>
+      </c>
+      <c r="AC29" s="117">
+        <v>1000</v>
+      </c>
       <c r="AD29" s="158"/>
     </row>
     <row r="30" spans="1:32" ht="15.75">
@@ -19128,11 +19450,17 @@
       <c r="G30" s="111"/>
       <c r="H30" s="111"/>
       <c r="I30" s="111"/>
-      <c r="J30" s="111"/>
+      <c r="J30" s="111">
+        <f>1510</f>
+        <v>1510</v>
+      </c>
       <c r="K30" s="111"/>
       <c r="L30" s="111"/>
       <c r="M30" s="111"/>
-      <c r="N30" s="111"/>
+      <c r="N30" s="111">
+        <f>799</f>
+        <v>799</v>
+      </c>
       <c r="O30" s="111"/>
       <c r="P30" s="111"/>
       <c r="Q30" s="111"/>
@@ -19140,7 +19468,10 @@
       <c r="S30" s="111"/>
       <c r="T30" s="111"/>
       <c r="U30" s="111"/>
-      <c r="V30" s="111"/>
+      <c r="V30" s="111">
+        <f>1707.5</f>
+        <v>1707.5</v>
+      </c>
       <c r="W30" s="111"/>
       <c r="X30" s="111"/>
       <c r="Y30" s="111"/>
@@ -19148,7 +19479,7 @@
       <c r="AA30" s="112"/>
       <c r="AB30" s="128">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>4016.5</v>
       </c>
       <c r="AC30" s="117"/>
       <c r="AD30" s="158"/>
@@ -19161,14 +19492,19 @@
         <v>7</v>
       </c>
       <c r="C31" s="107"/>
-      <c r="D31" s="107"/>
+      <c r="D31" s="107">
+        <v>131.78</v>
+      </c>
       <c r="E31" s="107"/>
       <c r="F31" s="107"/>
       <c r="G31" s="107"/>
       <c r="H31" s="107"/>
       <c r="I31" s="107"/>
       <c r="J31" s="107"/>
-      <c r="K31" s="107"/>
+      <c r="K31" s="107">
+        <f>2450+220</f>
+        <v>2670</v>
+      </c>
       <c r="L31" s="107"/>
       <c r="M31" s="107"/>
       <c r="N31" s="107"/>
@@ -19187,7 +19523,7 @@
       <c r="AA31" s="108"/>
       <c r="AB31" s="128">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2801.78</v>
       </c>
       <c r="AC31" s="117"/>
       <c r="AD31" s="158"/>
@@ -19202,12 +19538,17 @@
       <c r="C32" s="111"/>
       <c r="D32" s="111"/>
       <c r="E32" s="111"/>
-      <c r="F32" s="111"/>
+      <c r="F32" s="111">
+        <v>396</v>
+      </c>
       <c r="G32" s="111"/>
       <c r="H32" s="111"/>
       <c r="I32" s="111"/>
       <c r="J32" s="111"/>
-      <c r="K32" s="111"/>
+      <c r="K32" s="111">
+        <f>1870</f>
+        <v>1870</v>
+      </c>
       <c r="L32" s="111"/>
       <c r="M32" s="111"/>
       <c r="N32" s="111"/>
@@ -19218,15 +19559,20 @@
       <c r="S32" s="111"/>
       <c r="T32" s="111"/>
       <c r="U32" s="111"/>
-      <c r="V32" s="111"/>
-      <c r="W32" s="111"/>
+      <c r="V32" s="111">
+        <v>301.11</v>
+      </c>
+      <c r="W32" s="111">
+        <f>320+920</f>
+        <v>1240</v>
+      </c>
       <c r="X32" s="111"/>
       <c r="Y32" s="111"/>
       <c r="Z32" s="111"/>
       <c r="AA32" s="112"/>
       <c r="AB32" s="128">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3807.11</v>
       </c>
       <c r="AC32" s="117"/>
       <c r="AD32" s="158"/>
@@ -19249,7 +19595,9 @@
       <c r="K33" s="107"/>
       <c r="L33" s="107"/>
       <c r="M33" s="107"/>
-      <c r="N33" s="107"/>
+      <c r="N33" s="107">
+        <v>399</v>
+      </c>
       <c r="O33" s="107"/>
       <c r="P33" s="107"/>
       <c r="Q33" s="107"/>
@@ -19257,7 +19605,10 @@
       <c r="S33" s="107"/>
       <c r="T33" s="107"/>
       <c r="U33" s="107"/>
-      <c r="V33" s="107"/>
+      <c r="V33" s="107">
+        <f>276.44</f>
+        <v>276.44</v>
+      </c>
       <c r="W33" s="107"/>
       <c r="X33" s="107"/>
       <c r="Y33" s="107"/>
@@ -19265,7 +19616,7 @@
       <c r="AA33" s="108"/>
       <c r="AB33" s="128">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>675.44</v>
       </c>
       <c r="AC33" s="117"/>
       <c r="AD33" s="158"/>
@@ -19297,305 +19648,271 @@
       <c r="T34" s="111"/>
       <c r="U34" s="111"/>
       <c r="V34" s="111"/>
-      <c r="W34" s="111"/>
+      <c r="W34" s="111">
+        <f>1000+100-500</f>
+        <v>600</v>
+      </c>
       <c r="X34" s="111"/>
       <c r="Y34" s="111"/>
       <c r="Z34" s="111"/>
       <c r="AA34" s="112"/>
       <c r="AB34" s="128">
         <f t="shared" si="2"/>
+        <v>600</v>
+      </c>
+      <c r="AC34" s="137">
+        <v>1000</v>
+      </c>
+      <c r="AD34" s="158"/>
+    </row>
+    <row r="35" spans="1:30" ht="14.25" customHeight="1">
+      <c r="A35" s="159" t="s">
+        <v>36</v>
+      </c>
+      <c r="B35" s="159"/>
+      <c r="C35" s="113">
+        <f>SUM(C20:C34)</f>
+        <v>2169.6999999999998</v>
+      </c>
+      <c r="D35" s="113">
+        <f>SUM(D20:D34)</f>
+        <v>2676.8500000000004</v>
+      </c>
+      <c r="E35" s="113">
+        <f>SUM(E20:E34)</f>
         <v>0</v>
       </c>
-      <c r="AC34" s="117"/>
-      <c r="AD34" s="158"/>
-    </row>
-    <row r="35" spans="1:30" ht="15.75">
-      <c r="A35" s="105">
-        <v>4</v>
-      </c>
-      <c r="B35" s="106" t="s">
-        <v>4</v>
-      </c>
-      <c r="C35" s="107"/>
-      <c r="D35" s="107"/>
-      <c r="E35" s="107"/>
-      <c r="F35" s="107"/>
-      <c r="G35" s="107"/>
-      <c r="H35" s="107"/>
-      <c r="I35" s="107"/>
-      <c r="J35" s="107"/>
-      <c r="K35" s="107"/>
-      <c r="L35" s="107"/>
-      <c r="M35" s="107"/>
-      <c r="N35" s="107"/>
-      <c r="O35" s="107"/>
-      <c r="P35" s="107"/>
-      <c r="Q35" s="107"/>
-      <c r="R35" s="107"/>
-      <c r="S35" s="107"/>
-      <c r="T35" s="107"/>
-      <c r="U35" s="107"/>
-      <c r="V35" s="107"/>
-      <c r="W35" s="107"/>
-      <c r="X35" s="107"/>
-      <c r="Y35" s="107"/>
-      <c r="Z35" s="107"/>
-      <c r="AA35" s="108"/>
-      <c r="AB35" s="128">
-        <f t="shared" si="2"/>
+      <c r="F35" s="113">
+        <f>SUM(F20:F34)</f>
+        <v>500</v>
+      </c>
+      <c r="G35" s="113">
+        <f>SUM(G20:G34)</f>
         <v>0</v>
       </c>
-      <c r="AC35" s="117"/>
-      <c r="AD35" s="158"/>
-    </row>
-    <row r="36" spans="1:30" ht="14.25" customHeight="1">
-      <c r="A36" s="159" t="s">
-        <v>36</v>
-      </c>
-      <c r="B36" s="159"/>
-      <c r="C36" s="113">
-        <f>SUM(C20:C35)</f>
-        <v>1313.79</v>
-      </c>
-      <c r="D36" s="113">
-        <f t="shared" ref="D36:K36" si="3">SUM(D20:D35)</f>
-        <v>1714.15</v>
-      </c>
-      <c r="E36" s="113">
-        <f t="shared" si="3"/>
+      <c r="H35" s="113">
+        <f>SUM(H20:H34)</f>
+        <v>2450</v>
+      </c>
+      <c r="I35" s="113">
+        <f>SUM(I20:I34)</f>
+        <v>1910</v>
+      </c>
+      <c r="J35" s="113">
+        <f>SUM(J20:J34)</f>
+        <v>4099</v>
+      </c>
+      <c r="K35" s="113">
+        <f>SUM(K20:K34)</f>
+        <v>10406.200000000001</v>
+      </c>
+      <c r="L35" s="114">
+        <f>SUM(L20:L34)</f>
         <v>0</v>
       </c>
-      <c r="F36" s="113">
-        <f t="shared" si="3"/>
-        <v>104</v>
-      </c>
-      <c r="G36" s="113">
-        <f t="shared" si="3"/>
+      <c r="M35" s="114">
+        <f>SUM(M20:M34)</f>
         <v>0</v>
       </c>
-      <c r="H36" s="113">
-        <f t="shared" si="3"/>
-        <v>2450</v>
-      </c>
-      <c r="I36" s="113">
-        <f t="shared" si="3"/>
-        <v>1910</v>
-      </c>
-      <c r="J36" s="113">
-        <f t="shared" si="3"/>
-        <v>1748</v>
-      </c>
-      <c r="K36" s="113">
-        <f t="shared" si="3"/>
-        <v>4626.2</v>
-      </c>
-      <c r="L36" s="114">
-        <f>SUM(L20:L35)</f>
+      <c r="N35" s="114">
+        <f>SUM(N20:N34)</f>
+        <v>1447</v>
+      </c>
+      <c r="O35" s="114">
+        <f>SUM(O20:O34)</f>
         <v>0</v>
       </c>
-      <c r="M36" s="114">
-        <f t="shared" ref="M36:Q36" si="4">SUM(M20:M35)</f>
+      <c r="P35" s="114">
+        <f>SUM(P20:P34)</f>
         <v>0</v>
       </c>
-      <c r="N36" s="114">
-        <f t="shared" si="4"/>
+      <c r="Q35" s="114">
+        <f>SUM(Q20:Q34)</f>
         <v>0</v>
       </c>
-      <c r="O36" s="114">
-        <f t="shared" si="4"/>
+      <c r="R35" s="115">
+        <f>SUM(R20:R34)</f>
+        <v>1798.27</v>
+      </c>
+      <c r="S35" s="115">
+        <f>SUM(S20:S34)</f>
         <v>0</v>
       </c>
-      <c r="P36" s="114">
-        <f t="shared" si="4"/>
+      <c r="T35" s="115">
+        <f>SUM(T20:T34)</f>
         <v>0</v>
       </c>
-      <c r="Q36" s="114">
-        <f t="shared" si="4"/>
+      <c r="U35" s="115">
+        <f>SUM(U20:U34)</f>
+        <v>1155</v>
+      </c>
+      <c r="V35" s="115">
+        <f>SUM(V20:V34)</f>
+        <v>4095.69</v>
+      </c>
+      <c r="W35" s="115">
+        <f>SUM(W20:W34)</f>
+        <v>16453</v>
+      </c>
+      <c r="X35" s="115">
+        <f>SUM(X20:X34)</f>
+        <v>1336</v>
+      </c>
+      <c r="Y35" s="115">
+        <f>SUM(Y20:Y34)</f>
         <v>0</v>
       </c>
-      <c r="R36" s="115">
-        <f>SUM(R20:R35)</f>
+      <c r="Z35" s="115">
+        <f>SUM(Z20:Z34)</f>
+        <v>3580</v>
+      </c>
+      <c r="AA35" s="124">
+        <f>SUM(AA20:AA34)</f>
+        <v>0</v>
+      </c>
+      <c r="AB35" s="129">
+        <f>SUM(AB20:AB34)</f>
+        <v>54076.710000000006</v>
+      </c>
+      <c r="AC35" s="130">
+        <f>SUM(AC20:AC34)</f>
+        <v>48738.04</v>
+      </c>
+      <c r="AD35" s="133">
+        <f>AC35-AB35</f>
+        <v>-5338.6700000000055</v>
+      </c>
+    </row>
+    <row r="36" spans="1:30" ht="31.5" customHeight="1">
+      <c r="A36" s="156" t="s">
+        <v>37</v>
+      </c>
+      <c r="B36" s="156"/>
+      <c r="C36" s="116">
+        <f>SUM(C19,C35)</f>
+        <v>3573.59</v>
+      </c>
+      <c r="D36" s="116"/>
+      <c r="E36" s="116"/>
+      <c r="F36" s="116">
+        <f>SUM(F19,F35)</f>
+        <v>2946</v>
+      </c>
+      <c r="G36" s="116"/>
+      <c r="H36" s="116">
+        <f>SUM(H19,H35)</f>
+        <v>6920</v>
+      </c>
+      <c r="I36" s="116">
+        <f>SUM(I19,I35)</f>
+        <v>14025</v>
+      </c>
+      <c r="J36" s="116">
+        <f>SUM(J19,J35)</f>
+        <v>9158.98</v>
+      </c>
+      <c r="K36" s="116">
+        <f>SUM(K19,K35)</f>
+        <v>12686.2</v>
+      </c>
+      <c r="L36" s="116">
+        <f>SUM(L19,L35)</f>
+        <v>10858.130000000001</v>
+      </c>
+      <c r="M36" s="116">
+        <f>SUM(M19,M35)</f>
+        <v>0</v>
+      </c>
+      <c r="N36" s="116">
+        <f>SUM(N19,N35)</f>
+        <v>4336</v>
+      </c>
+      <c r="O36" s="116"/>
+      <c r="P36" s="116"/>
+      <c r="Q36" s="116"/>
+      <c r="R36" s="116">
+        <f>SUM(R19,R35)</f>
         <v>1798.27</v>
       </c>
-      <c r="S36" s="115">
-        <f t="shared" ref="S36:AA36" si="5">SUM(S20:S35)</f>
+      <c r="S36" s="116"/>
+      <c r="T36" s="116">
+        <f>SUM(T19,T35)</f>
         <v>0</v>
       </c>
-      <c r="T36" s="115">
-        <f t="shared" si="5"/>
+      <c r="U36" s="116">
+        <f>SUM(U19,U35)</f>
+        <v>4111</v>
+      </c>
+      <c r="V36" s="116">
+        <f>SUM(V19,V35)</f>
+        <v>6897.4600000000009</v>
+      </c>
+      <c r="W36" s="116">
+        <f>SUM(W19,W35)</f>
+        <v>35678.97</v>
+      </c>
+      <c r="X36" s="116">
+        <f>SUM(X19,X35)</f>
+        <v>5267.98</v>
+      </c>
+      <c r="Y36" s="116">
+        <f>SUM(Y19,Y35)</f>
         <v>0</v>
       </c>
-      <c r="U36" s="115">
-        <f t="shared" si="5"/>
-        <v>554</v>
-      </c>
-      <c r="V36" s="115">
-        <f t="shared" si="5"/>
-        <v>1810.6399999999999</v>
-      </c>
-      <c r="W36" s="115">
-        <f t="shared" si="5"/>
-        <v>11829</v>
-      </c>
-      <c r="X36" s="115">
-        <f t="shared" si="5"/>
+      <c r="Z36" s="116">
+        <f>SUM(Z19,Z35)</f>
+        <v>4386</v>
+      </c>
+      <c r="AA36" s="125">
+        <f>SUM(AA19,AA35)</f>
         <v>0</v>
       </c>
-      <c r="Y36" s="115">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="Z36" s="115">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AA36" s="124">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AB36" s="129">
-        <f>SUM(AB20:AB35)</f>
-        <v>29858.050000000003</v>
-      </c>
-      <c r="AC36" s="130">
-        <f>SUM(AC20:AC35)</f>
-        <v>46738.04</v>
-      </c>
-      <c r="AD36" s="133">
-        <f>AC36-AB36</f>
-        <v>16879.989999999998</v>
-      </c>
-    </row>
-    <row r="37" spans="1:30" ht="31.5" customHeight="1">
-      <c r="A37" s="156" t="s">
-        <v>37</v>
-      </c>
-      <c r="B37" s="156"/>
-      <c r="C37" s="116">
-        <f>SUM(C19,C36)</f>
-        <v>2717.6800000000003</v>
-      </c>
-      <c r="D37" s="116"/>
-      <c r="E37" s="116"/>
-      <c r="F37" s="116">
-        <f t="shared" ref="F37:AB37" si="6">SUM(F19,F36)</f>
-        <v>2550</v>
-      </c>
-      <c r="G37" s="116"/>
-      <c r="H37" s="116">
-        <f t="shared" si="6"/>
-        <v>6920</v>
-      </c>
-      <c r="I37" s="116">
-        <f t="shared" si="6"/>
-        <v>14025</v>
-      </c>
-      <c r="J37" s="116">
-        <f t="shared" si="6"/>
-        <v>6807.98</v>
-      </c>
-      <c r="K37" s="116">
-        <f t="shared" si="6"/>
-        <v>6906.2</v>
-      </c>
-      <c r="L37" s="116">
-        <f t="shared" si="6"/>
-        <v>10858.130000000001</v>
-      </c>
-      <c r="M37" s="116">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="N37" s="116">
-        <f t="shared" si="6"/>
-        <v>2889</v>
-      </c>
-      <c r="O37" s="116"/>
-      <c r="P37" s="116"/>
-      <c r="Q37" s="116"/>
-      <c r="R37" s="116">
-        <f t="shared" si="6"/>
-        <v>1798.27</v>
-      </c>
-      <c r="S37" s="116"/>
-      <c r="T37" s="116">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="U37" s="116">
-        <f t="shared" si="6"/>
-        <v>3510</v>
-      </c>
-      <c r="V37" s="116">
-        <f t="shared" si="6"/>
-        <v>4612.41</v>
-      </c>
-      <c r="W37" s="116">
-        <f t="shared" si="6"/>
-        <v>31054.97</v>
-      </c>
-      <c r="X37" s="116">
-        <f t="shared" si="6"/>
-        <v>3931.98</v>
-      </c>
-      <c r="Y37" s="116">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Z37" s="116">
-        <f>SUM(Z19,Z36)</f>
-        <v>806</v>
-      </c>
-      <c r="AA37" s="125">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="AB37" s="131">
-        <f t="shared" si="6"/>
-        <v>122283.07</v>
-      </c>
-      <c r="AC37" s="132">
-        <f>SUM(AC19,AC36)</f>
-        <v>143443.15000000002</v>
-      </c>
-      <c r="AD37" s="134">
-        <f>SUM(AD19,AD36)</f>
-        <v>21160.080000000009</v>
-      </c>
-    </row>
-    <row r="41" spans="1:30">
-      <c r="B41" s="6"/>
-      <c r="C41" s="6"/>
-      <c r="D41" s="6"/>
-      <c r="E41" s="6"/>
-      <c r="F41" s="6"/>
-      <c r="G41" s="6"/>
-      <c r="H41" s="6"/>
-      <c r="I41" s="6"/>
-      <c r="J41" s="6"/>
-      <c r="K41" s="6"/>
-      <c r="L41" s="6"/>
-      <c r="M41" s="6"/>
-      <c r="N41" s="6"/>
-      <c r="O41" s="6"/>
-      <c r="P41" s="6"/>
-      <c r="Q41" s="6"/>
+      <c r="AB36" s="131">
+        <f>SUM(AB19,AB35)</f>
+        <v>146501.73000000001</v>
+      </c>
+      <c r="AC36" s="132">
+        <f>SUM(AC19,AC35)</f>
+        <v>145443.15000000002</v>
+      </c>
+      <c r="AD36" s="134">
+        <f>SUM(AD19,AD35)</f>
+        <v>-1058.5799999999945</v>
+      </c>
+    </row>
+    <row r="40" spans="1:30">
+      <c r="B40" s="6"/>
+      <c r="C40" s="6"/>
+      <c r="D40" s="6"/>
+      <c r="E40" s="6"/>
+      <c r="F40" s="6"/>
+      <c r="G40" s="6"/>
+      <c r="H40" s="6"/>
+      <c r="I40" s="6"/>
+      <c r="J40" s="6"/>
+      <c r="K40" s="6"/>
+      <c r="L40" s="6"/>
+      <c r="M40" s="6"/>
+      <c r="N40" s="6"/>
+      <c r="O40" s="6"/>
+      <c r="P40" s="6"/>
+      <c r="Q40" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="A36:B36"/>
     <mergeCell ref="A1:AD1"/>
     <mergeCell ref="AD4:AD18"/>
     <mergeCell ref="A19:B19"/>
-    <mergeCell ref="AD20:AD35"/>
-    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="AD20:AD34"/>
+    <mergeCell ref="A35:B35"/>
     <mergeCell ref="C2:K2"/>
     <mergeCell ref="L2:Q2"/>
     <mergeCell ref="R2:AA2"/>
     <mergeCell ref="AB2:AD2"/>
     <mergeCell ref="A2:B2"/>
   </mergeCells>
-  <conditionalFormatting sqref="AD19:AD20 AD36:AD37">
+  <conditionalFormatting sqref="AD35:AD36 AD19:AD20">
     <cfRule type="expression" dxfId="1" priority="1">
       <formula>AD19&lt;0</formula>
     </cfRule>
